--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="176">
   <si>
     <r>
       <rPr>
@@ -3513,7 +3513,13 @@
     <t xml:space="preserve">하</t>
   </si>
   <si>
+    <t xml:space="preserve">중하</t>
+  </si>
+  <si>
     <t xml:space="preserve">중</t>
+  </si>
+  <si>
+    <t xml:space="preserve">중상</t>
   </si>
   <si>
     <t xml:space="preserve">상</t>
@@ -5830,7 +5836,7 @@
       </c>
       <c r="D19" s="10" t="n">
         <f aca="false">SUMIF(공수1!$D$4:$W$4,B19,공수1!$D$3:$W$3)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>31</v>
@@ -5849,7 +5855,7 @@
       </c>
       <c r="D20" s="10" t="n">
         <f aca="false">SUMIF(공수1!$D$4:$W$4,B20,공수1!$D$3:$W$3)</f>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>33</v>
@@ -5887,7 +5893,7 @@
       </c>
       <c r="D22" s="10" t="n">
         <f aca="false">SUMIF(공수1!$D$4:$W$4,B22,공수1!$D$3:$W$3)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>37</v>
@@ -5925,7 +5931,7 @@
       </c>
       <c r="D24" s="10" t="n">
         <f aca="false">SUMIF(공수2!$D$4:$W$4,B24,공수2!$D$3:$W$3)</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>42</v>
@@ -5963,7 +5969,7 @@
       </c>
       <c r="D26" s="10" t="n">
         <f aca="false">SUMIF(공수2!$D$4:$W$4,B26,공수2!$D$3:$W$3)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>46</v>
@@ -7414,13 +7420,13 @@
         <v>3</v>
       </c>
       <c r="G3" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" s="20" t="n">
         <v>5</v>
@@ -7429,7 +7435,7 @@
         <v>5</v>
       </c>
       <c r="L3" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3" s="20" t="n">
         <v>6</v>
@@ -7438,19 +7444,19 @@
         <v>6</v>
       </c>
       <c r="O3" s="20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P3" s="20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q3" s="20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R3" s="20" t="n">
         <v>3</v>
       </c>
       <c r="S3" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" s="20" t="n">
         <v>5</v>
@@ -7474,11 +7480,11 @@
       </c>
       <c r="Z3" s="18" t="n">
         <f aca="false">SUMIF($D$4:$W$4,Z$6,$D$3:$W$3)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA3" s="18" t="n">
         <f aca="false">SUMIF($D$4:$W$4,AA$6,$D$3:$W$3)</f>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AB3" s="18" t="n">
         <f aca="false">SUMIF($D$4:$W$4,AB$6,$D$3:$W$3)</f>
@@ -7486,7 +7492,7 @@
       </c>
       <c r="AC3" s="18" t="n">
         <f aca="false">SUMIF($D$4:$W$4,AC$6,$D$3:$W$3)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7572,7 +7578,7 @@
         <v>101</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>102</v>
@@ -7581,64 +7587,64 @@
         <v>102</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>103</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="R5" s="6" t="s">
         <v>101</v>
       </c>
       <c r="S5" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T5" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U5" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V5" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W5" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="X5" s="27" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Y5" s="27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Z5" s="27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AA5" s="27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AB5" s="27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AC5" s="27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7652,70 +7658,70 @@
         <v>84</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K6" s="28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L6" s="28" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="M6" s="28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N6" s="28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="O6" s="28" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="P6" s="28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q6" s="28" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R6" s="29" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="S6" s="29" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="T6" s="29" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="U6" s="29" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V6" s="29" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W6" s="29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Z6" s="30" t="str">
         <f aca="false">설정!B19</f>
@@ -12314,14 +12320,6 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:W4" type="list">
-      <formula1>설정!$B$19:$B$22</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:W5" type="list">
-      <formula1>"하,중,상,최상"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="객관식은 1~5 사이 정수만 입력" errorStyle="stop" errorTitle="입력 오류" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:Q2 D7:Q86" type="whole">
       <formula1>1</formula1>
       <formula2>5</formula2>
@@ -12329,6 +12327,14 @@
     <dataValidation allowBlank="true" error="단답형은 0~999 사이 정수만 입력" errorStyle="stop" errorTitle="입력 오류" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R2:W2 R7:W86" type="whole">
       <formula1>0</formula1>
       <formula2>999</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:W4" type="list">
+      <formula1>설정!$B$19:$B$22</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:W5" type="list">
+      <formula1>"하,중하,중,중상,상,최상"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -12360,7 +12366,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12475,13 +12481,13 @@
         <v>3</v>
       </c>
       <c r="G3" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" s="20" t="n">
         <v>5</v>
@@ -12490,7 +12496,7 @@
         <v>5</v>
       </c>
       <c r="L3" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3" s="20" t="n">
         <v>6</v>
@@ -12499,19 +12505,19 @@
         <v>6</v>
       </c>
       <c r="O3" s="20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P3" s="20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q3" s="20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R3" s="20" t="n">
         <v>3</v>
       </c>
       <c r="S3" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" s="20" t="n">
         <v>5</v>
@@ -12535,7 +12541,7 @@
       </c>
       <c r="Z3" s="18" t="n">
         <f aca="false">SUMIF($D$4:$W$4,Z$6,$D$3:$W$3)</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA3" s="18" t="n">
         <f aca="false">SUMIF($D$4:$W$4,AA$6,$D$3:$W$3)</f>
@@ -12543,7 +12549,7 @@
       </c>
       <c r="AB3" s="18" t="n">
         <f aca="false">SUMIF($D$4:$W$4,AB$6,$D$3:$W$3)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12629,7 +12635,7 @@
         <v>101</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>102</v>
@@ -12638,61 +12644,61 @@
         <v>102</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>103</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="R5" s="6" t="s">
         <v>101</v>
       </c>
       <c r="S5" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T5" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U5" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V5" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W5" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="X5" s="27" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Y5" s="27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Z5" s="27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AA5" s="27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AB5" s="27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12706,70 +12712,70 @@
         <v>84</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K6" s="28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L6" s="28" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="M6" s="28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N6" s="28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="O6" s="28" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="P6" s="28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q6" s="28" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R6" s="29" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="S6" s="29" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="T6" s="29" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="U6" s="29" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V6" s="29" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W6" s="29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Z6" s="30" t="str">
         <f aca="false">설정!B24</f>
@@ -17044,6 +17050,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:W4" type="list">
+      <formula1>설정!$B$24:$B$26</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:W5" type="list">
+      <formula1>"하,중하,중,중상,상,최상"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="객관식은 1~5 사이 정수만 입력" errorStyle="stop" errorTitle="입력 오류" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:Q2 D7:Q86" type="whole">
       <formula1>1</formula1>
       <formula2>5</formula2>
@@ -17051,14 +17065,6 @@
     <dataValidation allowBlank="true" error="단답형은 0~999 사이 정수만 입력" errorStyle="stop" errorTitle="입력 오류" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R2:W2 R7:W86" type="whole">
       <formula1>0</formula1>
       <formula2>999</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:W4" type="list">
-      <formula1>설정!$B$24:$B$26</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:W5" type="list">
-      <formula1>"하,중,상,최상"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -17096,7 +17102,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -17121,7 +17127,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -17146,7 +17152,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P5" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17163,55 +17169,55 @@
         <v>85</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="W6" s="4" t="s">
         <v>91</v>
@@ -17665,7 +17671,7 @@
         <v/>
       </c>
       <c r="P12" s="22" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q12" s="22"/>
       <c r="R12" s="22"/>
@@ -21745,7 +21751,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -21759,7 +21765,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -21773,7 +21779,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>83</v>
@@ -21785,22 +21791,22 @@
         <v>85</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H6" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="J6" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25852,7 +25858,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -25874,7 +25880,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -25896,7 +25902,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="42" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B4" s="42"/>
       <c r="C4" s="42"/>
@@ -25905,31 +25911,31 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J5" s="4" t="str">
         <f aca="false">설정!$B$6&amp;" 정답률"</f>
@@ -25944,25 +25950,25 @@
         <v>기본반 정답률</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O5" s="19" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P5" s="19" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q5" s="19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="R5" s="19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="S5" s="19" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25970,7 +25976,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C6" s="43" t="str">
         <f aca="false">공수1!D4</f>
@@ -26046,7 +26052,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C7" s="43" t="str">
         <f aca="false">공수1!E4</f>
@@ -26122,7 +26128,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C8" s="43" t="str">
         <f aca="false">공수1!F4</f>
@@ -26198,7 +26204,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C9" s="43" t="str">
         <f aca="false">공수1!G4</f>
@@ -26206,11 +26212,11 @@
       </c>
       <c r="D9" s="10" t="str">
         <f aca="false">공수1!G5</f>
-        <v>하</v>
+        <v>중하</v>
       </c>
       <c r="E9" s="10" t="n">
         <f aca="false">공수1!G3</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="44" t="n">
         <f aca="false">IF(공수1!$G$2="","",공수1!$G$2)</f>
@@ -26274,7 +26280,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C10" s="43" t="str">
         <f aca="false">공수1!H4</f>
@@ -26282,11 +26288,11 @@
       </c>
       <c r="D10" s="10" t="str">
         <f aca="false">공수1!H5</f>
-        <v>중</v>
+        <v>중하</v>
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">공수1!H3</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10" s="44" t="n">
         <f aca="false">IF(공수1!$H$2="","",공수1!$H$2)</f>
@@ -26350,7 +26356,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C11" s="43" t="str">
         <f aca="false">공수1!I4</f>
@@ -26358,11 +26364,11 @@
       </c>
       <c r="D11" s="10" t="str">
         <f aca="false">공수1!I5</f>
-        <v>중</v>
+        <v>중하</v>
       </c>
       <c r="E11" s="10" t="n">
         <f aca="false">공수1!I3</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="44" t="n">
         <f aca="false">IF(공수1!$I$2="","",공수1!$I$2)</f>
@@ -26426,7 +26432,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C12" s="43" t="str">
         <f aca="false">공수1!J4</f>
@@ -26502,7 +26508,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C13" s="43" t="str">
         <f aca="false">공수1!K4</f>
@@ -26578,7 +26584,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C14" s="43" t="str">
         <f aca="false">공수1!L4</f>
@@ -26586,11 +26592,11 @@
       </c>
       <c r="D14" s="10" t="str">
         <f aca="false">공수1!L5</f>
-        <v>상</v>
+        <v>중</v>
       </c>
       <c r="E14" s="10" t="n">
         <f aca="false">공수1!L3</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" s="44" t="n">
         <f aca="false">IF(공수1!$L$2="","",공수1!$L$2)</f>
@@ -26654,7 +26660,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C15" s="43" t="str">
         <f aca="false">공수1!M4</f>
@@ -26662,7 +26668,7 @@
       </c>
       <c r="D15" s="10" t="str">
         <f aca="false">공수1!M5</f>
-        <v>상</v>
+        <v>중상</v>
       </c>
       <c r="E15" s="10" t="n">
         <f aca="false">공수1!M3</f>
@@ -26730,7 +26736,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C16" s="43" t="str">
         <f aca="false">공수1!N4</f>
@@ -26738,7 +26744,7 @@
       </c>
       <c r="D16" s="10" t="str">
         <f aca="false">공수1!N5</f>
-        <v>상</v>
+        <v>중상</v>
       </c>
       <c r="E16" s="10" t="n">
         <f aca="false">공수1!N3</f>
@@ -26806,7 +26812,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C17" s="43" t="str">
         <f aca="false">공수1!O4</f>
@@ -26818,7 +26824,7 @@
       </c>
       <c r="E17" s="10" t="n">
         <f aca="false">공수1!O3</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" s="44" t="n">
         <f aca="false">IF(공수1!$O$2="","",공수1!$O$2)</f>
@@ -26882,7 +26888,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C18" s="43" t="str">
         <f aca="false">공수1!P4</f>
@@ -26894,7 +26900,7 @@
       </c>
       <c r="E18" s="10" t="n">
         <f aca="false">공수1!P3</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" s="44" t="n">
         <f aca="false">IF(공수1!$P$2="","",공수1!$P$2)</f>
@@ -26958,7 +26964,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C19" s="43" t="str">
         <f aca="false">공수1!Q4</f>
@@ -26970,7 +26976,7 @@
       </c>
       <c r="E19" s="10" t="n">
         <f aca="false">공수1!Q3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" s="44" t="n">
         <f aca="false">IF(공수1!$Q$2="","",공수1!$Q$2)</f>
@@ -27034,7 +27040,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C20" s="43" t="str">
         <f aca="false">공수1!R4</f>
@@ -27085,19 +27091,19 @@
         <v/>
       </c>
       <c r="O20" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P20" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q20" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R20" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S20" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27105,7 +27111,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C21" s="43" t="str">
         <f aca="false">공수1!S4</f>
@@ -27113,11 +27119,11 @@
       </c>
       <c r="D21" s="10" t="str">
         <f aca="false">공수1!S5</f>
-        <v>하</v>
+        <v>중하</v>
       </c>
       <c r="E21" s="10" t="n">
         <f aca="false">공수1!S3</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" s="44" t="n">
         <f aca="false">IF(공수1!$S$2="","",공수1!$S$2)</f>
@@ -27156,19 +27162,19 @@
         <v/>
       </c>
       <c r="O21" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P21" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q21" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R21" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S21" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27176,7 +27182,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C22" s="43" t="str">
         <f aca="false">공수1!T4</f>
@@ -27227,19 +27233,19 @@
         <v/>
       </c>
       <c r="O22" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P22" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q22" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R22" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S22" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27247,7 +27253,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C23" s="43" t="str">
         <f aca="false">공수1!U4</f>
@@ -27298,19 +27304,19 @@
         <v/>
       </c>
       <c r="O23" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P23" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q23" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R23" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S23" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27318,7 +27324,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C24" s="43" t="str">
         <f aca="false">공수1!V4</f>
@@ -27326,7 +27332,7 @@
       </c>
       <c r="D24" s="10" t="str">
         <f aca="false">공수1!V5</f>
-        <v>상</v>
+        <v>중상</v>
       </c>
       <c r="E24" s="10" t="n">
         <f aca="false">공수1!V3</f>
@@ -27369,19 +27375,19 @@
         <v/>
       </c>
       <c r="O24" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P24" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q24" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R24" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S24" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27389,7 +27395,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C25" s="43" t="str">
         <f aca="false">공수1!W4</f>
@@ -27440,24 +27446,24 @@
         <v/>
       </c>
       <c r="O25" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P25" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q25" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R25" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S25" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="42" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="42"/>
@@ -27466,31 +27472,31 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J29" s="4" t="str">
         <f aca="false">설정!$B$6&amp;" 정답률"</f>
@@ -27505,25 +27511,25 @@
         <v>기본반 정답률</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O29" s="19" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P29" s="19" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q29" s="19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="R29" s="19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="S29" s="19" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27531,7 +27537,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C30" s="43" t="str">
         <f aca="false">공수2!D4</f>
@@ -27607,7 +27613,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C31" s="43" t="str">
         <f aca="false">공수2!E4</f>
@@ -27683,7 +27689,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C32" s="43" t="str">
         <f aca="false">공수2!F4</f>
@@ -27759,7 +27765,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C33" s="43" t="str">
         <f aca="false">공수2!G4</f>
@@ -27767,11 +27773,11 @@
       </c>
       <c r="D33" s="10" t="str">
         <f aca="false">공수2!G5</f>
-        <v>하</v>
+        <v>중하</v>
       </c>
       <c r="E33" s="10" t="n">
         <f aca="false">공수2!G3</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" s="44" t="n">
         <f aca="false">IF(공수2!$G$2="","",공수2!$G$2)</f>
@@ -27835,7 +27841,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C34" s="43" t="str">
         <f aca="false">공수2!H4</f>
@@ -27843,11 +27849,11 @@
       </c>
       <c r="D34" s="10" t="str">
         <f aca="false">공수2!H5</f>
-        <v>중</v>
+        <v>중하</v>
       </c>
       <c r="E34" s="10" t="n">
         <f aca="false">공수2!H3</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F34" s="44" t="n">
         <f aca="false">IF(공수2!$H$2="","",공수2!$H$2)</f>
@@ -27911,7 +27917,7 @@
         <v>6</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C35" s="43" t="str">
         <f aca="false">공수2!I4</f>
@@ -27919,11 +27925,11 @@
       </c>
       <c r="D35" s="10" t="str">
         <f aca="false">공수2!I5</f>
-        <v>중</v>
+        <v>중하</v>
       </c>
       <c r="E35" s="10" t="n">
         <f aca="false">공수2!I3</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F35" s="44" t="n">
         <f aca="false">IF(공수2!$I$2="","",공수2!$I$2)</f>
@@ -27987,7 +27993,7 @@
         <v>7</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C36" s="43" t="str">
         <f aca="false">공수2!J4</f>
@@ -28063,7 +28069,7 @@
         <v>8</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C37" s="43" t="str">
         <f aca="false">공수2!K4</f>
@@ -28139,7 +28145,7 @@
         <v>9</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C38" s="43" t="str">
         <f aca="false">공수2!L4</f>
@@ -28147,11 +28153,11 @@
       </c>
       <c r="D38" s="10" t="str">
         <f aca="false">공수2!L5</f>
-        <v>상</v>
+        <v>중</v>
       </c>
       <c r="E38" s="10" t="n">
         <f aca="false">공수2!L3</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F38" s="44" t="n">
         <f aca="false">IF(공수2!$L$2="","",공수2!$L$2)</f>
@@ -28215,7 +28221,7 @@
         <v>10</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C39" s="43" t="str">
         <f aca="false">공수2!M4</f>
@@ -28223,7 +28229,7 @@
       </c>
       <c r="D39" s="10" t="str">
         <f aca="false">공수2!M5</f>
-        <v>상</v>
+        <v>중상</v>
       </c>
       <c r="E39" s="10" t="n">
         <f aca="false">공수2!M3</f>
@@ -28291,7 +28297,7 @@
         <v>11</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C40" s="43" t="str">
         <f aca="false">공수2!N4</f>
@@ -28299,7 +28305,7 @@
       </c>
       <c r="D40" s="10" t="str">
         <f aca="false">공수2!N5</f>
-        <v>상</v>
+        <v>중상</v>
       </c>
       <c r="E40" s="10" t="n">
         <f aca="false">공수2!N3</f>
@@ -28367,7 +28373,7 @@
         <v>12</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C41" s="43" t="str">
         <f aca="false">공수2!O4</f>
@@ -28379,7 +28385,7 @@
       </c>
       <c r="E41" s="10" t="n">
         <f aca="false">공수2!O3</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F41" s="44" t="n">
         <f aca="false">IF(공수2!$O$2="","",공수2!$O$2)</f>
@@ -28443,7 +28449,7 @@
         <v>13</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C42" s="43" t="str">
         <f aca="false">공수2!P4</f>
@@ -28455,7 +28461,7 @@
       </c>
       <c r="E42" s="10" t="n">
         <f aca="false">공수2!P3</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F42" s="44" t="n">
         <f aca="false">IF(공수2!$P$2="","",공수2!$P$2)</f>
@@ -28519,7 +28525,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C43" s="43" t="str">
         <f aca="false">공수2!Q4</f>
@@ -28531,7 +28537,7 @@
       </c>
       <c r="E43" s="10" t="n">
         <f aca="false">공수2!Q3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F43" s="44" t="n">
         <f aca="false">IF(공수2!$Q$2="","",공수2!$Q$2)</f>
@@ -28595,7 +28601,7 @@
         <v>15</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C44" s="43" t="str">
         <f aca="false">공수2!R4</f>
@@ -28646,19 +28652,19 @@
         <v/>
       </c>
       <c r="O44" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P44" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q44" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R44" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S44" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28666,7 +28672,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C45" s="43" t="str">
         <f aca="false">공수2!S4</f>
@@ -28674,11 +28680,11 @@
       </c>
       <c r="D45" s="10" t="str">
         <f aca="false">공수2!S5</f>
-        <v>하</v>
+        <v>중하</v>
       </c>
       <c r="E45" s="10" t="n">
         <f aca="false">공수2!S3</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" s="44" t="n">
         <f aca="false">IF(공수2!$S$2="","",공수2!$S$2)</f>
@@ -28717,19 +28723,19 @@
         <v/>
       </c>
       <c r="O45" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P45" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q45" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R45" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S45" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28737,7 +28743,7 @@
         <v>17</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C46" s="43" t="str">
         <f aca="false">공수2!T4</f>
@@ -28788,19 +28794,19 @@
         <v/>
       </c>
       <c r="O46" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P46" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R46" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S46" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28808,7 +28814,7 @@
         <v>18</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C47" s="43" t="str">
         <f aca="false">공수2!U4</f>
@@ -28859,19 +28865,19 @@
         <v/>
       </c>
       <c r="O47" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P47" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R47" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S47" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28879,7 +28885,7 @@
         <v>19</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C48" s="43" t="str">
         <f aca="false">공수2!V4</f>
@@ -28887,7 +28893,7 @@
       </c>
       <c r="D48" s="10" t="str">
         <f aca="false">공수2!V5</f>
-        <v>상</v>
+        <v>중상</v>
       </c>
       <c r="E48" s="10" t="n">
         <f aca="false">공수2!V3</f>
@@ -28930,19 +28936,19 @@
         <v/>
       </c>
       <c r="O48" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P48" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q48" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R48" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S48" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28950,7 +28956,7 @@
         <v>20</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C49" s="43" t="str">
         <f aca="false">공수2!W4</f>
@@ -29001,19 +29007,19 @@
         <v/>
       </c>
       <c r="O49" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P49" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q49" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R49" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S49" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="179">
   <si>
     <r>
       <rPr>
@@ -2799,6 +2799,287 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">무리함수의 그래프를 직접 그려 보는 학습이 필요합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">⑥ 반 소개 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">학부모 보고서의 추천 반 아래 문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">소개 문구</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공통수학</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1·2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모두 탄탄한 기초를 갖춘 학생을 위한 반으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개념 심화와 고난도 문항 해결력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내신 상위권 대비까지 진행합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공통수학</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 강점을 살리면서 공통수학</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 개념을 처음부터 체계적으로 다져</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">두 과목의 균형을 맞추는 반입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중등 연계 개념부터 차근차근 점검하며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공통수학</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1·2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 핵심 개념과 기본 유형을 확실히 완성하는 반입니다</t>
     </r>
     <r>
       <rPr>
@@ -4103,6 +4384,25 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최종반이 학부모 보고서의 추천 반으로 들어갑니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -5700,7 +6000,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -6304,8 +6604,60 @@
       <c r="D51" s="20"/>
       <c r="E51" s="20"/>
     </row>
+    <row r="53" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="9" t="str">
+        <f aca="false">B6</f>
+        <v>TF1반</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" s="20"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+    </row>
+    <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="9" t="str">
+        <f aca="false">B7</f>
+        <v>TF2반</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+    </row>
+    <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="9" t="str">
+        <f aca="false">B8</f>
+        <v>TF3반</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C57" s="20"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="26">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="H5:L9"/>
@@ -6328,6 +6680,10 @@
     <mergeCell ref="B49:E49"/>
     <mergeCell ref="B50:E50"/>
     <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B57:E57"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B35" type="list">
@@ -6362,7 +6718,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6372,7 +6728,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6382,22 +6738,22 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6405,19 +6761,19 @@
         <v>1</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7250,12 +7606,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="5" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
@@ -7285,7 +7641,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -7352,7 +7708,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B3" s="26"/>
       <c r="C3" s="26"/>
@@ -7443,7 +7799,7 @@
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
@@ -7510,164 +7866,164 @@
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B5" s="26"/>
       <c r="C5" s="26"/>
       <c r="D5" s="14" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="Q5" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="R5" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="R5" s="14" t="s">
-        <v>100</v>
-      </c>
       <c r="S5" s="14" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="V5" s="14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="W5" s="14" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="X5" s="30" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="Y5" s="30" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="Z5" s="30" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="AA5" s="30" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="AB5" s="30" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="AC5" s="30" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L6" s="31" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="M6" s="31" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N6" s="31" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="O6" s="31" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="P6" s="31" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="Q6" s="31" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="R6" s="32" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="S6" s="32" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="T6" s="32" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="U6" s="32" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="V6" s="32" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="W6" s="32" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="Z6" s="33" t="str">
         <f aca="false">설정!B19</f>
@@ -12312,12 +12668,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="5" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
@@ -12346,7 +12702,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -12413,7 +12769,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B3" s="26"/>
       <c r="C3" s="26"/>
@@ -12500,7 +12856,7 @@
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
@@ -12567,161 +12923,161 @@
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B5" s="26"/>
       <c r="C5" s="26"/>
       <c r="D5" s="14" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="Q5" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="R5" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="R5" s="14" t="s">
-        <v>100</v>
-      </c>
       <c r="S5" s="14" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="V5" s="14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="W5" s="14" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="X5" s="30" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="Y5" s="30" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="Z5" s="30" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="AA5" s="30" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="AB5" s="30" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L6" s="31" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="M6" s="31" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N6" s="31" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="O6" s="31" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="P6" s="31" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="Q6" s="31" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="R6" s="32" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="S6" s="32" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="T6" s="32" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="U6" s="32" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="V6" s="32" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="W6" s="32" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="Z6" s="33" t="str">
         <f aca="false">설정!B24</f>
@@ -17048,7 +17404,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -17075,7 +17431,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -17102,69 +17458,69 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="O5" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17684,7 +18040,7 @@
         <v/>
       </c>
       <c r="O13" s="5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
@@ -21738,7 +22094,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -21752,7 +22108,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -21766,34 +22122,34 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25848,7 +26204,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -25870,7 +26226,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -25892,7 +26248,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="45" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B4" s="45"/>
       <c r="C4" s="45"/>
@@ -25901,31 +26257,31 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J5" s="4" t="str">
         <f aca="false">설정!$B$6&amp;" 정답률"</f>
@@ -25940,25 +26296,25 @@
         <v>TF3반 정답률</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="O5" s="24" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="P5" s="24" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="Q5" s="24" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="R5" s="24" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25966,7 +26322,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C6" s="46" t="str">
         <f aca="false">공수1!D4</f>
@@ -26042,7 +26398,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C7" s="46" t="str">
         <f aca="false">공수1!E4</f>
@@ -26118,7 +26474,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C8" s="46" t="str">
         <f aca="false">공수1!F4</f>
@@ -26194,7 +26550,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C9" s="46" t="str">
         <f aca="false">공수1!G4</f>
@@ -26270,7 +26626,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C10" s="46" t="str">
         <f aca="false">공수1!H4</f>
@@ -26346,7 +26702,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C11" s="46" t="str">
         <f aca="false">공수1!I4</f>
@@ -26422,7 +26778,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C12" s="46" t="str">
         <f aca="false">공수1!J4</f>
@@ -26498,7 +26854,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C13" s="46" t="str">
         <f aca="false">공수1!K4</f>
@@ -26574,7 +26930,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C14" s="46" t="str">
         <f aca="false">공수1!L4</f>
@@ -26650,7 +27006,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C15" s="46" t="str">
         <f aca="false">공수1!M4</f>
@@ -26726,7 +27082,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C16" s="46" t="str">
         <f aca="false">공수1!N4</f>
@@ -26802,7 +27158,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C17" s="46" t="str">
         <f aca="false">공수1!O4</f>
@@ -26878,7 +27234,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C18" s="46" t="str">
         <f aca="false">공수1!P4</f>
@@ -26954,7 +27310,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C19" s="46" t="str">
         <f aca="false">공수1!Q4</f>
@@ -27030,7 +27386,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C20" s="46" t="str">
         <f aca="false">공수1!R4</f>
@@ -27081,19 +27437,19 @@
         <v/>
       </c>
       <c r="O20" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="P20" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q20" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="R20" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="S20" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27101,7 +27457,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C21" s="46" t="str">
         <f aca="false">공수1!S4</f>
@@ -27152,19 +27508,19 @@
         <v/>
       </c>
       <c r="O21" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="P21" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q21" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="R21" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="S21" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27172,7 +27528,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C22" s="46" t="str">
         <f aca="false">공수1!T4</f>
@@ -27223,19 +27579,19 @@
         <v/>
       </c>
       <c r="O22" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="P22" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q22" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="R22" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="S22" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27243,7 +27599,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C23" s="46" t="str">
         <f aca="false">공수1!U4</f>
@@ -27294,19 +27650,19 @@
         <v/>
       </c>
       <c r="O23" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="P23" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q23" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="R23" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="S23" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27314,7 +27670,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C24" s="46" t="str">
         <f aca="false">공수1!V4</f>
@@ -27365,19 +27721,19 @@
         <v/>
       </c>
       <c r="O24" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="P24" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q24" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="R24" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="S24" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27385,7 +27741,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C25" s="46" t="str">
         <f aca="false">공수1!W4</f>
@@ -27436,24 +27792,24 @@
         <v/>
       </c>
       <c r="O25" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="P25" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q25" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="R25" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="S25" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="45" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B28" s="45"/>
       <c r="C28" s="45"/>
@@ -27462,31 +27818,31 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J29" s="4" t="str">
         <f aca="false">설정!$B$6&amp;" 정답률"</f>
@@ -27501,25 +27857,25 @@
         <v>TF3반 정답률</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="O29" s="24" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="P29" s="24" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="Q29" s="24" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="R29" s="24" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="S29" s="24" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27527,7 +27883,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C30" s="46" t="str">
         <f aca="false">공수2!D4</f>
@@ -27603,7 +27959,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C31" s="46" t="str">
         <f aca="false">공수2!E4</f>
@@ -27679,7 +28035,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C32" s="46" t="str">
         <f aca="false">공수2!F4</f>
@@ -27755,7 +28111,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C33" s="46" t="str">
         <f aca="false">공수2!G4</f>
@@ -27831,7 +28187,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C34" s="46" t="str">
         <f aca="false">공수2!H4</f>
@@ -27907,7 +28263,7 @@
         <v>6</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C35" s="46" t="str">
         <f aca="false">공수2!I4</f>
@@ -27983,7 +28339,7 @@
         <v>7</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C36" s="46" t="str">
         <f aca="false">공수2!J4</f>
@@ -28059,7 +28415,7 @@
         <v>8</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C37" s="46" t="str">
         <f aca="false">공수2!K4</f>
@@ -28135,7 +28491,7 @@
         <v>9</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C38" s="46" t="str">
         <f aca="false">공수2!L4</f>
@@ -28211,7 +28567,7 @@
         <v>10</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C39" s="46" t="str">
         <f aca="false">공수2!M4</f>
@@ -28287,7 +28643,7 @@
         <v>11</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C40" s="46" t="str">
         <f aca="false">공수2!N4</f>
@@ -28363,7 +28719,7 @@
         <v>12</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C41" s="46" t="str">
         <f aca="false">공수2!O4</f>
@@ -28439,7 +28795,7 @@
         <v>13</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C42" s="46" t="str">
         <f aca="false">공수2!P4</f>
@@ -28515,7 +28871,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C43" s="46" t="str">
         <f aca="false">공수2!Q4</f>
@@ -28591,7 +28947,7 @@
         <v>15</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C44" s="46" t="str">
         <f aca="false">공수2!R4</f>
@@ -28642,19 +28998,19 @@
         <v/>
       </c>
       <c r="O44" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="P44" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q44" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="R44" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="S44" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28662,7 +29018,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C45" s="46" t="str">
         <f aca="false">공수2!S4</f>
@@ -28713,19 +29069,19 @@
         <v/>
       </c>
       <c r="O45" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="P45" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q45" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="R45" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="S45" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28733,7 +29089,7 @@
         <v>17</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C46" s="46" t="str">
         <f aca="false">공수2!T4</f>
@@ -28784,19 +29140,19 @@
         <v/>
       </c>
       <c r="O46" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="P46" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q46" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="R46" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="S46" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28804,7 +29160,7 @@
         <v>18</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C47" s="46" t="str">
         <f aca="false">공수2!U4</f>
@@ -28855,19 +29211,19 @@
         <v/>
       </c>
       <c r="O47" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="P47" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q47" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="R47" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="S47" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28875,7 +29231,7 @@
         <v>19</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C48" s="46" t="str">
         <f aca="false">공수2!V4</f>
@@ -28926,19 +29282,19 @@
         <v/>
       </c>
       <c r="O48" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="P48" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q48" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="R48" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="S48" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28946,7 +29302,7 @@
         <v>20</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C49" s="46" t="str">
         <f aca="false">공수2!W4</f>
@@ -28997,19 +29353,19 @@
         <v/>
       </c>
       <c r="O49" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="P49" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q49" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="R49" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="S49" s="52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="183">
   <si>
     <r>
       <rPr>
@@ -3227,7 +3227,83 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기존 반명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">재원생은 현재 반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">신규 학생은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">신규</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'.</t>
     </r>
   </si>
   <si>
@@ -3243,6 +3319,12 @@
     <t xml:space="preserve">구분</t>
   </si>
   <si>
+    <t xml:space="preserve">기존 반명</t>
+  </si>
+  <si>
+    <t xml:space="preserve">학습 진도</t>
+  </si>
+  <si>
     <t xml:space="preserve">연락처</t>
   </si>
   <si>
@@ -3352,6 +3434,77 @@
   </si>
   <si>
     <t xml:space="preserve">외부</t>
+  </si>
+  <si>
+    <t xml:space="preserve">신규</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공통수학</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회독 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공통수학</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">집합까지</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">010-0000-0000</t>
@@ -6706,14 +6859,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6725,6 +6880,8 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -6735,6 +6892,8 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
@@ -6755,25 +6914,37 @@
       <c r="F6" s="4" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>98</v>
+        <v>100</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6785,6 +6956,8 @@
       <c r="D8" s="14"/>
       <c r="E8" s="8"/>
       <c r="F8" s="25"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="n">
@@ -6795,6 +6968,8 @@
       <c r="D9" s="14"/>
       <c r="E9" s="8"/>
       <c r="F9" s="25"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="25"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
@@ -6805,6 +6980,8 @@
       <c r="D10" s="14"/>
       <c r="E10" s="8"/>
       <c r="F10" s="25"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
@@ -6815,6 +6992,8 @@
       <c r="D11" s="14"/>
       <c r="E11" s="8"/>
       <c r="F11" s="25"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="25"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="n">
@@ -6825,6 +7004,8 @@
       <c r="D12" s="14"/>
       <c r="E12" s="8"/>
       <c r="F12" s="25"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="n">
@@ -6835,6 +7016,8 @@
       <c r="D13" s="14"/>
       <c r="E13" s="8"/>
       <c r="F13" s="25"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
@@ -6845,6 +7028,8 @@
       <c r="D14" s="14"/>
       <c r="E14" s="8"/>
       <c r="F14" s="25"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="25"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
@@ -6855,6 +7040,8 @@
       <c r="D15" s="14"/>
       <c r="E15" s="8"/>
       <c r="F15" s="25"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="25"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
@@ -6865,6 +7052,8 @@
       <c r="D16" s="14"/>
       <c r="E16" s="8"/>
       <c r="F16" s="25"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="25"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="n">
@@ -6875,6 +7064,8 @@
       <c r="D17" s="14"/>
       <c r="E17" s="8"/>
       <c r="F17" s="25"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="25"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="n">
@@ -6885,6 +7076,8 @@
       <c r="D18" s="14"/>
       <c r="E18" s="8"/>
       <c r="F18" s="25"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="25"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="n">
@@ -6895,6 +7088,8 @@
       <c r="D19" s="14"/>
       <c r="E19" s="8"/>
       <c r="F19" s="25"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="n">
@@ -6905,6 +7100,8 @@
       <c r="D20" s="14"/>
       <c r="E20" s="8"/>
       <c r="F20" s="25"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="n">
@@ -6915,6 +7112,8 @@
       <c r="D21" s="14"/>
       <c r="E21" s="8"/>
       <c r="F21" s="25"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="n">
@@ -6925,6 +7124,8 @@
       <c r="D22" s="14"/>
       <c r="E22" s="8"/>
       <c r="F22" s="25"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="25"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="n">
@@ -6935,6 +7136,8 @@
       <c r="D23" s="14"/>
       <c r="E23" s="8"/>
       <c r="F23" s="25"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="25"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="n">
@@ -6945,6 +7148,8 @@
       <c r="D24" s="14"/>
       <c r="E24" s="8"/>
       <c r="F24" s="25"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="25"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="n">
@@ -6955,6 +7160,8 @@
       <c r="D25" s="14"/>
       <c r="E25" s="8"/>
       <c r="F25" s="25"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="25"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="n">
@@ -6965,6 +7172,8 @@
       <c r="D26" s="14"/>
       <c r="E26" s="8"/>
       <c r="F26" s="25"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="25"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="n">
@@ -6975,6 +7184,8 @@
       <c r="D27" s="14"/>
       <c r="E27" s="8"/>
       <c r="F27" s="25"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="n">
@@ -6985,6 +7196,8 @@
       <c r="D28" s="14"/>
       <c r="E28" s="8"/>
       <c r="F28" s="25"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="n">
@@ -6995,6 +7208,8 @@
       <c r="D29" s="14"/>
       <c r="E29" s="8"/>
       <c r="F29" s="25"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="n">
@@ -7005,6 +7220,8 @@
       <c r="D30" s="14"/>
       <c r="E30" s="8"/>
       <c r="F30" s="25"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="25"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="n">
@@ -7015,6 +7232,8 @@
       <c r="D31" s="14"/>
       <c r="E31" s="8"/>
       <c r="F31" s="25"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="25"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="n">
@@ -7025,6 +7244,8 @@
       <c r="D32" s="14"/>
       <c r="E32" s="8"/>
       <c r="F32" s="25"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="25"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="n">
@@ -7035,6 +7256,8 @@
       <c r="D33" s="14"/>
       <c r="E33" s="8"/>
       <c r="F33" s="25"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="25"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="n">
@@ -7045,6 +7268,8 @@
       <c r="D34" s="14"/>
       <c r="E34" s="8"/>
       <c r="F34" s="25"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="25"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="n">
@@ -7055,6 +7280,8 @@
       <c r="D35" s="14"/>
       <c r="E35" s="8"/>
       <c r="F35" s="25"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="25"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="n">
@@ -7065,6 +7292,8 @@
       <c r="D36" s="14"/>
       <c r="E36" s="8"/>
       <c r="F36" s="25"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="25"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="n">
@@ -7075,6 +7304,8 @@
       <c r="D37" s="14"/>
       <c r="E37" s="8"/>
       <c r="F37" s="25"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="25"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="n">
@@ -7085,6 +7316,8 @@
       <c r="D38" s="14"/>
       <c r="E38" s="8"/>
       <c r="F38" s="25"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="25"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="n">
@@ -7095,6 +7328,8 @@
       <c r="D39" s="14"/>
       <c r="E39" s="8"/>
       <c r="F39" s="25"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="25"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="n">
@@ -7105,6 +7340,8 @@
       <c r="D40" s="14"/>
       <c r="E40" s="8"/>
       <c r="F40" s="25"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="25"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="n">
@@ -7115,6 +7352,8 @@
       <c r="D41" s="14"/>
       <c r="E41" s="8"/>
       <c r="F41" s="25"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="25"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="n">
@@ -7125,6 +7364,8 @@
       <c r="D42" s="14"/>
       <c r="E42" s="8"/>
       <c r="F42" s="25"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="25"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="n">
@@ -7135,6 +7376,8 @@
       <c r="D43" s="14"/>
       <c r="E43" s="8"/>
       <c r="F43" s="25"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="25"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="n">
@@ -7145,6 +7388,8 @@
       <c r="D44" s="14"/>
       <c r="E44" s="8"/>
       <c r="F44" s="25"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="25"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="n">
@@ -7155,6 +7400,8 @@
       <c r="D45" s="14"/>
       <c r="E45" s="8"/>
       <c r="F45" s="25"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="25"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="n">
@@ -7165,6 +7412,8 @@
       <c r="D46" s="14"/>
       <c r="E46" s="8"/>
       <c r="F46" s="25"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="25"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="n">
@@ -7175,6 +7424,8 @@
       <c r="D47" s="14"/>
       <c r="E47" s="8"/>
       <c r="F47" s="25"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="25"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="n">
@@ -7185,6 +7436,8 @@
       <c r="D48" s="14"/>
       <c r="E48" s="8"/>
       <c r="F48" s="25"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="25"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="n">
@@ -7195,6 +7448,8 @@
       <c r="D49" s="14"/>
       <c r="E49" s="8"/>
       <c r="F49" s="25"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="25"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="n">
@@ -7205,6 +7460,8 @@
       <c r="D50" s="14"/>
       <c r="E50" s="8"/>
       <c r="F50" s="25"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="25"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="n">
@@ -7215,6 +7472,8 @@
       <c r="D51" s="14"/>
       <c r="E51" s="8"/>
       <c r="F51" s="25"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="25"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="n">
@@ -7225,6 +7484,8 @@
       <c r="D52" s="14"/>
       <c r="E52" s="8"/>
       <c r="F52" s="25"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="25"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="n">
@@ -7235,6 +7496,8 @@
       <c r="D53" s="14"/>
       <c r="E53" s="8"/>
       <c r="F53" s="25"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="25"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="n">
@@ -7245,6 +7508,8 @@
       <c r="D54" s="14"/>
       <c r="E54" s="8"/>
       <c r="F54" s="25"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="25"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="n">
@@ -7255,6 +7520,8 @@
       <c r="D55" s="14"/>
       <c r="E55" s="8"/>
       <c r="F55" s="25"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="25"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="n">
@@ -7265,6 +7532,8 @@
       <c r="D56" s="14"/>
       <c r="E56" s="8"/>
       <c r="F56" s="25"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="25"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="n">
@@ -7275,6 +7544,8 @@
       <c r="D57" s="14"/>
       <c r="E57" s="8"/>
       <c r="F57" s="25"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="25"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="n">
@@ -7285,6 +7556,8 @@
       <c r="D58" s="14"/>
       <c r="E58" s="8"/>
       <c r="F58" s="25"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="25"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="n">
@@ -7295,6 +7568,8 @@
       <c r="D59" s="14"/>
       <c r="E59" s="8"/>
       <c r="F59" s="25"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="25"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="n">
@@ -7305,6 +7580,8 @@
       <c r="D60" s="14"/>
       <c r="E60" s="8"/>
       <c r="F60" s="25"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="25"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="n">
@@ -7315,6 +7592,8 @@
       <c r="D61" s="14"/>
       <c r="E61" s="8"/>
       <c r="F61" s="25"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="25"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="n">
@@ -7325,6 +7604,8 @@
       <c r="D62" s="14"/>
       <c r="E62" s="8"/>
       <c r="F62" s="25"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="25"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="n">
@@ -7335,6 +7616,8 @@
       <c r="D63" s="14"/>
       <c r="E63" s="8"/>
       <c r="F63" s="25"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="25"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="n">
@@ -7345,6 +7628,8 @@
       <c r="D64" s="14"/>
       <c r="E64" s="8"/>
       <c r="F64" s="25"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="25"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="n">
@@ -7355,6 +7640,8 @@
       <c r="D65" s="14"/>
       <c r="E65" s="8"/>
       <c r="F65" s="25"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="25"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="n">
@@ -7365,6 +7652,8 @@
       <c r="D66" s="14"/>
       <c r="E66" s="8"/>
       <c r="F66" s="25"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="25"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="n">
@@ -7375,6 +7664,8 @@
       <c r="D67" s="14"/>
       <c r="E67" s="8"/>
       <c r="F67" s="25"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="25"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="n">
@@ -7385,6 +7676,8 @@
       <c r="D68" s="14"/>
       <c r="E68" s="8"/>
       <c r="F68" s="25"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="25"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="n">
@@ -7395,6 +7688,8 @@
       <c r="D69" s="14"/>
       <c r="E69" s="8"/>
       <c r="F69" s="25"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="25"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="n">
@@ -7405,6 +7700,8 @@
       <c r="D70" s="14"/>
       <c r="E70" s="8"/>
       <c r="F70" s="25"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="25"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="n">
@@ -7415,6 +7712,8 @@
       <c r="D71" s="14"/>
       <c r="E71" s="8"/>
       <c r="F71" s="25"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="25"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="n">
@@ -7425,6 +7724,8 @@
       <c r="D72" s="14"/>
       <c r="E72" s="8"/>
       <c r="F72" s="25"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="25"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="n">
@@ -7435,6 +7736,8 @@
       <c r="D73" s="14"/>
       <c r="E73" s="8"/>
       <c r="F73" s="25"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="25"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="n">
@@ -7445,6 +7748,8 @@
       <c r="D74" s="14"/>
       <c r="E74" s="8"/>
       <c r="F74" s="25"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="25"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="n">
@@ -7455,6 +7760,8 @@
       <c r="D75" s="14"/>
       <c r="E75" s="8"/>
       <c r="F75" s="25"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="25"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="n">
@@ -7465,6 +7772,8 @@
       <c r="D76" s="14"/>
       <c r="E76" s="8"/>
       <c r="F76" s="25"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="25"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="n">
@@ -7475,6 +7784,8 @@
       <c r="D77" s="14"/>
       <c r="E77" s="8"/>
       <c r="F77" s="25"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="25"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="n">
@@ -7485,6 +7796,8 @@
       <c r="D78" s="14"/>
       <c r="E78" s="8"/>
       <c r="F78" s="25"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="25"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="n">
@@ -7495,6 +7808,8 @@
       <c r="D79" s="14"/>
       <c r="E79" s="8"/>
       <c r="F79" s="25"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="25"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="n">
@@ -7505,6 +7820,8 @@
       <c r="D80" s="14"/>
       <c r="E80" s="8"/>
       <c r="F80" s="25"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="25"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="n">
@@ -7515,6 +7832,8 @@
       <c r="D81" s="14"/>
       <c r="E81" s="8"/>
       <c r="F81" s="25"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="25"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="n">
@@ -7525,6 +7844,8 @@
       <c r="D82" s="14"/>
       <c r="E82" s="8"/>
       <c r="F82" s="25"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="25"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="n">
@@ -7535,6 +7856,8 @@
       <c r="D83" s="14"/>
       <c r="E83" s="8"/>
       <c r="F83" s="25"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="25"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="n">
@@ -7545,6 +7868,8 @@
       <c r="D84" s="14"/>
       <c r="E84" s="8"/>
       <c r="F84" s="25"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="25"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="n">
@@ -7555,6 +7880,8 @@
       <c r="D85" s="14"/>
       <c r="E85" s="8"/>
       <c r="F85" s="25"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="25"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="n">
@@ -7565,11 +7892,13 @@
       <c r="D86" s="14"/>
       <c r="E86" s="8"/>
       <c r="F86" s="25"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D7:D86" type="list">
@@ -7606,12 +7935,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
@@ -7641,7 +7970,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -7708,7 +8037,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B3" s="26"/>
       <c r="C3" s="26"/>
@@ -7799,7 +8128,7 @@
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
@@ -7866,87 +8195,87 @@
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B5" s="26"/>
       <c r="C5" s="26"/>
       <c r="D5" s="14" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O5" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q5" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="R5" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="P5" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q5" s="14" t="s">
+      <c r="S5" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="R5" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="S5" s="14" t="s">
-        <v>106</v>
-      </c>
       <c r="T5" s="14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="V5" s="14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="W5" s="14" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="X5" s="30" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Y5" s="30" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="Z5" s="30" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AA5" s="30" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AB5" s="30" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AC5" s="30" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7960,70 +8289,70 @@
         <v>90</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="L6" s="31" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="M6" s="31" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N6" s="31" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="O6" s="31" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="P6" s="31" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="Q6" s="31" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="R6" s="32" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="S6" s="32" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="T6" s="32" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="U6" s="32" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="V6" s="32" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="W6" s="32" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="Z6" s="33" t="str">
         <f aca="false">설정!B19</f>
@@ -12622,6 +12951,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:W4" type="list">
+      <formula1>설정!$B$19:$B$22</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:W5" type="list">
+      <formula1>"하,중하,중,중상,상,최상"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="객관식은 1~5 사이 정수만 입력" errorStyle="stop" errorTitle="입력 오류" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:Q2 D7:Q86" type="whole">
       <formula1>1</formula1>
       <formula2>5</formula2>
@@ -12629,14 +12966,6 @@
     <dataValidation allowBlank="true" error="단답형은 0~999 사이 정수만 입력" errorStyle="stop" errorTitle="입력 오류" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R2:W2 R7:W86" type="whole">
       <formula1>0</formula1>
       <formula2>999</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:W4" type="list">
-      <formula1>설정!$B$19:$B$22</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:W5" type="list">
-      <formula1>"하,중하,중,중상,상,최상"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -12668,12 +12997,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
@@ -12702,7 +13031,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -12769,7 +13098,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B3" s="26"/>
       <c r="C3" s="26"/>
@@ -12856,7 +13185,7 @@
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
@@ -12923,84 +13252,84 @@
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B5" s="26"/>
       <c r="C5" s="26"/>
       <c r="D5" s="14" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O5" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q5" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="R5" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="P5" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q5" s="14" t="s">
+      <c r="S5" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="R5" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="S5" s="14" t="s">
-        <v>106</v>
-      </c>
       <c r="T5" s="14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="V5" s="14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="W5" s="14" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="X5" s="30" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Y5" s="30" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="Z5" s="30" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AA5" s="30" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AB5" s="30" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13014,70 +13343,70 @@
         <v>90</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="L6" s="31" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="M6" s="31" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N6" s="31" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="O6" s="31" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="P6" s="31" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="Q6" s="31" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="R6" s="32" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="S6" s="32" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="T6" s="32" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="U6" s="32" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="V6" s="32" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="W6" s="32" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="Z6" s="33" t="str">
         <f aca="false">설정!B24</f>
@@ -17352,6 +17681,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
+    <dataValidation allowBlank="true" error="객관식은 1~5 사이 정수만 입력" errorStyle="stop" errorTitle="입력 오류" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:Q2 D7:Q86" type="whole">
+      <formula1>1</formula1>
+      <formula2>5</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="단답형은 0~999 사이 정수만 입력" errorStyle="stop" errorTitle="입력 오류" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R2:W2 R7:W86" type="whole">
+      <formula1>0</formula1>
+      <formula2>999</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:W4" type="list">
       <formula1>설정!$B$24:$B$26</formula1>
       <formula2>0</formula2>
@@ -17359,14 +17696,6 @@
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:W5" type="list">
       <formula1>"하,중하,중,중상,상,최상"</formula1>
       <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="객관식은 1~5 사이 정수만 입력" errorStyle="stop" errorTitle="입력 오류" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:Q2 D7:Q86" type="whole">
-      <formula1>1</formula1>
-      <formula2>5</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="단답형은 0~999 사이 정수만 입력" errorStyle="stop" errorTitle="입력 오류" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R2:W2 R7:W86" type="whole">
-      <formula1>0</formula1>
-      <formula2>999</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -17404,7 +17733,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -17431,7 +17760,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -17458,7 +17787,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="O5" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17475,52 +17804,52 @@
         <v>91</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18040,7 +18369,7 @@
         <v/>
       </c>
       <c r="O13" s="5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
@@ -22094,7 +22423,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -22108,7 +22437,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -22122,7 +22451,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>89</v>
@@ -22134,22 +22463,22 @@
         <v>91</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26204,7 +26533,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -26226,7 +26555,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -26248,7 +26577,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="45" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B4" s="45"/>
       <c r="C4" s="45"/>
@@ -26257,31 +26586,31 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J5" s="4" t="str">
         <f aca="false">설정!$B$6&amp;" 정답률"</f>
@@ -26296,25 +26625,25 @@
         <v>TF3반 정답률</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="O5" s="24" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="P5" s="24" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q5" s="24" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="R5" s="24" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26322,7 +26651,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C6" s="46" t="str">
         <f aca="false">공수1!D4</f>
@@ -26398,7 +26727,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C7" s="46" t="str">
         <f aca="false">공수1!E4</f>
@@ -26474,7 +26803,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C8" s="46" t="str">
         <f aca="false">공수1!F4</f>
@@ -26550,7 +26879,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C9" s="46" t="str">
         <f aca="false">공수1!G4</f>
@@ -26626,7 +26955,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C10" s="46" t="str">
         <f aca="false">공수1!H4</f>
@@ -26702,7 +27031,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C11" s="46" t="str">
         <f aca="false">공수1!I4</f>
@@ -26778,7 +27107,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C12" s="46" t="str">
         <f aca="false">공수1!J4</f>
@@ -26854,7 +27183,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C13" s="46" t="str">
         <f aca="false">공수1!K4</f>
@@ -26930,7 +27259,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C14" s="46" t="str">
         <f aca="false">공수1!L4</f>
@@ -27006,7 +27335,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C15" s="46" t="str">
         <f aca="false">공수1!M4</f>
@@ -27082,7 +27411,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C16" s="46" t="str">
         <f aca="false">공수1!N4</f>
@@ -27158,7 +27487,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C17" s="46" t="str">
         <f aca="false">공수1!O4</f>
@@ -27234,7 +27563,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C18" s="46" t="str">
         <f aca="false">공수1!P4</f>
@@ -27310,7 +27639,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C19" s="46" t="str">
         <f aca="false">공수1!Q4</f>
@@ -27386,7 +27715,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C20" s="46" t="str">
         <f aca="false">공수1!R4</f>
@@ -27437,19 +27766,19 @@
         <v/>
       </c>
       <c r="O20" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P20" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q20" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="R20" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="S20" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27457,7 +27786,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C21" s="46" t="str">
         <f aca="false">공수1!S4</f>
@@ -27508,19 +27837,19 @@
         <v/>
       </c>
       <c r="O21" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P21" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q21" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="R21" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="S21" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27528,7 +27857,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C22" s="46" t="str">
         <f aca="false">공수1!T4</f>
@@ -27579,19 +27908,19 @@
         <v/>
       </c>
       <c r="O22" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P22" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q22" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="R22" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="S22" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27599,7 +27928,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C23" s="46" t="str">
         <f aca="false">공수1!U4</f>
@@ -27650,19 +27979,19 @@
         <v/>
       </c>
       <c r="O23" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P23" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q23" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="R23" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="S23" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27670,7 +27999,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C24" s="46" t="str">
         <f aca="false">공수1!V4</f>
@@ -27721,19 +28050,19 @@
         <v/>
       </c>
       <c r="O24" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P24" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q24" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="R24" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="S24" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27741,7 +28070,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C25" s="46" t="str">
         <f aca="false">공수1!W4</f>
@@ -27792,24 +28121,24 @@
         <v/>
       </c>
       <c r="O25" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P25" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q25" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="R25" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="S25" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="45" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B28" s="45"/>
       <c r="C28" s="45"/>
@@ -27818,31 +28147,31 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J29" s="4" t="str">
         <f aca="false">설정!$B$6&amp;" 정답률"</f>
@@ -27857,25 +28186,25 @@
         <v>TF3반 정답률</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="O29" s="24" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="P29" s="24" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q29" s="24" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="R29" s="24" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="S29" s="24" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27883,7 +28212,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C30" s="46" t="str">
         <f aca="false">공수2!D4</f>
@@ -27959,7 +28288,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C31" s="46" t="str">
         <f aca="false">공수2!E4</f>
@@ -28035,7 +28364,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C32" s="46" t="str">
         <f aca="false">공수2!F4</f>
@@ -28111,7 +28440,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C33" s="46" t="str">
         <f aca="false">공수2!G4</f>
@@ -28187,7 +28516,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C34" s="46" t="str">
         <f aca="false">공수2!H4</f>
@@ -28263,7 +28592,7 @@
         <v>6</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C35" s="46" t="str">
         <f aca="false">공수2!I4</f>
@@ -28339,7 +28668,7 @@
         <v>7</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C36" s="46" t="str">
         <f aca="false">공수2!J4</f>
@@ -28415,7 +28744,7 @@
         <v>8</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C37" s="46" t="str">
         <f aca="false">공수2!K4</f>
@@ -28491,7 +28820,7 @@
         <v>9</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C38" s="46" t="str">
         <f aca="false">공수2!L4</f>
@@ -28567,7 +28896,7 @@
         <v>10</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C39" s="46" t="str">
         <f aca="false">공수2!M4</f>
@@ -28643,7 +28972,7 @@
         <v>11</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C40" s="46" t="str">
         <f aca="false">공수2!N4</f>
@@ -28719,7 +29048,7 @@
         <v>12</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C41" s="46" t="str">
         <f aca="false">공수2!O4</f>
@@ -28795,7 +29124,7 @@
         <v>13</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C42" s="46" t="str">
         <f aca="false">공수2!P4</f>
@@ -28871,7 +29200,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C43" s="46" t="str">
         <f aca="false">공수2!Q4</f>
@@ -28947,7 +29276,7 @@
         <v>15</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C44" s="46" t="str">
         <f aca="false">공수2!R4</f>
@@ -28998,19 +29327,19 @@
         <v/>
       </c>
       <c r="O44" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P44" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q44" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="R44" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="S44" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29018,7 +29347,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C45" s="46" t="str">
         <f aca="false">공수2!S4</f>
@@ -29069,19 +29398,19 @@
         <v/>
       </c>
       <c r="O45" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P45" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q45" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="R45" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="S45" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29089,7 +29418,7 @@
         <v>17</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C46" s="46" t="str">
         <f aca="false">공수2!T4</f>
@@ -29140,19 +29469,19 @@
         <v/>
       </c>
       <c r="O46" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P46" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q46" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="R46" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="S46" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29160,7 +29489,7 @@
         <v>18</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C47" s="46" t="str">
         <f aca="false">공수2!U4</f>
@@ -29211,19 +29540,19 @@
         <v/>
       </c>
       <c r="O47" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P47" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q47" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="R47" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="S47" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29231,7 +29560,7 @@
         <v>19</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C48" s="46" t="str">
         <f aca="false">공수2!V4</f>
@@ -29282,19 +29611,19 @@
         <v/>
       </c>
       <c r="O48" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P48" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="R48" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="S48" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29302,7 +29631,7 @@
         <v>20</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C49" s="46" t="str">
         <f aca="false">공수2!W4</f>
@@ -29353,19 +29682,19 @@
         <v/>
       </c>
       <c r="O49" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P49" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q49" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="R49" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="S49" s="52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="198">
   <si>
     <r>
       <rPr>
@@ -1925,7 +1925,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">반편성 진단평가 결과 보고서</t>
+      <t xml:space="preserve">진단평가 결과 보고서</t>
     </r>
   </si>
   <si>
@@ -2820,7 +2820,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">⑥ 반 소개 </t>
+      <t xml:space="preserve">⑥ 공통수학반 소개 </t>
     </r>
     <r>
       <rPr>
@@ -2841,7 +2841,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">학부모 보고서 추천 반 카드 문구 </t>
+      <t xml:space="preserve">공통수학 시험 결과로 배정 </t>
     </r>
     <r>
       <rPr>
@@ -2862,7 +2862,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">추천 반 선택 목록</t>
+      <t xml:space="preserve">학부모 보고서 문구 </t>
     </r>
     <r>
       <rPr>
@@ -2873,8 +2873,32 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선택 목록</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">)</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">공통수학반 이름</t>
   </si>
   <si>
     <t xml:space="preserve">소개 문구</t>
@@ -3114,7 +3138,428 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">← 추천할 반이 더 있으면 반 이름과 소개를 추가</t>
+    <t xml:space="preserve">← 공통수학반이 더 있으면 반 이름과 소개를 추가</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">⑦ 선행 과목반 소개 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">학습 진도에 따라 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과목 선택 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">학부모 보고서 문구 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선택 목록</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">선행 과목반 이름</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대수반</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지수와 로그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지수함수와 로그함수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">삼각함수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수열을 선행하는 반으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공통수학을 마친 학생이 다음 단계로 나아가기 좋은 과정입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">← 실제 운영하는 선행반 이름</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">소개로 수정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빈 줄에 추가 가능</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">미적분Ⅰ반</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">함수의 극한과 연속</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적분을 선행하는 반으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대수 학습을 마친 학생에게 권장하는 과정입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">확률과 통계반</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">순열과 조합</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확률</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">통계를 선행하는 반으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공통수학의 경우의 수를 바탕으로 개념을 넓혀 가는 과정입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">학생 명단</t>
@@ -4376,7 +4821,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">절대평가</t>
+      <t xml:space="preserve">공통수학반 </t>
     </r>
     <r>
       <rPr>
@@ -4387,6 +4832,27 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선행 과목반</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">)</t>
     </r>
   </si>
@@ -4398,7 +4864,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">자동배정 </t>
+      <t xml:space="preserve">학생마다 </t>
     </r>
     <r>
       <rPr>
@@ -4408,7 +4874,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">= '</t>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -4417,7 +4883,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">설정</t>
+      <t xml:space="preserve">개 반 수강</t>
     </r>
     <r>
       <rPr>
@@ -4427,7 +4893,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">' ①</t>
+      <t xml:space="preserve">: ① </t>
     </r>
     <r>
       <rPr>
@@ -4436,7 +4902,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">의 과목별 점수 기준</t>
+      <t xml:space="preserve">공통수학반 </t>
     </r>
     <r>
       <rPr>
@@ -4446,7 +4912,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve">= </t>
     </r>
     <r>
       <rPr>
@@ -4455,7 +4921,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">해당 없으면 </t>
+      <t xml:space="preserve">시험 결과 기준 자동배정</t>
     </r>
     <r>
       <rPr>
@@ -4465,7 +4931,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">'</t>
+      <t xml:space="preserve">('</t>
     </r>
     <r>
       <rPr>
@@ -4474,7 +4940,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">보류</t>
+      <t xml:space="preserve">설정</t>
     </r>
     <r>
       <rPr>
@@ -4484,7 +4950,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">'. </t>
+      <t xml:space="preserve">' ①, </t>
     </r>
     <r>
       <rPr>
@@ -4493,7 +4959,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">노란 칸 </t>
+      <t xml:space="preserve">해당 없으면 보류</t>
     </r>
     <r>
       <rPr>
@@ -4503,7 +4969,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">'</t>
+      <t xml:space="preserve">). </t>
     </r>
     <r>
       <rPr>
@@ -4512,7 +4978,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">추천 반 </t>
+      <t xml:space="preserve">노란 칸 </t>
     </r>
     <r>
       <rPr>
@@ -4522,7 +4988,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1·2'</t>
+      <t xml:space="preserve">'</t>
     </r>
     <r>
       <rPr>
@@ -4531,7 +4997,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">에 상담 후 반을 적으면 최종반 </t>
+      <t xml:space="preserve">공통수학반</t>
     </r>
     <r>
       <rPr>
@@ -4541,7 +5007,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">= </t>
+      <t xml:space="preserve">'</t>
     </r>
     <r>
       <rPr>
@@ -4550,7 +5016,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">추천 반 </t>
+      <t xml:space="preserve">에 적으면 그 반이 우선</t>
     </r>
     <r>
       <rPr>
@@ -4560,7 +5026,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1(</t>
+      <t xml:space="preserve">. ② </t>
     </r>
     <r>
       <rPr>
@@ -4569,7 +5035,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">비어 있으면 자동배정</t>
+      <t xml:space="preserve">선행반 </t>
     </r>
     <r>
       <rPr>
@@ -4579,7 +5045,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">). </t>
+      <t xml:space="preserve">= </t>
     </r>
     <r>
       <rPr>
@@ -4588,7 +5054,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">학부모 보고서에는 최종반이 </t>
+      <t xml:space="preserve">학습 진도를 보고 노란 칸 </t>
     </r>
     <r>
       <rPr>
@@ -4598,7 +5064,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">'</t>
     </r>
     <r>
       <rPr>
@@ -4607,7 +5073,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">순위</t>
+      <t xml:space="preserve">선행반</t>
     </r>
     <r>
       <rPr>
@@ -4617,7 +5083,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve">'</t>
     </r>
     <r>
       <rPr>
@@ -4626,7 +5092,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">추천 반 </t>
+      <t xml:space="preserve">에서 </t>
     </r>
     <r>
       <rPr>
@@ -4636,7 +5102,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -4645,7 +5111,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가 </t>
+      <t xml:space="preserve">과목 선택</t>
     </r>
     <r>
       <rPr>
@@ -4655,7 +5121,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">('</t>
     </r>
     <r>
       <rPr>
@@ -4664,7 +5130,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">순위로 들어갑니다</t>
+      <t xml:space="preserve">설정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">' ⑦ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">두 반 모두 학부모 보고서에 들어갑니다</t>
     </r>
     <r>
       <rPr>
@@ -4724,7 +5228,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">반별 요약 </t>
+      <t xml:space="preserve">공통수학반별 요약 </t>
     </r>
     <r>
       <rPr>
@@ -4745,7 +5249,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">최종반 기준</t>
+      <t xml:space="preserve">최종 기준</t>
     </r>
     <r>
       <rPr>
@@ -4829,7 +5333,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">추천 반 </t>
+      <t xml:space="preserve">공통수학반
+</t>
     </r>
     <r>
       <rPr>
@@ -4840,10 +5345,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">(</t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -4852,7 +5355,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">추천 반 </t>
+      <t xml:space="preserve">입력</t>
     </r>
     <r>
       <rPr>
@@ -4863,11 +5366,98 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">최종반</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선행반
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공통수학반
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최종</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">비고</t>
@@ -5088,7 +5678,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">추천 반 </t>
+      <t xml:space="preserve">공통수학반</t>
     </r>
     <r>
       <rPr>
@@ -5098,7 +5688,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1·2</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -5107,7 +5697,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">는 목록에서 고르거나 직접 입력</t>
+      <t xml:space="preserve">선행반은 목록에서 고르거나 직접 입력</t>
     </r>
     <r>
       <rPr>
@@ -5136,7 +5726,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">' ⑥</t>
+      <t xml:space="preserve">' ⑥·⑦</t>
     </r>
     <r>
       <rPr>
@@ -5291,6 +5881,12 @@
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">공통수학반</t>
+  </si>
+  <si>
+    <t xml:space="preserve">선행반</t>
   </si>
   <si>
     <t xml:space="preserve">문항 분석</t>
@@ -6401,7 +6997,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -7005,17 +7601,17 @@
       <c r="D51" s="20"/>
       <c r="E51" s="20"/>
     </row>
-    <row r="53" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
@@ -7027,7 +7623,7 @@
         <v>TF1반</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C55" s="20"/>
       <c r="D55" s="20"/>
@@ -7039,7 +7635,7 @@
         <v>TF2반</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C56" s="20"/>
       <c r="D56" s="20"/>
@@ -7051,7 +7647,7 @@
         <v>TF3반</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C57" s="20"/>
       <c r="D57" s="20"/>
@@ -7064,7 +7660,7 @@
       <c r="D58" s="19"/>
       <c r="E58" s="19"/>
       <c r="F58" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7081,8 +7677,81 @@
       <c r="D60" s="19"/>
       <c r="E60" s="19"/>
     </row>
+    <row r="62" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C64" s="20"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+    </row>
+    <row r="66" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+    </row>
+    <row r="67" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="7"/>
+      <c r="B67" s="19"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="19"/>
+    </row>
+    <row r="68" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="7"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+    </row>
+    <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="7"/>
+      <c r="B69" s="19"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+    </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="36">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="H5:L9"/>
@@ -7112,6 +7781,13 @@
     <mergeCell ref="B58:E58"/>
     <mergeCell ref="B59:E59"/>
     <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B69:E69"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B35" type="list">
@@ -7148,7 +7824,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7160,7 +7836,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7172,28 +7848,28 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7201,25 +7877,25 @@
         <v>1</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8210,12 +8886,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="5" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
@@ -8245,7 +8921,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -8312,7 +8988,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B3" s="26"/>
       <c r="C3" s="26"/>
@@ -8403,7 +9079,7 @@
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
@@ -8470,164 +9146,164 @@
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B5" s="26"/>
       <c r="C5" s="26"/>
       <c r="D5" s="14" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="R5" s="14" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="S5" s="14" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="V5" s="14" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="W5" s="14" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="X5" s="30" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="Y5" s="30" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="Z5" s="30" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="AA5" s="30" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="AB5" s="30" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="AC5" s="30" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="L6" s="31" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="M6" s="31" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="N6" s="31" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="O6" s="31" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="P6" s="31" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="Q6" s="31" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="R6" s="32" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="S6" s="32" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="T6" s="32" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="U6" s="32" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="V6" s="32" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="W6" s="32" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="Z6" s="33" t="str">
         <f aca="false">설정!B19</f>
@@ -13226,6 +13902,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:W5" type="list">
+      <formula1>"하,중하,중,중상,상,최상"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="객관식은 1~5 사이 정수만 입력" errorStyle="stop" errorTitle="입력 오류" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:Q2 D7:Q86" type="whole">
       <formula1>1</formula1>
       <formula2>5</formula2>
@@ -13236,10 +13916,6 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:W4" type="list">
       <formula1>설정!$B$19:$B$22</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:W5" type="list">
-      <formula1>"하,중하,중,중상,상,최상"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -13272,12 +13948,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="5" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
@@ -13306,7 +13982,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -13373,7 +14049,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B3" s="26"/>
       <c r="C3" s="26"/>
@@ -13460,7 +14136,7 @@
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
@@ -13527,161 +14203,161 @@
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B5" s="26"/>
       <c r="C5" s="26"/>
       <c r="D5" s="14" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="R5" s="14" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="S5" s="14" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="V5" s="14" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="W5" s="14" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="X5" s="30" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="Y5" s="30" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="Z5" s="30" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="AA5" s="30" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="AB5" s="30" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="L6" s="31" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="M6" s="31" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="N6" s="31" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="O6" s="31" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="P6" s="31" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="Q6" s="31" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="R6" s="32" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="S6" s="32" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="T6" s="32" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="U6" s="32" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="V6" s="32" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="W6" s="32" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="Z6" s="33" t="str">
         <f aca="false">설정!B24</f>
@@ -18011,7 +18687,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18040,7 +18716,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -18067,80 +18743,80 @@
       <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="S5" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18723,7 +19399,7 @@
         <v/>
       </c>
       <c r="S13" s="5" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
@@ -23405,9 +24081,13 @@
       <formula>AND($O7&lt;&gt;"",$O7=설정!$B$9)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M7:N86" type="list">
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M7:M86" type="list">
       <formula1>설정!$A$55:$A$60</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N7:N86" type="list">
+      <formula1>설정!$A$64:$A$69</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -23443,7 +24123,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -23459,7 +24139,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -23475,40 +24155,40 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28203,7 +28883,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -28225,7 +28905,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -28247,7 +28927,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="46" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B4" s="46"/>
       <c r="C4" s="46"/>
@@ -28256,31 +28936,31 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="J5" s="4" t="str">
         <f aca="false">설정!$B$6&amp;" 정답률"</f>
@@ -28295,25 +28975,25 @@
         <v>TF3반 정답률</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="O5" s="24" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="P5" s="24" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="Q5" s="24" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="R5" s="24" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28321,7 +29001,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C6" s="47" t="str">
         <f aca="false">공수1!D4</f>
@@ -28397,7 +29077,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C7" s="47" t="str">
         <f aca="false">공수1!E4</f>
@@ -28473,7 +29153,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C8" s="47" t="str">
         <f aca="false">공수1!F4</f>
@@ -28549,7 +29229,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C9" s="47" t="str">
         <f aca="false">공수1!G4</f>
@@ -28625,7 +29305,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C10" s="47" t="str">
         <f aca="false">공수1!H4</f>
@@ -28701,7 +29381,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C11" s="47" t="str">
         <f aca="false">공수1!I4</f>
@@ -28777,7 +29457,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C12" s="47" t="str">
         <f aca="false">공수1!J4</f>
@@ -28853,7 +29533,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C13" s="47" t="str">
         <f aca="false">공수1!K4</f>
@@ -28929,7 +29609,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C14" s="47" t="str">
         <f aca="false">공수1!L4</f>
@@ -29005,7 +29685,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C15" s="47" t="str">
         <f aca="false">공수1!M4</f>
@@ -29081,7 +29761,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C16" s="47" t="str">
         <f aca="false">공수1!N4</f>
@@ -29157,7 +29837,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C17" s="47" t="str">
         <f aca="false">공수1!O4</f>
@@ -29233,7 +29913,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C18" s="47" t="str">
         <f aca="false">공수1!P4</f>
@@ -29309,7 +29989,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C19" s="47" t="str">
         <f aca="false">공수1!Q4</f>
@@ -29385,7 +30065,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C20" s="47" t="str">
         <f aca="false">공수1!R4</f>
@@ -29436,19 +30116,19 @@
         <v/>
       </c>
       <c r="O20" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="P20" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Q20" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="R20" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="S20" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29456,7 +30136,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C21" s="47" t="str">
         <f aca="false">공수1!S4</f>
@@ -29507,19 +30187,19 @@
         <v/>
       </c>
       <c r="O21" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="P21" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Q21" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="R21" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="S21" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29527,7 +30207,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C22" s="47" t="str">
         <f aca="false">공수1!T4</f>
@@ -29578,19 +30258,19 @@
         <v/>
       </c>
       <c r="O22" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="P22" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Q22" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="R22" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="S22" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29598,7 +30278,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C23" s="47" t="str">
         <f aca="false">공수1!U4</f>
@@ -29649,19 +30329,19 @@
         <v/>
       </c>
       <c r="O23" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="P23" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Q23" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="R23" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="S23" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29669,7 +30349,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C24" s="47" t="str">
         <f aca="false">공수1!V4</f>
@@ -29720,19 +30400,19 @@
         <v/>
       </c>
       <c r="O24" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="P24" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Q24" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="R24" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="S24" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29740,7 +30420,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C25" s="47" t="str">
         <f aca="false">공수1!W4</f>
@@ -29791,24 +30471,24 @@
         <v/>
       </c>
       <c r="O25" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="P25" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Q25" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="R25" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="S25" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="46" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B28" s="46"/>
       <c r="C28" s="46"/>
@@ -29817,31 +30497,31 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="J29" s="4" t="str">
         <f aca="false">설정!$B$6&amp;" 정답률"</f>
@@ -29856,25 +30536,25 @@
         <v>TF3반 정답률</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="O29" s="24" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="P29" s="24" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="Q29" s="24" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="R29" s="24" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="S29" s="24" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29882,7 +30562,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C30" s="47" t="str">
         <f aca="false">공수2!D4</f>
@@ -29958,7 +30638,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C31" s="47" t="str">
         <f aca="false">공수2!E4</f>
@@ -30034,7 +30714,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C32" s="47" t="str">
         <f aca="false">공수2!F4</f>
@@ -30110,7 +30790,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C33" s="47" t="str">
         <f aca="false">공수2!G4</f>
@@ -30186,7 +30866,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C34" s="47" t="str">
         <f aca="false">공수2!H4</f>
@@ -30262,7 +30942,7 @@
         <v>6</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C35" s="47" t="str">
         <f aca="false">공수2!I4</f>
@@ -30338,7 +31018,7 @@
         <v>7</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C36" s="47" t="str">
         <f aca="false">공수2!J4</f>
@@ -30414,7 +31094,7 @@
         <v>8</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C37" s="47" t="str">
         <f aca="false">공수2!K4</f>
@@ -30490,7 +31170,7 @@
         <v>9</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C38" s="47" t="str">
         <f aca="false">공수2!L4</f>
@@ -30566,7 +31246,7 @@
         <v>10</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C39" s="47" t="str">
         <f aca="false">공수2!M4</f>
@@ -30642,7 +31322,7 @@
         <v>11</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C40" s="47" t="str">
         <f aca="false">공수2!N4</f>
@@ -30718,7 +31398,7 @@
         <v>12</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C41" s="47" t="str">
         <f aca="false">공수2!O4</f>
@@ -30794,7 +31474,7 @@
         <v>13</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C42" s="47" t="str">
         <f aca="false">공수2!P4</f>
@@ -30870,7 +31550,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C43" s="47" t="str">
         <f aca="false">공수2!Q4</f>
@@ -30946,7 +31626,7 @@
         <v>15</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C44" s="47" t="str">
         <f aca="false">공수2!R4</f>
@@ -30997,19 +31677,19 @@
         <v/>
       </c>
       <c r="O44" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="P44" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Q44" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="R44" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="S44" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31017,7 +31697,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C45" s="47" t="str">
         <f aca="false">공수2!S4</f>
@@ -31068,19 +31748,19 @@
         <v/>
       </c>
       <c r="O45" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="P45" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Q45" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="R45" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="S45" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31088,7 +31768,7 @@
         <v>17</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C46" s="47" t="str">
         <f aca="false">공수2!T4</f>
@@ -31139,19 +31819,19 @@
         <v/>
       </c>
       <c r="O46" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="P46" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Q46" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="R46" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="S46" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31159,7 +31839,7 @@
         <v>18</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C47" s="47" t="str">
         <f aca="false">공수2!U4</f>
@@ -31210,19 +31890,19 @@
         <v/>
       </c>
       <c r="O47" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="P47" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Q47" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="R47" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="S47" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31230,7 +31910,7 @@
         <v>19</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C48" s="47" t="str">
         <f aca="false">공수2!V4</f>
@@ -31281,19 +31961,19 @@
         <v/>
       </c>
       <c r="O48" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="P48" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Q48" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="R48" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="S48" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31301,7 +31981,7 @@
         <v>20</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C49" s="47" t="str">
         <f aca="false">공수2!W4</f>
@@ -31352,19 +32032,19 @@
         <v/>
       </c>
       <c r="O49" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="P49" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Q49" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="R49" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="S49" s="53" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="192">
   <si>
     <r>
       <rPr>
@@ -3251,106 +3251,6 @@
     <t xml:space="preserve">선행 과목반 이름</t>
   </si>
   <si>
-    <t xml:space="preserve">대수반</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지수와 로그</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지수함수와 로그함수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">삼각함수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수열을 선행하는 반으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">공통수학을 마친 학생이 다음 단계로 나아가기 좋은 과정입니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -3358,7 +3258,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">← 실제 운영하는 선행반 이름</t>
+      <t xml:space="preserve">← 선행 과목반 이름</t>
     </r>
     <r>
       <rPr>
@@ -3377,7 +3277,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">소개로 수정</t>
+      <t xml:space="preserve">소개가 정해지면 입력</t>
     </r>
     <r>
       <rPr>
@@ -3387,7 +3287,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -3396,169 +3296,83 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">빈 줄에 추가 가능</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">미적분Ⅰ반</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">함수의 극한과 연속</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t xml:space="preserve">예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">미분</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t xml:space="preserve">대수반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">적분을 선행하는 반으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t xml:space="preserve">비어 있어도 보고서는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">대수 학습을 마친 학생에게 권장하는 과정입니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t xml:space="preserve">상담을 통해 안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">확률과 통계반</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">순열과 조합</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확률</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">통계를 선행하는 반으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">공통수학의 경우의 수를 바탕으로 개념을 넓혀 가는 과정입니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
+      <t xml:space="preserve">로 표시</t>
     </r>
   </si>
   <si>
@@ -7694,40 +7508,28 @@
       <c r="E63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="7"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="B64" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="C64" s="20"/>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="13" t="s">
-        <v>92</v>
-      </c>
     </row>
     <row r="65" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B65" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
+      <c r="A65" s="7"/>
+      <c r="B65" s="19"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
     </row>
     <row r="66" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B66" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="C66" s="20"/>
-      <c r="D66" s="20"/>
-      <c r="E66" s="20"/>
+      <c r="A66" s="7"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
     </row>
     <row r="67" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7"/>
@@ -7824,7 +7626,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7836,7 +7638,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7848,28 +7650,28 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7877,25 +7679,25 @@
         <v>1</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H7" s="25" t="s">
         <v>107</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8886,12 +8688,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
@@ -8921,7 +8723,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -8988,7 +8790,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B3" s="26"/>
       <c r="C3" s="26"/>
@@ -9079,7 +8881,7 @@
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
@@ -9146,164 +8948,164 @@
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B5" s="26"/>
       <c r="C5" s="26"/>
       <c r="D5" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q5" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="R5" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="S5" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="T5" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="U5" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="V5" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="W5" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="X5" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="G5" s="14" t="s">
+      <c r="Y5" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="Z5" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="AA5" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="J5" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="O5" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="P5" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q5" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="R5" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="S5" s="14" t="s">
+      <c r="AB5" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="T5" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="U5" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="V5" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="W5" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="X5" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y5" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="Z5" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA5" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="AB5" s="30" t="s">
-        <v>127</v>
-      </c>
       <c r="AC5" s="30" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D6" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="J6" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="K6" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="L6" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="M6" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="H6" s="31" t="s">
+      <c r="N6" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="I6" s="31" t="s">
+      <c r="O6" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="J6" s="31" t="s">
+      <c r="P6" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="K6" s="31" t="s">
+      <c r="Q6" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="L6" s="31" t="s">
+      <c r="R6" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="M6" s="31" t="s">
+      <c r="S6" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="N6" s="31" t="s">
+      <c r="T6" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="O6" s="31" t="s">
+      <c r="U6" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="P6" s="31" t="s">
+      <c r="V6" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="Q6" s="31" t="s">
+      <c r="W6" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="R6" s="32" t="s">
+      <c r="X6" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="S6" s="32" t="s">
+      <c r="Y6" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="T6" s="32" t="s">
-        <v>144</v>
-      </c>
-      <c r="U6" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="V6" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="W6" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="X6" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>149</v>
       </c>
       <c r="Z6" s="33" t="str">
         <f aca="false">설정!B19</f>
@@ -13902,10 +13704,6 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:W5" type="list">
-      <formula1>"하,중하,중,중상,상,최상"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="객관식은 1~5 사이 정수만 입력" errorStyle="stop" errorTitle="입력 오류" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:Q2 D7:Q86" type="whole">
       <formula1>1</formula1>
       <formula2>5</formula2>
@@ -13916,6 +13714,10 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:W4" type="list">
       <formula1>설정!$B$19:$B$22</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:W5" type="list">
+      <formula1>"하,중하,중,중상,상,최상"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -13948,12 +13750,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
@@ -13982,7 +13784,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -14049,7 +13851,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B3" s="26"/>
       <c r="C3" s="26"/>
@@ -14136,7 +13938,7 @@
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
@@ -14203,161 +14005,161 @@
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B5" s="26"/>
       <c r="C5" s="26"/>
       <c r="D5" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q5" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="R5" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="S5" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="T5" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="U5" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="V5" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="W5" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="X5" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="G5" s="14" t="s">
+      <c r="Y5" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="Z5" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="AA5" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="J5" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="O5" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="P5" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q5" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="R5" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="S5" s="14" t="s">
+      <c r="AB5" s="30" t="s">
         <v>121</v>
-      </c>
-      <c r="T5" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="U5" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="V5" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="W5" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="X5" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y5" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="Z5" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA5" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="AB5" s="30" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D6" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="J6" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="K6" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="L6" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="M6" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="H6" s="31" t="s">
+      <c r="N6" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="I6" s="31" t="s">
+      <c r="O6" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="J6" s="31" t="s">
+      <c r="P6" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="K6" s="31" t="s">
+      <c r="Q6" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="L6" s="31" t="s">
+      <c r="R6" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="M6" s="31" t="s">
+      <c r="S6" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="N6" s="31" t="s">
+      <c r="T6" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="O6" s="31" t="s">
+      <c r="U6" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="P6" s="31" t="s">
+      <c r="V6" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="Q6" s="31" t="s">
+      <c r="W6" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="R6" s="32" t="s">
+      <c r="X6" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="S6" s="32" t="s">
+      <c r="Y6" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="T6" s="32" t="s">
-        <v>144</v>
-      </c>
-      <c r="U6" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="V6" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="W6" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="X6" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>149</v>
       </c>
       <c r="Z6" s="33" t="str">
         <f aca="false">설정!B24</f>
@@ -18687,7 +18489,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18716,7 +18518,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -18745,78 +18547,78 @@
     </row>
     <row r="5" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="S5" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="M6" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="N6" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="P6" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="S6" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="T6" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="U6" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="V6" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="W6" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="X6" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="S6" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="U6" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="V6" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="W6" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="X6" s="4" t="s">
-        <v>170</v>
-      </c>
       <c r="Y6" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19399,7 +19201,7 @@
         <v/>
       </c>
       <c r="S13" s="5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
@@ -24123,7 +23925,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -24139,7 +23941,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -24155,40 +23957,40 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28883,7 +28685,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -28905,7 +28707,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -28927,7 +28729,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="46" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B4" s="46"/>
       <c r="C4" s="46"/>
@@ -28936,31 +28738,31 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="J5" s="4" t="str">
         <f aca="false">설정!$B$6&amp;" 정답률"</f>
@@ -28975,25 +28777,25 @@
         <v>TF3반 정답률</v>
       </c>
       <c r="M5" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="O5" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="P5" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q5" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="R5" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="S5" s="24" t="s">
         <v>187</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="O5" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="P5" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q5" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="R5" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="S5" s="24" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29001,7 +28803,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C6" s="47" t="str">
         <f aca="false">공수1!D4</f>
@@ -29077,7 +28879,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C7" s="47" t="str">
         <f aca="false">공수1!E4</f>
@@ -29153,7 +28955,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C8" s="47" t="str">
         <f aca="false">공수1!F4</f>
@@ -29229,7 +29031,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C9" s="47" t="str">
         <f aca="false">공수1!G4</f>
@@ -29305,7 +29107,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C10" s="47" t="str">
         <f aca="false">공수1!H4</f>
@@ -29381,7 +29183,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C11" s="47" t="str">
         <f aca="false">공수1!I4</f>
@@ -29457,7 +29259,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C12" s="47" t="str">
         <f aca="false">공수1!J4</f>
@@ -29533,7 +29335,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C13" s="47" t="str">
         <f aca="false">공수1!K4</f>
@@ -29609,7 +29411,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C14" s="47" t="str">
         <f aca="false">공수1!L4</f>
@@ -29685,7 +29487,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C15" s="47" t="str">
         <f aca="false">공수1!M4</f>
@@ -29761,7 +29563,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C16" s="47" t="str">
         <f aca="false">공수1!N4</f>
@@ -29837,7 +29639,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C17" s="47" t="str">
         <f aca="false">공수1!O4</f>
@@ -29913,7 +29715,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C18" s="47" t="str">
         <f aca="false">공수1!P4</f>
@@ -29989,7 +29791,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C19" s="47" t="str">
         <f aca="false">공수1!Q4</f>
@@ -30065,7 +29867,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C20" s="47" t="str">
         <f aca="false">공수1!R4</f>
@@ -30116,19 +29918,19 @@
         <v/>
       </c>
       <c r="O20" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P20" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q20" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="R20" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="S20" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30136,7 +29938,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C21" s="47" t="str">
         <f aca="false">공수1!S4</f>
@@ -30187,19 +29989,19 @@
         <v/>
       </c>
       <c r="O21" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P21" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q21" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="R21" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="S21" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30207,7 +30009,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C22" s="47" t="str">
         <f aca="false">공수1!T4</f>
@@ -30258,19 +30060,19 @@
         <v/>
       </c>
       <c r="O22" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P22" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q22" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="R22" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="S22" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30278,7 +30080,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C23" s="47" t="str">
         <f aca="false">공수1!U4</f>
@@ -30329,19 +30131,19 @@
         <v/>
       </c>
       <c r="O23" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P23" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q23" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="R23" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="S23" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30349,7 +30151,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C24" s="47" t="str">
         <f aca="false">공수1!V4</f>
@@ -30400,19 +30202,19 @@
         <v/>
       </c>
       <c r="O24" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P24" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q24" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="R24" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="S24" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30420,7 +30222,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C25" s="47" t="str">
         <f aca="false">공수1!W4</f>
@@ -30471,24 +30273,24 @@
         <v/>
       </c>
       <c r="O25" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P25" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q25" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="R25" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="S25" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="46" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B28" s="46"/>
       <c r="C28" s="46"/>
@@ -30497,31 +30299,31 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="J29" s="4" t="str">
         <f aca="false">설정!$B$6&amp;" 정답률"</f>
@@ -30536,25 +30338,25 @@
         <v>TF3반 정답률</v>
       </c>
       <c r="M29" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="O29" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="P29" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q29" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="R29" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="S29" s="24" t="s">
         <v>187</v>
-      </c>
-      <c r="N29" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="O29" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="P29" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q29" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="R29" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="S29" s="24" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30562,7 +30364,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C30" s="47" t="str">
         <f aca="false">공수2!D4</f>
@@ -30638,7 +30440,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C31" s="47" t="str">
         <f aca="false">공수2!E4</f>
@@ -30714,7 +30516,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C32" s="47" t="str">
         <f aca="false">공수2!F4</f>
@@ -30790,7 +30592,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C33" s="47" t="str">
         <f aca="false">공수2!G4</f>
@@ -30866,7 +30668,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C34" s="47" t="str">
         <f aca="false">공수2!H4</f>
@@ -30942,7 +30744,7 @@
         <v>6</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C35" s="47" t="str">
         <f aca="false">공수2!I4</f>
@@ -31018,7 +30820,7 @@
         <v>7</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C36" s="47" t="str">
         <f aca="false">공수2!J4</f>
@@ -31094,7 +30896,7 @@
         <v>8</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C37" s="47" t="str">
         <f aca="false">공수2!K4</f>
@@ -31170,7 +30972,7 @@
         <v>9</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C38" s="47" t="str">
         <f aca="false">공수2!L4</f>
@@ -31246,7 +31048,7 @@
         <v>10</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C39" s="47" t="str">
         <f aca="false">공수2!M4</f>
@@ -31322,7 +31124,7 @@
         <v>11</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C40" s="47" t="str">
         <f aca="false">공수2!N4</f>
@@ -31398,7 +31200,7 @@
         <v>12</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C41" s="47" t="str">
         <f aca="false">공수2!O4</f>
@@ -31474,7 +31276,7 @@
         <v>13</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C42" s="47" t="str">
         <f aca="false">공수2!P4</f>
@@ -31550,7 +31352,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C43" s="47" t="str">
         <f aca="false">공수2!Q4</f>
@@ -31626,7 +31428,7 @@
         <v>15</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C44" s="47" t="str">
         <f aca="false">공수2!R4</f>
@@ -31677,19 +31479,19 @@
         <v/>
       </c>
       <c r="O44" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P44" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q44" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="R44" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="S44" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31697,7 +31499,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C45" s="47" t="str">
         <f aca="false">공수2!S4</f>
@@ -31748,19 +31550,19 @@
         <v/>
       </c>
       <c r="O45" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P45" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q45" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="R45" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="S45" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31768,7 +31570,7 @@
         <v>17</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C46" s="47" t="str">
         <f aca="false">공수2!T4</f>
@@ -31819,19 +31621,19 @@
         <v/>
       </c>
       <c r="O46" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P46" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q46" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="R46" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="S46" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31839,7 +31641,7 @@
         <v>18</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C47" s="47" t="str">
         <f aca="false">공수2!U4</f>
@@ -31890,19 +31692,19 @@
         <v/>
       </c>
       <c r="O47" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P47" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q47" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="R47" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="S47" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31910,7 +31712,7 @@
         <v>19</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C48" s="47" t="str">
         <f aca="false">공수2!V4</f>
@@ -31961,19 +31763,19 @@
         <v/>
       </c>
       <c r="O48" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P48" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q48" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="R48" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="S48" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31981,7 +31783,7 @@
         <v>20</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C49" s="47" t="str">
         <f aca="false">공수2!W4</f>
@@ -32032,19 +31834,19 @@
         <v/>
       </c>
       <c r="O49" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P49" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q49" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="R49" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="S49" s="53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -3000,7 +3000,7 @@
       </c>
       <c r="I4" s="21" t="inlineStr">
         <is>
-          <t>행렬</t>
+          <t>경우의 수</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t>행렬</t>
+          <t>방정식과 부등식</t>
         </is>
       </c>
       <c r="M4" s="21" t="inlineStr">

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -2870,7 +2870,7 @@
         <v>76</v>
       </c>
       <c r="V2" s="19" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="W2" s="19" t="n">
         <v>65</v>
@@ -3000,72 +3000,72 @@
       </c>
       <c r="I4" s="21" t="inlineStr">
         <is>
+          <t>방정식과 부등식</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>방정식과 부등식</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
           <t>경우의 수</t>
         </is>
       </c>
-      <c r="J4" s="21" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t>방정식과 부등식</t>
         </is>
       </c>
-      <c r="K4" s="21" t="inlineStr">
+      <c r="M4" s="21" t="inlineStr">
+        <is>
+          <t>행렬</t>
+        </is>
+      </c>
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t>경우의 수</t>
         </is>
       </c>
-      <c r="L4" s="21" t="inlineStr">
+      <c r="O4" s="21" t="inlineStr">
         <is>
           <t>방정식과 부등식</t>
         </is>
       </c>
-      <c r="M4" s="21" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t>다항식</t>
+        </is>
+      </c>
+      <c r="Q4" s="21" t="inlineStr">
+        <is>
+          <t>방정식과 부등식</t>
+        </is>
+      </c>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t>방정식과 부등식</t>
+        </is>
+      </c>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>경우의 수</t>
+        </is>
+      </c>
+      <c r="T4" s="21" t="inlineStr">
+        <is>
+          <t>다항식</t>
+        </is>
+      </c>
+      <c r="U4" s="21" t="inlineStr">
         <is>
           <t>행렬</t>
         </is>
       </c>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t>경우의 수</t>
-        </is>
-      </c>
-      <c r="O4" s="21" t="inlineStr">
+      <c r="V4" s="21" t="inlineStr">
         <is>
           <t>방정식과 부등식</t>
-        </is>
-      </c>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t>다항식</t>
-        </is>
-      </c>
-      <c r="Q4" s="21" t="inlineStr">
-        <is>
-          <t>방정식과 부등식</t>
-        </is>
-      </c>
-      <c r="R4" s="21" t="inlineStr">
-        <is>
-          <t>방정식과 부등식</t>
-        </is>
-      </c>
-      <c r="S4" s="21" t="inlineStr">
-        <is>
-          <t>경우의 수</t>
-        </is>
-      </c>
-      <c r="T4" s="21" t="inlineStr">
-        <is>
-          <t>다항식</t>
-        </is>
-      </c>
-      <c r="U4" s="21" t="inlineStr">
-        <is>
-          <t>행렬</t>
-        </is>
-      </c>
-      <c r="V4" s="21" t="inlineStr">
-        <is>
-          <t>경우의 수</t>
         </is>
       </c>
       <c r="W4" s="21" t="inlineStr">

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -246,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -299,6 +299,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2805,7 +2808,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>① 2~5행(노란 칸)에 정답·배점·단원·난이도 입력  ② 학생 행에 학생이 쓴 답을 그대로 입력(객관식 1~5, 단답형 0~999) → 틀린 답은 빨간 칸, 점수 자동 계산. 결시생은 비워두면 미응시 처리.</t>
+          <t>객관식 1~14번: 학생이 고른 번호(1~5, 답안지 스캔으로 자동 입력 가능)  단답형 15~20번: 직접 채점해 맞으면 1, 틀리면 0 → 틀린 칸은 빨간색, 점수 자동 계산. 결시생은 비워두면 미응시 처리.</t>
         </is>
       </c>
     </row>
@@ -2857,23 +2860,23 @@
       <c r="Q2" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="R2" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="S2" s="19" t="n">
-        <v>864</v>
-      </c>
-      <c r="T2" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="U2" s="19" t="n">
-        <v>76</v>
-      </c>
-      <c r="V2" s="19" t="n">
-        <v>27</v>
-      </c>
-      <c r="W2" s="19" t="n">
-        <v>65</v>
+      <c r="R2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" s="20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2946,7 +2949,7 @@
         <f>COUNT(D2:W2)</f>
         <v/>
       </c>
-      <c r="Y3" s="20">
+      <c r="Y3" s="21">
         <f>SUM(D3:W3)</f>
         <v/>
       </c>
@@ -2973,102 +2976,102 @@
           <t>단원 ▶</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>다항식</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="22" t="inlineStr">
         <is>
           <t>행렬</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>방정식과 부등식</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="G4" s="22" t="inlineStr">
         <is>
           <t>방정식과 부등식</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>다항식</t>
         </is>
       </c>
-      <c r="I4" s="21" t="inlineStr">
+      <c r="I4" s="22" t="inlineStr">
         <is>
           <t>방정식과 부등식</t>
         </is>
       </c>
-      <c r="J4" s="21" t="inlineStr">
+      <c r="J4" s="22" t="inlineStr">
         <is>
           <t>방정식과 부등식</t>
         </is>
       </c>
-      <c r="K4" s="21" t="inlineStr">
+      <c r="K4" s="22" t="inlineStr">
         <is>
           <t>경우의 수</t>
         </is>
       </c>
-      <c r="L4" s="21" t="inlineStr">
+      <c r="L4" s="22" t="inlineStr">
         <is>
           <t>방정식과 부등식</t>
         </is>
       </c>
-      <c r="M4" s="21" t="inlineStr">
+      <c r="M4" s="22" t="inlineStr">
         <is>
           <t>행렬</t>
         </is>
       </c>
-      <c r="N4" s="21" t="inlineStr">
+      <c r="N4" s="22" t="inlineStr">
         <is>
           <t>경우의 수</t>
         </is>
       </c>
-      <c r="O4" s="21" t="inlineStr">
+      <c r="O4" s="22" t="inlineStr">
         <is>
           <t>방정식과 부등식</t>
         </is>
       </c>
-      <c r="P4" s="21" t="inlineStr">
+      <c r="P4" s="22" t="inlineStr">
         <is>
           <t>다항식</t>
         </is>
       </c>
-      <c r="Q4" s="21" t="inlineStr">
+      <c r="Q4" s="22" t="inlineStr">
         <is>
           <t>방정식과 부등식</t>
         </is>
       </c>
-      <c r="R4" s="21" t="inlineStr">
+      <c r="R4" s="22" t="inlineStr">
         <is>
           <t>방정식과 부등식</t>
         </is>
       </c>
-      <c r="S4" s="21" t="inlineStr">
+      <c r="S4" s="22" t="inlineStr">
         <is>
           <t>경우의 수</t>
         </is>
       </c>
-      <c r="T4" s="21" t="inlineStr">
+      <c r="T4" s="22" t="inlineStr">
         <is>
           <t>다항식</t>
         </is>
       </c>
-      <c r="U4" s="21" t="inlineStr">
+      <c r="U4" s="22" t="inlineStr">
         <is>
           <t>행렬</t>
         </is>
       </c>
-      <c r="V4" s="21" t="inlineStr">
+      <c r="V4" s="22" t="inlineStr">
         <is>
           <t>방정식과 부등식</t>
         </is>
       </c>
-      <c r="W4" s="21" t="inlineStr">
+      <c r="W4" s="22" t="inlineStr">
         <is>
           <t>다항식</t>
         </is>
@@ -3180,38 +3183,38 @@
           <t>최상</t>
         </is>
       </c>
-      <c r="X5" s="22" t="inlineStr">
+      <c r="X5" s="23" t="inlineStr">
         <is>
           <t>정답입력수▲</t>
         </is>
       </c>
-      <c r="Y5" s="22" t="inlineStr">
+      <c r="Y5" s="23" t="inlineStr">
         <is>
           <t>만점 ▲</t>
         </is>
       </c>
-      <c r="Z5" s="22" t="inlineStr">
+      <c r="Z5" s="23" t="inlineStr">
         <is>
           <t>만점 ▲</t>
         </is>
       </c>
-      <c r="AA5" s="22" t="inlineStr">
+      <c r="AA5" s="23" t="inlineStr">
         <is>
           <t>만점 ▲</t>
         </is>
       </c>
-      <c r="AB5" s="22" t="inlineStr">
+      <c r="AB5" s="23" t="inlineStr">
         <is>
           <t>만점 ▲</t>
         </is>
       </c>
-      <c r="AC5" s="22" t="inlineStr">
+      <c r="AC5" s="23" t="inlineStr">
         <is>
           <t>만점 ▲</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="44" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>No</t>
@@ -3227,124 +3230,130 @@
           <t>학교</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>1
 객관식</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>2
 객관식</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>3
 객관식</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>4
 객관식</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>5
 객관식</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t>6
 객관식</t>
         </is>
       </c>
-      <c r="J6" s="23" t="inlineStr">
+      <c r="J6" s="24" t="inlineStr">
         <is>
           <t>7
 객관식</t>
         </is>
       </c>
-      <c r="K6" s="23" t="inlineStr">
+      <c r="K6" s="24" t="inlineStr">
         <is>
           <t>8
 객관식</t>
         </is>
       </c>
-      <c r="L6" s="23" t="inlineStr">
+      <c r="L6" s="24" t="inlineStr">
         <is>
           <t>9
 객관식</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M6" s="24" t="inlineStr">
         <is>
           <t>10
 객관식</t>
         </is>
       </c>
-      <c r="N6" s="23" t="inlineStr">
+      <c r="N6" s="24" t="inlineStr">
         <is>
           <t>11
 객관식</t>
         </is>
       </c>
-      <c r="O6" s="23" t="inlineStr">
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t>12
 객관식</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P6" s="24" t="inlineStr">
         <is>
           <t>13
 객관식</t>
         </is>
       </c>
-      <c r="Q6" s="23" t="inlineStr">
+      <c r="Q6" s="24" t="inlineStr">
         <is>
           <t>14
 객관식</t>
         </is>
       </c>
-      <c r="R6" s="24" t="inlineStr">
+      <c r="R6" s="25" t="inlineStr">
         <is>
           <t>15
-단답형</t>
-        </is>
-      </c>
-      <c r="S6" s="24" t="inlineStr">
+단답형
+답 24</t>
+        </is>
+      </c>
+      <c r="S6" s="25" t="inlineStr">
         <is>
           <t>16
-단답형</t>
-        </is>
-      </c>
-      <c r="T6" s="24" t="inlineStr">
+단답형
+답 864</t>
+        </is>
+      </c>
+      <c r="T6" s="25" t="inlineStr">
         <is>
           <t>17
-단답형</t>
-        </is>
-      </c>
-      <c r="U6" s="24" t="inlineStr">
+단답형
+답 8</t>
+        </is>
+      </c>
+      <c r="U6" s="25" t="inlineStr">
         <is>
           <t>18
-단답형</t>
-        </is>
-      </c>
-      <c r="V6" s="24" t="inlineStr">
+단답형
+답 76</t>
+        </is>
+      </c>
+      <c r="V6" s="25" t="inlineStr">
         <is>
           <t>19
-단답형</t>
-        </is>
-      </c>
-      <c r="W6" s="24" t="inlineStr">
+단답형
+답 27</t>
+        </is>
+      </c>
+      <c r="W6" s="25" t="inlineStr">
         <is>
           <t>20
-단답형</t>
+단답형
+답 65</t>
         </is>
       </c>
       <c r="X6" s="4" t="inlineStr">
@@ -3358,19 +3367,19 @@
           <t>총점</t>
         </is>
       </c>
-      <c r="Z6" s="25">
+      <c r="Z6" s="26">
         <f>'설정'!B19</f>
         <v/>
       </c>
-      <c r="AA6" s="25">
+      <c r="AA6" s="26">
         <f>'설정'!B20</f>
         <v/>
       </c>
-      <c r="AB6" s="25">
+      <c r="AB6" s="26">
         <f>'설정'!B21</f>
         <v/>
       </c>
-      <c r="AC6" s="25">
+      <c r="AC6" s="26">
         <f>'설정'!B22</f>
         <v/>
       </c>
@@ -3411,7 +3420,7 @@
         <f>IF(COUNTA(D7:W7)=0,"",SUMPRODUCT((D7:W7=$D$2:$W$2)*(D7:W7&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y7" s="26">
+      <c r="Y7" s="27">
         <f>IF(COUNTA(D7:W7)=0,"",SUMPRODUCT((D7:W7=$D$2:$W$2)*(D7:W7&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -3468,7 +3477,7 @@
         <f>IF(COUNTA(D8:W8)=0,"",SUMPRODUCT((D8:W8=$D$2:$W$2)*(D8:W8&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y8" s="26">
+      <c r="Y8" s="27">
         <f>IF(COUNTA(D8:W8)=0,"",SUMPRODUCT((D8:W8=$D$2:$W$2)*(D8:W8&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -3525,7 +3534,7 @@
         <f>IF(COUNTA(D9:W9)=0,"",SUMPRODUCT((D9:W9=$D$2:$W$2)*(D9:W9&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y9" s="26">
+      <c r="Y9" s="27">
         <f>IF(COUNTA(D9:W9)=0,"",SUMPRODUCT((D9:W9=$D$2:$W$2)*(D9:W9&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -3582,7 +3591,7 @@
         <f>IF(COUNTA(D10:W10)=0,"",SUMPRODUCT((D10:W10=$D$2:$W$2)*(D10:W10&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y10" s="26">
+      <c r="Y10" s="27">
         <f>IF(COUNTA(D10:W10)=0,"",SUMPRODUCT((D10:W10=$D$2:$W$2)*(D10:W10&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -3639,7 +3648,7 @@
         <f>IF(COUNTA(D11:W11)=0,"",SUMPRODUCT((D11:W11=$D$2:$W$2)*(D11:W11&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y11" s="26">
+      <c r="Y11" s="27">
         <f>IF(COUNTA(D11:W11)=0,"",SUMPRODUCT((D11:W11=$D$2:$W$2)*(D11:W11&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -3696,7 +3705,7 @@
         <f>IF(COUNTA(D12:W12)=0,"",SUMPRODUCT((D12:W12=$D$2:$W$2)*(D12:W12&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y12" s="26">
+      <c r="Y12" s="27">
         <f>IF(COUNTA(D12:W12)=0,"",SUMPRODUCT((D12:W12=$D$2:$W$2)*(D12:W12&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -3753,7 +3762,7 @@
         <f>IF(COUNTA(D13:W13)=0,"",SUMPRODUCT((D13:W13=$D$2:$W$2)*(D13:W13&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y13" s="26">
+      <c r="Y13" s="27">
         <f>IF(COUNTA(D13:W13)=0,"",SUMPRODUCT((D13:W13=$D$2:$W$2)*(D13:W13&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -3810,7 +3819,7 @@
         <f>IF(COUNTA(D14:W14)=0,"",SUMPRODUCT((D14:W14=$D$2:$W$2)*(D14:W14&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y14" s="26">
+      <c r="Y14" s="27">
         <f>IF(COUNTA(D14:W14)=0,"",SUMPRODUCT((D14:W14=$D$2:$W$2)*(D14:W14&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -3867,7 +3876,7 @@
         <f>IF(COUNTA(D15:W15)=0,"",SUMPRODUCT((D15:W15=$D$2:$W$2)*(D15:W15&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y15" s="26">
+      <c r="Y15" s="27">
         <f>IF(COUNTA(D15:W15)=0,"",SUMPRODUCT((D15:W15=$D$2:$W$2)*(D15:W15&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -3924,7 +3933,7 @@
         <f>IF(COUNTA(D16:W16)=0,"",SUMPRODUCT((D16:W16=$D$2:$W$2)*(D16:W16&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y16" s="26">
+      <c r="Y16" s="27">
         <f>IF(COUNTA(D16:W16)=0,"",SUMPRODUCT((D16:W16=$D$2:$W$2)*(D16:W16&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -3981,7 +3990,7 @@
         <f>IF(COUNTA(D17:W17)=0,"",SUMPRODUCT((D17:W17=$D$2:$W$2)*(D17:W17&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y17" s="26">
+      <c r="Y17" s="27">
         <f>IF(COUNTA(D17:W17)=0,"",SUMPRODUCT((D17:W17=$D$2:$W$2)*(D17:W17&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4038,7 +4047,7 @@
         <f>IF(COUNTA(D18:W18)=0,"",SUMPRODUCT((D18:W18=$D$2:$W$2)*(D18:W18&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y18" s="26">
+      <c r="Y18" s="27">
         <f>IF(COUNTA(D18:W18)=0,"",SUMPRODUCT((D18:W18=$D$2:$W$2)*(D18:W18&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4095,7 +4104,7 @@
         <f>IF(COUNTA(D19:W19)=0,"",SUMPRODUCT((D19:W19=$D$2:$W$2)*(D19:W19&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y19" s="26">
+      <c r="Y19" s="27">
         <f>IF(COUNTA(D19:W19)=0,"",SUMPRODUCT((D19:W19=$D$2:$W$2)*(D19:W19&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4152,7 +4161,7 @@
         <f>IF(COUNTA(D20:W20)=0,"",SUMPRODUCT((D20:W20=$D$2:$W$2)*(D20:W20&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y20" s="26">
+      <c r="Y20" s="27">
         <f>IF(COUNTA(D20:W20)=0,"",SUMPRODUCT((D20:W20=$D$2:$W$2)*(D20:W20&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4209,7 +4218,7 @@
         <f>IF(COUNTA(D21:W21)=0,"",SUMPRODUCT((D21:W21=$D$2:$W$2)*(D21:W21&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y21" s="26">
+      <c r="Y21" s="27">
         <f>IF(COUNTA(D21:W21)=0,"",SUMPRODUCT((D21:W21=$D$2:$W$2)*(D21:W21&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4266,7 +4275,7 @@
         <f>IF(COUNTA(D22:W22)=0,"",SUMPRODUCT((D22:W22=$D$2:$W$2)*(D22:W22&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y22" s="26">
+      <c r="Y22" s="27">
         <f>IF(COUNTA(D22:W22)=0,"",SUMPRODUCT((D22:W22=$D$2:$W$2)*(D22:W22&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4323,7 +4332,7 @@
         <f>IF(COUNTA(D23:W23)=0,"",SUMPRODUCT((D23:W23=$D$2:$W$2)*(D23:W23&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y23" s="26">
+      <c r="Y23" s="27">
         <f>IF(COUNTA(D23:W23)=0,"",SUMPRODUCT((D23:W23=$D$2:$W$2)*(D23:W23&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4380,7 +4389,7 @@
         <f>IF(COUNTA(D24:W24)=0,"",SUMPRODUCT((D24:W24=$D$2:$W$2)*(D24:W24&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y24" s="26">
+      <c r="Y24" s="27">
         <f>IF(COUNTA(D24:W24)=0,"",SUMPRODUCT((D24:W24=$D$2:$W$2)*(D24:W24&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4437,7 +4446,7 @@
         <f>IF(COUNTA(D25:W25)=0,"",SUMPRODUCT((D25:W25=$D$2:$W$2)*(D25:W25&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y25" s="26">
+      <c r="Y25" s="27">
         <f>IF(COUNTA(D25:W25)=0,"",SUMPRODUCT((D25:W25=$D$2:$W$2)*(D25:W25&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4494,7 +4503,7 @@
         <f>IF(COUNTA(D26:W26)=0,"",SUMPRODUCT((D26:W26=$D$2:$W$2)*(D26:W26&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y26" s="26">
+      <c r="Y26" s="27">
         <f>IF(COUNTA(D26:W26)=0,"",SUMPRODUCT((D26:W26=$D$2:$W$2)*(D26:W26&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4551,7 +4560,7 @@
         <f>IF(COUNTA(D27:W27)=0,"",SUMPRODUCT((D27:W27=$D$2:$W$2)*(D27:W27&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y27" s="26">
+      <c r="Y27" s="27">
         <f>IF(COUNTA(D27:W27)=0,"",SUMPRODUCT((D27:W27=$D$2:$W$2)*(D27:W27&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4608,7 +4617,7 @@
         <f>IF(COUNTA(D28:W28)=0,"",SUMPRODUCT((D28:W28=$D$2:$W$2)*(D28:W28&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y28" s="26">
+      <c r="Y28" s="27">
         <f>IF(COUNTA(D28:W28)=0,"",SUMPRODUCT((D28:W28=$D$2:$W$2)*(D28:W28&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4665,7 +4674,7 @@
         <f>IF(COUNTA(D29:W29)=0,"",SUMPRODUCT((D29:W29=$D$2:$W$2)*(D29:W29&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y29" s="26">
+      <c r="Y29" s="27">
         <f>IF(COUNTA(D29:W29)=0,"",SUMPRODUCT((D29:W29=$D$2:$W$2)*(D29:W29&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4722,7 +4731,7 @@
         <f>IF(COUNTA(D30:W30)=0,"",SUMPRODUCT((D30:W30=$D$2:$W$2)*(D30:W30&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y30" s="26">
+      <c r="Y30" s="27">
         <f>IF(COUNTA(D30:W30)=0,"",SUMPRODUCT((D30:W30=$D$2:$W$2)*(D30:W30&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4779,7 +4788,7 @@
         <f>IF(COUNTA(D31:W31)=0,"",SUMPRODUCT((D31:W31=$D$2:$W$2)*(D31:W31&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y31" s="26">
+      <c r="Y31" s="27">
         <f>IF(COUNTA(D31:W31)=0,"",SUMPRODUCT((D31:W31=$D$2:$W$2)*(D31:W31&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4836,7 +4845,7 @@
         <f>IF(COUNTA(D32:W32)=0,"",SUMPRODUCT((D32:W32=$D$2:$W$2)*(D32:W32&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y32" s="26">
+      <c r="Y32" s="27">
         <f>IF(COUNTA(D32:W32)=0,"",SUMPRODUCT((D32:W32=$D$2:$W$2)*(D32:W32&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4893,7 +4902,7 @@
         <f>IF(COUNTA(D33:W33)=0,"",SUMPRODUCT((D33:W33=$D$2:$W$2)*(D33:W33&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y33" s="26">
+      <c r="Y33" s="27">
         <f>IF(COUNTA(D33:W33)=0,"",SUMPRODUCT((D33:W33=$D$2:$W$2)*(D33:W33&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -4950,7 +4959,7 @@
         <f>IF(COUNTA(D34:W34)=0,"",SUMPRODUCT((D34:W34=$D$2:$W$2)*(D34:W34&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y34" s="26">
+      <c r="Y34" s="27">
         <f>IF(COUNTA(D34:W34)=0,"",SUMPRODUCT((D34:W34=$D$2:$W$2)*(D34:W34&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5007,7 +5016,7 @@
         <f>IF(COUNTA(D35:W35)=0,"",SUMPRODUCT((D35:W35=$D$2:$W$2)*(D35:W35&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y35" s="26">
+      <c r="Y35" s="27">
         <f>IF(COUNTA(D35:W35)=0,"",SUMPRODUCT((D35:W35=$D$2:$W$2)*(D35:W35&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5064,7 +5073,7 @@
         <f>IF(COUNTA(D36:W36)=0,"",SUMPRODUCT((D36:W36=$D$2:$W$2)*(D36:W36&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y36" s="26">
+      <c r="Y36" s="27">
         <f>IF(COUNTA(D36:W36)=0,"",SUMPRODUCT((D36:W36=$D$2:$W$2)*(D36:W36&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5121,7 +5130,7 @@
         <f>IF(COUNTA(D37:W37)=0,"",SUMPRODUCT((D37:W37=$D$2:$W$2)*(D37:W37&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y37" s="26">
+      <c r="Y37" s="27">
         <f>IF(COUNTA(D37:W37)=0,"",SUMPRODUCT((D37:W37=$D$2:$W$2)*(D37:W37&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5178,7 +5187,7 @@
         <f>IF(COUNTA(D38:W38)=0,"",SUMPRODUCT((D38:W38=$D$2:$W$2)*(D38:W38&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y38" s="26">
+      <c r="Y38" s="27">
         <f>IF(COUNTA(D38:W38)=0,"",SUMPRODUCT((D38:W38=$D$2:$W$2)*(D38:W38&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5235,7 +5244,7 @@
         <f>IF(COUNTA(D39:W39)=0,"",SUMPRODUCT((D39:W39=$D$2:$W$2)*(D39:W39&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y39" s="26">
+      <c r="Y39" s="27">
         <f>IF(COUNTA(D39:W39)=0,"",SUMPRODUCT((D39:W39=$D$2:$W$2)*(D39:W39&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5292,7 +5301,7 @@
         <f>IF(COUNTA(D40:W40)=0,"",SUMPRODUCT((D40:W40=$D$2:$W$2)*(D40:W40&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y40" s="26">
+      <c r="Y40" s="27">
         <f>IF(COUNTA(D40:W40)=0,"",SUMPRODUCT((D40:W40=$D$2:$W$2)*(D40:W40&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5349,7 +5358,7 @@
         <f>IF(COUNTA(D41:W41)=0,"",SUMPRODUCT((D41:W41=$D$2:$W$2)*(D41:W41&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y41" s="26">
+      <c r="Y41" s="27">
         <f>IF(COUNTA(D41:W41)=0,"",SUMPRODUCT((D41:W41=$D$2:$W$2)*(D41:W41&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5406,7 +5415,7 @@
         <f>IF(COUNTA(D42:W42)=0,"",SUMPRODUCT((D42:W42=$D$2:$W$2)*(D42:W42&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y42" s="26">
+      <c r="Y42" s="27">
         <f>IF(COUNTA(D42:W42)=0,"",SUMPRODUCT((D42:W42=$D$2:$W$2)*(D42:W42&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5463,7 +5472,7 @@
         <f>IF(COUNTA(D43:W43)=0,"",SUMPRODUCT((D43:W43=$D$2:$W$2)*(D43:W43&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y43" s="26">
+      <c r="Y43" s="27">
         <f>IF(COUNTA(D43:W43)=0,"",SUMPRODUCT((D43:W43=$D$2:$W$2)*(D43:W43&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5520,7 +5529,7 @@
         <f>IF(COUNTA(D44:W44)=0,"",SUMPRODUCT((D44:W44=$D$2:$W$2)*(D44:W44&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y44" s="26">
+      <c r="Y44" s="27">
         <f>IF(COUNTA(D44:W44)=0,"",SUMPRODUCT((D44:W44=$D$2:$W$2)*(D44:W44&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5577,7 +5586,7 @@
         <f>IF(COUNTA(D45:W45)=0,"",SUMPRODUCT((D45:W45=$D$2:$W$2)*(D45:W45&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y45" s="26">
+      <c r="Y45" s="27">
         <f>IF(COUNTA(D45:W45)=0,"",SUMPRODUCT((D45:W45=$D$2:$W$2)*(D45:W45&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5634,7 +5643,7 @@
         <f>IF(COUNTA(D46:W46)=0,"",SUMPRODUCT((D46:W46=$D$2:$W$2)*(D46:W46&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y46" s="26">
+      <c r="Y46" s="27">
         <f>IF(COUNTA(D46:W46)=0,"",SUMPRODUCT((D46:W46=$D$2:$W$2)*(D46:W46&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5691,7 +5700,7 @@
         <f>IF(COUNTA(D47:W47)=0,"",SUMPRODUCT((D47:W47=$D$2:$W$2)*(D47:W47&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y47" s="26">
+      <c r="Y47" s="27">
         <f>IF(COUNTA(D47:W47)=0,"",SUMPRODUCT((D47:W47=$D$2:$W$2)*(D47:W47&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5748,7 +5757,7 @@
         <f>IF(COUNTA(D48:W48)=0,"",SUMPRODUCT((D48:W48=$D$2:$W$2)*(D48:W48&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y48" s="26">
+      <c r="Y48" s="27">
         <f>IF(COUNTA(D48:W48)=0,"",SUMPRODUCT((D48:W48=$D$2:$W$2)*(D48:W48&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5805,7 +5814,7 @@
         <f>IF(COUNTA(D49:W49)=0,"",SUMPRODUCT((D49:W49=$D$2:$W$2)*(D49:W49&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y49" s="26">
+      <c r="Y49" s="27">
         <f>IF(COUNTA(D49:W49)=0,"",SUMPRODUCT((D49:W49=$D$2:$W$2)*(D49:W49&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5862,7 +5871,7 @@
         <f>IF(COUNTA(D50:W50)=0,"",SUMPRODUCT((D50:W50=$D$2:$W$2)*(D50:W50&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y50" s="26">
+      <c r="Y50" s="27">
         <f>IF(COUNTA(D50:W50)=0,"",SUMPRODUCT((D50:W50=$D$2:$W$2)*(D50:W50&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5919,7 +5928,7 @@
         <f>IF(COUNTA(D51:W51)=0,"",SUMPRODUCT((D51:W51=$D$2:$W$2)*(D51:W51&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y51" s="26">
+      <c r="Y51" s="27">
         <f>IF(COUNTA(D51:W51)=0,"",SUMPRODUCT((D51:W51=$D$2:$W$2)*(D51:W51&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -5976,7 +5985,7 @@
         <f>IF(COUNTA(D52:W52)=0,"",SUMPRODUCT((D52:W52=$D$2:$W$2)*(D52:W52&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y52" s="26">
+      <c r="Y52" s="27">
         <f>IF(COUNTA(D52:W52)=0,"",SUMPRODUCT((D52:W52=$D$2:$W$2)*(D52:W52&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6033,7 +6042,7 @@
         <f>IF(COUNTA(D53:W53)=0,"",SUMPRODUCT((D53:W53=$D$2:$W$2)*(D53:W53&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y53" s="26">
+      <c r="Y53" s="27">
         <f>IF(COUNTA(D53:W53)=0,"",SUMPRODUCT((D53:W53=$D$2:$W$2)*(D53:W53&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6090,7 +6099,7 @@
         <f>IF(COUNTA(D54:W54)=0,"",SUMPRODUCT((D54:W54=$D$2:$W$2)*(D54:W54&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y54" s="26">
+      <c r="Y54" s="27">
         <f>IF(COUNTA(D54:W54)=0,"",SUMPRODUCT((D54:W54=$D$2:$W$2)*(D54:W54&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6147,7 +6156,7 @@
         <f>IF(COUNTA(D55:W55)=0,"",SUMPRODUCT((D55:W55=$D$2:$W$2)*(D55:W55&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y55" s="26">
+      <c r="Y55" s="27">
         <f>IF(COUNTA(D55:W55)=0,"",SUMPRODUCT((D55:W55=$D$2:$W$2)*(D55:W55&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6204,7 +6213,7 @@
         <f>IF(COUNTA(D56:W56)=0,"",SUMPRODUCT((D56:W56=$D$2:$W$2)*(D56:W56&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y56" s="26">
+      <c r="Y56" s="27">
         <f>IF(COUNTA(D56:W56)=0,"",SUMPRODUCT((D56:W56=$D$2:$W$2)*(D56:W56&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6261,7 +6270,7 @@
         <f>IF(COUNTA(D57:W57)=0,"",SUMPRODUCT((D57:W57=$D$2:$W$2)*(D57:W57&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y57" s="26">
+      <c r="Y57" s="27">
         <f>IF(COUNTA(D57:W57)=0,"",SUMPRODUCT((D57:W57=$D$2:$W$2)*(D57:W57&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6318,7 +6327,7 @@
         <f>IF(COUNTA(D58:W58)=0,"",SUMPRODUCT((D58:W58=$D$2:$W$2)*(D58:W58&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y58" s="26">
+      <c r="Y58" s="27">
         <f>IF(COUNTA(D58:W58)=0,"",SUMPRODUCT((D58:W58=$D$2:$W$2)*(D58:W58&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6375,7 +6384,7 @@
         <f>IF(COUNTA(D59:W59)=0,"",SUMPRODUCT((D59:W59=$D$2:$W$2)*(D59:W59&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y59" s="26">
+      <c r="Y59" s="27">
         <f>IF(COUNTA(D59:W59)=0,"",SUMPRODUCT((D59:W59=$D$2:$W$2)*(D59:W59&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6432,7 +6441,7 @@
         <f>IF(COUNTA(D60:W60)=0,"",SUMPRODUCT((D60:W60=$D$2:$W$2)*(D60:W60&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y60" s="26">
+      <c r="Y60" s="27">
         <f>IF(COUNTA(D60:W60)=0,"",SUMPRODUCT((D60:W60=$D$2:$W$2)*(D60:W60&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6489,7 +6498,7 @@
         <f>IF(COUNTA(D61:W61)=0,"",SUMPRODUCT((D61:W61=$D$2:$W$2)*(D61:W61&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y61" s="26">
+      <c r="Y61" s="27">
         <f>IF(COUNTA(D61:W61)=0,"",SUMPRODUCT((D61:W61=$D$2:$W$2)*(D61:W61&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6546,7 +6555,7 @@
         <f>IF(COUNTA(D62:W62)=0,"",SUMPRODUCT((D62:W62=$D$2:$W$2)*(D62:W62&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y62" s="26">
+      <c r="Y62" s="27">
         <f>IF(COUNTA(D62:W62)=0,"",SUMPRODUCT((D62:W62=$D$2:$W$2)*(D62:W62&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6603,7 +6612,7 @@
         <f>IF(COUNTA(D63:W63)=0,"",SUMPRODUCT((D63:W63=$D$2:$W$2)*(D63:W63&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y63" s="26">
+      <c r="Y63" s="27">
         <f>IF(COUNTA(D63:W63)=0,"",SUMPRODUCT((D63:W63=$D$2:$W$2)*(D63:W63&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6660,7 +6669,7 @@
         <f>IF(COUNTA(D64:W64)=0,"",SUMPRODUCT((D64:W64=$D$2:$W$2)*(D64:W64&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y64" s="26">
+      <c r="Y64" s="27">
         <f>IF(COUNTA(D64:W64)=0,"",SUMPRODUCT((D64:W64=$D$2:$W$2)*(D64:W64&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6717,7 +6726,7 @@
         <f>IF(COUNTA(D65:W65)=0,"",SUMPRODUCT((D65:W65=$D$2:$W$2)*(D65:W65&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y65" s="26">
+      <c r="Y65" s="27">
         <f>IF(COUNTA(D65:W65)=0,"",SUMPRODUCT((D65:W65=$D$2:$W$2)*(D65:W65&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6774,7 +6783,7 @@
         <f>IF(COUNTA(D66:W66)=0,"",SUMPRODUCT((D66:W66=$D$2:$W$2)*(D66:W66&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y66" s="26">
+      <c r="Y66" s="27">
         <f>IF(COUNTA(D66:W66)=0,"",SUMPRODUCT((D66:W66=$D$2:$W$2)*(D66:W66&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6831,7 +6840,7 @@
         <f>IF(COUNTA(D67:W67)=0,"",SUMPRODUCT((D67:W67=$D$2:$W$2)*(D67:W67&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y67" s="26">
+      <c r="Y67" s="27">
         <f>IF(COUNTA(D67:W67)=0,"",SUMPRODUCT((D67:W67=$D$2:$W$2)*(D67:W67&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6888,7 +6897,7 @@
         <f>IF(COUNTA(D68:W68)=0,"",SUMPRODUCT((D68:W68=$D$2:$W$2)*(D68:W68&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y68" s="26">
+      <c r="Y68" s="27">
         <f>IF(COUNTA(D68:W68)=0,"",SUMPRODUCT((D68:W68=$D$2:$W$2)*(D68:W68&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -6945,7 +6954,7 @@
         <f>IF(COUNTA(D69:W69)=0,"",SUMPRODUCT((D69:W69=$D$2:$W$2)*(D69:W69&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y69" s="26">
+      <c r="Y69" s="27">
         <f>IF(COUNTA(D69:W69)=0,"",SUMPRODUCT((D69:W69=$D$2:$W$2)*(D69:W69&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7002,7 +7011,7 @@
         <f>IF(COUNTA(D70:W70)=0,"",SUMPRODUCT((D70:W70=$D$2:$W$2)*(D70:W70&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y70" s="26">
+      <c r="Y70" s="27">
         <f>IF(COUNTA(D70:W70)=0,"",SUMPRODUCT((D70:W70=$D$2:$W$2)*(D70:W70&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7059,7 +7068,7 @@
         <f>IF(COUNTA(D71:W71)=0,"",SUMPRODUCT((D71:W71=$D$2:$W$2)*(D71:W71&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y71" s="26">
+      <c r="Y71" s="27">
         <f>IF(COUNTA(D71:W71)=0,"",SUMPRODUCT((D71:W71=$D$2:$W$2)*(D71:W71&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7116,7 +7125,7 @@
         <f>IF(COUNTA(D72:W72)=0,"",SUMPRODUCT((D72:W72=$D$2:$W$2)*(D72:W72&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y72" s="26">
+      <c r="Y72" s="27">
         <f>IF(COUNTA(D72:W72)=0,"",SUMPRODUCT((D72:W72=$D$2:$W$2)*(D72:W72&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7173,7 +7182,7 @@
         <f>IF(COUNTA(D73:W73)=0,"",SUMPRODUCT((D73:W73=$D$2:$W$2)*(D73:W73&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y73" s="26">
+      <c r="Y73" s="27">
         <f>IF(COUNTA(D73:W73)=0,"",SUMPRODUCT((D73:W73=$D$2:$W$2)*(D73:W73&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7230,7 +7239,7 @@
         <f>IF(COUNTA(D74:W74)=0,"",SUMPRODUCT((D74:W74=$D$2:$W$2)*(D74:W74&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y74" s="26">
+      <c r="Y74" s="27">
         <f>IF(COUNTA(D74:W74)=0,"",SUMPRODUCT((D74:W74=$D$2:$W$2)*(D74:W74&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7287,7 +7296,7 @@
         <f>IF(COUNTA(D75:W75)=0,"",SUMPRODUCT((D75:W75=$D$2:$W$2)*(D75:W75&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y75" s="26">
+      <c r="Y75" s="27">
         <f>IF(COUNTA(D75:W75)=0,"",SUMPRODUCT((D75:W75=$D$2:$W$2)*(D75:W75&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7344,7 +7353,7 @@
         <f>IF(COUNTA(D76:W76)=0,"",SUMPRODUCT((D76:W76=$D$2:$W$2)*(D76:W76&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y76" s="26">
+      <c r="Y76" s="27">
         <f>IF(COUNTA(D76:W76)=0,"",SUMPRODUCT((D76:W76=$D$2:$W$2)*(D76:W76&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7401,7 +7410,7 @@
         <f>IF(COUNTA(D77:W77)=0,"",SUMPRODUCT((D77:W77=$D$2:$W$2)*(D77:W77&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y77" s="26">
+      <c r="Y77" s="27">
         <f>IF(COUNTA(D77:W77)=0,"",SUMPRODUCT((D77:W77=$D$2:$W$2)*(D77:W77&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7458,7 +7467,7 @@
         <f>IF(COUNTA(D78:W78)=0,"",SUMPRODUCT((D78:W78=$D$2:$W$2)*(D78:W78&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y78" s="26">
+      <c r="Y78" s="27">
         <f>IF(COUNTA(D78:W78)=0,"",SUMPRODUCT((D78:W78=$D$2:$W$2)*(D78:W78&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7515,7 +7524,7 @@
         <f>IF(COUNTA(D79:W79)=0,"",SUMPRODUCT((D79:W79=$D$2:$W$2)*(D79:W79&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y79" s="26">
+      <c r="Y79" s="27">
         <f>IF(COUNTA(D79:W79)=0,"",SUMPRODUCT((D79:W79=$D$2:$W$2)*(D79:W79&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7572,7 +7581,7 @@
         <f>IF(COUNTA(D80:W80)=0,"",SUMPRODUCT((D80:W80=$D$2:$W$2)*(D80:W80&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y80" s="26">
+      <c r="Y80" s="27">
         <f>IF(COUNTA(D80:W80)=0,"",SUMPRODUCT((D80:W80=$D$2:$W$2)*(D80:W80&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7629,7 +7638,7 @@
         <f>IF(COUNTA(D81:W81)=0,"",SUMPRODUCT((D81:W81=$D$2:$W$2)*(D81:W81&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y81" s="26">
+      <c r="Y81" s="27">
         <f>IF(COUNTA(D81:W81)=0,"",SUMPRODUCT((D81:W81=$D$2:$W$2)*(D81:W81&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7686,7 +7695,7 @@
         <f>IF(COUNTA(D82:W82)=0,"",SUMPRODUCT((D82:W82=$D$2:$W$2)*(D82:W82&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y82" s="26">
+      <c r="Y82" s="27">
         <f>IF(COUNTA(D82:W82)=0,"",SUMPRODUCT((D82:W82=$D$2:$W$2)*(D82:W82&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7743,7 +7752,7 @@
         <f>IF(COUNTA(D83:W83)=0,"",SUMPRODUCT((D83:W83=$D$2:$W$2)*(D83:W83&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y83" s="26">
+      <c r="Y83" s="27">
         <f>IF(COUNTA(D83:W83)=0,"",SUMPRODUCT((D83:W83=$D$2:$W$2)*(D83:W83&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7800,7 +7809,7 @@
         <f>IF(COUNTA(D84:W84)=0,"",SUMPRODUCT((D84:W84=$D$2:$W$2)*(D84:W84&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y84" s="26">
+      <c r="Y84" s="27">
         <f>IF(COUNTA(D84:W84)=0,"",SUMPRODUCT((D84:W84=$D$2:$W$2)*(D84:W84&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7857,7 +7866,7 @@
         <f>IF(COUNTA(D85:W85)=0,"",SUMPRODUCT((D85:W85=$D$2:$W$2)*(D85:W85&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y85" s="26">
+      <c r="Y85" s="27">
         <f>IF(COUNTA(D85:W85)=0,"",SUMPRODUCT((D85:W85=$D$2:$W$2)*(D85:W85&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7914,7 +7923,7 @@
         <f>IF(COUNTA(D86:W86)=0,"",SUMPRODUCT((D86:W86=$D$2:$W$2)*(D86:W86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y86" s="26">
+      <c r="Y86" s="27">
         <f>IF(COUNTA(D86:W86)=0,"",SUMPRODUCT((D86:W86=$D$2:$W$2)*(D86:W86&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -7965,9 +7974,9 @@
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="R2 R7:R86 S2 S7:S86 T2 T7:T86 U2 U7:U86 V2 V7:V86 W2 W7:W86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 오류" error="단답형은 0~999 사이 정수만 입력" type="whole" operator="between">
+    <dataValidation sqref="R7:R86 S7:S86 T7:T86 U7:U86 V7:V86 W7:W86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 오류" error="단답형은 맞으면 1, 틀리면 0을 입력" type="whole" operator="between">
       <formula1>0</formula1>
-      <formula2>999</formula2>
+      <formula2>1</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8022,7 +8031,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>① 2~5행(노란 칸)에 정답·배점·단원·난이도 입력  ② 학생 행에 학생이 쓴 답을 그대로 입력(객관식 1~5, 단답형 0~999) → 틀린 답은 빨간 칸, 점수 자동 계산. 결시생은 비워두면 미응시 처리.</t>
+          <t>객관식 1~14번: 학생이 고른 번호(1~5, 답안지 스캔으로 자동 입력 가능)  단답형 15~20번: 직접 채점해 맞으면 1, 틀리면 0 → 틀린 칸은 빨간색, 점수 자동 계산. 결시생은 비워두면 미응시 처리.</t>
         </is>
       </c>
     </row>
@@ -8074,23 +8083,23 @@
       <c r="Q2" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="R2" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="S2" s="19" t="n">
-        <v>160</v>
-      </c>
-      <c r="T2" s="19" t="n">
-        <v>210</v>
-      </c>
-      <c r="U2" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="V2" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="W2" s="19" t="n">
-        <v>13</v>
+      <c r="R2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" s="20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -8163,7 +8172,7 @@
         <f>COUNT(D2:W2)</f>
         <v/>
       </c>
-      <c r="Y3" s="20">
+      <c r="Y3" s="21">
         <f>SUM(D3:W3)</f>
         <v/>
       </c>
@@ -8186,102 +8195,102 @@
           <t>단원 ▶</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>도형의 방정식</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="22" t="inlineStr">
         <is>
           <t>함수와 그래프</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>함수와 그래프</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="G4" s="22" t="inlineStr">
         <is>
           <t>도형의 방정식</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>도형의 방정식</t>
         </is>
       </c>
-      <c r="I4" s="21" t="inlineStr">
+      <c r="I4" s="22" t="inlineStr">
         <is>
           <t>집합과 명제</t>
         </is>
       </c>
-      <c r="J4" s="21" t="inlineStr">
+      <c r="J4" s="22" t="inlineStr">
         <is>
           <t>집합과 명제</t>
         </is>
       </c>
-      <c r="K4" s="21" t="inlineStr">
+      <c r="K4" s="22" t="inlineStr">
         <is>
           <t>도형의 방정식</t>
         </is>
       </c>
-      <c r="L4" s="21" t="inlineStr">
+      <c r="L4" s="22" t="inlineStr">
         <is>
           <t>함수와 그래프</t>
         </is>
       </c>
-      <c r="M4" s="21" t="inlineStr">
+      <c r="M4" s="22" t="inlineStr">
         <is>
           <t>함수와 그래프</t>
         </is>
       </c>
-      <c r="N4" s="21" t="inlineStr">
+      <c r="N4" s="22" t="inlineStr">
         <is>
           <t>도형의 방정식</t>
         </is>
       </c>
-      <c r="O4" s="21" t="inlineStr">
+      <c r="O4" s="22" t="inlineStr">
         <is>
           <t>함수와 그래프</t>
         </is>
       </c>
-      <c r="P4" s="21" t="inlineStr">
+      <c r="P4" s="22" t="inlineStr">
         <is>
           <t>도형의 방정식</t>
         </is>
       </c>
-      <c r="Q4" s="21" t="inlineStr">
+      <c r="Q4" s="22" t="inlineStr">
         <is>
           <t>도형의 방정식</t>
         </is>
       </c>
-      <c r="R4" s="21" t="inlineStr">
+      <c r="R4" s="22" t="inlineStr">
         <is>
           <t>집합과 명제</t>
         </is>
       </c>
-      <c r="S4" s="21" t="inlineStr">
+      <c r="S4" s="22" t="inlineStr">
         <is>
           <t>도형의 방정식</t>
         </is>
       </c>
-      <c r="T4" s="21" t="inlineStr">
+      <c r="T4" s="22" t="inlineStr">
         <is>
           <t>함수와 그래프</t>
         </is>
       </c>
-      <c r="U4" s="21" t="inlineStr">
+      <c r="U4" s="22" t="inlineStr">
         <is>
           <t>집합과 명제</t>
         </is>
       </c>
-      <c r="V4" s="21" t="inlineStr">
+      <c r="V4" s="22" t="inlineStr">
         <is>
           <t>집합과 명제</t>
         </is>
       </c>
-      <c r="W4" s="21" t="inlineStr">
+      <c r="W4" s="22" t="inlineStr">
         <is>
           <t>함수와 그래프</t>
         </is>
@@ -8393,33 +8402,33 @@
           <t>최상</t>
         </is>
       </c>
-      <c r="X5" s="22" t="inlineStr">
+      <c r="X5" s="23" t="inlineStr">
         <is>
           <t>정답입력수▲</t>
         </is>
       </c>
-      <c r="Y5" s="22" t="inlineStr">
+      <c r="Y5" s="23" t="inlineStr">
         <is>
           <t>만점 ▲</t>
         </is>
       </c>
-      <c r="Z5" s="22" t="inlineStr">
+      <c r="Z5" s="23" t="inlineStr">
         <is>
           <t>만점 ▲</t>
         </is>
       </c>
-      <c r="AA5" s="22" t="inlineStr">
+      <c r="AA5" s="23" t="inlineStr">
         <is>
           <t>만점 ▲</t>
         </is>
       </c>
-      <c r="AB5" s="22" t="inlineStr">
+      <c r="AB5" s="23" t="inlineStr">
         <is>
           <t>만점 ▲</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="44" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>No</t>
@@ -8435,124 +8444,130 @@
           <t>학교</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>1
 객관식</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>2
 객관식</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>3
 객관식</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>4
 객관식</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>5
 객관식</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t>6
 객관식</t>
         </is>
       </c>
-      <c r="J6" s="23" t="inlineStr">
+      <c r="J6" s="24" t="inlineStr">
         <is>
           <t>7
 객관식</t>
         </is>
       </c>
-      <c r="K6" s="23" t="inlineStr">
+      <c r="K6" s="24" t="inlineStr">
         <is>
           <t>8
 객관식</t>
         </is>
       </c>
-      <c r="L6" s="23" t="inlineStr">
+      <c r="L6" s="24" t="inlineStr">
         <is>
           <t>9
 객관식</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M6" s="24" t="inlineStr">
         <is>
           <t>10
 객관식</t>
         </is>
       </c>
-      <c r="N6" s="23" t="inlineStr">
+      <c r="N6" s="24" t="inlineStr">
         <is>
           <t>11
 객관식</t>
         </is>
       </c>
-      <c r="O6" s="23" t="inlineStr">
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t>12
 객관식</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P6" s="24" t="inlineStr">
         <is>
           <t>13
 객관식</t>
         </is>
       </c>
-      <c r="Q6" s="23" t="inlineStr">
+      <c r="Q6" s="24" t="inlineStr">
         <is>
           <t>14
 객관식</t>
         </is>
       </c>
-      <c r="R6" s="24" t="inlineStr">
+      <c r="R6" s="25" t="inlineStr">
         <is>
           <t>15
-단답형</t>
-        </is>
-      </c>
-      <c r="S6" s="24" t="inlineStr">
+단답형
+답 9</t>
+        </is>
+      </c>
+      <c r="S6" s="25" t="inlineStr">
         <is>
           <t>16
-단답형</t>
-        </is>
-      </c>
-      <c r="T6" s="24" t="inlineStr">
+단답형
+답 160</t>
+        </is>
+      </c>
+      <c r="T6" s="25" t="inlineStr">
         <is>
           <t>17
-단답형</t>
-        </is>
-      </c>
-      <c r="U6" s="24" t="inlineStr">
+단답형
+답 210</t>
+        </is>
+      </c>
+      <c r="U6" s="25" t="inlineStr">
         <is>
           <t>18
-단답형</t>
-        </is>
-      </c>
-      <c r="V6" s="24" t="inlineStr">
+단답형
+답 40</t>
+        </is>
+      </c>
+      <c r="V6" s="25" t="inlineStr">
         <is>
           <t>19
-단답형</t>
-        </is>
-      </c>
-      <c r="W6" s="24" t="inlineStr">
+단답형
+답 15</t>
+        </is>
+      </c>
+      <c r="W6" s="25" t="inlineStr">
         <is>
           <t>20
-단답형</t>
+단답형
+답 13</t>
         </is>
       </c>
       <c r="X6" s="4" t="inlineStr">
@@ -8566,15 +8581,15 @@
           <t>총점</t>
         </is>
       </c>
-      <c r="Z6" s="25">
+      <c r="Z6" s="26">
         <f>'설정'!B24</f>
         <v/>
       </c>
-      <c r="AA6" s="25">
+      <c r="AA6" s="26">
         <f>'설정'!B25</f>
         <v/>
       </c>
-      <c r="AB6" s="25">
+      <c r="AB6" s="26">
         <f>'설정'!B26</f>
         <v/>
       </c>
@@ -8615,7 +8630,7 @@
         <f>IF(COUNTA(D7:W7)=0,"",SUMPRODUCT((D7:W7=$D$2:$W$2)*(D7:W7&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y7" s="26">
+      <c r="Y7" s="27">
         <f>IF(COUNTA(D7:W7)=0,"",SUMPRODUCT((D7:W7=$D$2:$W$2)*(D7:W7&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -8668,7 +8683,7 @@
         <f>IF(COUNTA(D8:W8)=0,"",SUMPRODUCT((D8:W8=$D$2:$W$2)*(D8:W8&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y8" s="26">
+      <c r="Y8" s="27">
         <f>IF(COUNTA(D8:W8)=0,"",SUMPRODUCT((D8:W8=$D$2:$W$2)*(D8:W8&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -8721,7 +8736,7 @@
         <f>IF(COUNTA(D9:W9)=0,"",SUMPRODUCT((D9:W9=$D$2:$W$2)*(D9:W9&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y9" s="26">
+      <c r="Y9" s="27">
         <f>IF(COUNTA(D9:W9)=0,"",SUMPRODUCT((D9:W9=$D$2:$W$2)*(D9:W9&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -8774,7 +8789,7 @@
         <f>IF(COUNTA(D10:W10)=0,"",SUMPRODUCT((D10:W10=$D$2:$W$2)*(D10:W10&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y10" s="26">
+      <c r="Y10" s="27">
         <f>IF(COUNTA(D10:W10)=0,"",SUMPRODUCT((D10:W10=$D$2:$W$2)*(D10:W10&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -8827,7 +8842,7 @@
         <f>IF(COUNTA(D11:W11)=0,"",SUMPRODUCT((D11:W11=$D$2:$W$2)*(D11:W11&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y11" s="26">
+      <c r="Y11" s="27">
         <f>IF(COUNTA(D11:W11)=0,"",SUMPRODUCT((D11:W11=$D$2:$W$2)*(D11:W11&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -8880,7 +8895,7 @@
         <f>IF(COUNTA(D12:W12)=0,"",SUMPRODUCT((D12:W12=$D$2:$W$2)*(D12:W12&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y12" s="26">
+      <c r="Y12" s="27">
         <f>IF(COUNTA(D12:W12)=0,"",SUMPRODUCT((D12:W12=$D$2:$W$2)*(D12:W12&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -8933,7 +8948,7 @@
         <f>IF(COUNTA(D13:W13)=0,"",SUMPRODUCT((D13:W13=$D$2:$W$2)*(D13:W13&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y13" s="26">
+      <c r="Y13" s="27">
         <f>IF(COUNTA(D13:W13)=0,"",SUMPRODUCT((D13:W13=$D$2:$W$2)*(D13:W13&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -8986,7 +9001,7 @@
         <f>IF(COUNTA(D14:W14)=0,"",SUMPRODUCT((D14:W14=$D$2:$W$2)*(D14:W14&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y14" s="26">
+      <c r="Y14" s="27">
         <f>IF(COUNTA(D14:W14)=0,"",SUMPRODUCT((D14:W14=$D$2:$W$2)*(D14:W14&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9039,7 +9054,7 @@
         <f>IF(COUNTA(D15:W15)=0,"",SUMPRODUCT((D15:W15=$D$2:$W$2)*(D15:W15&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y15" s="26">
+      <c r="Y15" s="27">
         <f>IF(COUNTA(D15:W15)=0,"",SUMPRODUCT((D15:W15=$D$2:$W$2)*(D15:W15&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9092,7 +9107,7 @@
         <f>IF(COUNTA(D16:W16)=0,"",SUMPRODUCT((D16:W16=$D$2:$W$2)*(D16:W16&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y16" s="26">
+      <c r="Y16" s="27">
         <f>IF(COUNTA(D16:W16)=0,"",SUMPRODUCT((D16:W16=$D$2:$W$2)*(D16:W16&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9145,7 +9160,7 @@
         <f>IF(COUNTA(D17:W17)=0,"",SUMPRODUCT((D17:W17=$D$2:$W$2)*(D17:W17&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y17" s="26">
+      <c r="Y17" s="27">
         <f>IF(COUNTA(D17:W17)=0,"",SUMPRODUCT((D17:W17=$D$2:$W$2)*(D17:W17&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9198,7 +9213,7 @@
         <f>IF(COUNTA(D18:W18)=0,"",SUMPRODUCT((D18:W18=$D$2:$W$2)*(D18:W18&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y18" s="26">
+      <c r="Y18" s="27">
         <f>IF(COUNTA(D18:W18)=0,"",SUMPRODUCT((D18:W18=$D$2:$W$2)*(D18:W18&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9251,7 +9266,7 @@
         <f>IF(COUNTA(D19:W19)=0,"",SUMPRODUCT((D19:W19=$D$2:$W$2)*(D19:W19&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y19" s="26">
+      <c r="Y19" s="27">
         <f>IF(COUNTA(D19:W19)=0,"",SUMPRODUCT((D19:W19=$D$2:$W$2)*(D19:W19&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9304,7 +9319,7 @@
         <f>IF(COUNTA(D20:W20)=0,"",SUMPRODUCT((D20:W20=$D$2:$W$2)*(D20:W20&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y20" s="26">
+      <c r="Y20" s="27">
         <f>IF(COUNTA(D20:W20)=0,"",SUMPRODUCT((D20:W20=$D$2:$W$2)*(D20:W20&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9357,7 +9372,7 @@
         <f>IF(COUNTA(D21:W21)=0,"",SUMPRODUCT((D21:W21=$D$2:$W$2)*(D21:W21&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y21" s="26">
+      <c r="Y21" s="27">
         <f>IF(COUNTA(D21:W21)=0,"",SUMPRODUCT((D21:W21=$D$2:$W$2)*(D21:W21&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9410,7 +9425,7 @@
         <f>IF(COUNTA(D22:W22)=0,"",SUMPRODUCT((D22:W22=$D$2:$W$2)*(D22:W22&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y22" s="26">
+      <c r="Y22" s="27">
         <f>IF(COUNTA(D22:W22)=0,"",SUMPRODUCT((D22:W22=$D$2:$W$2)*(D22:W22&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9463,7 +9478,7 @@
         <f>IF(COUNTA(D23:W23)=0,"",SUMPRODUCT((D23:W23=$D$2:$W$2)*(D23:W23&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y23" s="26">
+      <c r="Y23" s="27">
         <f>IF(COUNTA(D23:W23)=0,"",SUMPRODUCT((D23:W23=$D$2:$W$2)*(D23:W23&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9516,7 +9531,7 @@
         <f>IF(COUNTA(D24:W24)=0,"",SUMPRODUCT((D24:W24=$D$2:$W$2)*(D24:W24&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y24" s="26">
+      <c r="Y24" s="27">
         <f>IF(COUNTA(D24:W24)=0,"",SUMPRODUCT((D24:W24=$D$2:$W$2)*(D24:W24&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9569,7 +9584,7 @@
         <f>IF(COUNTA(D25:W25)=0,"",SUMPRODUCT((D25:W25=$D$2:$W$2)*(D25:W25&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y25" s="26">
+      <c r="Y25" s="27">
         <f>IF(COUNTA(D25:W25)=0,"",SUMPRODUCT((D25:W25=$D$2:$W$2)*(D25:W25&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9622,7 +9637,7 @@
         <f>IF(COUNTA(D26:W26)=0,"",SUMPRODUCT((D26:W26=$D$2:$W$2)*(D26:W26&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y26" s="26">
+      <c r="Y26" s="27">
         <f>IF(COUNTA(D26:W26)=0,"",SUMPRODUCT((D26:W26=$D$2:$W$2)*(D26:W26&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9675,7 +9690,7 @@
         <f>IF(COUNTA(D27:W27)=0,"",SUMPRODUCT((D27:W27=$D$2:$W$2)*(D27:W27&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y27" s="26">
+      <c r="Y27" s="27">
         <f>IF(COUNTA(D27:W27)=0,"",SUMPRODUCT((D27:W27=$D$2:$W$2)*(D27:W27&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9728,7 +9743,7 @@
         <f>IF(COUNTA(D28:W28)=0,"",SUMPRODUCT((D28:W28=$D$2:$W$2)*(D28:W28&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y28" s="26">
+      <c r="Y28" s="27">
         <f>IF(COUNTA(D28:W28)=0,"",SUMPRODUCT((D28:W28=$D$2:$W$2)*(D28:W28&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9781,7 +9796,7 @@
         <f>IF(COUNTA(D29:W29)=0,"",SUMPRODUCT((D29:W29=$D$2:$W$2)*(D29:W29&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y29" s="26">
+      <c r="Y29" s="27">
         <f>IF(COUNTA(D29:W29)=0,"",SUMPRODUCT((D29:W29=$D$2:$W$2)*(D29:W29&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9834,7 +9849,7 @@
         <f>IF(COUNTA(D30:W30)=0,"",SUMPRODUCT((D30:W30=$D$2:$W$2)*(D30:W30&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y30" s="26">
+      <c r="Y30" s="27">
         <f>IF(COUNTA(D30:W30)=0,"",SUMPRODUCT((D30:W30=$D$2:$W$2)*(D30:W30&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9887,7 +9902,7 @@
         <f>IF(COUNTA(D31:W31)=0,"",SUMPRODUCT((D31:W31=$D$2:$W$2)*(D31:W31&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y31" s="26">
+      <c r="Y31" s="27">
         <f>IF(COUNTA(D31:W31)=0,"",SUMPRODUCT((D31:W31=$D$2:$W$2)*(D31:W31&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9940,7 +9955,7 @@
         <f>IF(COUNTA(D32:W32)=0,"",SUMPRODUCT((D32:W32=$D$2:$W$2)*(D32:W32&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y32" s="26">
+      <c r="Y32" s="27">
         <f>IF(COUNTA(D32:W32)=0,"",SUMPRODUCT((D32:W32=$D$2:$W$2)*(D32:W32&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -9993,7 +10008,7 @@
         <f>IF(COUNTA(D33:W33)=0,"",SUMPRODUCT((D33:W33=$D$2:$W$2)*(D33:W33&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y33" s="26">
+      <c r="Y33" s="27">
         <f>IF(COUNTA(D33:W33)=0,"",SUMPRODUCT((D33:W33=$D$2:$W$2)*(D33:W33&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10046,7 +10061,7 @@
         <f>IF(COUNTA(D34:W34)=0,"",SUMPRODUCT((D34:W34=$D$2:$W$2)*(D34:W34&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y34" s="26">
+      <c r="Y34" s="27">
         <f>IF(COUNTA(D34:W34)=0,"",SUMPRODUCT((D34:W34=$D$2:$W$2)*(D34:W34&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10099,7 +10114,7 @@
         <f>IF(COUNTA(D35:W35)=0,"",SUMPRODUCT((D35:W35=$D$2:$W$2)*(D35:W35&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y35" s="26">
+      <c r="Y35" s="27">
         <f>IF(COUNTA(D35:W35)=0,"",SUMPRODUCT((D35:W35=$D$2:$W$2)*(D35:W35&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10152,7 +10167,7 @@
         <f>IF(COUNTA(D36:W36)=0,"",SUMPRODUCT((D36:W36=$D$2:$W$2)*(D36:W36&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y36" s="26">
+      <c r="Y36" s="27">
         <f>IF(COUNTA(D36:W36)=0,"",SUMPRODUCT((D36:W36=$D$2:$W$2)*(D36:W36&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10205,7 +10220,7 @@
         <f>IF(COUNTA(D37:W37)=0,"",SUMPRODUCT((D37:W37=$D$2:$W$2)*(D37:W37&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y37" s="26">
+      <c r="Y37" s="27">
         <f>IF(COUNTA(D37:W37)=0,"",SUMPRODUCT((D37:W37=$D$2:$W$2)*(D37:W37&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10258,7 +10273,7 @@
         <f>IF(COUNTA(D38:W38)=0,"",SUMPRODUCT((D38:W38=$D$2:$W$2)*(D38:W38&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y38" s="26">
+      <c r="Y38" s="27">
         <f>IF(COUNTA(D38:W38)=0,"",SUMPRODUCT((D38:W38=$D$2:$W$2)*(D38:W38&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10311,7 +10326,7 @@
         <f>IF(COUNTA(D39:W39)=0,"",SUMPRODUCT((D39:W39=$D$2:$W$2)*(D39:W39&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y39" s="26">
+      <c r="Y39" s="27">
         <f>IF(COUNTA(D39:W39)=0,"",SUMPRODUCT((D39:W39=$D$2:$W$2)*(D39:W39&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10364,7 +10379,7 @@
         <f>IF(COUNTA(D40:W40)=0,"",SUMPRODUCT((D40:W40=$D$2:$W$2)*(D40:W40&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y40" s="26">
+      <c r="Y40" s="27">
         <f>IF(COUNTA(D40:W40)=0,"",SUMPRODUCT((D40:W40=$D$2:$W$2)*(D40:W40&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10417,7 +10432,7 @@
         <f>IF(COUNTA(D41:W41)=0,"",SUMPRODUCT((D41:W41=$D$2:$W$2)*(D41:W41&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y41" s="26">
+      <c r="Y41" s="27">
         <f>IF(COUNTA(D41:W41)=0,"",SUMPRODUCT((D41:W41=$D$2:$W$2)*(D41:W41&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10470,7 +10485,7 @@
         <f>IF(COUNTA(D42:W42)=0,"",SUMPRODUCT((D42:W42=$D$2:$W$2)*(D42:W42&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y42" s="26">
+      <c r="Y42" s="27">
         <f>IF(COUNTA(D42:W42)=0,"",SUMPRODUCT((D42:W42=$D$2:$W$2)*(D42:W42&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10523,7 +10538,7 @@
         <f>IF(COUNTA(D43:W43)=0,"",SUMPRODUCT((D43:W43=$D$2:$W$2)*(D43:W43&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y43" s="26">
+      <c r="Y43" s="27">
         <f>IF(COUNTA(D43:W43)=0,"",SUMPRODUCT((D43:W43=$D$2:$W$2)*(D43:W43&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10576,7 +10591,7 @@
         <f>IF(COUNTA(D44:W44)=0,"",SUMPRODUCT((D44:W44=$D$2:$W$2)*(D44:W44&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y44" s="26">
+      <c r="Y44" s="27">
         <f>IF(COUNTA(D44:W44)=0,"",SUMPRODUCT((D44:W44=$D$2:$W$2)*(D44:W44&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10629,7 +10644,7 @@
         <f>IF(COUNTA(D45:W45)=0,"",SUMPRODUCT((D45:W45=$D$2:$W$2)*(D45:W45&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y45" s="26">
+      <c r="Y45" s="27">
         <f>IF(COUNTA(D45:W45)=0,"",SUMPRODUCT((D45:W45=$D$2:$W$2)*(D45:W45&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10682,7 +10697,7 @@
         <f>IF(COUNTA(D46:W46)=0,"",SUMPRODUCT((D46:W46=$D$2:$W$2)*(D46:W46&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y46" s="26">
+      <c r="Y46" s="27">
         <f>IF(COUNTA(D46:W46)=0,"",SUMPRODUCT((D46:W46=$D$2:$W$2)*(D46:W46&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10735,7 +10750,7 @@
         <f>IF(COUNTA(D47:W47)=0,"",SUMPRODUCT((D47:W47=$D$2:$W$2)*(D47:W47&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y47" s="26">
+      <c r="Y47" s="27">
         <f>IF(COUNTA(D47:W47)=0,"",SUMPRODUCT((D47:W47=$D$2:$W$2)*(D47:W47&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10788,7 +10803,7 @@
         <f>IF(COUNTA(D48:W48)=0,"",SUMPRODUCT((D48:W48=$D$2:$W$2)*(D48:W48&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y48" s="26">
+      <c r="Y48" s="27">
         <f>IF(COUNTA(D48:W48)=0,"",SUMPRODUCT((D48:W48=$D$2:$W$2)*(D48:W48&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10841,7 +10856,7 @@
         <f>IF(COUNTA(D49:W49)=0,"",SUMPRODUCT((D49:W49=$D$2:$W$2)*(D49:W49&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y49" s="26">
+      <c r="Y49" s="27">
         <f>IF(COUNTA(D49:W49)=0,"",SUMPRODUCT((D49:W49=$D$2:$W$2)*(D49:W49&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10894,7 +10909,7 @@
         <f>IF(COUNTA(D50:W50)=0,"",SUMPRODUCT((D50:W50=$D$2:$W$2)*(D50:W50&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y50" s="26">
+      <c r="Y50" s="27">
         <f>IF(COUNTA(D50:W50)=0,"",SUMPRODUCT((D50:W50=$D$2:$W$2)*(D50:W50&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -10947,7 +10962,7 @@
         <f>IF(COUNTA(D51:W51)=0,"",SUMPRODUCT((D51:W51=$D$2:$W$2)*(D51:W51&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y51" s="26">
+      <c r="Y51" s="27">
         <f>IF(COUNTA(D51:W51)=0,"",SUMPRODUCT((D51:W51=$D$2:$W$2)*(D51:W51&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11000,7 +11015,7 @@
         <f>IF(COUNTA(D52:W52)=0,"",SUMPRODUCT((D52:W52=$D$2:$W$2)*(D52:W52&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y52" s="26">
+      <c r="Y52" s="27">
         <f>IF(COUNTA(D52:W52)=0,"",SUMPRODUCT((D52:W52=$D$2:$W$2)*(D52:W52&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11053,7 +11068,7 @@
         <f>IF(COUNTA(D53:W53)=0,"",SUMPRODUCT((D53:W53=$D$2:$W$2)*(D53:W53&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y53" s="26">
+      <c r="Y53" s="27">
         <f>IF(COUNTA(D53:W53)=0,"",SUMPRODUCT((D53:W53=$D$2:$W$2)*(D53:W53&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11106,7 +11121,7 @@
         <f>IF(COUNTA(D54:W54)=0,"",SUMPRODUCT((D54:W54=$D$2:$W$2)*(D54:W54&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y54" s="26">
+      <c r="Y54" s="27">
         <f>IF(COUNTA(D54:W54)=0,"",SUMPRODUCT((D54:W54=$D$2:$W$2)*(D54:W54&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11159,7 +11174,7 @@
         <f>IF(COUNTA(D55:W55)=0,"",SUMPRODUCT((D55:W55=$D$2:$W$2)*(D55:W55&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y55" s="26">
+      <c r="Y55" s="27">
         <f>IF(COUNTA(D55:W55)=0,"",SUMPRODUCT((D55:W55=$D$2:$W$2)*(D55:W55&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11212,7 +11227,7 @@
         <f>IF(COUNTA(D56:W56)=0,"",SUMPRODUCT((D56:W56=$D$2:$W$2)*(D56:W56&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y56" s="26">
+      <c r="Y56" s="27">
         <f>IF(COUNTA(D56:W56)=0,"",SUMPRODUCT((D56:W56=$D$2:$W$2)*(D56:W56&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11265,7 +11280,7 @@
         <f>IF(COUNTA(D57:W57)=0,"",SUMPRODUCT((D57:W57=$D$2:$W$2)*(D57:W57&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y57" s="26">
+      <c r="Y57" s="27">
         <f>IF(COUNTA(D57:W57)=0,"",SUMPRODUCT((D57:W57=$D$2:$W$2)*(D57:W57&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11318,7 +11333,7 @@
         <f>IF(COUNTA(D58:W58)=0,"",SUMPRODUCT((D58:W58=$D$2:$W$2)*(D58:W58&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y58" s="26">
+      <c r="Y58" s="27">
         <f>IF(COUNTA(D58:W58)=0,"",SUMPRODUCT((D58:W58=$D$2:$W$2)*(D58:W58&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11371,7 +11386,7 @@
         <f>IF(COUNTA(D59:W59)=0,"",SUMPRODUCT((D59:W59=$D$2:$W$2)*(D59:W59&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y59" s="26">
+      <c r="Y59" s="27">
         <f>IF(COUNTA(D59:W59)=0,"",SUMPRODUCT((D59:W59=$D$2:$W$2)*(D59:W59&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11424,7 +11439,7 @@
         <f>IF(COUNTA(D60:W60)=0,"",SUMPRODUCT((D60:W60=$D$2:$W$2)*(D60:W60&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y60" s="26">
+      <c r="Y60" s="27">
         <f>IF(COUNTA(D60:W60)=0,"",SUMPRODUCT((D60:W60=$D$2:$W$2)*(D60:W60&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11477,7 +11492,7 @@
         <f>IF(COUNTA(D61:W61)=0,"",SUMPRODUCT((D61:W61=$D$2:$W$2)*(D61:W61&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y61" s="26">
+      <c r="Y61" s="27">
         <f>IF(COUNTA(D61:W61)=0,"",SUMPRODUCT((D61:W61=$D$2:$W$2)*(D61:W61&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11530,7 +11545,7 @@
         <f>IF(COUNTA(D62:W62)=0,"",SUMPRODUCT((D62:W62=$D$2:$W$2)*(D62:W62&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y62" s="26">
+      <c r="Y62" s="27">
         <f>IF(COUNTA(D62:W62)=0,"",SUMPRODUCT((D62:W62=$D$2:$W$2)*(D62:W62&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11583,7 +11598,7 @@
         <f>IF(COUNTA(D63:W63)=0,"",SUMPRODUCT((D63:W63=$D$2:$W$2)*(D63:W63&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y63" s="26">
+      <c r="Y63" s="27">
         <f>IF(COUNTA(D63:W63)=0,"",SUMPRODUCT((D63:W63=$D$2:$W$2)*(D63:W63&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11636,7 +11651,7 @@
         <f>IF(COUNTA(D64:W64)=0,"",SUMPRODUCT((D64:W64=$D$2:$W$2)*(D64:W64&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y64" s="26">
+      <c r="Y64" s="27">
         <f>IF(COUNTA(D64:W64)=0,"",SUMPRODUCT((D64:W64=$D$2:$W$2)*(D64:W64&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11689,7 +11704,7 @@
         <f>IF(COUNTA(D65:W65)=0,"",SUMPRODUCT((D65:W65=$D$2:$W$2)*(D65:W65&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y65" s="26">
+      <c r="Y65" s="27">
         <f>IF(COUNTA(D65:W65)=0,"",SUMPRODUCT((D65:W65=$D$2:$W$2)*(D65:W65&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11742,7 +11757,7 @@
         <f>IF(COUNTA(D66:W66)=0,"",SUMPRODUCT((D66:W66=$D$2:$W$2)*(D66:W66&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y66" s="26">
+      <c r="Y66" s="27">
         <f>IF(COUNTA(D66:W66)=0,"",SUMPRODUCT((D66:W66=$D$2:$W$2)*(D66:W66&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11795,7 +11810,7 @@
         <f>IF(COUNTA(D67:W67)=0,"",SUMPRODUCT((D67:W67=$D$2:$W$2)*(D67:W67&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y67" s="26">
+      <c r="Y67" s="27">
         <f>IF(COUNTA(D67:W67)=0,"",SUMPRODUCT((D67:W67=$D$2:$W$2)*(D67:W67&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11848,7 +11863,7 @@
         <f>IF(COUNTA(D68:W68)=0,"",SUMPRODUCT((D68:W68=$D$2:$W$2)*(D68:W68&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y68" s="26">
+      <c r="Y68" s="27">
         <f>IF(COUNTA(D68:W68)=0,"",SUMPRODUCT((D68:W68=$D$2:$W$2)*(D68:W68&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11901,7 +11916,7 @@
         <f>IF(COUNTA(D69:W69)=0,"",SUMPRODUCT((D69:W69=$D$2:$W$2)*(D69:W69&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y69" s="26">
+      <c r="Y69" s="27">
         <f>IF(COUNTA(D69:W69)=0,"",SUMPRODUCT((D69:W69=$D$2:$W$2)*(D69:W69&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -11954,7 +11969,7 @@
         <f>IF(COUNTA(D70:W70)=0,"",SUMPRODUCT((D70:W70=$D$2:$W$2)*(D70:W70&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y70" s="26">
+      <c r="Y70" s="27">
         <f>IF(COUNTA(D70:W70)=0,"",SUMPRODUCT((D70:W70=$D$2:$W$2)*(D70:W70&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12007,7 +12022,7 @@
         <f>IF(COUNTA(D71:W71)=0,"",SUMPRODUCT((D71:W71=$D$2:$W$2)*(D71:W71&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y71" s="26">
+      <c r="Y71" s="27">
         <f>IF(COUNTA(D71:W71)=0,"",SUMPRODUCT((D71:W71=$D$2:$W$2)*(D71:W71&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12060,7 +12075,7 @@
         <f>IF(COUNTA(D72:W72)=0,"",SUMPRODUCT((D72:W72=$D$2:$W$2)*(D72:W72&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y72" s="26">
+      <c r="Y72" s="27">
         <f>IF(COUNTA(D72:W72)=0,"",SUMPRODUCT((D72:W72=$D$2:$W$2)*(D72:W72&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12113,7 +12128,7 @@
         <f>IF(COUNTA(D73:W73)=0,"",SUMPRODUCT((D73:W73=$D$2:$W$2)*(D73:W73&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y73" s="26">
+      <c r="Y73" s="27">
         <f>IF(COUNTA(D73:W73)=0,"",SUMPRODUCT((D73:W73=$D$2:$W$2)*(D73:W73&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12166,7 +12181,7 @@
         <f>IF(COUNTA(D74:W74)=0,"",SUMPRODUCT((D74:W74=$D$2:$W$2)*(D74:W74&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y74" s="26">
+      <c r="Y74" s="27">
         <f>IF(COUNTA(D74:W74)=0,"",SUMPRODUCT((D74:W74=$D$2:$W$2)*(D74:W74&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12219,7 +12234,7 @@
         <f>IF(COUNTA(D75:W75)=0,"",SUMPRODUCT((D75:W75=$D$2:$W$2)*(D75:W75&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y75" s="26">
+      <c r="Y75" s="27">
         <f>IF(COUNTA(D75:W75)=0,"",SUMPRODUCT((D75:W75=$D$2:$W$2)*(D75:W75&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12272,7 +12287,7 @@
         <f>IF(COUNTA(D76:W76)=0,"",SUMPRODUCT((D76:W76=$D$2:$W$2)*(D76:W76&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y76" s="26">
+      <c r="Y76" s="27">
         <f>IF(COUNTA(D76:W76)=0,"",SUMPRODUCT((D76:W76=$D$2:$W$2)*(D76:W76&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12325,7 +12340,7 @@
         <f>IF(COUNTA(D77:W77)=0,"",SUMPRODUCT((D77:W77=$D$2:$W$2)*(D77:W77&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y77" s="26">
+      <c r="Y77" s="27">
         <f>IF(COUNTA(D77:W77)=0,"",SUMPRODUCT((D77:W77=$D$2:$W$2)*(D77:W77&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12378,7 +12393,7 @@
         <f>IF(COUNTA(D78:W78)=0,"",SUMPRODUCT((D78:W78=$D$2:$W$2)*(D78:W78&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y78" s="26">
+      <c r="Y78" s="27">
         <f>IF(COUNTA(D78:W78)=0,"",SUMPRODUCT((D78:W78=$D$2:$W$2)*(D78:W78&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12431,7 +12446,7 @@
         <f>IF(COUNTA(D79:W79)=0,"",SUMPRODUCT((D79:W79=$D$2:$W$2)*(D79:W79&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y79" s="26">
+      <c r="Y79" s="27">
         <f>IF(COUNTA(D79:W79)=0,"",SUMPRODUCT((D79:W79=$D$2:$W$2)*(D79:W79&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12484,7 +12499,7 @@
         <f>IF(COUNTA(D80:W80)=0,"",SUMPRODUCT((D80:W80=$D$2:$W$2)*(D80:W80&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y80" s="26">
+      <c r="Y80" s="27">
         <f>IF(COUNTA(D80:W80)=0,"",SUMPRODUCT((D80:W80=$D$2:$W$2)*(D80:W80&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12537,7 +12552,7 @@
         <f>IF(COUNTA(D81:W81)=0,"",SUMPRODUCT((D81:W81=$D$2:$W$2)*(D81:W81&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y81" s="26">
+      <c r="Y81" s="27">
         <f>IF(COUNTA(D81:W81)=0,"",SUMPRODUCT((D81:W81=$D$2:$W$2)*(D81:W81&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12590,7 +12605,7 @@
         <f>IF(COUNTA(D82:W82)=0,"",SUMPRODUCT((D82:W82=$D$2:$W$2)*(D82:W82&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y82" s="26">
+      <c r="Y82" s="27">
         <f>IF(COUNTA(D82:W82)=0,"",SUMPRODUCT((D82:W82=$D$2:$W$2)*(D82:W82&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12643,7 +12658,7 @@
         <f>IF(COUNTA(D83:W83)=0,"",SUMPRODUCT((D83:W83=$D$2:$W$2)*(D83:W83&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y83" s="26">
+      <c r="Y83" s="27">
         <f>IF(COUNTA(D83:W83)=0,"",SUMPRODUCT((D83:W83=$D$2:$W$2)*(D83:W83&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12696,7 +12711,7 @@
         <f>IF(COUNTA(D84:W84)=0,"",SUMPRODUCT((D84:W84=$D$2:$W$2)*(D84:W84&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y84" s="26">
+      <c r="Y84" s="27">
         <f>IF(COUNTA(D84:W84)=0,"",SUMPRODUCT((D84:W84=$D$2:$W$2)*(D84:W84&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12749,7 +12764,7 @@
         <f>IF(COUNTA(D85:W85)=0,"",SUMPRODUCT((D85:W85=$D$2:$W$2)*(D85:W85&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y85" s="26">
+      <c r="Y85" s="27">
         <f>IF(COUNTA(D85:W85)=0,"",SUMPRODUCT((D85:W85=$D$2:$W$2)*(D85:W85&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12802,7 +12817,7 @@
         <f>IF(COUNTA(D86:W86)=0,"",SUMPRODUCT((D86:W86=$D$2:$W$2)*(D86:W86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="Y86" s="26">
+      <c r="Y86" s="27">
         <f>IF(COUNTA(D86:W86)=0,"",SUMPRODUCT((D86:W86=$D$2:$W$2)*(D86:W86&lt;&gt;"")*$D$3:$W$3))</f>
         <v/>
       </c>
@@ -12849,9 +12864,9 @@
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="R2 R7:R86 S2 S7:S86 T2 T7:T86 U2 U7:U86 V2 V7:V86 W2 W7:W86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 오류" error="단답형은 0~999 사이 정수만 입력" type="whole" operator="between">
+    <dataValidation sqref="R7:R86 S7:S86 T7:T86 U7:U86 V7:V86 W7:W86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 오류" error="단답형은 맞으면 1, 틀리면 0을 입력" type="whole" operator="between">
       <formula1>0</formula1>
-      <formula2>999</formula2>
+      <formula2>1</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13071,7 +13086,7 @@
         <f>'공수2'!Y7</f>
         <v/>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="28">
         <f>IF(AND(G7="",H7=""),"",N(G7)*'설정'!$C$13+N(H7)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -13079,21 +13094,21 @@
         <f>IF(I7="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I7)+1)</f>
         <v/>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="27">
         <f>IF(I7="","",IF(OR(G7="",H7=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G7&gt;='설정'!$C$6),OR('설정'!$D$6="",G7&lt;'설정'!$D$6),OR('설정'!$E$6="",H7&gt;='설정'!$E$6),OR('설정'!$F$6="",H7&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G7&gt;='설정'!$C$7),OR('설정'!$D$7="",G7&lt;'설정'!$D$7),OR('설정'!$E$7="",H7&gt;='설정'!$E$7),OR('설정'!$F$7="",H7&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G7&gt;='설정'!$C$8),OR('설정'!$D$8="",G7&lt;'설정'!$D$8),OR('설정'!$E$8="",H7&gt;='설정'!$E$8),OR('설정'!$F$8="",H7&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="29">
         <f>IF(OR(G7="",H7=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G7-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H7-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M7" s="7" t="n"/>
       <c r="N7" s="7" t="n"/>
-      <c r="O7" s="26">
+      <c r="O7" s="27">
         <f>IF(M7&lt;&gt;"",M7,K7)</f>
         <v/>
       </c>
-      <c r="P7" s="29">
+      <c r="P7" s="30">
         <f>IF(I7="","",IF(G7="","공수1 미응시",IF(H7="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -13101,7 +13116,7 @@
         <f>IF(J7="","",J7+ROW()/100000)</f>
         <v/>
       </c>
-      <c r="S7" s="30">
+      <c r="S7" s="31">
         <f>'설정'!$B$6</f>
         <v/>
       </c>
@@ -13109,15 +13124,15 @@
         <f>COUNTIF($K$7:$K$86,S7)</f>
         <v/>
       </c>
-      <c r="U7" s="26">
+      <c r="U7" s="27">
         <f>COUNTIF($O$7:$O$86,S7)</f>
         <v/>
       </c>
-      <c r="V7" s="31">
+      <c r="V7" s="32">
         <f>IFERROR(AVERAGEIF($O$7:$O$86,S7,$G$7:$G$86),"")</f>
         <v/>
       </c>
-      <c r="W7" s="31">
+      <c r="W7" s="32">
         <f>IFERROR(AVERAGEIF($O$7:$O$86,S7,$H$7:$H$86),"")</f>
         <v/>
       </c>
@@ -13162,7 +13177,7 @@
         <f>'공수2'!Y8</f>
         <v/>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="28">
         <f>IF(AND(G8="",H8=""),"",N(G8)*'설정'!$C$13+N(H8)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -13170,21 +13185,21 @@
         <f>IF(I8="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I8)+1)</f>
         <v/>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="27">
         <f>IF(I8="","",IF(OR(G8="",H8=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G8&gt;='설정'!$C$6),OR('설정'!$D$6="",G8&lt;'설정'!$D$6),OR('설정'!$E$6="",H8&gt;='설정'!$E$6),OR('설정'!$F$6="",H8&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G8&gt;='설정'!$C$7),OR('설정'!$D$7="",G8&lt;'설정'!$D$7),OR('설정'!$E$7="",H8&gt;='설정'!$E$7),OR('설정'!$F$7="",H8&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G8&gt;='설정'!$C$8),OR('설정'!$D$8="",G8&lt;'설정'!$D$8),OR('설정'!$E$8="",H8&gt;='설정'!$E$8),OR('설정'!$F$8="",H8&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="29">
         <f>IF(OR(G8="",H8=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G8-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H8-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M8" s="7" t="n"/>
       <c r="N8" s="7" t="n"/>
-      <c r="O8" s="26">
+      <c r="O8" s="27">
         <f>IF(M8&lt;&gt;"",M8,K8)</f>
         <v/>
       </c>
-      <c r="P8" s="29">
+      <c r="P8" s="30">
         <f>IF(I8="","",IF(G8="","공수1 미응시",IF(H8="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -13192,7 +13207,7 @@
         <f>IF(J8="","",J8+ROW()/100000)</f>
         <v/>
       </c>
-      <c r="S8" s="32">
+      <c r="S8" s="33">
         <f>'설정'!$B$7</f>
         <v/>
       </c>
@@ -13200,15 +13215,15 @@
         <f>COUNTIF($K$7:$K$86,S8)</f>
         <v/>
       </c>
-      <c r="U8" s="26">
+      <c r="U8" s="27">
         <f>COUNTIF($O$7:$O$86,S8)</f>
         <v/>
       </c>
-      <c r="V8" s="31">
+      <c r="V8" s="32">
         <f>IFERROR(AVERAGEIF($O$7:$O$86,S8,$G$7:$G$86),"")</f>
         <v/>
       </c>
-      <c r="W8" s="31">
+      <c r="W8" s="32">
         <f>IFERROR(AVERAGEIF($O$7:$O$86,S8,$H$7:$H$86),"")</f>
         <v/>
       </c>
@@ -13253,7 +13268,7 @@
         <f>'공수2'!Y9</f>
         <v/>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="28">
         <f>IF(AND(G9="",H9=""),"",N(G9)*'설정'!$C$13+N(H9)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -13261,21 +13276,21 @@
         <f>IF(I9="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I9)+1)</f>
         <v/>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="27">
         <f>IF(I9="","",IF(OR(G9="",H9=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G9&gt;='설정'!$C$6),OR('설정'!$D$6="",G9&lt;'설정'!$D$6),OR('설정'!$E$6="",H9&gt;='설정'!$E$6),OR('설정'!$F$6="",H9&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G9&gt;='설정'!$C$7),OR('설정'!$D$7="",G9&lt;'설정'!$D$7),OR('설정'!$E$7="",H9&gt;='설정'!$E$7),OR('설정'!$F$7="",H9&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G9&gt;='설정'!$C$8),OR('설정'!$D$8="",G9&lt;'설정'!$D$8),OR('설정'!$E$8="",H9&gt;='설정'!$E$8),OR('설정'!$F$8="",H9&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="29">
         <f>IF(OR(G9="",H9=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G9-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H9-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M9" s="7" t="n"/>
       <c r="N9" s="7" t="n"/>
-      <c r="O9" s="26">
+      <c r="O9" s="27">
         <f>IF(M9&lt;&gt;"",M9,K9)</f>
         <v/>
       </c>
-      <c r="P9" s="29">
+      <c r="P9" s="30">
         <f>IF(I9="","",IF(G9="","공수1 미응시",IF(H9="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -13283,7 +13298,7 @@
         <f>IF(J9="","",J9+ROW()/100000)</f>
         <v/>
       </c>
-      <c r="S9" s="33">
+      <c r="S9" s="34">
         <f>'설정'!$B$8</f>
         <v/>
       </c>
@@ -13291,15 +13306,15 @@
         <f>COUNTIF($K$7:$K$86,S9)</f>
         <v/>
       </c>
-      <c r="U9" s="26">
+      <c r="U9" s="27">
         <f>COUNTIF($O$7:$O$86,S9)</f>
         <v/>
       </c>
-      <c r="V9" s="31">
+      <c r="V9" s="32">
         <f>IFERROR(AVERAGEIF($O$7:$O$86,S9,$G$7:$G$86),"")</f>
         <v/>
       </c>
-      <c r="W9" s="31">
+      <c r="W9" s="32">
         <f>IFERROR(AVERAGEIF($O$7:$O$86,S9,$H$7:$H$86),"")</f>
         <v/>
       </c>
@@ -13344,7 +13359,7 @@
         <f>'공수2'!Y10</f>
         <v/>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="28">
         <f>IF(AND(G10="",H10=""),"",N(G10)*'설정'!$C$13+N(H10)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -13352,21 +13367,21 @@
         <f>IF(I10="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I10)+1)</f>
         <v/>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="27">
         <f>IF(I10="","",IF(OR(G10="",H10=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G10&gt;='설정'!$C$6),OR('설정'!$D$6="",G10&lt;'설정'!$D$6),OR('설정'!$E$6="",H10&gt;='설정'!$E$6),OR('설정'!$F$6="",H10&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G10&gt;='설정'!$C$7),OR('설정'!$D$7="",G10&lt;'설정'!$D$7),OR('설정'!$E$7="",H10&gt;='설정'!$E$7),OR('설정'!$F$7="",H10&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G10&gt;='설정'!$C$8),OR('설정'!$D$8="",G10&lt;'설정'!$D$8),OR('설정'!$E$8="",H10&gt;='설정'!$E$8),OR('설정'!$F$8="",H10&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="29">
         <f>IF(OR(G10="",H10=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G10-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H10-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M10" s="7" t="n"/>
       <c r="N10" s="7" t="n"/>
-      <c r="O10" s="26">
+      <c r="O10" s="27">
         <f>IF(M10&lt;&gt;"",M10,K10)</f>
         <v/>
       </c>
-      <c r="P10" s="29">
+      <c r="P10" s="30">
         <f>IF(I10="","",IF(G10="","공수1 미응시",IF(H10="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -13374,7 +13389,7 @@
         <f>IF(J10="","",J10+ROW()/100000)</f>
         <v/>
       </c>
-      <c r="S10" s="34">
+      <c r="S10" s="35">
         <f>'설정'!$B$9</f>
         <v/>
       </c>
@@ -13382,15 +13397,15 @@
         <f>COUNTIF($K$7:$K$86,S10)</f>
         <v/>
       </c>
-      <c r="U10" s="26">
+      <c r="U10" s="27">
         <f>COUNTIF($O$7:$O$86,S10)</f>
         <v/>
       </c>
-      <c r="V10" s="31">
+      <c r="V10" s="32">
         <f>IFERROR(AVERAGEIF($O$7:$O$86,S10,$G$7:$G$86),"")</f>
         <v/>
       </c>
-      <c r="W10" s="31">
+      <c r="W10" s="32">
         <f>IFERROR(AVERAGEIF($O$7:$O$86,S10,$H$7:$H$86),"")</f>
         <v/>
       </c>
@@ -13435,7 +13450,7 @@
         <f>'공수2'!Y11</f>
         <v/>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="28">
         <f>IF(AND(G11="",H11=""),"",N(G11)*'설정'!$C$13+N(H11)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -13443,21 +13458,21 @@
         <f>IF(I11="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I11)+1)</f>
         <v/>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="27">
         <f>IF(I11="","",IF(OR(G11="",H11=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G11&gt;='설정'!$C$6),OR('설정'!$D$6="",G11&lt;'설정'!$D$6),OR('설정'!$E$6="",H11&gt;='설정'!$E$6),OR('설정'!$F$6="",H11&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G11&gt;='설정'!$C$7),OR('설정'!$D$7="",G11&lt;'설정'!$D$7),OR('설정'!$E$7="",H11&gt;='설정'!$E$7),OR('설정'!$F$7="",H11&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G11&gt;='설정'!$C$8),OR('설정'!$D$8="",G11&lt;'설정'!$D$8),OR('설정'!$E$8="",H11&gt;='설정'!$E$8),OR('설정'!$F$8="",H11&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="29">
         <f>IF(OR(G11="",H11=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G11-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H11-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M11" s="7" t="n"/>
       <c r="N11" s="7" t="n"/>
-      <c r="O11" s="26">
+      <c r="O11" s="27">
         <f>IF(M11&lt;&gt;"",M11,K11)</f>
         <v/>
       </c>
-      <c r="P11" s="29">
+      <c r="P11" s="30">
         <f>IF(I11="","",IF(G11="","공수1 미응시",IF(H11="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -13478,11 +13493,11 @@
         <f>SUM(U7:U10)</f>
         <v/>
       </c>
-      <c r="V11" s="35">
+      <c r="V11" s="36">
         <f>IFERROR(AVERAGE($G$7:$G$86),"")</f>
         <v/>
       </c>
-      <c r="W11" s="35">
+      <c r="W11" s="36">
         <f>IFERROR(AVERAGE($H$7:$H$86),"")</f>
         <v/>
       </c>
@@ -13527,7 +13542,7 @@
         <f>'공수2'!Y12</f>
         <v/>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="28">
         <f>IF(AND(G12="",H12=""),"",N(G12)*'설정'!$C$13+N(H12)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -13535,21 +13550,21 @@
         <f>IF(I12="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I12)+1)</f>
         <v/>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="27">
         <f>IF(I12="","",IF(OR(G12="",H12=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G12&gt;='설정'!$C$6),OR('설정'!$D$6="",G12&lt;'설정'!$D$6),OR('설정'!$E$6="",H12&gt;='설정'!$E$6),OR('설정'!$F$6="",H12&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G12&gt;='설정'!$C$7),OR('설정'!$D$7="",G12&lt;'설정'!$D$7),OR('설정'!$E$7="",H12&gt;='설정'!$E$7),OR('설정'!$F$7="",H12&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G12&gt;='설정'!$C$8),OR('설정'!$D$8="",G12&lt;'설정'!$D$8),OR('설정'!$E$8="",H12&gt;='설정'!$E$8),OR('설정'!$F$8="",H12&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="29">
         <f>IF(OR(G12="",H12=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G12-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H12-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M12" s="7" t="n"/>
       <c r="N12" s="7" t="n"/>
-      <c r="O12" s="26">
+      <c r="O12" s="27">
         <f>IF(M12&lt;&gt;"",M12,K12)</f>
         <v/>
       </c>
-      <c r="P12" s="29">
+      <c r="P12" s="30">
         <f>IF(I12="","",IF(G12="","공수1 미응시",IF(H12="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -13590,7 +13605,7 @@
         <f>'공수2'!Y13</f>
         <v/>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="28">
         <f>IF(AND(G13="",H13=""),"",N(G13)*'설정'!$C$13+N(H13)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -13598,21 +13613,21 @@
         <f>IF(I13="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I13)+1)</f>
         <v/>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="27">
         <f>IF(I13="","",IF(OR(G13="",H13=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G13&gt;='설정'!$C$6),OR('설정'!$D$6="",G13&lt;'설정'!$D$6),OR('설정'!$E$6="",H13&gt;='설정'!$E$6),OR('설정'!$F$6="",H13&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G13&gt;='설정'!$C$7),OR('설정'!$D$7="",G13&lt;'설정'!$D$7),OR('설정'!$E$7="",H13&gt;='설정'!$E$7),OR('설정'!$F$7="",H13&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G13&gt;='설정'!$C$8),OR('설정'!$D$8="",G13&lt;'설정'!$D$8),OR('설정'!$E$8="",H13&gt;='설정'!$E$8),OR('설정'!$F$8="",H13&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="29">
         <f>IF(OR(G13="",H13=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G13-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H13-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n"/>
-      <c r="O13" s="26">
+      <c r="O13" s="27">
         <f>IF(M13&lt;&gt;"",M13,K13)</f>
         <v/>
       </c>
-      <c r="P13" s="29">
+      <c r="P13" s="30">
         <f>IF(I13="","",IF(G13="","공수1 미응시",IF(H13="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -13661,7 +13676,7 @@
         <f>'공수2'!Y14</f>
         <v/>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="28">
         <f>IF(AND(G14="",H14=""),"",N(G14)*'설정'!$C$13+N(H14)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -13669,21 +13684,21 @@
         <f>IF(I14="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I14)+1)</f>
         <v/>
       </c>
-      <c r="K14" s="26">
+      <c r="K14" s="27">
         <f>IF(I14="","",IF(OR(G14="",H14=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G14&gt;='설정'!$C$6),OR('설정'!$D$6="",G14&lt;'설정'!$D$6),OR('설정'!$E$6="",H14&gt;='설정'!$E$6),OR('설정'!$F$6="",H14&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G14&gt;='설정'!$C$7),OR('설정'!$D$7="",G14&lt;'설정'!$D$7),OR('설정'!$E$7="",H14&gt;='설정'!$E$7),OR('설정'!$F$7="",H14&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G14&gt;='설정'!$C$8),OR('설정'!$D$8="",G14&lt;'설정'!$D$8),OR('설정'!$E$8="",H14&gt;='설정'!$E$8),OR('설정'!$F$8="",H14&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="29">
         <f>IF(OR(G14="",H14=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G14-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H14-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M14" s="7" t="n"/>
       <c r="N14" s="7" t="n"/>
-      <c r="O14" s="26">
+      <c r="O14" s="27">
         <f>IF(M14&lt;&gt;"",M14,K14)</f>
         <v/>
       </c>
-      <c r="P14" s="29">
+      <c r="P14" s="30">
         <f>IF(I14="","",IF(G14="","공수1 미응시",IF(H14="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -13724,7 +13739,7 @@
         <f>'공수2'!Y15</f>
         <v/>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="28">
         <f>IF(AND(G15="",H15=""),"",N(G15)*'설정'!$C$13+N(H15)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -13732,21 +13747,21 @@
         <f>IF(I15="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I15)+1)</f>
         <v/>
       </c>
-      <c r="K15" s="26">
+      <c r="K15" s="27">
         <f>IF(I15="","",IF(OR(G15="",H15=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G15&gt;='설정'!$C$6),OR('설정'!$D$6="",G15&lt;'설정'!$D$6),OR('설정'!$E$6="",H15&gt;='설정'!$E$6),OR('설정'!$F$6="",H15&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G15&gt;='설정'!$C$7),OR('설정'!$D$7="",G15&lt;'설정'!$D$7),OR('설정'!$E$7="",H15&gt;='설정'!$E$7),OR('설정'!$F$7="",H15&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G15&gt;='설정'!$C$8),OR('설정'!$D$8="",G15&lt;'설정'!$D$8),OR('설정'!$E$8="",H15&gt;='설정'!$E$8),OR('설정'!$F$8="",H15&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="29">
         <f>IF(OR(G15="",H15=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G15-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H15-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
-      <c r="O15" s="26">
+      <c r="O15" s="27">
         <f>IF(M15&lt;&gt;"",M15,K15)</f>
         <v/>
       </c>
-      <c r="P15" s="29">
+      <c r="P15" s="30">
         <f>IF(I15="","",IF(G15="","공수1 미응시",IF(H15="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -13787,7 +13802,7 @@
         <f>'공수2'!Y16</f>
         <v/>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="28">
         <f>IF(AND(G16="",H16=""),"",N(G16)*'설정'!$C$13+N(H16)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -13795,21 +13810,21 @@
         <f>IF(I16="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I16)+1)</f>
         <v/>
       </c>
-      <c r="K16" s="26">
+      <c r="K16" s="27">
         <f>IF(I16="","",IF(OR(G16="",H16=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G16&gt;='설정'!$C$6),OR('설정'!$D$6="",G16&lt;'설정'!$D$6),OR('설정'!$E$6="",H16&gt;='설정'!$E$6),OR('설정'!$F$6="",H16&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G16&gt;='설정'!$C$7),OR('설정'!$D$7="",G16&lt;'설정'!$D$7),OR('설정'!$E$7="",H16&gt;='설정'!$E$7),OR('설정'!$F$7="",H16&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G16&gt;='설정'!$C$8),OR('설정'!$D$8="",G16&lt;'설정'!$D$8),OR('설정'!$E$8="",H16&gt;='설정'!$E$8),OR('설정'!$F$8="",H16&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="29">
         <f>IF(OR(G16="",H16=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G16-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H16-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M16" s="7" t="n"/>
       <c r="N16" s="7" t="n"/>
-      <c r="O16" s="26">
+      <c r="O16" s="27">
         <f>IF(M16&lt;&gt;"",M16,K16)</f>
         <v/>
       </c>
-      <c r="P16" s="29">
+      <c r="P16" s="30">
         <f>IF(I16="","",IF(G16="","공수1 미응시",IF(H16="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -13850,7 +13865,7 @@
         <f>'공수2'!Y17</f>
         <v/>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="28">
         <f>IF(AND(G17="",H17=""),"",N(G17)*'설정'!$C$13+N(H17)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -13858,21 +13873,21 @@
         <f>IF(I17="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I17)+1)</f>
         <v/>
       </c>
-      <c r="K17" s="26">
+      <c r="K17" s="27">
         <f>IF(I17="","",IF(OR(G17="",H17=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G17&gt;='설정'!$C$6),OR('설정'!$D$6="",G17&lt;'설정'!$D$6),OR('설정'!$E$6="",H17&gt;='설정'!$E$6),OR('설정'!$F$6="",H17&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G17&gt;='설정'!$C$7),OR('설정'!$D$7="",G17&lt;'설정'!$D$7),OR('설정'!$E$7="",H17&gt;='설정'!$E$7),OR('설정'!$F$7="",H17&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G17&gt;='설정'!$C$8),OR('설정'!$D$8="",G17&lt;'설정'!$D$8),OR('설정'!$E$8="",H17&gt;='설정'!$E$8),OR('설정'!$F$8="",H17&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L17" s="28">
+      <c r="L17" s="29">
         <f>IF(OR(G17="",H17=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G17-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H17-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="7" t="n"/>
-      <c r="O17" s="26">
+      <c r="O17" s="27">
         <f>IF(M17&lt;&gt;"",M17,K17)</f>
         <v/>
       </c>
-      <c r="P17" s="29">
+      <c r="P17" s="30">
         <f>IF(I17="","",IF(G17="","공수1 미응시",IF(H17="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -13913,7 +13928,7 @@
         <f>'공수2'!Y18</f>
         <v/>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="28">
         <f>IF(AND(G18="",H18=""),"",N(G18)*'설정'!$C$13+N(H18)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -13921,21 +13936,21 @@
         <f>IF(I18="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I18)+1)</f>
         <v/>
       </c>
-      <c r="K18" s="26">
+      <c r="K18" s="27">
         <f>IF(I18="","",IF(OR(G18="",H18=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G18&gt;='설정'!$C$6),OR('설정'!$D$6="",G18&lt;'설정'!$D$6),OR('설정'!$E$6="",H18&gt;='설정'!$E$6),OR('설정'!$F$6="",H18&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G18&gt;='설정'!$C$7),OR('설정'!$D$7="",G18&lt;'설정'!$D$7),OR('설정'!$E$7="",H18&gt;='설정'!$E$7),OR('설정'!$F$7="",H18&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G18&gt;='설정'!$C$8),OR('설정'!$D$8="",G18&lt;'설정'!$D$8),OR('설정'!$E$8="",H18&gt;='설정'!$E$8),OR('설정'!$F$8="",H18&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L18" s="28">
+      <c r="L18" s="29">
         <f>IF(OR(G18="",H18=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G18-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H18-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M18" s="7" t="n"/>
       <c r="N18" s="7" t="n"/>
-      <c r="O18" s="26">
+      <c r="O18" s="27">
         <f>IF(M18&lt;&gt;"",M18,K18)</f>
         <v/>
       </c>
-      <c r="P18" s="29">
+      <c r="P18" s="30">
         <f>IF(I18="","",IF(G18="","공수1 미응시",IF(H18="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -13976,7 +13991,7 @@
         <f>'공수2'!Y19</f>
         <v/>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="28">
         <f>IF(AND(G19="",H19=""),"",N(G19)*'설정'!$C$13+N(H19)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -13984,21 +13999,21 @@
         <f>IF(I19="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I19)+1)</f>
         <v/>
       </c>
-      <c r="K19" s="26">
+      <c r="K19" s="27">
         <f>IF(I19="","",IF(OR(G19="",H19=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G19&gt;='설정'!$C$6),OR('설정'!$D$6="",G19&lt;'설정'!$D$6),OR('설정'!$E$6="",H19&gt;='설정'!$E$6),OR('설정'!$F$6="",H19&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G19&gt;='설정'!$C$7),OR('설정'!$D$7="",G19&lt;'설정'!$D$7),OR('설정'!$E$7="",H19&gt;='설정'!$E$7),OR('설정'!$F$7="",H19&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G19&gt;='설정'!$C$8),OR('설정'!$D$8="",G19&lt;'설정'!$D$8),OR('설정'!$E$8="",H19&gt;='설정'!$E$8),OR('설정'!$F$8="",H19&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L19" s="28">
+      <c r="L19" s="29">
         <f>IF(OR(G19="",H19=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G19-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H19-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n"/>
-      <c r="O19" s="26">
+      <c r="O19" s="27">
         <f>IF(M19&lt;&gt;"",M19,K19)</f>
         <v/>
       </c>
-      <c r="P19" s="29">
+      <c r="P19" s="30">
         <f>IF(I19="","",IF(G19="","공수1 미응시",IF(H19="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14039,7 +14054,7 @@
         <f>'공수2'!Y20</f>
         <v/>
       </c>
-      <c r="I20" s="27">
+      <c r="I20" s="28">
         <f>IF(AND(G20="",H20=""),"",N(G20)*'설정'!$C$13+N(H20)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14047,21 +14062,21 @@
         <f>IF(I20="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I20)+1)</f>
         <v/>
       </c>
-      <c r="K20" s="26">
+      <c r="K20" s="27">
         <f>IF(I20="","",IF(OR(G20="",H20=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G20&gt;='설정'!$C$6),OR('설정'!$D$6="",G20&lt;'설정'!$D$6),OR('설정'!$E$6="",H20&gt;='설정'!$E$6),OR('설정'!$F$6="",H20&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G20&gt;='설정'!$C$7),OR('설정'!$D$7="",G20&lt;'설정'!$D$7),OR('설정'!$E$7="",H20&gt;='설정'!$E$7),OR('설정'!$F$7="",H20&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G20&gt;='설정'!$C$8),OR('설정'!$D$8="",G20&lt;'설정'!$D$8),OR('설정'!$E$8="",H20&gt;='설정'!$E$8),OR('설정'!$F$8="",H20&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L20" s="28">
+      <c r="L20" s="29">
         <f>IF(OR(G20="",H20=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G20-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H20-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M20" s="7" t="n"/>
       <c r="N20" s="7" t="n"/>
-      <c r="O20" s="26">
+      <c r="O20" s="27">
         <f>IF(M20&lt;&gt;"",M20,K20)</f>
         <v/>
       </c>
-      <c r="P20" s="29">
+      <c r="P20" s="30">
         <f>IF(I20="","",IF(G20="","공수1 미응시",IF(H20="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14102,7 +14117,7 @@
         <f>'공수2'!Y21</f>
         <v/>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="28">
         <f>IF(AND(G21="",H21=""),"",N(G21)*'설정'!$C$13+N(H21)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14110,21 +14125,21 @@
         <f>IF(I21="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I21)+1)</f>
         <v/>
       </c>
-      <c r="K21" s="26">
+      <c r="K21" s="27">
         <f>IF(I21="","",IF(OR(G21="",H21=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G21&gt;='설정'!$C$6),OR('설정'!$D$6="",G21&lt;'설정'!$D$6),OR('설정'!$E$6="",H21&gt;='설정'!$E$6),OR('설정'!$F$6="",H21&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G21&gt;='설정'!$C$7),OR('설정'!$D$7="",G21&lt;'설정'!$D$7),OR('설정'!$E$7="",H21&gt;='설정'!$E$7),OR('설정'!$F$7="",H21&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G21&gt;='설정'!$C$8),OR('설정'!$D$8="",G21&lt;'설정'!$D$8),OR('설정'!$E$8="",H21&gt;='설정'!$E$8),OR('설정'!$F$8="",H21&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="29">
         <f>IF(OR(G21="",H21=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G21-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H21-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n"/>
-      <c r="O21" s="26">
+      <c r="O21" s="27">
         <f>IF(M21&lt;&gt;"",M21,K21)</f>
         <v/>
       </c>
-      <c r="P21" s="29">
+      <c r="P21" s="30">
         <f>IF(I21="","",IF(G21="","공수1 미응시",IF(H21="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14165,7 +14180,7 @@
         <f>'공수2'!Y22</f>
         <v/>
       </c>
-      <c r="I22" s="27">
+      <c r="I22" s="28">
         <f>IF(AND(G22="",H22=""),"",N(G22)*'설정'!$C$13+N(H22)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14173,21 +14188,21 @@
         <f>IF(I22="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I22)+1)</f>
         <v/>
       </c>
-      <c r="K22" s="26">
+      <c r="K22" s="27">
         <f>IF(I22="","",IF(OR(G22="",H22=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G22&gt;='설정'!$C$6),OR('설정'!$D$6="",G22&lt;'설정'!$D$6),OR('설정'!$E$6="",H22&gt;='설정'!$E$6),OR('설정'!$F$6="",H22&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G22&gt;='설정'!$C$7),OR('설정'!$D$7="",G22&lt;'설정'!$D$7),OR('설정'!$E$7="",H22&gt;='설정'!$E$7),OR('설정'!$F$7="",H22&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G22&gt;='설정'!$C$8),OR('설정'!$D$8="",G22&lt;'설정'!$D$8),OR('설정'!$E$8="",H22&gt;='설정'!$E$8),OR('설정'!$F$8="",H22&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L22" s="28">
+      <c r="L22" s="29">
         <f>IF(OR(G22="",H22=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G22-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H22-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M22" s="7" t="n"/>
       <c r="N22" s="7" t="n"/>
-      <c r="O22" s="26">
+      <c r="O22" s="27">
         <f>IF(M22&lt;&gt;"",M22,K22)</f>
         <v/>
       </c>
-      <c r="P22" s="29">
+      <c r="P22" s="30">
         <f>IF(I22="","",IF(G22="","공수1 미응시",IF(H22="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14228,7 +14243,7 @@
         <f>'공수2'!Y23</f>
         <v/>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="28">
         <f>IF(AND(G23="",H23=""),"",N(G23)*'설정'!$C$13+N(H23)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14236,21 +14251,21 @@
         <f>IF(I23="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I23)+1)</f>
         <v/>
       </c>
-      <c r="K23" s="26">
+      <c r="K23" s="27">
         <f>IF(I23="","",IF(OR(G23="",H23=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G23&gt;='설정'!$C$6),OR('설정'!$D$6="",G23&lt;'설정'!$D$6),OR('설정'!$E$6="",H23&gt;='설정'!$E$6),OR('설정'!$F$6="",H23&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G23&gt;='설정'!$C$7),OR('설정'!$D$7="",G23&lt;'설정'!$D$7),OR('설정'!$E$7="",H23&gt;='설정'!$E$7),OR('설정'!$F$7="",H23&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G23&gt;='설정'!$C$8),OR('설정'!$D$8="",G23&lt;'설정'!$D$8),OR('설정'!$E$8="",H23&gt;='설정'!$E$8),OR('설정'!$F$8="",H23&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="29">
         <f>IF(OR(G23="",H23=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G23-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H23-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n"/>
-      <c r="O23" s="26">
+      <c r="O23" s="27">
         <f>IF(M23&lt;&gt;"",M23,K23)</f>
         <v/>
       </c>
-      <c r="P23" s="29">
+      <c r="P23" s="30">
         <f>IF(I23="","",IF(G23="","공수1 미응시",IF(H23="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14291,7 +14306,7 @@
         <f>'공수2'!Y24</f>
         <v/>
       </c>
-      <c r="I24" s="27">
+      <c r="I24" s="28">
         <f>IF(AND(G24="",H24=""),"",N(G24)*'설정'!$C$13+N(H24)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14299,21 +14314,21 @@
         <f>IF(I24="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I24)+1)</f>
         <v/>
       </c>
-      <c r="K24" s="26">
+      <c r="K24" s="27">
         <f>IF(I24="","",IF(OR(G24="",H24=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G24&gt;='설정'!$C$6),OR('설정'!$D$6="",G24&lt;'설정'!$D$6),OR('설정'!$E$6="",H24&gt;='설정'!$E$6),OR('설정'!$F$6="",H24&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G24&gt;='설정'!$C$7),OR('설정'!$D$7="",G24&lt;'설정'!$D$7),OR('설정'!$E$7="",H24&gt;='설정'!$E$7),OR('설정'!$F$7="",H24&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G24&gt;='설정'!$C$8),OR('설정'!$D$8="",G24&lt;'설정'!$D$8),OR('설정'!$E$8="",H24&gt;='설정'!$E$8),OR('설정'!$F$8="",H24&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L24" s="28">
+      <c r="L24" s="29">
         <f>IF(OR(G24="",H24=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G24-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H24-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M24" s="7" t="n"/>
       <c r="N24" s="7" t="n"/>
-      <c r="O24" s="26">
+      <c r="O24" s="27">
         <f>IF(M24&lt;&gt;"",M24,K24)</f>
         <v/>
       </c>
-      <c r="P24" s="29">
+      <c r="P24" s="30">
         <f>IF(I24="","",IF(G24="","공수1 미응시",IF(H24="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14354,7 +14369,7 @@
         <f>'공수2'!Y25</f>
         <v/>
       </c>
-      <c r="I25" s="27">
+      <c r="I25" s="28">
         <f>IF(AND(G25="",H25=""),"",N(G25)*'설정'!$C$13+N(H25)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14362,21 +14377,21 @@
         <f>IF(I25="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I25)+1)</f>
         <v/>
       </c>
-      <c r="K25" s="26">
+      <c r="K25" s="27">
         <f>IF(I25="","",IF(OR(G25="",H25=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G25&gt;='설정'!$C$6),OR('설정'!$D$6="",G25&lt;'설정'!$D$6),OR('설정'!$E$6="",H25&gt;='설정'!$E$6),OR('설정'!$F$6="",H25&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G25&gt;='설정'!$C$7),OR('설정'!$D$7="",G25&lt;'설정'!$D$7),OR('설정'!$E$7="",H25&gt;='설정'!$E$7),OR('설정'!$F$7="",H25&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G25&gt;='설정'!$C$8),OR('설정'!$D$8="",G25&lt;'설정'!$D$8),OR('설정'!$E$8="",H25&gt;='설정'!$E$8),OR('설정'!$F$8="",H25&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L25" s="28">
+      <c r="L25" s="29">
         <f>IF(OR(G25="",H25=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G25-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H25-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
-      <c r="O25" s="26">
+      <c r="O25" s="27">
         <f>IF(M25&lt;&gt;"",M25,K25)</f>
         <v/>
       </c>
-      <c r="P25" s="29">
+      <c r="P25" s="30">
         <f>IF(I25="","",IF(G25="","공수1 미응시",IF(H25="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14417,7 +14432,7 @@
         <f>'공수2'!Y26</f>
         <v/>
       </c>
-      <c r="I26" s="27">
+      <c r="I26" s="28">
         <f>IF(AND(G26="",H26=""),"",N(G26)*'설정'!$C$13+N(H26)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14425,21 +14440,21 @@
         <f>IF(I26="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I26)+1)</f>
         <v/>
       </c>
-      <c r="K26" s="26">
+      <c r="K26" s="27">
         <f>IF(I26="","",IF(OR(G26="",H26=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G26&gt;='설정'!$C$6),OR('설정'!$D$6="",G26&lt;'설정'!$D$6),OR('설정'!$E$6="",H26&gt;='설정'!$E$6),OR('설정'!$F$6="",H26&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G26&gt;='설정'!$C$7),OR('설정'!$D$7="",G26&lt;'설정'!$D$7),OR('설정'!$E$7="",H26&gt;='설정'!$E$7),OR('설정'!$F$7="",H26&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G26&gt;='설정'!$C$8),OR('설정'!$D$8="",G26&lt;'설정'!$D$8),OR('설정'!$E$8="",H26&gt;='설정'!$E$8),OR('설정'!$F$8="",H26&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L26" s="28">
+      <c r="L26" s="29">
         <f>IF(OR(G26="",H26=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G26-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H26-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="7" t="n"/>
-      <c r="O26" s="26">
+      <c r="O26" s="27">
         <f>IF(M26&lt;&gt;"",M26,K26)</f>
         <v/>
       </c>
-      <c r="P26" s="29">
+      <c r="P26" s="30">
         <f>IF(I26="","",IF(G26="","공수1 미응시",IF(H26="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14480,7 +14495,7 @@
         <f>'공수2'!Y27</f>
         <v/>
       </c>
-      <c r="I27" s="27">
+      <c r="I27" s="28">
         <f>IF(AND(G27="",H27=""),"",N(G27)*'설정'!$C$13+N(H27)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14488,21 +14503,21 @@
         <f>IF(I27="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I27)+1)</f>
         <v/>
       </c>
-      <c r="K27" s="26">
+      <c r="K27" s="27">
         <f>IF(I27="","",IF(OR(G27="",H27=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G27&gt;='설정'!$C$6),OR('설정'!$D$6="",G27&lt;'설정'!$D$6),OR('설정'!$E$6="",H27&gt;='설정'!$E$6),OR('설정'!$F$6="",H27&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G27&gt;='설정'!$C$7),OR('설정'!$D$7="",G27&lt;'설정'!$D$7),OR('설정'!$E$7="",H27&gt;='설정'!$E$7),OR('설정'!$F$7="",H27&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G27&gt;='설정'!$C$8),OR('설정'!$D$8="",G27&lt;'설정'!$D$8),OR('설정'!$E$8="",H27&gt;='설정'!$E$8),OR('설정'!$F$8="",H27&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L27" s="28">
+      <c r="L27" s="29">
         <f>IF(OR(G27="",H27=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G27-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H27-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
-      <c r="O27" s="26">
+      <c r="O27" s="27">
         <f>IF(M27&lt;&gt;"",M27,K27)</f>
         <v/>
       </c>
-      <c r="P27" s="29">
+      <c r="P27" s="30">
         <f>IF(I27="","",IF(G27="","공수1 미응시",IF(H27="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14543,7 +14558,7 @@
         <f>'공수2'!Y28</f>
         <v/>
       </c>
-      <c r="I28" s="27">
+      <c r="I28" s="28">
         <f>IF(AND(G28="",H28=""),"",N(G28)*'설정'!$C$13+N(H28)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14551,21 +14566,21 @@
         <f>IF(I28="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I28)+1)</f>
         <v/>
       </c>
-      <c r="K28" s="26">
+      <c r="K28" s="27">
         <f>IF(I28="","",IF(OR(G28="",H28=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G28&gt;='설정'!$C$6),OR('설정'!$D$6="",G28&lt;'설정'!$D$6),OR('설정'!$E$6="",H28&gt;='설정'!$E$6),OR('설정'!$F$6="",H28&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G28&gt;='설정'!$C$7),OR('설정'!$D$7="",G28&lt;'설정'!$D$7),OR('설정'!$E$7="",H28&gt;='설정'!$E$7),OR('설정'!$F$7="",H28&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G28&gt;='설정'!$C$8),OR('설정'!$D$8="",G28&lt;'설정'!$D$8),OR('설정'!$E$8="",H28&gt;='설정'!$E$8),OR('설정'!$F$8="",H28&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L28" s="28">
+      <c r="L28" s="29">
         <f>IF(OR(G28="",H28=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G28-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H28-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="7" t="n"/>
-      <c r="O28" s="26">
+      <c r="O28" s="27">
         <f>IF(M28&lt;&gt;"",M28,K28)</f>
         <v/>
       </c>
-      <c r="P28" s="29">
+      <c r="P28" s="30">
         <f>IF(I28="","",IF(G28="","공수1 미응시",IF(H28="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14606,7 +14621,7 @@
         <f>'공수2'!Y29</f>
         <v/>
       </c>
-      <c r="I29" s="27">
+      <c r="I29" s="28">
         <f>IF(AND(G29="",H29=""),"",N(G29)*'설정'!$C$13+N(H29)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14614,21 +14629,21 @@
         <f>IF(I29="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I29)+1)</f>
         <v/>
       </c>
-      <c r="K29" s="26">
+      <c r="K29" s="27">
         <f>IF(I29="","",IF(OR(G29="",H29=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G29&gt;='설정'!$C$6),OR('설정'!$D$6="",G29&lt;'설정'!$D$6),OR('설정'!$E$6="",H29&gt;='설정'!$E$6),OR('설정'!$F$6="",H29&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G29&gt;='설정'!$C$7),OR('설정'!$D$7="",G29&lt;'설정'!$D$7),OR('설정'!$E$7="",H29&gt;='설정'!$E$7),OR('설정'!$F$7="",H29&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G29&gt;='설정'!$C$8),OR('설정'!$D$8="",G29&lt;'설정'!$D$8),OR('설정'!$E$8="",H29&gt;='설정'!$E$8),OR('설정'!$F$8="",H29&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L29" s="28">
+      <c r="L29" s="29">
         <f>IF(OR(G29="",H29=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G29-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H29-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
-      <c r="O29" s="26">
+      <c r="O29" s="27">
         <f>IF(M29&lt;&gt;"",M29,K29)</f>
         <v/>
       </c>
-      <c r="P29" s="29">
+      <c r="P29" s="30">
         <f>IF(I29="","",IF(G29="","공수1 미응시",IF(H29="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14669,7 +14684,7 @@
         <f>'공수2'!Y30</f>
         <v/>
       </c>
-      <c r="I30" s="27">
+      <c r="I30" s="28">
         <f>IF(AND(G30="",H30=""),"",N(G30)*'설정'!$C$13+N(H30)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14677,21 +14692,21 @@
         <f>IF(I30="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I30)+1)</f>
         <v/>
       </c>
-      <c r="K30" s="26">
+      <c r="K30" s="27">
         <f>IF(I30="","",IF(OR(G30="",H30=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G30&gt;='설정'!$C$6),OR('설정'!$D$6="",G30&lt;'설정'!$D$6),OR('설정'!$E$6="",H30&gt;='설정'!$E$6),OR('설정'!$F$6="",H30&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G30&gt;='설정'!$C$7),OR('설정'!$D$7="",G30&lt;'설정'!$D$7),OR('설정'!$E$7="",H30&gt;='설정'!$E$7),OR('설정'!$F$7="",H30&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G30&gt;='설정'!$C$8),OR('설정'!$D$8="",G30&lt;'설정'!$D$8),OR('설정'!$E$8="",H30&gt;='설정'!$E$8),OR('설정'!$F$8="",H30&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L30" s="28">
+      <c r="L30" s="29">
         <f>IF(OR(G30="",H30=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G30-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H30-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M30" s="7" t="n"/>
       <c r="N30" s="7" t="n"/>
-      <c r="O30" s="26">
+      <c r="O30" s="27">
         <f>IF(M30&lt;&gt;"",M30,K30)</f>
         <v/>
       </c>
-      <c r="P30" s="29">
+      <c r="P30" s="30">
         <f>IF(I30="","",IF(G30="","공수1 미응시",IF(H30="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14732,7 +14747,7 @@
         <f>'공수2'!Y31</f>
         <v/>
       </c>
-      <c r="I31" s="27">
+      <c r="I31" s="28">
         <f>IF(AND(G31="",H31=""),"",N(G31)*'설정'!$C$13+N(H31)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14740,21 +14755,21 @@
         <f>IF(I31="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I31)+1)</f>
         <v/>
       </c>
-      <c r="K31" s="26">
+      <c r="K31" s="27">
         <f>IF(I31="","",IF(OR(G31="",H31=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G31&gt;='설정'!$C$6),OR('설정'!$D$6="",G31&lt;'설정'!$D$6),OR('설정'!$E$6="",H31&gt;='설정'!$E$6),OR('설정'!$F$6="",H31&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G31&gt;='설정'!$C$7),OR('설정'!$D$7="",G31&lt;'설정'!$D$7),OR('설정'!$E$7="",H31&gt;='설정'!$E$7),OR('설정'!$F$7="",H31&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G31&gt;='설정'!$C$8),OR('설정'!$D$8="",G31&lt;'설정'!$D$8),OR('설정'!$E$8="",H31&gt;='설정'!$E$8),OR('설정'!$F$8="",H31&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="29">
         <f>IF(OR(G31="",H31=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G31-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H31-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n"/>
-      <c r="O31" s="26">
+      <c r="O31" s="27">
         <f>IF(M31&lt;&gt;"",M31,K31)</f>
         <v/>
       </c>
-      <c r="P31" s="29">
+      <c r="P31" s="30">
         <f>IF(I31="","",IF(G31="","공수1 미응시",IF(H31="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14795,7 +14810,7 @@
         <f>'공수2'!Y32</f>
         <v/>
       </c>
-      <c r="I32" s="27">
+      <c r="I32" s="28">
         <f>IF(AND(G32="",H32=""),"",N(G32)*'설정'!$C$13+N(H32)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14803,21 +14818,21 @@
         <f>IF(I32="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I32)+1)</f>
         <v/>
       </c>
-      <c r="K32" s="26">
+      <c r="K32" s="27">
         <f>IF(I32="","",IF(OR(G32="",H32=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G32&gt;='설정'!$C$6),OR('설정'!$D$6="",G32&lt;'설정'!$D$6),OR('설정'!$E$6="",H32&gt;='설정'!$E$6),OR('설정'!$F$6="",H32&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G32&gt;='설정'!$C$7),OR('설정'!$D$7="",G32&lt;'설정'!$D$7),OR('설정'!$E$7="",H32&gt;='설정'!$E$7),OR('설정'!$F$7="",H32&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G32&gt;='설정'!$C$8),OR('설정'!$D$8="",G32&lt;'설정'!$D$8),OR('설정'!$E$8="",H32&gt;='설정'!$E$8),OR('설정'!$F$8="",H32&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L32" s="28">
+      <c r="L32" s="29">
         <f>IF(OR(G32="",H32=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G32-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H32-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M32" s="7" t="n"/>
       <c r="N32" s="7" t="n"/>
-      <c r="O32" s="26">
+      <c r="O32" s="27">
         <f>IF(M32&lt;&gt;"",M32,K32)</f>
         <v/>
       </c>
-      <c r="P32" s="29">
+      <c r="P32" s="30">
         <f>IF(I32="","",IF(G32="","공수1 미응시",IF(H32="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14858,7 +14873,7 @@
         <f>'공수2'!Y33</f>
         <v/>
       </c>
-      <c r="I33" s="27">
+      <c r="I33" s="28">
         <f>IF(AND(G33="",H33=""),"",N(G33)*'설정'!$C$13+N(H33)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14866,21 +14881,21 @@
         <f>IF(I33="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I33)+1)</f>
         <v/>
       </c>
-      <c r="K33" s="26">
+      <c r="K33" s="27">
         <f>IF(I33="","",IF(OR(G33="",H33=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G33&gt;='설정'!$C$6),OR('설정'!$D$6="",G33&lt;'설정'!$D$6),OR('설정'!$E$6="",H33&gt;='설정'!$E$6),OR('설정'!$F$6="",H33&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G33&gt;='설정'!$C$7),OR('설정'!$D$7="",G33&lt;'설정'!$D$7),OR('설정'!$E$7="",H33&gt;='설정'!$E$7),OR('설정'!$F$7="",H33&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G33&gt;='설정'!$C$8),OR('설정'!$D$8="",G33&lt;'설정'!$D$8),OR('설정'!$E$8="",H33&gt;='설정'!$E$8),OR('설정'!$F$8="",H33&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L33" s="28">
+      <c r="L33" s="29">
         <f>IF(OR(G33="",H33=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G33-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H33-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M33" s="7" t="n"/>
       <c r="N33" s="7" t="n"/>
-      <c r="O33" s="26">
+      <c r="O33" s="27">
         <f>IF(M33&lt;&gt;"",M33,K33)</f>
         <v/>
       </c>
-      <c r="P33" s="29">
+      <c r="P33" s="30">
         <f>IF(I33="","",IF(G33="","공수1 미응시",IF(H33="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14921,7 +14936,7 @@
         <f>'공수2'!Y34</f>
         <v/>
       </c>
-      <c r="I34" s="27">
+      <c r="I34" s="28">
         <f>IF(AND(G34="",H34=""),"",N(G34)*'설정'!$C$13+N(H34)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14929,21 +14944,21 @@
         <f>IF(I34="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I34)+1)</f>
         <v/>
       </c>
-      <c r="K34" s="26">
+      <c r="K34" s="27">
         <f>IF(I34="","",IF(OR(G34="",H34=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G34&gt;='설정'!$C$6),OR('설정'!$D$6="",G34&lt;'설정'!$D$6),OR('설정'!$E$6="",H34&gt;='설정'!$E$6),OR('설정'!$F$6="",H34&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G34&gt;='설정'!$C$7),OR('설정'!$D$7="",G34&lt;'설정'!$D$7),OR('설정'!$E$7="",H34&gt;='설정'!$E$7),OR('설정'!$F$7="",H34&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G34&gt;='설정'!$C$8),OR('설정'!$D$8="",G34&lt;'설정'!$D$8),OR('설정'!$E$8="",H34&gt;='설정'!$E$8),OR('설정'!$F$8="",H34&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L34" s="28">
+      <c r="L34" s="29">
         <f>IF(OR(G34="",H34=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G34-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H34-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M34" s="7" t="n"/>
       <c r="N34" s="7" t="n"/>
-      <c r="O34" s="26">
+      <c r="O34" s="27">
         <f>IF(M34&lt;&gt;"",M34,K34)</f>
         <v/>
       </c>
-      <c r="P34" s="29">
+      <c r="P34" s="30">
         <f>IF(I34="","",IF(G34="","공수1 미응시",IF(H34="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -14984,7 +14999,7 @@
         <f>'공수2'!Y35</f>
         <v/>
       </c>
-      <c r="I35" s="27">
+      <c r="I35" s="28">
         <f>IF(AND(G35="",H35=""),"",N(G35)*'설정'!$C$13+N(H35)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -14992,21 +15007,21 @@
         <f>IF(I35="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I35)+1)</f>
         <v/>
       </c>
-      <c r="K35" s="26">
+      <c r="K35" s="27">
         <f>IF(I35="","",IF(OR(G35="",H35=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G35&gt;='설정'!$C$6),OR('설정'!$D$6="",G35&lt;'설정'!$D$6),OR('설정'!$E$6="",H35&gt;='설정'!$E$6),OR('설정'!$F$6="",H35&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G35&gt;='설정'!$C$7),OR('설정'!$D$7="",G35&lt;'설정'!$D$7),OR('설정'!$E$7="",H35&gt;='설정'!$E$7),OR('설정'!$F$7="",H35&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G35&gt;='설정'!$C$8),OR('설정'!$D$8="",G35&lt;'설정'!$D$8),OR('설정'!$E$8="",H35&gt;='설정'!$E$8),OR('설정'!$F$8="",H35&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L35" s="28">
+      <c r="L35" s="29">
         <f>IF(OR(G35="",H35=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G35-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H35-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M35" s="7" t="n"/>
       <c r="N35" s="7" t="n"/>
-      <c r="O35" s="26">
+      <c r="O35" s="27">
         <f>IF(M35&lt;&gt;"",M35,K35)</f>
         <v/>
       </c>
-      <c r="P35" s="29">
+      <c r="P35" s="30">
         <f>IF(I35="","",IF(G35="","공수1 미응시",IF(H35="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15047,7 +15062,7 @@
         <f>'공수2'!Y36</f>
         <v/>
       </c>
-      <c r="I36" s="27">
+      <c r="I36" s="28">
         <f>IF(AND(G36="",H36=""),"",N(G36)*'설정'!$C$13+N(H36)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -15055,21 +15070,21 @@
         <f>IF(I36="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I36)+1)</f>
         <v/>
       </c>
-      <c r="K36" s="26">
+      <c r="K36" s="27">
         <f>IF(I36="","",IF(OR(G36="",H36=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G36&gt;='설정'!$C$6),OR('설정'!$D$6="",G36&lt;'설정'!$D$6),OR('설정'!$E$6="",H36&gt;='설정'!$E$6),OR('설정'!$F$6="",H36&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G36&gt;='설정'!$C$7),OR('설정'!$D$7="",G36&lt;'설정'!$D$7),OR('설정'!$E$7="",H36&gt;='설정'!$E$7),OR('설정'!$F$7="",H36&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G36&gt;='설정'!$C$8),OR('설정'!$D$8="",G36&lt;'설정'!$D$8),OR('설정'!$E$8="",H36&gt;='설정'!$E$8),OR('설정'!$F$8="",H36&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L36" s="28">
+      <c r="L36" s="29">
         <f>IF(OR(G36="",H36=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G36-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H36-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M36" s="7" t="n"/>
       <c r="N36" s="7" t="n"/>
-      <c r="O36" s="26">
+      <c r="O36" s="27">
         <f>IF(M36&lt;&gt;"",M36,K36)</f>
         <v/>
       </c>
-      <c r="P36" s="29">
+      <c r="P36" s="30">
         <f>IF(I36="","",IF(G36="","공수1 미응시",IF(H36="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15110,7 +15125,7 @@
         <f>'공수2'!Y37</f>
         <v/>
       </c>
-      <c r="I37" s="27">
+      <c r="I37" s="28">
         <f>IF(AND(G37="",H37=""),"",N(G37)*'설정'!$C$13+N(H37)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -15118,21 +15133,21 @@
         <f>IF(I37="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I37)+1)</f>
         <v/>
       </c>
-      <c r="K37" s="26">
+      <c r="K37" s="27">
         <f>IF(I37="","",IF(OR(G37="",H37=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G37&gt;='설정'!$C$6),OR('설정'!$D$6="",G37&lt;'설정'!$D$6),OR('설정'!$E$6="",H37&gt;='설정'!$E$6),OR('설정'!$F$6="",H37&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G37&gt;='설정'!$C$7),OR('설정'!$D$7="",G37&lt;'설정'!$D$7),OR('설정'!$E$7="",H37&gt;='설정'!$E$7),OR('설정'!$F$7="",H37&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G37&gt;='설정'!$C$8),OR('설정'!$D$8="",G37&lt;'설정'!$D$8),OR('설정'!$E$8="",H37&gt;='설정'!$E$8),OR('설정'!$F$8="",H37&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L37" s="28">
+      <c r="L37" s="29">
         <f>IF(OR(G37="",H37=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G37-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H37-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M37" s="7" t="n"/>
       <c r="N37" s="7" t="n"/>
-      <c r="O37" s="26">
+      <c r="O37" s="27">
         <f>IF(M37&lt;&gt;"",M37,K37)</f>
         <v/>
       </c>
-      <c r="P37" s="29">
+      <c r="P37" s="30">
         <f>IF(I37="","",IF(G37="","공수1 미응시",IF(H37="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15173,7 +15188,7 @@
         <f>'공수2'!Y38</f>
         <v/>
       </c>
-      <c r="I38" s="27">
+      <c r="I38" s="28">
         <f>IF(AND(G38="",H38=""),"",N(G38)*'설정'!$C$13+N(H38)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -15181,21 +15196,21 @@
         <f>IF(I38="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I38)+1)</f>
         <v/>
       </c>
-      <c r="K38" s="26">
+      <c r="K38" s="27">
         <f>IF(I38="","",IF(OR(G38="",H38=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G38&gt;='설정'!$C$6),OR('설정'!$D$6="",G38&lt;'설정'!$D$6),OR('설정'!$E$6="",H38&gt;='설정'!$E$6),OR('설정'!$F$6="",H38&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G38&gt;='설정'!$C$7),OR('설정'!$D$7="",G38&lt;'설정'!$D$7),OR('설정'!$E$7="",H38&gt;='설정'!$E$7),OR('설정'!$F$7="",H38&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G38&gt;='설정'!$C$8),OR('설정'!$D$8="",G38&lt;'설정'!$D$8),OR('설정'!$E$8="",H38&gt;='설정'!$E$8),OR('설정'!$F$8="",H38&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L38" s="28">
+      <c r="L38" s="29">
         <f>IF(OR(G38="",H38=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G38-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H38-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M38" s="7" t="n"/>
       <c r="N38" s="7" t="n"/>
-      <c r="O38" s="26">
+      <c r="O38" s="27">
         <f>IF(M38&lt;&gt;"",M38,K38)</f>
         <v/>
       </c>
-      <c r="P38" s="29">
+      <c r="P38" s="30">
         <f>IF(I38="","",IF(G38="","공수1 미응시",IF(H38="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15236,7 +15251,7 @@
         <f>'공수2'!Y39</f>
         <v/>
       </c>
-      <c r="I39" s="27">
+      <c r="I39" s="28">
         <f>IF(AND(G39="",H39=""),"",N(G39)*'설정'!$C$13+N(H39)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -15244,21 +15259,21 @@
         <f>IF(I39="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I39)+1)</f>
         <v/>
       </c>
-      <c r="K39" s="26">
+      <c r="K39" s="27">
         <f>IF(I39="","",IF(OR(G39="",H39=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G39&gt;='설정'!$C$6),OR('설정'!$D$6="",G39&lt;'설정'!$D$6),OR('설정'!$E$6="",H39&gt;='설정'!$E$6),OR('설정'!$F$6="",H39&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G39&gt;='설정'!$C$7),OR('설정'!$D$7="",G39&lt;'설정'!$D$7),OR('설정'!$E$7="",H39&gt;='설정'!$E$7),OR('설정'!$F$7="",H39&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G39&gt;='설정'!$C$8),OR('설정'!$D$8="",G39&lt;'설정'!$D$8),OR('설정'!$E$8="",H39&gt;='설정'!$E$8),OR('설정'!$F$8="",H39&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L39" s="28">
+      <c r="L39" s="29">
         <f>IF(OR(G39="",H39=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G39-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H39-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M39" s="7" t="n"/>
       <c r="N39" s="7" t="n"/>
-      <c r="O39" s="26">
+      <c r="O39" s="27">
         <f>IF(M39&lt;&gt;"",M39,K39)</f>
         <v/>
       </c>
-      <c r="P39" s="29">
+      <c r="P39" s="30">
         <f>IF(I39="","",IF(G39="","공수1 미응시",IF(H39="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15299,7 +15314,7 @@
         <f>'공수2'!Y40</f>
         <v/>
       </c>
-      <c r="I40" s="27">
+      <c r="I40" s="28">
         <f>IF(AND(G40="",H40=""),"",N(G40)*'설정'!$C$13+N(H40)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -15307,21 +15322,21 @@
         <f>IF(I40="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I40)+1)</f>
         <v/>
       </c>
-      <c r="K40" s="26">
+      <c r="K40" s="27">
         <f>IF(I40="","",IF(OR(G40="",H40=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G40&gt;='설정'!$C$6),OR('설정'!$D$6="",G40&lt;'설정'!$D$6),OR('설정'!$E$6="",H40&gt;='설정'!$E$6),OR('설정'!$F$6="",H40&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G40&gt;='설정'!$C$7),OR('설정'!$D$7="",G40&lt;'설정'!$D$7),OR('설정'!$E$7="",H40&gt;='설정'!$E$7),OR('설정'!$F$7="",H40&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G40&gt;='설정'!$C$8),OR('설정'!$D$8="",G40&lt;'설정'!$D$8),OR('설정'!$E$8="",H40&gt;='설정'!$E$8),OR('설정'!$F$8="",H40&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L40" s="28">
+      <c r="L40" s="29">
         <f>IF(OR(G40="",H40=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G40-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H40-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M40" s="7" t="n"/>
       <c r="N40" s="7" t="n"/>
-      <c r="O40" s="26">
+      <c r="O40" s="27">
         <f>IF(M40&lt;&gt;"",M40,K40)</f>
         <v/>
       </c>
-      <c r="P40" s="29">
+      <c r="P40" s="30">
         <f>IF(I40="","",IF(G40="","공수1 미응시",IF(H40="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15362,7 +15377,7 @@
         <f>'공수2'!Y41</f>
         <v/>
       </c>
-      <c r="I41" s="27">
+      <c r="I41" s="28">
         <f>IF(AND(G41="",H41=""),"",N(G41)*'설정'!$C$13+N(H41)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -15370,21 +15385,21 @@
         <f>IF(I41="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I41)+1)</f>
         <v/>
       </c>
-      <c r="K41" s="26">
+      <c r="K41" s="27">
         <f>IF(I41="","",IF(OR(G41="",H41=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G41&gt;='설정'!$C$6),OR('설정'!$D$6="",G41&lt;'설정'!$D$6),OR('설정'!$E$6="",H41&gt;='설정'!$E$6),OR('설정'!$F$6="",H41&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G41&gt;='설정'!$C$7),OR('설정'!$D$7="",G41&lt;'설정'!$D$7),OR('설정'!$E$7="",H41&gt;='설정'!$E$7),OR('설정'!$F$7="",H41&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G41&gt;='설정'!$C$8),OR('설정'!$D$8="",G41&lt;'설정'!$D$8),OR('설정'!$E$8="",H41&gt;='설정'!$E$8),OR('설정'!$F$8="",H41&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L41" s="28">
+      <c r="L41" s="29">
         <f>IF(OR(G41="",H41=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G41-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H41-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M41" s="7" t="n"/>
       <c r="N41" s="7" t="n"/>
-      <c r="O41" s="26">
+      <c r="O41" s="27">
         <f>IF(M41&lt;&gt;"",M41,K41)</f>
         <v/>
       </c>
-      <c r="P41" s="29">
+      <c r="P41" s="30">
         <f>IF(I41="","",IF(G41="","공수1 미응시",IF(H41="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15425,7 +15440,7 @@
         <f>'공수2'!Y42</f>
         <v/>
       </c>
-      <c r="I42" s="27">
+      <c r="I42" s="28">
         <f>IF(AND(G42="",H42=""),"",N(G42)*'설정'!$C$13+N(H42)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -15433,21 +15448,21 @@
         <f>IF(I42="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I42)+1)</f>
         <v/>
       </c>
-      <c r="K42" s="26">
+      <c r="K42" s="27">
         <f>IF(I42="","",IF(OR(G42="",H42=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G42&gt;='설정'!$C$6),OR('설정'!$D$6="",G42&lt;'설정'!$D$6),OR('설정'!$E$6="",H42&gt;='설정'!$E$6),OR('설정'!$F$6="",H42&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G42&gt;='설정'!$C$7),OR('설정'!$D$7="",G42&lt;'설정'!$D$7),OR('설정'!$E$7="",H42&gt;='설정'!$E$7),OR('설정'!$F$7="",H42&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G42&gt;='설정'!$C$8),OR('설정'!$D$8="",G42&lt;'설정'!$D$8),OR('설정'!$E$8="",H42&gt;='설정'!$E$8),OR('설정'!$F$8="",H42&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L42" s="28">
+      <c r="L42" s="29">
         <f>IF(OR(G42="",H42=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G42-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H42-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M42" s="7" t="n"/>
       <c r="N42" s="7" t="n"/>
-      <c r="O42" s="26">
+      <c r="O42" s="27">
         <f>IF(M42&lt;&gt;"",M42,K42)</f>
         <v/>
       </c>
-      <c r="P42" s="29">
+      <c r="P42" s="30">
         <f>IF(I42="","",IF(G42="","공수1 미응시",IF(H42="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15488,7 +15503,7 @@
         <f>'공수2'!Y43</f>
         <v/>
       </c>
-      <c r="I43" s="27">
+      <c r="I43" s="28">
         <f>IF(AND(G43="",H43=""),"",N(G43)*'설정'!$C$13+N(H43)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -15496,21 +15511,21 @@
         <f>IF(I43="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I43)+1)</f>
         <v/>
       </c>
-      <c r="K43" s="26">
+      <c r="K43" s="27">
         <f>IF(I43="","",IF(OR(G43="",H43=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G43&gt;='설정'!$C$6),OR('설정'!$D$6="",G43&lt;'설정'!$D$6),OR('설정'!$E$6="",H43&gt;='설정'!$E$6),OR('설정'!$F$6="",H43&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G43&gt;='설정'!$C$7),OR('설정'!$D$7="",G43&lt;'설정'!$D$7),OR('설정'!$E$7="",H43&gt;='설정'!$E$7),OR('설정'!$F$7="",H43&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G43&gt;='설정'!$C$8),OR('설정'!$D$8="",G43&lt;'설정'!$D$8),OR('설정'!$E$8="",H43&gt;='설정'!$E$8),OR('설정'!$F$8="",H43&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L43" s="28">
+      <c r="L43" s="29">
         <f>IF(OR(G43="",H43=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G43-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H43-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M43" s="7" t="n"/>
       <c r="N43" s="7" t="n"/>
-      <c r="O43" s="26">
+      <c r="O43" s="27">
         <f>IF(M43&lt;&gt;"",M43,K43)</f>
         <v/>
       </c>
-      <c r="P43" s="29">
+      <c r="P43" s="30">
         <f>IF(I43="","",IF(G43="","공수1 미응시",IF(H43="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15551,7 +15566,7 @@
         <f>'공수2'!Y44</f>
         <v/>
       </c>
-      <c r="I44" s="27">
+      <c r="I44" s="28">
         <f>IF(AND(G44="",H44=""),"",N(G44)*'설정'!$C$13+N(H44)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -15559,21 +15574,21 @@
         <f>IF(I44="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I44)+1)</f>
         <v/>
       </c>
-      <c r="K44" s="26">
+      <c r="K44" s="27">
         <f>IF(I44="","",IF(OR(G44="",H44=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G44&gt;='설정'!$C$6),OR('설정'!$D$6="",G44&lt;'설정'!$D$6),OR('설정'!$E$6="",H44&gt;='설정'!$E$6),OR('설정'!$F$6="",H44&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G44&gt;='설정'!$C$7),OR('설정'!$D$7="",G44&lt;'설정'!$D$7),OR('설정'!$E$7="",H44&gt;='설정'!$E$7),OR('설정'!$F$7="",H44&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G44&gt;='설정'!$C$8),OR('설정'!$D$8="",G44&lt;'설정'!$D$8),OR('설정'!$E$8="",H44&gt;='설정'!$E$8),OR('설정'!$F$8="",H44&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L44" s="28">
+      <c r="L44" s="29">
         <f>IF(OR(G44="",H44=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G44-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H44-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M44" s="7" t="n"/>
       <c r="N44" s="7" t="n"/>
-      <c r="O44" s="26">
+      <c r="O44" s="27">
         <f>IF(M44&lt;&gt;"",M44,K44)</f>
         <v/>
       </c>
-      <c r="P44" s="29">
+      <c r="P44" s="30">
         <f>IF(I44="","",IF(G44="","공수1 미응시",IF(H44="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15614,7 +15629,7 @@
         <f>'공수2'!Y45</f>
         <v/>
       </c>
-      <c r="I45" s="27">
+      <c r="I45" s="28">
         <f>IF(AND(G45="",H45=""),"",N(G45)*'설정'!$C$13+N(H45)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -15622,21 +15637,21 @@
         <f>IF(I45="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I45)+1)</f>
         <v/>
       </c>
-      <c r="K45" s="26">
+      <c r="K45" s="27">
         <f>IF(I45="","",IF(OR(G45="",H45=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G45&gt;='설정'!$C$6),OR('설정'!$D$6="",G45&lt;'설정'!$D$6),OR('설정'!$E$6="",H45&gt;='설정'!$E$6),OR('설정'!$F$6="",H45&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G45&gt;='설정'!$C$7),OR('설정'!$D$7="",G45&lt;'설정'!$D$7),OR('설정'!$E$7="",H45&gt;='설정'!$E$7),OR('설정'!$F$7="",H45&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G45&gt;='설정'!$C$8),OR('설정'!$D$8="",G45&lt;'설정'!$D$8),OR('설정'!$E$8="",H45&gt;='설정'!$E$8),OR('설정'!$F$8="",H45&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L45" s="28">
+      <c r="L45" s="29">
         <f>IF(OR(G45="",H45=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G45-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H45-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M45" s="7" t="n"/>
       <c r="N45" s="7" t="n"/>
-      <c r="O45" s="26">
+      <c r="O45" s="27">
         <f>IF(M45&lt;&gt;"",M45,K45)</f>
         <v/>
       </c>
-      <c r="P45" s="29">
+      <c r="P45" s="30">
         <f>IF(I45="","",IF(G45="","공수1 미응시",IF(H45="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15677,7 +15692,7 @@
         <f>'공수2'!Y46</f>
         <v/>
       </c>
-      <c r="I46" s="27">
+      <c r="I46" s="28">
         <f>IF(AND(G46="",H46=""),"",N(G46)*'설정'!$C$13+N(H46)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -15685,21 +15700,21 @@
         <f>IF(I46="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I46)+1)</f>
         <v/>
       </c>
-      <c r="K46" s="26">
+      <c r="K46" s="27">
         <f>IF(I46="","",IF(OR(G46="",H46=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G46&gt;='설정'!$C$6),OR('설정'!$D$6="",G46&lt;'설정'!$D$6),OR('설정'!$E$6="",H46&gt;='설정'!$E$6),OR('설정'!$F$6="",H46&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G46&gt;='설정'!$C$7),OR('설정'!$D$7="",G46&lt;'설정'!$D$7),OR('설정'!$E$7="",H46&gt;='설정'!$E$7),OR('설정'!$F$7="",H46&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G46&gt;='설정'!$C$8),OR('설정'!$D$8="",G46&lt;'설정'!$D$8),OR('설정'!$E$8="",H46&gt;='설정'!$E$8),OR('설정'!$F$8="",H46&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L46" s="28">
+      <c r="L46" s="29">
         <f>IF(OR(G46="",H46=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G46-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H46-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M46" s="7" t="n"/>
       <c r="N46" s="7" t="n"/>
-      <c r="O46" s="26">
+      <c r="O46" s="27">
         <f>IF(M46&lt;&gt;"",M46,K46)</f>
         <v/>
       </c>
-      <c r="P46" s="29">
+      <c r="P46" s="30">
         <f>IF(I46="","",IF(G46="","공수1 미응시",IF(H46="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15740,7 +15755,7 @@
         <f>'공수2'!Y47</f>
         <v/>
       </c>
-      <c r="I47" s="27">
+      <c r="I47" s="28">
         <f>IF(AND(G47="",H47=""),"",N(G47)*'설정'!$C$13+N(H47)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -15748,21 +15763,21 @@
         <f>IF(I47="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I47)+1)</f>
         <v/>
       </c>
-      <c r="K47" s="26">
+      <c r="K47" s="27">
         <f>IF(I47="","",IF(OR(G47="",H47=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G47&gt;='설정'!$C$6),OR('설정'!$D$6="",G47&lt;'설정'!$D$6),OR('설정'!$E$6="",H47&gt;='설정'!$E$6),OR('설정'!$F$6="",H47&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G47&gt;='설정'!$C$7),OR('설정'!$D$7="",G47&lt;'설정'!$D$7),OR('설정'!$E$7="",H47&gt;='설정'!$E$7),OR('설정'!$F$7="",H47&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G47&gt;='설정'!$C$8),OR('설정'!$D$8="",G47&lt;'설정'!$D$8),OR('설정'!$E$8="",H47&gt;='설정'!$E$8),OR('설정'!$F$8="",H47&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L47" s="28">
+      <c r="L47" s="29">
         <f>IF(OR(G47="",H47=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G47-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H47-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M47" s="7" t="n"/>
       <c r="N47" s="7" t="n"/>
-      <c r="O47" s="26">
+      <c r="O47" s="27">
         <f>IF(M47&lt;&gt;"",M47,K47)</f>
         <v/>
       </c>
-      <c r="P47" s="29">
+      <c r="P47" s="30">
         <f>IF(I47="","",IF(G47="","공수1 미응시",IF(H47="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15803,7 +15818,7 @@
         <f>'공수2'!Y48</f>
         <v/>
       </c>
-      <c r="I48" s="27">
+      <c r="I48" s="28">
         <f>IF(AND(G48="",H48=""),"",N(G48)*'설정'!$C$13+N(H48)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -15811,21 +15826,21 @@
         <f>IF(I48="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I48)+1)</f>
         <v/>
       </c>
-      <c r="K48" s="26">
+      <c r="K48" s="27">
         <f>IF(I48="","",IF(OR(G48="",H48=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G48&gt;='설정'!$C$6),OR('설정'!$D$6="",G48&lt;'설정'!$D$6),OR('설정'!$E$6="",H48&gt;='설정'!$E$6),OR('설정'!$F$6="",H48&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G48&gt;='설정'!$C$7),OR('설정'!$D$7="",G48&lt;'설정'!$D$7),OR('설정'!$E$7="",H48&gt;='설정'!$E$7),OR('설정'!$F$7="",H48&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G48&gt;='설정'!$C$8),OR('설정'!$D$8="",G48&lt;'설정'!$D$8),OR('설정'!$E$8="",H48&gt;='설정'!$E$8),OR('설정'!$F$8="",H48&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L48" s="28">
+      <c r="L48" s="29">
         <f>IF(OR(G48="",H48=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G48-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H48-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M48" s="7" t="n"/>
       <c r="N48" s="7" t="n"/>
-      <c r="O48" s="26">
+      <c r="O48" s="27">
         <f>IF(M48&lt;&gt;"",M48,K48)</f>
         <v/>
       </c>
-      <c r="P48" s="29">
+      <c r="P48" s="30">
         <f>IF(I48="","",IF(G48="","공수1 미응시",IF(H48="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15866,7 +15881,7 @@
         <f>'공수2'!Y49</f>
         <v/>
       </c>
-      <c r="I49" s="27">
+      <c r="I49" s="28">
         <f>IF(AND(G49="",H49=""),"",N(G49)*'설정'!$C$13+N(H49)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -15874,21 +15889,21 @@
         <f>IF(I49="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I49)+1)</f>
         <v/>
       </c>
-      <c r="K49" s="26">
+      <c r="K49" s="27">
         <f>IF(I49="","",IF(OR(G49="",H49=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G49&gt;='설정'!$C$6),OR('설정'!$D$6="",G49&lt;'설정'!$D$6),OR('설정'!$E$6="",H49&gt;='설정'!$E$6),OR('설정'!$F$6="",H49&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G49&gt;='설정'!$C$7),OR('설정'!$D$7="",G49&lt;'설정'!$D$7),OR('설정'!$E$7="",H49&gt;='설정'!$E$7),OR('설정'!$F$7="",H49&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G49&gt;='설정'!$C$8),OR('설정'!$D$8="",G49&lt;'설정'!$D$8),OR('설정'!$E$8="",H49&gt;='설정'!$E$8),OR('설정'!$F$8="",H49&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L49" s="28">
+      <c r="L49" s="29">
         <f>IF(OR(G49="",H49=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G49-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H49-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M49" s="7" t="n"/>
       <c r="N49" s="7" t="n"/>
-      <c r="O49" s="26">
+      <c r="O49" s="27">
         <f>IF(M49&lt;&gt;"",M49,K49)</f>
         <v/>
       </c>
-      <c r="P49" s="29">
+      <c r="P49" s="30">
         <f>IF(I49="","",IF(G49="","공수1 미응시",IF(H49="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15929,7 +15944,7 @@
         <f>'공수2'!Y50</f>
         <v/>
       </c>
-      <c r="I50" s="27">
+      <c r="I50" s="28">
         <f>IF(AND(G50="",H50=""),"",N(G50)*'설정'!$C$13+N(H50)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -15937,21 +15952,21 @@
         <f>IF(I50="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I50)+1)</f>
         <v/>
       </c>
-      <c r="K50" s="26">
+      <c r="K50" s="27">
         <f>IF(I50="","",IF(OR(G50="",H50=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G50&gt;='설정'!$C$6),OR('설정'!$D$6="",G50&lt;'설정'!$D$6),OR('설정'!$E$6="",H50&gt;='설정'!$E$6),OR('설정'!$F$6="",H50&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G50&gt;='설정'!$C$7),OR('설정'!$D$7="",G50&lt;'설정'!$D$7),OR('설정'!$E$7="",H50&gt;='설정'!$E$7),OR('설정'!$F$7="",H50&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G50&gt;='설정'!$C$8),OR('설정'!$D$8="",G50&lt;'설정'!$D$8),OR('설정'!$E$8="",H50&gt;='설정'!$E$8),OR('설정'!$F$8="",H50&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L50" s="28">
+      <c r="L50" s="29">
         <f>IF(OR(G50="",H50=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G50-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H50-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M50" s="7" t="n"/>
       <c r="N50" s="7" t="n"/>
-      <c r="O50" s="26">
+      <c r="O50" s="27">
         <f>IF(M50&lt;&gt;"",M50,K50)</f>
         <v/>
       </c>
-      <c r="P50" s="29">
+      <c r="P50" s="30">
         <f>IF(I50="","",IF(G50="","공수1 미응시",IF(H50="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -15992,7 +16007,7 @@
         <f>'공수2'!Y51</f>
         <v/>
       </c>
-      <c r="I51" s="27">
+      <c r="I51" s="28">
         <f>IF(AND(G51="",H51=""),"",N(G51)*'설정'!$C$13+N(H51)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16000,21 +16015,21 @@
         <f>IF(I51="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I51)+1)</f>
         <v/>
       </c>
-      <c r="K51" s="26">
+      <c r="K51" s="27">
         <f>IF(I51="","",IF(OR(G51="",H51=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G51&gt;='설정'!$C$6),OR('설정'!$D$6="",G51&lt;'설정'!$D$6),OR('설정'!$E$6="",H51&gt;='설정'!$E$6),OR('설정'!$F$6="",H51&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G51&gt;='설정'!$C$7),OR('설정'!$D$7="",G51&lt;'설정'!$D$7),OR('설정'!$E$7="",H51&gt;='설정'!$E$7),OR('설정'!$F$7="",H51&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G51&gt;='설정'!$C$8),OR('설정'!$D$8="",G51&lt;'설정'!$D$8),OR('설정'!$E$8="",H51&gt;='설정'!$E$8),OR('설정'!$F$8="",H51&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L51" s="28">
+      <c r="L51" s="29">
         <f>IF(OR(G51="",H51=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G51-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H51-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M51" s="7" t="n"/>
       <c r="N51" s="7" t="n"/>
-      <c r="O51" s="26">
+      <c r="O51" s="27">
         <f>IF(M51&lt;&gt;"",M51,K51)</f>
         <v/>
       </c>
-      <c r="P51" s="29">
+      <c r="P51" s="30">
         <f>IF(I51="","",IF(G51="","공수1 미응시",IF(H51="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -16055,7 +16070,7 @@
         <f>'공수2'!Y52</f>
         <v/>
       </c>
-      <c r="I52" s="27">
+      <c r="I52" s="28">
         <f>IF(AND(G52="",H52=""),"",N(G52)*'설정'!$C$13+N(H52)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16063,21 +16078,21 @@
         <f>IF(I52="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I52)+1)</f>
         <v/>
       </c>
-      <c r="K52" s="26">
+      <c r="K52" s="27">
         <f>IF(I52="","",IF(OR(G52="",H52=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G52&gt;='설정'!$C$6),OR('설정'!$D$6="",G52&lt;'설정'!$D$6),OR('설정'!$E$6="",H52&gt;='설정'!$E$6),OR('설정'!$F$6="",H52&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G52&gt;='설정'!$C$7),OR('설정'!$D$7="",G52&lt;'설정'!$D$7),OR('설정'!$E$7="",H52&gt;='설정'!$E$7),OR('설정'!$F$7="",H52&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G52&gt;='설정'!$C$8),OR('설정'!$D$8="",G52&lt;'설정'!$D$8),OR('설정'!$E$8="",H52&gt;='설정'!$E$8),OR('설정'!$F$8="",H52&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L52" s="28">
+      <c r="L52" s="29">
         <f>IF(OR(G52="",H52=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G52-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H52-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M52" s="7" t="n"/>
       <c r="N52" s="7" t="n"/>
-      <c r="O52" s="26">
+      <c r="O52" s="27">
         <f>IF(M52&lt;&gt;"",M52,K52)</f>
         <v/>
       </c>
-      <c r="P52" s="29">
+      <c r="P52" s="30">
         <f>IF(I52="","",IF(G52="","공수1 미응시",IF(H52="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -16118,7 +16133,7 @@
         <f>'공수2'!Y53</f>
         <v/>
       </c>
-      <c r="I53" s="27">
+      <c r="I53" s="28">
         <f>IF(AND(G53="",H53=""),"",N(G53)*'설정'!$C$13+N(H53)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16126,21 +16141,21 @@
         <f>IF(I53="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I53)+1)</f>
         <v/>
       </c>
-      <c r="K53" s="26">
+      <c r="K53" s="27">
         <f>IF(I53="","",IF(OR(G53="",H53=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G53&gt;='설정'!$C$6),OR('설정'!$D$6="",G53&lt;'설정'!$D$6),OR('설정'!$E$6="",H53&gt;='설정'!$E$6),OR('설정'!$F$6="",H53&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G53&gt;='설정'!$C$7),OR('설정'!$D$7="",G53&lt;'설정'!$D$7),OR('설정'!$E$7="",H53&gt;='설정'!$E$7),OR('설정'!$F$7="",H53&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G53&gt;='설정'!$C$8),OR('설정'!$D$8="",G53&lt;'설정'!$D$8),OR('설정'!$E$8="",H53&gt;='설정'!$E$8),OR('설정'!$F$8="",H53&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L53" s="28">
+      <c r="L53" s="29">
         <f>IF(OR(G53="",H53=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G53-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H53-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M53" s="7" t="n"/>
       <c r="N53" s="7" t="n"/>
-      <c r="O53" s="26">
+      <c r="O53" s="27">
         <f>IF(M53&lt;&gt;"",M53,K53)</f>
         <v/>
       </c>
-      <c r="P53" s="29">
+      <c r="P53" s="30">
         <f>IF(I53="","",IF(G53="","공수1 미응시",IF(H53="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -16181,7 +16196,7 @@
         <f>'공수2'!Y54</f>
         <v/>
       </c>
-      <c r="I54" s="27">
+      <c r="I54" s="28">
         <f>IF(AND(G54="",H54=""),"",N(G54)*'설정'!$C$13+N(H54)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16189,21 +16204,21 @@
         <f>IF(I54="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I54)+1)</f>
         <v/>
       </c>
-      <c r="K54" s="26">
+      <c r="K54" s="27">
         <f>IF(I54="","",IF(OR(G54="",H54=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G54&gt;='설정'!$C$6),OR('설정'!$D$6="",G54&lt;'설정'!$D$6),OR('설정'!$E$6="",H54&gt;='설정'!$E$6),OR('설정'!$F$6="",H54&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G54&gt;='설정'!$C$7),OR('설정'!$D$7="",G54&lt;'설정'!$D$7),OR('설정'!$E$7="",H54&gt;='설정'!$E$7),OR('설정'!$F$7="",H54&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G54&gt;='설정'!$C$8),OR('설정'!$D$8="",G54&lt;'설정'!$D$8),OR('설정'!$E$8="",H54&gt;='설정'!$E$8),OR('설정'!$F$8="",H54&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L54" s="28">
+      <c r="L54" s="29">
         <f>IF(OR(G54="",H54=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G54-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H54-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M54" s="7" t="n"/>
       <c r="N54" s="7" t="n"/>
-      <c r="O54" s="26">
+      <c r="O54" s="27">
         <f>IF(M54&lt;&gt;"",M54,K54)</f>
         <v/>
       </c>
-      <c r="P54" s="29">
+      <c r="P54" s="30">
         <f>IF(I54="","",IF(G54="","공수1 미응시",IF(H54="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -16244,7 +16259,7 @@
         <f>'공수2'!Y55</f>
         <v/>
       </c>
-      <c r="I55" s="27">
+      <c r="I55" s="28">
         <f>IF(AND(G55="",H55=""),"",N(G55)*'설정'!$C$13+N(H55)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16252,21 +16267,21 @@
         <f>IF(I55="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I55)+1)</f>
         <v/>
       </c>
-      <c r="K55" s="26">
+      <c r="K55" s="27">
         <f>IF(I55="","",IF(OR(G55="",H55=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G55&gt;='설정'!$C$6),OR('설정'!$D$6="",G55&lt;'설정'!$D$6),OR('설정'!$E$6="",H55&gt;='설정'!$E$6),OR('설정'!$F$6="",H55&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G55&gt;='설정'!$C$7),OR('설정'!$D$7="",G55&lt;'설정'!$D$7),OR('설정'!$E$7="",H55&gt;='설정'!$E$7),OR('설정'!$F$7="",H55&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G55&gt;='설정'!$C$8),OR('설정'!$D$8="",G55&lt;'설정'!$D$8),OR('설정'!$E$8="",H55&gt;='설정'!$E$8),OR('설정'!$F$8="",H55&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L55" s="28">
+      <c r="L55" s="29">
         <f>IF(OR(G55="",H55=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G55-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H55-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M55" s="7" t="n"/>
       <c r="N55" s="7" t="n"/>
-      <c r="O55" s="26">
+      <c r="O55" s="27">
         <f>IF(M55&lt;&gt;"",M55,K55)</f>
         <v/>
       </c>
-      <c r="P55" s="29">
+      <c r="P55" s="30">
         <f>IF(I55="","",IF(G55="","공수1 미응시",IF(H55="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -16307,7 +16322,7 @@
         <f>'공수2'!Y56</f>
         <v/>
       </c>
-      <c r="I56" s="27">
+      <c r="I56" s="28">
         <f>IF(AND(G56="",H56=""),"",N(G56)*'설정'!$C$13+N(H56)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16315,21 +16330,21 @@
         <f>IF(I56="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I56)+1)</f>
         <v/>
       </c>
-      <c r="K56" s="26">
+      <c r="K56" s="27">
         <f>IF(I56="","",IF(OR(G56="",H56=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G56&gt;='설정'!$C$6),OR('설정'!$D$6="",G56&lt;'설정'!$D$6),OR('설정'!$E$6="",H56&gt;='설정'!$E$6),OR('설정'!$F$6="",H56&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G56&gt;='설정'!$C$7),OR('설정'!$D$7="",G56&lt;'설정'!$D$7),OR('설정'!$E$7="",H56&gt;='설정'!$E$7),OR('설정'!$F$7="",H56&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G56&gt;='설정'!$C$8),OR('설정'!$D$8="",G56&lt;'설정'!$D$8),OR('설정'!$E$8="",H56&gt;='설정'!$E$8),OR('설정'!$F$8="",H56&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L56" s="28">
+      <c r="L56" s="29">
         <f>IF(OR(G56="",H56=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G56-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H56-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M56" s="7" t="n"/>
       <c r="N56" s="7" t="n"/>
-      <c r="O56" s="26">
+      <c r="O56" s="27">
         <f>IF(M56&lt;&gt;"",M56,K56)</f>
         <v/>
       </c>
-      <c r="P56" s="29">
+      <c r="P56" s="30">
         <f>IF(I56="","",IF(G56="","공수1 미응시",IF(H56="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -16370,7 +16385,7 @@
         <f>'공수2'!Y57</f>
         <v/>
       </c>
-      <c r="I57" s="27">
+      <c r="I57" s="28">
         <f>IF(AND(G57="",H57=""),"",N(G57)*'설정'!$C$13+N(H57)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16378,21 +16393,21 @@
         <f>IF(I57="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I57)+1)</f>
         <v/>
       </c>
-      <c r="K57" s="26">
+      <c r="K57" s="27">
         <f>IF(I57="","",IF(OR(G57="",H57=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G57&gt;='설정'!$C$6),OR('설정'!$D$6="",G57&lt;'설정'!$D$6),OR('설정'!$E$6="",H57&gt;='설정'!$E$6),OR('설정'!$F$6="",H57&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G57&gt;='설정'!$C$7),OR('설정'!$D$7="",G57&lt;'설정'!$D$7),OR('설정'!$E$7="",H57&gt;='설정'!$E$7),OR('설정'!$F$7="",H57&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G57&gt;='설정'!$C$8),OR('설정'!$D$8="",G57&lt;'설정'!$D$8),OR('설정'!$E$8="",H57&gt;='설정'!$E$8),OR('설정'!$F$8="",H57&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L57" s="28">
+      <c r="L57" s="29">
         <f>IF(OR(G57="",H57=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G57-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H57-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M57" s="7" t="n"/>
       <c r="N57" s="7" t="n"/>
-      <c r="O57" s="26">
+      <c r="O57" s="27">
         <f>IF(M57&lt;&gt;"",M57,K57)</f>
         <v/>
       </c>
-      <c r="P57" s="29">
+      <c r="P57" s="30">
         <f>IF(I57="","",IF(G57="","공수1 미응시",IF(H57="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -16433,7 +16448,7 @@
         <f>'공수2'!Y58</f>
         <v/>
       </c>
-      <c r="I58" s="27">
+      <c r="I58" s="28">
         <f>IF(AND(G58="",H58=""),"",N(G58)*'설정'!$C$13+N(H58)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16441,21 +16456,21 @@
         <f>IF(I58="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I58)+1)</f>
         <v/>
       </c>
-      <c r="K58" s="26">
+      <c r="K58" s="27">
         <f>IF(I58="","",IF(OR(G58="",H58=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G58&gt;='설정'!$C$6),OR('설정'!$D$6="",G58&lt;'설정'!$D$6),OR('설정'!$E$6="",H58&gt;='설정'!$E$6),OR('설정'!$F$6="",H58&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G58&gt;='설정'!$C$7),OR('설정'!$D$7="",G58&lt;'설정'!$D$7),OR('설정'!$E$7="",H58&gt;='설정'!$E$7),OR('설정'!$F$7="",H58&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G58&gt;='설정'!$C$8),OR('설정'!$D$8="",G58&lt;'설정'!$D$8),OR('설정'!$E$8="",H58&gt;='설정'!$E$8),OR('설정'!$F$8="",H58&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L58" s="28">
+      <c r="L58" s="29">
         <f>IF(OR(G58="",H58=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G58-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H58-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M58" s="7" t="n"/>
       <c r="N58" s="7" t="n"/>
-      <c r="O58" s="26">
+      <c r="O58" s="27">
         <f>IF(M58&lt;&gt;"",M58,K58)</f>
         <v/>
       </c>
-      <c r="P58" s="29">
+      <c r="P58" s="30">
         <f>IF(I58="","",IF(G58="","공수1 미응시",IF(H58="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -16496,7 +16511,7 @@
         <f>'공수2'!Y59</f>
         <v/>
       </c>
-      <c r="I59" s="27">
+      <c r="I59" s="28">
         <f>IF(AND(G59="",H59=""),"",N(G59)*'설정'!$C$13+N(H59)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16504,21 +16519,21 @@
         <f>IF(I59="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I59)+1)</f>
         <v/>
       </c>
-      <c r="K59" s="26">
+      <c r="K59" s="27">
         <f>IF(I59="","",IF(OR(G59="",H59=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G59&gt;='설정'!$C$6),OR('설정'!$D$6="",G59&lt;'설정'!$D$6),OR('설정'!$E$6="",H59&gt;='설정'!$E$6),OR('설정'!$F$6="",H59&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G59&gt;='설정'!$C$7),OR('설정'!$D$7="",G59&lt;'설정'!$D$7),OR('설정'!$E$7="",H59&gt;='설정'!$E$7),OR('설정'!$F$7="",H59&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G59&gt;='설정'!$C$8),OR('설정'!$D$8="",G59&lt;'설정'!$D$8),OR('설정'!$E$8="",H59&gt;='설정'!$E$8),OR('설정'!$F$8="",H59&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L59" s="28">
+      <c r="L59" s="29">
         <f>IF(OR(G59="",H59=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G59-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H59-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M59" s="7" t="n"/>
       <c r="N59" s="7" t="n"/>
-      <c r="O59" s="26">
+      <c r="O59" s="27">
         <f>IF(M59&lt;&gt;"",M59,K59)</f>
         <v/>
       </c>
-      <c r="P59" s="29">
+      <c r="P59" s="30">
         <f>IF(I59="","",IF(G59="","공수1 미응시",IF(H59="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -16559,7 +16574,7 @@
         <f>'공수2'!Y60</f>
         <v/>
       </c>
-      <c r="I60" s="27">
+      <c r="I60" s="28">
         <f>IF(AND(G60="",H60=""),"",N(G60)*'설정'!$C$13+N(H60)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16567,21 +16582,21 @@
         <f>IF(I60="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I60)+1)</f>
         <v/>
       </c>
-      <c r="K60" s="26">
+      <c r="K60" s="27">
         <f>IF(I60="","",IF(OR(G60="",H60=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G60&gt;='설정'!$C$6),OR('설정'!$D$6="",G60&lt;'설정'!$D$6),OR('설정'!$E$6="",H60&gt;='설정'!$E$6),OR('설정'!$F$6="",H60&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G60&gt;='설정'!$C$7),OR('설정'!$D$7="",G60&lt;'설정'!$D$7),OR('설정'!$E$7="",H60&gt;='설정'!$E$7),OR('설정'!$F$7="",H60&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G60&gt;='설정'!$C$8),OR('설정'!$D$8="",G60&lt;'설정'!$D$8),OR('설정'!$E$8="",H60&gt;='설정'!$E$8),OR('설정'!$F$8="",H60&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L60" s="28">
+      <c r="L60" s="29">
         <f>IF(OR(G60="",H60=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G60-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H60-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M60" s="7" t="n"/>
       <c r="N60" s="7" t="n"/>
-      <c r="O60" s="26">
+      <c r="O60" s="27">
         <f>IF(M60&lt;&gt;"",M60,K60)</f>
         <v/>
       </c>
-      <c r="P60" s="29">
+      <c r="P60" s="30">
         <f>IF(I60="","",IF(G60="","공수1 미응시",IF(H60="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -16622,7 +16637,7 @@
         <f>'공수2'!Y61</f>
         <v/>
       </c>
-      <c r="I61" s="27">
+      <c r="I61" s="28">
         <f>IF(AND(G61="",H61=""),"",N(G61)*'설정'!$C$13+N(H61)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16630,21 +16645,21 @@
         <f>IF(I61="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I61)+1)</f>
         <v/>
       </c>
-      <c r="K61" s="26">
+      <c r="K61" s="27">
         <f>IF(I61="","",IF(OR(G61="",H61=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G61&gt;='설정'!$C$6),OR('설정'!$D$6="",G61&lt;'설정'!$D$6),OR('설정'!$E$6="",H61&gt;='설정'!$E$6),OR('설정'!$F$6="",H61&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G61&gt;='설정'!$C$7),OR('설정'!$D$7="",G61&lt;'설정'!$D$7),OR('설정'!$E$7="",H61&gt;='설정'!$E$7),OR('설정'!$F$7="",H61&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G61&gt;='설정'!$C$8),OR('설정'!$D$8="",G61&lt;'설정'!$D$8),OR('설정'!$E$8="",H61&gt;='설정'!$E$8),OR('설정'!$F$8="",H61&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L61" s="28">
+      <c r="L61" s="29">
         <f>IF(OR(G61="",H61=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G61-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H61-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M61" s="7" t="n"/>
       <c r="N61" s="7" t="n"/>
-      <c r="O61" s="26">
+      <c r="O61" s="27">
         <f>IF(M61&lt;&gt;"",M61,K61)</f>
         <v/>
       </c>
-      <c r="P61" s="29">
+      <c r="P61" s="30">
         <f>IF(I61="","",IF(G61="","공수1 미응시",IF(H61="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -16685,7 +16700,7 @@
         <f>'공수2'!Y62</f>
         <v/>
       </c>
-      <c r="I62" s="27">
+      <c r="I62" s="28">
         <f>IF(AND(G62="",H62=""),"",N(G62)*'설정'!$C$13+N(H62)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16693,21 +16708,21 @@
         <f>IF(I62="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I62)+1)</f>
         <v/>
       </c>
-      <c r="K62" s="26">
+      <c r="K62" s="27">
         <f>IF(I62="","",IF(OR(G62="",H62=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G62&gt;='설정'!$C$6),OR('설정'!$D$6="",G62&lt;'설정'!$D$6),OR('설정'!$E$6="",H62&gt;='설정'!$E$6),OR('설정'!$F$6="",H62&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G62&gt;='설정'!$C$7),OR('설정'!$D$7="",G62&lt;'설정'!$D$7),OR('설정'!$E$7="",H62&gt;='설정'!$E$7),OR('설정'!$F$7="",H62&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G62&gt;='설정'!$C$8),OR('설정'!$D$8="",G62&lt;'설정'!$D$8),OR('설정'!$E$8="",H62&gt;='설정'!$E$8),OR('설정'!$F$8="",H62&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L62" s="28">
+      <c r="L62" s="29">
         <f>IF(OR(G62="",H62=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G62-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H62-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M62" s="7" t="n"/>
       <c r="N62" s="7" t="n"/>
-      <c r="O62" s="26">
+      <c r="O62" s="27">
         <f>IF(M62&lt;&gt;"",M62,K62)</f>
         <v/>
       </c>
-      <c r="P62" s="29">
+      <c r="P62" s="30">
         <f>IF(I62="","",IF(G62="","공수1 미응시",IF(H62="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -16748,7 +16763,7 @@
         <f>'공수2'!Y63</f>
         <v/>
       </c>
-      <c r="I63" s="27">
+      <c r="I63" s="28">
         <f>IF(AND(G63="",H63=""),"",N(G63)*'설정'!$C$13+N(H63)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16756,21 +16771,21 @@
         <f>IF(I63="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I63)+1)</f>
         <v/>
       </c>
-      <c r="K63" s="26">
+      <c r="K63" s="27">
         <f>IF(I63="","",IF(OR(G63="",H63=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G63&gt;='설정'!$C$6),OR('설정'!$D$6="",G63&lt;'설정'!$D$6),OR('설정'!$E$6="",H63&gt;='설정'!$E$6),OR('설정'!$F$6="",H63&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G63&gt;='설정'!$C$7),OR('설정'!$D$7="",G63&lt;'설정'!$D$7),OR('설정'!$E$7="",H63&gt;='설정'!$E$7),OR('설정'!$F$7="",H63&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G63&gt;='설정'!$C$8),OR('설정'!$D$8="",G63&lt;'설정'!$D$8),OR('설정'!$E$8="",H63&gt;='설정'!$E$8),OR('설정'!$F$8="",H63&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L63" s="28">
+      <c r="L63" s="29">
         <f>IF(OR(G63="",H63=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G63-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H63-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M63" s="7" t="n"/>
       <c r="N63" s="7" t="n"/>
-      <c r="O63" s="26">
+      <c r="O63" s="27">
         <f>IF(M63&lt;&gt;"",M63,K63)</f>
         <v/>
       </c>
-      <c r="P63" s="29">
+      <c r="P63" s="30">
         <f>IF(I63="","",IF(G63="","공수1 미응시",IF(H63="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -16811,7 +16826,7 @@
         <f>'공수2'!Y64</f>
         <v/>
       </c>
-      <c r="I64" s="27">
+      <c r="I64" s="28">
         <f>IF(AND(G64="",H64=""),"",N(G64)*'설정'!$C$13+N(H64)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16819,21 +16834,21 @@
         <f>IF(I64="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I64)+1)</f>
         <v/>
       </c>
-      <c r="K64" s="26">
+      <c r="K64" s="27">
         <f>IF(I64="","",IF(OR(G64="",H64=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G64&gt;='설정'!$C$6),OR('설정'!$D$6="",G64&lt;'설정'!$D$6),OR('설정'!$E$6="",H64&gt;='설정'!$E$6),OR('설정'!$F$6="",H64&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G64&gt;='설정'!$C$7),OR('설정'!$D$7="",G64&lt;'설정'!$D$7),OR('설정'!$E$7="",H64&gt;='설정'!$E$7),OR('설정'!$F$7="",H64&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G64&gt;='설정'!$C$8),OR('설정'!$D$8="",G64&lt;'설정'!$D$8),OR('설정'!$E$8="",H64&gt;='설정'!$E$8),OR('설정'!$F$8="",H64&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L64" s="28">
+      <c r="L64" s="29">
         <f>IF(OR(G64="",H64=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G64-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H64-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M64" s="7" t="n"/>
       <c r="N64" s="7" t="n"/>
-      <c r="O64" s="26">
+      <c r="O64" s="27">
         <f>IF(M64&lt;&gt;"",M64,K64)</f>
         <v/>
       </c>
-      <c r="P64" s="29">
+      <c r="P64" s="30">
         <f>IF(I64="","",IF(G64="","공수1 미응시",IF(H64="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -16874,7 +16889,7 @@
         <f>'공수2'!Y65</f>
         <v/>
       </c>
-      <c r="I65" s="27">
+      <c r="I65" s="28">
         <f>IF(AND(G65="",H65=""),"",N(G65)*'설정'!$C$13+N(H65)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16882,21 +16897,21 @@
         <f>IF(I65="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I65)+1)</f>
         <v/>
       </c>
-      <c r="K65" s="26">
+      <c r="K65" s="27">
         <f>IF(I65="","",IF(OR(G65="",H65=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G65&gt;='설정'!$C$6),OR('설정'!$D$6="",G65&lt;'설정'!$D$6),OR('설정'!$E$6="",H65&gt;='설정'!$E$6),OR('설정'!$F$6="",H65&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G65&gt;='설정'!$C$7),OR('설정'!$D$7="",G65&lt;'설정'!$D$7),OR('설정'!$E$7="",H65&gt;='설정'!$E$7),OR('설정'!$F$7="",H65&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G65&gt;='설정'!$C$8),OR('설정'!$D$8="",G65&lt;'설정'!$D$8),OR('설정'!$E$8="",H65&gt;='설정'!$E$8),OR('설정'!$F$8="",H65&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L65" s="28">
+      <c r="L65" s="29">
         <f>IF(OR(G65="",H65=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G65-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H65-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M65" s="7" t="n"/>
       <c r="N65" s="7" t="n"/>
-      <c r="O65" s="26">
+      <c r="O65" s="27">
         <f>IF(M65&lt;&gt;"",M65,K65)</f>
         <v/>
       </c>
-      <c r="P65" s="29">
+      <c r="P65" s="30">
         <f>IF(I65="","",IF(G65="","공수1 미응시",IF(H65="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -16937,7 +16952,7 @@
         <f>'공수2'!Y66</f>
         <v/>
       </c>
-      <c r="I66" s="27">
+      <c r="I66" s="28">
         <f>IF(AND(G66="",H66=""),"",N(G66)*'설정'!$C$13+N(H66)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -16945,21 +16960,21 @@
         <f>IF(I66="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I66)+1)</f>
         <v/>
       </c>
-      <c r="K66" s="26">
+      <c r="K66" s="27">
         <f>IF(I66="","",IF(OR(G66="",H66=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G66&gt;='설정'!$C$6),OR('설정'!$D$6="",G66&lt;'설정'!$D$6),OR('설정'!$E$6="",H66&gt;='설정'!$E$6),OR('설정'!$F$6="",H66&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G66&gt;='설정'!$C$7),OR('설정'!$D$7="",G66&lt;'설정'!$D$7),OR('설정'!$E$7="",H66&gt;='설정'!$E$7),OR('설정'!$F$7="",H66&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G66&gt;='설정'!$C$8),OR('설정'!$D$8="",G66&lt;'설정'!$D$8),OR('설정'!$E$8="",H66&gt;='설정'!$E$8),OR('설정'!$F$8="",H66&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L66" s="28">
+      <c r="L66" s="29">
         <f>IF(OR(G66="",H66=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G66-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H66-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M66" s="7" t="n"/>
       <c r="N66" s="7" t="n"/>
-      <c r="O66" s="26">
+      <c r="O66" s="27">
         <f>IF(M66&lt;&gt;"",M66,K66)</f>
         <v/>
       </c>
-      <c r="P66" s="29">
+      <c r="P66" s="30">
         <f>IF(I66="","",IF(G66="","공수1 미응시",IF(H66="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17000,7 +17015,7 @@
         <f>'공수2'!Y67</f>
         <v/>
       </c>
-      <c r="I67" s="27">
+      <c r="I67" s="28">
         <f>IF(AND(G67="",H67=""),"",N(G67)*'설정'!$C$13+N(H67)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17008,21 +17023,21 @@
         <f>IF(I67="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I67)+1)</f>
         <v/>
       </c>
-      <c r="K67" s="26">
+      <c r="K67" s="27">
         <f>IF(I67="","",IF(OR(G67="",H67=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G67&gt;='설정'!$C$6),OR('설정'!$D$6="",G67&lt;'설정'!$D$6),OR('설정'!$E$6="",H67&gt;='설정'!$E$6),OR('설정'!$F$6="",H67&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G67&gt;='설정'!$C$7),OR('설정'!$D$7="",G67&lt;'설정'!$D$7),OR('설정'!$E$7="",H67&gt;='설정'!$E$7),OR('설정'!$F$7="",H67&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G67&gt;='설정'!$C$8),OR('설정'!$D$8="",G67&lt;'설정'!$D$8),OR('설정'!$E$8="",H67&gt;='설정'!$E$8),OR('설정'!$F$8="",H67&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L67" s="28">
+      <c r="L67" s="29">
         <f>IF(OR(G67="",H67=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G67-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H67-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M67" s="7" t="n"/>
       <c r="N67" s="7" t="n"/>
-      <c r="O67" s="26">
+      <c r="O67" s="27">
         <f>IF(M67&lt;&gt;"",M67,K67)</f>
         <v/>
       </c>
-      <c r="P67" s="29">
+      <c r="P67" s="30">
         <f>IF(I67="","",IF(G67="","공수1 미응시",IF(H67="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17063,7 +17078,7 @@
         <f>'공수2'!Y68</f>
         <v/>
       </c>
-      <c r="I68" s="27">
+      <c r="I68" s="28">
         <f>IF(AND(G68="",H68=""),"",N(G68)*'설정'!$C$13+N(H68)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17071,21 +17086,21 @@
         <f>IF(I68="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I68)+1)</f>
         <v/>
       </c>
-      <c r="K68" s="26">
+      <c r="K68" s="27">
         <f>IF(I68="","",IF(OR(G68="",H68=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G68&gt;='설정'!$C$6),OR('설정'!$D$6="",G68&lt;'설정'!$D$6),OR('설정'!$E$6="",H68&gt;='설정'!$E$6),OR('설정'!$F$6="",H68&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G68&gt;='설정'!$C$7),OR('설정'!$D$7="",G68&lt;'설정'!$D$7),OR('설정'!$E$7="",H68&gt;='설정'!$E$7),OR('설정'!$F$7="",H68&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G68&gt;='설정'!$C$8),OR('설정'!$D$8="",G68&lt;'설정'!$D$8),OR('설정'!$E$8="",H68&gt;='설정'!$E$8),OR('설정'!$F$8="",H68&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L68" s="28">
+      <c r="L68" s="29">
         <f>IF(OR(G68="",H68=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G68-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H68-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M68" s="7" t="n"/>
       <c r="N68" s="7" t="n"/>
-      <c r="O68" s="26">
+      <c r="O68" s="27">
         <f>IF(M68&lt;&gt;"",M68,K68)</f>
         <v/>
       </c>
-      <c r="P68" s="29">
+      <c r="P68" s="30">
         <f>IF(I68="","",IF(G68="","공수1 미응시",IF(H68="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17126,7 +17141,7 @@
         <f>'공수2'!Y69</f>
         <v/>
       </c>
-      <c r="I69" s="27">
+      <c r="I69" s="28">
         <f>IF(AND(G69="",H69=""),"",N(G69)*'설정'!$C$13+N(H69)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17134,21 +17149,21 @@
         <f>IF(I69="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I69)+1)</f>
         <v/>
       </c>
-      <c r="K69" s="26">
+      <c r="K69" s="27">
         <f>IF(I69="","",IF(OR(G69="",H69=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G69&gt;='설정'!$C$6),OR('설정'!$D$6="",G69&lt;'설정'!$D$6),OR('설정'!$E$6="",H69&gt;='설정'!$E$6),OR('설정'!$F$6="",H69&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G69&gt;='설정'!$C$7),OR('설정'!$D$7="",G69&lt;'설정'!$D$7),OR('설정'!$E$7="",H69&gt;='설정'!$E$7),OR('설정'!$F$7="",H69&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G69&gt;='설정'!$C$8),OR('설정'!$D$8="",G69&lt;'설정'!$D$8),OR('설정'!$E$8="",H69&gt;='설정'!$E$8),OR('설정'!$F$8="",H69&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L69" s="28">
+      <c r="L69" s="29">
         <f>IF(OR(G69="",H69=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G69-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H69-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M69" s="7" t="n"/>
       <c r="N69" s="7" t="n"/>
-      <c r="O69" s="26">
+      <c r="O69" s="27">
         <f>IF(M69&lt;&gt;"",M69,K69)</f>
         <v/>
       </c>
-      <c r="P69" s="29">
+      <c r="P69" s="30">
         <f>IF(I69="","",IF(G69="","공수1 미응시",IF(H69="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17189,7 +17204,7 @@
         <f>'공수2'!Y70</f>
         <v/>
       </c>
-      <c r="I70" s="27">
+      <c r="I70" s="28">
         <f>IF(AND(G70="",H70=""),"",N(G70)*'설정'!$C$13+N(H70)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17197,21 +17212,21 @@
         <f>IF(I70="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I70)+1)</f>
         <v/>
       </c>
-      <c r="K70" s="26">
+      <c r="K70" s="27">
         <f>IF(I70="","",IF(OR(G70="",H70=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G70&gt;='설정'!$C$6),OR('설정'!$D$6="",G70&lt;'설정'!$D$6),OR('설정'!$E$6="",H70&gt;='설정'!$E$6),OR('설정'!$F$6="",H70&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G70&gt;='설정'!$C$7),OR('설정'!$D$7="",G70&lt;'설정'!$D$7),OR('설정'!$E$7="",H70&gt;='설정'!$E$7),OR('설정'!$F$7="",H70&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G70&gt;='설정'!$C$8),OR('설정'!$D$8="",G70&lt;'설정'!$D$8),OR('설정'!$E$8="",H70&gt;='설정'!$E$8),OR('설정'!$F$8="",H70&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L70" s="28">
+      <c r="L70" s="29">
         <f>IF(OR(G70="",H70=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G70-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H70-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M70" s="7" t="n"/>
       <c r="N70" s="7" t="n"/>
-      <c r="O70" s="26">
+      <c r="O70" s="27">
         <f>IF(M70&lt;&gt;"",M70,K70)</f>
         <v/>
       </c>
-      <c r="P70" s="29">
+      <c r="P70" s="30">
         <f>IF(I70="","",IF(G70="","공수1 미응시",IF(H70="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17252,7 +17267,7 @@
         <f>'공수2'!Y71</f>
         <v/>
       </c>
-      <c r="I71" s="27">
+      <c r="I71" s="28">
         <f>IF(AND(G71="",H71=""),"",N(G71)*'설정'!$C$13+N(H71)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17260,21 +17275,21 @@
         <f>IF(I71="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I71)+1)</f>
         <v/>
       </c>
-      <c r="K71" s="26">
+      <c r="K71" s="27">
         <f>IF(I71="","",IF(OR(G71="",H71=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G71&gt;='설정'!$C$6),OR('설정'!$D$6="",G71&lt;'설정'!$D$6),OR('설정'!$E$6="",H71&gt;='설정'!$E$6),OR('설정'!$F$6="",H71&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G71&gt;='설정'!$C$7),OR('설정'!$D$7="",G71&lt;'설정'!$D$7),OR('설정'!$E$7="",H71&gt;='설정'!$E$7),OR('설정'!$F$7="",H71&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G71&gt;='설정'!$C$8),OR('설정'!$D$8="",G71&lt;'설정'!$D$8),OR('설정'!$E$8="",H71&gt;='설정'!$E$8),OR('설정'!$F$8="",H71&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L71" s="28">
+      <c r="L71" s="29">
         <f>IF(OR(G71="",H71=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G71-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H71-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M71" s="7" t="n"/>
       <c r="N71" s="7" t="n"/>
-      <c r="O71" s="26">
+      <c r="O71" s="27">
         <f>IF(M71&lt;&gt;"",M71,K71)</f>
         <v/>
       </c>
-      <c r="P71" s="29">
+      <c r="P71" s="30">
         <f>IF(I71="","",IF(G71="","공수1 미응시",IF(H71="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17315,7 +17330,7 @@
         <f>'공수2'!Y72</f>
         <v/>
       </c>
-      <c r="I72" s="27">
+      <c r="I72" s="28">
         <f>IF(AND(G72="",H72=""),"",N(G72)*'설정'!$C$13+N(H72)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17323,21 +17338,21 @@
         <f>IF(I72="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I72)+1)</f>
         <v/>
       </c>
-      <c r="K72" s="26">
+      <c r="K72" s="27">
         <f>IF(I72="","",IF(OR(G72="",H72=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G72&gt;='설정'!$C$6),OR('설정'!$D$6="",G72&lt;'설정'!$D$6),OR('설정'!$E$6="",H72&gt;='설정'!$E$6),OR('설정'!$F$6="",H72&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G72&gt;='설정'!$C$7),OR('설정'!$D$7="",G72&lt;'설정'!$D$7),OR('설정'!$E$7="",H72&gt;='설정'!$E$7),OR('설정'!$F$7="",H72&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G72&gt;='설정'!$C$8),OR('설정'!$D$8="",G72&lt;'설정'!$D$8),OR('설정'!$E$8="",H72&gt;='설정'!$E$8),OR('설정'!$F$8="",H72&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L72" s="28">
+      <c r="L72" s="29">
         <f>IF(OR(G72="",H72=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G72-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H72-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M72" s="7" t="n"/>
       <c r="N72" s="7" t="n"/>
-      <c r="O72" s="26">
+      <c r="O72" s="27">
         <f>IF(M72&lt;&gt;"",M72,K72)</f>
         <v/>
       </c>
-      <c r="P72" s="29">
+      <c r="P72" s="30">
         <f>IF(I72="","",IF(G72="","공수1 미응시",IF(H72="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17378,7 +17393,7 @@
         <f>'공수2'!Y73</f>
         <v/>
       </c>
-      <c r="I73" s="27">
+      <c r="I73" s="28">
         <f>IF(AND(G73="",H73=""),"",N(G73)*'설정'!$C$13+N(H73)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17386,21 +17401,21 @@
         <f>IF(I73="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I73)+1)</f>
         <v/>
       </c>
-      <c r="K73" s="26">
+      <c r="K73" s="27">
         <f>IF(I73="","",IF(OR(G73="",H73=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G73&gt;='설정'!$C$6),OR('설정'!$D$6="",G73&lt;'설정'!$D$6),OR('설정'!$E$6="",H73&gt;='설정'!$E$6),OR('설정'!$F$6="",H73&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G73&gt;='설정'!$C$7),OR('설정'!$D$7="",G73&lt;'설정'!$D$7),OR('설정'!$E$7="",H73&gt;='설정'!$E$7),OR('설정'!$F$7="",H73&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G73&gt;='설정'!$C$8),OR('설정'!$D$8="",G73&lt;'설정'!$D$8),OR('설정'!$E$8="",H73&gt;='설정'!$E$8),OR('설정'!$F$8="",H73&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L73" s="28">
+      <c r="L73" s="29">
         <f>IF(OR(G73="",H73=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G73-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H73-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M73" s="7" t="n"/>
       <c r="N73" s="7" t="n"/>
-      <c r="O73" s="26">
+      <c r="O73" s="27">
         <f>IF(M73&lt;&gt;"",M73,K73)</f>
         <v/>
       </c>
-      <c r="P73" s="29">
+      <c r="P73" s="30">
         <f>IF(I73="","",IF(G73="","공수1 미응시",IF(H73="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17441,7 +17456,7 @@
         <f>'공수2'!Y74</f>
         <v/>
       </c>
-      <c r="I74" s="27">
+      <c r="I74" s="28">
         <f>IF(AND(G74="",H74=""),"",N(G74)*'설정'!$C$13+N(H74)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17449,21 +17464,21 @@
         <f>IF(I74="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I74)+1)</f>
         <v/>
       </c>
-      <c r="K74" s="26">
+      <c r="K74" s="27">
         <f>IF(I74="","",IF(OR(G74="",H74=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G74&gt;='설정'!$C$6),OR('설정'!$D$6="",G74&lt;'설정'!$D$6),OR('설정'!$E$6="",H74&gt;='설정'!$E$6),OR('설정'!$F$6="",H74&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G74&gt;='설정'!$C$7),OR('설정'!$D$7="",G74&lt;'설정'!$D$7),OR('설정'!$E$7="",H74&gt;='설정'!$E$7),OR('설정'!$F$7="",H74&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G74&gt;='설정'!$C$8),OR('설정'!$D$8="",G74&lt;'설정'!$D$8),OR('설정'!$E$8="",H74&gt;='설정'!$E$8),OR('설정'!$F$8="",H74&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L74" s="28">
+      <c r="L74" s="29">
         <f>IF(OR(G74="",H74=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G74-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H74-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M74" s="7" t="n"/>
       <c r="N74" s="7" t="n"/>
-      <c r="O74" s="26">
+      <c r="O74" s="27">
         <f>IF(M74&lt;&gt;"",M74,K74)</f>
         <v/>
       </c>
-      <c r="P74" s="29">
+      <c r="P74" s="30">
         <f>IF(I74="","",IF(G74="","공수1 미응시",IF(H74="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17504,7 +17519,7 @@
         <f>'공수2'!Y75</f>
         <v/>
       </c>
-      <c r="I75" s="27">
+      <c r="I75" s="28">
         <f>IF(AND(G75="",H75=""),"",N(G75)*'설정'!$C$13+N(H75)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17512,21 +17527,21 @@
         <f>IF(I75="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I75)+1)</f>
         <v/>
       </c>
-      <c r="K75" s="26">
+      <c r="K75" s="27">
         <f>IF(I75="","",IF(OR(G75="",H75=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G75&gt;='설정'!$C$6),OR('설정'!$D$6="",G75&lt;'설정'!$D$6),OR('설정'!$E$6="",H75&gt;='설정'!$E$6),OR('설정'!$F$6="",H75&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G75&gt;='설정'!$C$7),OR('설정'!$D$7="",G75&lt;'설정'!$D$7),OR('설정'!$E$7="",H75&gt;='설정'!$E$7),OR('설정'!$F$7="",H75&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G75&gt;='설정'!$C$8),OR('설정'!$D$8="",G75&lt;'설정'!$D$8),OR('설정'!$E$8="",H75&gt;='설정'!$E$8),OR('설정'!$F$8="",H75&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L75" s="28">
+      <c r="L75" s="29">
         <f>IF(OR(G75="",H75=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G75-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H75-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M75" s="7" t="n"/>
       <c r="N75" s="7" t="n"/>
-      <c r="O75" s="26">
+      <c r="O75" s="27">
         <f>IF(M75&lt;&gt;"",M75,K75)</f>
         <v/>
       </c>
-      <c r="P75" s="29">
+      <c r="P75" s="30">
         <f>IF(I75="","",IF(G75="","공수1 미응시",IF(H75="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17567,7 +17582,7 @@
         <f>'공수2'!Y76</f>
         <v/>
       </c>
-      <c r="I76" s="27">
+      <c r="I76" s="28">
         <f>IF(AND(G76="",H76=""),"",N(G76)*'설정'!$C$13+N(H76)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17575,21 +17590,21 @@
         <f>IF(I76="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I76)+1)</f>
         <v/>
       </c>
-      <c r="K76" s="26">
+      <c r="K76" s="27">
         <f>IF(I76="","",IF(OR(G76="",H76=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G76&gt;='설정'!$C$6),OR('설정'!$D$6="",G76&lt;'설정'!$D$6),OR('설정'!$E$6="",H76&gt;='설정'!$E$6),OR('설정'!$F$6="",H76&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G76&gt;='설정'!$C$7),OR('설정'!$D$7="",G76&lt;'설정'!$D$7),OR('설정'!$E$7="",H76&gt;='설정'!$E$7),OR('설정'!$F$7="",H76&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G76&gt;='설정'!$C$8),OR('설정'!$D$8="",G76&lt;'설정'!$D$8),OR('설정'!$E$8="",H76&gt;='설정'!$E$8),OR('설정'!$F$8="",H76&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L76" s="28">
+      <c r="L76" s="29">
         <f>IF(OR(G76="",H76=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G76-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H76-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M76" s="7" t="n"/>
       <c r="N76" s="7" t="n"/>
-      <c r="O76" s="26">
+      <c r="O76" s="27">
         <f>IF(M76&lt;&gt;"",M76,K76)</f>
         <v/>
       </c>
-      <c r="P76" s="29">
+      <c r="P76" s="30">
         <f>IF(I76="","",IF(G76="","공수1 미응시",IF(H76="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17630,7 +17645,7 @@
         <f>'공수2'!Y77</f>
         <v/>
       </c>
-      <c r="I77" s="27">
+      <c r="I77" s="28">
         <f>IF(AND(G77="",H77=""),"",N(G77)*'설정'!$C$13+N(H77)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17638,21 +17653,21 @@
         <f>IF(I77="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I77)+1)</f>
         <v/>
       </c>
-      <c r="K77" s="26">
+      <c r="K77" s="27">
         <f>IF(I77="","",IF(OR(G77="",H77=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G77&gt;='설정'!$C$6),OR('설정'!$D$6="",G77&lt;'설정'!$D$6),OR('설정'!$E$6="",H77&gt;='설정'!$E$6),OR('설정'!$F$6="",H77&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G77&gt;='설정'!$C$7),OR('설정'!$D$7="",G77&lt;'설정'!$D$7),OR('설정'!$E$7="",H77&gt;='설정'!$E$7),OR('설정'!$F$7="",H77&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G77&gt;='설정'!$C$8),OR('설정'!$D$8="",G77&lt;'설정'!$D$8),OR('설정'!$E$8="",H77&gt;='설정'!$E$8),OR('설정'!$F$8="",H77&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L77" s="28">
+      <c r="L77" s="29">
         <f>IF(OR(G77="",H77=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G77-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H77-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M77" s="7" t="n"/>
       <c r="N77" s="7" t="n"/>
-      <c r="O77" s="26">
+      <c r="O77" s="27">
         <f>IF(M77&lt;&gt;"",M77,K77)</f>
         <v/>
       </c>
-      <c r="P77" s="29">
+      <c r="P77" s="30">
         <f>IF(I77="","",IF(G77="","공수1 미응시",IF(H77="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17693,7 +17708,7 @@
         <f>'공수2'!Y78</f>
         <v/>
       </c>
-      <c r="I78" s="27">
+      <c r="I78" s="28">
         <f>IF(AND(G78="",H78=""),"",N(G78)*'설정'!$C$13+N(H78)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17701,21 +17716,21 @@
         <f>IF(I78="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I78)+1)</f>
         <v/>
       </c>
-      <c r="K78" s="26">
+      <c r="K78" s="27">
         <f>IF(I78="","",IF(OR(G78="",H78=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G78&gt;='설정'!$C$6),OR('설정'!$D$6="",G78&lt;'설정'!$D$6),OR('설정'!$E$6="",H78&gt;='설정'!$E$6),OR('설정'!$F$6="",H78&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G78&gt;='설정'!$C$7),OR('설정'!$D$7="",G78&lt;'설정'!$D$7),OR('설정'!$E$7="",H78&gt;='설정'!$E$7),OR('설정'!$F$7="",H78&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G78&gt;='설정'!$C$8),OR('설정'!$D$8="",G78&lt;'설정'!$D$8),OR('설정'!$E$8="",H78&gt;='설정'!$E$8),OR('설정'!$F$8="",H78&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L78" s="28">
+      <c r="L78" s="29">
         <f>IF(OR(G78="",H78=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G78-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H78-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M78" s="7" t="n"/>
       <c r="N78" s="7" t="n"/>
-      <c r="O78" s="26">
+      <c r="O78" s="27">
         <f>IF(M78&lt;&gt;"",M78,K78)</f>
         <v/>
       </c>
-      <c r="P78" s="29">
+      <c r="P78" s="30">
         <f>IF(I78="","",IF(G78="","공수1 미응시",IF(H78="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17756,7 +17771,7 @@
         <f>'공수2'!Y79</f>
         <v/>
       </c>
-      <c r="I79" s="27">
+      <c r="I79" s="28">
         <f>IF(AND(G79="",H79=""),"",N(G79)*'설정'!$C$13+N(H79)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17764,21 +17779,21 @@
         <f>IF(I79="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I79)+1)</f>
         <v/>
       </c>
-      <c r="K79" s="26">
+      <c r="K79" s="27">
         <f>IF(I79="","",IF(OR(G79="",H79=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G79&gt;='설정'!$C$6),OR('설정'!$D$6="",G79&lt;'설정'!$D$6),OR('설정'!$E$6="",H79&gt;='설정'!$E$6),OR('설정'!$F$6="",H79&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G79&gt;='설정'!$C$7),OR('설정'!$D$7="",G79&lt;'설정'!$D$7),OR('설정'!$E$7="",H79&gt;='설정'!$E$7),OR('설정'!$F$7="",H79&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G79&gt;='설정'!$C$8),OR('설정'!$D$8="",G79&lt;'설정'!$D$8),OR('설정'!$E$8="",H79&gt;='설정'!$E$8),OR('설정'!$F$8="",H79&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L79" s="28">
+      <c r="L79" s="29">
         <f>IF(OR(G79="",H79=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G79-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H79-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M79" s="7" t="n"/>
       <c r="N79" s="7" t="n"/>
-      <c r="O79" s="26">
+      <c r="O79" s="27">
         <f>IF(M79&lt;&gt;"",M79,K79)</f>
         <v/>
       </c>
-      <c r="P79" s="29">
+      <c r="P79" s="30">
         <f>IF(I79="","",IF(G79="","공수1 미응시",IF(H79="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17819,7 +17834,7 @@
         <f>'공수2'!Y80</f>
         <v/>
       </c>
-      <c r="I80" s="27">
+      <c r="I80" s="28">
         <f>IF(AND(G80="",H80=""),"",N(G80)*'설정'!$C$13+N(H80)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17827,21 +17842,21 @@
         <f>IF(I80="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I80)+1)</f>
         <v/>
       </c>
-      <c r="K80" s="26">
+      <c r="K80" s="27">
         <f>IF(I80="","",IF(OR(G80="",H80=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G80&gt;='설정'!$C$6),OR('설정'!$D$6="",G80&lt;'설정'!$D$6),OR('설정'!$E$6="",H80&gt;='설정'!$E$6),OR('설정'!$F$6="",H80&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G80&gt;='설정'!$C$7),OR('설정'!$D$7="",G80&lt;'설정'!$D$7),OR('설정'!$E$7="",H80&gt;='설정'!$E$7),OR('설정'!$F$7="",H80&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G80&gt;='설정'!$C$8),OR('설정'!$D$8="",G80&lt;'설정'!$D$8),OR('설정'!$E$8="",H80&gt;='설정'!$E$8),OR('설정'!$F$8="",H80&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L80" s="28">
+      <c r="L80" s="29">
         <f>IF(OR(G80="",H80=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G80-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H80-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M80" s="7" t="n"/>
       <c r="N80" s="7" t="n"/>
-      <c r="O80" s="26">
+      <c r="O80" s="27">
         <f>IF(M80&lt;&gt;"",M80,K80)</f>
         <v/>
       </c>
-      <c r="P80" s="29">
+      <c r="P80" s="30">
         <f>IF(I80="","",IF(G80="","공수1 미응시",IF(H80="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17882,7 +17897,7 @@
         <f>'공수2'!Y81</f>
         <v/>
       </c>
-      <c r="I81" s="27">
+      <c r="I81" s="28">
         <f>IF(AND(G81="",H81=""),"",N(G81)*'설정'!$C$13+N(H81)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17890,21 +17905,21 @@
         <f>IF(I81="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I81)+1)</f>
         <v/>
       </c>
-      <c r="K81" s="26">
+      <c r="K81" s="27">
         <f>IF(I81="","",IF(OR(G81="",H81=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G81&gt;='설정'!$C$6),OR('설정'!$D$6="",G81&lt;'설정'!$D$6),OR('설정'!$E$6="",H81&gt;='설정'!$E$6),OR('설정'!$F$6="",H81&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G81&gt;='설정'!$C$7),OR('설정'!$D$7="",G81&lt;'설정'!$D$7),OR('설정'!$E$7="",H81&gt;='설정'!$E$7),OR('설정'!$F$7="",H81&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G81&gt;='설정'!$C$8),OR('설정'!$D$8="",G81&lt;'설정'!$D$8),OR('설정'!$E$8="",H81&gt;='설정'!$E$8),OR('설정'!$F$8="",H81&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L81" s="28">
+      <c r="L81" s="29">
         <f>IF(OR(G81="",H81=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G81-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H81-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M81" s="7" t="n"/>
       <c r="N81" s="7" t="n"/>
-      <c r="O81" s="26">
+      <c r="O81" s="27">
         <f>IF(M81&lt;&gt;"",M81,K81)</f>
         <v/>
       </c>
-      <c r="P81" s="29">
+      <c r="P81" s="30">
         <f>IF(I81="","",IF(G81="","공수1 미응시",IF(H81="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -17945,7 +17960,7 @@
         <f>'공수2'!Y82</f>
         <v/>
       </c>
-      <c r="I82" s="27">
+      <c r="I82" s="28">
         <f>IF(AND(G82="",H82=""),"",N(G82)*'설정'!$C$13+N(H82)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -17953,21 +17968,21 @@
         <f>IF(I82="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I82)+1)</f>
         <v/>
       </c>
-      <c r="K82" s="26">
+      <c r="K82" s="27">
         <f>IF(I82="","",IF(OR(G82="",H82=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G82&gt;='설정'!$C$6),OR('설정'!$D$6="",G82&lt;'설정'!$D$6),OR('설정'!$E$6="",H82&gt;='설정'!$E$6),OR('설정'!$F$6="",H82&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G82&gt;='설정'!$C$7),OR('설정'!$D$7="",G82&lt;'설정'!$D$7),OR('설정'!$E$7="",H82&gt;='설정'!$E$7),OR('설정'!$F$7="",H82&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G82&gt;='설정'!$C$8),OR('설정'!$D$8="",G82&lt;'설정'!$D$8),OR('설정'!$E$8="",H82&gt;='설정'!$E$8),OR('설정'!$F$8="",H82&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L82" s="28">
+      <c r="L82" s="29">
         <f>IF(OR(G82="",H82=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G82-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H82-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M82" s="7" t="n"/>
       <c r="N82" s="7" t="n"/>
-      <c r="O82" s="26">
+      <c r="O82" s="27">
         <f>IF(M82&lt;&gt;"",M82,K82)</f>
         <v/>
       </c>
-      <c r="P82" s="29">
+      <c r="P82" s="30">
         <f>IF(I82="","",IF(G82="","공수1 미응시",IF(H82="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -18008,7 +18023,7 @@
         <f>'공수2'!Y83</f>
         <v/>
       </c>
-      <c r="I83" s="27">
+      <c r="I83" s="28">
         <f>IF(AND(G83="",H83=""),"",N(G83)*'설정'!$C$13+N(H83)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -18016,21 +18031,21 @@
         <f>IF(I83="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I83)+1)</f>
         <v/>
       </c>
-      <c r="K83" s="26">
+      <c r="K83" s="27">
         <f>IF(I83="","",IF(OR(G83="",H83=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G83&gt;='설정'!$C$6),OR('설정'!$D$6="",G83&lt;'설정'!$D$6),OR('설정'!$E$6="",H83&gt;='설정'!$E$6),OR('설정'!$F$6="",H83&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G83&gt;='설정'!$C$7),OR('설정'!$D$7="",G83&lt;'설정'!$D$7),OR('설정'!$E$7="",H83&gt;='설정'!$E$7),OR('설정'!$F$7="",H83&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G83&gt;='설정'!$C$8),OR('설정'!$D$8="",G83&lt;'설정'!$D$8),OR('설정'!$E$8="",H83&gt;='설정'!$E$8),OR('설정'!$F$8="",H83&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L83" s="28">
+      <c r="L83" s="29">
         <f>IF(OR(G83="",H83=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G83-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H83-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M83" s="7" t="n"/>
       <c r="N83" s="7" t="n"/>
-      <c r="O83" s="26">
+      <c r="O83" s="27">
         <f>IF(M83&lt;&gt;"",M83,K83)</f>
         <v/>
       </c>
-      <c r="P83" s="29">
+      <c r="P83" s="30">
         <f>IF(I83="","",IF(G83="","공수1 미응시",IF(H83="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -18071,7 +18086,7 @@
         <f>'공수2'!Y84</f>
         <v/>
       </c>
-      <c r="I84" s="27">
+      <c r="I84" s="28">
         <f>IF(AND(G84="",H84=""),"",N(G84)*'설정'!$C$13+N(H84)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -18079,21 +18094,21 @@
         <f>IF(I84="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I84)+1)</f>
         <v/>
       </c>
-      <c r="K84" s="26">
+      <c r="K84" s="27">
         <f>IF(I84="","",IF(OR(G84="",H84=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G84&gt;='설정'!$C$6),OR('설정'!$D$6="",G84&lt;'설정'!$D$6),OR('설정'!$E$6="",H84&gt;='설정'!$E$6),OR('설정'!$F$6="",H84&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G84&gt;='설정'!$C$7),OR('설정'!$D$7="",G84&lt;'설정'!$D$7),OR('설정'!$E$7="",H84&gt;='설정'!$E$7),OR('설정'!$F$7="",H84&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G84&gt;='설정'!$C$8),OR('설정'!$D$8="",G84&lt;'설정'!$D$8),OR('설정'!$E$8="",H84&gt;='설정'!$E$8),OR('설정'!$F$8="",H84&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L84" s="28">
+      <c r="L84" s="29">
         <f>IF(OR(G84="",H84=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G84-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H84-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M84" s="7" t="n"/>
       <c r="N84" s="7" t="n"/>
-      <c r="O84" s="26">
+      <c r="O84" s="27">
         <f>IF(M84&lt;&gt;"",M84,K84)</f>
         <v/>
       </c>
-      <c r="P84" s="29">
+      <c r="P84" s="30">
         <f>IF(I84="","",IF(G84="","공수1 미응시",IF(H84="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -18134,7 +18149,7 @@
         <f>'공수2'!Y85</f>
         <v/>
       </c>
-      <c r="I85" s="27">
+      <c r="I85" s="28">
         <f>IF(AND(G85="",H85=""),"",N(G85)*'설정'!$C$13+N(H85)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -18142,21 +18157,21 @@
         <f>IF(I85="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I85)+1)</f>
         <v/>
       </c>
-      <c r="K85" s="26">
+      <c r="K85" s="27">
         <f>IF(I85="","",IF(OR(G85="",H85=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G85&gt;='설정'!$C$6),OR('설정'!$D$6="",G85&lt;'설정'!$D$6),OR('설정'!$E$6="",H85&gt;='설정'!$E$6),OR('설정'!$F$6="",H85&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G85&gt;='설정'!$C$7),OR('설정'!$D$7="",G85&lt;'설정'!$D$7),OR('설정'!$E$7="",H85&gt;='설정'!$E$7),OR('설정'!$F$7="",H85&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G85&gt;='설정'!$C$8),OR('설정'!$D$8="",G85&lt;'설정'!$D$8),OR('설정'!$E$8="",H85&gt;='설정'!$E$8),OR('설정'!$F$8="",H85&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L85" s="28">
+      <c r="L85" s="29">
         <f>IF(OR(G85="",H85=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G85-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H85-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M85" s="7" t="n"/>
       <c r="N85" s="7" t="n"/>
-      <c r="O85" s="26">
+      <c r="O85" s="27">
         <f>IF(M85&lt;&gt;"",M85,K85)</f>
         <v/>
       </c>
-      <c r="P85" s="29">
+      <c r="P85" s="30">
         <f>IF(I85="","",IF(G85="","공수1 미응시",IF(H85="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -18197,7 +18212,7 @@
         <f>'공수2'!Y86</f>
         <v/>
       </c>
-      <c r="I86" s="27">
+      <c r="I86" s="28">
         <f>IF(AND(G86="",H86=""),"",N(G86)*'설정'!$C$13+N(H86)*'설정'!$C$14)</f>
         <v/>
       </c>
@@ -18205,21 +18220,21 @@
         <f>IF(I86="","",COUNTIF($I$7:$I$86,"&gt;"&amp;I86)+1)</f>
         <v/>
       </c>
-      <c r="K86" s="26">
+      <c r="K86" s="27">
         <f>IF(I86="","",IF(OR(G86="",H86=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G86&gt;='설정'!$C$6),OR('설정'!$D$6="",G86&lt;'설정'!$D$6),OR('설정'!$E$6="",H86&gt;='설정'!$E$6),OR('설정'!$F$6="",H86&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G86&gt;='설정'!$C$7),OR('설정'!$D$7="",G86&lt;'설정'!$D$7),OR('설정'!$E$7="",H86&gt;='설정'!$E$7),OR('설정'!$F$7="",H86&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G86&gt;='설정'!$C$8),OR('설정'!$D$8="",G86&lt;'설정'!$D$8),OR('설정'!$E$8="",H86&gt;='설정'!$E$8),OR('설정'!$F$8="",H86&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
         <v/>
       </c>
-      <c r="L86" s="28">
+      <c r="L86" s="29">
         <f>IF(OR(G86="",H86=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G86-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H86-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M86" s="7" t="n"/>
       <c r="N86" s="7" t="n"/>
-      <c r="O86" s="26">
+      <c r="O86" s="27">
         <f>IF(M86&lt;&gt;"",M86,K86)</f>
         <v/>
       </c>
-      <c r="P86" s="29">
+      <c r="P86" s="30">
         <f>IF(I86="","",IF(G86="","공수1 미응시",IF(H86="","공수2 미응시","")))</f>
         <v/>
       </c>
@@ -18410,11 +18425,11 @@
         <f>IF($N7="","",INDEX('반배정'!H$7:H$86,$N7))</f>
         <v/>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="37">
         <f>IF($N7="","",INDEX('반배정'!I$7:I$86,$N7))</f>
         <v/>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="27">
         <f>IF($N7="","",INDEX('반배정'!O$7:O$86,$N7))</f>
         <v/>
       </c>
@@ -18468,11 +18483,11 @@
         <f>IF($N8="","",INDEX('반배정'!H$7:H$86,$N8))</f>
         <v/>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="37">
         <f>IF($N8="","",INDEX('반배정'!I$7:I$86,$N8))</f>
         <v/>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="27">
         <f>IF($N8="","",INDEX('반배정'!O$7:O$86,$N8))</f>
         <v/>
       </c>
@@ -18526,11 +18541,11 @@
         <f>IF($N9="","",INDEX('반배정'!H$7:H$86,$N9))</f>
         <v/>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="37">
         <f>IF($N9="","",INDEX('반배정'!I$7:I$86,$N9))</f>
         <v/>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="27">
         <f>IF($N9="","",INDEX('반배정'!O$7:O$86,$N9))</f>
         <v/>
       </c>
@@ -18584,11 +18599,11 @@
         <f>IF($N10="","",INDEX('반배정'!H$7:H$86,$N10))</f>
         <v/>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="37">
         <f>IF($N10="","",INDEX('반배정'!I$7:I$86,$N10))</f>
         <v/>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="27">
         <f>IF($N10="","",INDEX('반배정'!O$7:O$86,$N10))</f>
         <v/>
       </c>
@@ -18642,11 +18657,11 @@
         <f>IF($N11="","",INDEX('반배정'!H$7:H$86,$N11))</f>
         <v/>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="37">
         <f>IF($N11="","",INDEX('반배정'!I$7:I$86,$N11))</f>
         <v/>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="27">
         <f>IF($N11="","",INDEX('반배정'!O$7:O$86,$N11))</f>
         <v/>
       </c>
@@ -18700,11 +18715,11 @@
         <f>IF($N12="","",INDEX('반배정'!H$7:H$86,$N12))</f>
         <v/>
       </c>
-      <c r="H12" s="36">
+      <c r="H12" s="37">
         <f>IF($N12="","",INDEX('반배정'!I$7:I$86,$N12))</f>
         <v/>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="27">
         <f>IF($N12="","",INDEX('반배정'!O$7:O$86,$N12))</f>
         <v/>
       </c>
@@ -18758,11 +18773,11 @@
         <f>IF($N13="","",INDEX('반배정'!H$7:H$86,$N13))</f>
         <v/>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="37">
         <f>IF($N13="","",INDEX('반배정'!I$7:I$86,$N13))</f>
         <v/>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="27">
         <f>IF($N13="","",INDEX('반배정'!O$7:O$86,$N13))</f>
         <v/>
       </c>
@@ -18816,11 +18831,11 @@
         <f>IF($N14="","",INDEX('반배정'!H$7:H$86,$N14))</f>
         <v/>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="37">
         <f>IF($N14="","",INDEX('반배정'!I$7:I$86,$N14))</f>
         <v/>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="27">
         <f>IF($N14="","",INDEX('반배정'!O$7:O$86,$N14))</f>
         <v/>
       </c>
@@ -18874,11 +18889,11 @@
         <f>IF($N15="","",INDEX('반배정'!H$7:H$86,$N15))</f>
         <v/>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="37">
         <f>IF($N15="","",INDEX('반배정'!I$7:I$86,$N15))</f>
         <v/>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="27">
         <f>IF($N15="","",INDEX('반배정'!O$7:O$86,$N15))</f>
         <v/>
       </c>
@@ -18932,11 +18947,11 @@
         <f>IF($N16="","",INDEX('반배정'!H$7:H$86,$N16))</f>
         <v/>
       </c>
-      <c r="H16" s="36">
+      <c r="H16" s="37">
         <f>IF($N16="","",INDEX('반배정'!I$7:I$86,$N16))</f>
         <v/>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="27">
         <f>IF($N16="","",INDEX('반배정'!O$7:O$86,$N16))</f>
         <v/>
       </c>
@@ -18990,11 +19005,11 @@
         <f>IF($N17="","",INDEX('반배정'!H$7:H$86,$N17))</f>
         <v/>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="37">
         <f>IF($N17="","",INDEX('반배정'!I$7:I$86,$N17))</f>
         <v/>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="27">
         <f>IF($N17="","",INDEX('반배정'!O$7:O$86,$N17))</f>
         <v/>
       </c>
@@ -19048,11 +19063,11 @@
         <f>IF($N18="","",INDEX('반배정'!H$7:H$86,$N18))</f>
         <v/>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="37">
         <f>IF($N18="","",INDEX('반배정'!I$7:I$86,$N18))</f>
         <v/>
       </c>
-      <c r="I18" s="26">
+      <c r="I18" s="27">
         <f>IF($N18="","",INDEX('반배정'!O$7:O$86,$N18))</f>
         <v/>
       </c>
@@ -19106,11 +19121,11 @@
         <f>IF($N19="","",INDEX('반배정'!H$7:H$86,$N19))</f>
         <v/>
       </c>
-      <c r="H19" s="36">
+      <c r="H19" s="37">
         <f>IF($N19="","",INDEX('반배정'!I$7:I$86,$N19))</f>
         <v/>
       </c>
-      <c r="I19" s="26">
+      <c r="I19" s="27">
         <f>IF($N19="","",INDEX('반배정'!O$7:O$86,$N19))</f>
         <v/>
       </c>
@@ -19164,11 +19179,11 @@
         <f>IF($N20="","",INDEX('반배정'!H$7:H$86,$N20))</f>
         <v/>
       </c>
-      <c r="H20" s="36">
+      <c r="H20" s="37">
         <f>IF($N20="","",INDEX('반배정'!I$7:I$86,$N20))</f>
         <v/>
       </c>
-      <c r="I20" s="26">
+      <c r="I20" s="27">
         <f>IF($N20="","",INDEX('반배정'!O$7:O$86,$N20))</f>
         <v/>
       </c>
@@ -19222,11 +19237,11 @@
         <f>IF($N21="","",INDEX('반배정'!H$7:H$86,$N21))</f>
         <v/>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="37">
         <f>IF($N21="","",INDEX('반배정'!I$7:I$86,$N21))</f>
         <v/>
       </c>
-      <c r="I21" s="26">
+      <c r="I21" s="27">
         <f>IF($N21="","",INDEX('반배정'!O$7:O$86,$N21))</f>
         <v/>
       </c>
@@ -19280,11 +19295,11 @@
         <f>IF($N22="","",INDEX('반배정'!H$7:H$86,$N22))</f>
         <v/>
       </c>
-      <c r="H22" s="36">
+      <c r="H22" s="37">
         <f>IF($N22="","",INDEX('반배정'!I$7:I$86,$N22))</f>
         <v/>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="27">
         <f>IF($N22="","",INDEX('반배정'!O$7:O$86,$N22))</f>
         <v/>
       </c>
@@ -19338,11 +19353,11 @@
         <f>IF($N23="","",INDEX('반배정'!H$7:H$86,$N23))</f>
         <v/>
       </c>
-      <c r="H23" s="36">
+      <c r="H23" s="37">
         <f>IF($N23="","",INDEX('반배정'!I$7:I$86,$N23))</f>
         <v/>
       </c>
-      <c r="I23" s="26">
+      <c r="I23" s="27">
         <f>IF($N23="","",INDEX('반배정'!O$7:O$86,$N23))</f>
         <v/>
       </c>
@@ -19396,11 +19411,11 @@
         <f>IF($N24="","",INDEX('반배정'!H$7:H$86,$N24))</f>
         <v/>
       </c>
-      <c r="H24" s="36">
+      <c r="H24" s="37">
         <f>IF($N24="","",INDEX('반배정'!I$7:I$86,$N24))</f>
         <v/>
       </c>
-      <c r="I24" s="26">
+      <c r="I24" s="27">
         <f>IF($N24="","",INDEX('반배정'!O$7:O$86,$N24))</f>
         <v/>
       </c>
@@ -19454,11 +19469,11 @@
         <f>IF($N25="","",INDEX('반배정'!H$7:H$86,$N25))</f>
         <v/>
       </c>
-      <c r="H25" s="36">
+      <c r="H25" s="37">
         <f>IF($N25="","",INDEX('반배정'!I$7:I$86,$N25))</f>
         <v/>
       </c>
-      <c r="I25" s="26">
+      <c r="I25" s="27">
         <f>IF($N25="","",INDEX('반배정'!O$7:O$86,$N25))</f>
         <v/>
       </c>
@@ -19512,11 +19527,11 @@
         <f>IF($N26="","",INDEX('반배정'!H$7:H$86,$N26))</f>
         <v/>
       </c>
-      <c r="H26" s="36">
+      <c r="H26" s="37">
         <f>IF($N26="","",INDEX('반배정'!I$7:I$86,$N26))</f>
         <v/>
       </c>
-      <c r="I26" s="26">
+      <c r="I26" s="27">
         <f>IF($N26="","",INDEX('반배정'!O$7:O$86,$N26))</f>
         <v/>
       </c>
@@ -19570,11 +19585,11 @@
         <f>IF($N27="","",INDEX('반배정'!H$7:H$86,$N27))</f>
         <v/>
       </c>
-      <c r="H27" s="36">
+      <c r="H27" s="37">
         <f>IF($N27="","",INDEX('반배정'!I$7:I$86,$N27))</f>
         <v/>
       </c>
-      <c r="I27" s="26">
+      <c r="I27" s="27">
         <f>IF($N27="","",INDEX('반배정'!O$7:O$86,$N27))</f>
         <v/>
       </c>
@@ -19628,11 +19643,11 @@
         <f>IF($N28="","",INDEX('반배정'!H$7:H$86,$N28))</f>
         <v/>
       </c>
-      <c r="H28" s="36">
+      <c r="H28" s="37">
         <f>IF($N28="","",INDEX('반배정'!I$7:I$86,$N28))</f>
         <v/>
       </c>
-      <c r="I28" s="26">
+      <c r="I28" s="27">
         <f>IF($N28="","",INDEX('반배정'!O$7:O$86,$N28))</f>
         <v/>
       </c>
@@ -19686,11 +19701,11 @@
         <f>IF($N29="","",INDEX('반배정'!H$7:H$86,$N29))</f>
         <v/>
       </c>
-      <c r="H29" s="36">
+      <c r="H29" s="37">
         <f>IF($N29="","",INDEX('반배정'!I$7:I$86,$N29))</f>
         <v/>
       </c>
-      <c r="I29" s="26">
+      <c r="I29" s="27">
         <f>IF($N29="","",INDEX('반배정'!O$7:O$86,$N29))</f>
         <v/>
       </c>
@@ -19744,11 +19759,11 @@
         <f>IF($N30="","",INDEX('반배정'!H$7:H$86,$N30))</f>
         <v/>
       </c>
-      <c r="H30" s="36">
+      <c r="H30" s="37">
         <f>IF($N30="","",INDEX('반배정'!I$7:I$86,$N30))</f>
         <v/>
       </c>
-      <c r="I30" s="26">
+      <c r="I30" s="27">
         <f>IF($N30="","",INDEX('반배정'!O$7:O$86,$N30))</f>
         <v/>
       </c>
@@ -19802,11 +19817,11 @@
         <f>IF($N31="","",INDEX('반배정'!H$7:H$86,$N31))</f>
         <v/>
       </c>
-      <c r="H31" s="36">
+      <c r="H31" s="37">
         <f>IF($N31="","",INDEX('반배정'!I$7:I$86,$N31))</f>
         <v/>
       </c>
-      <c r="I31" s="26">
+      <c r="I31" s="27">
         <f>IF($N31="","",INDEX('반배정'!O$7:O$86,$N31))</f>
         <v/>
       </c>
@@ -19860,11 +19875,11 @@
         <f>IF($N32="","",INDEX('반배정'!H$7:H$86,$N32))</f>
         <v/>
       </c>
-      <c r="H32" s="36">
+      <c r="H32" s="37">
         <f>IF($N32="","",INDEX('반배정'!I$7:I$86,$N32))</f>
         <v/>
       </c>
-      <c r="I32" s="26">
+      <c r="I32" s="27">
         <f>IF($N32="","",INDEX('반배정'!O$7:O$86,$N32))</f>
         <v/>
       </c>
@@ -19918,11 +19933,11 @@
         <f>IF($N33="","",INDEX('반배정'!H$7:H$86,$N33))</f>
         <v/>
       </c>
-      <c r="H33" s="36">
+      <c r="H33" s="37">
         <f>IF($N33="","",INDEX('반배정'!I$7:I$86,$N33))</f>
         <v/>
       </c>
-      <c r="I33" s="26">
+      <c r="I33" s="27">
         <f>IF($N33="","",INDEX('반배정'!O$7:O$86,$N33))</f>
         <v/>
       </c>
@@ -19976,11 +19991,11 @@
         <f>IF($N34="","",INDEX('반배정'!H$7:H$86,$N34))</f>
         <v/>
       </c>
-      <c r="H34" s="36">
+      <c r="H34" s="37">
         <f>IF($N34="","",INDEX('반배정'!I$7:I$86,$N34))</f>
         <v/>
       </c>
-      <c r="I34" s="26">
+      <c r="I34" s="27">
         <f>IF($N34="","",INDEX('반배정'!O$7:O$86,$N34))</f>
         <v/>
       </c>
@@ -20034,11 +20049,11 @@
         <f>IF($N35="","",INDEX('반배정'!H$7:H$86,$N35))</f>
         <v/>
       </c>
-      <c r="H35" s="36">
+      <c r="H35" s="37">
         <f>IF($N35="","",INDEX('반배정'!I$7:I$86,$N35))</f>
         <v/>
       </c>
-      <c r="I35" s="26">
+      <c r="I35" s="27">
         <f>IF($N35="","",INDEX('반배정'!O$7:O$86,$N35))</f>
         <v/>
       </c>
@@ -20092,11 +20107,11 @@
         <f>IF($N36="","",INDEX('반배정'!H$7:H$86,$N36))</f>
         <v/>
       </c>
-      <c r="H36" s="36">
+      <c r="H36" s="37">
         <f>IF($N36="","",INDEX('반배정'!I$7:I$86,$N36))</f>
         <v/>
       </c>
-      <c r="I36" s="26">
+      <c r="I36" s="27">
         <f>IF($N36="","",INDEX('반배정'!O$7:O$86,$N36))</f>
         <v/>
       </c>
@@ -20150,11 +20165,11 @@
         <f>IF($N37="","",INDEX('반배정'!H$7:H$86,$N37))</f>
         <v/>
       </c>
-      <c r="H37" s="36">
+      <c r="H37" s="37">
         <f>IF($N37="","",INDEX('반배정'!I$7:I$86,$N37))</f>
         <v/>
       </c>
-      <c r="I37" s="26">
+      <c r="I37" s="27">
         <f>IF($N37="","",INDEX('반배정'!O$7:O$86,$N37))</f>
         <v/>
       </c>
@@ -20208,11 +20223,11 @@
         <f>IF($N38="","",INDEX('반배정'!H$7:H$86,$N38))</f>
         <v/>
       </c>
-      <c r="H38" s="36">
+      <c r="H38" s="37">
         <f>IF($N38="","",INDEX('반배정'!I$7:I$86,$N38))</f>
         <v/>
       </c>
-      <c r="I38" s="26">
+      <c r="I38" s="27">
         <f>IF($N38="","",INDEX('반배정'!O$7:O$86,$N38))</f>
         <v/>
       </c>
@@ -20266,11 +20281,11 @@
         <f>IF($N39="","",INDEX('반배정'!H$7:H$86,$N39))</f>
         <v/>
       </c>
-      <c r="H39" s="36">
+      <c r="H39" s="37">
         <f>IF($N39="","",INDEX('반배정'!I$7:I$86,$N39))</f>
         <v/>
       </c>
-      <c r="I39" s="26">
+      <c r="I39" s="27">
         <f>IF($N39="","",INDEX('반배정'!O$7:O$86,$N39))</f>
         <v/>
       </c>
@@ -20324,11 +20339,11 @@
         <f>IF($N40="","",INDEX('반배정'!H$7:H$86,$N40))</f>
         <v/>
       </c>
-      <c r="H40" s="36">
+      <c r="H40" s="37">
         <f>IF($N40="","",INDEX('반배정'!I$7:I$86,$N40))</f>
         <v/>
       </c>
-      <c r="I40" s="26">
+      <c r="I40" s="27">
         <f>IF($N40="","",INDEX('반배정'!O$7:O$86,$N40))</f>
         <v/>
       </c>
@@ -20382,11 +20397,11 @@
         <f>IF($N41="","",INDEX('반배정'!H$7:H$86,$N41))</f>
         <v/>
       </c>
-      <c r="H41" s="36">
+      <c r="H41" s="37">
         <f>IF($N41="","",INDEX('반배정'!I$7:I$86,$N41))</f>
         <v/>
       </c>
-      <c r="I41" s="26">
+      <c r="I41" s="27">
         <f>IF($N41="","",INDEX('반배정'!O$7:O$86,$N41))</f>
         <v/>
       </c>
@@ -20440,11 +20455,11 @@
         <f>IF($N42="","",INDEX('반배정'!H$7:H$86,$N42))</f>
         <v/>
       </c>
-      <c r="H42" s="36">
+      <c r="H42" s="37">
         <f>IF($N42="","",INDEX('반배정'!I$7:I$86,$N42))</f>
         <v/>
       </c>
-      <c r="I42" s="26">
+      <c r="I42" s="27">
         <f>IF($N42="","",INDEX('반배정'!O$7:O$86,$N42))</f>
         <v/>
       </c>
@@ -20498,11 +20513,11 @@
         <f>IF($N43="","",INDEX('반배정'!H$7:H$86,$N43))</f>
         <v/>
       </c>
-      <c r="H43" s="36">
+      <c r="H43" s="37">
         <f>IF($N43="","",INDEX('반배정'!I$7:I$86,$N43))</f>
         <v/>
       </c>
-      <c r="I43" s="26">
+      <c r="I43" s="27">
         <f>IF($N43="","",INDEX('반배정'!O$7:O$86,$N43))</f>
         <v/>
       </c>
@@ -20556,11 +20571,11 @@
         <f>IF($N44="","",INDEX('반배정'!H$7:H$86,$N44))</f>
         <v/>
       </c>
-      <c r="H44" s="36">
+      <c r="H44" s="37">
         <f>IF($N44="","",INDEX('반배정'!I$7:I$86,$N44))</f>
         <v/>
       </c>
-      <c r="I44" s="26">
+      <c r="I44" s="27">
         <f>IF($N44="","",INDEX('반배정'!O$7:O$86,$N44))</f>
         <v/>
       </c>
@@ -20614,11 +20629,11 @@
         <f>IF($N45="","",INDEX('반배정'!H$7:H$86,$N45))</f>
         <v/>
       </c>
-      <c r="H45" s="36">
+      <c r="H45" s="37">
         <f>IF($N45="","",INDEX('반배정'!I$7:I$86,$N45))</f>
         <v/>
       </c>
-      <c r="I45" s="26">
+      <c r="I45" s="27">
         <f>IF($N45="","",INDEX('반배정'!O$7:O$86,$N45))</f>
         <v/>
       </c>
@@ -20672,11 +20687,11 @@
         <f>IF($N46="","",INDEX('반배정'!H$7:H$86,$N46))</f>
         <v/>
       </c>
-      <c r="H46" s="36">
+      <c r="H46" s="37">
         <f>IF($N46="","",INDEX('반배정'!I$7:I$86,$N46))</f>
         <v/>
       </c>
-      <c r="I46" s="26">
+      <c r="I46" s="27">
         <f>IF($N46="","",INDEX('반배정'!O$7:O$86,$N46))</f>
         <v/>
       </c>
@@ -20730,11 +20745,11 @@
         <f>IF($N47="","",INDEX('반배정'!H$7:H$86,$N47))</f>
         <v/>
       </c>
-      <c r="H47" s="36">
+      <c r="H47" s="37">
         <f>IF($N47="","",INDEX('반배정'!I$7:I$86,$N47))</f>
         <v/>
       </c>
-      <c r="I47" s="26">
+      <c r="I47" s="27">
         <f>IF($N47="","",INDEX('반배정'!O$7:O$86,$N47))</f>
         <v/>
       </c>
@@ -20788,11 +20803,11 @@
         <f>IF($N48="","",INDEX('반배정'!H$7:H$86,$N48))</f>
         <v/>
       </c>
-      <c r="H48" s="36">
+      <c r="H48" s="37">
         <f>IF($N48="","",INDEX('반배정'!I$7:I$86,$N48))</f>
         <v/>
       </c>
-      <c r="I48" s="26">
+      <c r="I48" s="27">
         <f>IF($N48="","",INDEX('반배정'!O$7:O$86,$N48))</f>
         <v/>
       </c>
@@ -20846,11 +20861,11 @@
         <f>IF($N49="","",INDEX('반배정'!H$7:H$86,$N49))</f>
         <v/>
       </c>
-      <c r="H49" s="36">
+      <c r="H49" s="37">
         <f>IF($N49="","",INDEX('반배정'!I$7:I$86,$N49))</f>
         <v/>
       </c>
-      <c r="I49" s="26">
+      <c r="I49" s="27">
         <f>IF($N49="","",INDEX('반배정'!O$7:O$86,$N49))</f>
         <v/>
       </c>
@@ -20904,11 +20919,11 @@
         <f>IF($N50="","",INDEX('반배정'!H$7:H$86,$N50))</f>
         <v/>
       </c>
-      <c r="H50" s="36">
+      <c r="H50" s="37">
         <f>IF($N50="","",INDEX('반배정'!I$7:I$86,$N50))</f>
         <v/>
       </c>
-      <c r="I50" s="26">
+      <c r="I50" s="27">
         <f>IF($N50="","",INDEX('반배정'!O$7:O$86,$N50))</f>
         <v/>
       </c>
@@ -20962,11 +20977,11 @@
         <f>IF($N51="","",INDEX('반배정'!H$7:H$86,$N51))</f>
         <v/>
       </c>
-      <c r="H51" s="36">
+      <c r="H51" s="37">
         <f>IF($N51="","",INDEX('반배정'!I$7:I$86,$N51))</f>
         <v/>
       </c>
-      <c r="I51" s="26">
+      <c r="I51" s="27">
         <f>IF($N51="","",INDEX('반배정'!O$7:O$86,$N51))</f>
         <v/>
       </c>
@@ -21020,11 +21035,11 @@
         <f>IF($N52="","",INDEX('반배정'!H$7:H$86,$N52))</f>
         <v/>
       </c>
-      <c r="H52" s="36">
+      <c r="H52" s="37">
         <f>IF($N52="","",INDEX('반배정'!I$7:I$86,$N52))</f>
         <v/>
       </c>
-      <c r="I52" s="26">
+      <c r="I52" s="27">
         <f>IF($N52="","",INDEX('반배정'!O$7:O$86,$N52))</f>
         <v/>
       </c>
@@ -21078,11 +21093,11 @@
         <f>IF($N53="","",INDEX('반배정'!H$7:H$86,$N53))</f>
         <v/>
       </c>
-      <c r="H53" s="36">
+      <c r="H53" s="37">
         <f>IF($N53="","",INDEX('반배정'!I$7:I$86,$N53))</f>
         <v/>
       </c>
-      <c r="I53" s="26">
+      <c r="I53" s="27">
         <f>IF($N53="","",INDEX('반배정'!O$7:O$86,$N53))</f>
         <v/>
       </c>
@@ -21136,11 +21151,11 @@
         <f>IF($N54="","",INDEX('반배정'!H$7:H$86,$N54))</f>
         <v/>
       </c>
-      <c r="H54" s="36">
+      <c r="H54" s="37">
         <f>IF($N54="","",INDEX('반배정'!I$7:I$86,$N54))</f>
         <v/>
       </c>
-      <c r="I54" s="26">
+      <c r="I54" s="27">
         <f>IF($N54="","",INDEX('반배정'!O$7:O$86,$N54))</f>
         <v/>
       </c>
@@ -21194,11 +21209,11 @@
         <f>IF($N55="","",INDEX('반배정'!H$7:H$86,$N55))</f>
         <v/>
       </c>
-      <c r="H55" s="36">
+      <c r="H55" s="37">
         <f>IF($N55="","",INDEX('반배정'!I$7:I$86,$N55))</f>
         <v/>
       </c>
-      <c r="I55" s="26">
+      <c r="I55" s="27">
         <f>IF($N55="","",INDEX('반배정'!O$7:O$86,$N55))</f>
         <v/>
       </c>
@@ -21252,11 +21267,11 @@
         <f>IF($N56="","",INDEX('반배정'!H$7:H$86,$N56))</f>
         <v/>
       </c>
-      <c r="H56" s="36">
+      <c r="H56" s="37">
         <f>IF($N56="","",INDEX('반배정'!I$7:I$86,$N56))</f>
         <v/>
       </c>
-      <c r="I56" s="26">
+      <c r="I56" s="27">
         <f>IF($N56="","",INDEX('반배정'!O$7:O$86,$N56))</f>
         <v/>
       </c>
@@ -21310,11 +21325,11 @@
         <f>IF($N57="","",INDEX('반배정'!H$7:H$86,$N57))</f>
         <v/>
       </c>
-      <c r="H57" s="36">
+      <c r="H57" s="37">
         <f>IF($N57="","",INDEX('반배정'!I$7:I$86,$N57))</f>
         <v/>
       </c>
-      <c r="I57" s="26">
+      <c r="I57" s="27">
         <f>IF($N57="","",INDEX('반배정'!O$7:O$86,$N57))</f>
         <v/>
       </c>
@@ -21368,11 +21383,11 @@
         <f>IF($N58="","",INDEX('반배정'!H$7:H$86,$N58))</f>
         <v/>
       </c>
-      <c r="H58" s="36">
+      <c r="H58" s="37">
         <f>IF($N58="","",INDEX('반배정'!I$7:I$86,$N58))</f>
         <v/>
       </c>
-      <c r="I58" s="26">
+      <c r="I58" s="27">
         <f>IF($N58="","",INDEX('반배정'!O$7:O$86,$N58))</f>
         <v/>
       </c>
@@ -21426,11 +21441,11 @@
         <f>IF($N59="","",INDEX('반배정'!H$7:H$86,$N59))</f>
         <v/>
       </c>
-      <c r="H59" s="36">
+      <c r="H59" s="37">
         <f>IF($N59="","",INDEX('반배정'!I$7:I$86,$N59))</f>
         <v/>
       </c>
-      <c r="I59" s="26">
+      <c r="I59" s="27">
         <f>IF($N59="","",INDEX('반배정'!O$7:O$86,$N59))</f>
         <v/>
       </c>
@@ -21484,11 +21499,11 @@
         <f>IF($N60="","",INDEX('반배정'!H$7:H$86,$N60))</f>
         <v/>
       </c>
-      <c r="H60" s="36">
+      <c r="H60" s="37">
         <f>IF($N60="","",INDEX('반배정'!I$7:I$86,$N60))</f>
         <v/>
       </c>
-      <c r="I60" s="26">
+      <c r="I60" s="27">
         <f>IF($N60="","",INDEX('반배정'!O$7:O$86,$N60))</f>
         <v/>
       </c>
@@ -21542,11 +21557,11 @@
         <f>IF($N61="","",INDEX('반배정'!H$7:H$86,$N61))</f>
         <v/>
       </c>
-      <c r="H61" s="36">
+      <c r="H61" s="37">
         <f>IF($N61="","",INDEX('반배정'!I$7:I$86,$N61))</f>
         <v/>
       </c>
-      <c r="I61" s="26">
+      <c r="I61" s="27">
         <f>IF($N61="","",INDEX('반배정'!O$7:O$86,$N61))</f>
         <v/>
       </c>
@@ -21600,11 +21615,11 @@
         <f>IF($N62="","",INDEX('반배정'!H$7:H$86,$N62))</f>
         <v/>
       </c>
-      <c r="H62" s="36">
+      <c r="H62" s="37">
         <f>IF($N62="","",INDEX('반배정'!I$7:I$86,$N62))</f>
         <v/>
       </c>
-      <c r="I62" s="26">
+      <c r="I62" s="27">
         <f>IF($N62="","",INDEX('반배정'!O$7:O$86,$N62))</f>
         <v/>
       </c>
@@ -21658,11 +21673,11 @@
         <f>IF($N63="","",INDEX('반배정'!H$7:H$86,$N63))</f>
         <v/>
       </c>
-      <c r="H63" s="36">
+      <c r="H63" s="37">
         <f>IF($N63="","",INDEX('반배정'!I$7:I$86,$N63))</f>
         <v/>
       </c>
-      <c r="I63" s="26">
+      <c r="I63" s="27">
         <f>IF($N63="","",INDEX('반배정'!O$7:O$86,$N63))</f>
         <v/>
       </c>
@@ -21716,11 +21731,11 @@
         <f>IF($N64="","",INDEX('반배정'!H$7:H$86,$N64))</f>
         <v/>
       </c>
-      <c r="H64" s="36">
+      <c r="H64" s="37">
         <f>IF($N64="","",INDEX('반배정'!I$7:I$86,$N64))</f>
         <v/>
       </c>
-      <c r="I64" s="26">
+      <c r="I64" s="27">
         <f>IF($N64="","",INDEX('반배정'!O$7:O$86,$N64))</f>
         <v/>
       </c>
@@ -21774,11 +21789,11 @@
         <f>IF($N65="","",INDEX('반배정'!H$7:H$86,$N65))</f>
         <v/>
       </c>
-      <c r="H65" s="36">
+      <c r="H65" s="37">
         <f>IF($N65="","",INDEX('반배정'!I$7:I$86,$N65))</f>
         <v/>
       </c>
-      <c r="I65" s="26">
+      <c r="I65" s="27">
         <f>IF($N65="","",INDEX('반배정'!O$7:O$86,$N65))</f>
         <v/>
       </c>
@@ -21832,11 +21847,11 @@
         <f>IF($N66="","",INDEX('반배정'!H$7:H$86,$N66))</f>
         <v/>
       </c>
-      <c r="H66" s="36">
+      <c r="H66" s="37">
         <f>IF($N66="","",INDEX('반배정'!I$7:I$86,$N66))</f>
         <v/>
       </c>
-      <c r="I66" s="26">
+      <c r="I66" s="27">
         <f>IF($N66="","",INDEX('반배정'!O$7:O$86,$N66))</f>
         <v/>
       </c>
@@ -21890,11 +21905,11 @@
         <f>IF($N67="","",INDEX('반배정'!H$7:H$86,$N67))</f>
         <v/>
       </c>
-      <c r="H67" s="36">
+      <c r="H67" s="37">
         <f>IF($N67="","",INDEX('반배정'!I$7:I$86,$N67))</f>
         <v/>
       </c>
-      <c r="I67" s="26">
+      <c r="I67" s="27">
         <f>IF($N67="","",INDEX('반배정'!O$7:O$86,$N67))</f>
         <v/>
       </c>
@@ -21948,11 +21963,11 @@
         <f>IF($N68="","",INDEX('반배정'!H$7:H$86,$N68))</f>
         <v/>
       </c>
-      <c r="H68" s="36">
+      <c r="H68" s="37">
         <f>IF($N68="","",INDEX('반배정'!I$7:I$86,$N68))</f>
         <v/>
       </c>
-      <c r="I68" s="26">
+      <c r="I68" s="27">
         <f>IF($N68="","",INDEX('반배정'!O$7:O$86,$N68))</f>
         <v/>
       </c>
@@ -22006,11 +22021,11 @@
         <f>IF($N69="","",INDEX('반배정'!H$7:H$86,$N69))</f>
         <v/>
       </c>
-      <c r="H69" s="36">
+      <c r="H69" s="37">
         <f>IF($N69="","",INDEX('반배정'!I$7:I$86,$N69))</f>
         <v/>
       </c>
-      <c r="I69" s="26">
+      <c r="I69" s="27">
         <f>IF($N69="","",INDEX('반배정'!O$7:O$86,$N69))</f>
         <v/>
       </c>
@@ -22064,11 +22079,11 @@
         <f>IF($N70="","",INDEX('반배정'!H$7:H$86,$N70))</f>
         <v/>
       </c>
-      <c r="H70" s="36">
+      <c r="H70" s="37">
         <f>IF($N70="","",INDEX('반배정'!I$7:I$86,$N70))</f>
         <v/>
       </c>
-      <c r="I70" s="26">
+      <c r="I70" s="27">
         <f>IF($N70="","",INDEX('반배정'!O$7:O$86,$N70))</f>
         <v/>
       </c>
@@ -22122,11 +22137,11 @@
         <f>IF($N71="","",INDEX('반배정'!H$7:H$86,$N71))</f>
         <v/>
       </c>
-      <c r="H71" s="36">
+      <c r="H71" s="37">
         <f>IF($N71="","",INDEX('반배정'!I$7:I$86,$N71))</f>
         <v/>
       </c>
-      <c r="I71" s="26">
+      <c r="I71" s="27">
         <f>IF($N71="","",INDEX('반배정'!O$7:O$86,$N71))</f>
         <v/>
       </c>
@@ -22180,11 +22195,11 @@
         <f>IF($N72="","",INDEX('반배정'!H$7:H$86,$N72))</f>
         <v/>
       </c>
-      <c r="H72" s="36">
+      <c r="H72" s="37">
         <f>IF($N72="","",INDEX('반배정'!I$7:I$86,$N72))</f>
         <v/>
       </c>
-      <c r="I72" s="26">
+      <c r="I72" s="27">
         <f>IF($N72="","",INDEX('반배정'!O$7:O$86,$N72))</f>
         <v/>
       </c>
@@ -22238,11 +22253,11 @@
         <f>IF($N73="","",INDEX('반배정'!H$7:H$86,$N73))</f>
         <v/>
       </c>
-      <c r="H73" s="36">
+      <c r="H73" s="37">
         <f>IF($N73="","",INDEX('반배정'!I$7:I$86,$N73))</f>
         <v/>
       </c>
-      <c r="I73" s="26">
+      <c r="I73" s="27">
         <f>IF($N73="","",INDEX('반배정'!O$7:O$86,$N73))</f>
         <v/>
       </c>
@@ -22296,11 +22311,11 @@
         <f>IF($N74="","",INDEX('반배정'!H$7:H$86,$N74))</f>
         <v/>
       </c>
-      <c r="H74" s="36">
+      <c r="H74" s="37">
         <f>IF($N74="","",INDEX('반배정'!I$7:I$86,$N74))</f>
         <v/>
       </c>
-      <c r="I74" s="26">
+      <c r="I74" s="27">
         <f>IF($N74="","",INDEX('반배정'!O$7:O$86,$N74))</f>
         <v/>
       </c>
@@ -22354,11 +22369,11 @@
         <f>IF($N75="","",INDEX('반배정'!H$7:H$86,$N75))</f>
         <v/>
       </c>
-      <c r="H75" s="36">
+      <c r="H75" s="37">
         <f>IF($N75="","",INDEX('반배정'!I$7:I$86,$N75))</f>
         <v/>
       </c>
-      <c r="I75" s="26">
+      <c r="I75" s="27">
         <f>IF($N75="","",INDEX('반배정'!O$7:O$86,$N75))</f>
         <v/>
       </c>
@@ -22412,11 +22427,11 @@
         <f>IF($N76="","",INDEX('반배정'!H$7:H$86,$N76))</f>
         <v/>
       </c>
-      <c r="H76" s="36">
+      <c r="H76" s="37">
         <f>IF($N76="","",INDEX('반배정'!I$7:I$86,$N76))</f>
         <v/>
       </c>
-      <c r="I76" s="26">
+      <c r="I76" s="27">
         <f>IF($N76="","",INDEX('반배정'!O$7:O$86,$N76))</f>
         <v/>
       </c>
@@ -22470,11 +22485,11 @@
         <f>IF($N77="","",INDEX('반배정'!H$7:H$86,$N77))</f>
         <v/>
       </c>
-      <c r="H77" s="36">
+      <c r="H77" s="37">
         <f>IF($N77="","",INDEX('반배정'!I$7:I$86,$N77))</f>
         <v/>
       </c>
-      <c r="I77" s="26">
+      <c r="I77" s="27">
         <f>IF($N77="","",INDEX('반배정'!O$7:O$86,$N77))</f>
         <v/>
       </c>
@@ -22528,11 +22543,11 @@
         <f>IF($N78="","",INDEX('반배정'!H$7:H$86,$N78))</f>
         <v/>
       </c>
-      <c r="H78" s="36">
+      <c r="H78" s="37">
         <f>IF($N78="","",INDEX('반배정'!I$7:I$86,$N78))</f>
         <v/>
       </c>
-      <c r="I78" s="26">
+      <c r="I78" s="27">
         <f>IF($N78="","",INDEX('반배정'!O$7:O$86,$N78))</f>
         <v/>
       </c>
@@ -22586,11 +22601,11 @@
         <f>IF($N79="","",INDEX('반배정'!H$7:H$86,$N79))</f>
         <v/>
       </c>
-      <c r="H79" s="36">
+      <c r="H79" s="37">
         <f>IF($N79="","",INDEX('반배정'!I$7:I$86,$N79))</f>
         <v/>
       </c>
-      <c r="I79" s="26">
+      <c r="I79" s="27">
         <f>IF($N79="","",INDEX('반배정'!O$7:O$86,$N79))</f>
         <v/>
       </c>
@@ -22644,11 +22659,11 @@
         <f>IF($N80="","",INDEX('반배정'!H$7:H$86,$N80))</f>
         <v/>
       </c>
-      <c r="H80" s="36">
+      <c r="H80" s="37">
         <f>IF($N80="","",INDEX('반배정'!I$7:I$86,$N80))</f>
         <v/>
       </c>
-      <c r="I80" s="26">
+      <c r="I80" s="27">
         <f>IF($N80="","",INDEX('반배정'!O$7:O$86,$N80))</f>
         <v/>
       </c>
@@ -22702,11 +22717,11 @@
         <f>IF($N81="","",INDEX('반배정'!H$7:H$86,$N81))</f>
         <v/>
       </c>
-      <c r="H81" s="36">
+      <c r="H81" s="37">
         <f>IF($N81="","",INDEX('반배정'!I$7:I$86,$N81))</f>
         <v/>
       </c>
-      <c r="I81" s="26">
+      <c r="I81" s="27">
         <f>IF($N81="","",INDEX('반배정'!O$7:O$86,$N81))</f>
         <v/>
       </c>
@@ -22760,11 +22775,11 @@
         <f>IF($N82="","",INDEX('반배정'!H$7:H$86,$N82))</f>
         <v/>
       </c>
-      <c r="H82" s="36">
+      <c r="H82" s="37">
         <f>IF($N82="","",INDEX('반배정'!I$7:I$86,$N82))</f>
         <v/>
       </c>
-      <c r="I82" s="26">
+      <c r="I82" s="27">
         <f>IF($N82="","",INDEX('반배정'!O$7:O$86,$N82))</f>
         <v/>
       </c>
@@ -22818,11 +22833,11 @@
         <f>IF($N83="","",INDEX('반배정'!H$7:H$86,$N83))</f>
         <v/>
       </c>
-      <c r="H83" s="36">
+      <c r="H83" s="37">
         <f>IF($N83="","",INDEX('반배정'!I$7:I$86,$N83))</f>
         <v/>
       </c>
-      <c r="I83" s="26">
+      <c r="I83" s="27">
         <f>IF($N83="","",INDEX('반배정'!O$7:O$86,$N83))</f>
         <v/>
       </c>
@@ -22876,11 +22891,11 @@
         <f>IF($N84="","",INDEX('반배정'!H$7:H$86,$N84))</f>
         <v/>
       </c>
-      <c r="H84" s="36">
+      <c r="H84" s="37">
         <f>IF($N84="","",INDEX('반배정'!I$7:I$86,$N84))</f>
         <v/>
       </c>
-      <c r="I84" s="26">
+      <c r="I84" s="27">
         <f>IF($N84="","",INDEX('반배정'!O$7:O$86,$N84))</f>
         <v/>
       </c>
@@ -22934,11 +22949,11 @@
         <f>IF($N85="","",INDEX('반배정'!H$7:H$86,$N85))</f>
         <v/>
       </c>
-      <c r="H85" s="36">
+      <c r="H85" s="37">
         <f>IF($N85="","",INDEX('반배정'!I$7:I$86,$N85))</f>
         <v/>
       </c>
-      <c r="I85" s="26">
+      <c r="I85" s="27">
         <f>IF($N85="","",INDEX('반배정'!O$7:O$86,$N85))</f>
         <v/>
       </c>
@@ -22992,11 +23007,11 @@
         <f>IF($N86="","",INDEX('반배정'!H$7:H$86,$N86))</f>
         <v/>
       </c>
-      <c r="H86" s="36">
+      <c r="H86" s="37">
         <f>IF($N86="","",INDEX('반배정'!I$7:I$86,$N86))</f>
         <v/>
       </c>
-      <c r="I86" s="26">
+      <c r="I86" s="27">
         <f>IF($N86="","",INDEX('반배정'!O$7:O$86,$N86))</f>
         <v/>
       </c>
@@ -23090,7 +23105,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>공통수학1</t>
         </is>
@@ -23199,7 +23214,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="39">
         <f>'공수1'!D4</f>
         <v/>
       </c>
@@ -23211,7 +23226,7 @@
         <f>'공수1'!D3</f>
         <v/>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="40">
         <f>IF('공수1'!$D$2="","",'공수1'!$D$2)</f>
         <v/>
       </c>
@@ -23223,47 +23238,47 @@
         <f>IF(F6="","",SUMPRODUCT(('공수1'!$D$7:$D$86='공수1'!$D$2)*('공수1'!$D$7:$D$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I6" s="40">
+      <c r="I6" s="41">
         <f>IF(OR(F6="",G6=0),"",H6/G6)</f>
         <v/>
       </c>
-      <c r="J6" s="41">
+      <c r="J6" s="42">
         <f>IF(F6="","",IFERROR(SUMPRODUCT(('공수1'!$D$7:$D$86='공수1'!$D$2)*('공수1'!$D$7:$D$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K6" s="41">
+      <c r="K6" s="42">
         <f>IF(F6="","",IFERROR(SUMPRODUCT(('공수1'!$D$7:$D$86='공수1'!$D$2)*('공수1'!$D$7:$D$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L6" s="41">
+      <c r="L6" s="42">
         <f>IF(F6="","",IFERROR(SUMPRODUCT(('공수1'!$D$7:$D$86='공수1'!$D$2)*('공수1'!$D$7:$D$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M6" s="42">
+      <c r="M6" s="43">
         <f>IF(OR(J6="",L6=""),"",J6-L6)</f>
         <v/>
       </c>
-      <c r="N6" s="38">
+      <c r="N6" s="39">
         <f>IF(I6="","",IF(AND(M6&lt;&gt;"",M6&lt;0),"역변별·문항검토",IF(I6&gt;=0.9,"매우 쉬움",IF(I6&lt;=0.15,"매우 어려움",IF(AND(M6&lt;&gt;"",M6&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O6" s="38">
+      <c r="O6" s="39">
         <f>IF(G6=0,"",COUNTIF('공수1'!$D$7:$D$86,1))</f>
         <v/>
       </c>
-      <c r="P6" s="38">
+      <c r="P6" s="39">
         <f>IF(G6=0,"",COUNTIF('공수1'!$D$7:$D$86,2))</f>
         <v/>
       </c>
-      <c r="Q6" s="38">
+      <c r="Q6" s="39">
         <f>IF(G6=0,"",COUNTIF('공수1'!$D$7:$D$86,3))</f>
         <v/>
       </c>
-      <c r="R6" s="38">
+      <c r="R6" s="39">
         <f>IF(G6=0,"",COUNTIF('공수1'!$D$7:$D$86,4))</f>
         <v/>
       </c>
-      <c r="S6" s="38">
+      <c r="S6" s="39">
         <f>IF(G6=0,"",COUNTIF('공수1'!$D$7:$D$86,5))</f>
         <v/>
       </c>
@@ -23277,7 +23292,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C7" s="38">
+      <c r="C7" s="39">
         <f>'공수1'!E4</f>
         <v/>
       </c>
@@ -23289,7 +23304,7 @@
         <f>'공수1'!E3</f>
         <v/>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="40">
         <f>IF('공수1'!$E$2="","",'공수1'!$E$2)</f>
         <v/>
       </c>
@@ -23301,47 +23316,47 @@
         <f>IF(F7="","",SUMPRODUCT(('공수1'!$E$7:$E$86='공수1'!$E$2)*('공수1'!$E$7:$E$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I7" s="40">
+      <c r="I7" s="41">
         <f>IF(OR(F7="",G7=0),"",H7/G7)</f>
         <v/>
       </c>
-      <c r="J7" s="41">
+      <c r="J7" s="42">
         <f>IF(F7="","",IFERROR(SUMPRODUCT(('공수1'!$E$7:$E$86='공수1'!$E$2)*('공수1'!$E$7:$E$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K7" s="41">
+      <c r="K7" s="42">
         <f>IF(F7="","",IFERROR(SUMPRODUCT(('공수1'!$E$7:$E$86='공수1'!$E$2)*('공수1'!$E$7:$E$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L7" s="41">
+      <c r="L7" s="42">
         <f>IF(F7="","",IFERROR(SUMPRODUCT(('공수1'!$E$7:$E$86='공수1'!$E$2)*('공수1'!$E$7:$E$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M7" s="42">
+      <c r="M7" s="43">
         <f>IF(OR(J7="",L7=""),"",J7-L7)</f>
         <v/>
       </c>
-      <c r="N7" s="38">
+      <c r="N7" s="39">
         <f>IF(I7="","",IF(AND(M7&lt;&gt;"",M7&lt;0),"역변별·문항검토",IF(I7&gt;=0.9,"매우 쉬움",IF(I7&lt;=0.15,"매우 어려움",IF(AND(M7&lt;&gt;"",M7&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O7" s="38">
+      <c r="O7" s="39">
         <f>IF(G7=0,"",COUNTIF('공수1'!$E$7:$E$86,1))</f>
         <v/>
       </c>
-      <c r="P7" s="38">
+      <c r="P7" s="39">
         <f>IF(G7=0,"",COUNTIF('공수1'!$E$7:$E$86,2))</f>
         <v/>
       </c>
-      <c r="Q7" s="38">
+      <c r="Q7" s="39">
         <f>IF(G7=0,"",COUNTIF('공수1'!$E$7:$E$86,3))</f>
         <v/>
       </c>
-      <c r="R7" s="38">
+      <c r="R7" s="39">
         <f>IF(G7=0,"",COUNTIF('공수1'!$E$7:$E$86,4))</f>
         <v/>
       </c>
-      <c r="S7" s="38">
+      <c r="S7" s="39">
         <f>IF(G7=0,"",COUNTIF('공수1'!$E$7:$E$86,5))</f>
         <v/>
       </c>
@@ -23355,7 +23370,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="39">
         <f>'공수1'!F4</f>
         <v/>
       </c>
@@ -23367,7 +23382,7 @@
         <f>'공수1'!F3</f>
         <v/>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="40">
         <f>IF('공수1'!$F$2="","",'공수1'!$F$2)</f>
         <v/>
       </c>
@@ -23379,47 +23394,47 @@
         <f>IF(F8="","",SUMPRODUCT(('공수1'!$F$7:$F$86='공수1'!$F$2)*('공수1'!$F$7:$F$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I8" s="40">
+      <c r="I8" s="41">
         <f>IF(OR(F8="",G8=0),"",H8/G8)</f>
         <v/>
       </c>
-      <c r="J8" s="41">
+      <c r="J8" s="42">
         <f>IF(F8="","",IFERROR(SUMPRODUCT(('공수1'!$F$7:$F$86='공수1'!$F$2)*('공수1'!$F$7:$F$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K8" s="41">
+      <c r="K8" s="42">
         <f>IF(F8="","",IFERROR(SUMPRODUCT(('공수1'!$F$7:$F$86='공수1'!$F$2)*('공수1'!$F$7:$F$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L8" s="41">
+      <c r="L8" s="42">
         <f>IF(F8="","",IFERROR(SUMPRODUCT(('공수1'!$F$7:$F$86='공수1'!$F$2)*('공수1'!$F$7:$F$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M8" s="42">
+      <c r="M8" s="43">
         <f>IF(OR(J8="",L8=""),"",J8-L8)</f>
         <v/>
       </c>
-      <c r="N8" s="38">
+      <c r="N8" s="39">
         <f>IF(I8="","",IF(AND(M8&lt;&gt;"",M8&lt;0),"역변별·문항검토",IF(I8&gt;=0.9,"매우 쉬움",IF(I8&lt;=0.15,"매우 어려움",IF(AND(M8&lt;&gt;"",M8&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O8" s="38">
+      <c r="O8" s="39">
         <f>IF(G8=0,"",COUNTIF('공수1'!$F$7:$F$86,1))</f>
         <v/>
       </c>
-      <c r="P8" s="38">
+      <c r="P8" s="39">
         <f>IF(G8=0,"",COUNTIF('공수1'!$F$7:$F$86,2))</f>
         <v/>
       </c>
-      <c r="Q8" s="38">
+      <c r="Q8" s="39">
         <f>IF(G8=0,"",COUNTIF('공수1'!$F$7:$F$86,3))</f>
         <v/>
       </c>
-      <c r="R8" s="38">
+      <c r="R8" s="39">
         <f>IF(G8=0,"",COUNTIF('공수1'!$F$7:$F$86,4))</f>
         <v/>
       </c>
-      <c r="S8" s="38">
+      <c r="S8" s="39">
         <f>IF(G8=0,"",COUNTIF('공수1'!$F$7:$F$86,5))</f>
         <v/>
       </c>
@@ -23433,7 +23448,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="39">
         <f>'공수1'!G4</f>
         <v/>
       </c>
@@ -23445,7 +23460,7 @@
         <f>'공수1'!G3</f>
         <v/>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="40">
         <f>IF('공수1'!$G$2="","",'공수1'!$G$2)</f>
         <v/>
       </c>
@@ -23457,47 +23472,47 @@
         <f>IF(F9="","",SUMPRODUCT(('공수1'!$G$7:$G$86='공수1'!$G$2)*('공수1'!$G$7:$G$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I9" s="40">
+      <c r="I9" s="41">
         <f>IF(OR(F9="",G9=0),"",H9/G9)</f>
         <v/>
       </c>
-      <c r="J9" s="41">
+      <c r="J9" s="42">
         <f>IF(F9="","",IFERROR(SUMPRODUCT(('공수1'!$G$7:$G$86='공수1'!$G$2)*('공수1'!$G$7:$G$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K9" s="41">
+      <c r="K9" s="42">
         <f>IF(F9="","",IFERROR(SUMPRODUCT(('공수1'!$G$7:$G$86='공수1'!$G$2)*('공수1'!$G$7:$G$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L9" s="41">
+      <c r="L9" s="42">
         <f>IF(F9="","",IFERROR(SUMPRODUCT(('공수1'!$G$7:$G$86='공수1'!$G$2)*('공수1'!$G$7:$G$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M9" s="42">
+      <c r="M9" s="43">
         <f>IF(OR(J9="",L9=""),"",J9-L9)</f>
         <v/>
       </c>
-      <c r="N9" s="38">
+      <c r="N9" s="39">
         <f>IF(I9="","",IF(AND(M9&lt;&gt;"",M9&lt;0),"역변별·문항검토",IF(I9&gt;=0.9,"매우 쉬움",IF(I9&lt;=0.15,"매우 어려움",IF(AND(M9&lt;&gt;"",M9&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O9" s="38">
+      <c r="O9" s="39">
         <f>IF(G9=0,"",COUNTIF('공수1'!$G$7:$G$86,1))</f>
         <v/>
       </c>
-      <c r="P9" s="38">
+      <c r="P9" s="39">
         <f>IF(G9=0,"",COUNTIF('공수1'!$G$7:$G$86,2))</f>
         <v/>
       </c>
-      <c r="Q9" s="38">
+      <c r="Q9" s="39">
         <f>IF(G9=0,"",COUNTIF('공수1'!$G$7:$G$86,3))</f>
         <v/>
       </c>
-      <c r="R9" s="38">
+      <c r="R9" s="39">
         <f>IF(G9=0,"",COUNTIF('공수1'!$G$7:$G$86,4))</f>
         <v/>
       </c>
-      <c r="S9" s="38">
+      <c r="S9" s="39">
         <f>IF(G9=0,"",COUNTIF('공수1'!$G$7:$G$86,5))</f>
         <v/>
       </c>
@@ -23511,7 +23526,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="39">
         <f>'공수1'!H4</f>
         <v/>
       </c>
@@ -23523,7 +23538,7 @@
         <f>'공수1'!H3</f>
         <v/>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="40">
         <f>IF('공수1'!$H$2="","",'공수1'!$H$2)</f>
         <v/>
       </c>
@@ -23535,47 +23550,47 @@
         <f>IF(F10="","",SUMPRODUCT(('공수1'!$H$7:$H$86='공수1'!$H$2)*('공수1'!$H$7:$H$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I10" s="40">
+      <c r="I10" s="41">
         <f>IF(OR(F10="",G10=0),"",H10/G10)</f>
         <v/>
       </c>
-      <c r="J10" s="41">
+      <c r="J10" s="42">
         <f>IF(F10="","",IFERROR(SUMPRODUCT(('공수1'!$H$7:$H$86='공수1'!$H$2)*('공수1'!$H$7:$H$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K10" s="41">
+      <c r="K10" s="42">
         <f>IF(F10="","",IFERROR(SUMPRODUCT(('공수1'!$H$7:$H$86='공수1'!$H$2)*('공수1'!$H$7:$H$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L10" s="41">
+      <c r="L10" s="42">
         <f>IF(F10="","",IFERROR(SUMPRODUCT(('공수1'!$H$7:$H$86='공수1'!$H$2)*('공수1'!$H$7:$H$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M10" s="42">
+      <c r="M10" s="43">
         <f>IF(OR(J10="",L10=""),"",J10-L10)</f>
         <v/>
       </c>
-      <c r="N10" s="38">
+      <c r="N10" s="39">
         <f>IF(I10="","",IF(AND(M10&lt;&gt;"",M10&lt;0),"역변별·문항검토",IF(I10&gt;=0.9,"매우 쉬움",IF(I10&lt;=0.15,"매우 어려움",IF(AND(M10&lt;&gt;"",M10&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O10" s="38">
+      <c r="O10" s="39">
         <f>IF(G10=0,"",COUNTIF('공수1'!$H$7:$H$86,1))</f>
         <v/>
       </c>
-      <c r="P10" s="38">
+      <c r="P10" s="39">
         <f>IF(G10=0,"",COUNTIF('공수1'!$H$7:$H$86,2))</f>
         <v/>
       </c>
-      <c r="Q10" s="38">
+      <c r="Q10" s="39">
         <f>IF(G10=0,"",COUNTIF('공수1'!$H$7:$H$86,3))</f>
         <v/>
       </c>
-      <c r="R10" s="38">
+      <c r="R10" s="39">
         <f>IF(G10=0,"",COUNTIF('공수1'!$H$7:$H$86,4))</f>
         <v/>
       </c>
-      <c r="S10" s="38">
+      <c r="S10" s="39">
         <f>IF(G10=0,"",COUNTIF('공수1'!$H$7:$H$86,5))</f>
         <v/>
       </c>
@@ -23589,7 +23604,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="39">
         <f>'공수1'!I4</f>
         <v/>
       </c>
@@ -23601,7 +23616,7 @@
         <f>'공수1'!I3</f>
         <v/>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="40">
         <f>IF('공수1'!$I$2="","",'공수1'!$I$2)</f>
         <v/>
       </c>
@@ -23613,47 +23628,47 @@
         <f>IF(F11="","",SUMPRODUCT(('공수1'!$I$7:$I$86='공수1'!$I$2)*('공수1'!$I$7:$I$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I11" s="40">
+      <c r="I11" s="41">
         <f>IF(OR(F11="",G11=0),"",H11/G11)</f>
         <v/>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="42">
         <f>IF(F11="","",IFERROR(SUMPRODUCT(('공수1'!$I$7:$I$86='공수1'!$I$2)*('공수1'!$I$7:$I$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K11" s="41">
+      <c r="K11" s="42">
         <f>IF(F11="","",IFERROR(SUMPRODUCT(('공수1'!$I$7:$I$86='공수1'!$I$2)*('공수1'!$I$7:$I$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L11" s="41">
+      <c r="L11" s="42">
         <f>IF(F11="","",IFERROR(SUMPRODUCT(('공수1'!$I$7:$I$86='공수1'!$I$2)*('공수1'!$I$7:$I$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M11" s="42">
+      <c r="M11" s="43">
         <f>IF(OR(J11="",L11=""),"",J11-L11)</f>
         <v/>
       </c>
-      <c r="N11" s="38">
+      <c r="N11" s="39">
         <f>IF(I11="","",IF(AND(M11&lt;&gt;"",M11&lt;0),"역변별·문항검토",IF(I11&gt;=0.9,"매우 쉬움",IF(I11&lt;=0.15,"매우 어려움",IF(AND(M11&lt;&gt;"",M11&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O11" s="38">
+      <c r="O11" s="39">
         <f>IF(G11=0,"",COUNTIF('공수1'!$I$7:$I$86,1))</f>
         <v/>
       </c>
-      <c r="P11" s="38">
+      <c r="P11" s="39">
         <f>IF(G11=0,"",COUNTIF('공수1'!$I$7:$I$86,2))</f>
         <v/>
       </c>
-      <c r="Q11" s="38">
+      <c r="Q11" s="39">
         <f>IF(G11=0,"",COUNTIF('공수1'!$I$7:$I$86,3))</f>
         <v/>
       </c>
-      <c r="R11" s="38">
+      <c r="R11" s="39">
         <f>IF(G11=0,"",COUNTIF('공수1'!$I$7:$I$86,4))</f>
         <v/>
       </c>
-      <c r="S11" s="38">
+      <c r="S11" s="39">
         <f>IF(G11=0,"",COUNTIF('공수1'!$I$7:$I$86,5))</f>
         <v/>
       </c>
@@ -23667,7 +23682,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="39">
         <f>'공수1'!J4</f>
         <v/>
       </c>
@@ -23679,7 +23694,7 @@
         <f>'공수1'!J3</f>
         <v/>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="40">
         <f>IF('공수1'!$J$2="","",'공수1'!$J$2)</f>
         <v/>
       </c>
@@ -23691,47 +23706,47 @@
         <f>IF(F12="","",SUMPRODUCT(('공수1'!$J$7:$J$86='공수1'!$J$2)*('공수1'!$J$7:$J$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I12" s="40">
+      <c r="I12" s="41">
         <f>IF(OR(F12="",G12=0),"",H12/G12)</f>
         <v/>
       </c>
-      <c r="J12" s="41">
+      <c r="J12" s="42">
         <f>IF(F12="","",IFERROR(SUMPRODUCT(('공수1'!$J$7:$J$86='공수1'!$J$2)*('공수1'!$J$7:$J$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K12" s="41">
+      <c r="K12" s="42">
         <f>IF(F12="","",IFERROR(SUMPRODUCT(('공수1'!$J$7:$J$86='공수1'!$J$2)*('공수1'!$J$7:$J$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L12" s="41">
+      <c r="L12" s="42">
         <f>IF(F12="","",IFERROR(SUMPRODUCT(('공수1'!$J$7:$J$86='공수1'!$J$2)*('공수1'!$J$7:$J$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M12" s="42">
+      <c r="M12" s="43">
         <f>IF(OR(J12="",L12=""),"",J12-L12)</f>
         <v/>
       </c>
-      <c r="N12" s="38">
+      <c r="N12" s="39">
         <f>IF(I12="","",IF(AND(M12&lt;&gt;"",M12&lt;0),"역변별·문항검토",IF(I12&gt;=0.9,"매우 쉬움",IF(I12&lt;=0.15,"매우 어려움",IF(AND(M12&lt;&gt;"",M12&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O12" s="38">
+      <c r="O12" s="39">
         <f>IF(G12=0,"",COUNTIF('공수1'!$J$7:$J$86,1))</f>
         <v/>
       </c>
-      <c r="P12" s="38">
+      <c r="P12" s="39">
         <f>IF(G12=0,"",COUNTIF('공수1'!$J$7:$J$86,2))</f>
         <v/>
       </c>
-      <c r="Q12" s="38">
+      <c r="Q12" s="39">
         <f>IF(G12=0,"",COUNTIF('공수1'!$J$7:$J$86,3))</f>
         <v/>
       </c>
-      <c r="R12" s="38">
+      <c r="R12" s="39">
         <f>IF(G12=0,"",COUNTIF('공수1'!$J$7:$J$86,4))</f>
         <v/>
       </c>
-      <c r="S12" s="38">
+      <c r="S12" s="39">
         <f>IF(G12=0,"",COUNTIF('공수1'!$J$7:$J$86,5))</f>
         <v/>
       </c>
@@ -23745,7 +23760,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C13" s="38">
+      <c r="C13" s="39">
         <f>'공수1'!K4</f>
         <v/>
       </c>
@@ -23757,7 +23772,7 @@
         <f>'공수1'!K3</f>
         <v/>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="40">
         <f>IF('공수1'!$K$2="","",'공수1'!$K$2)</f>
         <v/>
       </c>
@@ -23769,47 +23784,47 @@
         <f>IF(F13="","",SUMPRODUCT(('공수1'!$K$7:$K$86='공수1'!$K$2)*('공수1'!$K$7:$K$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I13" s="40">
+      <c r="I13" s="41">
         <f>IF(OR(F13="",G13=0),"",H13/G13)</f>
         <v/>
       </c>
-      <c r="J13" s="41">
+      <c r="J13" s="42">
         <f>IF(F13="","",IFERROR(SUMPRODUCT(('공수1'!$K$7:$K$86='공수1'!$K$2)*('공수1'!$K$7:$K$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K13" s="41">
+      <c r="K13" s="42">
         <f>IF(F13="","",IFERROR(SUMPRODUCT(('공수1'!$K$7:$K$86='공수1'!$K$2)*('공수1'!$K$7:$K$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L13" s="41">
+      <c r="L13" s="42">
         <f>IF(F13="","",IFERROR(SUMPRODUCT(('공수1'!$K$7:$K$86='공수1'!$K$2)*('공수1'!$K$7:$K$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M13" s="42">
+      <c r="M13" s="43">
         <f>IF(OR(J13="",L13=""),"",J13-L13)</f>
         <v/>
       </c>
-      <c r="N13" s="38">
+      <c r="N13" s="39">
         <f>IF(I13="","",IF(AND(M13&lt;&gt;"",M13&lt;0),"역변별·문항검토",IF(I13&gt;=0.9,"매우 쉬움",IF(I13&lt;=0.15,"매우 어려움",IF(AND(M13&lt;&gt;"",M13&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O13" s="38">
+      <c r="O13" s="39">
         <f>IF(G13=0,"",COUNTIF('공수1'!$K$7:$K$86,1))</f>
         <v/>
       </c>
-      <c r="P13" s="38">
+      <c r="P13" s="39">
         <f>IF(G13=0,"",COUNTIF('공수1'!$K$7:$K$86,2))</f>
         <v/>
       </c>
-      <c r="Q13" s="38">
+      <c r="Q13" s="39">
         <f>IF(G13=0,"",COUNTIF('공수1'!$K$7:$K$86,3))</f>
         <v/>
       </c>
-      <c r="R13" s="38">
+      <c r="R13" s="39">
         <f>IF(G13=0,"",COUNTIF('공수1'!$K$7:$K$86,4))</f>
         <v/>
       </c>
-      <c r="S13" s="38">
+      <c r="S13" s="39">
         <f>IF(G13=0,"",COUNTIF('공수1'!$K$7:$K$86,5))</f>
         <v/>
       </c>
@@ -23823,7 +23838,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C14" s="38">
+      <c r="C14" s="39">
         <f>'공수1'!L4</f>
         <v/>
       </c>
@@ -23835,7 +23850,7 @@
         <f>'공수1'!L3</f>
         <v/>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="40">
         <f>IF('공수1'!$L$2="","",'공수1'!$L$2)</f>
         <v/>
       </c>
@@ -23847,47 +23862,47 @@
         <f>IF(F14="","",SUMPRODUCT(('공수1'!$L$7:$L$86='공수1'!$L$2)*('공수1'!$L$7:$L$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I14" s="40">
+      <c r="I14" s="41">
         <f>IF(OR(F14="",G14=0),"",H14/G14)</f>
         <v/>
       </c>
-      <c r="J14" s="41">
+      <c r="J14" s="42">
         <f>IF(F14="","",IFERROR(SUMPRODUCT(('공수1'!$L$7:$L$86='공수1'!$L$2)*('공수1'!$L$7:$L$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K14" s="41">
+      <c r="K14" s="42">
         <f>IF(F14="","",IFERROR(SUMPRODUCT(('공수1'!$L$7:$L$86='공수1'!$L$2)*('공수1'!$L$7:$L$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L14" s="41">
+      <c r="L14" s="42">
         <f>IF(F14="","",IFERROR(SUMPRODUCT(('공수1'!$L$7:$L$86='공수1'!$L$2)*('공수1'!$L$7:$L$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M14" s="42">
+      <c r="M14" s="43">
         <f>IF(OR(J14="",L14=""),"",J14-L14)</f>
         <v/>
       </c>
-      <c r="N14" s="38">
+      <c r="N14" s="39">
         <f>IF(I14="","",IF(AND(M14&lt;&gt;"",M14&lt;0),"역변별·문항검토",IF(I14&gt;=0.9,"매우 쉬움",IF(I14&lt;=0.15,"매우 어려움",IF(AND(M14&lt;&gt;"",M14&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O14" s="38">
+      <c r="O14" s="39">
         <f>IF(G14=0,"",COUNTIF('공수1'!$L$7:$L$86,1))</f>
         <v/>
       </c>
-      <c r="P14" s="38">
+      <c r="P14" s="39">
         <f>IF(G14=0,"",COUNTIF('공수1'!$L$7:$L$86,2))</f>
         <v/>
       </c>
-      <c r="Q14" s="38">
+      <c r="Q14" s="39">
         <f>IF(G14=0,"",COUNTIF('공수1'!$L$7:$L$86,3))</f>
         <v/>
       </c>
-      <c r="R14" s="38">
+      <c r="R14" s="39">
         <f>IF(G14=0,"",COUNTIF('공수1'!$L$7:$L$86,4))</f>
         <v/>
       </c>
-      <c r="S14" s="38">
+      <c r="S14" s="39">
         <f>IF(G14=0,"",COUNTIF('공수1'!$L$7:$L$86,5))</f>
         <v/>
       </c>
@@ -23901,7 +23916,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="39">
         <f>'공수1'!M4</f>
         <v/>
       </c>
@@ -23913,7 +23928,7 @@
         <f>'공수1'!M3</f>
         <v/>
       </c>
-      <c r="F15" s="39">
+      <c r="F15" s="40">
         <f>IF('공수1'!$M$2="","",'공수1'!$M$2)</f>
         <v/>
       </c>
@@ -23925,47 +23940,47 @@
         <f>IF(F15="","",SUMPRODUCT(('공수1'!$M$7:$M$86='공수1'!$M$2)*('공수1'!$M$7:$M$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I15" s="40">
+      <c r="I15" s="41">
         <f>IF(OR(F15="",G15=0),"",H15/G15)</f>
         <v/>
       </c>
-      <c r="J15" s="41">
+      <c r="J15" s="42">
         <f>IF(F15="","",IFERROR(SUMPRODUCT(('공수1'!$M$7:$M$86='공수1'!$M$2)*('공수1'!$M$7:$M$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K15" s="41">
+      <c r="K15" s="42">
         <f>IF(F15="","",IFERROR(SUMPRODUCT(('공수1'!$M$7:$M$86='공수1'!$M$2)*('공수1'!$M$7:$M$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L15" s="41">
+      <c r="L15" s="42">
         <f>IF(F15="","",IFERROR(SUMPRODUCT(('공수1'!$M$7:$M$86='공수1'!$M$2)*('공수1'!$M$7:$M$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M15" s="42">
+      <c r="M15" s="43">
         <f>IF(OR(J15="",L15=""),"",J15-L15)</f>
         <v/>
       </c>
-      <c r="N15" s="38">
+      <c r="N15" s="39">
         <f>IF(I15="","",IF(AND(M15&lt;&gt;"",M15&lt;0),"역변별·문항검토",IF(I15&gt;=0.9,"매우 쉬움",IF(I15&lt;=0.15,"매우 어려움",IF(AND(M15&lt;&gt;"",M15&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O15" s="38">
+      <c r="O15" s="39">
         <f>IF(G15=0,"",COUNTIF('공수1'!$M$7:$M$86,1))</f>
         <v/>
       </c>
-      <c r="P15" s="38">
+      <c r="P15" s="39">
         <f>IF(G15=0,"",COUNTIF('공수1'!$M$7:$M$86,2))</f>
         <v/>
       </c>
-      <c r="Q15" s="38">
+      <c r="Q15" s="39">
         <f>IF(G15=0,"",COUNTIF('공수1'!$M$7:$M$86,3))</f>
         <v/>
       </c>
-      <c r="R15" s="38">
+      <c r="R15" s="39">
         <f>IF(G15=0,"",COUNTIF('공수1'!$M$7:$M$86,4))</f>
         <v/>
       </c>
-      <c r="S15" s="38">
+      <c r="S15" s="39">
         <f>IF(G15=0,"",COUNTIF('공수1'!$M$7:$M$86,5))</f>
         <v/>
       </c>
@@ -23979,7 +23994,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="39">
         <f>'공수1'!N4</f>
         <v/>
       </c>
@@ -23991,7 +24006,7 @@
         <f>'공수1'!N3</f>
         <v/>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="40">
         <f>IF('공수1'!$N$2="","",'공수1'!$N$2)</f>
         <v/>
       </c>
@@ -24003,47 +24018,47 @@
         <f>IF(F16="","",SUMPRODUCT(('공수1'!$N$7:$N$86='공수1'!$N$2)*('공수1'!$N$7:$N$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I16" s="40">
+      <c r="I16" s="41">
         <f>IF(OR(F16="",G16=0),"",H16/G16)</f>
         <v/>
       </c>
-      <c r="J16" s="41">
+      <c r="J16" s="42">
         <f>IF(F16="","",IFERROR(SUMPRODUCT(('공수1'!$N$7:$N$86='공수1'!$N$2)*('공수1'!$N$7:$N$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K16" s="41">
+      <c r="K16" s="42">
         <f>IF(F16="","",IFERROR(SUMPRODUCT(('공수1'!$N$7:$N$86='공수1'!$N$2)*('공수1'!$N$7:$N$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L16" s="41">
+      <c r="L16" s="42">
         <f>IF(F16="","",IFERROR(SUMPRODUCT(('공수1'!$N$7:$N$86='공수1'!$N$2)*('공수1'!$N$7:$N$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M16" s="42">
+      <c r="M16" s="43">
         <f>IF(OR(J16="",L16=""),"",J16-L16)</f>
         <v/>
       </c>
-      <c r="N16" s="38">
+      <c r="N16" s="39">
         <f>IF(I16="","",IF(AND(M16&lt;&gt;"",M16&lt;0),"역변별·문항검토",IF(I16&gt;=0.9,"매우 쉬움",IF(I16&lt;=0.15,"매우 어려움",IF(AND(M16&lt;&gt;"",M16&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O16" s="38">
+      <c r="O16" s="39">
         <f>IF(G16=0,"",COUNTIF('공수1'!$N$7:$N$86,1))</f>
         <v/>
       </c>
-      <c r="P16" s="38">
+      <c r="P16" s="39">
         <f>IF(G16=0,"",COUNTIF('공수1'!$N$7:$N$86,2))</f>
         <v/>
       </c>
-      <c r="Q16" s="38">
+      <c r="Q16" s="39">
         <f>IF(G16=0,"",COUNTIF('공수1'!$N$7:$N$86,3))</f>
         <v/>
       </c>
-      <c r="R16" s="38">
+      <c r="R16" s="39">
         <f>IF(G16=0,"",COUNTIF('공수1'!$N$7:$N$86,4))</f>
         <v/>
       </c>
-      <c r="S16" s="38">
+      <c r="S16" s="39">
         <f>IF(G16=0,"",COUNTIF('공수1'!$N$7:$N$86,5))</f>
         <v/>
       </c>
@@ -24057,7 +24072,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="39">
         <f>'공수1'!O4</f>
         <v/>
       </c>
@@ -24069,7 +24084,7 @@
         <f>'공수1'!O3</f>
         <v/>
       </c>
-      <c r="F17" s="39">
+      <c r="F17" s="40">
         <f>IF('공수1'!$O$2="","",'공수1'!$O$2)</f>
         <v/>
       </c>
@@ -24081,47 +24096,47 @@
         <f>IF(F17="","",SUMPRODUCT(('공수1'!$O$7:$O$86='공수1'!$O$2)*('공수1'!$O$7:$O$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I17" s="40">
+      <c r="I17" s="41">
         <f>IF(OR(F17="",G17=0),"",H17/G17)</f>
         <v/>
       </c>
-      <c r="J17" s="41">
+      <c r="J17" s="42">
         <f>IF(F17="","",IFERROR(SUMPRODUCT(('공수1'!$O$7:$O$86='공수1'!$O$2)*('공수1'!$O$7:$O$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K17" s="41">
+      <c r="K17" s="42">
         <f>IF(F17="","",IFERROR(SUMPRODUCT(('공수1'!$O$7:$O$86='공수1'!$O$2)*('공수1'!$O$7:$O$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L17" s="41">
+      <c r="L17" s="42">
         <f>IF(F17="","",IFERROR(SUMPRODUCT(('공수1'!$O$7:$O$86='공수1'!$O$2)*('공수1'!$O$7:$O$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M17" s="42">
+      <c r="M17" s="43">
         <f>IF(OR(J17="",L17=""),"",J17-L17)</f>
         <v/>
       </c>
-      <c r="N17" s="38">
+      <c r="N17" s="39">
         <f>IF(I17="","",IF(AND(M17&lt;&gt;"",M17&lt;0),"역변별·문항검토",IF(I17&gt;=0.9,"매우 쉬움",IF(I17&lt;=0.15,"매우 어려움",IF(AND(M17&lt;&gt;"",M17&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O17" s="38">
+      <c r="O17" s="39">
         <f>IF(G17=0,"",COUNTIF('공수1'!$O$7:$O$86,1))</f>
         <v/>
       </c>
-      <c r="P17" s="38">
+      <c r="P17" s="39">
         <f>IF(G17=0,"",COUNTIF('공수1'!$O$7:$O$86,2))</f>
         <v/>
       </c>
-      <c r="Q17" s="38">
+      <c r="Q17" s="39">
         <f>IF(G17=0,"",COUNTIF('공수1'!$O$7:$O$86,3))</f>
         <v/>
       </c>
-      <c r="R17" s="38">
+      <c r="R17" s="39">
         <f>IF(G17=0,"",COUNTIF('공수1'!$O$7:$O$86,4))</f>
         <v/>
       </c>
-      <c r="S17" s="38">
+      <c r="S17" s="39">
         <f>IF(G17=0,"",COUNTIF('공수1'!$O$7:$O$86,5))</f>
         <v/>
       </c>
@@ -24135,7 +24150,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C18" s="38">
+      <c r="C18" s="39">
         <f>'공수1'!P4</f>
         <v/>
       </c>
@@ -24147,7 +24162,7 @@
         <f>'공수1'!P3</f>
         <v/>
       </c>
-      <c r="F18" s="39">
+      <c r="F18" s="40">
         <f>IF('공수1'!$P$2="","",'공수1'!$P$2)</f>
         <v/>
       </c>
@@ -24159,47 +24174,47 @@
         <f>IF(F18="","",SUMPRODUCT(('공수1'!$P$7:$P$86='공수1'!$P$2)*('공수1'!$P$7:$P$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I18" s="40">
+      <c r="I18" s="41">
         <f>IF(OR(F18="",G18=0),"",H18/G18)</f>
         <v/>
       </c>
-      <c r="J18" s="41">
+      <c r="J18" s="42">
         <f>IF(F18="","",IFERROR(SUMPRODUCT(('공수1'!$P$7:$P$86='공수1'!$P$2)*('공수1'!$P$7:$P$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K18" s="41">
+      <c r="K18" s="42">
         <f>IF(F18="","",IFERROR(SUMPRODUCT(('공수1'!$P$7:$P$86='공수1'!$P$2)*('공수1'!$P$7:$P$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L18" s="41">
+      <c r="L18" s="42">
         <f>IF(F18="","",IFERROR(SUMPRODUCT(('공수1'!$P$7:$P$86='공수1'!$P$2)*('공수1'!$P$7:$P$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M18" s="42">
+      <c r="M18" s="43">
         <f>IF(OR(J18="",L18=""),"",J18-L18)</f>
         <v/>
       </c>
-      <c r="N18" s="38">
+      <c r="N18" s="39">
         <f>IF(I18="","",IF(AND(M18&lt;&gt;"",M18&lt;0),"역변별·문항검토",IF(I18&gt;=0.9,"매우 쉬움",IF(I18&lt;=0.15,"매우 어려움",IF(AND(M18&lt;&gt;"",M18&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O18" s="38">
+      <c r="O18" s="39">
         <f>IF(G18=0,"",COUNTIF('공수1'!$P$7:$P$86,1))</f>
         <v/>
       </c>
-      <c r="P18" s="38">
+      <c r="P18" s="39">
         <f>IF(G18=0,"",COUNTIF('공수1'!$P$7:$P$86,2))</f>
         <v/>
       </c>
-      <c r="Q18" s="38">
+      <c r="Q18" s="39">
         <f>IF(G18=0,"",COUNTIF('공수1'!$P$7:$P$86,3))</f>
         <v/>
       </c>
-      <c r="R18" s="38">
+      <c r="R18" s="39">
         <f>IF(G18=0,"",COUNTIF('공수1'!$P$7:$P$86,4))</f>
         <v/>
       </c>
-      <c r="S18" s="38">
+      <c r="S18" s="39">
         <f>IF(G18=0,"",COUNTIF('공수1'!$P$7:$P$86,5))</f>
         <v/>
       </c>
@@ -24213,7 +24228,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C19" s="38">
+      <c r="C19" s="39">
         <f>'공수1'!Q4</f>
         <v/>
       </c>
@@ -24225,7 +24240,7 @@
         <f>'공수1'!Q3</f>
         <v/>
       </c>
-      <c r="F19" s="39">
+      <c r="F19" s="40">
         <f>IF('공수1'!$Q$2="","",'공수1'!$Q$2)</f>
         <v/>
       </c>
@@ -24237,47 +24252,47 @@
         <f>IF(F19="","",SUMPRODUCT(('공수1'!$Q$7:$Q$86='공수1'!$Q$2)*('공수1'!$Q$7:$Q$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I19" s="40">
+      <c r="I19" s="41">
         <f>IF(OR(F19="",G19=0),"",H19/G19)</f>
         <v/>
       </c>
-      <c r="J19" s="41">
+      <c r="J19" s="42">
         <f>IF(F19="","",IFERROR(SUMPRODUCT(('공수1'!$Q$7:$Q$86='공수1'!$Q$2)*('공수1'!$Q$7:$Q$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K19" s="41">
+      <c r="K19" s="42">
         <f>IF(F19="","",IFERROR(SUMPRODUCT(('공수1'!$Q$7:$Q$86='공수1'!$Q$2)*('공수1'!$Q$7:$Q$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L19" s="41">
+      <c r="L19" s="42">
         <f>IF(F19="","",IFERROR(SUMPRODUCT(('공수1'!$Q$7:$Q$86='공수1'!$Q$2)*('공수1'!$Q$7:$Q$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M19" s="42">
+      <c r="M19" s="43">
         <f>IF(OR(J19="",L19=""),"",J19-L19)</f>
         <v/>
       </c>
-      <c r="N19" s="38">
+      <c r="N19" s="39">
         <f>IF(I19="","",IF(AND(M19&lt;&gt;"",M19&lt;0),"역변별·문항검토",IF(I19&gt;=0.9,"매우 쉬움",IF(I19&lt;=0.15,"매우 어려움",IF(AND(M19&lt;&gt;"",M19&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O19" s="38">
+      <c r="O19" s="39">
         <f>IF(G19=0,"",COUNTIF('공수1'!$Q$7:$Q$86,1))</f>
         <v/>
       </c>
-      <c r="P19" s="38">
+      <c r="P19" s="39">
         <f>IF(G19=0,"",COUNTIF('공수1'!$Q$7:$Q$86,2))</f>
         <v/>
       </c>
-      <c r="Q19" s="38">
+      <c r="Q19" s="39">
         <f>IF(G19=0,"",COUNTIF('공수1'!$Q$7:$Q$86,3))</f>
         <v/>
       </c>
-      <c r="R19" s="38">
+      <c r="R19" s="39">
         <f>IF(G19=0,"",COUNTIF('공수1'!$Q$7:$Q$86,4))</f>
         <v/>
       </c>
-      <c r="S19" s="38">
+      <c r="S19" s="39">
         <f>IF(G19=0,"",COUNTIF('공수1'!$Q$7:$Q$86,5))</f>
         <v/>
       </c>
@@ -24291,7 +24306,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C20" s="38">
+      <c r="C20" s="39">
         <f>'공수1'!R4</f>
         <v/>
       </c>
@@ -24303,8 +24318,8 @@
         <f>'공수1'!R3</f>
         <v/>
       </c>
-      <c r="F20" s="39">
-        <f>IF('공수1'!$R$2="","",'공수1'!$R$2)</f>
+      <c r="F20" s="40">
+        <f>IF('공수1'!$R$2="","","24")</f>
         <v/>
       </c>
       <c r="G20" s="10">
@@ -24315,51 +24330,51 @@
         <f>IF(F20="","",SUMPRODUCT(('공수1'!$R$7:$R$86='공수1'!$R$2)*('공수1'!$R$7:$R$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I20" s="40">
+      <c r="I20" s="41">
         <f>IF(OR(F20="",G20=0),"",H20/G20)</f>
         <v/>
       </c>
-      <c r="J20" s="41">
+      <c r="J20" s="42">
         <f>IF(F20="","",IFERROR(SUMPRODUCT(('공수1'!$R$7:$R$86='공수1'!$R$2)*('공수1'!$R$7:$R$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K20" s="41">
+      <c r="K20" s="42">
         <f>IF(F20="","",IFERROR(SUMPRODUCT(('공수1'!$R$7:$R$86='공수1'!$R$2)*('공수1'!$R$7:$R$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L20" s="41">
+      <c r="L20" s="42">
         <f>IF(F20="","",IFERROR(SUMPRODUCT(('공수1'!$R$7:$R$86='공수1'!$R$2)*('공수1'!$R$7:$R$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M20" s="42">
+      <c r="M20" s="43">
         <f>IF(OR(J20="",L20=""),"",J20-L20)</f>
         <v/>
       </c>
-      <c r="N20" s="38">
+      <c r="N20" s="39">
         <f>IF(I20="","",IF(AND(M20&lt;&gt;"",M20&lt;0),"역변별·문항검토",IF(I20&gt;=0.9,"매우 쉬움",IF(I20&lt;=0.15,"매우 어려움",IF(AND(M20&lt;&gt;"",M20&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O20" s="43" t="inlineStr">
+      <c r="O20" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P20" s="43" t="inlineStr">
+      <c r="P20" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q20" s="43" t="inlineStr">
+      <c r="Q20" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R20" s="43" t="inlineStr">
+      <c r="R20" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S20" s="43" t="inlineStr">
+      <c r="S20" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -24374,7 +24389,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C21" s="38">
+      <c r="C21" s="39">
         <f>'공수1'!S4</f>
         <v/>
       </c>
@@ -24386,8 +24401,8 @@
         <f>'공수1'!S3</f>
         <v/>
       </c>
-      <c r="F21" s="39">
-        <f>IF('공수1'!$S$2="","",'공수1'!$S$2)</f>
+      <c r="F21" s="40">
+        <f>IF('공수1'!$S$2="","","864")</f>
         <v/>
       </c>
       <c r="G21" s="10">
@@ -24398,51 +24413,51 @@
         <f>IF(F21="","",SUMPRODUCT(('공수1'!$S$7:$S$86='공수1'!$S$2)*('공수1'!$S$7:$S$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I21" s="40">
+      <c r="I21" s="41">
         <f>IF(OR(F21="",G21=0),"",H21/G21)</f>
         <v/>
       </c>
-      <c r="J21" s="41">
+      <c r="J21" s="42">
         <f>IF(F21="","",IFERROR(SUMPRODUCT(('공수1'!$S$7:$S$86='공수1'!$S$2)*('공수1'!$S$7:$S$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K21" s="41">
+      <c r="K21" s="42">
         <f>IF(F21="","",IFERROR(SUMPRODUCT(('공수1'!$S$7:$S$86='공수1'!$S$2)*('공수1'!$S$7:$S$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L21" s="41">
+      <c r="L21" s="42">
         <f>IF(F21="","",IFERROR(SUMPRODUCT(('공수1'!$S$7:$S$86='공수1'!$S$2)*('공수1'!$S$7:$S$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M21" s="42">
+      <c r="M21" s="43">
         <f>IF(OR(J21="",L21=""),"",J21-L21)</f>
         <v/>
       </c>
-      <c r="N21" s="38">
+      <c r="N21" s="39">
         <f>IF(I21="","",IF(AND(M21&lt;&gt;"",M21&lt;0),"역변별·문항검토",IF(I21&gt;=0.9,"매우 쉬움",IF(I21&lt;=0.15,"매우 어려움",IF(AND(M21&lt;&gt;"",M21&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O21" s="43" t="inlineStr">
+      <c r="O21" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P21" s="43" t="inlineStr">
+      <c r="P21" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q21" s="43" t="inlineStr">
+      <c r="Q21" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R21" s="43" t="inlineStr">
+      <c r="R21" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S21" s="43" t="inlineStr">
+      <c r="S21" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -24457,7 +24472,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C22" s="38">
+      <c r="C22" s="39">
         <f>'공수1'!T4</f>
         <v/>
       </c>
@@ -24469,8 +24484,8 @@
         <f>'공수1'!T3</f>
         <v/>
       </c>
-      <c r="F22" s="39">
-        <f>IF('공수1'!$T$2="","",'공수1'!$T$2)</f>
+      <c r="F22" s="40">
+        <f>IF('공수1'!$T$2="","","8")</f>
         <v/>
       </c>
       <c r="G22" s="10">
@@ -24481,51 +24496,51 @@
         <f>IF(F22="","",SUMPRODUCT(('공수1'!$T$7:$T$86='공수1'!$T$2)*('공수1'!$T$7:$T$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I22" s="40">
+      <c r="I22" s="41">
         <f>IF(OR(F22="",G22=0),"",H22/G22)</f>
         <v/>
       </c>
-      <c r="J22" s="41">
+      <c r="J22" s="42">
         <f>IF(F22="","",IFERROR(SUMPRODUCT(('공수1'!$T$7:$T$86='공수1'!$T$2)*('공수1'!$T$7:$T$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K22" s="41">
+      <c r="K22" s="42">
         <f>IF(F22="","",IFERROR(SUMPRODUCT(('공수1'!$T$7:$T$86='공수1'!$T$2)*('공수1'!$T$7:$T$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L22" s="41">
+      <c r="L22" s="42">
         <f>IF(F22="","",IFERROR(SUMPRODUCT(('공수1'!$T$7:$T$86='공수1'!$T$2)*('공수1'!$T$7:$T$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M22" s="42">
+      <c r="M22" s="43">
         <f>IF(OR(J22="",L22=""),"",J22-L22)</f>
         <v/>
       </c>
-      <c r="N22" s="38">
+      <c r="N22" s="39">
         <f>IF(I22="","",IF(AND(M22&lt;&gt;"",M22&lt;0),"역변별·문항검토",IF(I22&gt;=0.9,"매우 쉬움",IF(I22&lt;=0.15,"매우 어려움",IF(AND(M22&lt;&gt;"",M22&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O22" s="43" t="inlineStr">
+      <c r="O22" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P22" s="43" t="inlineStr">
+      <c r="P22" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q22" s="43" t="inlineStr">
+      <c r="Q22" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R22" s="43" t="inlineStr">
+      <c r="R22" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S22" s="43" t="inlineStr">
+      <c r="S22" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -24540,7 +24555,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C23" s="38">
+      <c r="C23" s="39">
         <f>'공수1'!U4</f>
         <v/>
       </c>
@@ -24552,8 +24567,8 @@
         <f>'공수1'!U3</f>
         <v/>
       </c>
-      <c r="F23" s="39">
-        <f>IF('공수1'!$U$2="","",'공수1'!$U$2)</f>
+      <c r="F23" s="40">
+        <f>IF('공수1'!$U$2="","","76")</f>
         <v/>
       </c>
       <c r="G23" s="10">
@@ -24564,51 +24579,51 @@
         <f>IF(F23="","",SUMPRODUCT(('공수1'!$U$7:$U$86='공수1'!$U$2)*('공수1'!$U$7:$U$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I23" s="40">
+      <c r="I23" s="41">
         <f>IF(OR(F23="",G23=0),"",H23/G23)</f>
         <v/>
       </c>
-      <c r="J23" s="41">
+      <c r="J23" s="42">
         <f>IF(F23="","",IFERROR(SUMPRODUCT(('공수1'!$U$7:$U$86='공수1'!$U$2)*('공수1'!$U$7:$U$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K23" s="41">
+      <c r="K23" s="42">
         <f>IF(F23="","",IFERROR(SUMPRODUCT(('공수1'!$U$7:$U$86='공수1'!$U$2)*('공수1'!$U$7:$U$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L23" s="41">
+      <c r="L23" s="42">
         <f>IF(F23="","",IFERROR(SUMPRODUCT(('공수1'!$U$7:$U$86='공수1'!$U$2)*('공수1'!$U$7:$U$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M23" s="42">
+      <c r="M23" s="43">
         <f>IF(OR(J23="",L23=""),"",J23-L23)</f>
         <v/>
       </c>
-      <c r="N23" s="38">
+      <c r="N23" s="39">
         <f>IF(I23="","",IF(AND(M23&lt;&gt;"",M23&lt;0),"역변별·문항검토",IF(I23&gt;=0.9,"매우 쉬움",IF(I23&lt;=0.15,"매우 어려움",IF(AND(M23&lt;&gt;"",M23&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O23" s="43" t="inlineStr">
+      <c r="O23" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P23" s="43" t="inlineStr">
+      <c r="P23" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q23" s="43" t="inlineStr">
+      <c r="Q23" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R23" s="43" t="inlineStr">
+      <c r="R23" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S23" s="43" t="inlineStr">
+      <c r="S23" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -24623,7 +24638,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C24" s="38">
+      <c r="C24" s="39">
         <f>'공수1'!V4</f>
         <v/>
       </c>
@@ -24635,8 +24650,8 @@
         <f>'공수1'!V3</f>
         <v/>
       </c>
-      <c r="F24" s="39">
-        <f>IF('공수1'!$V$2="","",'공수1'!$V$2)</f>
+      <c r="F24" s="40">
+        <f>IF('공수1'!$V$2="","","27")</f>
         <v/>
       </c>
       <c r="G24" s="10">
@@ -24647,51 +24662,51 @@
         <f>IF(F24="","",SUMPRODUCT(('공수1'!$V$7:$V$86='공수1'!$V$2)*('공수1'!$V$7:$V$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I24" s="40">
+      <c r="I24" s="41">
         <f>IF(OR(F24="",G24=0),"",H24/G24)</f>
         <v/>
       </c>
-      <c r="J24" s="41">
+      <c r="J24" s="42">
         <f>IF(F24="","",IFERROR(SUMPRODUCT(('공수1'!$V$7:$V$86='공수1'!$V$2)*('공수1'!$V$7:$V$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K24" s="41">
+      <c r="K24" s="42">
         <f>IF(F24="","",IFERROR(SUMPRODUCT(('공수1'!$V$7:$V$86='공수1'!$V$2)*('공수1'!$V$7:$V$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L24" s="41">
+      <c r="L24" s="42">
         <f>IF(F24="","",IFERROR(SUMPRODUCT(('공수1'!$V$7:$V$86='공수1'!$V$2)*('공수1'!$V$7:$V$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M24" s="42">
+      <c r="M24" s="43">
         <f>IF(OR(J24="",L24=""),"",J24-L24)</f>
         <v/>
       </c>
-      <c r="N24" s="38">
+      <c r="N24" s="39">
         <f>IF(I24="","",IF(AND(M24&lt;&gt;"",M24&lt;0),"역변별·문항검토",IF(I24&gt;=0.9,"매우 쉬움",IF(I24&lt;=0.15,"매우 어려움",IF(AND(M24&lt;&gt;"",M24&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O24" s="43" t="inlineStr">
+      <c r="O24" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P24" s="43" t="inlineStr">
+      <c r="P24" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q24" s="43" t="inlineStr">
+      <c r="Q24" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R24" s="43" t="inlineStr">
+      <c r="R24" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S24" s="43" t="inlineStr">
+      <c r="S24" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -24706,7 +24721,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C25" s="38">
+      <c r="C25" s="39">
         <f>'공수1'!W4</f>
         <v/>
       </c>
@@ -24718,8 +24733,8 @@
         <f>'공수1'!W3</f>
         <v/>
       </c>
-      <c r="F25" s="39">
-        <f>IF('공수1'!$W$2="","",'공수1'!$W$2)</f>
+      <c r="F25" s="40">
+        <f>IF('공수1'!$W$2="","","65")</f>
         <v/>
       </c>
       <c r="G25" s="10">
@@ -24730,58 +24745,58 @@
         <f>IF(F25="","",SUMPRODUCT(('공수1'!$W$7:$W$86='공수1'!$W$2)*('공수1'!$W$7:$W$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I25" s="40">
+      <c r="I25" s="41">
         <f>IF(OR(F25="",G25=0),"",H25/G25)</f>
         <v/>
       </c>
-      <c r="J25" s="41">
+      <c r="J25" s="42">
         <f>IF(F25="","",IFERROR(SUMPRODUCT(('공수1'!$W$7:$W$86='공수1'!$W$2)*('공수1'!$W$7:$W$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K25" s="41">
+      <c r="K25" s="42">
         <f>IF(F25="","",IFERROR(SUMPRODUCT(('공수1'!$W$7:$W$86='공수1'!$W$2)*('공수1'!$W$7:$W$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L25" s="41">
+      <c r="L25" s="42">
         <f>IF(F25="","",IFERROR(SUMPRODUCT(('공수1'!$W$7:$W$86='공수1'!$W$2)*('공수1'!$W$7:$W$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수1'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M25" s="42">
+      <c r="M25" s="43">
         <f>IF(OR(J25="",L25=""),"",J25-L25)</f>
         <v/>
       </c>
-      <c r="N25" s="38">
+      <c r="N25" s="39">
         <f>IF(I25="","",IF(AND(M25&lt;&gt;"",M25&lt;0),"역변별·문항검토",IF(I25&gt;=0.9,"매우 쉬움",IF(I25&lt;=0.15,"매우 어려움",IF(AND(M25&lt;&gt;"",M25&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O25" s="43" t="inlineStr">
+      <c r="O25" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P25" s="43" t="inlineStr">
+      <c r="P25" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q25" s="43" t="inlineStr">
+      <c r="Q25" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R25" s="43" t="inlineStr">
+      <c r="R25" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S25" s="43" t="inlineStr">
+      <c r="S25" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="inlineStr">
+      <c r="A28" s="38" t="inlineStr">
         <is>
           <t>공통수학2</t>
         </is>
@@ -24890,7 +24905,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C30" s="38">
+      <c r="C30" s="39">
         <f>'공수2'!D4</f>
         <v/>
       </c>
@@ -24902,7 +24917,7 @@
         <f>'공수2'!D3</f>
         <v/>
       </c>
-      <c r="F30" s="39">
+      <c r="F30" s="40">
         <f>IF('공수2'!$D$2="","",'공수2'!$D$2)</f>
         <v/>
       </c>
@@ -24914,47 +24929,47 @@
         <f>IF(F30="","",SUMPRODUCT(('공수2'!$D$7:$D$86='공수2'!$D$2)*('공수2'!$D$7:$D$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I30" s="40">
+      <c r="I30" s="41">
         <f>IF(OR(F30="",G30=0),"",H30/G30)</f>
         <v/>
       </c>
-      <c r="J30" s="41">
+      <c r="J30" s="42">
         <f>IF(F30="","",IFERROR(SUMPRODUCT(('공수2'!$D$7:$D$86='공수2'!$D$2)*('공수2'!$D$7:$D$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K30" s="41">
+      <c r="K30" s="42">
         <f>IF(F30="","",IFERROR(SUMPRODUCT(('공수2'!$D$7:$D$86='공수2'!$D$2)*('공수2'!$D$7:$D$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L30" s="41">
+      <c r="L30" s="42">
         <f>IF(F30="","",IFERROR(SUMPRODUCT(('공수2'!$D$7:$D$86='공수2'!$D$2)*('공수2'!$D$7:$D$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M30" s="42">
+      <c r="M30" s="43">
         <f>IF(OR(J30="",L30=""),"",J30-L30)</f>
         <v/>
       </c>
-      <c r="N30" s="38">
+      <c r="N30" s="39">
         <f>IF(I30="","",IF(AND(M30&lt;&gt;"",M30&lt;0),"역변별·문항검토",IF(I30&gt;=0.9,"매우 쉬움",IF(I30&lt;=0.15,"매우 어려움",IF(AND(M30&lt;&gt;"",M30&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O30" s="38">
+      <c r="O30" s="39">
         <f>IF(G30=0,"",COUNTIF('공수2'!$D$7:$D$86,1))</f>
         <v/>
       </c>
-      <c r="P30" s="38">
+      <c r="P30" s="39">
         <f>IF(G30=0,"",COUNTIF('공수2'!$D$7:$D$86,2))</f>
         <v/>
       </c>
-      <c r="Q30" s="38">
+      <c r="Q30" s="39">
         <f>IF(G30=0,"",COUNTIF('공수2'!$D$7:$D$86,3))</f>
         <v/>
       </c>
-      <c r="R30" s="38">
+      <c r="R30" s="39">
         <f>IF(G30=0,"",COUNTIF('공수2'!$D$7:$D$86,4))</f>
         <v/>
       </c>
-      <c r="S30" s="38">
+      <c r="S30" s="39">
         <f>IF(G30=0,"",COUNTIF('공수2'!$D$7:$D$86,5))</f>
         <v/>
       </c>
@@ -24968,7 +24983,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C31" s="38">
+      <c r="C31" s="39">
         <f>'공수2'!E4</f>
         <v/>
       </c>
@@ -24980,7 +24995,7 @@
         <f>'공수2'!E3</f>
         <v/>
       </c>
-      <c r="F31" s="39">
+      <c r="F31" s="40">
         <f>IF('공수2'!$E$2="","",'공수2'!$E$2)</f>
         <v/>
       </c>
@@ -24992,47 +25007,47 @@
         <f>IF(F31="","",SUMPRODUCT(('공수2'!$E$7:$E$86='공수2'!$E$2)*('공수2'!$E$7:$E$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I31" s="40">
+      <c r="I31" s="41">
         <f>IF(OR(F31="",G31=0),"",H31/G31)</f>
         <v/>
       </c>
-      <c r="J31" s="41">
+      <c r="J31" s="42">
         <f>IF(F31="","",IFERROR(SUMPRODUCT(('공수2'!$E$7:$E$86='공수2'!$E$2)*('공수2'!$E$7:$E$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K31" s="41">
+      <c r="K31" s="42">
         <f>IF(F31="","",IFERROR(SUMPRODUCT(('공수2'!$E$7:$E$86='공수2'!$E$2)*('공수2'!$E$7:$E$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L31" s="41">
+      <c r="L31" s="42">
         <f>IF(F31="","",IFERROR(SUMPRODUCT(('공수2'!$E$7:$E$86='공수2'!$E$2)*('공수2'!$E$7:$E$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M31" s="42">
+      <c r="M31" s="43">
         <f>IF(OR(J31="",L31=""),"",J31-L31)</f>
         <v/>
       </c>
-      <c r="N31" s="38">
+      <c r="N31" s="39">
         <f>IF(I31="","",IF(AND(M31&lt;&gt;"",M31&lt;0),"역변별·문항검토",IF(I31&gt;=0.9,"매우 쉬움",IF(I31&lt;=0.15,"매우 어려움",IF(AND(M31&lt;&gt;"",M31&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O31" s="38">
+      <c r="O31" s="39">
         <f>IF(G31=0,"",COUNTIF('공수2'!$E$7:$E$86,1))</f>
         <v/>
       </c>
-      <c r="P31" s="38">
+      <c r="P31" s="39">
         <f>IF(G31=0,"",COUNTIF('공수2'!$E$7:$E$86,2))</f>
         <v/>
       </c>
-      <c r="Q31" s="38">
+      <c r="Q31" s="39">
         <f>IF(G31=0,"",COUNTIF('공수2'!$E$7:$E$86,3))</f>
         <v/>
       </c>
-      <c r="R31" s="38">
+      <c r="R31" s="39">
         <f>IF(G31=0,"",COUNTIF('공수2'!$E$7:$E$86,4))</f>
         <v/>
       </c>
-      <c r="S31" s="38">
+      <c r="S31" s="39">
         <f>IF(G31=0,"",COUNTIF('공수2'!$E$7:$E$86,5))</f>
         <v/>
       </c>
@@ -25046,7 +25061,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C32" s="38">
+      <c r="C32" s="39">
         <f>'공수2'!F4</f>
         <v/>
       </c>
@@ -25058,7 +25073,7 @@
         <f>'공수2'!F3</f>
         <v/>
       </c>
-      <c r="F32" s="39">
+      <c r="F32" s="40">
         <f>IF('공수2'!$F$2="","",'공수2'!$F$2)</f>
         <v/>
       </c>
@@ -25070,47 +25085,47 @@
         <f>IF(F32="","",SUMPRODUCT(('공수2'!$F$7:$F$86='공수2'!$F$2)*('공수2'!$F$7:$F$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I32" s="40">
+      <c r="I32" s="41">
         <f>IF(OR(F32="",G32=0),"",H32/G32)</f>
         <v/>
       </c>
-      <c r="J32" s="41">
+      <c r="J32" s="42">
         <f>IF(F32="","",IFERROR(SUMPRODUCT(('공수2'!$F$7:$F$86='공수2'!$F$2)*('공수2'!$F$7:$F$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K32" s="41">
+      <c r="K32" s="42">
         <f>IF(F32="","",IFERROR(SUMPRODUCT(('공수2'!$F$7:$F$86='공수2'!$F$2)*('공수2'!$F$7:$F$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L32" s="41">
+      <c r="L32" s="42">
         <f>IF(F32="","",IFERROR(SUMPRODUCT(('공수2'!$F$7:$F$86='공수2'!$F$2)*('공수2'!$F$7:$F$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M32" s="42">
+      <c r="M32" s="43">
         <f>IF(OR(J32="",L32=""),"",J32-L32)</f>
         <v/>
       </c>
-      <c r="N32" s="38">
+      <c r="N32" s="39">
         <f>IF(I32="","",IF(AND(M32&lt;&gt;"",M32&lt;0),"역변별·문항검토",IF(I32&gt;=0.9,"매우 쉬움",IF(I32&lt;=0.15,"매우 어려움",IF(AND(M32&lt;&gt;"",M32&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O32" s="38">
+      <c r="O32" s="39">
         <f>IF(G32=0,"",COUNTIF('공수2'!$F$7:$F$86,1))</f>
         <v/>
       </c>
-      <c r="P32" s="38">
+      <c r="P32" s="39">
         <f>IF(G32=0,"",COUNTIF('공수2'!$F$7:$F$86,2))</f>
         <v/>
       </c>
-      <c r="Q32" s="38">
+      <c r="Q32" s="39">
         <f>IF(G32=0,"",COUNTIF('공수2'!$F$7:$F$86,3))</f>
         <v/>
       </c>
-      <c r="R32" s="38">
+      <c r="R32" s="39">
         <f>IF(G32=0,"",COUNTIF('공수2'!$F$7:$F$86,4))</f>
         <v/>
       </c>
-      <c r="S32" s="38">
+      <c r="S32" s="39">
         <f>IF(G32=0,"",COUNTIF('공수2'!$F$7:$F$86,5))</f>
         <v/>
       </c>
@@ -25124,7 +25139,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C33" s="38">
+      <c r="C33" s="39">
         <f>'공수2'!G4</f>
         <v/>
       </c>
@@ -25136,7 +25151,7 @@
         <f>'공수2'!G3</f>
         <v/>
       </c>
-      <c r="F33" s="39">
+      <c r="F33" s="40">
         <f>IF('공수2'!$G$2="","",'공수2'!$G$2)</f>
         <v/>
       </c>
@@ -25148,47 +25163,47 @@
         <f>IF(F33="","",SUMPRODUCT(('공수2'!$G$7:$G$86='공수2'!$G$2)*('공수2'!$G$7:$G$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I33" s="40">
+      <c r="I33" s="41">
         <f>IF(OR(F33="",G33=0),"",H33/G33)</f>
         <v/>
       </c>
-      <c r="J33" s="41">
+      <c r="J33" s="42">
         <f>IF(F33="","",IFERROR(SUMPRODUCT(('공수2'!$G$7:$G$86='공수2'!$G$2)*('공수2'!$G$7:$G$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K33" s="41">
+      <c r="K33" s="42">
         <f>IF(F33="","",IFERROR(SUMPRODUCT(('공수2'!$G$7:$G$86='공수2'!$G$2)*('공수2'!$G$7:$G$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L33" s="41">
+      <c r="L33" s="42">
         <f>IF(F33="","",IFERROR(SUMPRODUCT(('공수2'!$G$7:$G$86='공수2'!$G$2)*('공수2'!$G$7:$G$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M33" s="42">
+      <c r="M33" s="43">
         <f>IF(OR(J33="",L33=""),"",J33-L33)</f>
         <v/>
       </c>
-      <c r="N33" s="38">
+      <c r="N33" s="39">
         <f>IF(I33="","",IF(AND(M33&lt;&gt;"",M33&lt;0),"역변별·문항검토",IF(I33&gt;=0.9,"매우 쉬움",IF(I33&lt;=0.15,"매우 어려움",IF(AND(M33&lt;&gt;"",M33&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O33" s="38">
+      <c r="O33" s="39">
         <f>IF(G33=0,"",COUNTIF('공수2'!$G$7:$G$86,1))</f>
         <v/>
       </c>
-      <c r="P33" s="38">
+      <c r="P33" s="39">
         <f>IF(G33=0,"",COUNTIF('공수2'!$G$7:$G$86,2))</f>
         <v/>
       </c>
-      <c r="Q33" s="38">
+      <c r="Q33" s="39">
         <f>IF(G33=0,"",COUNTIF('공수2'!$G$7:$G$86,3))</f>
         <v/>
       </c>
-      <c r="R33" s="38">
+      <c r="R33" s="39">
         <f>IF(G33=0,"",COUNTIF('공수2'!$G$7:$G$86,4))</f>
         <v/>
       </c>
-      <c r="S33" s="38">
+      <c r="S33" s="39">
         <f>IF(G33=0,"",COUNTIF('공수2'!$G$7:$G$86,5))</f>
         <v/>
       </c>
@@ -25202,7 +25217,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C34" s="38">
+      <c r="C34" s="39">
         <f>'공수2'!H4</f>
         <v/>
       </c>
@@ -25214,7 +25229,7 @@
         <f>'공수2'!H3</f>
         <v/>
       </c>
-      <c r="F34" s="39">
+      <c r="F34" s="40">
         <f>IF('공수2'!$H$2="","",'공수2'!$H$2)</f>
         <v/>
       </c>
@@ -25226,47 +25241,47 @@
         <f>IF(F34="","",SUMPRODUCT(('공수2'!$H$7:$H$86='공수2'!$H$2)*('공수2'!$H$7:$H$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I34" s="40">
+      <c r="I34" s="41">
         <f>IF(OR(F34="",G34=0),"",H34/G34)</f>
         <v/>
       </c>
-      <c r="J34" s="41">
+      <c r="J34" s="42">
         <f>IF(F34="","",IFERROR(SUMPRODUCT(('공수2'!$H$7:$H$86='공수2'!$H$2)*('공수2'!$H$7:$H$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K34" s="41">
+      <c r="K34" s="42">
         <f>IF(F34="","",IFERROR(SUMPRODUCT(('공수2'!$H$7:$H$86='공수2'!$H$2)*('공수2'!$H$7:$H$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L34" s="41">
+      <c r="L34" s="42">
         <f>IF(F34="","",IFERROR(SUMPRODUCT(('공수2'!$H$7:$H$86='공수2'!$H$2)*('공수2'!$H$7:$H$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M34" s="42">
+      <c r="M34" s="43">
         <f>IF(OR(J34="",L34=""),"",J34-L34)</f>
         <v/>
       </c>
-      <c r="N34" s="38">
+      <c r="N34" s="39">
         <f>IF(I34="","",IF(AND(M34&lt;&gt;"",M34&lt;0),"역변별·문항검토",IF(I34&gt;=0.9,"매우 쉬움",IF(I34&lt;=0.15,"매우 어려움",IF(AND(M34&lt;&gt;"",M34&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O34" s="38">
+      <c r="O34" s="39">
         <f>IF(G34=0,"",COUNTIF('공수2'!$H$7:$H$86,1))</f>
         <v/>
       </c>
-      <c r="P34" s="38">
+      <c r="P34" s="39">
         <f>IF(G34=0,"",COUNTIF('공수2'!$H$7:$H$86,2))</f>
         <v/>
       </c>
-      <c r="Q34" s="38">
+      <c r="Q34" s="39">
         <f>IF(G34=0,"",COUNTIF('공수2'!$H$7:$H$86,3))</f>
         <v/>
       </c>
-      <c r="R34" s="38">
+      <c r="R34" s="39">
         <f>IF(G34=0,"",COUNTIF('공수2'!$H$7:$H$86,4))</f>
         <v/>
       </c>
-      <c r="S34" s="38">
+      <c r="S34" s="39">
         <f>IF(G34=0,"",COUNTIF('공수2'!$H$7:$H$86,5))</f>
         <v/>
       </c>
@@ -25280,7 +25295,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C35" s="38">
+      <c r="C35" s="39">
         <f>'공수2'!I4</f>
         <v/>
       </c>
@@ -25292,7 +25307,7 @@
         <f>'공수2'!I3</f>
         <v/>
       </c>
-      <c r="F35" s="39">
+      <c r="F35" s="40">
         <f>IF('공수2'!$I$2="","",'공수2'!$I$2)</f>
         <v/>
       </c>
@@ -25304,47 +25319,47 @@
         <f>IF(F35="","",SUMPRODUCT(('공수2'!$I$7:$I$86='공수2'!$I$2)*('공수2'!$I$7:$I$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I35" s="40">
+      <c r="I35" s="41">
         <f>IF(OR(F35="",G35=0),"",H35/G35)</f>
         <v/>
       </c>
-      <c r="J35" s="41">
+      <c r="J35" s="42">
         <f>IF(F35="","",IFERROR(SUMPRODUCT(('공수2'!$I$7:$I$86='공수2'!$I$2)*('공수2'!$I$7:$I$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K35" s="41">
+      <c r="K35" s="42">
         <f>IF(F35="","",IFERROR(SUMPRODUCT(('공수2'!$I$7:$I$86='공수2'!$I$2)*('공수2'!$I$7:$I$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L35" s="41">
+      <c r="L35" s="42">
         <f>IF(F35="","",IFERROR(SUMPRODUCT(('공수2'!$I$7:$I$86='공수2'!$I$2)*('공수2'!$I$7:$I$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M35" s="42">
+      <c r="M35" s="43">
         <f>IF(OR(J35="",L35=""),"",J35-L35)</f>
         <v/>
       </c>
-      <c r="N35" s="38">
+      <c r="N35" s="39">
         <f>IF(I35="","",IF(AND(M35&lt;&gt;"",M35&lt;0),"역변별·문항검토",IF(I35&gt;=0.9,"매우 쉬움",IF(I35&lt;=0.15,"매우 어려움",IF(AND(M35&lt;&gt;"",M35&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O35" s="38">
+      <c r="O35" s="39">
         <f>IF(G35=0,"",COUNTIF('공수2'!$I$7:$I$86,1))</f>
         <v/>
       </c>
-      <c r="P35" s="38">
+      <c r="P35" s="39">
         <f>IF(G35=0,"",COUNTIF('공수2'!$I$7:$I$86,2))</f>
         <v/>
       </c>
-      <c r="Q35" s="38">
+      <c r="Q35" s="39">
         <f>IF(G35=0,"",COUNTIF('공수2'!$I$7:$I$86,3))</f>
         <v/>
       </c>
-      <c r="R35" s="38">
+      <c r="R35" s="39">
         <f>IF(G35=0,"",COUNTIF('공수2'!$I$7:$I$86,4))</f>
         <v/>
       </c>
-      <c r="S35" s="38">
+      <c r="S35" s="39">
         <f>IF(G35=0,"",COUNTIF('공수2'!$I$7:$I$86,5))</f>
         <v/>
       </c>
@@ -25358,7 +25373,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C36" s="38">
+      <c r="C36" s="39">
         <f>'공수2'!J4</f>
         <v/>
       </c>
@@ -25370,7 +25385,7 @@
         <f>'공수2'!J3</f>
         <v/>
       </c>
-      <c r="F36" s="39">
+      <c r="F36" s="40">
         <f>IF('공수2'!$J$2="","",'공수2'!$J$2)</f>
         <v/>
       </c>
@@ -25382,47 +25397,47 @@
         <f>IF(F36="","",SUMPRODUCT(('공수2'!$J$7:$J$86='공수2'!$J$2)*('공수2'!$J$7:$J$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I36" s="40">
+      <c r="I36" s="41">
         <f>IF(OR(F36="",G36=0),"",H36/G36)</f>
         <v/>
       </c>
-      <c r="J36" s="41">
+      <c r="J36" s="42">
         <f>IF(F36="","",IFERROR(SUMPRODUCT(('공수2'!$J$7:$J$86='공수2'!$J$2)*('공수2'!$J$7:$J$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K36" s="41">
+      <c r="K36" s="42">
         <f>IF(F36="","",IFERROR(SUMPRODUCT(('공수2'!$J$7:$J$86='공수2'!$J$2)*('공수2'!$J$7:$J$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L36" s="41">
+      <c r="L36" s="42">
         <f>IF(F36="","",IFERROR(SUMPRODUCT(('공수2'!$J$7:$J$86='공수2'!$J$2)*('공수2'!$J$7:$J$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M36" s="42">
+      <c r="M36" s="43">
         <f>IF(OR(J36="",L36=""),"",J36-L36)</f>
         <v/>
       </c>
-      <c r="N36" s="38">
+      <c r="N36" s="39">
         <f>IF(I36="","",IF(AND(M36&lt;&gt;"",M36&lt;0),"역변별·문항검토",IF(I36&gt;=0.9,"매우 쉬움",IF(I36&lt;=0.15,"매우 어려움",IF(AND(M36&lt;&gt;"",M36&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O36" s="38">
+      <c r="O36" s="39">
         <f>IF(G36=0,"",COUNTIF('공수2'!$J$7:$J$86,1))</f>
         <v/>
       </c>
-      <c r="P36" s="38">
+      <c r="P36" s="39">
         <f>IF(G36=0,"",COUNTIF('공수2'!$J$7:$J$86,2))</f>
         <v/>
       </c>
-      <c r="Q36" s="38">
+      <c r="Q36" s="39">
         <f>IF(G36=0,"",COUNTIF('공수2'!$J$7:$J$86,3))</f>
         <v/>
       </c>
-      <c r="R36" s="38">
+      <c r="R36" s="39">
         <f>IF(G36=0,"",COUNTIF('공수2'!$J$7:$J$86,4))</f>
         <v/>
       </c>
-      <c r="S36" s="38">
+      <c r="S36" s="39">
         <f>IF(G36=0,"",COUNTIF('공수2'!$J$7:$J$86,5))</f>
         <v/>
       </c>
@@ -25436,7 +25451,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C37" s="38">
+      <c r="C37" s="39">
         <f>'공수2'!K4</f>
         <v/>
       </c>
@@ -25448,7 +25463,7 @@
         <f>'공수2'!K3</f>
         <v/>
       </c>
-      <c r="F37" s="39">
+      <c r="F37" s="40">
         <f>IF('공수2'!$K$2="","",'공수2'!$K$2)</f>
         <v/>
       </c>
@@ -25460,47 +25475,47 @@
         <f>IF(F37="","",SUMPRODUCT(('공수2'!$K$7:$K$86='공수2'!$K$2)*('공수2'!$K$7:$K$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I37" s="40">
+      <c r="I37" s="41">
         <f>IF(OR(F37="",G37=0),"",H37/G37)</f>
         <v/>
       </c>
-      <c r="J37" s="41">
+      <c r="J37" s="42">
         <f>IF(F37="","",IFERROR(SUMPRODUCT(('공수2'!$K$7:$K$86='공수2'!$K$2)*('공수2'!$K$7:$K$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K37" s="41">
+      <c r="K37" s="42">
         <f>IF(F37="","",IFERROR(SUMPRODUCT(('공수2'!$K$7:$K$86='공수2'!$K$2)*('공수2'!$K$7:$K$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L37" s="41">
+      <c r="L37" s="42">
         <f>IF(F37="","",IFERROR(SUMPRODUCT(('공수2'!$K$7:$K$86='공수2'!$K$2)*('공수2'!$K$7:$K$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M37" s="42">
+      <c r="M37" s="43">
         <f>IF(OR(J37="",L37=""),"",J37-L37)</f>
         <v/>
       </c>
-      <c r="N37" s="38">
+      <c r="N37" s="39">
         <f>IF(I37="","",IF(AND(M37&lt;&gt;"",M37&lt;0),"역변별·문항검토",IF(I37&gt;=0.9,"매우 쉬움",IF(I37&lt;=0.15,"매우 어려움",IF(AND(M37&lt;&gt;"",M37&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O37" s="38">
+      <c r="O37" s="39">
         <f>IF(G37=0,"",COUNTIF('공수2'!$K$7:$K$86,1))</f>
         <v/>
       </c>
-      <c r="P37" s="38">
+      <c r="P37" s="39">
         <f>IF(G37=0,"",COUNTIF('공수2'!$K$7:$K$86,2))</f>
         <v/>
       </c>
-      <c r="Q37" s="38">
+      <c r="Q37" s="39">
         <f>IF(G37=0,"",COUNTIF('공수2'!$K$7:$K$86,3))</f>
         <v/>
       </c>
-      <c r="R37" s="38">
+      <c r="R37" s="39">
         <f>IF(G37=0,"",COUNTIF('공수2'!$K$7:$K$86,4))</f>
         <v/>
       </c>
-      <c r="S37" s="38">
+      <c r="S37" s="39">
         <f>IF(G37=0,"",COUNTIF('공수2'!$K$7:$K$86,5))</f>
         <v/>
       </c>
@@ -25514,7 +25529,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C38" s="38">
+      <c r="C38" s="39">
         <f>'공수2'!L4</f>
         <v/>
       </c>
@@ -25526,7 +25541,7 @@
         <f>'공수2'!L3</f>
         <v/>
       </c>
-      <c r="F38" s="39">
+      <c r="F38" s="40">
         <f>IF('공수2'!$L$2="","",'공수2'!$L$2)</f>
         <v/>
       </c>
@@ -25538,47 +25553,47 @@
         <f>IF(F38="","",SUMPRODUCT(('공수2'!$L$7:$L$86='공수2'!$L$2)*('공수2'!$L$7:$L$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I38" s="40">
+      <c r="I38" s="41">
         <f>IF(OR(F38="",G38=0),"",H38/G38)</f>
         <v/>
       </c>
-      <c r="J38" s="41">
+      <c r="J38" s="42">
         <f>IF(F38="","",IFERROR(SUMPRODUCT(('공수2'!$L$7:$L$86='공수2'!$L$2)*('공수2'!$L$7:$L$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K38" s="41">
+      <c r="K38" s="42">
         <f>IF(F38="","",IFERROR(SUMPRODUCT(('공수2'!$L$7:$L$86='공수2'!$L$2)*('공수2'!$L$7:$L$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L38" s="41">
+      <c r="L38" s="42">
         <f>IF(F38="","",IFERROR(SUMPRODUCT(('공수2'!$L$7:$L$86='공수2'!$L$2)*('공수2'!$L$7:$L$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M38" s="42">
+      <c r="M38" s="43">
         <f>IF(OR(J38="",L38=""),"",J38-L38)</f>
         <v/>
       </c>
-      <c r="N38" s="38">
+      <c r="N38" s="39">
         <f>IF(I38="","",IF(AND(M38&lt;&gt;"",M38&lt;0),"역변별·문항검토",IF(I38&gt;=0.9,"매우 쉬움",IF(I38&lt;=0.15,"매우 어려움",IF(AND(M38&lt;&gt;"",M38&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O38" s="38">
+      <c r="O38" s="39">
         <f>IF(G38=0,"",COUNTIF('공수2'!$L$7:$L$86,1))</f>
         <v/>
       </c>
-      <c r="P38" s="38">
+      <c r="P38" s="39">
         <f>IF(G38=0,"",COUNTIF('공수2'!$L$7:$L$86,2))</f>
         <v/>
       </c>
-      <c r="Q38" s="38">
+      <c r="Q38" s="39">
         <f>IF(G38=0,"",COUNTIF('공수2'!$L$7:$L$86,3))</f>
         <v/>
       </c>
-      <c r="R38" s="38">
+      <c r="R38" s="39">
         <f>IF(G38=0,"",COUNTIF('공수2'!$L$7:$L$86,4))</f>
         <v/>
       </c>
-      <c r="S38" s="38">
+      <c r="S38" s="39">
         <f>IF(G38=0,"",COUNTIF('공수2'!$L$7:$L$86,5))</f>
         <v/>
       </c>
@@ -25592,7 +25607,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C39" s="38">
+      <c r="C39" s="39">
         <f>'공수2'!M4</f>
         <v/>
       </c>
@@ -25604,7 +25619,7 @@
         <f>'공수2'!M3</f>
         <v/>
       </c>
-      <c r="F39" s="39">
+      <c r="F39" s="40">
         <f>IF('공수2'!$M$2="","",'공수2'!$M$2)</f>
         <v/>
       </c>
@@ -25616,47 +25631,47 @@
         <f>IF(F39="","",SUMPRODUCT(('공수2'!$M$7:$M$86='공수2'!$M$2)*('공수2'!$M$7:$M$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I39" s="40">
+      <c r="I39" s="41">
         <f>IF(OR(F39="",G39=0),"",H39/G39)</f>
         <v/>
       </c>
-      <c r="J39" s="41">
+      <c r="J39" s="42">
         <f>IF(F39="","",IFERROR(SUMPRODUCT(('공수2'!$M$7:$M$86='공수2'!$M$2)*('공수2'!$M$7:$M$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K39" s="41">
+      <c r="K39" s="42">
         <f>IF(F39="","",IFERROR(SUMPRODUCT(('공수2'!$M$7:$M$86='공수2'!$M$2)*('공수2'!$M$7:$M$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L39" s="41">
+      <c r="L39" s="42">
         <f>IF(F39="","",IFERROR(SUMPRODUCT(('공수2'!$M$7:$M$86='공수2'!$M$2)*('공수2'!$M$7:$M$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M39" s="42">
+      <c r="M39" s="43">
         <f>IF(OR(J39="",L39=""),"",J39-L39)</f>
         <v/>
       </c>
-      <c r="N39" s="38">
+      <c r="N39" s="39">
         <f>IF(I39="","",IF(AND(M39&lt;&gt;"",M39&lt;0),"역변별·문항검토",IF(I39&gt;=0.9,"매우 쉬움",IF(I39&lt;=0.15,"매우 어려움",IF(AND(M39&lt;&gt;"",M39&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O39" s="38">
+      <c r="O39" s="39">
         <f>IF(G39=0,"",COUNTIF('공수2'!$M$7:$M$86,1))</f>
         <v/>
       </c>
-      <c r="P39" s="38">
+      <c r="P39" s="39">
         <f>IF(G39=0,"",COUNTIF('공수2'!$M$7:$M$86,2))</f>
         <v/>
       </c>
-      <c r="Q39" s="38">
+      <c r="Q39" s="39">
         <f>IF(G39=0,"",COUNTIF('공수2'!$M$7:$M$86,3))</f>
         <v/>
       </c>
-      <c r="R39" s="38">
+      <c r="R39" s="39">
         <f>IF(G39=0,"",COUNTIF('공수2'!$M$7:$M$86,4))</f>
         <v/>
       </c>
-      <c r="S39" s="38">
+      <c r="S39" s="39">
         <f>IF(G39=0,"",COUNTIF('공수2'!$M$7:$M$86,5))</f>
         <v/>
       </c>
@@ -25670,7 +25685,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C40" s="38">
+      <c r="C40" s="39">
         <f>'공수2'!N4</f>
         <v/>
       </c>
@@ -25682,7 +25697,7 @@
         <f>'공수2'!N3</f>
         <v/>
       </c>
-      <c r="F40" s="39">
+      <c r="F40" s="40">
         <f>IF('공수2'!$N$2="","",'공수2'!$N$2)</f>
         <v/>
       </c>
@@ -25694,47 +25709,47 @@
         <f>IF(F40="","",SUMPRODUCT(('공수2'!$N$7:$N$86='공수2'!$N$2)*('공수2'!$N$7:$N$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I40" s="40">
+      <c r="I40" s="41">
         <f>IF(OR(F40="",G40=0),"",H40/G40)</f>
         <v/>
       </c>
-      <c r="J40" s="41">
+      <c r="J40" s="42">
         <f>IF(F40="","",IFERROR(SUMPRODUCT(('공수2'!$N$7:$N$86='공수2'!$N$2)*('공수2'!$N$7:$N$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K40" s="41">
+      <c r="K40" s="42">
         <f>IF(F40="","",IFERROR(SUMPRODUCT(('공수2'!$N$7:$N$86='공수2'!$N$2)*('공수2'!$N$7:$N$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L40" s="41">
+      <c r="L40" s="42">
         <f>IF(F40="","",IFERROR(SUMPRODUCT(('공수2'!$N$7:$N$86='공수2'!$N$2)*('공수2'!$N$7:$N$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M40" s="42">
+      <c r="M40" s="43">
         <f>IF(OR(J40="",L40=""),"",J40-L40)</f>
         <v/>
       </c>
-      <c r="N40" s="38">
+      <c r="N40" s="39">
         <f>IF(I40="","",IF(AND(M40&lt;&gt;"",M40&lt;0),"역변별·문항검토",IF(I40&gt;=0.9,"매우 쉬움",IF(I40&lt;=0.15,"매우 어려움",IF(AND(M40&lt;&gt;"",M40&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O40" s="38">
+      <c r="O40" s="39">
         <f>IF(G40=0,"",COUNTIF('공수2'!$N$7:$N$86,1))</f>
         <v/>
       </c>
-      <c r="P40" s="38">
+      <c r="P40" s="39">
         <f>IF(G40=0,"",COUNTIF('공수2'!$N$7:$N$86,2))</f>
         <v/>
       </c>
-      <c r="Q40" s="38">
+      <c r="Q40" s="39">
         <f>IF(G40=0,"",COUNTIF('공수2'!$N$7:$N$86,3))</f>
         <v/>
       </c>
-      <c r="R40" s="38">
+      <c r="R40" s="39">
         <f>IF(G40=0,"",COUNTIF('공수2'!$N$7:$N$86,4))</f>
         <v/>
       </c>
-      <c r="S40" s="38">
+      <c r="S40" s="39">
         <f>IF(G40=0,"",COUNTIF('공수2'!$N$7:$N$86,5))</f>
         <v/>
       </c>
@@ -25748,7 +25763,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C41" s="38">
+      <c r="C41" s="39">
         <f>'공수2'!O4</f>
         <v/>
       </c>
@@ -25760,7 +25775,7 @@
         <f>'공수2'!O3</f>
         <v/>
       </c>
-      <c r="F41" s="39">
+      <c r="F41" s="40">
         <f>IF('공수2'!$O$2="","",'공수2'!$O$2)</f>
         <v/>
       </c>
@@ -25772,47 +25787,47 @@
         <f>IF(F41="","",SUMPRODUCT(('공수2'!$O$7:$O$86='공수2'!$O$2)*('공수2'!$O$7:$O$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I41" s="40">
+      <c r="I41" s="41">
         <f>IF(OR(F41="",G41=0),"",H41/G41)</f>
         <v/>
       </c>
-      <c r="J41" s="41">
+      <c r="J41" s="42">
         <f>IF(F41="","",IFERROR(SUMPRODUCT(('공수2'!$O$7:$O$86='공수2'!$O$2)*('공수2'!$O$7:$O$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K41" s="41">
+      <c r="K41" s="42">
         <f>IF(F41="","",IFERROR(SUMPRODUCT(('공수2'!$O$7:$O$86='공수2'!$O$2)*('공수2'!$O$7:$O$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L41" s="41">
+      <c r="L41" s="42">
         <f>IF(F41="","",IFERROR(SUMPRODUCT(('공수2'!$O$7:$O$86='공수2'!$O$2)*('공수2'!$O$7:$O$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M41" s="42">
+      <c r="M41" s="43">
         <f>IF(OR(J41="",L41=""),"",J41-L41)</f>
         <v/>
       </c>
-      <c r="N41" s="38">
+      <c r="N41" s="39">
         <f>IF(I41="","",IF(AND(M41&lt;&gt;"",M41&lt;0),"역변별·문항검토",IF(I41&gt;=0.9,"매우 쉬움",IF(I41&lt;=0.15,"매우 어려움",IF(AND(M41&lt;&gt;"",M41&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O41" s="38">
+      <c r="O41" s="39">
         <f>IF(G41=0,"",COUNTIF('공수2'!$O$7:$O$86,1))</f>
         <v/>
       </c>
-      <c r="P41" s="38">
+      <c r="P41" s="39">
         <f>IF(G41=0,"",COUNTIF('공수2'!$O$7:$O$86,2))</f>
         <v/>
       </c>
-      <c r="Q41" s="38">
+      <c r="Q41" s="39">
         <f>IF(G41=0,"",COUNTIF('공수2'!$O$7:$O$86,3))</f>
         <v/>
       </c>
-      <c r="R41" s="38">
+      <c r="R41" s="39">
         <f>IF(G41=0,"",COUNTIF('공수2'!$O$7:$O$86,4))</f>
         <v/>
       </c>
-      <c r="S41" s="38">
+      <c r="S41" s="39">
         <f>IF(G41=0,"",COUNTIF('공수2'!$O$7:$O$86,5))</f>
         <v/>
       </c>
@@ -25826,7 +25841,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C42" s="38">
+      <c r="C42" s="39">
         <f>'공수2'!P4</f>
         <v/>
       </c>
@@ -25838,7 +25853,7 @@
         <f>'공수2'!P3</f>
         <v/>
       </c>
-      <c r="F42" s="39">
+      <c r="F42" s="40">
         <f>IF('공수2'!$P$2="","",'공수2'!$P$2)</f>
         <v/>
       </c>
@@ -25850,47 +25865,47 @@
         <f>IF(F42="","",SUMPRODUCT(('공수2'!$P$7:$P$86='공수2'!$P$2)*('공수2'!$P$7:$P$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I42" s="40">
+      <c r="I42" s="41">
         <f>IF(OR(F42="",G42=0),"",H42/G42)</f>
         <v/>
       </c>
-      <c r="J42" s="41">
+      <c r="J42" s="42">
         <f>IF(F42="","",IFERROR(SUMPRODUCT(('공수2'!$P$7:$P$86='공수2'!$P$2)*('공수2'!$P$7:$P$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K42" s="41">
+      <c r="K42" s="42">
         <f>IF(F42="","",IFERROR(SUMPRODUCT(('공수2'!$P$7:$P$86='공수2'!$P$2)*('공수2'!$P$7:$P$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L42" s="41">
+      <c r="L42" s="42">
         <f>IF(F42="","",IFERROR(SUMPRODUCT(('공수2'!$P$7:$P$86='공수2'!$P$2)*('공수2'!$P$7:$P$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M42" s="42">
+      <c r="M42" s="43">
         <f>IF(OR(J42="",L42=""),"",J42-L42)</f>
         <v/>
       </c>
-      <c r="N42" s="38">
+      <c r="N42" s="39">
         <f>IF(I42="","",IF(AND(M42&lt;&gt;"",M42&lt;0),"역변별·문항검토",IF(I42&gt;=0.9,"매우 쉬움",IF(I42&lt;=0.15,"매우 어려움",IF(AND(M42&lt;&gt;"",M42&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O42" s="38">
+      <c r="O42" s="39">
         <f>IF(G42=0,"",COUNTIF('공수2'!$P$7:$P$86,1))</f>
         <v/>
       </c>
-      <c r="P42" s="38">
+      <c r="P42" s="39">
         <f>IF(G42=0,"",COUNTIF('공수2'!$P$7:$P$86,2))</f>
         <v/>
       </c>
-      <c r="Q42" s="38">
+      <c r="Q42" s="39">
         <f>IF(G42=0,"",COUNTIF('공수2'!$P$7:$P$86,3))</f>
         <v/>
       </c>
-      <c r="R42" s="38">
+      <c r="R42" s="39">
         <f>IF(G42=0,"",COUNTIF('공수2'!$P$7:$P$86,4))</f>
         <v/>
       </c>
-      <c r="S42" s="38">
+      <c r="S42" s="39">
         <f>IF(G42=0,"",COUNTIF('공수2'!$P$7:$P$86,5))</f>
         <v/>
       </c>
@@ -25904,7 +25919,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C43" s="38">
+      <c r="C43" s="39">
         <f>'공수2'!Q4</f>
         <v/>
       </c>
@@ -25916,7 +25931,7 @@
         <f>'공수2'!Q3</f>
         <v/>
       </c>
-      <c r="F43" s="39">
+      <c r="F43" s="40">
         <f>IF('공수2'!$Q$2="","",'공수2'!$Q$2)</f>
         <v/>
       </c>
@@ -25928,47 +25943,47 @@
         <f>IF(F43="","",SUMPRODUCT(('공수2'!$Q$7:$Q$86='공수2'!$Q$2)*('공수2'!$Q$7:$Q$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I43" s="40">
+      <c r="I43" s="41">
         <f>IF(OR(F43="",G43=0),"",H43/G43)</f>
         <v/>
       </c>
-      <c r="J43" s="41">
+      <c r="J43" s="42">
         <f>IF(F43="","",IFERROR(SUMPRODUCT(('공수2'!$Q$7:$Q$86='공수2'!$Q$2)*('공수2'!$Q$7:$Q$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K43" s="41">
+      <c r="K43" s="42">
         <f>IF(F43="","",IFERROR(SUMPRODUCT(('공수2'!$Q$7:$Q$86='공수2'!$Q$2)*('공수2'!$Q$7:$Q$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L43" s="41">
+      <c r="L43" s="42">
         <f>IF(F43="","",IFERROR(SUMPRODUCT(('공수2'!$Q$7:$Q$86='공수2'!$Q$2)*('공수2'!$Q$7:$Q$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M43" s="42">
+      <c r="M43" s="43">
         <f>IF(OR(J43="",L43=""),"",J43-L43)</f>
         <v/>
       </c>
-      <c r="N43" s="38">
+      <c r="N43" s="39">
         <f>IF(I43="","",IF(AND(M43&lt;&gt;"",M43&lt;0),"역변별·문항검토",IF(I43&gt;=0.9,"매우 쉬움",IF(I43&lt;=0.15,"매우 어려움",IF(AND(M43&lt;&gt;"",M43&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O43" s="38">
+      <c r="O43" s="39">
         <f>IF(G43=0,"",COUNTIF('공수2'!$Q$7:$Q$86,1))</f>
         <v/>
       </c>
-      <c r="P43" s="38">
+      <c r="P43" s="39">
         <f>IF(G43=0,"",COUNTIF('공수2'!$Q$7:$Q$86,2))</f>
         <v/>
       </c>
-      <c r="Q43" s="38">
+      <c r="Q43" s="39">
         <f>IF(G43=0,"",COUNTIF('공수2'!$Q$7:$Q$86,3))</f>
         <v/>
       </c>
-      <c r="R43" s="38">
+      <c r="R43" s="39">
         <f>IF(G43=0,"",COUNTIF('공수2'!$Q$7:$Q$86,4))</f>
         <v/>
       </c>
-      <c r="S43" s="38">
+      <c r="S43" s="39">
         <f>IF(G43=0,"",COUNTIF('공수2'!$Q$7:$Q$86,5))</f>
         <v/>
       </c>
@@ -25982,7 +25997,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C44" s="38">
+      <c r="C44" s="39">
         <f>'공수2'!R4</f>
         <v/>
       </c>
@@ -25994,8 +26009,8 @@
         <f>'공수2'!R3</f>
         <v/>
       </c>
-      <c r="F44" s="39">
-        <f>IF('공수2'!$R$2="","",'공수2'!$R$2)</f>
+      <c r="F44" s="40">
+        <f>IF('공수2'!$R$2="","","9")</f>
         <v/>
       </c>
       <c r="G44" s="10">
@@ -26006,51 +26021,51 @@
         <f>IF(F44="","",SUMPRODUCT(('공수2'!$R$7:$R$86='공수2'!$R$2)*('공수2'!$R$7:$R$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I44" s="40">
+      <c r="I44" s="41">
         <f>IF(OR(F44="",G44=0),"",H44/G44)</f>
         <v/>
       </c>
-      <c r="J44" s="41">
+      <c r="J44" s="42">
         <f>IF(F44="","",IFERROR(SUMPRODUCT(('공수2'!$R$7:$R$86='공수2'!$R$2)*('공수2'!$R$7:$R$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K44" s="41">
+      <c r="K44" s="42">
         <f>IF(F44="","",IFERROR(SUMPRODUCT(('공수2'!$R$7:$R$86='공수2'!$R$2)*('공수2'!$R$7:$R$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L44" s="41">
+      <c r="L44" s="42">
         <f>IF(F44="","",IFERROR(SUMPRODUCT(('공수2'!$R$7:$R$86='공수2'!$R$2)*('공수2'!$R$7:$R$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M44" s="42">
+      <c r="M44" s="43">
         <f>IF(OR(J44="",L44=""),"",J44-L44)</f>
         <v/>
       </c>
-      <c r="N44" s="38">
+      <c r="N44" s="39">
         <f>IF(I44="","",IF(AND(M44&lt;&gt;"",M44&lt;0),"역변별·문항검토",IF(I44&gt;=0.9,"매우 쉬움",IF(I44&lt;=0.15,"매우 어려움",IF(AND(M44&lt;&gt;"",M44&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O44" s="43" t="inlineStr">
+      <c r="O44" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P44" s="43" t="inlineStr">
+      <c r="P44" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q44" s="43" t="inlineStr">
+      <c r="Q44" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R44" s="43" t="inlineStr">
+      <c r="R44" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S44" s="43" t="inlineStr">
+      <c r="S44" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -26065,7 +26080,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C45" s="38">
+      <c r="C45" s="39">
         <f>'공수2'!S4</f>
         <v/>
       </c>
@@ -26077,8 +26092,8 @@
         <f>'공수2'!S3</f>
         <v/>
       </c>
-      <c r="F45" s="39">
-        <f>IF('공수2'!$S$2="","",'공수2'!$S$2)</f>
+      <c r="F45" s="40">
+        <f>IF('공수2'!$S$2="","","160")</f>
         <v/>
       </c>
       <c r="G45" s="10">
@@ -26089,51 +26104,51 @@
         <f>IF(F45="","",SUMPRODUCT(('공수2'!$S$7:$S$86='공수2'!$S$2)*('공수2'!$S$7:$S$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I45" s="40">
+      <c r="I45" s="41">
         <f>IF(OR(F45="",G45=0),"",H45/G45)</f>
         <v/>
       </c>
-      <c r="J45" s="41">
+      <c r="J45" s="42">
         <f>IF(F45="","",IFERROR(SUMPRODUCT(('공수2'!$S$7:$S$86='공수2'!$S$2)*('공수2'!$S$7:$S$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K45" s="41">
+      <c r="K45" s="42">
         <f>IF(F45="","",IFERROR(SUMPRODUCT(('공수2'!$S$7:$S$86='공수2'!$S$2)*('공수2'!$S$7:$S$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L45" s="41">
+      <c r="L45" s="42">
         <f>IF(F45="","",IFERROR(SUMPRODUCT(('공수2'!$S$7:$S$86='공수2'!$S$2)*('공수2'!$S$7:$S$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M45" s="42">
+      <c r="M45" s="43">
         <f>IF(OR(J45="",L45=""),"",J45-L45)</f>
         <v/>
       </c>
-      <c r="N45" s="38">
+      <c r="N45" s="39">
         <f>IF(I45="","",IF(AND(M45&lt;&gt;"",M45&lt;0),"역변별·문항검토",IF(I45&gt;=0.9,"매우 쉬움",IF(I45&lt;=0.15,"매우 어려움",IF(AND(M45&lt;&gt;"",M45&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O45" s="43" t="inlineStr">
+      <c r="O45" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P45" s="43" t="inlineStr">
+      <c r="P45" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q45" s="43" t="inlineStr">
+      <c r="Q45" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R45" s="43" t="inlineStr">
+      <c r="R45" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S45" s="43" t="inlineStr">
+      <c r="S45" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -26148,7 +26163,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C46" s="38">
+      <c r="C46" s="39">
         <f>'공수2'!T4</f>
         <v/>
       </c>
@@ -26160,8 +26175,8 @@
         <f>'공수2'!T3</f>
         <v/>
       </c>
-      <c r="F46" s="39">
-        <f>IF('공수2'!$T$2="","",'공수2'!$T$2)</f>
+      <c r="F46" s="40">
+        <f>IF('공수2'!$T$2="","","210")</f>
         <v/>
       </c>
       <c r="G46" s="10">
@@ -26172,51 +26187,51 @@
         <f>IF(F46="","",SUMPRODUCT(('공수2'!$T$7:$T$86='공수2'!$T$2)*('공수2'!$T$7:$T$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I46" s="40">
+      <c r="I46" s="41">
         <f>IF(OR(F46="",G46=0),"",H46/G46)</f>
         <v/>
       </c>
-      <c r="J46" s="41">
+      <c r="J46" s="42">
         <f>IF(F46="","",IFERROR(SUMPRODUCT(('공수2'!$T$7:$T$86='공수2'!$T$2)*('공수2'!$T$7:$T$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K46" s="41">
+      <c r="K46" s="42">
         <f>IF(F46="","",IFERROR(SUMPRODUCT(('공수2'!$T$7:$T$86='공수2'!$T$2)*('공수2'!$T$7:$T$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L46" s="41">
+      <c r="L46" s="42">
         <f>IF(F46="","",IFERROR(SUMPRODUCT(('공수2'!$T$7:$T$86='공수2'!$T$2)*('공수2'!$T$7:$T$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M46" s="42">
+      <c r="M46" s="43">
         <f>IF(OR(J46="",L46=""),"",J46-L46)</f>
         <v/>
       </c>
-      <c r="N46" s="38">
+      <c r="N46" s="39">
         <f>IF(I46="","",IF(AND(M46&lt;&gt;"",M46&lt;0),"역변별·문항검토",IF(I46&gt;=0.9,"매우 쉬움",IF(I46&lt;=0.15,"매우 어려움",IF(AND(M46&lt;&gt;"",M46&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O46" s="43" t="inlineStr">
+      <c r="O46" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P46" s="43" t="inlineStr">
+      <c r="P46" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q46" s="43" t="inlineStr">
+      <c r="Q46" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R46" s="43" t="inlineStr">
+      <c r="R46" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S46" s="43" t="inlineStr">
+      <c r="S46" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -26231,7 +26246,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C47" s="38">
+      <c r="C47" s="39">
         <f>'공수2'!U4</f>
         <v/>
       </c>
@@ -26243,8 +26258,8 @@
         <f>'공수2'!U3</f>
         <v/>
       </c>
-      <c r="F47" s="39">
-        <f>IF('공수2'!$U$2="","",'공수2'!$U$2)</f>
+      <c r="F47" s="40">
+        <f>IF('공수2'!$U$2="","","40")</f>
         <v/>
       </c>
       <c r="G47" s="10">
@@ -26255,51 +26270,51 @@
         <f>IF(F47="","",SUMPRODUCT(('공수2'!$U$7:$U$86='공수2'!$U$2)*('공수2'!$U$7:$U$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I47" s="40">
+      <c r="I47" s="41">
         <f>IF(OR(F47="",G47=0),"",H47/G47)</f>
         <v/>
       </c>
-      <c r="J47" s="41">
+      <c r="J47" s="42">
         <f>IF(F47="","",IFERROR(SUMPRODUCT(('공수2'!$U$7:$U$86='공수2'!$U$2)*('공수2'!$U$7:$U$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K47" s="41">
+      <c r="K47" s="42">
         <f>IF(F47="","",IFERROR(SUMPRODUCT(('공수2'!$U$7:$U$86='공수2'!$U$2)*('공수2'!$U$7:$U$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L47" s="41">
+      <c r="L47" s="42">
         <f>IF(F47="","",IFERROR(SUMPRODUCT(('공수2'!$U$7:$U$86='공수2'!$U$2)*('공수2'!$U$7:$U$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M47" s="42">
+      <c r="M47" s="43">
         <f>IF(OR(J47="",L47=""),"",J47-L47)</f>
         <v/>
       </c>
-      <c r="N47" s="38">
+      <c r="N47" s="39">
         <f>IF(I47="","",IF(AND(M47&lt;&gt;"",M47&lt;0),"역변별·문항검토",IF(I47&gt;=0.9,"매우 쉬움",IF(I47&lt;=0.15,"매우 어려움",IF(AND(M47&lt;&gt;"",M47&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O47" s="43" t="inlineStr">
+      <c r="O47" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P47" s="43" t="inlineStr">
+      <c r="P47" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q47" s="43" t="inlineStr">
+      <c r="Q47" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R47" s="43" t="inlineStr">
+      <c r="R47" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S47" s="43" t="inlineStr">
+      <c r="S47" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -26314,7 +26329,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C48" s="38">
+      <c r="C48" s="39">
         <f>'공수2'!V4</f>
         <v/>
       </c>
@@ -26326,8 +26341,8 @@
         <f>'공수2'!V3</f>
         <v/>
       </c>
-      <c r="F48" s="39">
-        <f>IF('공수2'!$V$2="","",'공수2'!$V$2)</f>
+      <c r="F48" s="40">
+        <f>IF('공수2'!$V$2="","","15")</f>
         <v/>
       </c>
       <c r="G48" s="10">
@@ -26338,51 +26353,51 @@
         <f>IF(F48="","",SUMPRODUCT(('공수2'!$V$7:$V$86='공수2'!$V$2)*('공수2'!$V$7:$V$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I48" s="40">
+      <c r="I48" s="41">
         <f>IF(OR(F48="",G48=0),"",H48/G48)</f>
         <v/>
       </c>
-      <c r="J48" s="41">
+      <c r="J48" s="42">
         <f>IF(F48="","",IFERROR(SUMPRODUCT(('공수2'!$V$7:$V$86='공수2'!$V$2)*('공수2'!$V$7:$V$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K48" s="41">
+      <c r="K48" s="42">
         <f>IF(F48="","",IFERROR(SUMPRODUCT(('공수2'!$V$7:$V$86='공수2'!$V$2)*('공수2'!$V$7:$V$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L48" s="41">
+      <c r="L48" s="42">
         <f>IF(F48="","",IFERROR(SUMPRODUCT(('공수2'!$V$7:$V$86='공수2'!$V$2)*('공수2'!$V$7:$V$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M48" s="42">
+      <c r="M48" s="43">
         <f>IF(OR(J48="",L48=""),"",J48-L48)</f>
         <v/>
       </c>
-      <c r="N48" s="38">
+      <c r="N48" s="39">
         <f>IF(I48="","",IF(AND(M48&lt;&gt;"",M48&lt;0),"역변별·문항검토",IF(I48&gt;=0.9,"매우 쉬움",IF(I48&lt;=0.15,"매우 어려움",IF(AND(M48&lt;&gt;"",M48&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O48" s="43" t="inlineStr">
+      <c r="O48" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P48" s="43" t="inlineStr">
+      <c r="P48" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q48" s="43" t="inlineStr">
+      <c r="Q48" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R48" s="43" t="inlineStr">
+      <c r="R48" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S48" s="43" t="inlineStr">
+      <c r="S48" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -26397,7 +26412,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C49" s="38">
+      <c r="C49" s="39">
         <f>'공수2'!W4</f>
         <v/>
       </c>
@@ -26409,8 +26424,8 @@
         <f>'공수2'!W3</f>
         <v/>
       </c>
-      <c r="F49" s="39">
-        <f>IF('공수2'!$W$2="","",'공수2'!$W$2)</f>
+      <c r="F49" s="40">
+        <f>IF('공수2'!$W$2="","","13")</f>
         <v/>
       </c>
       <c r="G49" s="10">
@@ -26421,51 +26436,51 @@
         <f>IF(F49="","",SUMPRODUCT(('공수2'!$W$7:$W$86='공수2'!$W$2)*('공수2'!$W$7:$W$86&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I49" s="40">
+      <c r="I49" s="41">
         <f>IF(OR(F49="",G49=0),"",H49/G49)</f>
         <v/>
       </c>
-      <c r="J49" s="41">
+      <c r="J49" s="42">
         <f>IF(F49="","",IFERROR(SUMPRODUCT(('공수2'!$W$7:$W$86='공수2'!$W$2)*('공수2'!$W$7:$W$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$6,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K49" s="41">
+      <c r="K49" s="42">
         <f>IF(F49="","",IFERROR(SUMPRODUCT(('공수2'!$W$7:$W$86='공수2'!$W$2)*('공수2'!$W$7:$W$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$7,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L49" s="41">
+      <c r="L49" s="42">
         <f>IF(F49="","",IFERROR(SUMPRODUCT(('공수2'!$W$7:$W$86='공수2'!$W$2)*('공수2'!$W$7:$W$86&lt;&gt;"")*('반배정'!$K$7:$K$86='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$86,'설정'!$B$8,'공수2'!$Y$7:$Y$86,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M49" s="42">
+      <c r="M49" s="43">
         <f>IF(OR(J49="",L49=""),"",J49-L49)</f>
         <v/>
       </c>
-      <c r="N49" s="38">
+      <c r="N49" s="39">
         <f>IF(I49="","",IF(AND(M49&lt;&gt;"",M49&lt;0),"역변별·문항검토",IF(I49&gt;=0.9,"매우 쉬움",IF(I49&lt;=0.15,"매우 어려움",IF(AND(M49&lt;&gt;"",M49&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O49" s="43" t="inlineStr">
+      <c r="O49" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P49" s="43" t="inlineStr">
+      <c r="P49" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q49" s="43" t="inlineStr">
+      <c r="Q49" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R49" s="43" t="inlineStr">
+      <c r="R49" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S49" s="43" t="inlineStr">
+      <c r="S49" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -8109,13 +8109,13 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>4</v>
@@ -8136,7 +8136,7 @@
         <v>5</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N3" s="7" t="n">
         <v>6</v>
@@ -8148,19 +8148,19 @@
         <v>6</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R3" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" s="7" t="n">
         <v>5</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V3" s="7" t="n">
         <v>6</v>
@@ -8207,82 +8207,82 @@
       </c>
       <c r="F4" s="22" t="inlineStr">
         <is>
+          <t>도형의 방정식</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>도형의 방정식</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>도형의 방정식</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
+        <is>
+          <t>집합과 명제</t>
+        </is>
+      </c>
+      <c r="J4" s="22" t="inlineStr">
+        <is>
+          <t>집합과 명제</t>
+        </is>
+      </c>
+      <c r="K4" s="22" t="inlineStr">
+        <is>
+          <t>도형의 방정식</t>
+        </is>
+      </c>
+      <c r="L4" s="22" t="inlineStr">
+        <is>
+          <t>도형의 방정식</t>
+        </is>
+      </c>
+      <c r="M4" s="22" t="inlineStr">
+        <is>
           <t>함수와 그래프</t>
         </is>
       </c>
-      <c r="G4" s="22" t="inlineStr">
+      <c r="N4" s="22" t="inlineStr">
+        <is>
+          <t>함수와 그래프</t>
+        </is>
+      </c>
+      <c r="O4" s="22" t="inlineStr">
+        <is>
+          <t>함수와 그래프</t>
+        </is>
+      </c>
+      <c r="P4" s="22" t="inlineStr">
         <is>
           <t>도형의 방정식</t>
         </is>
       </c>
-      <c r="H4" s="22" t="inlineStr">
+      <c r="Q4" s="22" t="inlineStr">
         <is>
           <t>도형의 방정식</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="R4" s="22" t="inlineStr">
         <is>
           <t>집합과 명제</t>
         </is>
       </c>
-      <c r="J4" s="22" t="inlineStr">
+      <c r="S4" s="22" t="inlineStr">
+        <is>
+          <t>도형의 방정식</t>
+        </is>
+      </c>
+      <c r="T4" s="22" t="inlineStr">
         <is>
           <t>집합과 명제</t>
         </is>
       </c>
-      <c r="K4" s="22" t="inlineStr">
-        <is>
-          <t>도형의 방정식</t>
-        </is>
-      </c>
-      <c r="L4" s="22" t="inlineStr">
+      <c r="U4" s="22" t="inlineStr">
         <is>
           <t>함수와 그래프</t>
-        </is>
-      </c>
-      <c r="M4" s="22" t="inlineStr">
-        <is>
-          <t>함수와 그래프</t>
-        </is>
-      </c>
-      <c r="N4" s="22" t="inlineStr">
-        <is>
-          <t>도형의 방정식</t>
-        </is>
-      </c>
-      <c r="O4" s="22" t="inlineStr">
-        <is>
-          <t>함수와 그래프</t>
-        </is>
-      </c>
-      <c r="P4" s="22" t="inlineStr">
-        <is>
-          <t>도형의 방정식</t>
-        </is>
-      </c>
-      <c r="Q4" s="22" t="inlineStr">
-        <is>
-          <t>도형의 방정식</t>
-        </is>
-      </c>
-      <c r="R4" s="22" t="inlineStr">
-        <is>
-          <t>집합과 명제</t>
-        </is>
-      </c>
-      <c r="S4" s="22" t="inlineStr">
-        <is>
-          <t>도형의 방정식</t>
-        </is>
-      </c>
-      <c r="T4" s="22" t="inlineStr">
-        <is>
-          <t>함수와 그래프</t>
-        </is>
-      </c>
-      <c r="U4" s="22" t="inlineStr">
-        <is>
-          <t>집합과 명제</t>
         </is>
       </c>
       <c r="V4" s="22" t="inlineStr">
@@ -8546,14 +8546,14 @@
         <is>
           <t>17
 단답형
-답 210</t>
+답 12</t>
         </is>
       </c>
       <c r="U6" s="25" t="inlineStr">
         <is>
           <t>18
 단답형
-답 40</t>
+답 14</t>
         </is>
       </c>
       <c r="V6" s="25" t="inlineStr">
@@ -26176,7 +26176,7 @@
         <v/>
       </c>
       <c r="F46" s="40">
-        <f>IF('공수2'!$T$2="","","210")</f>
+        <f>IF('공수2'!$T$2="","","12")</f>
         <v/>
       </c>
       <c r="G46" s="10">
@@ -26259,7 +26259,7 @@
         <v/>
       </c>
       <c r="F47" s="40">
-        <f>IF('공수2'!$U$2="","","40")</f>
+        <f>IF('공수2'!$U$2="","","14")</f>
         <v/>
       </c>
       <c r="G47" s="10">

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -8339,14 +8339,14 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
           <t>중상</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>중상</t>
-        </is>
-      </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
           <t>상</t>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>최상</t>
+          <t>상</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -1810,8 +1810,14 @@
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
+      <c r="I7" s="8">
+        <f>IF('공수1'!Y7="","",'공수1'!Y7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="8">
+        <f>IF('공수2'!Y7="","",'공수2'!Y7)</f>
+        <v/>
+      </c>
       <c r="K7" s="7" t="n"/>
     </row>
     <row r="8">
@@ -1825,8 +1831,14 @@
       <c r="F8" s="16" t="n"/>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
+      <c r="I8" s="8">
+        <f>IF('공수1'!Y8="","",'공수1'!Y8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="8">
+        <f>IF('공수2'!Y8="","",'공수2'!Y8)</f>
+        <v/>
+      </c>
       <c r="K8" s="7" t="n"/>
     </row>
     <row r="9">
@@ -1840,8 +1852,14 @@
       <c r="F9" s="16" t="n"/>
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
+      <c r="I9" s="8">
+        <f>IF('공수1'!Y9="","",'공수1'!Y9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="8">
+        <f>IF('공수2'!Y9="","",'공수2'!Y9)</f>
+        <v/>
+      </c>
       <c r="K9" s="7" t="n"/>
     </row>
     <row r="10">
@@ -1855,8 +1873,14 @@
       <c r="F10" s="16" t="n"/>
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
+      <c r="I10" s="8">
+        <f>IF('공수1'!Y10="","",'공수1'!Y10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="8">
+        <f>IF('공수2'!Y10="","",'공수2'!Y10)</f>
+        <v/>
+      </c>
       <c r="K10" s="7" t="n"/>
     </row>
     <row r="11">
@@ -1870,8 +1894,14 @@
       <c r="F11" s="16" t="n"/>
       <c r="G11" s="7" t="n"/>
       <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
+      <c r="I11" s="8">
+        <f>IF('공수1'!Y11="","",'공수1'!Y11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="8">
+        <f>IF('공수2'!Y11="","",'공수2'!Y11)</f>
+        <v/>
+      </c>
       <c r="K11" s="7" t="n"/>
     </row>
     <row r="12">
@@ -1885,8 +1915,14 @@
       <c r="F12" s="16" t="n"/>
       <c r="G12" s="7" t="n"/>
       <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
+      <c r="I12" s="8">
+        <f>IF('공수1'!Y12="","",'공수1'!Y12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="8">
+        <f>IF('공수2'!Y12="","",'공수2'!Y12)</f>
+        <v/>
+      </c>
       <c r="K12" s="7" t="n"/>
     </row>
     <row r="13">
@@ -1900,8 +1936,14 @@
       <c r="F13" s="16" t="n"/>
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
+      <c r="I13" s="8">
+        <f>IF('공수1'!Y13="","",'공수1'!Y13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="8">
+        <f>IF('공수2'!Y13="","",'공수2'!Y13)</f>
+        <v/>
+      </c>
       <c r="K13" s="7" t="n"/>
     </row>
     <row r="14">
@@ -1915,8 +1957,14 @@
       <c r="F14" s="16" t="n"/>
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
+      <c r="I14" s="8">
+        <f>IF('공수1'!Y14="","",'공수1'!Y14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="8">
+        <f>IF('공수2'!Y14="","",'공수2'!Y14)</f>
+        <v/>
+      </c>
       <c r="K14" s="7" t="n"/>
     </row>
     <row r="15">
@@ -1930,8 +1978,14 @@
       <c r="F15" s="16" t="n"/>
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
+      <c r="I15" s="8">
+        <f>IF('공수1'!Y15="","",'공수1'!Y15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="8">
+        <f>IF('공수2'!Y15="","",'공수2'!Y15)</f>
+        <v/>
+      </c>
       <c r="K15" s="7" t="n"/>
     </row>
     <row r="16">
@@ -1945,8 +1999,14 @@
       <c r="F16" s="16" t="n"/>
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
+      <c r="I16" s="8">
+        <f>IF('공수1'!Y16="","",'공수1'!Y16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="8">
+        <f>IF('공수2'!Y16="","",'공수2'!Y16)</f>
+        <v/>
+      </c>
       <c r="K16" s="7" t="n"/>
     </row>
     <row r="17">
@@ -1960,8 +2020,14 @@
       <c r="F17" s="16" t="n"/>
       <c r="G17" s="7" t="n"/>
       <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
+      <c r="I17" s="8">
+        <f>IF('공수1'!Y17="","",'공수1'!Y17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="8">
+        <f>IF('공수2'!Y17="","",'공수2'!Y17)</f>
+        <v/>
+      </c>
       <c r="K17" s="7" t="n"/>
     </row>
     <row r="18">
@@ -1975,8 +2041,14 @@
       <c r="F18" s="16" t="n"/>
       <c r="G18" s="7" t="n"/>
       <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-      <c r="J18" s="7" t="n"/>
+      <c r="I18" s="8">
+        <f>IF('공수1'!Y18="","",'공수1'!Y18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="8">
+        <f>IF('공수2'!Y18="","",'공수2'!Y18)</f>
+        <v/>
+      </c>
       <c r="K18" s="7" t="n"/>
     </row>
     <row r="19">
@@ -1990,8 +2062,14 @@
       <c r="F19" s="16" t="n"/>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
+      <c r="I19" s="8">
+        <f>IF('공수1'!Y19="","",'공수1'!Y19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="8">
+        <f>IF('공수2'!Y19="","",'공수2'!Y19)</f>
+        <v/>
+      </c>
       <c r="K19" s="7" t="n"/>
     </row>
     <row r="20">
@@ -2005,8 +2083,14 @@
       <c r="F20" s="16" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
+      <c r="I20" s="8">
+        <f>IF('공수1'!Y20="","",'공수1'!Y20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="8">
+        <f>IF('공수2'!Y20="","",'공수2'!Y20)</f>
+        <v/>
+      </c>
       <c r="K20" s="7" t="n"/>
     </row>
     <row r="21">
@@ -2020,8 +2104,14 @@
       <c r="F21" s="16" t="n"/>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
+      <c r="I21" s="8">
+        <f>IF('공수1'!Y21="","",'공수1'!Y21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="8">
+        <f>IF('공수2'!Y21="","",'공수2'!Y21)</f>
+        <v/>
+      </c>
       <c r="K21" s="7" t="n"/>
     </row>
     <row r="22">
@@ -2035,8 +2125,14 @@
       <c r="F22" s="16" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
+      <c r="I22" s="8">
+        <f>IF('공수1'!Y22="","",'공수1'!Y22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="8">
+        <f>IF('공수2'!Y22="","",'공수2'!Y22)</f>
+        <v/>
+      </c>
       <c r="K22" s="7" t="n"/>
     </row>
     <row r="23">
@@ -2050,8 +2146,14 @@
       <c r="F23" s="16" t="n"/>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
+      <c r="I23" s="8">
+        <f>IF('공수1'!Y23="","",'공수1'!Y23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="8">
+        <f>IF('공수2'!Y23="","",'공수2'!Y23)</f>
+        <v/>
+      </c>
       <c r="K23" s="7" t="n"/>
     </row>
     <row r="24">
@@ -2065,8 +2167,14 @@
       <c r="F24" s="16" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
-      <c r="I24" s="7" t="n"/>
-      <c r="J24" s="7" t="n"/>
+      <c r="I24" s="8">
+        <f>IF('공수1'!Y24="","",'공수1'!Y24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="8">
+        <f>IF('공수2'!Y24="","",'공수2'!Y24)</f>
+        <v/>
+      </c>
       <c r="K24" s="7" t="n"/>
     </row>
     <row r="25">
@@ -2080,8 +2188,14 @@
       <c r="F25" s="16" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
-      <c r="I25" s="7" t="n"/>
-      <c r="J25" s="7" t="n"/>
+      <c r="I25" s="8">
+        <f>IF('공수1'!Y25="","",'공수1'!Y25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="8">
+        <f>IF('공수2'!Y25="","",'공수2'!Y25)</f>
+        <v/>
+      </c>
       <c r="K25" s="7" t="n"/>
     </row>
     <row r="26">
@@ -2095,8 +2209,14 @@
       <c r="F26" s="16" t="n"/>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
-      <c r="I26" s="7" t="n"/>
-      <c r="J26" s="7" t="n"/>
+      <c r="I26" s="8">
+        <f>IF('공수1'!Y26="","",'공수1'!Y26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="8">
+        <f>IF('공수2'!Y26="","",'공수2'!Y26)</f>
+        <v/>
+      </c>
       <c r="K26" s="7" t="n"/>
     </row>
     <row r="27">
@@ -2110,8 +2230,14 @@
       <c r="F27" s="16" t="n"/>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
-      <c r="I27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
+      <c r="I27" s="8">
+        <f>IF('공수1'!Y27="","",'공수1'!Y27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="8">
+        <f>IF('공수2'!Y27="","",'공수2'!Y27)</f>
+        <v/>
+      </c>
       <c r="K27" s="7" t="n"/>
     </row>
     <row r="28">
@@ -2125,8 +2251,14 @@
       <c r="F28" s="16" t="n"/>
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="n"/>
-      <c r="I28" s="7" t="n"/>
-      <c r="J28" s="7" t="n"/>
+      <c r="I28" s="8">
+        <f>IF('공수1'!Y28="","",'공수1'!Y28)</f>
+        <v/>
+      </c>
+      <c r="J28" s="8">
+        <f>IF('공수2'!Y28="","",'공수2'!Y28)</f>
+        <v/>
+      </c>
       <c r="K28" s="7" t="n"/>
     </row>
     <row r="29">
@@ -2140,8 +2272,14 @@
       <c r="F29" s="16" t="n"/>
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="7" t="n"/>
-      <c r="I29" s="7" t="n"/>
-      <c r="J29" s="7" t="n"/>
+      <c r="I29" s="8">
+        <f>IF('공수1'!Y29="","",'공수1'!Y29)</f>
+        <v/>
+      </c>
+      <c r="J29" s="8">
+        <f>IF('공수2'!Y29="","",'공수2'!Y29)</f>
+        <v/>
+      </c>
       <c r="K29" s="7" t="n"/>
     </row>
     <row r="30">
@@ -2155,8 +2293,14 @@
       <c r="F30" s="16" t="n"/>
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
+      <c r="I30" s="8">
+        <f>IF('공수1'!Y30="","",'공수1'!Y30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="8">
+        <f>IF('공수2'!Y30="","",'공수2'!Y30)</f>
+        <v/>
+      </c>
       <c r="K30" s="7" t="n"/>
     </row>
     <row r="31">
@@ -2170,8 +2314,14 @@
       <c r="F31" s="16" t="n"/>
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="7" t="n"/>
-      <c r="I31" s="7" t="n"/>
-      <c r="J31" s="7" t="n"/>
+      <c r="I31" s="8">
+        <f>IF('공수1'!Y31="","",'공수1'!Y31)</f>
+        <v/>
+      </c>
+      <c r="J31" s="8">
+        <f>IF('공수2'!Y31="","",'공수2'!Y31)</f>
+        <v/>
+      </c>
       <c r="K31" s="7" t="n"/>
     </row>
     <row r="32">
@@ -2185,8 +2335,14 @@
       <c r="F32" s="16" t="n"/>
       <c r="G32" s="7" t="n"/>
       <c r="H32" s="7" t="n"/>
-      <c r="I32" s="7" t="n"/>
-      <c r="J32" s="7" t="n"/>
+      <c r="I32" s="8">
+        <f>IF('공수1'!Y32="","",'공수1'!Y32)</f>
+        <v/>
+      </c>
+      <c r="J32" s="8">
+        <f>IF('공수2'!Y32="","",'공수2'!Y32)</f>
+        <v/>
+      </c>
       <c r="K32" s="7" t="n"/>
     </row>
     <row r="33">
@@ -2200,8 +2356,14 @@
       <c r="F33" s="16" t="n"/>
       <c r="G33" s="7" t="n"/>
       <c r="H33" s="7" t="n"/>
-      <c r="I33" s="7" t="n"/>
-      <c r="J33" s="7" t="n"/>
+      <c r="I33" s="8">
+        <f>IF('공수1'!Y33="","",'공수1'!Y33)</f>
+        <v/>
+      </c>
+      <c r="J33" s="8">
+        <f>IF('공수2'!Y33="","",'공수2'!Y33)</f>
+        <v/>
+      </c>
       <c r="K33" s="7" t="n"/>
     </row>
     <row r="34">
@@ -2215,8 +2377,14 @@
       <c r="F34" s="16" t="n"/>
       <c r="G34" s="7" t="n"/>
       <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n"/>
-      <c r="J34" s="7" t="n"/>
+      <c r="I34" s="8">
+        <f>IF('공수1'!Y34="","",'공수1'!Y34)</f>
+        <v/>
+      </c>
+      <c r="J34" s="8">
+        <f>IF('공수2'!Y34="","",'공수2'!Y34)</f>
+        <v/>
+      </c>
       <c r="K34" s="7" t="n"/>
     </row>
     <row r="35">
@@ -2230,8 +2398,14 @@
       <c r="F35" s="16" t="n"/>
       <c r="G35" s="7" t="n"/>
       <c r="H35" s="7" t="n"/>
-      <c r="I35" s="7" t="n"/>
-      <c r="J35" s="7" t="n"/>
+      <c r="I35" s="8">
+        <f>IF('공수1'!Y35="","",'공수1'!Y35)</f>
+        <v/>
+      </c>
+      <c r="J35" s="8">
+        <f>IF('공수2'!Y35="","",'공수2'!Y35)</f>
+        <v/>
+      </c>
       <c r="K35" s="7" t="n"/>
     </row>
     <row r="36">
@@ -2245,8 +2419,14 @@
       <c r="F36" s="16" t="n"/>
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="7" t="n"/>
-      <c r="I36" s="7" t="n"/>
-      <c r="J36" s="7" t="n"/>
+      <c r="I36" s="8">
+        <f>IF('공수1'!Y36="","",'공수1'!Y36)</f>
+        <v/>
+      </c>
+      <c r="J36" s="8">
+        <f>IF('공수2'!Y36="","",'공수2'!Y36)</f>
+        <v/>
+      </c>
       <c r="K36" s="7" t="n"/>
     </row>
     <row r="37">
@@ -2260,8 +2440,14 @@
       <c r="F37" s="16" t="n"/>
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="7" t="n"/>
-      <c r="I37" s="7" t="n"/>
-      <c r="J37" s="7" t="n"/>
+      <c r="I37" s="8">
+        <f>IF('공수1'!Y37="","",'공수1'!Y37)</f>
+        <v/>
+      </c>
+      <c r="J37" s="8">
+        <f>IF('공수2'!Y37="","",'공수2'!Y37)</f>
+        <v/>
+      </c>
       <c r="K37" s="7" t="n"/>
     </row>
     <row r="38">
@@ -2275,8 +2461,14 @@
       <c r="F38" s="16" t="n"/>
       <c r="G38" s="7" t="n"/>
       <c r="H38" s="7" t="n"/>
-      <c r="I38" s="7" t="n"/>
-      <c r="J38" s="7" t="n"/>
+      <c r="I38" s="8">
+        <f>IF('공수1'!Y38="","",'공수1'!Y38)</f>
+        <v/>
+      </c>
+      <c r="J38" s="8">
+        <f>IF('공수2'!Y38="","",'공수2'!Y38)</f>
+        <v/>
+      </c>
       <c r="K38" s="7" t="n"/>
     </row>
     <row r="39">
@@ -2290,8 +2482,14 @@
       <c r="F39" s="16" t="n"/>
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="7" t="n"/>
-      <c r="I39" s="7" t="n"/>
-      <c r="J39" s="7" t="n"/>
+      <c r="I39" s="8">
+        <f>IF('공수1'!Y39="","",'공수1'!Y39)</f>
+        <v/>
+      </c>
+      <c r="J39" s="8">
+        <f>IF('공수2'!Y39="","",'공수2'!Y39)</f>
+        <v/>
+      </c>
       <c r="K39" s="7" t="n"/>
     </row>
     <row r="40">
@@ -2305,8 +2503,14 @@
       <c r="F40" s="16" t="n"/>
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="7" t="n"/>
-      <c r="I40" s="7" t="n"/>
-      <c r="J40" s="7" t="n"/>
+      <c r="I40" s="8">
+        <f>IF('공수1'!Y40="","",'공수1'!Y40)</f>
+        <v/>
+      </c>
+      <c r="J40" s="8">
+        <f>IF('공수2'!Y40="","",'공수2'!Y40)</f>
+        <v/>
+      </c>
       <c r="K40" s="7" t="n"/>
     </row>
     <row r="41">
@@ -2320,8 +2524,14 @@
       <c r="F41" s="16" t="n"/>
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="7" t="n"/>
-      <c r="I41" s="7" t="n"/>
-      <c r="J41" s="7" t="n"/>
+      <c r="I41" s="8">
+        <f>IF('공수1'!Y41="","",'공수1'!Y41)</f>
+        <v/>
+      </c>
+      <c r="J41" s="8">
+        <f>IF('공수2'!Y41="","",'공수2'!Y41)</f>
+        <v/>
+      </c>
       <c r="K41" s="7" t="n"/>
     </row>
     <row r="42">
@@ -2335,8 +2545,14 @@
       <c r="F42" s="16" t="n"/>
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="7" t="n"/>
-      <c r="I42" s="7" t="n"/>
-      <c r="J42" s="7" t="n"/>
+      <c r="I42" s="8">
+        <f>IF('공수1'!Y42="","",'공수1'!Y42)</f>
+        <v/>
+      </c>
+      <c r="J42" s="8">
+        <f>IF('공수2'!Y42="","",'공수2'!Y42)</f>
+        <v/>
+      </c>
       <c r="K42" s="7" t="n"/>
     </row>
     <row r="43">
@@ -2350,8 +2566,14 @@
       <c r="F43" s="16" t="n"/>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
-      <c r="I43" s="7" t="n"/>
-      <c r="J43" s="7" t="n"/>
+      <c r="I43" s="8">
+        <f>IF('공수1'!Y43="","",'공수1'!Y43)</f>
+        <v/>
+      </c>
+      <c r="J43" s="8">
+        <f>IF('공수2'!Y43="","",'공수2'!Y43)</f>
+        <v/>
+      </c>
       <c r="K43" s="7" t="n"/>
     </row>
     <row r="44">
@@ -2365,8 +2587,14 @@
       <c r="F44" s="16" t="n"/>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="7" t="n"/>
-      <c r="I44" s="7" t="n"/>
-      <c r="J44" s="7" t="n"/>
+      <c r="I44" s="8">
+        <f>IF('공수1'!Y44="","",'공수1'!Y44)</f>
+        <v/>
+      </c>
+      <c r="J44" s="8">
+        <f>IF('공수2'!Y44="","",'공수2'!Y44)</f>
+        <v/>
+      </c>
       <c r="K44" s="7" t="n"/>
     </row>
     <row r="45">
@@ -2380,8 +2608,14 @@
       <c r="F45" s="16" t="n"/>
       <c r="G45" s="7" t="n"/>
       <c r="H45" s="7" t="n"/>
-      <c r="I45" s="7" t="n"/>
-      <c r="J45" s="7" t="n"/>
+      <c r="I45" s="8">
+        <f>IF('공수1'!Y45="","",'공수1'!Y45)</f>
+        <v/>
+      </c>
+      <c r="J45" s="8">
+        <f>IF('공수2'!Y45="","",'공수2'!Y45)</f>
+        <v/>
+      </c>
       <c r="K45" s="7" t="n"/>
     </row>
     <row r="46">
@@ -2395,8 +2629,14 @@
       <c r="F46" s="16" t="n"/>
       <c r="G46" s="7" t="n"/>
       <c r="H46" s="7" t="n"/>
-      <c r="I46" s="7" t="n"/>
-      <c r="J46" s="7" t="n"/>
+      <c r="I46" s="8">
+        <f>IF('공수1'!Y46="","",'공수1'!Y46)</f>
+        <v/>
+      </c>
+      <c r="J46" s="8">
+        <f>IF('공수2'!Y46="","",'공수2'!Y46)</f>
+        <v/>
+      </c>
       <c r="K46" s="7" t="n"/>
     </row>
     <row r="47">
@@ -2410,8 +2650,14 @@
       <c r="F47" s="16" t="n"/>
       <c r="G47" s="7" t="n"/>
       <c r="H47" s="7" t="n"/>
-      <c r="I47" s="7" t="n"/>
-      <c r="J47" s="7" t="n"/>
+      <c r="I47" s="8">
+        <f>IF('공수1'!Y47="","",'공수1'!Y47)</f>
+        <v/>
+      </c>
+      <c r="J47" s="8">
+        <f>IF('공수2'!Y47="","",'공수2'!Y47)</f>
+        <v/>
+      </c>
       <c r="K47" s="7" t="n"/>
     </row>
     <row r="48">
@@ -2425,8 +2671,14 @@
       <c r="F48" s="16" t="n"/>
       <c r="G48" s="7" t="n"/>
       <c r="H48" s="7" t="n"/>
-      <c r="I48" s="7" t="n"/>
-      <c r="J48" s="7" t="n"/>
+      <c r="I48" s="8">
+        <f>IF('공수1'!Y48="","",'공수1'!Y48)</f>
+        <v/>
+      </c>
+      <c r="J48" s="8">
+        <f>IF('공수2'!Y48="","",'공수2'!Y48)</f>
+        <v/>
+      </c>
       <c r="K48" s="7" t="n"/>
     </row>
     <row r="49">
@@ -2440,8 +2692,14 @@
       <c r="F49" s="16" t="n"/>
       <c r="G49" s="7" t="n"/>
       <c r="H49" s="7" t="n"/>
-      <c r="I49" s="7" t="n"/>
-      <c r="J49" s="7" t="n"/>
+      <c r="I49" s="8">
+        <f>IF('공수1'!Y49="","",'공수1'!Y49)</f>
+        <v/>
+      </c>
+      <c r="J49" s="8">
+        <f>IF('공수2'!Y49="","",'공수2'!Y49)</f>
+        <v/>
+      </c>
       <c r="K49" s="7" t="n"/>
     </row>
     <row r="50">
@@ -2455,8 +2713,14 @@
       <c r="F50" s="16" t="n"/>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
-      <c r="I50" s="7" t="n"/>
-      <c r="J50" s="7" t="n"/>
+      <c r="I50" s="8">
+        <f>IF('공수1'!Y50="","",'공수1'!Y50)</f>
+        <v/>
+      </c>
+      <c r="J50" s="8">
+        <f>IF('공수2'!Y50="","",'공수2'!Y50)</f>
+        <v/>
+      </c>
       <c r="K50" s="7" t="n"/>
     </row>
     <row r="51">
@@ -2470,8 +2734,14 @@
       <c r="F51" s="16" t="n"/>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
-      <c r="I51" s="7" t="n"/>
-      <c r="J51" s="7" t="n"/>
+      <c r="I51" s="8">
+        <f>IF('공수1'!Y51="","",'공수1'!Y51)</f>
+        <v/>
+      </c>
+      <c r="J51" s="8">
+        <f>IF('공수2'!Y51="","",'공수2'!Y51)</f>
+        <v/>
+      </c>
       <c r="K51" s="7" t="n"/>
     </row>
     <row r="52">
@@ -2485,8 +2755,14 @@
       <c r="F52" s="16" t="n"/>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
-      <c r="I52" s="7" t="n"/>
-      <c r="J52" s="7" t="n"/>
+      <c r="I52" s="8">
+        <f>IF('공수1'!Y52="","",'공수1'!Y52)</f>
+        <v/>
+      </c>
+      <c r="J52" s="8">
+        <f>IF('공수2'!Y52="","",'공수2'!Y52)</f>
+        <v/>
+      </c>
       <c r="K52" s="7" t="n"/>
     </row>
     <row r="53">
@@ -2500,8 +2776,14 @@
       <c r="F53" s="16" t="n"/>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
-      <c r="I53" s="7" t="n"/>
-      <c r="J53" s="7" t="n"/>
+      <c r="I53" s="8">
+        <f>IF('공수1'!Y53="","",'공수1'!Y53)</f>
+        <v/>
+      </c>
+      <c r="J53" s="8">
+        <f>IF('공수2'!Y53="","",'공수2'!Y53)</f>
+        <v/>
+      </c>
       <c r="K53" s="7" t="n"/>
     </row>
     <row r="54">
@@ -2515,8 +2797,14 @@
       <c r="F54" s="16" t="n"/>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
-      <c r="I54" s="7" t="n"/>
-      <c r="J54" s="7" t="n"/>
+      <c r="I54" s="8">
+        <f>IF('공수1'!Y54="","",'공수1'!Y54)</f>
+        <v/>
+      </c>
+      <c r="J54" s="8">
+        <f>IF('공수2'!Y54="","",'공수2'!Y54)</f>
+        <v/>
+      </c>
       <c r="K54" s="7" t="n"/>
     </row>
     <row r="55">
@@ -2530,8 +2818,14 @@
       <c r="F55" s="16" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
-      <c r="I55" s="7" t="n"/>
-      <c r="J55" s="7" t="n"/>
+      <c r="I55" s="8">
+        <f>IF('공수1'!Y55="","",'공수1'!Y55)</f>
+        <v/>
+      </c>
+      <c r="J55" s="8">
+        <f>IF('공수2'!Y55="","",'공수2'!Y55)</f>
+        <v/>
+      </c>
       <c r="K55" s="7" t="n"/>
     </row>
     <row r="56">
@@ -2545,8 +2839,14 @@
       <c r="F56" s="16" t="n"/>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
-      <c r="I56" s="7" t="n"/>
-      <c r="J56" s="7" t="n"/>
+      <c r="I56" s="8">
+        <f>IF('공수1'!Y56="","",'공수1'!Y56)</f>
+        <v/>
+      </c>
+      <c r="J56" s="8">
+        <f>IF('공수2'!Y56="","",'공수2'!Y56)</f>
+        <v/>
+      </c>
       <c r="K56" s="7" t="n"/>
     </row>
     <row r="57">
@@ -2560,8 +2860,14 @@
       <c r="F57" s="16" t="n"/>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
-      <c r="I57" s="7" t="n"/>
-      <c r="J57" s="7" t="n"/>
+      <c r="I57" s="8">
+        <f>IF('공수1'!Y57="","",'공수1'!Y57)</f>
+        <v/>
+      </c>
+      <c r="J57" s="8">
+        <f>IF('공수2'!Y57="","",'공수2'!Y57)</f>
+        <v/>
+      </c>
       <c r="K57" s="7" t="n"/>
     </row>
     <row r="58">
@@ -2575,8 +2881,14 @@
       <c r="F58" s="16" t="n"/>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
-      <c r="I58" s="7" t="n"/>
-      <c r="J58" s="7" t="n"/>
+      <c r="I58" s="8">
+        <f>IF('공수1'!Y58="","",'공수1'!Y58)</f>
+        <v/>
+      </c>
+      <c r="J58" s="8">
+        <f>IF('공수2'!Y58="","",'공수2'!Y58)</f>
+        <v/>
+      </c>
       <c r="K58" s="7" t="n"/>
     </row>
     <row r="59">
@@ -2590,8 +2902,14 @@
       <c r="F59" s="16" t="n"/>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
-      <c r="I59" s="7" t="n"/>
-      <c r="J59" s="7" t="n"/>
+      <c r="I59" s="8">
+        <f>IF('공수1'!Y59="","",'공수1'!Y59)</f>
+        <v/>
+      </c>
+      <c r="J59" s="8">
+        <f>IF('공수2'!Y59="","",'공수2'!Y59)</f>
+        <v/>
+      </c>
       <c r="K59" s="7" t="n"/>
     </row>
     <row r="60">
@@ -2605,8 +2923,14 @@
       <c r="F60" s="16" t="n"/>
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
-      <c r="I60" s="7" t="n"/>
-      <c r="J60" s="7" t="n"/>
+      <c r="I60" s="8">
+        <f>IF('공수1'!Y60="","",'공수1'!Y60)</f>
+        <v/>
+      </c>
+      <c r="J60" s="8">
+        <f>IF('공수2'!Y60="","",'공수2'!Y60)</f>
+        <v/>
+      </c>
       <c r="K60" s="7" t="n"/>
     </row>
     <row r="61">
@@ -2620,8 +2944,14 @@
       <c r="F61" s="16" t="n"/>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
-      <c r="I61" s="7" t="n"/>
-      <c r="J61" s="7" t="n"/>
+      <c r="I61" s="8">
+        <f>IF('공수1'!Y61="","",'공수1'!Y61)</f>
+        <v/>
+      </c>
+      <c r="J61" s="8">
+        <f>IF('공수2'!Y61="","",'공수2'!Y61)</f>
+        <v/>
+      </c>
       <c r="K61" s="7" t="n"/>
     </row>
     <row r="62">
@@ -2635,8 +2965,14 @@
       <c r="F62" s="16" t="n"/>
       <c r="G62" s="7" t="n"/>
       <c r="H62" s="7" t="n"/>
-      <c r="I62" s="7" t="n"/>
-      <c r="J62" s="7" t="n"/>
+      <c r="I62" s="8">
+        <f>IF('공수1'!Y62="","",'공수1'!Y62)</f>
+        <v/>
+      </c>
+      <c r="J62" s="8">
+        <f>IF('공수2'!Y62="","",'공수2'!Y62)</f>
+        <v/>
+      </c>
       <c r="K62" s="7" t="n"/>
     </row>
     <row r="63">
@@ -2650,8 +2986,14 @@
       <c r="F63" s="16" t="n"/>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="n"/>
-      <c r="I63" s="7" t="n"/>
-      <c r="J63" s="7" t="n"/>
+      <c r="I63" s="8">
+        <f>IF('공수1'!Y63="","",'공수1'!Y63)</f>
+        <v/>
+      </c>
+      <c r="J63" s="8">
+        <f>IF('공수2'!Y63="","",'공수2'!Y63)</f>
+        <v/>
+      </c>
       <c r="K63" s="7" t="n"/>
     </row>
     <row r="64">
@@ -2665,8 +3007,14 @@
       <c r="F64" s="16" t="n"/>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
-      <c r="I64" s="7" t="n"/>
-      <c r="J64" s="7" t="n"/>
+      <c r="I64" s="8">
+        <f>IF('공수1'!Y64="","",'공수1'!Y64)</f>
+        <v/>
+      </c>
+      <c r="J64" s="8">
+        <f>IF('공수2'!Y64="","",'공수2'!Y64)</f>
+        <v/>
+      </c>
       <c r="K64" s="7" t="n"/>
     </row>
     <row r="65">
@@ -2680,8 +3028,14 @@
       <c r="F65" s="16" t="n"/>
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="7" t="n"/>
-      <c r="I65" s="7" t="n"/>
-      <c r="J65" s="7" t="n"/>
+      <c r="I65" s="8">
+        <f>IF('공수1'!Y65="","",'공수1'!Y65)</f>
+        <v/>
+      </c>
+      <c r="J65" s="8">
+        <f>IF('공수2'!Y65="","",'공수2'!Y65)</f>
+        <v/>
+      </c>
       <c r="K65" s="7" t="n"/>
     </row>
     <row r="66">
@@ -2695,8 +3049,14 @@
       <c r="F66" s="16" t="n"/>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="n"/>
-      <c r="I66" s="7" t="n"/>
-      <c r="J66" s="7" t="n"/>
+      <c r="I66" s="8">
+        <f>IF('공수1'!Y66="","",'공수1'!Y66)</f>
+        <v/>
+      </c>
+      <c r="J66" s="8">
+        <f>IF('공수2'!Y66="","",'공수2'!Y66)</f>
+        <v/>
+      </c>
       <c r="K66" s="7" t="n"/>
     </row>
     <row r="67">
@@ -2710,8 +3070,14 @@
       <c r="F67" s="16" t="n"/>
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="n"/>
-      <c r="I67" s="7" t="n"/>
-      <c r="J67" s="7" t="n"/>
+      <c r="I67" s="8">
+        <f>IF('공수1'!Y67="","",'공수1'!Y67)</f>
+        <v/>
+      </c>
+      <c r="J67" s="8">
+        <f>IF('공수2'!Y67="","",'공수2'!Y67)</f>
+        <v/>
+      </c>
       <c r="K67" s="7" t="n"/>
     </row>
     <row r="68">
@@ -2725,8 +3091,14 @@
       <c r="F68" s="16" t="n"/>
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="n"/>
-      <c r="I68" s="7" t="n"/>
-      <c r="J68" s="7" t="n"/>
+      <c r="I68" s="8">
+        <f>IF('공수1'!Y68="","",'공수1'!Y68)</f>
+        <v/>
+      </c>
+      <c r="J68" s="8">
+        <f>IF('공수2'!Y68="","",'공수2'!Y68)</f>
+        <v/>
+      </c>
       <c r="K68" s="7" t="n"/>
     </row>
     <row r="69">
@@ -2740,8 +3112,14 @@
       <c r="F69" s="16" t="n"/>
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="7" t="n"/>
-      <c r="I69" s="7" t="n"/>
-      <c r="J69" s="7" t="n"/>
+      <c r="I69" s="8">
+        <f>IF('공수1'!Y69="","",'공수1'!Y69)</f>
+        <v/>
+      </c>
+      <c r="J69" s="8">
+        <f>IF('공수2'!Y69="","",'공수2'!Y69)</f>
+        <v/>
+      </c>
       <c r="K69" s="7" t="n"/>
     </row>
     <row r="70">
@@ -2755,8 +3133,14 @@
       <c r="F70" s="16" t="n"/>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="7" t="n"/>
-      <c r="I70" s="7" t="n"/>
-      <c r="J70" s="7" t="n"/>
+      <c r="I70" s="8">
+        <f>IF('공수1'!Y70="","",'공수1'!Y70)</f>
+        <v/>
+      </c>
+      <c r="J70" s="8">
+        <f>IF('공수2'!Y70="","",'공수2'!Y70)</f>
+        <v/>
+      </c>
       <c r="K70" s="7" t="n"/>
     </row>
     <row r="71">
@@ -2770,8 +3154,14 @@
       <c r="F71" s="16" t="n"/>
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="7" t="n"/>
-      <c r="I71" s="7" t="n"/>
-      <c r="J71" s="7" t="n"/>
+      <c r="I71" s="8">
+        <f>IF('공수1'!Y71="","",'공수1'!Y71)</f>
+        <v/>
+      </c>
+      <c r="J71" s="8">
+        <f>IF('공수2'!Y71="","",'공수2'!Y71)</f>
+        <v/>
+      </c>
       <c r="K71" s="7" t="n"/>
     </row>
     <row r="72">
@@ -2785,8 +3175,14 @@
       <c r="F72" s="16" t="n"/>
       <c r="G72" s="7" t="n"/>
       <c r="H72" s="7" t="n"/>
-      <c r="I72" s="7" t="n"/>
-      <c r="J72" s="7" t="n"/>
+      <c r="I72" s="8">
+        <f>IF('공수1'!Y72="","",'공수1'!Y72)</f>
+        <v/>
+      </c>
+      <c r="J72" s="8">
+        <f>IF('공수2'!Y72="","",'공수2'!Y72)</f>
+        <v/>
+      </c>
       <c r="K72" s="7" t="n"/>
     </row>
     <row r="73">
@@ -2800,8 +3196,14 @@
       <c r="F73" s="16" t="n"/>
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="n"/>
-      <c r="I73" s="7" t="n"/>
-      <c r="J73" s="7" t="n"/>
+      <c r="I73" s="8">
+        <f>IF('공수1'!Y73="","",'공수1'!Y73)</f>
+        <v/>
+      </c>
+      <c r="J73" s="8">
+        <f>IF('공수2'!Y73="","",'공수2'!Y73)</f>
+        <v/>
+      </c>
       <c r="K73" s="7" t="n"/>
     </row>
     <row r="74">
@@ -2815,8 +3217,14 @@
       <c r="F74" s="16" t="n"/>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
-      <c r="I74" s="7" t="n"/>
-      <c r="J74" s="7" t="n"/>
+      <c r="I74" s="8">
+        <f>IF('공수1'!Y74="","",'공수1'!Y74)</f>
+        <v/>
+      </c>
+      <c r="J74" s="8">
+        <f>IF('공수2'!Y74="","",'공수2'!Y74)</f>
+        <v/>
+      </c>
       <c r="K74" s="7" t="n"/>
     </row>
     <row r="75">
@@ -2830,8 +3238,14 @@
       <c r="F75" s="16" t="n"/>
       <c r="G75" s="7" t="n"/>
       <c r="H75" s="7" t="n"/>
-      <c r="I75" s="7" t="n"/>
-      <c r="J75" s="7" t="n"/>
+      <c r="I75" s="8">
+        <f>IF('공수1'!Y75="","",'공수1'!Y75)</f>
+        <v/>
+      </c>
+      <c r="J75" s="8">
+        <f>IF('공수2'!Y75="","",'공수2'!Y75)</f>
+        <v/>
+      </c>
       <c r="K75" s="7" t="n"/>
     </row>
     <row r="76">
@@ -2845,8 +3259,14 @@
       <c r="F76" s="16" t="n"/>
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="7" t="n"/>
-      <c r="I76" s="7" t="n"/>
-      <c r="J76" s="7" t="n"/>
+      <c r="I76" s="8">
+        <f>IF('공수1'!Y76="","",'공수1'!Y76)</f>
+        <v/>
+      </c>
+      <c r="J76" s="8">
+        <f>IF('공수2'!Y76="","",'공수2'!Y76)</f>
+        <v/>
+      </c>
       <c r="K76" s="7" t="n"/>
     </row>
     <row r="77">
@@ -2860,8 +3280,14 @@
       <c r="F77" s="16" t="n"/>
       <c r="G77" s="7" t="n"/>
       <c r="H77" s="7" t="n"/>
-      <c r="I77" s="7" t="n"/>
-      <c r="J77" s="7" t="n"/>
+      <c r="I77" s="8">
+        <f>IF('공수1'!Y77="","",'공수1'!Y77)</f>
+        <v/>
+      </c>
+      <c r="J77" s="8">
+        <f>IF('공수2'!Y77="","",'공수2'!Y77)</f>
+        <v/>
+      </c>
       <c r="K77" s="7" t="n"/>
     </row>
     <row r="78">
@@ -2875,8 +3301,14 @@
       <c r="F78" s="16" t="n"/>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="7" t="n"/>
-      <c r="I78" s="7" t="n"/>
-      <c r="J78" s="7" t="n"/>
+      <c r="I78" s="8">
+        <f>IF('공수1'!Y78="","",'공수1'!Y78)</f>
+        <v/>
+      </c>
+      <c r="J78" s="8">
+        <f>IF('공수2'!Y78="","",'공수2'!Y78)</f>
+        <v/>
+      </c>
       <c r="K78" s="7" t="n"/>
     </row>
     <row r="79">
@@ -2890,8 +3322,14 @@
       <c r="F79" s="16" t="n"/>
       <c r="G79" s="7" t="n"/>
       <c r="H79" s="7" t="n"/>
-      <c r="I79" s="7" t="n"/>
-      <c r="J79" s="7" t="n"/>
+      <c r="I79" s="8">
+        <f>IF('공수1'!Y79="","",'공수1'!Y79)</f>
+        <v/>
+      </c>
+      <c r="J79" s="8">
+        <f>IF('공수2'!Y79="","",'공수2'!Y79)</f>
+        <v/>
+      </c>
       <c r="K79" s="7" t="n"/>
     </row>
     <row r="80">
@@ -2905,8 +3343,14 @@
       <c r="F80" s="16" t="n"/>
       <c r="G80" s="7" t="n"/>
       <c r="H80" s="7" t="n"/>
-      <c r="I80" s="7" t="n"/>
-      <c r="J80" s="7" t="n"/>
+      <c r="I80" s="8">
+        <f>IF('공수1'!Y80="","",'공수1'!Y80)</f>
+        <v/>
+      </c>
+      <c r="J80" s="8">
+        <f>IF('공수2'!Y80="","",'공수2'!Y80)</f>
+        <v/>
+      </c>
       <c r="K80" s="7" t="n"/>
     </row>
     <row r="81">
@@ -2920,8 +3364,14 @@
       <c r="F81" s="16" t="n"/>
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="7" t="n"/>
-      <c r="I81" s="7" t="n"/>
-      <c r="J81" s="7" t="n"/>
+      <c r="I81" s="8">
+        <f>IF('공수1'!Y81="","",'공수1'!Y81)</f>
+        <v/>
+      </c>
+      <c r="J81" s="8">
+        <f>IF('공수2'!Y81="","",'공수2'!Y81)</f>
+        <v/>
+      </c>
       <c r="K81" s="7" t="n"/>
     </row>
     <row r="82">
@@ -2935,8 +3385,14 @@
       <c r="F82" s="16" t="n"/>
       <c r="G82" s="7" t="n"/>
       <c r="H82" s="7" t="n"/>
-      <c r="I82" s="7" t="n"/>
-      <c r="J82" s="7" t="n"/>
+      <c r="I82" s="8">
+        <f>IF('공수1'!Y82="","",'공수1'!Y82)</f>
+        <v/>
+      </c>
+      <c r="J82" s="8">
+        <f>IF('공수2'!Y82="","",'공수2'!Y82)</f>
+        <v/>
+      </c>
       <c r="K82" s="7" t="n"/>
     </row>
     <row r="83">
@@ -2950,8 +3406,14 @@
       <c r="F83" s="16" t="n"/>
       <c r="G83" s="7" t="n"/>
       <c r="H83" s="7" t="n"/>
-      <c r="I83" s="7" t="n"/>
-      <c r="J83" s="7" t="n"/>
+      <c r="I83" s="8">
+        <f>IF('공수1'!Y83="","",'공수1'!Y83)</f>
+        <v/>
+      </c>
+      <c r="J83" s="8">
+        <f>IF('공수2'!Y83="","",'공수2'!Y83)</f>
+        <v/>
+      </c>
       <c r="K83" s="7" t="n"/>
     </row>
     <row r="84">
@@ -2965,8 +3427,14 @@
       <c r="F84" s="16" t="n"/>
       <c r="G84" s="7" t="n"/>
       <c r="H84" s="7" t="n"/>
-      <c r="I84" s="7" t="n"/>
-      <c r="J84" s="7" t="n"/>
+      <c r="I84" s="8">
+        <f>IF('공수1'!Y84="","",'공수1'!Y84)</f>
+        <v/>
+      </c>
+      <c r="J84" s="8">
+        <f>IF('공수2'!Y84="","",'공수2'!Y84)</f>
+        <v/>
+      </c>
       <c r="K84" s="7" t="n"/>
     </row>
     <row r="85">
@@ -2980,8 +3448,14 @@
       <c r="F85" s="16" t="n"/>
       <c r="G85" s="7" t="n"/>
       <c r="H85" s="7" t="n"/>
-      <c r="I85" s="7" t="n"/>
-      <c r="J85" s="7" t="n"/>
+      <c r="I85" s="8">
+        <f>IF('공수1'!Y85="","",'공수1'!Y85)</f>
+        <v/>
+      </c>
+      <c r="J85" s="8">
+        <f>IF('공수2'!Y85="","",'공수2'!Y85)</f>
+        <v/>
+      </c>
       <c r="K85" s="7" t="n"/>
     </row>
     <row r="86">
@@ -2995,8 +3469,14 @@
       <c r="F86" s="16" t="n"/>
       <c r="G86" s="7" t="n"/>
       <c r="H86" s="7" t="n"/>
-      <c r="I86" s="7" t="n"/>
-      <c r="J86" s="7" t="n"/>
+      <c r="I86" s="8">
+        <f>IF('공수1'!Y86="","",'공수1'!Y86)</f>
+        <v/>
+      </c>
+      <c r="J86" s="8">
+        <f>IF('공수2'!Y86="","",'공수2'!Y86)</f>
+        <v/>
+      </c>
       <c r="K86" s="7" t="n"/>
     </row>
     <row r="87">
@@ -3010,8 +3490,14 @@
       <c r="F87" s="16" t="n"/>
       <c r="G87" s="7" t="n"/>
       <c r="H87" s="7" t="n"/>
-      <c r="I87" s="7" t="n"/>
-      <c r="J87" s="7" t="n"/>
+      <c r="I87" s="8">
+        <f>IF('공수1'!Y87="","",'공수1'!Y87)</f>
+        <v/>
+      </c>
+      <c r="J87" s="8">
+        <f>IF('공수2'!Y87="","",'공수2'!Y87)</f>
+        <v/>
+      </c>
       <c r="K87" s="7" t="n"/>
     </row>
     <row r="88">
@@ -3025,8 +3511,14 @@
       <c r="F88" s="16" t="n"/>
       <c r="G88" s="7" t="n"/>
       <c r="H88" s="7" t="n"/>
-      <c r="I88" s="7" t="n"/>
-      <c r="J88" s="7" t="n"/>
+      <c r="I88" s="8">
+        <f>IF('공수1'!Y88="","",'공수1'!Y88)</f>
+        <v/>
+      </c>
+      <c r="J88" s="8">
+        <f>IF('공수2'!Y88="","",'공수2'!Y88)</f>
+        <v/>
+      </c>
       <c r="K88" s="7" t="n"/>
     </row>
     <row r="89">
@@ -3040,8 +3532,14 @@
       <c r="F89" s="16" t="n"/>
       <c r="G89" s="7" t="n"/>
       <c r="H89" s="7" t="n"/>
-      <c r="I89" s="7" t="n"/>
-      <c r="J89" s="7" t="n"/>
+      <c r="I89" s="8">
+        <f>IF('공수1'!Y89="","",'공수1'!Y89)</f>
+        <v/>
+      </c>
+      <c r="J89" s="8">
+        <f>IF('공수2'!Y89="","",'공수2'!Y89)</f>
+        <v/>
+      </c>
       <c r="K89" s="7" t="n"/>
     </row>
     <row r="90">
@@ -3055,8 +3553,14 @@
       <c r="F90" s="16" t="n"/>
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="n"/>
-      <c r="I90" s="7" t="n"/>
-      <c r="J90" s="7" t="n"/>
+      <c r="I90" s="8">
+        <f>IF('공수1'!Y90="","",'공수1'!Y90)</f>
+        <v/>
+      </c>
+      <c r="J90" s="8">
+        <f>IF('공수2'!Y90="","",'공수2'!Y90)</f>
+        <v/>
+      </c>
       <c r="K90" s="7" t="n"/>
     </row>
     <row r="91">
@@ -3070,8 +3574,14 @@
       <c r="F91" s="16" t="n"/>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
-      <c r="I91" s="7" t="n"/>
-      <c r="J91" s="7" t="n"/>
+      <c r="I91" s="8">
+        <f>IF('공수1'!Y91="","",'공수1'!Y91)</f>
+        <v/>
+      </c>
+      <c r="J91" s="8">
+        <f>IF('공수2'!Y91="","",'공수2'!Y91)</f>
+        <v/>
+      </c>
       <c r="K91" s="7" t="n"/>
     </row>
     <row r="92">
@@ -3085,8 +3595,14 @@
       <c r="F92" s="16" t="n"/>
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="n"/>
-      <c r="I92" s="7" t="n"/>
-      <c r="J92" s="7" t="n"/>
+      <c r="I92" s="8">
+        <f>IF('공수1'!Y92="","",'공수1'!Y92)</f>
+        <v/>
+      </c>
+      <c r="J92" s="8">
+        <f>IF('공수2'!Y92="","",'공수2'!Y92)</f>
+        <v/>
+      </c>
       <c r="K92" s="7" t="n"/>
     </row>
     <row r="93">
@@ -3100,8 +3616,14 @@
       <c r="F93" s="16" t="n"/>
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="7" t="n"/>
-      <c r="I93" s="7" t="n"/>
-      <c r="J93" s="7" t="n"/>
+      <c r="I93" s="8">
+        <f>IF('공수1'!Y93="","",'공수1'!Y93)</f>
+        <v/>
+      </c>
+      <c r="J93" s="8">
+        <f>IF('공수2'!Y93="","",'공수2'!Y93)</f>
+        <v/>
+      </c>
       <c r="K93" s="7" t="n"/>
     </row>
     <row r="94">
@@ -3115,8 +3637,14 @@
       <c r="F94" s="16" t="n"/>
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="7" t="n"/>
-      <c r="I94" s="7" t="n"/>
-      <c r="J94" s="7" t="n"/>
+      <c r="I94" s="8">
+        <f>IF('공수1'!Y94="","",'공수1'!Y94)</f>
+        <v/>
+      </c>
+      <c r="J94" s="8">
+        <f>IF('공수2'!Y94="","",'공수2'!Y94)</f>
+        <v/>
+      </c>
       <c r="K94" s="7" t="n"/>
     </row>
     <row r="95">
@@ -3130,8 +3658,14 @@
       <c r="F95" s="16" t="n"/>
       <c r="G95" s="7" t="n"/>
       <c r="H95" s="7" t="n"/>
-      <c r="I95" s="7" t="n"/>
-      <c r="J95" s="7" t="n"/>
+      <c r="I95" s="8">
+        <f>IF('공수1'!Y95="","",'공수1'!Y95)</f>
+        <v/>
+      </c>
+      <c r="J95" s="8">
+        <f>IF('공수2'!Y95="","",'공수2'!Y95)</f>
+        <v/>
+      </c>
       <c r="K95" s="7" t="n"/>
     </row>
     <row r="96">
@@ -3145,8 +3679,14 @@
       <c r="F96" s="16" t="n"/>
       <c r="G96" s="7" t="n"/>
       <c r="H96" s="7" t="n"/>
-      <c r="I96" s="7" t="n"/>
-      <c r="J96" s="7" t="n"/>
+      <c r="I96" s="8">
+        <f>IF('공수1'!Y96="","",'공수1'!Y96)</f>
+        <v/>
+      </c>
+      <c r="J96" s="8">
+        <f>IF('공수2'!Y96="","",'공수2'!Y96)</f>
+        <v/>
+      </c>
       <c r="K96" s="7" t="n"/>
     </row>
     <row r="97">
@@ -3160,8 +3700,14 @@
       <c r="F97" s="16" t="n"/>
       <c r="G97" s="7" t="n"/>
       <c r="H97" s="7" t="n"/>
-      <c r="I97" s="7" t="n"/>
-      <c r="J97" s="7" t="n"/>
+      <c r="I97" s="8">
+        <f>IF('공수1'!Y97="","",'공수1'!Y97)</f>
+        <v/>
+      </c>
+      <c r="J97" s="8">
+        <f>IF('공수2'!Y97="","",'공수2'!Y97)</f>
+        <v/>
+      </c>
       <c r="K97" s="7" t="n"/>
     </row>
     <row r="98">
@@ -3175,8 +3721,14 @@
       <c r="F98" s="16" t="n"/>
       <c r="G98" s="7" t="n"/>
       <c r="H98" s="7" t="n"/>
-      <c r="I98" s="7" t="n"/>
-      <c r="J98" s="7" t="n"/>
+      <c r="I98" s="8">
+        <f>IF('공수1'!Y98="","",'공수1'!Y98)</f>
+        <v/>
+      </c>
+      <c r="J98" s="8">
+        <f>IF('공수2'!Y98="","",'공수2'!Y98)</f>
+        <v/>
+      </c>
       <c r="K98" s="7" t="n"/>
     </row>
     <row r="99">
@@ -3190,8 +3742,14 @@
       <c r="F99" s="16" t="n"/>
       <c r="G99" s="7" t="n"/>
       <c r="H99" s="7" t="n"/>
-      <c r="I99" s="7" t="n"/>
-      <c r="J99" s="7" t="n"/>
+      <c r="I99" s="8">
+        <f>IF('공수1'!Y99="","",'공수1'!Y99)</f>
+        <v/>
+      </c>
+      <c r="J99" s="8">
+        <f>IF('공수2'!Y99="","",'공수2'!Y99)</f>
+        <v/>
+      </c>
       <c r="K99" s="7" t="n"/>
     </row>
     <row r="100">
@@ -3205,8 +3763,14 @@
       <c r="F100" s="16" t="n"/>
       <c r="G100" s="7" t="n"/>
       <c r="H100" s="7" t="n"/>
-      <c r="I100" s="7" t="n"/>
-      <c r="J100" s="7" t="n"/>
+      <c r="I100" s="8">
+        <f>IF('공수1'!Y100="","",'공수1'!Y100)</f>
+        <v/>
+      </c>
+      <c r="J100" s="8">
+        <f>IF('공수2'!Y100="","",'공수2'!Y100)</f>
+        <v/>
+      </c>
       <c r="K100" s="7" t="n"/>
     </row>
     <row r="101">
@@ -3220,8 +3784,14 @@
       <c r="F101" s="16" t="n"/>
       <c r="G101" s="7" t="n"/>
       <c r="H101" s="7" t="n"/>
-      <c r="I101" s="7" t="n"/>
-      <c r="J101" s="7" t="n"/>
+      <c r="I101" s="8">
+        <f>IF('공수1'!Y101="","",'공수1'!Y101)</f>
+        <v/>
+      </c>
+      <c r="J101" s="8">
+        <f>IF('공수2'!Y101="","",'공수2'!Y101)</f>
+        <v/>
+      </c>
       <c r="K101" s="7" t="n"/>
     </row>
     <row r="102">
@@ -3235,8 +3805,14 @@
       <c r="F102" s="16" t="n"/>
       <c r="G102" s="7" t="n"/>
       <c r="H102" s="7" t="n"/>
-      <c r="I102" s="7" t="n"/>
-      <c r="J102" s="7" t="n"/>
+      <c r="I102" s="8">
+        <f>IF('공수1'!Y102="","",'공수1'!Y102)</f>
+        <v/>
+      </c>
+      <c r="J102" s="8">
+        <f>IF('공수2'!Y102="","",'공수2'!Y102)</f>
+        <v/>
+      </c>
       <c r="K102" s="7" t="n"/>
     </row>
     <row r="103">
@@ -3250,8 +3826,14 @@
       <c r="F103" s="16" t="n"/>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="7" t="n"/>
-      <c r="I103" s="7" t="n"/>
-      <c r="J103" s="7" t="n"/>
+      <c r="I103" s="8">
+        <f>IF('공수1'!Y103="","",'공수1'!Y103)</f>
+        <v/>
+      </c>
+      <c r="J103" s="8">
+        <f>IF('공수2'!Y103="","",'공수2'!Y103)</f>
+        <v/>
+      </c>
       <c r="K103" s="7" t="n"/>
     </row>
     <row r="104">
@@ -3265,8 +3847,14 @@
       <c r="F104" s="16" t="n"/>
       <c r="G104" s="7" t="n"/>
       <c r="H104" s="7" t="n"/>
-      <c r="I104" s="7" t="n"/>
-      <c r="J104" s="7" t="n"/>
+      <c r="I104" s="8">
+        <f>IF('공수1'!Y104="","",'공수1'!Y104)</f>
+        <v/>
+      </c>
+      <c r="J104" s="8">
+        <f>IF('공수2'!Y104="","",'공수2'!Y104)</f>
+        <v/>
+      </c>
       <c r="K104" s="7" t="n"/>
     </row>
     <row r="105">
@@ -3280,8 +3868,14 @@
       <c r="F105" s="16" t="n"/>
       <c r="G105" s="7" t="n"/>
       <c r="H105" s="7" t="n"/>
-      <c r="I105" s="7" t="n"/>
-      <c r="J105" s="7" t="n"/>
+      <c r="I105" s="8">
+        <f>IF('공수1'!Y105="","",'공수1'!Y105)</f>
+        <v/>
+      </c>
+      <c r="J105" s="8">
+        <f>IF('공수2'!Y105="","",'공수2'!Y105)</f>
+        <v/>
+      </c>
       <c r="K105" s="7" t="n"/>
     </row>
     <row r="106">
@@ -3295,8 +3889,14 @@
       <c r="F106" s="16" t="n"/>
       <c r="G106" s="7" t="n"/>
       <c r="H106" s="7" t="n"/>
-      <c r="I106" s="7" t="n"/>
-      <c r="J106" s="7" t="n"/>
+      <c r="I106" s="8">
+        <f>IF('공수1'!Y106="","",'공수1'!Y106)</f>
+        <v/>
+      </c>
+      <c r="J106" s="8">
+        <f>IF('공수2'!Y106="","",'공수2'!Y106)</f>
+        <v/>
+      </c>
       <c r="K106" s="7" t="n"/>
     </row>
     <row r="107">
@@ -3310,8 +3910,14 @@
       <c r="F107" s="16" t="n"/>
       <c r="G107" s="7" t="n"/>
       <c r="H107" s="7" t="n"/>
-      <c r="I107" s="7" t="n"/>
-      <c r="J107" s="7" t="n"/>
+      <c r="I107" s="8">
+        <f>IF('공수1'!Y107="","",'공수1'!Y107)</f>
+        <v/>
+      </c>
+      <c r="J107" s="8">
+        <f>IF('공수2'!Y107="","",'공수2'!Y107)</f>
+        <v/>
+      </c>
       <c r="K107" s="7" t="n"/>
     </row>
     <row r="108">
@@ -3325,8 +3931,14 @@
       <c r="F108" s="16" t="n"/>
       <c r="G108" s="7" t="n"/>
       <c r="H108" s="7" t="n"/>
-      <c r="I108" s="7" t="n"/>
-      <c r="J108" s="7" t="n"/>
+      <c r="I108" s="8">
+        <f>IF('공수1'!Y108="","",'공수1'!Y108)</f>
+        <v/>
+      </c>
+      <c r="J108" s="8">
+        <f>IF('공수2'!Y108="","",'공수2'!Y108)</f>
+        <v/>
+      </c>
       <c r="K108" s="7" t="n"/>
     </row>
     <row r="109">
@@ -3340,8 +3952,14 @@
       <c r="F109" s="16" t="n"/>
       <c r="G109" s="7" t="n"/>
       <c r="H109" s="7" t="n"/>
-      <c r="I109" s="7" t="n"/>
-      <c r="J109" s="7" t="n"/>
+      <c r="I109" s="8">
+        <f>IF('공수1'!Y109="","",'공수1'!Y109)</f>
+        <v/>
+      </c>
+      <c r="J109" s="8">
+        <f>IF('공수2'!Y109="","",'공수2'!Y109)</f>
+        <v/>
+      </c>
       <c r="K109" s="7" t="n"/>
     </row>
     <row r="110">
@@ -3355,8 +3973,14 @@
       <c r="F110" s="16" t="n"/>
       <c r="G110" s="7" t="n"/>
       <c r="H110" s="7" t="n"/>
-      <c r="I110" s="7" t="n"/>
-      <c r="J110" s="7" t="n"/>
+      <c r="I110" s="8">
+        <f>IF('공수1'!Y110="","",'공수1'!Y110)</f>
+        <v/>
+      </c>
+      <c r="J110" s="8">
+        <f>IF('공수2'!Y110="","",'공수2'!Y110)</f>
+        <v/>
+      </c>
       <c r="K110" s="7" t="n"/>
     </row>
     <row r="111">
@@ -3370,8 +3994,14 @@
       <c r="F111" s="16" t="n"/>
       <c r="G111" s="7" t="n"/>
       <c r="H111" s="7" t="n"/>
-      <c r="I111" s="7" t="n"/>
-      <c r="J111" s="7" t="n"/>
+      <c r="I111" s="8">
+        <f>IF('공수1'!Y111="","",'공수1'!Y111)</f>
+        <v/>
+      </c>
+      <c r="J111" s="8">
+        <f>IF('공수2'!Y111="","",'공수2'!Y111)</f>
+        <v/>
+      </c>
       <c r="K111" s="7" t="n"/>
     </row>
     <row r="112">
@@ -3385,8 +4015,14 @@
       <c r="F112" s="16" t="n"/>
       <c r="G112" s="7" t="n"/>
       <c r="H112" s="7" t="n"/>
-      <c r="I112" s="7" t="n"/>
-      <c r="J112" s="7" t="n"/>
+      <c r="I112" s="8">
+        <f>IF('공수1'!Y112="","",'공수1'!Y112)</f>
+        <v/>
+      </c>
+      <c r="J112" s="8">
+        <f>IF('공수2'!Y112="","",'공수2'!Y112)</f>
+        <v/>
+      </c>
       <c r="K112" s="7" t="n"/>
     </row>
     <row r="113">
@@ -3400,8 +4036,14 @@
       <c r="F113" s="16" t="n"/>
       <c r="G113" s="7" t="n"/>
       <c r="H113" s="7" t="n"/>
-      <c r="I113" s="7" t="n"/>
-      <c r="J113" s="7" t="n"/>
+      <c r="I113" s="8">
+        <f>IF('공수1'!Y113="","",'공수1'!Y113)</f>
+        <v/>
+      </c>
+      <c r="J113" s="8">
+        <f>IF('공수2'!Y113="","",'공수2'!Y113)</f>
+        <v/>
+      </c>
       <c r="K113" s="7" t="n"/>
     </row>
     <row r="114">
@@ -3415,8 +4057,14 @@
       <c r="F114" s="16" t="n"/>
       <c r="G114" s="7" t="n"/>
       <c r="H114" s="7" t="n"/>
-      <c r="I114" s="7" t="n"/>
-      <c r="J114" s="7" t="n"/>
+      <c r="I114" s="8">
+        <f>IF('공수1'!Y114="","",'공수1'!Y114)</f>
+        <v/>
+      </c>
+      <c r="J114" s="8">
+        <f>IF('공수2'!Y114="","",'공수2'!Y114)</f>
+        <v/>
+      </c>
       <c r="K114" s="7" t="n"/>
     </row>
     <row r="115">
@@ -3430,8 +4078,14 @@
       <c r="F115" s="16" t="n"/>
       <c r="G115" s="7" t="n"/>
       <c r="H115" s="7" t="n"/>
-      <c r="I115" s="7" t="n"/>
-      <c r="J115" s="7" t="n"/>
+      <c r="I115" s="8">
+        <f>IF('공수1'!Y115="","",'공수1'!Y115)</f>
+        <v/>
+      </c>
+      <c r="J115" s="8">
+        <f>IF('공수2'!Y115="","",'공수2'!Y115)</f>
+        <v/>
+      </c>
       <c r="K115" s="7" t="n"/>
     </row>
     <row r="116">
@@ -3445,8 +4099,14 @@
       <c r="F116" s="16" t="n"/>
       <c r="G116" s="7" t="n"/>
       <c r="H116" s="7" t="n"/>
-      <c r="I116" s="7" t="n"/>
-      <c r="J116" s="7" t="n"/>
+      <c r="I116" s="8">
+        <f>IF('공수1'!Y116="","",'공수1'!Y116)</f>
+        <v/>
+      </c>
+      <c r="J116" s="8">
+        <f>IF('공수2'!Y116="","",'공수2'!Y116)</f>
+        <v/>
+      </c>
       <c r="K116" s="7" t="n"/>
     </row>
     <row r="117">
@@ -3460,8 +4120,14 @@
       <c r="F117" s="16" t="n"/>
       <c r="G117" s="7" t="n"/>
       <c r="H117" s="7" t="n"/>
-      <c r="I117" s="7" t="n"/>
-      <c r="J117" s="7" t="n"/>
+      <c r="I117" s="8">
+        <f>IF('공수1'!Y117="","",'공수1'!Y117)</f>
+        <v/>
+      </c>
+      <c r="J117" s="8">
+        <f>IF('공수2'!Y117="","",'공수2'!Y117)</f>
+        <v/>
+      </c>
       <c r="K117" s="7" t="n"/>
     </row>
     <row r="118">
@@ -3475,8 +4141,14 @@
       <c r="F118" s="16" t="n"/>
       <c r="G118" s="7" t="n"/>
       <c r="H118" s="7" t="n"/>
-      <c r="I118" s="7" t="n"/>
-      <c r="J118" s="7" t="n"/>
+      <c r="I118" s="8">
+        <f>IF('공수1'!Y118="","",'공수1'!Y118)</f>
+        <v/>
+      </c>
+      <c r="J118" s="8">
+        <f>IF('공수2'!Y118="","",'공수2'!Y118)</f>
+        <v/>
+      </c>
       <c r="K118" s="7" t="n"/>
     </row>
     <row r="119">
@@ -3490,8 +4162,14 @@
       <c r="F119" s="16" t="n"/>
       <c r="G119" s="7" t="n"/>
       <c r="H119" s="7" t="n"/>
-      <c r="I119" s="7" t="n"/>
-      <c r="J119" s="7" t="n"/>
+      <c r="I119" s="8">
+        <f>IF('공수1'!Y119="","",'공수1'!Y119)</f>
+        <v/>
+      </c>
+      <c r="J119" s="8">
+        <f>IF('공수2'!Y119="","",'공수2'!Y119)</f>
+        <v/>
+      </c>
       <c r="K119" s="7" t="n"/>
     </row>
     <row r="120">
@@ -3505,8 +4183,14 @@
       <c r="F120" s="16" t="n"/>
       <c r="G120" s="7" t="n"/>
       <c r="H120" s="7" t="n"/>
-      <c r="I120" s="7" t="n"/>
-      <c r="J120" s="7" t="n"/>
+      <c r="I120" s="8">
+        <f>IF('공수1'!Y120="","",'공수1'!Y120)</f>
+        <v/>
+      </c>
+      <c r="J120" s="8">
+        <f>IF('공수2'!Y120="","",'공수2'!Y120)</f>
+        <v/>
+      </c>
       <c r="K120" s="7" t="n"/>
     </row>
     <row r="121">
@@ -3520,8 +4204,14 @@
       <c r="F121" s="16" t="n"/>
       <c r="G121" s="7" t="n"/>
       <c r="H121" s="7" t="n"/>
-      <c r="I121" s="7" t="n"/>
-      <c r="J121" s="7" t="n"/>
+      <c r="I121" s="8">
+        <f>IF('공수1'!Y121="","",'공수1'!Y121)</f>
+        <v/>
+      </c>
+      <c r="J121" s="8">
+        <f>IF('공수2'!Y121="","",'공수2'!Y121)</f>
+        <v/>
+      </c>
       <c r="K121" s="7" t="n"/>
     </row>
     <row r="122">
@@ -3535,8 +4225,14 @@
       <c r="F122" s="16" t="n"/>
       <c r="G122" s="7" t="n"/>
       <c r="H122" s="7" t="n"/>
-      <c r="I122" s="7" t="n"/>
-      <c r="J122" s="7" t="n"/>
+      <c r="I122" s="8">
+        <f>IF('공수1'!Y122="","",'공수1'!Y122)</f>
+        <v/>
+      </c>
+      <c r="J122" s="8">
+        <f>IF('공수2'!Y122="","",'공수2'!Y122)</f>
+        <v/>
+      </c>
       <c r="K122" s="7" t="n"/>
     </row>
     <row r="123">
@@ -3550,8 +4246,14 @@
       <c r="F123" s="16" t="n"/>
       <c r="G123" s="7" t="n"/>
       <c r="H123" s="7" t="n"/>
-      <c r="I123" s="7" t="n"/>
-      <c r="J123" s="7" t="n"/>
+      <c r="I123" s="8">
+        <f>IF('공수1'!Y123="","",'공수1'!Y123)</f>
+        <v/>
+      </c>
+      <c r="J123" s="8">
+        <f>IF('공수2'!Y123="","",'공수2'!Y123)</f>
+        <v/>
+      </c>
       <c r="K123" s="7" t="n"/>
     </row>
     <row r="124">
@@ -3565,8 +4267,14 @@
       <c r="F124" s="16" t="n"/>
       <c r="G124" s="7" t="n"/>
       <c r="H124" s="7" t="n"/>
-      <c r="I124" s="7" t="n"/>
-      <c r="J124" s="7" t="n"/>
+      <c r="I124" s="8">
+        <f>IF('공수1'!Y124="","",'공수1'!Y124)</f>
+        <v/>
+      </c>
+      <c r="J124" s="8">
+        <f>IF('공수2'!Y124="","",'공수2'!Y124)</f>
+        <v/>
+      </c>
       <c r="K124" s="7" t="n"/>
     </row>
     <row r="125">
@@ -3580,8 +4288,14 @@
       <c r="F125" s="16" t="n"/>
       <c r="G125" s="7" t="n"/>
       <c r="H125" s="7" t="n"/>
-      <c r="I125" s="7" t="n"/>
-      <c r="J125" s="7" t="n"/>
+      <c r="I125" s="8">
+        <f>IF('공수1'!Y125="","",'공수1'!Y125)</f>
+        <v/>
+      </c>
+      <c r="J125" s="8">
+        <f>IF('공수2'!Y125="","",'공수2'!Y125)</f>
+        <v/>
+      </c>
       <c r="K125" s="7" t="n"/>
     </row>
     <row r="126">
@@ -3595,8 +4309,14 @@
       <c r="F126" s="16" t="n"/>
       <c r="G126" s="7" t="n"/>
       <c r="H126" s="7" t="n"/>
-      <c r="I126" s="7" t="n"/>
-      <c r="J126" s="7" t="n"/>
+      <c r="I126" s="8">
+        <f>IF('공수1'!Y126="","",'공수1'!Y126)</f>
+        <v/>
+      </c>
+      <c r="J126" s="8">
+        <f>IF('공수2'!Y126="","",'공수2'!Y126)</f>
+        <v/>
+      </c>
       <c r="K126" s="7" t="n"/>
     </row>
     <row r="127">
@@ -3610,8 +4330,14 @@
       <c r="F127" s="16" t="n"/>
       <c r="G127" s="7" t="n"/>
       <c r="H127" s="7" t="n"/>
-      <c r="I127" s="7" t="n"/>
-      <c r="J127" s="7" t="n"/>
+      <c r="I127" s="8">
+        <f>IF('공수1'!Y127="","",'공수1'!Y127)</f>
+        <v/>
+      </c>
+      <c r="J127" s="8">
+        <f>IF('공수2'!Y127="","",'공수2'!Y127)</f>
+        <v/>
+      </c>
       <c r="K127" s="7" t="n"/>
     </row>
     <row r="128">
@@ -3625,8 +4351,14 @@
       <c r="F128" s="16" t="n"/>
       <c r="G128" s="7" t="n"/>
       <c r="H128" s="7" t="n"/>
-      <c r="I128" s="7" t="n"/>
-      <c r="J128" s="7" t="n"/>
+      <c r="I128" s="8">
+        <f>IF('공수1'!Y128="","",'공수1'!Y128)</f>
+        <v/>
+      </c>
+      <c r="J128" s="8">
+        <f>IF('공수2'!Y128="","",'공수2'!Y128)</f>
+        <v/>
+      </c>
       <c r="K128" s="7" t="n"/>
     </row>
     <row r="129">
@@ -3640,8 +4372,14 @@
       <c r="F129" s="16" t="n"/>
       <c r="G129" s="7" t="n"/>
       <c r="H129" s="7" t="n"/>
-      <c r="I129" s="7" t="n"/>
-      <c r="J129" s="7" t="n"/>
+      <c r="I129" s="8">
+        <f>IF('공수1'!Y129="","",'공수1'!Y129)</f>
+        <v/>
+      </c>
+      <c r="J129" s="8">
+        <f>IF('공수2'!Y129="","",'공수2'!Y129)</f>
+        <v/>
+      </c>
       <c r="K129" s="7" t="n"/>
     </row>
     <row r="130">
@@ -3655,8 +4393,14 @@
       <c r="F130" s="16" t="n"/>
       <c r="G130" s="7" t="n"/>
       <c r="H130" s="7" t="n"/>
-      <c r="I130" s="7" t="n"/>
-      <c r="J130" s="7" t="n"/>
+      <c r="I130" s="8">
+        <f>IF('공수1'!Y130="","",'공수1'!Y130)</f>
+        <v/>
+      </c>
+      <c r="J130" s="8">
+        <f>IF('공수2'!Y130="","",'공수2'!Y130)</f>
+        <v/>
+      </c>
       <c r="K130" s="7" t="n"/>
     </row>
     <row r="131">
@@ -3670,8 +4414,14 @@
       <c r="F131" s="16" t="n"/>
       <c r="G131" s="7" t="n"/>
       <c r="H131" s="7" t="n"/>
-      <c r="I131" s="7" t="n"/>
-      <c r="J131" s="7" t="n"/>
+      <c r="I131" s="8">
+        <f>IF('공수1'!Y131="","",'공수1'!Y131)</f>
+        <v/>
+      </c>
+      <c r="J131" s="8">
+        <f>IF('공수2'!Y131="","",'공수2'!Y131)</f>
+        <v/>
+      </c>
       <c r="K131" s="7" t="n"/>
     </row>
     <row r="132">
@@ -3685,8 +4435,14 @@
       <c r="F132" s="16" t="n"/>
       <c r="G132" s="7" t="n"/>
       <c r="H132" s="7" t="n"/>
-      <c r="I132" s="7" t="n"/>
-      <c r="J132" s="7" t="n"/>
+      <c r="I132" s="8">
+        <f>IF('공수1'!Y132="","",'공수1'!Y132)</f>
+        <v/>
+      </c>
+      <c r="J132" s="8">
+        <f>IF('공수2'!Y132="","",'공수2'!Y132)</f>
+        <v/>
+      </c>
       <c r="K132" s="7" t="n"/>
     </row>
     <row r="133">
@@ -3700,8 +4456,14 @@
       <c r="F133" s="16" t="n"/>
       <c r="G133" s="7" t="n"/>
       <c r="H133" s="7" t="n"/>
-      <c r="I133" s="7" t="n"/>
-      <c r="J133" s="7" t="n"/>
+      <c r="I133" s="8">
+        <f>IF('공수1'!Y133="","",'공수1'!Y133)</f>
+        <v/>
+      </c>
+      <c r="J133" s="8">
+        <f>IF('공수2'!Y133="","",'공수2'!Y133)</f>
+        <v/>
+      </c>
       <c r="K133" s="7" t="n"/>
     </row>
     <row r="134">
@@ -3715,8 +4477,14 @@
       <c r="F134" s="16" t="n"/>
       <c r="G134" s="7" t="n"/>
       <c r="H134" s="7" t="n"/>
-      <c r="I134" s="7" t="n"/>
-      <c r="J134" s="7" t="n"/>
+      <c r="I134" s="8">
+        <f>IF('공수1'!Y134="","",'공수1'!Y134)</f>
+        <v/>
+      </c>
+      <c r="J134" s="8">
+        <f>IF('공수2'!Y134="","",'공수2'!Y134)</f>
+        <v/>
+      </c>
       <c r="K134" s="7" t="n"/>
     </row>
     <row r="135">
@@ -3730,8 +4498,14 @@
       <c r="F135" s="16" t="n"/>
       <c r="G135" s="7" t="n"/>
       <c r="H135" s="7" t="n"/>
-      <c r="I135" s="7" t="n"/>
-      <c r="J135" s="7" t="n"/>
+      <c r="I135" s="8">
+        <f>IF('공수1'!Y135="","",'공수1'!Y135)</f>
+        <v/>
+      </c>
+      <c r="J135" s="8">
+        <f>IF('공수2'!Y135="","",'공수2'!Y135)</f>
+        <v/>
+      </c>
       <c r="K135" s="7" t="n"/>
     </row>
     <row r="136">
@@ -3745,8 +4519,14 @@
       <c r="F136" s="16" t="n"/>
       <c r="G136" s="7" t="n"/>
       <c r="H136" s="7" t="n"/>
-      <c r="I136" s="7" t="n"/>
-      <c r="J136" s="7" t="n"/>
+      <c r="I136" s="8">
+        <f>IF('공수1'!Y136="","",'공수1'!Y136)</f>
+        <v/>
+      </c>
+      <c r="J136" s="8">
+        <f>IF('공수2'!Y136="","",'공수2'!Y136)</f>
+        <v/>
+      </c>
       <c r="K136" s="7" t="n"/>
     </row>
     <row r="137">
@@ -3760,8 +4540,14 @@
       <c r="F137" s="16" t="n"/>
       <c r="G137" s="7" t="n"/>
       <c r="H137" s="7" t="n"/>
-      <c r="I137" s="7" t="n"/>
-      <c r="J137" s="7" t="n"/>
+      <c r="I137" s="8">
+        <f>IF('공수1'!Y137="","",'공수1'!Y137)</f>
+        <v/>
+      </c>
+      <c r="J137" s="8">
+        <f>IF('공수2'!Y137="","",'공수2'!Y137)</f>
+        <v/>
+      </c>
       <c r="K137" s="7" t="n"/>
     </row>
     <row r="138">
@@ -3775,8 +4561,14 @@
       <c r="F138" s="16" t="n"/>
       <c r="G138" s="7" t="n"/>
       <c r="H138" s="7" t="n"/>
-      <c r="I138" s="7" t="n"/>
-      <c r="J138" s="7" t="n"/>
+      <c r="I138" s="8">
+        <f>IF('공수1'!Y138="","",'공수1'!Y138)</f>
+        <v/>
+      </c>
+      <c r="J138" s="8">
+        <f>IF('공수2'!Y138="","",'공수2'!Y138)</f>
+        <v/>
+      </c>
       <c r="K138" s="7" t="n"/>
     </row>
     <row r="139">
@@ -3790,8 +4582,14 @@
       <c r="F139" s="16" t="n"/>
       <c r="G139" s="7" t="n"/>
       <c r="H139" s="7" t="n"/>
-      <c r="I139" s="7" t="n"/>
-      <c r="J139" s="7" t="n"/>
+      <c r="I139" s="8">
+        <f>IF('공수1'!Y139="","",'공수1'!Y139)</f>
+        <v/>
+      </c>
+      <c r="J139" s="8">
+        <f>IF('공수2'!Y139="","",'공수2'!Y139)</f>
+        <v/>
+      </c>
       <c r="K139" s="7" t="n"/>
     </row>
     <row r="140">
@@ -3805,8 +4603,14 @@
       <c r="F140" s="16" t="n"/>
       <c r="G140" s="7" t="n"/>
       <c r="H140" s="7" t="n"/>
-      <c r="I140" s="7" t="n"/>
-      <c r="J140" s="7" t="n"/>
+      <c r="I140" s="8">
+        <f>IF('공수1'!Y140="","",'공수1'!Y140)</f>
+        <v/>
+      </c>
+      <c r="J140" s="8">
+        <f>IF('공수2'!Y140="","",'공수2'!Y140)</f>
+        <v/>
+      </c>
       <c r="K140" s="7" t="n"/>
     </row>
     <row r="141">
@@ -3820,8 +4624,14 @@
       <c r="F141" s="16" t="n"/>
       <c r="G141" s="7" t="n"/>
       <c r="H141" s="7" t="n"/>
-      <c r="I141" s="7" t="n"/>
-      <c r="J141" s="7" t="n"/>
+      <c r="I141" s="8">
+        <f>IF('공수1'!Y141="","",'공수1'!Y141)</f>
+        <v/>
+      </c>
+      <c r="J141" s="8">
+        <f>IF('공수2'!Y141="","",'공수2'!Y141)</f>
+        <v/>
+      </c>
       <c r="K141" s="7" t="n"/>
     </row>
     <row r="142">
@@ -3835,8 +4645,14 @@
       <c r="F142" s="16" t="n"/>
       <c r="G142" s="7" t="n"/>
       <c r="H142" s="7" t="n"/>
-      <c r="I142" s="7" t="n"/>
-      <c r="J142" s="7" t="n"/>
+      <c r="I142" s="8">
+        <f>IF('공수1'!Y142="","",'공수1'!Y142)</f>
+        <v/>
+      </c>
+      <c r="J142" s="8">
+        <f>IF('공수2'!Y142="","",'공수2'!Y142)</f>
+        <v/>
+      </c>
       <c r="K142" s="7" t="n"/>
     </row>
     <row r="143">
@@ -3850,8 +4666,14 @@
       <c r="F143" s="16" t="n"/>
       <c r="G143" s="7" t="n"/>
       <c r="H143" s="7" t="n"/>
-      <c r="I143" s="7" t="n"/>
-      <c r="J143" s="7" t="n"/>
+      <c r="I143" s="8">
+        <f>IF('공수1'!Y143="","",'공수1'!Y143)</f>
+        <v/>
+      </c>
+      <c r="J143" s="8">
+        <f>IF('공수2'!Y143="","",'공수2'!Y143)</f>
+        <v/>
+      </c>
       <c r="K143" s="7" t="n"/>
     </row>
     <row r="144">
@@ -3865,8 +4687,14 @@
       <c r="F144" s="16" t="n"/>
       <c r="G144" s="7" t="n"/>
       <c r="H144" s="7" t="n"/>
-      <c r="I144" s="7" t="n"/>
-      <c r="J144" s="7" t="n"/>
+      <c r="I144" s="8">
+        <f>IF('공수1'!Y144="","",'공수1'!Y144)</f>
+        <v/>
+      </c>
+      <c r="J144" s="8">
+        <f>IF('공수2'!Y144="","",'공수2'!Y144)</f>
+        <v/>
+      </c>
       <c r="K144" s="7" t="n"/>
     </row>
     <row r="145">
@@ -3880,8 +4708,14 @@
       <c r="F145" s="16" t="n"/>
       <c r="G145" s="7" t="n"/>
       <c r="H145" s="7" t="n"/>
-      <c r="I145" s="7" t="n"/>
-      <c r="J145" s="7" t="n"/>
+      <c r="I145" s="8">
+        <f>IF('공수1'!Y145="","",'공수1'!Y145)</f>
+        <v/>
+      </c>
+      <c r="J145" s="8">
+        <f>IF('공수2'!Y145="","",'공수2'!Y145)</f>
+        <v/>
+      </c>
       <c r="K145" s="7" t="n"/>
     </row>
     <row r="146">
@@ -3895,8 +4729,14 @@
       <c r="F146" s="16" t="n"/>
       <c r="G146" s="7" t="n"/>
       <c r="H146" s="7" t="n"/>
-      <c r="I146" s="7" t="n"/>
-      <c r="J146" s="7" t="n"/>
+      <c r="I146" s="8">
+        <f>IF('공수1'!Y146="","",'공수1'!Y146)</f>
+        <v/>
+      </c>
+      <c r="J146" s="8">
+        <f>IF('공수2'!Y146="","",'공수2'!Y146)</f>
+        <v/>
+      </c>
       <c r="K146" s="7" t="n"/>
     </row>
     <row r="147">
@@ -3910,8 +4750,14 @@
       <c r="F147" s="16" t="n"/>
       <c r="G147" s="7" t="n"/>
       <c r="H147" s="7" t="n"/>
-      <c r="I147" s="7" t="n"/>
-      <c r="J147" s="7" t="n"/>
+      <c r="I147" s="8">
+        <f>IF('공수1'!Y147="","",'공수1'!Y147)</f>
+        <v/>
+      </c>
+      <c r="J147" s="8">
+        <f>IF('공수2'!Y147="","",'공수2'!Y147)</f>
+        <v/>
+      </c>
       <c r="K147" s="7" t="n"/>
     </row>
     <row r="148">
@@ -3925,8 +4771,14 @@
       <c r="F148" s="16" t="n"/>
       <c r="G148" s="7" t="n"/>
       <c r="H148" s="7" t="n"/>
-      <c r="I148" s="7" t="n"/>
-      <c r="J148" s="7" t="n"/>
+      <c r="I148" s="8">
+        <f>IF('공수1'!Y148="","",'공수1'!Y148)</f>
+        <v/>
+      </c>
+      <c r="J148" s="8">
+        <f>IF('공수2'!Y148="","",'공수2'!Y148)</f>
+        <v/>
+      </c>
       <c r="K148" s="7" t="n"/>
     </row>
     <row r="149">
@@ -3940,8 +4792,14 @@
       <c r="F149" s="16" t="n"/>
       <c r="G149" s="7" t="n"/>
       <c r="H149" s="7" t="n"/>
-      <c r="I149" s="7" t="n"/>
-      <c r="J149" s="7" t="n"/>
+      <c r="I149" s="8">
+        <f>IF('공수1'!Y149="","",'공수1'!Y149)</f>
+        <v/>
+      </c>
+      <c r="J149" s="8">
+        <f>IF('공수2'!Y149="","",'공수2'!Y149)</f>
+        <v/>
+      </c>
       <c r="K149" s="7" t="n"/>
     </row>
     <row r="150">
@@ -3955,8 +4813,14 @@
       <c r="F150" s="16" t="n"/>
       <c r="G150" s="7" t="n"/>
       <c r="H150" s="7" t="n"/>
-      <c r="I150" s="7" t="n"/>
-      <c r="J150" s="7" t="n"/>
+      <c r="I150" s="8">
+        <f>IF('공수1'!Y150="","",'공수1'!Y150)</f>
+        <v/>
+      </c>
+      <c r="J150" s="8">
+        <f>IF('공수2'!Y150="","",'공수2'!Y150)</f>
+        <v/>
+      </c>
       <c r="K150" s="7" t="n"/>
     </row>
     <row r="151">
@@ -3970,8 +4834,14 @@
       <c r="F151" s="16" t="n"/>
       <c r="G151" s="7" t="n"/>
       <c r="H151" s="7" t="n"/>
-      <c r="I151" s="7" t="n"/>
-      <c r="J151" s="7" t="n"/>
+      <c r="I151" s="8">
+        <f>IF('공수1'!Y151="","",'공수1'!Y151)</f>
+        <v/>
+      </c>
+      <c r="J151" s="8">
+        <f>IF('공수2'!Y151="","",'공수2'!Y151)</f>
+        <v/>
+      </c>
       <c r="K151" s="7" t="n"/>
     </row>
     <row r="152">
@@ -3985,8 +4855,14 @@
       <c r="F152" s="16" t="n"/>
       <c r="G152" s="7" t="n"/>
       <c r="H152" s="7" t="n"/>
-      <c r="I152" s="7" t="n"/>
-      <c r="J152" s="7" t="n"/>
+      <c r="I152" s="8">
+        <f>IF('공수1'!Y152="","",'공수1'!Y152)</f>
+        <v/>
+      </c>
+      <c r="J152" s="8">
+        <f>IF('공수2'!Y152="","",'공수2'!Y152)</f>
+        <v/>
+      </c>
       <c r="K152" s="7" t="n"/>
     </row>
     <row r="153">
@@ -4000,8 +4876,14 @@
       <c r="F153" s="16" t="n"/>
       <c r="G153" s="7" t="n"/>
       <c r="H153" s="7" t="n"/>
-      <c r="I153" s="7" t="n"/>
-      <c r="J153" s="7" t="n"/>
+      <c r="I153" s="8">
+        <f>IF('공수1'!Y153="","",'공수1'!Y153)</f>
+        <v/>
+      </c>
+      <c r="J153" s="8">
+        <f>IF('공수2'!Y153="","",'공수2'!Y153)</f>
+        <v/>
+      </c>
       <c r="K153" s="7" t="n"/>
     </row>
     <row r="154">
@@ -4015,8 +4897,14 @@
       <c r="F154" s="16" t="n"/>
       <c r="G154" s="7" t="n"/>
       <c r="H154" s="7" t="n"/>
-      <c r="I154" s="7" t="n"/>
-      <c r="J154" s="7" t="n"/>
+      <c r="I154" s="8">
+        <f>IF('공수1'!Y154="","",'공수1'!Y154)</f>
+        <v/>
+      </c>
+      <c r="J154" s="8">
+        <f>IF('공수2'!Y154="","",'공수2'!Y154)</f>
+        <v/>
+      </c>
       <c r="K154" s="7" t="n"/>
     </row>
     <row r="155">
@@ -4030,8 +4918,14 @@
       <c r="F155" s="16" t="n"/>
       <c r="G155" s="7" t="n"/>
       <c r="H155" s="7" t="n"/>
-      <c r="I155" s="7" t="n"/>
-      <c r="J155" s="7" t="n"/>
+      <c r="I155" s="8">
+        <f>IF('공수1'!Y155="","",'공수1'!Y155)</f>
+        <v/>
+      </c>
+      <c r="J155" s="8">
+        <f>IF('공수2'!Y155="","",'공수2'!Y155)</f>
+        <v/>
+      </c>
       <c r="K155" s="7" t="n"/>
     </row>
     <row r="156">
@@ -4045,8 +4939,14 @@
       <c r="F156" s="16" t="n"/>
       <c r="G156" s="7" t="n"/>
       <c r="H156" s="7" t="n"/>
-      <c r="I156" s="7" t="n"/>
-      <c r="J156" s="7" t="n"/>
+      <c r="I156" s="8">
+        <f>IF('공수1'!Y156="","",'공수1'!Y156)</f>
+        <v/>
+      </c>
+      <c r="J156" s="8">
+        <f>IF('공수2'!Y156="","",'공수2'!Y156)</f>
+        <v/>
+      </c>
       <c r="K156" s="7" t="n"/>
     </row>
   </sheetData>

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -856,24 +856,25 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>공수1 미만</t>
+          <t>합계 이상</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>공수2 이상</t>
+          <t>한 과목 이하</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>공수2 미만</t>
+          <t>합계 이하</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>· 점수(100점 만점)로 판정, 빈칸은 조건 없음
-· 위 순위부터 차례로 확인해 처음 맞는 반에 배정
-· 예) TF2반: 공수1 60점 이상이고 공수2 40점 미만</t>
+          <t>· 점수(100점 만점)로 판정. 한 줄 안의 조건은 '하나라도' 맞으면 그 반(또는)
+· 위 순위부터 차례로 확인해 처음 맞는 반에 배정, 조건이 모두 빈 줄은 '나머지'
+· 합계 = 공수1 + 공수2, 한 과목 이하 = 공수1·공수2 중 하나라도 그 점수 이하
+· 예) TF1반: 공수1 51점 이상 또는 합계 120점 이상</t>
         </is>
       </c>
     </row>
@@ -889,12 +890,12 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n">
-        <v>60</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
@@ -905,16 +906,16 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>TF2반</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n">
+          <t>HF반</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" s="7" t="n">
         <v>60</v>
-      </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -925,17 +926,13 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>TF3반</t>
+          <t>TF2반</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n">
-        <v>40</v>
-      </c>
+      <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n">
-        <v>40</v>
-      </c>
+      <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -950,7 +947,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>위 조건에 모두 해당하지 않거나 미응시 과목이 있으면 보류 → 상담 후 수동 배정</t>
+          <t>미응시 과목이 있어 위 기준으로 정할 수 없으면 보류 → 상담 후 수동 배정</t>
         </is>
       </c>
     </row>
@@ -999,7 +996,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>반 배정은 ①의 과목별 점수 기준으로만 결정</t>
+          <t>반 배정은 ①의 기준(과목 점수·합계)으로만 결정</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1011,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>어느 과목이든 기준 점수(①의 숫자)와 차이가 이 값 이내면 '경계'로 표시 → 상담·재검토 대상</t>
+          <t>과목 점수나 합계가 ①의 기준 점수와 이 값 이내로 차이 나면 '경계'로 표시 → 상담·재검토 대상</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1536,7 @@
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>공통수학1·2 모두 탄탄한 기초를 갖춘 학생을 위한 반으로, 개념 심화와 고난도 문항 해결력, 고1 내신 상위권 대비까지 진행합니다.</t>
+          <t>공통수학1·2의 탄탄한 기초를 바탕으로 개념 심화와 고난도 문항 해결력, 고1 내신 상위권 대비까지 진행하는 반입니다.</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1547,7 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>공통수학1의 강점을 살리면서 공통수학2의 개념을 처음부터 체계적으로 다져, 두 과목의 균형을 맞추는 반입니다.</t>
+          <t>중등 연계 개념부터 차근차근 점검하며, 공통수학1·2의 핵심 개념과 기본 유형을 확실히 다지는 반입니다.</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1558,7 @@
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>중등 연계 개념부터 차근차근 점검하며, 공통수학1·2의 핵심 개념과 기본 유형을 확실히 완성하는 반입니다.</t>
+          <t>공통수학1·2의 개념을 체계적으로 정리하고 유형별 문제 해결력을 키워, 두 과목의 균형을 맞추는 반입니다.</t>
         </is>
       </c>
     </row>
@@ -22999,11 +22996,11 @@
         <v/>
       </c>
       <c r="K7" s="27">
-        <f>IF(I7="","",IF(OR(G7="",H7=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G7&gt;='설정'!$C$6),OR('설정'!$D$6="",G7&lt;'설정'!$D$6),OR('설정'!$E$6="",H7&gt;='설정'!$E$6),OR('설정'!$F$6="",H7&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G7&gt;='설정'!$C$7),OR('설정'!$D$7="",G7&lt;'설정'!$D$7),OR('설정'!$E$7="",H7&gt;='설정'!$E$7),OR('설정'!$F$7="",H7&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G7&gt;='설정'!$C$8),OR('설정'!$D$8="",G7&lt;'설정'!$D$8),OR('설정'!$E$8="",H7&gt;='설정'!$E$8),OR('설정'!$F$8="",H7&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I7="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G7&lt;&gt;"",H7&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G7&lt;&gt;"",N(G7)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G7&lt;&gt;"",H7&lt;&gt;""),(N(G7)+N(H7))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G7&lt;&gt;"",N(G7)&lt;='설정'!$E$6),AND(H7&lt;&gt;"",N(H7)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G7&lt;&gt;"",H7&lt;&gt;""),(N(G7)+N(H7))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G7&lt;&gt;"",H7&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G7&lt;&gt;"",N(G7)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G7&lt;&gt;"",H7&lt;&gt;""),(N(G7)+N(H7))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G7&lt;&gt;"",N(G7)&lt;='설정'!$E$7),AND(H7&lt;&gt;"",N(H7)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G7&lt;&gt;"",H7&lt;&gt;""),(N(G7)+N(H7))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G7&lt;&gt;"",H7&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G7&lt;&gt;"",N(G7)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G7&lt;&gt;"",H7&lt;&gt;""),(N(G7)+N(H7))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G7&lt;&gt;"",N(G7)&lt;='설정'!$E$8),AND(H7&lt;&gt;"",N(H7)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G7&lt;&gt;"",H7&lt;&gt;""),(N(G7)+N(H7))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L7" s="29">
-        <f>IF(OR(G7="",H7=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G7-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H7-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G7="",H7=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G7-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G7+H7)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G7+H7)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G7-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H7-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M7" s="7" t="n"/>
@@ -23090,11 +23087,11 @@
         <v/>
       </c>
       <c r="K8" s="27">
-        <f>IF(I8="","",IF(OR(G8="",H8=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G8&gt;='설정'!$C$6),OR('설정'!$D$6="",G8&lt;'설정'!$D$6),OR('설정'!$E$6="",H8&gt;='설정'!$E$6),OR('설정'!$F$6="",H8&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G8&gt;='설정'!$C$7),OR('설정'!$D$7="",G8&lt;'설정'!$D$7),OR('설정'!$E$7="",H8&gt;='설정'!$E$7),OR('설정'!$F$7="",H8&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G8&gt;='설정'!$C$8),OR('설정'!$D$8="",G8&lt;'설정'!$D$8),OR('설정'!$E$8="",H8&gt;='설정'!$E$8),OR('설정'!$F$8="",H8&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I8="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G8&lt;&gt;"",H8&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G8&lt;&gt;"",N(G8)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G8&lt;&gt;"",H8&lt;&gt;""),(N(G8)+N(H8))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G8&lt;&gt;"",N(G8)&lt;='설정'!$E$6),AND(H8&lt;&gt;"",N(H8)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G8&lt;&gt;"",H8&lt;&gt;""),(N(G8)+N(H8))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G8&lt;&gt;"",H8&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G8&lt;&gt;"",N(G8)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G8&lt;&gt;"",H8&lt;&gt;""),(N(G8)+N(H8))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G8&lt;&gt;"",N(G8)&lt;='설정'!$E$7),AND(H8&lt;&gt;"",N(H8)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G8&lt;&gt;"",H8&lt;&gt;""),(N(G8)+N(H8))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G8&lt;&gt;"",H8&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G8&lt;&gt;"",N(G8)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G8&lt;&gt;"",H8&lt;&gt;""),(N(G8)+N(H8))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G8&lt;&gt;"",N(G8)&lt;='설정'!$E$8),AND(H8&lt;&gt;"",N(H8)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G8&lt;&gt;"",H8&lt;&gt;""),(N(G8)+N(H8))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L8" s="29">
-        <f>IF(OR(G8="",H8=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G8-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H8-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G8="",H8=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G8-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G8+H8)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G8+H8)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G8-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H8-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M8" s="7" t="n"/>
@@ -23181,11 +23178,11 @@
         <v/>
       </c>
       <c r="K9" s="27">
-        <f>IF(I9="","",IF(OR(G9="",H9=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G9&gt;='설정'!$C$6),OR('설정'!$D$6="",G9&lt;'설정'!$D$6),OR('설정'!$E$6="",H9&gt;='설정'!$E$6),OR('설정'!$F$6="",H9&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G9&gt;='설정'!$C$7),OR('설정'!$D$7="",G9&lt;'설정'!$D$7),OR('설정'!$E$7="",H9&gt;='설정'!$E$7),OR('설정'!$F$7="",H9&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G9&gt;='설정'!$C$8),OR('설정'!$D$8="",G9&lt;'설정'!$D$8),OR('설정'!$E$8="",H9&gt;='설정'!$E$8),OR('설정'!$F$8="",H9&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I9="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G9&lt;&gt;"",H9&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G9&lt;&gt;"",N(G9)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G9&lt;&gt;"",H9&lt;&gt;""),(N(G9)+N(H9))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G9&lt;&gt;"",N(G9)&lt;='설정'!$E$6),AND(H9&lt;&gt;"",N(H9)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G9&lt;&gt;"",H9&lt;&gt;""),(N(G9)+N(H9))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G9&lt;&gt;"",H9&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G9&lt;&gt;"",N(G9)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G9&lt;&gt;"",H9&lt;&gt;""),(N(G9)+N(H9))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G9&lt;&gt;"",N(G9)&lt;='설정'!$E$7),AND(H9&lt;&gt;"",N(H9)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G9&lt;&gt;"",H9&lt;&gt;""),(N(G9)+N(H9))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G9&lt;&gt;"",H9&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G9&lt;&gt;"",N(G9)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G9&lt;&gt;"",H9&lt;&gt;""),(N(G9)+N(H9))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G9&lt;&gt;"",N(G9)&lt;='설정'!$E$8),AND(H9&lt;&gt;"",N(H9)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G9&lt;&gt;"",H9&lt;&gt;""),(N(G9)+N(H9))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L9" s="29">
-        <f>IF(OR(G9="",H9=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G9-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H9-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G9="",H9=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G9-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G9+H9)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G9+H9)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G9-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H9-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M9" s="7" t="n"/>
@@ -23272,11 +23269,11 @@
         <v/>
       </c>
       <c r="K10" s="27">
-        <f>IF(I10="","",IF(OR(G10="",H10=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G10&gt;='설정'!$C$6),OR('설정'!$D$6="",G10&lt;'설정'!$D$6),OR('설정'!$E$6="",H10&gt;='설정'!$E$6),OR('설정'!$F$6="",H10&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G10&gt;='설정'!$C$7),OR('설정'!$D$7="",G10&lt;'설정'!$D$7),OR('설정'!$E$7="",H10&gt;='설정'!$E$7),OR('설정'!$F$7="",H10&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G10&gt;='설정'!$C$8),OR('설정'!$D$8="",G10&lt;'설정'!$D$8),OR('설정'!$E$8="",H10&gt;='설정'!$E$8),OR('설정'!$F$8="",H10&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I10="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G10&lt;&gt;"",H10&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G10&lt;&gt;"",N(G10)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G10&lt;&gt;"",H10&lt;&gt;""),(N(G10)+N(H10))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G10&lt;&gt;"",N(G10)&lt;='설정'!$E$6),AND(H10&lt;&gt;"",N(H10)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G10&lt;&gt;"",H10&lt;&gt;""),(N(G10)+N(H10))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G10&lt;&gt;"",H10&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G10&lt;&gt;"",N(G10)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G10&lt;&gt;"",H10&lt;&gt;""),(N(G10)+N(H10))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G10&lt;&gt;"",N(G10)&lt;='설정'!$E$7),AND(H10&lt;&gt;"",N(H10)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G10&lt;&gt;"",H10&lt;&gt;""),(N(G10)+N(H10))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G10&lt;&gt;"",H10&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G10&lt;&gt;"",N(G10)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G10&lt;&gt;"",H10&lt;&gt;""),(N(G10)+N(H10))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G10&lt;&gt;"",N(G10)&lt;='설정'!$E$8),AND(H10&lt;&gt;"",N(H10)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G10&lt;&gt;"",H10&lt;&gt;""),(N(G10)+N(H10))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L10" s="29">
-        <f>IF(OR(G10="",H10=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G10-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H10-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G10="",H10=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G10-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G10+H10)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G10+H10)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G10-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H10-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M10" s="7" t="n"/>
@@ -23363,11 +23360,11 @@
         <v/>
       </c>
       <c r="K11" s="27">
-        <f>IF(I11="","",IF(OR(G11="",H11=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G11&gt;='설정'!$C$6),OR('설정'!$D$6="",G11&lt;'설정'!$D$6),OR('설정'!$E$6="",H11&gt;='설정'!$E$6),OR('설정'!$F$6="",H11&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G11&gt;='설정'!$C$7),OR('설정'!$D$7="",G11&lt;'설정'!$D$7),OR('설정'!$E$7="",H11&gt;='설정'!$E$7),OR('설정'!$F$7="",H11&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G11&gt;='설정'!$C$8),OR('설정'!$D$8="",G11&lt;'설정'!$D$8),OR('설정'!$E$8="",H11&gt;='설정'!$E$8),OR('설정'!$F$8="",H11&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I11="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G11&lt;&gt;"",H11&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G11&lt;&gt;"",N(G11)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G11&lt;&gt;"",H11&lt;&gt;""),(N(G11)+N(H11))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G11&lt;&gt;"",N(G11)&lt;='설정'!$E$6),AND(H11&lt;&gt;"",N(H11)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G11&lt;&gt;"",H11&lt;&gt;""),(N(G11)+N(H11))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G11&lt;&gt;"",H11&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G11&lt;&gt;"",N(G11)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G11&lt;&gt;"",H11&lt;&gt;""),(N(G11)+N(H11))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G11&lt;&gt;"",N(G11)&lt;='설정'!$E$7),AND(H11&lt;&gt;"",N(H11)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G11&lt;&gt;"",H11&lt;&gt;""),(N(G11)+N(H11))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G11&lt;&gt;"",H11&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G11&lt;&gt;"",N(G11)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G11&lt;&gt;"",H11&lt;&gt;""),(N(G11)+N(H11))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G11&lt;&gt;"",N(G11)&lt;='설정'!$E$8),AND(H11&lt;&gt;"",N(H11)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G11&lt;&gt;"",H11&lt;&gt;""),(N(G11)+N(H11))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L11" s="29">
-        <f>IF(OR(G11="",H11=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G11-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H11-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G11="",H11=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G11-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G11+H11)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G11+H11)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G11-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H11-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M11" s="7" t="n"/>
@@ -23455,11 +23452,11 @@
         <v/>
       </c>
       <c r="K12" s="27">
-        <f>IF(I12="","",IF(OR(G12="",H12=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G12&gt;='설정'!$C$6),OR('설정'!$D$6="",G12&lt;'설정'!$D$6),OR('설정'!$E$6="",H12&gt;='설정'!$E$6),OR('설정'!$F$6="",H12&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G12&gt;='설정'!$C$7),OR('설정'!$D$7="",G12&lt;'설정'!$D$7),OR('설정'!$E$7="",H12&gt;='설정'!$E$7),OR('설정'!$F$7="",H12&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G12&gt;='설정'!$C$8),OR('설정'!$D$8="",G12&lt;'설정'!$D$8),OR('설정'!$E$8="",H12&gt;='설정'!$E$8),OR('설정'!$F$8="",H12&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I12="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G12&lt;&gt;"",H12&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G12&lt;&gt;"",N(G12)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G12&lt;&gt;"",H12&lt;&gt;""),(N(G12)+N(H12))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G12&lt;&gt;"",N(G12)&lt;='설정'!$E$6),AND(H12&lt;&gt;"",N(H12)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G12&lt;&gt;"",H12&lt;&gt;""),(N(G12)+N(H12))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G12&lt;&gt;"",H12&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G12&lt;&gt;"",N(G12)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G12&lt;&gt;"",H12&lt;&gt;""),(N(G12)+N(H12))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G12&lt;&gt;"",N(G12)&lt;='설정'!$E$7),AND(H12&lt;&gt;"",N(H12)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G12&lt;&gt;"",H12&lt;&gt;""),(N(G12)+N(H12))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G12&lt;&gt;"",H12&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G12&lt;&gt;"",N(G12)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G12&lt;&gt;"",H12&lt;&gt;""),(N(G12)+N(H12))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G12&lt;&gt;"",N(G12)&lt;='설정'!$E$8),AND(H12&lt;&gt;"",N(H12)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G12&lt;&gt;"",H12&lt;&gt;""),(N(G12)+N(H12))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L12" s="29">
-        <f>IF(OR(G12="",H12=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G12-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H12-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G12="",H12=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G12-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G12+H12)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G12+H12)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G12-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H12-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M12" s="7" t="n"/>
@@ -23518,11 +23515,11 @@
         <v/>
       </c>
       <c r="K13" s="27">
-        <f>IF(I13="","",IF(OR(G13="",H13=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G13&gt;='설정'!$C$6),OR('설정'!$D$6="",G13&lt;'설정'!$D$6),OR('설정'!$E$6="",H13&gt;='설정'!$E$6),OR('설정'!$F$6="",H13&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G13&gt;='설정'!$C$7),OR('설정'!$D$7="",G13&lt;'설정'!$D$7),OR('설정'!$E$7="",H13&gt;='설정'!$E$7),OR('설정'!$F$7="",H13&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G13&gt;='설정'!$C$8),OR('설정'!$D$8="",G13&lt;'설정'!$D$8),OR('설정'!$E$8="",H13&gt;='설정'!$E$8),OR('설정'!$F$8="",H13&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I13="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G13&lt;&gt;"",H13&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G13&lt;&gt;"",N(G13)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G13&lt;&gt;"",H13&lt;&gt;""),(N(G13)+N(H13))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G13&lt;&gt;"",N(G13)&lt;='설정'!$E$6),AND(H13&lt;&gt;"",N(H13)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G13&lt;&gt;"",H13&lt;&gt;""),(N(G13)+N(H13))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G13&lt;&gt;"",H13&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G13&lt;&gt;"",N(G13)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G13&lt;&gt;"",H13&lt;&gt;""),(N(G13)+N(H13))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G13&lt;&gt;"",N(G13)&lt;='설정'!$E$7),AND(H13&lt;&gt;"",N(H13)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G13&lt;&gt;"",H13&lt;&gt;""),(N(G13)+N(H13))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G13&lt;&gt;"",H13&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G13&lt;&gt;"",N(G13)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G13&lt;&gt;"",H13&lt;&gt;""),(N(G13)+N(H13))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G13&lt;&gt;"",N(G13)&lt;='설정'!$E$8),AND(H13&lt;&gt;"",N(H13)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G13&lt;&gt;"",H13&lt;&gt;""),(N(G13)+N(H13))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L13" s="29">
-        <f>IF(OR(G13="",H13=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G13-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H13-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G13="",H13=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G13-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G13+H13)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G13+H13)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G13-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H13-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M13" s="7" t="n"/>
@@ -23541,8 +23538,8 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>· 자동배정은 '설정' ①의 과목별 점수 기준(절대평가)
-· 경계 = 어느 과목이든 기준 점수와의 차이가 경계 범위 이내
+          <t>· 자동배정은 '설정' ①의 기준(공수1 점수·한 과목 점수·합계)
+· 경계 = 과목 점수나 합계가 기준 점수와 경계 범위 이내
 · 공통수학반·선행반은 목록에서 고르거나 직접 입력('설정' ⑥·⑦에 반 소개 추가 가능)
 · 환산총점·석차는 참고용</t>
         </is>
@@ -23589,11 +23586,11 @@
         <v/>
       </c>
       <c r="K14" s="27">
-        <f>IF(I14="","",IF(OR(G14="",H14=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G14&gt;='설정'!$C$6),OR('설정'!$D$6="",G14&lt;'설정'!$D$6),OR('설정'!$E$6="",H14&gt;='설정'!$E$6),OR('설정'!$F$6="",H14&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G14&gt;='설정'!$C$7),OR('설정'!$D$7="",G14&lt;'설정'!$D$7),OR('설정'!$E$7="",H14&gt;='설정'!$E$7),OR('설정'!$F$7="",H14&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G14&gt;='설정'!$C$8),OR('설정'!$D$8="",G14&lt;'설정'!$D$8),OR('설정'!$E$8="",H14&gt;='설정'!$E$8),OR('설정'!$F$8="",H14&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I14="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G14&lt;&gt;"",H14&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G14&lt;&gt;"",N(G14)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G14&lt;&gt;"",H14&lt;&gt;""),(N(G14)+N(H14))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G14&lt;&gt;"",N(G14)&lt;='설정'!$E$6),AND(H14&lt;&gt;"",N(H14)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G14&lt;&gt;"",H14&lt;&gt;""),(N(G14)+N(H14))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G14&lt;&gt;"",H14&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G14&lt;&gt;"",N(G14)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G14&lt;&gt;"",H14&lt;&gt;""),(N(G14)+N(H14))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G14&lt;&gt;"",N(G14)&lt;='설정'!$E$7),AND(H14&lt;&gt;"",N(H14)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G14&lt;&gt;"",H14&lt;&gt;""),(N(G14)+N(H14))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G14&lt;&gt;"",H14&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G14&lt;&gt;"",N(G14)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G14&lt;&gt;"",H14&lt;&gt;""),(N(G14)+N(H14))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G14&lt;&gt;"",N(G14)&lt;='설정'!$E$8),AND(H14&lt;&gt;"",N(H14)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G14&lt;&gt;"",H14&lt;&gt;""),(N(G14)+N(H14))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L14" s="29">
-        <f>IF(OR(G14="",H14=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G14-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H14-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G14="",H14=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G14-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G14+H14)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G14+H14)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G14-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H14-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M14" s="7" t="n"/>
@@ -23652,11 +23649,11 @@
         <v/>
       </c>
       <c r="K15" s="27">
-        <f>IF(I15="","",IF(OR(G15="",H15=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G15&gt;='설정'!$C$6),OR('설정'!$D$6="",G15&lt;'설정'!$D$6),OR('설정'!$E$6="",H15&gt;='설정'!$E$6),OR('설정'!$F$6="",H15&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G15&gt;='설정'!$C$7),OR('설정'!$D$7="",G15&lt;'설정'!$D$7),OR('설정'!$E$7="",H15&gt;='설정'!$E$7),OR('설정'!$F$7="",H15&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G15&gt;='설정'!$C$8),OR('설정'!$D$8="",G15&lt;'설정'!$D$8),OR('설정'!$E$8="",H15&gt;='설정'!$E$8),OR('설정'!$F$8="",H15&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I15="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G15&lt;&gt;"",H15&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G15&lt;&gt;"",N(G15)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G15&lt;&gt;"",H15&lt;&gt;""),(N(G15)+N(H15))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G15&lt;&gt;"",N(G15)&lt;='설정'!$E$6),AND(H15&lt;&gt;"",N(H15)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G15&lt;&gt;"",H15&lt;&gt;""),(N(G15)+N(H15))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G15&lt;&gt;"",H15&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G15&lt;&gt;"",N(G15)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G15&lt;&gt;"",H15&lt;&gt;""),(N(G15)+N(H15))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G15&lt;&gt;"",N(G15)&lt;='설정'!$E$7),AND(H15&lt;&gt;"",N(H15)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G15&lt;&gt;"",H15&lt;&gt;""),(N(G15)+N(H15))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G15&lt;&gt;"",H15&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G15&lt;&gt;"",N(G15)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G15&lt;&gt;"",H15&lt;&gt;""),(N(G15)+N(H15))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G15&lt;&gt;"",N(G15)&lt;='설정'!$E$8),AND(H15&lt;&gt;"",N(H15)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G15&lt;&gt;"",H15&lt;&gt;""),(N(G15)+N(H15))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L15" s="29">
-        <f>IF(OR(G15="",H15=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G15-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H15-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G15="",H15=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G15-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G15+H15)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G15+H15)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G15-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H15-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M15" s="7" t="n"/>
@@ -23715,11 +23712,11 @@
         <v/>
       </c>
       <c r="K16" s="27">
-        <f>IF(I16="","",IF(OR(G16="",H16=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G16&gt;='설정'!$C$6),OR('설정'!$D$6="",G16&lt;'설정'!$D$6),OR('설정'!$E$6="",H16&gt;='설정'!$E$6),OR('설정'!$F$6="",H16&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G16&gt;='설정'!$C$7),OR('설정'!$D$7="",G16&lt;'설정'!$D$7),OR('설정'!$E$7="",H16&gt;='설정'!$E$7),OR('설정'!$F$7="",H16&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G16&gt;='설정'!$C$8),OR('설정'!$D$8="",G16&lt;'설정'!$D$8),OR('설정'!$E$8="",H16&gt;='설정'!$E$8),OR('설정'!$F$8="",H16&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I16="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G16&lt;&gt;"",H16&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G16&lt;&gt;"",N(G16)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G16&lt;&gt;"",H16&lt;&gt;""),(N(G16)+N(H16))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G16&lt;&gt;"",N(G16)&lt;='설정'!$E$6),AND(H16&lt;&gt;"",N(H16)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G16&lt;&gt;"",H16&lt;&gt;""),(N(G16)+N(H16))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G16&lt;&gt;"",H16&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G16&lt;&gt;"",N(G16)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G16&lt;&gt;"",H16&lt;&gt;""),(N(G16)+N(H16))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G16&lt;&gt;"",N(G16)&lt;='설정'!$E$7),AND(H16&lt;&gt;"",N(H16)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G16&lt;&gt;"",H16&lt;&gt;""),(N(G16)+N(H16))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G16&lt;&gt;"",H16&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G16&lt;&gt;"",N(G16)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G16&lt;&gt;"",H16&lt;&gt;""),(N(G16)+N(H16))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G16&lt;&gt;"",N(G16)&lt;='설정'!$E$8),AND(H16&lt;&gt;"",N(H16)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G16&lt;&gt;"",H16&lt;&gt;""),(N(G16)+N(H16))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L16" s="29">
-        <f>IF(OR(G16="",H16=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G16-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H16-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G16="",H16=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G16-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G16+H16)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G16+H16)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G16-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H16-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M16" s="7" t="n"/>
@@ -23778,11 +23775,11 @@
         <v/>
       </c>
       <c r="K17" s="27">
-        <f>IF(I17="","",IF(OR(G17="",H17=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G17&gt;='설정'!$C$6),OR('설정'!$D$6="",G17&lt;'설정'!$D$6),OR('설정'!$E$6="",H17&gt;='설정'!$E$6),OR('설정'!$F$6="",H17&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G17&gt;='설정'!$C$7),OR('설정'!$D$7="",G17&lt;'설정'!$D$7),OR('설정'!$E$7="",H17&gt;='설정'!$E$7),OR('설정'!$F$7="",H17&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G17&gt;='설정'!$C$8),OR('설정'!$D$8="",G17&lt;'설정'!$D$8),OR('설정'!$E$8="",H17&gt;='설정'!$E$8),OR('설정'!$F$8="",H17&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I17="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G17&lt;&gt;"",H17&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G17&lt;&gt;"",N(G17)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G17&lt;&gt;"",H17&lt;&gt;""),(N(G17)+N(H17))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G17&lt;&gt;"",N(G17)&lt;='설정'!$E$6),AND(H17&lt;&gt;"",N(H17)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G17&lt;&gt;"",H17&lt;&gt;""),(N(G17)+N(H17))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G17&lt;&gt;"",H17&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G17&lt;&gt;"",N(G17)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G17&lt;&gt;"",H17&lt;&gt;""),(N(G17)+N(H17))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G17&lt;&gt;"",N(G17)&lt;='설정'!$E$7),AND(H17&lt;&gt;"",N(H17)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G17&lt;&gt;"",H17&lt;&gt;""),(N(G17)+N(H17))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G17&lt;&gt;"",H17&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G17&lt;&gt;"",N(G17)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G17&lt;&gt;"",H17&lt;&gt;""),(N(G17)+N(H17))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G17&lt;&gt;"",N(G17)&lt;='설정'!$E$8),AND(H17&lt;&gt;"",N(H17)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G17&lt;&gt;"",H17&lt;&gt;""),(N(G17)+N(H17))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L17" s="29">
-        <f>IF(OR(G17="",H17=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G17-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H17-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G17="",H17=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G17-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G17+H17)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G17+H17)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G17-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H17-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M17" s="7" t="n"/>
@@ -23841,11 +23838,11 @@
         <v/>
       </c>
       <c r="K18" s="27">
-        <f>IF(I18="","",IF(OR(G18="",H18=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G18&gt;='설정'!$C$6),OR('설정'!$D$6="",G18&lt;'설정'!$D$6),OR('설정'!$E$6="",H18&gt;='설정'!$E$6),OR('설정'!$F$6="",H18&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G18&gt;='설정'!$C$7),OR('설정'!$D$7="",G18&lt;'설정'!$D$7),OR('설정'!$E$7="",H18&gt;='설정'!$E$7),OR('설정'!$F$7="",H18&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G18&gt;='설정'!$C$8),OR('설정'!$D$8="",G18&lt;'설정'!$D$8),OR('설정'!$E$8="",H18&gt;='설정'!$E$8),OR('설정'!$F$8="",H18&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I18="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G18&lt;&gt;"",H18&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G18&lt;&gt;"",N(G18)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G18&lt;&gt;"",H18&lt;&gt;""),(N(G18)+N(H18))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G18&lt;&gt;"",N(G18)&lt;='설정'!$E$6),AND(H18&lt;&gt;"",N(H18)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G18&lt;&gt;"",H18&lt;&gt;""),(N(G18)+N(H18))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G18&lt;&gt;"",H18&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G18&lt;&gt;"",N(G18)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G18&lt;&gt;"",H18&lt;&gt;""),(N(G18)+N(H18))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G18&lt;&gt;"",N(G18)&lt;='설정'!$E$7),AND(H18&lt;&gt;"",N(H18)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G18&lt;&gt;"",H18&lt;&gt;""),(N(G18)+N(H18))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G18&lt;&gt;"",H18&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G18&lt;&gt;"",N(G18)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G18&lt;&gt;"",H18&lt;&gt;""),(N(G18)+N(H18))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G18&lt;&gt;"",N(G18)&lt;='설정'!$E$8),AND(H18&lt;&gt;"",N(H18)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G18&lt;&gt;"",H18&lt;&gt;""),(N(G18)+N(H18))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L18" s="29">
-        <f>IF(OR(G18="",H18=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G18-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H18-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G18="",H18=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G18-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G18+H18)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G18+H18)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G18-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H18-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M18" s="7" t="n"/>
@@ -23904,11 +23901,11 @@
         <v/>
       </c>
       <c r="K19" s="27">
-        <f>IF(I19="","",IF(OR(G19="",H19=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G19&gt;='설정'!$C$6),OR('설정'!$D$6="",G19&lt;'설정'!$D$6),OR('설정'!$E$6="",H19&gt;='설정'!$E$6),OR('설정'!$F$6="",H19&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G19&gt;='설정'!$C$7),OR('설정'!$D$7="",G19&lt;'설정'!$D$7),OR('설정'!$E$7="",H19&gt;='설정'!$E$7),OR('설정'!$F$7="",H19&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G19&gt;='설정'!$C$8),OR('설정'!$D$8="",G19&lt;'설정'!$D$8),OR('설정'!$E$8="",H19&gt;='설정'!$E$8),OR('설정'!$F$8="",H19&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I19="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G19&lt;&gt;"",H19&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G19&lt;&gt;"",N(G19)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G19&lt;&gt;"",H19&lt;&gt;""),(N(G19)+N(H19))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G19&lt;&gt;"",N(G19)&lt;='설정'!$E$6),AND(H19&lt;&gt;"",N(H19)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G19&lt;&gt;"",H19&lt;&gt;""),(N(G19)+N(H19))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G19&lt;&gt;"",H19&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G19&lt;&gt;"",N(G19)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G19&lt;&gt;"",H19&lt;&gt;""),(N(G19)+N(H19))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G19&lt;&gt;"",N(G19)&lt;='설정'!$E$7),AND(H19&lt;&gt;"",N(H19)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G19&lt;&gt;"",H19&lt;&gt;""),(N(G19)+N(H19))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G19&lt;&gt;"",H19&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G19&lt;&gt;"",N(G19)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G19&lt;&gt;"",H19&lt;&gt;""),(N(G19)+N(H19))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G19&lt;&gt;"",N(G19)&lt;='설정'!$E$8),AND(H19&lt;&gt;"",N(H19)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G19&lt;&gt;"",H19&lt;&gt;""),(N(G19)+N(H19))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L19" s="29">
-        <f>IF(OR(G19="",H19=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G19-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H19-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G19="",H19=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G19-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G19+H19)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G19+H19)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G19-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H19-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M19" s="7" t="n"/>
@@ -23967,11 +23964,11 @@
         <v/>
       </c>
       <c r="K20" s="27">
-        <f>IF(I20="","",IF(OR(G20="",H20=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G20&gt;='설정'!$C$6),OR('설정'!$D$6="",G20&lt;'설정'!$D$6),OR('설정'!$E$6="",H20&gt;='설정'!$E$6),OR('설정'!$F$6="",H20&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G20&gt;='설정'!$C$7),OR('설정'!$D$7="",G20&lt;'설정'!$D$7),OR('설정'!$E$7="",H20&gt;='설정'!$E$7),OR('설정'!$F$7="",H20&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G20&gt;='설정'!$C$8),OR('설정'!$D$8="",G20&lt;'설정'!$D$8),OR('설정'!$E$8="",H20&gt;='설정'!$E$8),OR('설정'!$F$8="",H20&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I20="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G20&lt;&gt;"",H20&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G20&lt;&gt;"",N(G20)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G20&lt;&gt;"",H20&lt;&gt;""),(N(G20)+N(H20))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G20&lt;&gt;"",N(G20)&lt;='설정'!$E$6),AND(H20&lt;&gt;"",N(H20)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G20&lt;&gt;"",H20&lt;&gt;""),(N(G20)+N(H20))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G20&lt;&gt;"",H20&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G20&lt;&gt;"",N(G20)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G20&lt;&gt;"",H20&lt;&gt;""),(N(G20)+N(H20))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G20&lt;&gt;"",N(G20)&lt;='설정'!$E$7),AND(H20&lt;&gt;"",N(H20)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G20&lt;&gt;"",H20&lt;&gt;""),(N(G20)+N(H20))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G20&lt;&gt;"",H20&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G20&lt;&gt;"",N(G20)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G20&lt;&gt;"",H20&lt;&gt;""),(N(G20)+N(H20))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G20&lt;&gt;"",N(G20)&lt;='설정'!$E$8),AND(H20&lt;&gt;"",N(H20)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G20&lt;&gt;"",H20&lt;&gt;""),(N(G20)+N(H20))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L20" s="29">
-        <f>IF(OR(G20="",H20=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G20-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H20-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G20="",H20=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G20-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G20+H20)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G20+H20)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G20-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H20-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M20" s="7" t="n"/>
@@ -24030,11 +24027,11 @@
         <v/>
       </c>
       <c r="K21" s="27">
-        <f>IF(I21="","",IF(OR(G21="",H21=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G21&gt;='설정'!$C$6),OR('설정'!$D$6="",G21&lt;'설정'!$D$6),OR('설정'!$E$6="",H21&gt;='설정'!$E$6),OR('설정'!$F$6="",H21&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G21&gt;='설정'!$C$7),OR('설정'!$D$7="",G21&lt;'설정'!$D$7),OR('설정'!$E$7="",H21&gt;='설정'!$E$7),OR('설정'!$F$7="",H21&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G21&gt;='설정'!$C$8),OR('설정'!$D$8="",G21&lt;'설정'!$D$8),OR('설정'!$E$8="",H21&gt;='설정'!$E$8),OR('설정'!$F$8="",H21&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I21="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G21&lt;&gt;"",H21&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G21&lt;&gt;"",N(G21)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G21&lt;&gt;"",H21&lt;&gt;""),(N(G21)+N(H21))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G21&lt;&gt;"",N(G21)&lt;='설정'!$E$6),AND(H21&lt;&gt;"",N(H21)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G21&lt;&gt;"",H21&lt;&gt;""),(N(G21)+N(H21))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G21&lt;&gt;"",H21&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G21&lt;&gt;"",N(G21)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G21&lt;&gt;"",H21&lt;&gt;""),(N(G21)+N(H21))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G21&lt;&gt;"",N(G21)&lt;='설정'!$E$7),AND(H21&lt;&gt;"",N(H21)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G21&lt;&gt;"",H21&lt;&gt;""),(N(G21)+N(H21))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G21&lt;&gt;"",H21&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G21&lt;&gt;"",N(G21)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G21&lt;&gt;"",H21&lt;&gt;""),(N(G21)+N(H21))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G21&lt;&gt;"",N(G21)&lt;='설정'!$E$8),AND(H21&lt;&gt;"",N(H21)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G21&lt;&gt;"",H21&lt;&gt;""),(N(G21)+N(H21))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L21" s="29">
-        <f>IF(OR(G21="",H21=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G21-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H21-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G21="",H21=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G21-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G21+H21)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G21+H21)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G21-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H21-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M21" s="7" t="n"/>
@@ -24093,11 +24090,11 @@
         <v/>
       </c>
       <c r="K22" s="27">
-        <f>IF(I22="","",IF(OR(G22="",H22=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G22&gt;='설정'!$C$6),OR('설정'!$D$6="",G22&lt;'설정'!$D$6),OR('설정'!$E$6="",H22&gt;='설정'!$E$6),OR('설정'!$F$6="",H22&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G22&gt;='설정'!$C$7),OR('설정'!$D$7="",G22&lt;'설정'!$D$7),OR('설정'!$E$7="",H22&gt;='설정'!$E$7),OR('설정'!$F$7="",H22&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G22&gt;='설정'!$C$8),OR('설정'!$D$8="",G22&lt;'설정'!$D$8),OR('설정'!$E$8="",H22&gt;='설정'!$E$8),OR('설정'!$F$8="",H22&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I22="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G22&lt;&gt;"",H22&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G22&lt;&gt;"",N(G22)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G22&lt;&gt;"",H22&lt;&gt;""),(N(G22)+N(H22))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G22&lt;&gt;"",N(G22)&lt;='설정'!$E$6),AND(H22&lt;&gt;"",N(H22)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G22&lt;&gt;"",H22&lt;&gt;""),(N(G22)+N(H22))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G22&lt;&gt;"",H22&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G22&lt;&gt;"",N(G22)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G22&lt;&gt;"",H22&lt;&gt;""),(N(G22)+N(H22))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G22&lt;&gt;"",N(G22)&lt;='설정'!$E$7),AND(H22&lt;&gt;"",N(H22)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G22&lt;&gt;"",H22&lt;&gt;""),(N(G22)+N(H22))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G22&lt;&gt;"",H22&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G22&lt;&gt;"",N(G22)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G22&lt;&gt;"",H22&lt;&gt;""),(N(G22)+N(H22))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G22&lt;&gt;"",N(G22)&lt;='설정'!$E$8),AND(H22&lt;&gt;"",N(H22)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G22&lt;&gt;"",H22&lt;&gt;""),(N(G22)+N(H22))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L22" s="29">
-        <f>IF(OR(G22="",H22=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G22-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H22-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G22="",H22=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G22-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G22+H22)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G22+H22)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G22-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H22-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M22" s="7" t="n"/>
@@ -24156,11 +24153,11 @@
         <v/>
       </c>
       <c r="K23" s="27">
-        <f>IF(I23="","",IF(OR(G23="",H23=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G23&gt;='설정'!$C$6),OR('설정'!$D$6="",G23&lt;'설정'!$D$6),OR('설정'!$E$6="",H23&gt;='설정'!$E$6),OR('설정'!$F$6="",H23&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G23&gt;='설정'!$C$7),OR('설정'!$D$7="",G23&lt;'설정'!$D$7),OR('설정'!$E$7="",H23&gt;='설정'!$E$7),OR('설정'!$F$7="",H23&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G23&gt;='설정'!$C$8),OR('설정'!$D$8="",G23&lt;'설정'!$D$8),OR('설정'!$E$8="",H23&gt;='설정'!$E$8),OR('설정'!$F$8="",H23&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I23="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G23&lt;&gt;"",H23&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G23&lt;&gt;"",N(G23)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G23&lt;&gt;"",H23&lt;&gt;""),(N(G23)+N(H23))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G23&lt;&gt;"",N(G23)&lt;='설정'!$E$6),AND(H23&lt;&gt;"",N(H23)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G23&lt;&gt;"",H23&lt;&gt;""),(N(G23)+N(H23))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G23&lt;&gt;"",H23&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G23&lt;&gt;"",N(G23)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G23&lt;&gt;"",H23&lt;&gt;""),(N(G23)+N(H23))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G23&lt;&gt;"",N(G23)&lt;='설정'!$E$7),AND(H23&lt;&gt;"",N(H23)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G23&lt;&gt;"",H23&lt;&gt;""),(N(G23)+N(H23))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G23&lt;&gt;"",H23&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G23&lt;&gt;"",N(G23)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G23&lt;&gt;"",H23&lt;&gt;""),(N(G23)+N(H23))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G23&lt;&gt;"",N(G23)&lt;='설정'!$E$8),AND(H23&lt;&gt;"",N(H23)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G23&lt;&gt;"",H23&lt;&gt;""),(N(G23)+N(H23))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L23" s="29">
-        <f>IF(OR(G23="",H23=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G23-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H23-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G23="",H23=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G23-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G23+H23)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G23+H23)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G23-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H23-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M23" s="7" t="n"/>
@@ -24219,11 +24216,11 @@
         <v/>
       </c>
       <c r="K24" s="27">
-        <f>IF(I24="","",IF(OR(G24="",H24=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G24&gt;='설정'!$C$6),OR('설정'!$D$6="",G24&lt;'설정'!$D$6),OR('설정'!$E$6="",H24&gt;='설정'!$E$6),OR('설정'!$F$6="",H24&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G24&gt;='설정'!$C$7),OR('설정'!$D$7="",G24&lt;'설정'!$D$7),OR('설정'!$E$7="",H24&gt;='설정'!$E$7),OR('설정'!$F$7="",H24&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G24&gt;='설정'!$C$8),OR('설정'!$D$8="",G24&lt;'설정'!$D$8),OR('설정'!$E$8="",H24&gt;='설정'!$E$8),OR('설정'!$F$8="",H24&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I24="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G24&lt;&gt;"",H24&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G24&lt;&gt;"",N(G24)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G24&lt;&gt;"",H24&lt;&gt;""),(N(G24)+N(H24))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G24&lt;&gt;"",N(G24)&lt;='설정'!$E$6),AND(H24&lt;&gt;"",N(H24)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G24&lt;&gt;"",H24&lt;&gt;""),(N(G24)+N(H24))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G24&lt;&gt;"",H24&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G24&lt;&gt;"",N(G24)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G24&lt;&gt;"",H24&lt;&gt;""),(N(G24)+N(H24))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G24&lt;&gt;"",N(G24)&lt;='설정'!$E$7),AND(H24&lt;&gt;"",N(H24)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G24&lt;&gt;"",H24&lt;&gt;""),(N(G24)+N(H24))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G24&lt;&gt;"",H24&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G24&lt;&gt;"",N(G24)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G24&lt;&gt;"",H24&lt;&gt;""),(N(G24)+N(H24))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G24&lt;&gt;"",N(G24)&lt;='설정'!$E$8),AND(H24&lt;&gt;"",N(H24)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G24&lt;&gt;"",H24&lt;&gt;""),(N(G24)+N(H24))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L24" s="29">
-        <f>IF(OR(G24="",H24=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G24-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H24-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G24="",H24=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G24-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G24+H24)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G24+H24)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G24-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H24-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M24" s="7" t="n"/>
@@ -24282,11 +24279,11 @@
         <v/>
       </c>
       <c r="K25" s="27">
-        <f>IF(I25="","",IF(OR(G25="",H25=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G25&gt;='설정'!$C$6),OR('설정'!$D$6="",G25&lt;'설정'!$D$6),OR('설정'!$E$6="",H25&gt;='설정'!$E$6),OR('설정'!$F$6="",H25&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G25&gt;='설정'!$C$7),OR('설정'!$D$7="",G25&lt;'설정'!$D$7),OR('설정'!$E$7="",H25&gt;='설정'!$E$7),OR('설정'!$F$7="",H25&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G25&gt;='설정'!$C$8),OR('설정'!$D$8="",G25&lt;'설정'!$D$8),OR('설정'!$E$8="",H25&gt;='설정'!$E$8),OR('설정'!$F$8="",H25&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I25="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G25&lt;&gt;"",H25&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G25&lt;&gt;"",N(G25)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G25&lt;&gt;"",H25&lt;&gt;""),(N(G25)+N(H25))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G25&lt;&gt;"",N(G25)&lt;='설정'!$E$6),AND(H25&lt;&gt;"",N(H25)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G25&lt;&gt;"",H25&lt;&gt;""),(N(G25)+N(H25))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G25&lt;&gt;"",H25&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G25&lt;&gt;"",N(G25)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G25&lt;&gt;"",H25&lt;&gt;""),(N(G25)+N(H25))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G25&lt;&gt;"",N(G25)&lt;='설정'!$E$7),AND(H25&lt;&gt;"",N(H25)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G25&lt;&gt;"",H25&lt;&gt;""),(N(G25)+N(H25))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G25&lt;&gt;"",H25&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G25&lt;&gt;"",N(G25)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G25&lt;&gt;"",H25&lt;&gt;""),(N(G25)+N(H25))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G25&lt;&gt;"",N(G25)&lt;='설정'!$E$8),AND(H25&lt;&gt;"",N(H25)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G25&lt;&gt;"",H25&lt;&gt;""),(N(G25)+N(H25))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L25" s="29">
-        <f>IF(OR(G25="",H25=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G25-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H25-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G25="",H25=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G25-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G25+H25)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G25+H25)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G25-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H25-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M25" s="7" t="n"/>
@@ -24345,11 +24342,11 @@
         <v/>
       </c>
       <c r="K26" s="27">
-        <f>IF(I26="","",IF(OR(G26="",H26=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G26&gt;='설정'!$C$6),OR('설정'!$D$6="",G26&lt;'설정'!$D$6),OR('설정'!$E$6="",H26&gt;='설정'!$E$6),OR('설정'!$F$6="",H26&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G26&gt;='설정'!$C$7),OR('설정'!$D$7="",G26&lt;'설정'!$D$7),OR('설정'!$E$7="",H26&gt;='설정'!$E$7),OR('설정'!$F$7="",H26&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G26&gt;='설정'!$C$8),OR('설정'!$D$8="",G26&lt;'설정'!$D$8),OR('설정'!$E$8="",H26&gt;='설정'!$E$8),OR('설정'!$F$8="",H26&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I26="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G26&lt;&gt;"",H26&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G26&lt;&gt;"",N(G26)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G26&lt;&gt;"",H26&lt;&gt;""),(N(G26)+N(H26))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G26&lt;&gt;"",N(G26)&lt;='설정'!$E$6),AND(H26&lt;&gt;"",N(H26)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G26&lt;&gt;"",H26&lt;&gt;""),(N(G26)+N(H26))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G26&lt;&gt;"",H26&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G26&lt;&gt;"",N(G26)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G26&lt;&gt;"",H26&lt;&gt;""),(N(G26)+N(H26))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G26&lt;&gt;"",N(G26)&lt;='설정'!$E$7),AND(H26&lt;&gt;"",N(H26)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G26&lt;&gt;"",H26&lt;&gt;""),(N(G26)+N(H26))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G26&lt;&gt;"",H26&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G26&lt;&gt;"",N(G26)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G26&lt;&gt;"",H26&lt;&gt;""),(N(G26)+N(H26))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G26&lt;&gt;"",N(G26)&lt;='설정'!$E$8),AND(H26&lt;&gt;"",N(H26)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G26&lt;&gt;"",H26&lt;&gt;""),(N(G26)+N(H26))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L26" s="29">
-        <f>IF(OR(G26="",H26=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G26-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H26-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G26="",H26=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G26-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G26+H26)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G26+H26)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G26-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H26-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M26" s="7" t="n"/>
@@ -24408,11 +24405,11 @@
         <v/>
       </c>
       <c r="K27" s="27">
-        <f>IF(I27="","",IF(OR(G27="",H27=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G27&gt;='설정'!$C$6),OR('설정'!$D$6="",G27&lt;'설정'!$D$6),OR('설정'!$E$6="",H27&gt;='설정'!$E$6),OR('설정'!$F$6="",H27&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G27&gt;='설정'!$C$7),OR('설정'!$D$7="",G27&lt;'설정'!$D$7),OR('설정'!$E$7="",H27&gt;='설정'!$E$7),OR('설정'!$F$7="",H27&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G27&gt;='설정'!$C$8),OR('설정'!$D$8="",G27&lt;'설정'!$D$8),OR('설정'!$E$8="",H27&gt;='설정'!$E$8),OR('설정'!$F$8="",H27&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I27="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G27&lt;&gt;"",H27&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G27&lt;&gt;"",N(G27)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G27&lt;&gt;"",H27&lt;&gt;""),(N(G27)+N(H27))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G27&lt;&gt;"",N(G27)&lt;='설정'!$E$6),AND(H27&lt;&gt;"",N(H27)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G27&lt;&gt;"",H27&lt;&gt;""),(N(G27)+N(H27))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G27&lt;&gt;"",H27&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G27&lt;&gt;"",N(G27)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G27&lt;&gt;"",H27&lt;&gt;""),(N(G27)+N(H27))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G27&lt;&gt;"",N(G27)&lt;='설정'!$E$7),AND(H27&lt;&gt;"",N(H27)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G27&lt;&gt;"",H27&lt;&gt;""),(N(G27)+N(H27))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G27&lt;&gt;"",H27&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G27&lt;&gt;"",N(G27)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G27&lt;&gt;"",H27&lt;&gt;""),(N(G27)+N(H27))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G27&lt;&gt;"",N(G27)&lt;='설정'!$E$8),AND(H27&lt;&gt;"",N(H27)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G27&lt;&gt;"",H27&lt;&gt;""),(N(G27)+N(H27))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L27" s="29">
-        <f>IF(OR(G27="",H27=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G27-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H27-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G27="",H27=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G27-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G27+H27)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G27+H27)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G27-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H27-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M27" s="7" t="n"/>
@@ -24471,11 +24468,11 @@
         <v/>
       </c>
       <c r="K28" s="27">
-        <f>IF(I28="","",IF(OR(G28="",H28=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G28&gt;='설정'!$C$6),OR('설정'!$D$6="",G28&lt;'설정'!$D$6),OR('설정'!$E$6="",H28&gt;='설정'!$E$6),OR('설정'!$F$6="",H28&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G28&gt;='설정'!$C$7),OR('설정'!$D$7="",G28&lt;'설정'!$D$7),OR('설정'!$E$7="",H28&gt;='설정'!$E$7),OR('설정'!$F$7="",H28&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G28&gt;='설정'!$C$8),OR('설정'!$D$8="",G28&lt;'설정'!$D$8),OR('설정'!$E$8="",H28&gt;='설정'!$E$8),OR('설정'!$F$8="",H28&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I28="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G28&lt;&gt;"",H28&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G28&lt;&gt;"",N(G28)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G28&lt;&gt;"",H28&lt;&gt;""),(N(G28)+N(H28))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G28&lt;&gt;"",N(G28)&lt;='설정'!$E$6),AND(H28&lt;&gt;"",N(H28)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G28&lt;&gt;"",H28&lt;&gt;""),(N(G28)+N(H28))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G28&lt;&gt;"",H28&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G28&lt;&gt;"",N(G28)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G28&lt;&gt;"",H28&lt;&gt;""),(N(G28)+N(H28))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G28&lt;&gt;"",N(G28)&lt;='설정'!$E$7),AND(H28&lt;&gt;"",N(H28)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G28&lt;&gt;"",H28&lt;&gt;""),(N(G28)+N(H28))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G28&lt;&gt;"",H28&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G28&lt;&gt;"",N(G28)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G28&lt;&gt;"",H28&lt;&gt;""),(N(G28)+N(H28))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G28&lt;&gt;"",N(G28)&lt;='설정'!$E$8),AND(H28&lt;&gt;"",N(H28)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G28&lt;&gt;"",H28&lt;&gt;""),(N(G28)+N(H28))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L28" s="29">
-        <f>IF(OR(G28="",H28=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G28-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H28-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G28="",H28=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G28-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G28+H28)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G28+H28)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G28-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H28-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M28" s="7" t="n"/>
@@ -24534,11 +24531,11 @@
         <v/>
       </c>
       <c r="K29" s="27">
-        <f>IF(I29="","",IF(OR(G29="",H29=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G29&gt;='설정'!$C$6),OR('설정'!$D$6="",G29&lt;'설정'!$D$6),OR('설정'!$E$6="",H29&gt;='설정'!$E$6),OR('설정'!$F$6="",H29&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G29&gt;='설정'!$C$7),OR('설정'!$D$7="",G29&lt;'설정'!$D$7),OR('설정'!$E$7="",H29&gt;='설정'!$E$7),OR('설정'!$F$7="",H29&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G29&gt;='설정'!$C$8),OR('설정'!$D$8="",G29&lt;'설정'!$D$8),OR('설정'!$E$8="",H29&gt;='설정'!$E$8),OR('설정'!$F$8="",H29&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I29="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G29&lt;&gt;"",H29&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G29&lt;&gt;"",N(G29)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G29&lt;&gt;"",H29&lt;&gt;""),(N(G29)+N(H29))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G29&lt;&gt;"",N(G29)&lt;='설정'!$E$6),AND(H29&lt;&gt;"",N(H29)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G29&lt;&gt;"",H29&lt;&gt;""),(N(G29)+N(H29))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G29&lt;&gt;"",H29&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G29&lt;&gt;"",N(G29)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G29&lt;&gt;"",H29&lt;&gt;""),(N(G29)+N(H29))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G29&lt;&gt;"",N(G29)&lt;='설정'!$E$7),AND(H29&lt;&gt;"",N(H29)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G29&lt;&gt;"",H29&lt;&gt;""),(N(G29)+N(H29))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G29&lt;&gt;"",H29&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G29&lt;&gt;"",N(G29)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G29&lt;&gt;"",H29&lt;&gt;""),(N(G29)+N(H29))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G29&lt;&gt;"",N(G29)&lt;='설정'!$E$8),AND(H29&lt;&gt;"",N(H29)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G29&lt;&gt;"",H29&lt;&gt;""),(N(G29)+N(H29))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L29" s="29">
-        <f>IF(OR(G29="",H29=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G29-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H29-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G29="",H29=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G29-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G29+H29)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G29+H29)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G29-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H29-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M29" s="7" t="n"/>
@@ -24597,11 +24594,11 @@
         <v/>
       </c>
       <c r="K30" s="27">
-        <f>IF(I30="","",IF(OR(G30="",H30=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G30&gt;='설정'!$C$6),OR('설정'!$D$6="",G30&lt;'설정'!$D$6),OR('설정'!$E$6="",H30&gt;='설정'!$E$6),OR('설정'!$F$6="",H30&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G30&gt;='설정'!$C$7),OR('설정'!$D$7="",G30&lt;'설정'!$D$7),OR('설정'!$E$7="",H30&gt;='설정'!$E$7),OR('설정'!$F$7="",H30&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G30&gt;='설정'!$C$8),OR('설정'!$D$8="",G30&lt;'설정'!$D$8),OR('설정'!$E$8="",H30&gt;='설정'!$E$8),OR('설정'!$F$8="",H30&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I30="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G30&lt;&gt;"",H30&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G30&lt;&gt;"",N(G30)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G30&lt;&gt;"",H30&lt;&gt;""),(N(G30)+N(H30))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G30&lt;&gt;"",N(G30)&lt;='설정'!$E$6),AND(H30&lt;&gt;"",N(H30)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G30&lt;&gt;"",H30&lt;&gt;""),(N(G30)+N(H30))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G30&lt;&gt;"",H30&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G30&lt;&gt;"",N(G30)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G30&lt;&gt;"",H30&lt;&gt;""),(N(G30)+N(H30))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G30&lt;&gt;"",N(G30)&lt;='설정'!$E$7),AND(H30&lt;&gt;"",N(H30)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G30&lt;&gt;"",H30&lt;&gt;""),(N(G30)+N(H30))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G30&lt;&gt;"",H30&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G30&lt;&gt;"",N(G30)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G30&lt;&gt;"",H30&lt;&gt;""),(N(G30)+N(H30))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G30&lt;&gt;"",N(G30)&lt;='설정'!$E$8),AND(H30&lt;&gt;"",N(H30)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G30&lt;&gt;"",H30&lt;&gt;""),(N(G30)+N(H30))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L30" s="29">
-        <f>IF(OR(G30="",H30=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G30-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H30-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G30="",H30=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G30-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G30+H30)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G30+H30)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G30-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H30-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M30" s="7" t="n"/>
@@ -24660,11 +24657,11 @@
         <v/>
       </c>
       <c r="K31" s="27">
-        <f>IF(I31="","",IF(OR(G31="",H31=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G31&gt;='설정'!$C$6),OR('설정'!$D$6="",G31&lt;'설정'!$D$6),OR('설정'!$E$6="",H31&gt;='설정'!$E$6),OR('설정'!$F$6="",H31&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G31&gt;='설정'!$C$7),OR('설정'!$D$7="",G31&lt;'설정'!$D$7),OR('설정'!$E$7="",H31&gt;='설정'!$E$7),OR('설정'!$F$7="",H31&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G31&gt;='설정'!$C$8),OR('설정'!$D$8="",G31&lt;'설정'!$D$8),OR('설정'!$E$8="",H31&gt;='설정'!$E$8),OR('설정'!$F$8="",H31&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I31="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G31&lt;&gt;"",H31&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G31&lt;&gt;"",N(G31)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G31&lt;&gt;"",H31&lt;&gt;""),(N(G31)+N(H31))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G31&lt;&gt;"",N(G31)&lt;='설정'!$E$6),AND(H31&lt;&gt;"",N(H31)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G31&lt;&gt;"",H31&lt;&gt;""),(N(G31)+N(H31))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G31&lt;&gt;"",H31&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G31&lt;&gt;"",N(G31)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G31&lt;&gt;"",H31&lt;&gt;""),(N(G31)+N(H31))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G31&lt;&gt;"",N(G31)&lt;='설정'!$E$7),AND(H31&lt;&gt;"",N(H31)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G31&lt;&gt;"",H31&lt;&gt;""),(N(G31)+N(H31))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G31&lt;&gt;"",H31&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G31&lt;&gt;"",N(G31)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G31&lt;&gt;"",H31&lt;&gt;""),(N(G31)+N(H31))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G31&lt;&gt;"",N(G31)&lt;='설정'!$E$8),AND(H31&lt;&gt;"",N(H31)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G31&lt;&gt;"",H31&lt;&gt;""),(N(G31)+N(H31))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L31" s="29">
-        <f>IF(OR(G31="",H31=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G31-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H31-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G31="",H31=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G31-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G31+H31)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G31+H31)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G31-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H31-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M31" s="7" t="n"/>
@@ -24723,11 +24720,11 @@
         <v/>
       </c>
       <c r="K32" s="27">
-        <f>IF(I32="","",IF(OR(G32="",H32=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G32&gt;='설정'!$C$6),OR('설정'!$D$6="",G32&lt;'설정'!$D$6),OR('설정'!$E$6="",H32&gt;='설정'!$E$6),OR('설정'!$F$6="",H32&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G32&gt;='설정'!$C$7),OR('설정'!$D$7="",G32&lt;'설정'!$D$7),OR('설정'!$E$7="",H32&gt;='설정'!$E$7),OR('설정'!$F$7="",H32&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G32&gt;='설정'!$C$8),OR('설정'!$D$8="",G32&lt;'설정'!$D$8),OR('설정'!$E$8="",H32&gt;='설정'!$E$8),OR('설정'!$F$8="",H32&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I32="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G32&lt;&gt;"",H32&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G32&lt;&gt;"",N(G32)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G32&lt;&gt;"",H32&lt;&gt;""),(N(G32)+N(H32))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G32&lt;&gt;"",N(G32)&lt;='설정'!$E$6),AND(H32&lt;&gt;"",N(H32)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G32&lt;&gt;"",H32&lt;&gt;""),(N(G32)+N(H32))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G32&lt;&gt;"",H32&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G32&lt;&gt;"",N(G32)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G32&lt;&gt;"",H32&lt;&gt;""),(N(G32)+N(H32))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G32&lt;&gt;"",N(G32)&lt;='설정'!$E$7),AND(H32&lt;&gt;"",N(H32)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G32&lt;&gt;"",H32&lt;&gt;""),(N(G32)+N(H32))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G32&lt;&gt;"",H32&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G32&lt;&gt;"",N(G32)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G32&lt;&gt;"",H32&lt;&gt;""),(N(G32)+N(H32))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G32&lt;&gt;"",N(G32)&lt;='설정'!$E$8),AND(H32&lt;&gt;"",N(H32)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G32&lt;&gt;"",H32&lt;&gt;""),(N(G32)+N(H32))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L32" s="29">
-        <f>IF(OR(G32="",H32=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G32-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H32-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G32="",H32=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G32-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G32+H32)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G32+H32)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G32-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H32-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M32" s="7" t="n"/>
@@ -24786,11 +24783,11 @@
         <v/>
       </c>
       <c r="K33" s="27">
-        <f>IF(I33="","",IF(OR(G33="",H33=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G33&gt;='설정'!$C$6),OR('설정'!$D$6="",G33&lt;'설정'!$D$6),OR('설정'!$E$6="",H33&gt;='설정'!$E$6),OR('설정'!$F$6="",H33&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G33&gt;='설정'!$C$7),OR('설정'!$D$7="",G33&lt;'설정'!$D$7),OR('설정'!$E$7="",H33&gt;='설정'!$E$7),OR('설정'!$F$7="",H33&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G33&gt;='설정'!$C$8),OR('설정'!$D$8="",G33&lt;'설정'!$D$8),OR('설정'!$E$8="",H33&gt;='설정'!$E$8),OR('설정'!$F$8="",H33&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I33="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G33&lt;&gt;"",H33&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G33&lt;&gt;"",N(G33)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G33&lt;&gt;"",H33&lt;&gt;""),(N(G33)+N(H33))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G33&lt;&gt;"",N(G33)&lt;='설정'!$E$6),AND(H33&lt;&gt;"",N(H33)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G33&lt;&gt;"",H33&lt;&gt;""),(N(G33)+N(H33))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G33&lt;&gt;"",H33&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G33&lt;&gt;"",N(G33)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G33&lt;&gt;"",H33&lt;&gt;""),(N(G33)+N(H33))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G33&lt;&gt;"",N(G33)&lt;='설정'!$E$7),AND(H33&lt;&gt;"",N(H33)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G33&lt;&gt;"",H33&lt;&gt;""),(N(G33)+N(H33))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G33&lt;&gt;"",H33&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G33&lt;&gt;"",N(G33)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G33&lt;&gt;"",H33&lt;&gt;""),(N(G33)+N(H33))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G33&lt;&gt;"",N(G33)&lt;='설정'!$E$8),AND(H33&lt;&gt;"",N(H33)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G33&lt;&gt;"",H33&lt;&gt;""),(N(G33)+N(H33))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L33" s="29">
-        <f>IF(OR(G33="",H33=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G33-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H33-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G33="",H33=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G33-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G33+H33)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G33+H33)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G33-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H33-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M33" s="7" t="n"/>
@@ -24849,11 +24846,11 @@
         <v/>
       </c>
       <c r="K34" s="27">
-        <f>IF(I34="","",IF(OR(G34="",H34=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G34&gt;='설정'!$C$6),OR('설정'!$D$6="",G34&lt;'설정'!$D$6),OR('설정'!$E$6="",H34&gt;='설정'!$E$6),OR('설정'!$F$6="",H34&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G34&gt;='설정'!$C$7),OR('설정'!$D$7="",G34&lt;'설정'!$D$7),OR('설정'!$E$7="",H34&gt;='설정'!$E$7),OR('설정'!$F$7="",H34&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G34&gt;='설정'!$C$8),OR('설정'!$D$8="",G34&lt;'설정'!$D$8),OR('설정'!$E$8="",H34&gt;='설정'!$E$8),OR('설정'!$F$8="",H34&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I34="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G34&lt;&gt;"",H34&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G34&lt;&gt;"",N(G34)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G34&lt;&gt;"",H34&lt;&gt;""),(N(G34)+N(H34))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G34&lt;&gt;"",N(G34)&lt;='설정'!$E$6),AND(H34&lt;&gt;"",N(H34)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G34&lt;&gt;"",H34&lt;&gt;""),(N(G34)+N(H34))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G34&lt;&gt;"",H34&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G34&lt;&gt;"",N(G34)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G34&lt;&gt;"",H34&lt;&gt;""),(N(G34)+N(H34))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G34&lt;&gt;"",N(G34)&lt;='설정'!$E$7),AND(H34&lt;&gt;"",N(H34)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G34&lt;&gt;"",H34&lt;&gt;""),(N(G34)+N(H34))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G34&lt;&gt;"",H34&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G34&lt;&gt;"",N(G34)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G34&lt;&gt;"",H34&lt;&gt;""),(N(G34)+N(H34))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G34&lt;&gt;"",N(G34)&lt;='설정'!$E$8),AND(H34&lt;&gt;"",N(H34)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G34&lt;&gt;"",H34&lt;&gt;""),(N(G34)+N(H34))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L34" s="29">
-        <f>IF(OR(G34="",H34=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G34-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H34-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G34="",H34=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G34-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G34+H34)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G34+H34)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G34-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H34-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M34" s="7" t="n"/>
@@ -24912,11 +24909,11 @@
         <v/>
       </c>
       <c r="K35" s="27">
-        <f>IF(I35="","",IF(OR(G35="",H35=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G35&gt;='설정'!$C$6),OR('설정'!$D$6="",G35&lt;'설정'!$D$6),OR('설정'!$E$6="",H35&gt;='설정'!$E$6),OR('설정'!$F$6="",H35&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G35&gt;='설정'!$C$7),OR('설정'!$D$7="",G35&lt;'설정'!$D$7),OR('설정'!$E$7="",H35&gt;='설정'!$E$7),OR('설정'!$F$7="",H35&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G35&gt;='설정'!$C$8),OR('설정'!$D$8="",G35&lt;'설정'!$D$8),OR('설정'!$E$8="",H35&gt;='설정'!$E$8),OR('설정'!$F$8="",H35&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I35="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G35&lt;&gt;"",H35&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G35&lt;&gt;"",N(G35)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G35&lt;&gt;"",H35&lt;&gt;""),(N(G35)+N(H35))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G35&lt;&gt;"",N(G35)&lt;='설정'!$E$6),AND(H35&lt;&gt;"",N(H35)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G35&lt;&gt;"",H35&lt;&gt;""),(N(G35)+N(H35))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G35&lt;&gt;"",H35&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G35&lt;&gt;"",N(G35)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G35&lt;&gt;"",H35&lt;&gt;""),(N(G35)+N(H35))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G35&lt;&gt;"",N(G35)&lt;='설정'!$E$7),AND(H35&lt;&gt;"",N(H35)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G35&lt;&gt;"",H35&lt;&gt;""),(N(G35)+N(H35))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G35&lt;&gt;"",H35&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G35&lt;&gt;"",N(G35)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G35&lt;&gt;"",H35&lt;&gt;""),(N(G35)+N(H35))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G35&lt;&gt;"",N(G35)&lt;='설정'!$E$8),AND(H35&lt;&gt;"",N(H35)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G35&lt;&gt;"",H35&lt;&gt;""),(N(G35)+N(H35))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L35" s="29">
-        <f>IF(OR(G35="",H35=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G35-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H35-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G35="",H35=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G35-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G35+H35)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G35+H35)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G35-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H35-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M35" s="7" t="n"/>
@@ -24975,11 +24972,11 @@
         <v/>
       </c>
       <c r="K36" s="27">
-        <f>IF(I36="","",IF(OR(G36="",H36=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G36&gt;='설정'!$C$6),OR('설정'!$D$6="",G36&lt;'설정'!$D$6),OR('설정'!$E$6="",H36&gt;='설정'!$E$6),OR('설정'!$F$6="",H36&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G36&gt;='설정'!$C$7),OR('설정'!$D$7="",G36&lt;'설정'!$D$7),OR('설정'!$E$7="",H36&gt;='설정'!$E$7),OR('설정'!$F$7="",H36&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G36&gt;='설정'!$C$8),OR('설정'!$D$8="",G36&lt;'설정'!$D$8),OR('설정'!$E$8="",H36&gt;='설정'!$E$8),OR('설정'!$F$8="",H36&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I36="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G36&lt;&gt;"",H36&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G36&lt;&gt;"",N(G36)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G36&lt;&gt;"",H36&lt;&gt;""),(N(G36)+N(H36))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G36&lt;&gt;"",N(G36)&lt;='설정'!$E$6),AND(H36&lt;&gt;"",N(H36)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G36&lt;&gt;"",H36&lt;&gt;""),(N(G36)+N(H36))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G36&lt;&gt;"",H36&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G36&lt;&gt;"",N(G36)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G36&lt;&gt;"",H36&lt;&gt;""),(N(G36)+N(H36))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G36&lt;&gt;"",N(G36)&lt;='설정'!$E$7),AND(H36&lt;&gt;"",N(H36)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G36&lt;&gt;"",H36&lt;&gt;""),(N(G36)+N(H36))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G36&lt;&gt;"",H36&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G36&lt;&gt;"",N(G36)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G36&lt;&gt;"",H36&lt;&gt;""),(N(G36)+N(H36))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G36&lt;&gt;"",N(G36)&lt;='설정'!$E$8),AND(H36&lt;&gt;"",N(H36)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G36&lt;&gt;"",H36&lt;&gt;""),(N(G36)+N(H36))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L36" s="29">
-        <f>IF(OR(G36="",H36=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G36-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H36-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G36="",H36=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G36-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G36+H36)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G36+H36)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G36-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H36-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M36" s="7" t="n"/>
@@ -25038,11 +25035,11 @@
         <v/>
       </c>
       <c r="K37" s="27">
-        <f>IF(I37="","",IF(OR(G37="",H37=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G37&gt;='설정'!$C$6),OR('설정'!$D$6="",G37&lt;'설정'!$D$6),OR('설정'!$E$6="",H37&gt;='설정'!$E$6),OR('설정'!$F$6="",H37&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G37&gt;='설정'!$C$7),OR('설정'!$D$7="",G37&lt;'설정'!$D$7),OR('설정'!$E$7="",H37&gt;='설정'!$E$7),OR('설정'!$F$7="",H37&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G37&gt;='설정'!$C$8),OR('설정'!$D$8="",G37&lt;'설정'!$D$8),OR('설정'!$E$8="",H37&gt;='설정'!$E$8),OR('설정'!$F$8="",H37&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I37="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G37&lt;&gt;"",H37&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G37&lt;&gt;"",N(G37)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G37&lt;&gt;"",H37&lt;&gt;""),(N(G37)+N(H37))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G37&lt;&gt;"",N(G37)&lt;='설정'!$E$6),AND(H37&lt;&gt;"",N(H37)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G37&lt;&gt;"",H37&lt;&gt;""),(N(G37)+N(H37))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G37&lt;&gt;"",H37&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G37&lt;&gt;"",N(G37)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G37&lt;&gt;"",H37&lt;&gt;""),(N(G37)+N(H37))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G37&lt;&gt;"",N(G37)&lt;='설정'!$E$7),AND(H37&lt;&gt;"",N(H37)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G37&lt;&gt;"",H37&lt;&gt;""),(N(G37)+N(H37))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G37&lt;&gt;"",H37&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G37&lt;&gt;"",N(G37)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G37&lt;&gt;"",H37&lt;&gt;""),(N(G37)+N(H37))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G37&lt;&gt;"",N(G37)&lt;='설정'!$E$8),AND(H37&lt;&gt;"",N(H37)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G37&lt;&gt;"",H37&lt;&gt;""),(N(G37)+N(H37))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L37" s="29">
-        <f>IF(OR(G37="",H37=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G37-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H37-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G37="",H37=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G37-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G37+H37)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G37+H37)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G37-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H37-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M37" s="7" t="n"/>
@@ -25101,11 +25098,11 @@
         <v/>
       </c>
       <c r="K38" s="27">
-        <f>IF(I38="","",IF(OR(G38="",H38=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G38&gt;='설정'!$C$6),OR('설정'!$D$6="",G38&lt;'설정'!$D$6),OR('설정'!$E$6="",H38&gt;='설정'!$E$6),OR('설정'!$F$6="",H38&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G38&gt;='설정'!$C$7),OR('설정'!$D$7="",G38&lt;'설정'!$D$7),OR('설정'!$E$7="",H38&gt;='설정'!$E$7),OR('설정'!$F$7="",H38&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G38&gt;='설정'!$C$8),OR('설정'!$D$8="",G38&lt;'설정'!$D$8),OR('설정'!$E$8="",H38&gt;='설정'!$E$8),OR('설정'!$F$8="",H38&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I38="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G38&lt;&gt;"",H38&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G38&lt;&gt;"",N(G38)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G38&lt;&gt;"",H38&lt;&gt;""),(N(G38)+N(H38))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G38&lt;&gt;"",N(G38)&lt;='설정'!$E$6),AND(H38&lt;&gt;"",N(H38)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G38&lt;&gt;"",H38&lt;&gt;""),(N(G38)+N(H38))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G38&lt;&gt;"",H38&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G38&lt;&gt;"",N(G38)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G38&lt;&gt;"",H38&lt;&gt;""),(N(G38)+N(H38))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G38&lt;&gt;"",N(G38)&lt;='설정'!$E$7),AND(H38&lt;&gt;"",N(H38)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G38&lt;&gt;"",H38&lt;&gt;""),(N(G38)+N(H38))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G38&lt;&gt;"",H38&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G38&lt;&gt;"",N(G38)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G38&lt;&gt;"",H38&lt;&gt;""),(N(G38)+N(H38))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G38&lt;&gt;"",N(G38)&lt;='설정'!$E$8),AND(H38&lt;&gt;"",N(H38)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G38&lt;&gt;"",H38&lt;&gt;""),(N(G38)+N(H38))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L38" s="29">
-        <f>IF(OR(G38="",H38=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G38-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H38-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G38="",H38=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G38-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G38+H38)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G38+H38)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G38-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H38-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M38" s="7" t="n"/>
@@ -25164,11 +25161,11 @@
         <v/>
       </c>
       <c r="K39" s="27">
-        <f>IF(I39="","",IF(OR(G39="",H39=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G39&gt;='설정'!$C$6),OR('설정'!$D$6="",G39&lt;'설정'!$D$6),OR('설정'!$E$6="",H39&gt;='설정'!$E$6),OR('설정'!$F$6="",H39&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G39&gt;='설정'!$C$7),OR('설정'!$D$7="",G39&lt;'설정'!$D$7),OR('설정'!$E$7="",H39&gt;='설정'!$E$7),OR('설정'!$F$7="",H39&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G39&gt;='설정'!$C$8),OR('설정'!$D$8="",G39&lt;'설정'!$D$8),OR('설정'!$E$8="",H39&gt;='설정'!$E$8),OR('설정'!$F$8="",H39&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I39="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G39&lt;&gt;"",H39&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G39&lt;&gt;"",N(G39)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G39&lt;&gt;"",H39&lt;&gt;""),(N(G39)+N(H39))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G39&lt;&gt;"",N(G39)&lt;='설정'!$E$6),AND(H39&lt;&gt;"",N(H39)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G39&lt;&gt;"",H39&lt;&gt;""),(N(G39)+N(H39))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G39&lt;&gt;"",H39&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G39&lt;&gt;"",N(G39)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G39&lt;&gt;"",H39&lt;&gt;""),(N(G39)+N(H39))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G39&lt;&gt;"",N(G39)&lt;='설정'!$E$7),AND(H39&lt;&gt;"",N(H39)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G39&lt;&gt;"",H39&lt;&gt;""),(N(G39)+N(H39))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G39&lt;&gt;"",H39&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G39&lt;&gt;"",N(G39)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G39&lt;&gt;"",H39&lt;&gt;""),(N(G39)+N(H39))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G39&lt;&gt;"",N(G39)&lt;='설정'!$E$8),AND(H39&lt;&gt;"",N(H39)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G39&lt;&gt;"",H39&lt;&gt;""),(N(G39)+N(H39))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L39" s="29">
-        <f>IF(OR(G39="",H39=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G39-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H39-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G39="",H39=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G39-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G39+H39)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G39+H39)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G39-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H39-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M39" s="7" t="n"/>
@@ -25227,11 +25224,11 @@
         <v/>
       </c>
       <c r="K40" s="27">
-        <f>IF(I40="","",IF(OR(G40="",H40=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G40&gt;='설정'!$C$6),OR('설정'!$D$6="",G40&lt;'설정'!$D$6),OR('설정'!$E$6="",H40&gt;='설정'!$E$6),OR('설정'!$F$6="",H40&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G40&gt;='설정'!$C$7),OR('설정'!$D$7="",G40&lt;'설정'!$D$7),OR('설정'!$E$7="",H40&gt;='설정'!$E$7),OR('설정'!$F$7="",H40&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G40&gt;='설정'!$C$8),OR('설정'!$D$8="",G40&lt;'설정'!$D$8),OR('설정'!$E$8="",H40&gt;='설정'!$E$8),OR('설정'!$F$8="",H40&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I40="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G40&lt;&gt;"",H40&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G40&lt;&gt;"",N(G40)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G40&lt;&gt;"",H40&lt;&gt;""),(N(G40)+N(H40))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G40&lt;&gt;"",N(G40)&lt;='설정'!$E$6),AND(H40&lt;&gt;"",N(H40)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G40&lt;&gt;"",H40&lt;&gt;""),(N(G40)+N(H40))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G40&lt;&gt;"",H40&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G40&lt;&gt;"",N(G40)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G40&lt;&gt;"",H40&lt;&gt;""),(N(G40)+N(H40))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G40&lt;&gt;"",N(G40)&lt;='설정'!$E$7),AND(H40&lt;&gt;"",N(H40)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G40&lt;&gt;"",H40&lt;&gt;""),(N(G40)+N(H40))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G40&lt;&gt;"",H40&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G40&lt;&gt;"",N(G40)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G40&lt;&gt;"",H40&lt;&gt;""),(N(G40)+N(H40))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G40&lt;&gt;"",N(G40)&lt;='설정'!$E$8),AND(H40&lt;&gt;"",N(H40)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G40&lt;&gt;"",H40&lt;&gt;""),(N(G40)+N(H40))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L40" s="29">
-        <f>IF(OR(G40="",H40=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G40-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H40-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G40="",H40=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G40-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G40+H40)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G40+H40)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G40-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H40-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M40" s="7" t="n"/>
@@ -25290,11 +25287,11 @@
         <v/>
       </c>
       <c r="K41" s="27">
-        <f>IF(I41="","",IF(OR(G41="",H41=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G41&gt;='설정'!$C$6),OR('설정'!$D$6="",G41&lt;'설정'!$D$6),OR('설정'!$E$6="",H41&gt;='설정'!$E$6),OR('설정'!$F$6="",H41&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G41&gt;='설정'!$C$7),OR('설정'!$D$7="",G41&lt;'설정'!$D$7),OR('설정'!$E$7="",H41&gt;='설정'!$E$7),OR('설정'!$F$7="",H41&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G41&gt;='설정'!$C$8),OR('설정'!$D$8="",G41&lt;'설정'!$D$8),OR('설정'!$E$8="",H41&gt;='설정'!$E$8),OR('설정'!$F$8="",H41&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I41="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G41&lt;&gt;"",H41&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G41&lt;&gt;"",N(G41)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G41&lt;&gt;"",H41&lt;&gt;""),(N(G41)+N(H41))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G41&lt;&gt;"",N(G41)&lt;='설정'!$E$6),AND(H41&lt;&gt;"",N(H41)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G41&lt;&gt;"",H41&lt;&gt;""),(N(G41)+N(H41))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G41&lt;&gt;"",H41&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G41&lt;&gt;"",N(G41)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G41&lt;&gt;"",H41&lt;&gt;""),(N(G41)+N(H41))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G41&lt;&gt;"",N(G41)&lt;='설정'!$E$7),AND(H41&lt;&gt;"",N(H41)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G41&lt;&gt;"",H41&lt;&gt;""),(N(G41)+N(H41))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G41&lt;&gt;"",H41&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G41&lt;&gt;"",N(G41)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G41&lt;&gt;"",H41&lt;&gt;""),(N(G41)+N(H41))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G41&lt;&gt;"",N(G41)&lt;='설정'!$E$8),AND(H41&lt;&gt;"",N(H41)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G41&lt;&gt;"",H41&lt;&gt;""),(N(G41)+N(H41))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L41" s="29">
-        <f>IF(OR(G41="",H41=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G41-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H41-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G41="",H41=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G41-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G41+H41)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G41+H41)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G41-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H41-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M41" s="7" t="n"/>
@@ -25353,11 +25350,11 @@
         <v/>
       </c>
       <c r="K42" s="27">
-        <f>IF(I42="","",IF(OR(G42="",H42=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G42&gt;='설정'!$C$6),OR('설정'!$D$6="",G42&lt;'설정'!$D$6),OR('설정'!$E$6="",H42&gt;='설정'!$E$6),OR('설정'!$F$6="",H42&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G42&gt;='설정'!$C$7),OR('설정'!$D$7="",G42&lt;'설정'!$D$7),OR('설정'!$E$7="",H42&gt;='설정'!$E$7),OR('설정'!$F$7="",H42&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G42&gt;='설정'!$C$8),OR('설정'!$D$8="",G42&lt;'설정'!$D$8),OR('설정'!$E$8="",H42&gt;='설정'!$E$8),OR('설정'!$F$8="",H42&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I42="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G42&lt;&gt;"",H42&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G42&lt;&gt;"",N(G42)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G42&lt;&gt;"",H42&lt;&gt;""),(N(G42)+N(H42))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G42&lt;&gt;"",N(G42)&lt;='설정'!$E$6),AND(H42&lt;&gt;"",N(H42)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G42&lt;&gt;"",H42&lt;&gt;""),(N(G42)+N(H42))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G42&lt;&gt;"",H42&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G42&lt;&gt;"",N(G42)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G42&lt;&gt;"",H42&lt;&gt;""),(N(G42)+N(H42))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G42&lt;&gt;"",N(G42)&lt;='설정'!$E$7),AND(H42&lt;&gt;"",N(H42)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G42&lt;&gt;"",H42&lt;&gt;""),(N(G42)+N(H42))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G42&lt;&gt;"",H42&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G42&lt;&gt;"",N(G42)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G42&lt;&gt;"",H42&lt;&gt;""),(N(G42)+N(H42))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G42&lt;&gt;"",N(G42)&lt;='설정'!$E$8),AND(H42&lt;&gt;"",N(H42)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G42&lt;&gt;"",H42&lt;&gt;""),(N(G42)+N(H42))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L42" s="29">
-        <f>IF(OR(G42="",H42=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G42-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H42-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G42="",H42=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G42-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G42+H42)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G42+H42)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G42-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H42-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M42" s="7" t="n"/>
@@ -25416,11 +25413,11 @@
         <v/>
       </c>
       <c r="K43" s="27">
-        <f>IF(I43="","",IF(OR(G43="",H43=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G43&gt;='설정'!$C$6),OR('설정'!$D$6="",G43&lt;'설정'!$D$6),OR('설정'!$E$6="",H43&gt;='설정'!$E$6),OR('설정'!$F$6="",H43&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G43&gt;='설정'!$C$7),OR('설정'!$D$7="",G43&lt;'설정'!$D$7),OR('설정'!$E$7="",H43&gt;='설정'!$E$7),OR('설정'!$F$7="",H43&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G43&gt;='설정'!$C$8),OR('설정'!$D$8="",G43&lt;'설정'!$D$8),OR('설정'!$E$8="",H43&gt;='설정'!$E$8),OR('설정'!$F$8="",H43&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I43="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G43&lt;&gt;"",H43&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G43&lt;&gt;"",N(G43)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G43&lt;&gt;"",H43&lt;&gt;""),(N(G43)+N(H43))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G43&lt;&gt;"",N(G43)&lt;='설정'!$E$6),AND(H43&lt;&gt;"",N(H43)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G43&lt;&gt;"",H43&lt;&gt;""),(N(G43)+N(H43))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G43&lt;&gt;"",H43&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G43&lt;&gt;"",N(G43)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G43&lt;&gt;"",H43&lt;&gt;""),(N(G43)+N(H43))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G43&lt;&gt;"",N(G43)&lt;='설정'!$E$7),AND(H43&lt;&gt;"",N(H43)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G43&lt;&gt;"",H43&lt;&gt;""),(N(G43)+N(H43))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G43&lt;&gt;"",H43&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G43&lt;&gt;"",N(G43)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G43&lt;&gt;"",H43&lt;&gt;""),(N(G43)+N(H43))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G43&lt;&gt;"",N(G43)&lt;='설정'!$E$8),AND(H43&lt;&gt;"",N(H43)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G43&lt;&gt;"",H43&lt;&gt;""),(N(G43)+N(H43))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L43" s="29">
-        <f>IF(OR(G43="",H43=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G43-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H43-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G43="",H43=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G43-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G43+H43)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G43+H43)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G43-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H43-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M43" s="7" t="n"/>
@@ -25479,11 +25476,11 @@
         <v/>
       </c>
       <c r="K44" s="27">
-        <f>IF(I44="","",IF(OR(G44="",H44=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G44&gt;='설정'!$C$6),OR('설정'!$D$6="",G44&lt;'설정'!$D$6),OR('설정'!$E$6="",H44&gt;='설정'!$E$6),OR('설정'!$F$6="",H44&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G44&gt;='설정'!$C$7),OR('설정'!$D$7="",G44&lt;'설정'!$D$7),OR('설정'!$E$7="",H44&gt;='설정'!$E$7),OR('설정'!$F$7="",H44&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G44&gt;='설정'!$C$8),OR('설정'!$D$8="",G44&lt;'설정'!$D$8),OR('설정'!$E$8="",H44&gt;='설정'!$E$8),OR('설정'!$F$8="",H44&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I44="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G44&lt;&gt;"",H44&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G44&lt;&gt;"",N(G44)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G44&lt;&gt;"",H44&lt;&gt;""),(N(G44)+N(H44))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G44&lt;&gt;"",N(G44)&lt;='설정'!$E$6),AND(H44&lt;&gt;"",N(H44)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G44&lt;&gt;"",H44&lt;&gt;""),(N(G44)+N(H44))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G44&lt;&gt;"",H44&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G44&lt;&gt;"",N(G44)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G44&lt;&gt;"",H44&lt;&gt;""),(N(G44)+N(H44))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G44&lt;&gt;"",N(G44)&lt;='설정'!$E$7),AND(H44&lt;&gt;"",N(H44)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G44&lt;&gt;"",H44&lt;&gt;""),(N(G44)+N(H44))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G44&lt;&gt;"",H44&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G44&lt;&gt;"",N(G44)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G44&lt;&gt;"",H44&lt;&gt;""),(N(G44)+N(H44))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G44&lt;&gt;"",N(G44)&lt;='설정'!$E$8),AND(H44&lt;&gt;"",N(H44)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G44&lt;&gt;"",H44&lt;&gt;""),(N(G44)+N(H44))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L44" s="29">
-        <f>IF(OR(G44="",H44=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G44-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H44-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G44="",H44=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G44-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G44+H44)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G44+H44)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G44-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H44-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M44" s="7" t="n"/>
@@ -25542,11 +25539,11 @@
         <v/>
       </c>
       <c r="K45" s="27">
-        <f>IF(I45="","",IF(OR(G45="",H45=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G45&gt;='설정'!$C$6),OR('설정'!$D$6="",G45&lt;'설정'!$D$6),OR('설정'!$E$6="",H45&gt;='설정'!$E$6),OR('설정'!$F$6="",H45&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G45&gt;='설정'!$C$7),OR('설정'!$D$7="",G45&lt;'설정'!$D$7),OR('설정'!$E$7="",H45&gt;='설정'!$E$7),OR('설정'!$F$7="",H45&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G45&gt;='설정'!$C$8),OR('설정'!$D$8="",G45&lt;'설정'!$D$8),OR('설정'!$E$8="",H45&gt;='설정'!$E$8),OR('설정'!$F$8="",H45&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I45="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G45&lt;&gt;"",H45&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G45&lt;&gt;"",N(G45)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G45&lt;&gt;"",H45&lt;&gt;""),(N(G45)+N(H45))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G45&lt;&gt;"",N(G45)&lt;='설정'!$E$6),AND(H45&lt;&gt;"",N(H45)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G45&lt;&gt;"",H45&lt;&gt;""),(N(G45)+N(H45))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G45&lt;&gt;"",H45&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G45&lt;&gt;"",N(G45)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G45&lt;&gt;"",H45&lt;&gt;""),(N(G45)+N(H45))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G45&lt;&gt;"",N(G45)&lt;='설정'!$E$7),AND(H45&lt;&gt;"",N(H45)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G45&lt;&gt;"",H45&lt;&gt;""),(N(G45)+N(H45))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G45&lt;&gt;"",H45&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G45&lt;&gt;"",N(G45)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G45&lt;&gt;"",H45&lt;&gt;""),(N(G45)+N(H45))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G45&lt;&gt;"",N(G45)&lt;='설정'!$E$8),AND(H45&lt;&gt;"",N(H45)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G45&lt;&gt;"",H45&lt;&gt;""),(N(G45)+N(H45))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L45" s="29">
-        <f>IF(OR(G45="",H45=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G45-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H45-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G45="",H45=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G45-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G45+H45)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G45+H45)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G45-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H45-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M45" s="7" t="n"/>
@@ -25605,11 +25602,11 @@
         <v/>
       </c>
       <c r="K46" s="27">
-        <f>IF(I46="","",IF(OR(G46="",H46=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G46&gt;='설정'!$C$6),OR('설정'!$D$6="",G46&lt;'설정'!$D$6),OR('설정'!$E$6="",H46&gt;='설정'!$E$6),OR('설정'!$F$6="",H46&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G46&gt;='설정'!$C$7),OR('설정'!$D$7="",G46&lt;'설정'!$D$7),OR('설정'!$E$7="",H46&gt;='설정'!$E$7),OR('설정'!$F$7="",H46&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G46&gt;='설정'!$C$8),OR('설정'!$D$8="",G46&lt;'설정'!$D$8),OR('설정'!$E$8="",H46&gt;='설정'!$E$8),OR('설정'!$F$8="",H46&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I46="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G46&lt;&gt;"",H46&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G46&lt;&gt;"",N(G46)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G46&lt;&gt;"",H46&lt;&gt;""),(N(G46)+N(H46))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G46&lt;&gt;"",N(G46)&lt;='설정'!$E$6),AND(H46&lt;&gt;"",N(H46)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G46&lt;&gt;"",H46&lt;&gt;""),(N(G46)+N(H46))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G46&lt;&gt;"",H46&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G46&lt;&gt;"",N(G46)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G46&lt;&gt;"",H46&lt;&gt;""),(N(G46)+N(H46))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G46&lt;&gt;"",N(G46)&lt;='설정'!$E$7),AND(H46&lt;&gt;"",N(H46)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G46&lt;&gt;"",H46&lt;&gt;""),(N(G46)+N(H46))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G46&lt;&gt;"",H46&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G46&lt;&gt;"",N(G46)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G46&lt;&gt;"",H46&lt;&gt;""),(N(G46)+N(H46))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G46&lt;&gt;"",N(G46)&lt;='설정'!$E$8),AND(H46&lt;&gt;"",N(H46)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G46&lt;&gt;"",H46&lt;&gt;""),(N(G46)+N(H46))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L46" s="29">
-        <f>IF(OR(G46="",H46=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G46-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H46-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G46="",H46=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G46-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G46+H46)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G46+H46)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G46-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H46-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M46" s="7" t="n"/>
@@ -25668,11 +25665,11 @@
         <v/>
       </c>
       <c r="K47" s="27">
-        <f>IF(I47="","",IF(OR(G47="",H47=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G47&gt;='설정'!$C$6),OR('설정'!$D$6="",G47&lt;'설정'!$D$6),OR('설정'!$E$6="",H47&gt;='설정'!$E$6),OR('설정'!$F$6="",H47&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G47&gt;='설정'!$C$7),OR('설정'!$D$7="",G47&lt;'설정'!$D$7),OR('설정'!$E$7="",H47&gt;='설정'!$E$7),OR('설정'!$F$7="",H47&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G47&gt;='설정'!$C$8),OR('설정'!$D$8="",G47&lt;'설정'!$D$8),OR('설정'!$E$8="",H47&gt;='설정'!$E$8),OR('설정'!$F$8="",H47&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I47="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G47&lt;&gt;"",H47&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G47&lt;&gt;"",N(G47)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G47&lt;&gt;"",H47&lt;&gt;""),(N(G47)+N(H47))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G47&lt;&gt;"",N(G47)&lt;='설정'!$E$6),AND(H47&lt;&gt;"",N(H47)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G47&lt;&gt;"",H47&lt;&gt;""),(N(G47)+N(H47))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G47&lt;&gt;"",H47&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G47&lt;&gt;"",N(G47)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G47&lt;&gt;"",H47&lt;&gt;""),(N(G47)+N(H47))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G47&lt;&gt;"",N(G47)&lt;='설정'!$E$7),AND(H47&lt;&gt;"",N(H47)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G47&lt;&gt;"",H47&lt;&gt;""),(N(G47)+N(H47))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G47&lt;&gt;"",H47&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G47&lt;&gt;"",N(G47)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G47&lt;&gt;"",H47&lt;&gt;""),(N(G47)+N(H47))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G47&lt;&gt;"",N(G47)&lt;='설정'!$E$8),AND(H47&lt;&gt;"",N(H47)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G47&lt;&gt;"",H47&lt;&gt;""),(N(G47)+N(H47))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L47" s="29">
-        <f>IF(OR(G47="",H47=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G47-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H47-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G47="",H47=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G47-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G47+H47)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G47+H47)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G47-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H47-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M47" s="7" t="n"/>
@@ -25731,11 +25728,11 @@
         <v/>
       </c>
       <c r="K48" s="27">
-        <f>IF(I48="","",IF(OR(G48="",H48=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G48&gt;='설정'!$C$6),OR('설정'!$D$6="",G48&lt;'설정'!$D$6),OR('설정'!$E$6="",H48&gt;='설정'!$E$6),OR('설정'!$F$6="",H48&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G48&gt;='설정'!$C$7),OR('설정'!$D$7="",G48&lt;'설정'!$D$7),OR('설정'!$E$7="",H48&gt;='설정'!$E$7),OR('설정'!$F$7="",H48&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G48&gt;='설정'!$C$8),OR('설정'!$D$8="",G48&lt;'설정'!$D$8),OR('설정'!$E$8="",H48&gt;='설정'!$E$8),OR('설정'!$F$8="",H48&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I48="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G48&lt;&gt;"",H48&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G48&lt;&gt;"",N(G48)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G48&lt;&gt;"",H48&lt;&gt;""),(N(G48)+N(H48))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G48&lt;&gt;"",N(G48)&lt;='설정'!$E$6),AND(H48&lt;&gt;"",N(H48)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G48&lt;&gt;"",H48&lt;&gt;""),(N(G48)+N(H48))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G48&lt;&gt;"",H48&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G48&lt;&gt;"",N(G48)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G48&lt;&gt;"",H48&lt;&gt;""),(N(G48)+N(H48))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G48&lt;&gt;"",N(G48)&lt;='설정'!$E$7),AND(H48&lt;&gt;"",N(H48)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G48&lt;&gt;"",H48&lt;&gt;""),(N(G48)+N(H48))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G48&lt;&gt;"",H48&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G48&lt;&gt;"",N(G48)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G48&lt;&gt;"",H48&lt;&gt;""),(N(G48)+N(H48))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G48&lt;&gt;"",N(G48)&lt;='설정'!$E$8),AND(H48&lt;&gt;"",N(H48)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G48&lt;&gt;"",H48&lt;&gt;""),(N(G48)+N(H48))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L48" s="29">
-        <f>IF(OR(G48="",H48=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G48-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H48-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G48="",H48=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G48-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G48+H48)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G48+H48)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G48-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H48-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M48" s="7" t="n"/>
@@ -25794,11 +25791,11 @@
         <v/>
       </c>
       <c r="K49" s="27">
-        <f>IF(I49="","",IF(OR(G49="",H49=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G49&gt;='설정'!$C$6),OR('설정'!$D$6="",G49&lt;'설정'!$D$6),OR('설정'!$E$6="",H49&gt;='설정'!$E$6),OR('설정'!$F$6="",H49&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G49&gt;='설정'!$C$7),OR('설정'!$D$7="",G49&lt;'설정'!$D$7),OR('설정'!$E$7="",H49&gt;='설정'!$E$7),OR('설정'!$F$7="",H49&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G49&gt;='설정'!$C$8),OR('설정'!$D$8="",G49&lt;'설정'!$D$8),OR('설정'!$E$8="",H49&gt;='설정'!$E$8),OR('설정'!$F$8="",H49&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I49="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G49&lt;&gt;"",H49&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G49&lt;&gt;"",N(G49)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G49&lt;&gt;"",H49&lt;&gt;""),(N(G49)+N(H49))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G49&lt;&gt;"",N(G49)&lt;='설정'!$E$6),AND(H49&lt;&gt;"",N(H49)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G49&lt;&gt;"",H49&lt;&gt;""),(N(G49)+N(H49))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G49&lt;&gt;"",H49&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G49&lt;&gt;"",N(G49)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G49&lt;&gt;"",H49&lt;&gt;""),(N(G49)+N(H49))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G49&lt;&gt;"",N(G49)&lt;='설정'!$E$7),AND(H49&lt;&gt;"",N(H49)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G49&lt;&gt;"",H49&lt;&gt;""),(N(G49)+N(H49))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G49&lt;&gt;"",H49&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G49&lt;&gt;"",N(G49)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G49&lt;&gt;"",H49&lt;&gt;""),(N(G49)+N(H49))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G49&lt;&gt;"",N(G49)&lt;='설정'!$E$8),AND(H49&lt;&gt;"",N(H49)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G49&lt;&gt;"",H49&lt;&gt;""),(N(G49)+N(H49))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L49" s="29">
-        <f>IF(OR(G49="",H49=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G49-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H49-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G49="",H49=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G49-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G49+H49)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G49+H49)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G49-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H49-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M49" s="7" t="n"/>
@@ -25857,11 +25854,11 @@
         <v/>
       </c>
       <c r="K50" s="27">
-        <f>IF(I50="","",IF(OR(G50="",H50=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G50&gt;='설정'!$C$6),OR('설정'!$D$6="",G50&lt;'설정'!$D$6),OR('설정'!$E$6="",H50&gt;='설정'!$E$6),OR('설정'!$F$6="",H50&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G50&gt;='설정'!$C$7),OR('설정'!$D$7="",G50&lt;'설정'!$D$7),OR('설정'!$E$7="",H50&gt;='설정'!$E$7),OR('설정'!$F$7="",H50&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G50&gt;='설정'!$C$8),OR('설정'!$D$8="",G50&lt;'설정'!$D$8),OR('설정'!$E$8="",H50&gt;='설정'!$E$8),OR('설정'!$F$8="",H50&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I50="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G50&lt;&gt;"",H50&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G50&lt;&gt;"",N(G50)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G50&lt;&gt;"",H50&lt;&gt;""),(N(G50)+N(H50))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G50&lt;&gt;"",N(G50)&lt;='설정'!$E$6),AND(H50&lt;&gt;"",N(H50)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G50&lt;&gt;"",H50&lt;&gt;""),(N(G50)+N(H50))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G50&lt;&gt;"",H50&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G50&lt;&gt;"",N(G50)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G50&lt;&gt;"",H50&lt;&gt;""),(N(G50)+N(H50))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G50&lt;&gt;"",N(G50)&lt;='설정'!$E$7),AND(H50&lt;&gt;"",N(H50)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G50&lt;&gt;"",H50&lt;&gt;""),(N(G50)+N(H50))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G50&lt;&gt;"",H50&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G50&lt;&gt;"",N(G50)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G50&lt;&gt;"",H50&lt;&gt;""),(N(G50)+N(H50))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G50&lt;&gt;"",N(G50)&lt;='설정'!$E$8),AND(H50&lt;&gt;"",N(H50)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G50&lt;&gt;"",H50&lt;&gt;""),(N(G50)+N(H50))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L50" s="29">
-        <f>IF(OR(G50="",H50=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G50-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H50-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G50="",H50=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G50-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G50+H50)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G50+H50)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G50-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H50-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M50" s="7" t="n"/>
@@ -25920,11 +25917,11 @@
         <v/>
       </c>
       <c r="K51" s="27">
-        <f>IF(I51="","",IF(OR(G51="",H51=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G51&gt;='설정'!$C$6),OR('설정'!$D$6="",G51&lt;'설정'!$D$6),OR('설정'!$E$6="",H51&gt;='설정'!$E$6),OR('설정'!$F$6="",H51&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G51&gt;='설정'!$C$7),OR('설정'!$D$7="",G51&lt;'설정'!$D$7),OR('설정'!$E$7="",H51&gt;='설정'!$E$7),OR('설정'!$F$7="",H51&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G51&gt;='설정'!$C$8),OR('설정'!$D$8="",G51&lt;'설정'!$D$8),OR('설정'!$E$8="",H51&gt;='설정'!$E$8),OR('설정'!$F$8="",H51&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I51="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G51&lt;&gt;"",H51&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G51&lt;&gt;"",N(G51)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G51&lt;&gt;"",H51&lt;&gt;""),(N(G51)+N(H51))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G51&lt;&gt;"",N(G51)&lt;='설정'!$E$6),AND(H51&lt;&gt;"",N(H51)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G51&lt;&gt;"",H51&lt;&gt;""),(N(G51)+N(H51))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G51&lt;&gt;"",H51&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G51&lt;&gt;"",N(G51)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G51&lt;&gt;"",H51&lt;&gt;""),(N(G51)+N(H51))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G51&lt;&gt;"",N(G51)&lt;='설정'!$E$7),AND(H51&lt;&gt;"",N(H51)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G51&lt;&gt;"",H51&lt;&gt;""),(N(G51)+N(H51))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G51&lt;&gt;"",H51&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G51&lt;&gt;"",N(G51)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G51&lt;&gt;"",H51&lt;&gt;""),(N(G51)+N(H51))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G51&lt;&gt;"",N(G51)&lt;='설정'!$E$8),AND(H51&lt;&gt;"",N(H51)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G51&lt;&gt;"",H51&lt;&gt;""),(N(G51)+N(H51))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L51" s="29">
-        <f>IF(OR(G51="",H51=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G51-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H51-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G51="",H51=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G51-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G51+H51)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G51+H51)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G51-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H51-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M51" s="7" t="n"/>
@@ -25983,11 +25980,11 @@
         <v/>
       </c>
       <c r="K52" s="27">
-        <f>IF(I52="","",IF(OR(G52="",H52=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G52&gt;='설정'!$C$6),OR('설정'!$D$6="",G52&lt;'설정'!$D$6),OR('설정'!$E$6="",H52&gt;='설정'!$E$6),OR('설정'!$F$6="",H52&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G52&gt;='설정'!$C$7),OR('설정'!$D$7="",G52&lt;'설정'!$D$7),OR('설정'!$E$7="",H52&gt;='설정'!$E$7),OR('설정'!$F$7="",H52&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G52&gt;='설정'!$C$8),OR('설정'!$D$8="",G52&lt;'설정'!$D$8),OR('설정'!$E$8="",H52&gt;='설정'!$E$8),OR('설정'!$F$8="",H52&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I52="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G52&lt;&gt;"",H52&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G52&lt;&gt;"",N(G52)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G52&lt;&gt;"",H52&lt;&gt;""),(N(G52)+N(H52))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G52&lt;&gt;"",N(G52)&lt;='설정'!$E$6),AND(H52&lt;&gt;"",N(H52)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G52&lt;&gt;"",H52&lt;&gt;""),(N(G52)+N(H52))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G52&lt;&gt;"",H52&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G52&lt;&gt;"",N(G52)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G52&lt;&gt;"",H52&lt;&gt;""),(N(G52)+N(H52))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G52&lt;&gt;"",N(G52)&lt;='설정'!$E$7),AND(H52&lt;&gt;"",N(H52)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G52&lt;&gt;"",H52&lt;&gt;""),(N(G52)+N(H52))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G52&lt;&gt;"",H52&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G52&lt;&gt;"",N(G52)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G52&lt;&gt;"",H52&lt;&gt;""),(N(G52)+N(H52))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G52&lt;&gt;"",N(G52)&lt;='설정'!$E$8),AND(H52&lt;&gt;"",N(H52)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G52&lt;&gt;"",H52&lt;&gt;""),(N(G52)+N(H52))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L52" s="29">
-        <f>IF(OR(G52="",H52=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G52-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H52-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G52="",H52=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G52-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G52+H52)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G52+H52)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G52-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H52-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M52" s="7" t="n"/>
@@ -26046,11 +26043,11 @@
         <v/>
       </c>
       <c r="K53" s="27">
-        <f>IF(I53="","",IF(OR(G53="",H53=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G53&gt;='설정'!$C$6),OR('설정'!$D$6="",G53&lt;'설정'!$D$6),OR('설정'!$E$6="",H53&gt;='설정'!$E$6),OR('설정'!$F$6="",H53&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G53&gt;='설정'!$C$7),OR('설정'!$D$7="",G53&lt;'설정'!$D$7),OR('설정'!$E$7="",H53&gt;='설정'!$E$7),OR('설정'!$F$7="",H53&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G53&gt;='설정'!$C$8),OR('설정'!$D$8="",G53&lt;'설정'!$D$8),OR('설정'!$E$8="",H53&gt;='설정'!$E$8),OR('설정'!$F$8="",H53&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I53="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G53&lt;&gt;"",H53&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G53&lt;&gt;"",N(G53)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G53&lt;&gt;"",H53&lt;&gt;""),(N(G53)+N(H53))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G53&lt;&gt;"",N(G53)&lt;='설정'!$E$6),AND(H53&lt;&gt;"",N(H53)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G53&lt;&gt;"",H53&lt;&gt;""),(N(G53)+N(H53))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G53&lt;&gt;"",H53&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G53&lt;&gt;"",N(G53)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G53&lt;&gt;"",H53&lt;&gt;""),(N(G53)+N(H53))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G53&lt;&gt;"",N(G53)&lt;='설정'!$E$7),AND(H53&lt;&gt;"",N(H53)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G53&lt;&gt;"",H53&lt;&gt;""),(N(G53)+N(H53))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G53&lt;&gt;"",H53&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G53&lt;&gt;"",N(G53)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G53&lt;&gt;"",H53&lt;&gt;""),(N(G53)+N(H53))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G53&lt;&gt;"",N(G53)&lt;='설정'!$E$8),AND(H53&lt;&gt;"",N(H53)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G53&lt;&gt;"",H53&lt;&gt;""),(N(G53)+N(H53))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L53" s="29">
-        <f>IF(OR(G53="",H53=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G53-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H53-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G53="",H53=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G53-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G53+H53)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G53+H53)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G53-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H53-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M53" s="7" t="n"/>
@@ -26109,11 +26106,11 @@
         <v/>
       </c>
       <c r="K54" s="27">
-        <f>IF(I54="","",IF(OR(G54="",H54=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G54&gt;='설정'!$C$6),OR('설정'!$D$6="",G54&lt;'설정'!$D$6),OR('설정'!$E$6="",H54&gt;='설정'!$E$6),OR('설정'!$F$6="",H54&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G54&gt;='설정'!$C$7),OR('설정'!$D$7="",G54&lt;'설정'!$D$7),OR('설정'!$E$7="",H54&gt;='설정'!$E$7),OR('설정'!$F$7="",H54&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G54&gt;='설정'!$C$8),OR('설정'!$D$8="",G54&lt;'설정'!$D$8),OR('설정'!$E$8="",H54&gt;='설정'!$E$8),OR('설정'!$F$8="",H54&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I54="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G54&lt;&gt;"",H54&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G54&lt;&gt;"",N(G54)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G54&lt;&gt;"",H54&lt;&gt;""),(N(G54)+N(H54))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G54&lt;&gt;"",N(G54)&lt;='설정'!$E$6),AND(H54&lt;&gt;"",N(H54)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G54&lt;&gt;"",H54&lt;&gt;""),(N(G54)+N(H54))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G54&lt;&gt;"",H54&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G54&lt;&gt;"",N(G54)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G54&lt;&gt;"",H54&lt;&gt;""),(N(G54)+N(H54))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G54&lt;&gt;"",N(G54)&lt;='설정'!$E$7),AND(H54&lt;&gt;"",N(H54)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G54&lt;&gt;"",H54&lt;&gt;""),(N(G54)+N(H54))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G54&lt;&gt;"",H54&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G54&lt;&gt;"",N(G54)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G54&lt;&gt;"",H54&lt;&gt;""),(N(G54)+N(H54))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G54&lt;&gt;"",N(G54)&lt;='설정'!$E$8),AND(H54&lt;&gt;"",N(H54)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G54&lt;&gt;"",H54&lt;&gt;""),(N(G54)+N(H54))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L54" s="29">
-        <f>IF(OR(G54="",H54=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G54-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H54-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G54="",H54=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G54-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G54+H54)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G54+H54)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G54-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H54-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M54" s="7" t="n"/>
@@ -26172,11 +26169,11 @@
         <v/>
       </c>
       <c r="K55" s="27">
-        <f>IF(I55="","",IF(OR(G55="",H55=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G55&gt;='설정'!$C$6),OR('설정'!$D$6="",G55&lt;'설정'!$D$6),OR('설정'!$E$6="",H55&gt;='설정'!$E$6),OR('설정'!$F$6="",H55&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G55&gt;='설정'!$C$7),OR('설정'!$D$7="",G55&lt;'설정'!$D$7),OR('설정'!$E$7="",H55&gt;='설정'!$E$7),OR('설정'!$F$7="",H55&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G55&gt;='설정'!$C$8),OR('설정'!$D$8="",G55&lt;'설정'!$D$8),OR('설정'!$E$8="",H55&gt;='설정'!$E$8),OR('설정'!$F$8="",H55&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I55="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G55&lt;&gt;"",H55&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G55&lt;&gt;"",N(G55)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G55&lt;&gt;"",H55&lt;&gt;""),(N(G55)+N(H55))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G55&lt;&gt;"",N(G55)&lt;='설정'!$E$6),AND(H55&lt;&gt;"",N(H55)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G55&lt;&gt;"",H55&lt;&gt;""),(N(G55)+N(H55))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G55&lt;&gt;"",H55&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G55&lt;&gt;"",N(G55)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G55&lt;&gt;"",H55&lt;&gt;""),(N(G55)+N(H55))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G55&lt;&gt;"",N(G55)&lt;='설정'!$E$7),AND(H55&lt;&gt;"",N(H55)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G55&lt;&gt;"",H55&lt;&gt;""),(N(G55)+N(H55))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G55&lt;&gt;"",H55&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G55&lt;&gt;"",N(G55)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G55&lt;&gt;"",H55&lt;&gt;""),(N(G55)+N(H55))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G55&lt;&gt;"",N(G55)&lt;='설정'!$E$8),AND(H55&lt;&gt;"",N(H55)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G55&lt;&gt;"",H55&lt;&gt;""),(N(G55)+N(H55))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L55" s="29">
-        <f>IF(OR(G55="",H55=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G55-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H55-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G55="",H55=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G55-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G55+H55)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G55+H55)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G55-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H55-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M55" s="7" t="n"/>
@@ -26235,11 +26232,11 @@
         <v/>
       </c>
       <c r="K56" s="27">
-        <f>IF(I56="","",IF(OR(G56="",H56=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G56&gt;='설정'!$C$6),OR('설정'!$D$6="",G56&lt;'설정'!$D$6),OR('설정'!$E$6="",H56&gt;='설정'!$E$6),OR('설정'!$F$6="",H56&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G56&gt;='설정'!$C$7),OR('설정'!$D$7="",G56&lt;'설정'!$D$7),OR('설정'!$E$7="",H56&gt;='설정'!$E$7),OR('설정'!$F$7="",H56&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G56&gt;='설정'!$C$8),OR('설정'!$D$8="",G56&lt;'설정'!$D$8),OR('설정'!$E$8="",H56&gt;='설정'!$E$8),OR('설정'!$F$8="",H56&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I56="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G56&lt;&gt;"",H56&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G56&lt;&gt;"",N(G56)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G56&lt;&gt;"",H56&lt;&gt;""),(N(G56)+N(H56))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G56&lt;&gt;"",N(G56)&lt;='설정'!$E$6),AND(H56&lt;&gt;"",N(H56)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G56&lt;&gt;"",H56&lt;&gt;""),(N(G56)+N(H56))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G56&lt;&gt;"",H56&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G56&lt;&gt;"",N(G56)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G56&lt;&gt;"",H56&lt;&gt;""),(N(G56)+N(H56))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G56&lt;&gt;"",N(G56)&lt;='설정'!$E$7),AND(H56&lt;&gt;"",N(H56)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G56&lt;&gt;"",H56&lt;&gt;""),(N(G56)+N(H56))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G56&lt;&gt;"",H56&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G56&lt;&gt;"",N(G56)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G56&lt;&gt;"",H56&lt;&gt;""),(N(G56)+N(H56))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G56&lt;&gt;"",N(G56)&lt;='설정'!$E$8),AND(H56&lt;&gt;"",N(H56)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G56&lt;&gt;"",H56&lt;&gt;""),(N(G56)+N(H56))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L56" s="29">
-        <f>IF(OR(G56="",H56=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G56-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H56-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G56="",H56=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G56-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G56+H56)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G56+H56)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G56-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H56-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M56" s="7" t="n"/>
@@ -26298,11 +26295,11 @@
         <v/>
       </c>
       <c r="K57" s="27">
-        <f>IF(I57="","",IF(OR(G57="",H57=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G57&gt;='설정'!$C$6),OR('설정'!$D$6="",G57&lt;'설정'!$D$6),OR('설정'!$E$6="",H57&gt;='설정'!$E$6),OR('설정'!$F$6="",H57&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G57&gt;='설정'!$C$7),OR('설정'!$D$7="",G57&lt;'설정'!$D$7),OR('설정'!$E$7="",H57&gt;='설정'!$E$7),OR('설정'!$F$7="",H57&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G57&gt;='설정'!$C$8),OR('설정'!$D$8="",G57&lt;'설정'!$D$8),OR('설정'!$E$8="",H57&gt;='설정'!$E$8),OR('설정'!$F$8="",H57&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I57="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G57&lt;&gt;"",H57&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G57&lt;&gt;"",N(G57)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G57&lt;&gt;"",H57&lt;&gt;""),(N(G57)+N(H57))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G57&lt;&gt;"",N(G57)&lt;='설정'!$E$6),AND(H57&lt;&gt;"",N(H57)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G57&lt;&gt;"",H57&lt;&gt;""),(N(G57)+N(H57))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G57&lt;&gt;"",H57&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G57&lt;&gt;"",N(G57)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G57&lt;&gt;"",H57&lt;&gt;""),(N(G57)+N(H57))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G57&lt;&gt;"",N(G57)&lt;='설정'!$E$7),AND(H57&lt;&gt;"",N(H57)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G57&lt;&gt;"",H57&lt;&gt;""),(N(G57)+N(H57))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G57&lt;&gt;"",H57&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G57&lt;&gt;"",N(G57)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G57&lt;&gt;"",H57&lt;&gt;""),(N(G57)+N(H57))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G57&lt;&gt;"",N(G57)&lt;='설정'!$E$8),AND(H57&lt;&gt;"",N(H57)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G57&lt;&gt;"",H57&lt;&gt;""),(N(G57)+N(H57))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L57" s="29">
-        <f>IF(OR(G57="",H57=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G57-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H57-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G57="",H57=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G57-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G57+H57)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G57+H57)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G57-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H57-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M57" s="7" t="n"/>
@@ -26361,11 +26358,11 @@
         <v/>
       </c>
       <c r="K58" s="27">
-        <f>IF(I58="","",IF(OR(G58="",H58=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G58&gt;='설정'!$C$6),OR('설정'!$D$6="",G58&lt;'설정'!$D$6),OR('설정'!$E$6="",H58&gt;='설정'!$E$6),OR('설정'!$F$6="",H58&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G58&gt;='설정'!$C$7),OR('설정'!$D$7="",G58&lt;'설정'!$D$7),OR('설정'!$E$7="",H58&gt;='설정'!$E$7),OR('설정'!$F$7="",H58&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G58&gt;='설정'!$C$8),OR('설정'!$D$8="",G58&lt;'설정'!$D$8),OR('설정'!$E$8="",H58&gt;='설정'!$E$8),OR('설정'!$F$8="",H58&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I58="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G58&lt;&gt;"",H58&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G58&lt;&gt;"",N(G58)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G58&lt;&gt;"",H58&lt;&gt;""),(N(G58)+N(H58))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G58&lt;&gt;"",N(G58)&lt;='설정'!$E$6),AND(H58&lt;&gt;"",N(H58)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G58&lt;&gt;"",H58&lt;&gt;""),(N(G58)+N(H58))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G58&lt;&gt;"",H58&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G58&lt;&gt;"",N(G58)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G58&lt;&gt;"",H58&lt;&gt;""),(N(G58)+N(H58))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G58&lt;&gt;"",N(G58)&lt;='설정'!$E$7),AND(H58&lt;&gt;"",N(H58)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G58&lt;&gt;"",H58&lt;&gt;""),(N(G58)+N(H58))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G58&lt;&gt;"",H58&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G58&lt;&gt;"",N(G58)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G58&lt;&gt;"",H58&lt;&gt;""),(N(G58)+N(H58))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G58&lt;&gt;"",N(G58)&lt;='설정'!$E$8),AND(H58&lt;&gt;"",N(H58)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G58&lt;&gt;"",H58&lt;&gt;""),(N(G58)+N(H58))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L58" s="29">
-        <f>IF(OR(G58="",H58=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G58-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H58-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G58="",H58=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G58-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G58+H58)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G58+H58)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G58-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H58-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M58" s="7" t="n"/>
@@ -26424,11 +26421,11 @@
         <v/>
       </c>
       <c r="K59" s="27">
-        <f>IF(I59="","",IF(OR(G59="",H59=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G59&gt;='설정'!$C$6),OR('설정'!$D$6="",G59&lt;'설정'!$D$6),OR('설정'!$E$6="",H59&gt;='설정'!$E$6),OR('설정'!$F$6="",H59&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G59&gt;='설정'!$C$7),OR('설정'!$D$7="",G59&lt;'설정'!$D$7),OR('설정'!$E$7="",H59&gt;='설정'!$E$7),OR('설정'!$F$7="",H59&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G59&gt;='설정'!$C$8),OR('설정'!$D$8="",G59&lt;'설정'!$D$8),OR('설정'!$E$8="",H59&gt;='설정'!$E$8),OR('설정'!$F$8="",H59&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I59="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G59&lt;&gt;"",H59&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G59&lt;&gt;"",N(G59)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G59&lt;&gt;"",H59&lt;&gt;""),(N(G59)+N(H59))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G59&lt;&gt;"",N(G59)&lt;='설정'!$E$6),AND(H59&lt;&gt;"",N(H59)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G59&lt;&gt;"",H59&lt;&gt;""),(N(G59)+N(H59))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G59&lt;&gt;"",H59&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G59&lt;&gt;"",N(G59)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G59&lt;&gt;"",H59&lt;&gt;""),(N(G59)+N(H59))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G59&lt;&gt;"",N(G59)&lt;='설정'!$E$7),AND(H59&lt;&gt;"",N(H59)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G59&lt;&gt;"",H59&lt;&gt;""),(N(G59)+N(H59))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G59&lt;&gt;"",H59&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G59&lt;&gt;"",N(G59)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G59&lt;&gt;"",H59&lt;&gt;""),(N(G59)+N(H59))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G59&lt;&gt;"",N(G59)&lt;='설정'!$E$8),AND(H59&lt;&gt;"",N(H59)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G59&lt;&gt;"",H59&lt;&gt;""),(N(G59)+N(H59))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L59" s="29">
-        <f>IF(OR(G59="",H59=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G59-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H59-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G59="",H59=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G59-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G59+H59)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G59+H59)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G59-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H59-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M59" s="7" t="n"/>
@@ -26487,11 +26484,11 @@
         <v/>
       </c>
       <c r="K60" s="27">
-        <f>IF(I60="","",IF(OR(G60="",H60=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G60&gt;='설정'!$C$6),OR('설정'!$D$6="",G60&lt;'설정'!$D$6),OR('설정'!$E$6="",H60&gt;='설정'!$E$6),OR('설정'!$F$6="",H60&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G60&gt;='설정'!$C$7),OR('설정'!$D$7="",G60&lt;'설정'!$D$7),OR('설정'!$E$7="",H60&gt;='설정'!$E$7),OR('설정'!$F$7="",H60&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G60&gt;='설정'!$C$8),OR('설정'!$D$8="",G60&lt;'설정'!$D$8),OR('설정'!$E$8="",H60&gt;='설정'!$E$8),OR('설정'!$F$8="",H60&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I60="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G60&lt;&gt;"",H60&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G60&lt;&gt;"",N(G60)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G60&lt;&gt;"",H60&lt;&gt;""),(N(G60)+N(H60))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G60&lt;&gt;"",N(G60)&lt;='설정'!$E$6),AND(H60&lt;&gt;"",N(H60)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G60&lt;&gt;"",H60&lt;&gt;""),(N(G60)+N(H60))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G60&lt;&gt;"",H60&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G60&lt;&gt;"",N(G60)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G60&lt;&gt;"",H60&lt;&gt;""),(N(G60)+N(H60))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G60&lt;&gt;"",N(G60)&lt;='설정'!$E$7),AND(H60&lt;&gt;"",N(H60)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G60&lt;&gt;"",H60&lt;&gt;""),(N(G60)+N(H60))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G60&lt;&gt;"",H60&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G60&lt;&gt;"",N(G60)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G60&lt;&gt;"",H60&lt;&gt;""),(N(G60)+N(H60))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G60&lt;&gt;"",N(G60)&lt;='설정'!$E$8),AND(H60&lt;&gt;"",N(H60)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G60&lt;&gt;"",H60&lt;&gt;""),(N(G60)+N(H60))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L60" s="29">
-        <f>IF(OR(G60="",H60=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G60-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H60-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G60="",H60=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G60-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G60+H60)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G60+H60)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G60-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H60-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M60" s="7" t="n"/>
@@ -26550,11 +26547,11 @@
         <v/>
       </c>
       <c r="K61" s="27">
-        <f>IF(I61="","",IF(OR(G61="",H61=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G61&gt;='설정'!$C$6),OR('설정'!$D$6="",G61&lt;'설정'!$D$6),OR('설정'!$E$6="",H61&gt;='설정'!$E$6),OR('설정'!$F$6="",H61&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G61&gt;='설정'!$C$7),OR('설정'!$D$7="",G61&lt;'설정'!$D$7),OR('설정'!$E$7="",H61&gt;='설정'!$E$7),OR('설정'!$F$7="",H61&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G61&gt;='설정'!$C$8),OR('설정'!$D$8="",G61&lt;'설정'!$D$8),OR('설정'!$E$8="",H61&gt;='설정'!$E$8),OR('설정'!$F$8="",H61&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I61="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G61&lt;&gt;"",H61&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G61&lt;&gt;"",N(G61)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G61&lt;&gt;"",H61&lt;&gt;""),(N(G61)+N(H61))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G61&lt;&gt;"",N(G61)&lt;='설정'!$E$6),AND(H61&lt;&gt;"",N(H61)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G61&lt;&gt;"",H61&lt;&gt;""),(N(G61)+N(H61))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G61&lt;&gt;"",H61&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G61&lt;&gt;"",N(G61)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G61&lt;&gt;"",H61&lt;&gt;""),(N(G61)+N(H61))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G61&lt;&gt;"",N(G61)&lt;='설정'!$E$7),AND(H61&lt;&gt;"",N(H61)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G61&lt;&gt;"",H61&lt;&gt;""),(N(G61)+N(H61))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G61&lt;&gt;"",H61&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G61&lt;&gt;"",N(G61)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G61&lt;&gt;"",H61&lt;&gt;""),(N(G61)+N(H61))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G61&lt;&gt;"",N(G61)&lt;='설정'!$E$8),AND(H61&lt;&gt;"",N(H61)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G61&lt;&gt;"",H61&lt;&gt;""),(N(G61)+N(H61))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L61" s="29">
-        <f>IF(OR(G61="",H61=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G61-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H61-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G61="",H61=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G61-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G61+H61)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G61+H61)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G61-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H61-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M61" s="7" t="n"/>
@@ -26613,11 +26610,11 @@
         <v/>
       </c>
       <c r="K62" s="27">
-        <f>IF(I62="","",IF(OR(G62="",H62=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G62&gt;='설정'!$C$6),OR('설정'!$D$6="",G62&lt;'설정'!$D$6),OR('설정'!$E$6="",H62&gt;='설정'!$E$6),OR('설정'!$F$6="",H62&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G62&gt;='설정'!$C$7),OR('설정'!$D$7="",G62&lt;'설정'!$D$7),OR('설정'!$E$7="",H62&gt;='설정'!$E$7),OR('설정'!$F$7="",H62&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G62&gt;='설정'!$C$8),OR('설정'!$D$8="",G62&lt;'설정'!$D$8),OR('설정'!$E$8="",H62&gt;='설정'!$E$8),OR('설정'!$F$8="",H62&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I62="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G62&lt;&gt;"",H62&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G62&lt;&gt;"",N(G62)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G62&lt;&gt;"",H62&lt;&gt;""),(N(G62)+N(H62))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G62&lt;&gt;"",N(G62)&lt;='설정'!$E$6),AND(H62&lt;&gt;"",N(H62)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G62&lt;&gt;"",H62&lt;&gt;""),(N(G62)+N(H62))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G62&lt;&gt;"",H62&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G62&lt;&gt;"",N(G62)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G62&lt;&gt;"",H62&lt;&gt;""),(N(G62)+N(H62))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G62&lt;&gt;"",N(G62)&lt;='설정'!$E$7),AND(H62&lt;&gt;"",N(H62)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G62&lt;&gt;"",H62&lt;&gt;""),(N(G62)+N(H62))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G62&lt;&gt;"",H62&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G62&lt;&gt;"",N(G62)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G62&lt;&gt;"",H62&lt;&gt;""),(N(G62)+N(H62))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G62&lt;&gt;"",N(G62)&lt;='설정'!$E$8),AND(H62&lt;&gt;"",N(H62)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G62&lt;&gt;"",H62&lt;&gt;""),(N(G62)+N(H62))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L62" s="29">
-        <f>IF(OR(G62="",H62=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G62-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H62-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G62="",H62=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G62-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G62+H62)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G62+H62)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G62-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H62-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M62" s="7" t="n"/>
@@ -26676,11 +26673,11 @@
         <v/>
       </c>
       <c r="K63" s="27">
-        <f>IF(I63="","",IF(OR(G63="",H63=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G63&gt;='설정'!$C$6),OR('설정'!$D$6="",G63&lt;'설정'!$D$6),OR('설정'!$E$6="",H63&gt;='설정'!$E$6),OR('설정'!$F$6="",H63&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G63&gt;='설정'!$C$7),OR('설정'!$D$7="",G63&lt;'설정'!$D$7),OR('설정'!$E$7="",H63&gt;='설정'!$E$7),OR('설정'!$F$7="",H63&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G63&gt;='설정'!$C$8),OR('설정'!$D$8="",G63&lt;'설정'!$D$8),OR('설정'!$E$8="",H63&gt;='설정'!$E$8),OR('설정'!$F$8="",H63&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I63="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G63&lt;&gt;"",H63&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G63&lt;&gt;"",N(G63)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G63&lt;&gt;"",H63&lt;&gt;""),(N(G63)+N(H63))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G63&lt;&gt;"",N(G63)&lt;='설정'!$E$6),AND(H63&lt;&gt;"",N(H63)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G63&lt;&gt;"",H63&lt;&gt;""),(N(G63)+N(H63))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G63&lt;&gt;"",H63&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G63&lt;&gt;"",N(G63)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G63&lt;&gt;"",H63&lt;&gt;""),(N(G63)+N(H63))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G63&lt;&gt;"",N(G63)&lt;='설정'!$E$7),AND(H63&lt;&gt;"",N(H63)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G63&lt;&gt;"",H63&lt;&gt;""),(N(G63)+N(H63))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G63&lt;&gt;"",H63&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G63&lt;&gt;"",N(G63)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G63&lt;&gt;"",H63&lt;&gt;""),(N(G63)+N(H63))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G63&lt;&gt;"",N(G63)&lt;='설정'!$E$8),AND(H63&lt;&gt;"",N(H63)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G63&lt;&gt;"",H63&lt;&gt;""),(N(G63)+N(H63))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L63" s="29">
-        <f>IF(OR(G63="",H63=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G63-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H63-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G63="",H63=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G63-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G63+H63)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G63+H63)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G63-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H63-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M63" s="7" t="n"/>
@@ -26739,11 +26736,11 @@
         <v/>
       </c>
       <c r="K64" s="27">
-        <f>IF(I64="","",IF(OR(G64="",H64=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G64&gt;='설정'!$C$6),OR('설정'!$D$6="",G64&lt;'설정'!$D$6),OR('설정'!$E$6="",H64&gt;='설정'!$E$6),OR('설정'!$F$6="",H64&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G64&gt;='설정'!$C$7),OR('설정'!$D$7="",G64&lt;'설정'!$D$7),OR('설정'!$E$7="",H64&gt;='설정'!$E$7),OR('설정'!$F$7="",H64&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G64&gt;='설정'!$C$8),OR('설정'!$D$8="",G64&lt;'설정'!$D$8),OR('설정'!$E$8="",H64&gt;='설정'!$E$8),OR('설정'!$F$8="",H64&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I64="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G64&lt;&gt;"",H64&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G64&lt;&gt;"",N(G64)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G64&lt;&gt;"",H64&lt;&gt;""),(N(G64)+N(H64))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G64&lt;&gt;"",N(G64)&lt;='설정'!$E$6),AND(H64&lt;&gt;"",N(H64)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G64&lt;&gt;"",H64&lt;&gt;""),(N(G64)+N(H64))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G64&lt;&gt;"",H64&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G64&lt;&gt;"",N(G64)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G64&lt;&gt;"",H64&lt;&gt;""),(N(G64)+N(H64))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G64&lt;&gt;"",N(G64)&lt;='설정'!$E$7),AND(H64&lt;&gt;"",N(H64)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G64&lt;&gt;"",H64&lt;&gt;""),(N(G64)+N(H64))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G64&lt;&gt;"",H64&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G64&lt;&gt;"",N(G64)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G64&lt;&gt;"",H64&lt;&gt;""),(N(G64)+N(H64))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G64&lt;&gt;"",N(G64)&lt;='설정'!$E$8),AND(H64&lt;&gt;"",N(H64)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G64&lt;&gt;"",H64&lt;&gt;""),(N(G64)+N(H64))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L64" s="29">
-        <f>IF(OR(G64="",H64=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G64-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H64-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G64="",H64=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G64-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G64+H64)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G64+H64)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G64-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H64-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M64" s="7" t="n"/>
@@ -26802,11 +26799,11 @@
         <v/>
       </c>
       <c r="K65" s="27">
-        <f>IF(I65="","",IF(OR(G65="",H65=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G65&gt;='설정'!$C$6),OR('설정'!$D$6="",G65&lt;'설정'!$D$6),OR('설정'!$E$6="",H65&gt;='설정'!$E$6),OR('설정'!$F$6="",H65&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G65&gt;='설정'!$C$7),OR('설정'!$D$7="",G65&lt;'설정'!$D$7),OR('설정'!$E$7="",H65&gt;='설정'!$E$7),OR('설정'!$F$7="",H65&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G65&gt;='설정'!$C$8),OR('설정'!$D$8="",G65&lt;'설정'!$D$8),OR('설정'!$E$8="",H65&gt;='설정'!$E$8),OR('설정'!$F$8="",H65&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I65="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G65&lt;&gt;"",H65&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G65&lt;&gt;"",N(G65)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G65&lt;&gt;"",H65&lt;&gt;""),(N(G65)+N(H65))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G65&lt;&gt;"",N(G65)&lt;='설정'!$E$6),AND(H65&lt;&gt;"",N(H65)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G65&lt;&gt;"",H65&lt;&gt;""),(N(G65)+N(H65))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G65&lt;&gt;"",H65&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G65&lt;&gt;"",N(G65)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G65&lt;&gt;"",H65&lt;&gt;""),(N(G65)+N(H65))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G65&lt;&gt;"",N(G65)&lt;='설정'!$E$7),AND(H65&lt;&gt;"",N(H65)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G65&lt;&gt;"",H65&lt;&gt;""),(N(G65)+N(H65))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G65&lt;&gt;"",H65&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G65&lt;&gt;"",N(G65)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G65&lt;&gt;"",H65&lt;&gt;""),(N(G65)+N(H65))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G65&lt;&gt;"",N(G65)&lt;='설정'!$E$8),AND(H65&lt;&gt;"",N(H65)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G65&lt;&gt;"",H65&lt;&gt;""),(N(G65)+N(H65))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L65" s="29">
-        <f>IF(OR(G65="",H65=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G65-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H65-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G65="",H65=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G65-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G65+H65)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G65+H65)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G65-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H65-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M65" s="7" t="n"/>
@@ -26865,11 +26862,11 @@
         <v/>
       </c>
       <c r="K66" s="27">
-        <f>IF(I66="","",IF(OR(G66="",H66=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G66&gt;='설정'!$C$6),OR('설정'!$D$6="",G66&lt;'설정'!$D$6),OR('설정'!$E$6="",H66&gt;='설정'!$E$6),OR('설정'!$F$6="",H66&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G66&gt;='설정'!$C$7),OR('설정'!$D$7="",G66&lt;'설정'!$D$7),OR('설정'!$E$7="",H66&gt;='설정'!$E$7),OR('설정'!$F$7="",H66&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G66&gt;='설정'!$C$8),OR('설정'!$D$8="",G66&lt;'설정'!$D$8),OR('설정'!$E$8="",H66&gt;='설정'!$E$8),OR('설정'!$F$8="",H66&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I66="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G66&lt;&gt;"",H66&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G66&lt;&gt;"",N(G66)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G66&lt;&gt;"",H66&lt;&gt;""),(N(G66)+N(H66))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G66&lt;&gt;"",N(G66)&lt;='설정'!$E$6),AND(H66&lt;&gt;"",N(H66)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G66&lt;&gt;"",H66&lt;&gt;""),(N(G66)+N(H66))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G66&lt;&gt;"",H66&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G66&lt;&gt;"",N(G66)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G66&lt;&gt;"",H66&lt;&gt;""),(N(G66)+N(H66))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G66&lt;&gt;"",N(G66)&lt;='설정'!$E$7),AND(H66&lt;&gt;"",N(H66)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G66&lt;&gt;"",H66&lt;&gt;""),(N(G66)+N(H66))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G66&lt;&gt;"",H66&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G66&lt;&gt;"",N(G66)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G66&lt;&gt;"",H66&lt;&gt;""),(N(G66)+N(H66))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G66&lt;&gt;"",N(G66)&lt;='설정'!$E$8),AND(H66&lt;&gt;"",N(H66)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G66&lt;&gt;"",H66&lt;&gt;""),(N(G66)+N(H66))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L66" s="29">
-        <f>IF(OR(G66="",H66=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G66-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H66-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G66="",H66=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G66-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G66+H66)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G66+H66)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G66-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H66-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M66" s="7" t="n"/>
@@ -26928,11 +26925,11 @@
         <v/>
       </c>
       <c r="K67" s="27">
-        <f>IF(I67="","",IF(OR(G67="",H67=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G67&gt;='설정'!$C$6),OR('설정'!$D$6="",G67&lt;'설정'!$D$6),OR('설정'!$E$6="",H67&gt;='설정'!$E$6),OR('설정'!$F$6="",H67&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G67&gt;='설정'!$C$7),OR('설정'!$D$7="",G67&lt;'설정'!$D$7),OR('설정'!$E$7="",H67&gt;='설정'!$E$7),OR('설정'!$F$7="",H67&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G67&gt;='설정'!$C$8),OR('설정'!$D$8="",G67&lt;'설정'!$D$8),OR('설정'!$E$8="",H67&gt;='설정'!$E$8),OR('설정'!$F$8="",H67&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I67="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G67&lt;&gt;"",H67&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G67&lt;&gt;"",N(G67)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G67&lt;&gt;"",H67&lt;&gt;""),(N(G67)+N(H67))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G67&lt;&gt;"",N(G67)&lt;='설정'!$E$6),AND(H67&lt;&gt;"",N(H67)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G67&lt;&gt;"",H67&lt;&gt;""),(N(G67)+N(H67))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G67&lt;&gt;"",H67&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G67&lt;&gt;"",N(G67)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G67&lt;&gt;"",H67&lt;&gt;""),(N(G67)+N(H67))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G67&lt;&gt;"",N(G67)&lt;='설정'!$E$7),AND(H67&lt;&gt;"",N(H67)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G67&lt;&gt;"",H67&lt;&gt;""),(N(G67)+N(H67))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G67&lt;&gt;"",H67&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G67&lt;&gt;"",N(G67)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G67&lt;&gt;"",H67&lt;&gt;""),(N(G67)+N(H67))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G67&lt;&gt;"",N(G67)&lt;='설정'!$E$8),AND(H67&lt;&gt;"",N(H67)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G67&lt;&gt;"",H67&lt;&gt;""),(N(G67)+N(H67))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L67" s="29">
-        <f>IF(OR(G67="",H67=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G67-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H67-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G67="",H67=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G67-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G67+H67)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G67+H67)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G67-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H67-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M67" s="7" t="n"/>
@@ -26991,11 +26988,11 @@
         <v/>
       </c>
       <c r="K68" s="27">
-        <f>IF(I68="","",IF(OR(G68="",H68=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G68&gt;='설정'!$C$6),OR('설정'!$D$6="",G68&lt;'설정'!$D$6),OR('설정'!$E$6="",H68&gt;='설정'!$E$6),OR('설정'!$F$6="",H68&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G68&gt;='설정'!$C$7),OR('설정'!$D$7="",G68&lt;'설정'!$D$7),OR('설정'!$E$7="",H68&gt;='설정'!$E$7),OR('설정'!$F$7="",H68&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G68&gt;='설정'!$C$8),OR('설정'!$D$8="",G68&lt;'설정'!$D$8),OR('설정'!$E$8="",H68&gt;='설정'!$E$8),OR('설정'!$F$8="",H68&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I68="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G68&lt;&gt;"",H68&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G68&lt;&gt;"",N(G68)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G68&lt;&gt;"",H68&lt;&gt;""),(N(G68)+N(H68))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G68&lt;&gt;"",N(G68)&lt;='설정'!$E$6),AND(H68&lt;&gt;"",N(H68)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G68&lt;&gt;"",H68&lt;&gt;""),(N(G68)+N(H68))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G68&lt;&gt;"",H68&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G68&lt;&gt;"",N(G68)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G68&lt;&gt;"",H68&lt;&gt;""),(N(G68)+N(H68))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G68&lt;&gt;"",N(G68)&lt;='설정'!$E$7),AND(H68&lt;&gt;"",N(H68)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G68&lt;&gt;"",H68&lt;&gt;""),(N(G68)+N(H68))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G68&lt;&gt;"",H68&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G68&lt;&gt;"",N(G68)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G68&lt;&gt;"",H68&lt;&gt;""),(N(G68)+N(H68))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G68&lt;&gt;"",N(G68)&lt;='설정'!$E$8),AND(H68&lt;&gt;"",N(H68)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G68&lt;&gt;"",H68&lt;&gt;""),(N(G68)+N(H68))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L68" s="29">
-        <f>IF(OR(G68="",H68=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G68-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H68-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G68="",H68=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G68-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G68+H68)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G68+H68)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G68-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H68-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M68" s="7" t="n"/>
@@ -27054,11 +27051,11 @@
         <v/>
       </c>
       <c r="K69" s="27">
-        <f>IF(I69="","",IF(OR(G69="",H69=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G69&gt;='설정'!$C$6),OR('설정'!$D$6="",G69&lt;'설정'!$D$6),OR('설정'!$E$6="",H69&gt;='설정'!$E$6),OR('설정'!$F$6="",H69&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G69&gt;='설정'!$C$7),OR('설정'!$D$7="",G69&lt;'설정'!$D$7),OR('설정'!$E$7="",H69&gt;='설정'!$E$7),OR('설정'!$F$7="",H69&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G69&gt;='설정'!$C$8),OR('설정'!$D$8="",G69&lt;'설정'!$D$8),OR('설정'!$E$8="",H69&gt;='설정'!$E$8),OR('설정'!$F$8="",H69&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I69="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G69&lt;&gt;"",H69&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G69&lt;&gt;"",N(G69)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G69&lt;&gt;"",H69&lt;&gt;""),(N(G69)+N(H69))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G69&lt;&gt;"",N(G69)&lt;='설정'!$E$6),AND(H69&lt;&gt;"",N(H69)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G69&lt;&gt;"",H69&lt;&gt;""),(N(G69)+N(H69))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G69&lt;&gt;"",H69&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G69&lt;&gt;"",N(G69)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G69&lt;&gt;"",H69&lt;&gt;""),(N(G69)+N(H69))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G69&lt;&gt;"",N(G69)&lt;='설정'!$E$7),AND(H69&lt;&gt;"",N(H69)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G69&lt;&gt;"",H69&lt;&gt;""),(N(G69)+N(H69))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G69&lt;&gt;"",H69&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G69&lt;&gt;"",N(G69)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G69&lt;&gt;"",H69&lt;&gt;""),(N(G69)+N(H69))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G69&lt;&gt;"",N(G69)&lt;='설정'!$E$8),AND(H69&lt;&gt;"",N(H69)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G69&lt;&gt;"",H69&lt;&gt;""),(N(G69)+N(H69))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L69" s="29">
-        <f>IF(OR(G69="",H69=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G69-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H69-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G69="",H69=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G69-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G69+H69)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G69+H69)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G69-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H69-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M69" s="7" t="n"/>
@@ -27117,11 +27114,11 @@
         <v/>
       </c>
       <c r="K70" s="27">
-        <f>IF(I70="","",IF(OR(G70="",H70=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G70&gt;='설정'!$C$6),OR('설정'!$D$6="",G70&lt;'설정'!$D$6),OR('설정'!$E$6="",H70&gt;='설정'!$E$6),OR('설정'!$F$6="",H70&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G70&gt;='설정'!$C$7),OR('설정'!$D$7="",G70&lt;'설정'!$D$7),OR('설정'!$E$7="",H70&gt;='설정'!$E$7),OR('설정'!$F$7="",H70&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G70&gt;='설정'!$C$8),OR('설정'!$D$8="",G70&lt;'설정'!$D$8),OR('설정'!$E$8="",H70&gt;='설정'!$E$8),OR('설정'!$F$8="",H70&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I70="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G70&lt;&gt;"",H70&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G70&lt;&gt;"",N(G70)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G70&lt;&gt;"",H70&lt;&gt;""),(N(G70)+N(H70))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G70&lt;&gt;"",N(G70)&lt;='설정'!$E$6),AND(H70&lt;&gt;"",N(H70)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G70&lt;&gt;"",H70&lt;&gt;""),(N(G70)+N(H70))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G70&lt;&gt;"",H70&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G70&lt;&gt;"",N(G70)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G70&lt;&gt;"",H70&lt;&gt;""),(N(G70)+N(H70))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G70&lt;&gt;"",N(G70)&lt;='설정'!$E$7),AND(H70&lt;&gt;"",N(H70)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G70&lt;&gt;"",H70&lt;&gt;""),(N(G70)+N(H70))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G70&lt;&gt;"",H70&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G70&lt;&gt;"",N(G70)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G70&lt;&gt;"",H70&lt;&gt;""),(N(G70)+N(H70))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G70&lt;&gt;"",N(G70)&lt;='설정'!$E$8),AND(H70&lt;&gt;"",N(H70)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G70&lt;&gt;"",H70&lt;&gt;""),(N(G70)+N(H70))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L70" s="29">
-        <f>IF(OR(G70="",H70=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G70-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H70-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G70="",H70=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G70-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G70+H70)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G70+H70)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G70-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H70-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M70" s="7" t="n"/>
@@ -27180,11 +27177,11 @@
         <v/>
       </c>
       <c r="K71" s="27">
-        <f>IF(I71="","",IF(OR(G71="",H71=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G71&gt;='설정'!$C$6),OR('설정'!$D$6="",G71&lt;'설정'!$D$6),OR('설정'!$E$6="",H71&gt;='설정'!$E$6),OR('설정'!$F$6="",H71&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G71&gt;='설정'!$C$7),OR('설정'!$D$7="",G71&lt;'설정'!$D$7),OR('설정'!$E$7="",H71&gt;='설정'!$E$7),OR('설정'!$F$7="",H71&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G71&gt;='설정'!$C$8),OR('설정'!$D$8="",G71&lt;'설정'!$D$8),OR('설정'!$E$8="",H71&gt;='설정'!$E$8),OR('설정'!$F$8="",H71&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I71="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G71&lt;&gt;"",H71&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G71&lt;&gt;"",N(G71)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G71&lt;&gt;"",H71&lt;&gt;""),(N(G71)+N(H71))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G71&lt;&gt;"",N(G71)&lt;='설정'!$E$6),AND(H71&lt;&gt;"",N(H71)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G71&lt;&gt;"",H71&lt;&gt;""),(N(G71)+N(H71))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G71&lt;&gt;"",H71&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G71&lt;&gt;"",N(G71)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G71&lt;&gt;"",H71&lt;&gt;""),(N(G71)+N(H71))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G71&lt;&gt;"",N(G71)&lt;='설정'!$E$7),AND(H71&lt;&gt;"",N(H71)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G71&lt;&gt;"",H71&lt;&gt;""),(N(G71)+N(H71))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G71&lt;&gt;"",H71&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G71&lt;&gt;"",N(G71)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G71&lt;&gt;"",H71&lt;&gt;""),(N(G71)+N(H71))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G71&lt;&gt;"",N(G71)&lt;='설정'!$E$8),AND(H71&lt;&gt;"",N(H71)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G71&lt;&gt;"",H71&lt;&gt;""),(N(G71)+N(H71))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L71" s="29">
-        <f>IF(OR(G71="",H71=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G71-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H71-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G71="",H71=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G71-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G71+H71)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G71+H71)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G71-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H71-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M71" s="7" t="n"/>
@@ -27243,11 +27240,11 @@
         <v/>
       </c>
       <c r="K72" s="27">
-        <f>IF(I72="","",IF(OR(G72="",H72=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G72&gt;='설정'!$C$6),OR('설정'!$D$6="",G72&lt;'설정'!$D$6),OR('설정'!$E$6="",H72&gt;='설정'!$E$6),OR('설정'!$F$6="",H72&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G72&gt;='설정'!$C$7),OR('설정'!$D$7="",G72&lt;'설정'!$D$7),OR('설정'!$E$7="",H72&gt;='설정'!$E$7),OR('설정'!$F$7="",H72&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G72&gt;='설정'!$C$8),OR('설정'!$D$8="",G72&lt;'설정'!$D$8),OR('설정'!$E$8="",H72&gt;='설정'!$E$8),OR('설정'!$F$8="",H72&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I72="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G72&lt;&gt;"",H72&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G72&lt;&gt;"",N(G72)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G72&lt;&gt;"",H72&lt;&gt;""),(N(G72)+N(H72))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G72&lt;&gt;"",N(G72)&lt;='설정'!$E$6),AND(H72&lt;&gt;"",N(H72)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G72&lt;&gt;"",H72&lt;&gt;""),(N(G72)+N(H72))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G72&lt;&gt;"",H72&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G72&lt;&gt;"",N(G72)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G72&lt;&gt;"",H72&lt;&gt;""),(N(G72)+N(H72))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G72&lt;&gt;"",N(G72)&lt;='설정'!$E$7),AND(H72&lt;&gt;"",N(H72)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G72&lt;&gt;"",H72&lt;&gt;""),(N(G72)+N(H72))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G72&lt;&gt;"",H72&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G72&lt;&gt;"",N(G72)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G72&lt;&gt;"",H72&lt;&gt;""),(N(G72)+N(H72))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G72&lt;&gt;"",N(G72)&lt;='설정'!$E$8),AND(H72&lt;&gt;"",N(H72)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G72&lt;&gt;"",H72&lt;&gt;""),(N(G72)+N(H72))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L72" s="29">
-        <f>IF(OR(G72="",H72=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G72-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H72-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G72="",H72=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G72-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G72+H72)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G72+H72)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G72-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H72-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M72" s="7" t="n"/>
@@ -27306,11 +27303,11 @@
         <v/>
       </c>
       <c r="K73" s="27">
-        <f>IF(I73="","",IF(OR(G73="",H73=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G73&gt;='설정'!$C$6),OR('설정'!$D$6="",G73&lt;'설정'!$D$6),OR('설정'!$E$6="",H73&gt;='설정'!$E$6),OR('설정'!$F$6="",H73&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G73&gt;='설정'!$C$7),OR('설정'!$D$7="",G73&lt;'설정'!$D$7),OR('설정'!$E$7="",H73&gt;='설정'!$E$7),OR('설정'!$F$7="",H73&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G73&gt;='설정'!$C$8),OR('설정'!$D$8="",G73&lt;'설정'!$D$8),OR('설정'!$E$8="",H73&gt;='설정'!$E$8),OR('설정'!$F$8="",H73&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I73="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G73&lt;&gt;"",H73&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G73&lt;&gt;"",N(G73)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G73&lt;&gt;"",H73&lt;&gt;""),(N(G73)+N(H73))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G73&lt;&gt;"",N(G73)&lt;='설정'!$E$6),AND(H73&lt;&gt;"",N(H73)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G73&lt;&gt;"",H73&lt;&gt;""),(N(G73)+N(H73))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G73&lt;&gt;"",H73&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G73&lt;&gt;"",N(G73)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G73&lt;&gt;"",H73&lt;&gt;""),(N(G73)+N(H73))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G73&lt;&gt;"",N(G73)&lt;='설정'!$E$7),AND(H73&lt;&gt;"",N(H73)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G73&lt;&gt;"",H73&lt;&gt;""),(N(G73)+N(H73))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G73&lt;&gt;"",H73&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G73&lt;&gt;"",N(G73)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G73&lt;&gt;"",H73&lt;&gt;""),(N(G73)+N(H73))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G73&lt;&gt;"",N(G73)&lt;='설정'!$E$8),AND(H73&lt;&gt;"",N(H73)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G73&lt;&gt;"",H73&lt;&gt;""),(N(G73)+N(H73))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L73" s="29">
-        <f>IF(OR(G73="",H73=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G73-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H73-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G73="",H73=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G73-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G73+H73)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G73+H73)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G73-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H73-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M73" s="7" t="n"/>
@@ -27369,11 +27366,11 @@
         <v/>
       </c>
       <c r="K74" s="27">
-        <f>IF(I74="","",IF(OR(G74="",H74=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G74&gt;='설정'!$C$6),OR('설정'!$D$6="",G74&lt;'설정'!$D$6),OR('설정'!$E$6="",H74&gt;='설정'!$E$6),OR('설정'!$F$6="",H74&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G74&gt;='설정'!$C$7),OR('설정'!$D$7="",G74&lt;'설정'!$D$7),OR('설정'!$E$7="",H74&gt;='설정'!$E$7),OR('설정'!$F$7="",H74&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G74&gt;='설정'!$C$8),OR('설정'!$D$8="",G74&lt;'설정'!$D$8),OR('설정'!$E$8="",H74&gt;='설정'!$E$8),OR('설정'!$F$8="",H74&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I74="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G74&lt;&gt;"",H74&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G74&lt;&gt;"",N(G74)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G74&lt;&gt;"",H74&lt;&gt;""),(N(G74)+N(H74))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G74&lt;&gt;"",N(G74)&lt;='설정'!$E$6),AND(H74&lt;&gt;"",N(H74)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G74&lt;&gt;"",H74&lt;&gt;""),(N(G74)+N(H74))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G74&lt;&gt;"",H74&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G74&lt;&gt;"",N(G74)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G74&lt;&gt;"",H74&lt;&gt;""),(N(G74)+N(H74))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G74&lt;&gt;"",N(G74)&lt;='설정'!$E$7),AND(H74&lt;&gt;"",N(H74)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G74&lt;&gt;"",H74&lt;&gt;""),(N(G74)+N(H74))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G74&lt;&gt;"",H74&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G74&lt;&gt;"",N(G74)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G74&lt;&gt;"",H74&lt;&gt;""),(N(G74)+N(H74))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G74&lt;&gt;"",N(G74)&lt;='설정'!$E$8),AND(H74&lt;&gt;"",N(H74)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G74&lt;&gt;"",H74&lt;&gt;""),(N(G74)+N(H74))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L74" s="29">
-        <f>IF(OR(G74="",H74=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G74-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H74-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G74="",H74=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G74-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G74+H74)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G74+H74)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G74-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H74-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M74" s="7" t="n"/>
@@ -27432,11 +27429,11 @@
         <v/>
       </c>
       <c r="K75" s="27">
-        <f>IF(I75="","",IF(OR(G75="",H75=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G75&gt;='설정'!$C$6),OR('설정'!$D$6="",G75&lt;'설정'!$D$6),OR('설정'!$E$6="",H75&gt;='설정'!$E$6),OR('설정'!$F$6="",H75&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G75&gt;='설정'!$C$7),OR('설정'!$D$7="",G75&lt;'설정'!$D$7),OR('설정'!$E$7="",H75&gt;='설정'!$E$7),OR('설정'!$F$7="",H75&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G75&gt;='설정'!$C$8),OR('설정'!$D$8="",G75&lt;'설정'!$D$8),OR('설정'!$E$8="",H75&gt;='설정'!$E$8),OR('설정'!$F$8="",H75&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I75="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G75&lt;&gt;"",H75&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G75&lt;&gt;"",N(G75)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G75&lt;&gt;"",H75&lt;&gt;""),(N(G75)+N(H75))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G75&lt;&gt;"",N(G75)&lt;='설정'!$E$6),AND(H75&lt;&gt;"",N(H75)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G75&lt;&gt;"",H75&lt;&gt;""),(N(G75)+N(H75))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G75&lt;&gt;"",H75&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G75&lt;&gt;"",N(G75)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G75&lt;&gt;"",H75&lt;&gt;""),(N(G75)+N(H75))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G75&lt;&gt;"",N(G75)&lt;='설정'!$E$7),AND(H75&lt;&gt;"",N(H75)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G75&lt;&gt;"",H75&lt;&gt;""),(N(G75)+N(H75))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G75&lt;&gt;"",H75&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G75&lt;&gt;"",N(G75)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G75&lt;&gt;"",H75&lt;&gt;""),(N(G75)+N(H75))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G75&lt;&gt;"",N(G75)&lt;='설정'!$E$8),AND(H75&lt;&gt;"",N(H75)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G75&lt;&gt;"",H75&lt;&gt;""),(N(G75)+N(H75))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L75" s="29">
-        <f>IF(OR(G75="",H75=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G75-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H75-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G75="",H75=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G75-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G75+H75)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G75+H75)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G75-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H75-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M75" s="7" t="n"/>
@@ -27495,11 +27492,11 @@
         <v/>
       </c>
       <c r="K76" s="27">
-        <f>IF(I76="","",IF(OR(G76="",H76=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G76&gt;='설정'!$C$6),OR('설정'!$D$6="",G76&lt;'설정'!$D$6),OR('설정'!$E$6="",H76&gt;='설정'!$E$6),OR('설정'!$F$6="",H76&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G76&gt;='설정'!$C$7),OR('설정'!$D$7="",G76&lt;'설정'!$D$7),OR('설정'!$E$7="",H76&gt;='설정'!$E$7),OR('설정'!$F$7="",H76&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G76&gt;='설정'!$C$8),OR('설정'!$D$8="",G76&lt;'설정'!$D$8),OR('설정'!$E$8="",H76&gt;='설정'!$E$8),OR('설정'!$F$8="",H76&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I76="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G76&lt;&gt;"",H76&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G76&lt;&gt;"",N(G76)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G76&lt;&gt;"",H76&lt;&gt;""),(N(G76)+N(H76))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G76&lt;&gt;"",N(G76)&lt;='설정'!$E$6),AND(H76&lt;&gt;"",N(H76)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G76&lt;&gt;"",H76&lt;&gt;""),(N(G76)+N(H76))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G76&lt;&gt;"",H76&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G76&lt;&gt;"",N(G76)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G76&lt;&gt;"",H76&lt;&gt;""),(N(G76)+N(H76))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G76&lt;&gt;"",N(G76)&lt;='설정'!$E$7),AND(H76&lt;&gt;"",N(H76)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G76&lt;&gt;"",H76&lt;&gt;""),(N(G76)+N(H76))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G76&lt;&gt;"",H76&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G76&lt;&gt;"",N(G76)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G76&lt;&gt;"",H76&lt;&gt;""),(N(G76)+N(H76))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G76&lt;&gt;"",N(G76)&lt;='설정'!$E$8),AND(H76&lt;&gt;"",N(H76)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G76&lt;&gt;"",H76&lt;&gt;""),(N(G76)+N(H76))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L76" s="29">
-        <f>IF(OR(G76="",H76=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G76-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H76-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G76="",H76=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G76-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G76+H76)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G76+H76)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G76-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H76-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M76" s="7" t="n"/>
@@ -27558,11 +27555,11 @@
         <v/>
       </c>
       <c r="K77" s="27">
-        <f>IF(I77="","",IF(OR(G77="",H77=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G77&gt;='설정'!$C$6),OR('설정'!$D$6="",G77&lt;'설정'!$D$6),OR('설정'!$E$6="",H77&gt;='설정'!$E$6),OR('설정'!$F$6="",H77&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G77&gt;='설정'!$C$7),OR('설정'!$D$7="",G77&lt;'설정'!$D$7),OR('설정'!$E$7="",H77&gt;='설정'!$E$7),OR('설정'!$F$7="",H77&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G77&gt;='설정'!$C$8),OR('설정'!$D$8="",G77&lt;'설정'!$D$8),OR('설정'!$E$8="",H77&gt;='설정'!$E$8),OR('설정'!$F$8="",H77&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I77="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G77&lt;&gt;"",H77&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G77&lt;&gt;"",N(G77)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G77&lt;&gt;"",H77&lt;&gt;""),(N(G77)+N(H77))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G77&lt;&gt;"",N(G77)&lt;='설정'!$E$6),AND(H77&lt;&gt;"",N(H77)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G77&lt;&gt;"",H77&lt;&gt;""),(N(G77)+N(H77))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G77&lt;&gt;"",H77&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G77&lt;&gt;"",N(G77)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G77&lt;&gt;"",H77&lt;&gt;""),(N(G77)+N(H77))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G77&lt;&gt;"",N(G77)&lt;='설정'!$E$7),AND(H77&lt;&gt;"",N(H77)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G77&lt;&gt;"",H77&lt;&gt;""),(N(G77)+N(H77))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G77&lt;&gt;"",H77&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G77&lt;&gt;"",N(G77)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G77&lt;&gt;"",H77&lt;&gt;""),(N(G77)+N(H77))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G77&lt;&gt;"",N(G77)&lt;='설정'!$E$8),AND(H77&lt;&gt;"",N(H77)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G77&lt;&gt;"",H77&lt;&gt;""),(N(G77)+N(H77))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L77" s="29">
-        <f>IF(OR(G77="",H77=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G77-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H77-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G77="",H77=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G77-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G77+H77)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G77+H77)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G77-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H77-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M77" s="7" t="n"/>
@@ -27621,11 +27618,11 @@
         <v/>
       </c>
       <c r="K78" s="27">
-        <f>IF(I78="","",IF(OR(G78="",H78=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G78&gt;='설정'!$C$6),OR('설정'!$D$6="",G78&lt;'설정'!$D$6),OR('설정'!$E$6="",H78&gt;='설정'!$E$6),OR('설정'!$F$6="",H78&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G78&gt;='설정'!$C$7),OR('설정'!$D$7="",G78&lt;'설정'!$D$7),OR('설정'!$E$7="",H78&gt;='설정'!$E$7),OR('설정'!$F$7="",H78&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G78&gt;='설정'!$C$8),OR('설정'!$D$8="",G78&lt;'설정'!$D$8),OR('설정'!$E$8="",H78&gt;='설정'!$E$8),OR('설정'!$F$8="",H78&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I78="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G78&lt;&gt;"",H78&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G78&lt;&gt;"",N(G78)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G78&lt;&gt;"",H78&lt;&gt;""),(N(G78)+N(H78))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G78&lt;&gt;"",N(G78)&lt;='설정'!$E$6),AND(H78&lt;&gt;"",N(H78)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G78&lt;&gt;"",H78&lt;&gt;""),(N(G78)+N(H78))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G78&lt;&gt;"",H78&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G78&lt;&gt;"",N(G78)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G78&lt;&gt;"",H78&lt;&gt;""),(N(G78)+N(H78))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G78&lt;&gt;"",N(G78)&lt;='설정'!$E$7),AND(H78&lt;&gt;"",N(H78)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G78&lt;&gt;"",H78&lt;&gt;""),(N(G78)+N(H78))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G78&lt;&gt;"",H78&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G78&lt;&gt;"",N(G78)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G78&lt;&gt;"",H78&lt;&gt;""),(N(G78)+N(H78))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G78&lt;&gt;"",N(G78)&lt;='설정'!$E$8),AND(H78&lt;&gt;"",N(H78)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G78&lt;&gt;"",H78&lt;&gt;""),(N(G78)+N(H78))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L78" s="29">
-        <f>IF(OR(G78="",H78=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G78-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H78-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G78="",H78=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G78-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G78+H78)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G78+H78)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G78-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H78-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M78" s="7" t="n"/>
@@ -27684,11 +27681,11 @@
         <v/>
       </c>
       <c r="K79" s="27">
-        <f>IF(I79="","",IF(OR(G79="",H79=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G79&gt;='설정'!$C$6),OR('설정'!$D$6="",G79&lt;'설정'!$D$6),OR('설정'!$E$6="",H79&gt;='설정'!$E$6),OR('설정'!$F$6="",H79&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G79&gt;='설정'!$C$7),OR('설정'!$D$7="",G79&lt;'설정'!$D$7),OR('설정'!$E$7="",H79&gt;='설정'!$E$7),OR('설정'!$F$7="",H79&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G79&gt;='설정'!$C$8),OR('설정'!$D$8="",G79&lt;'설정'!$D$8),OR('설정'!$E$8="",H79&gt;='설정'!$E$8),OR('설정'!$F$8="",H79&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I79="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G79&lt;&gt;"",H79&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G79&lt;&gt;"",N(G79)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G79&lt;&gt;"",H79&lt;&gt;""),(N(G79)+N(H79))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G79&lt;&gt;"",N(G79)&lt;='설정'!$E$6),AND(H79&lt;&gt;"",N(H79)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G79&lt;&gt;"",H79&lt;&gt;""),(N(G79)+N(H79))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G79&lt;&gt;"",H79&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G79&lt;&gt;"",N(G79)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G79&lt;&gt;"",H79&lt;&gt;""),(N(G79)+N(H79))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G79&lt;&gt;"",N(G79)&lt;='설정'!$E$7),AND(H79&lt;&gt;"",N(H79)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G79&lt;&gt;"",H79&lt;&gt;""),(N(G79)+N(H79))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G79&lt;&gt;"",H79&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G79&lt;&gt;"",N(G79)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G79&lt;&gt;"",H79&lt;&gt;""),(N(G79)+N(H79))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G79&lt;&gt;"",N(G79)&lt;='설정'!$E$8),AND(H79&lt;&gt;"",N(H79)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G79&lt;&gt;"",H79&lt;&gt;""),(N(G79)+N(H79))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L79" s="29">
-        <f>IF(OR(G79="",H79=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G79-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H79-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G79="",H79=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G79-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G79+H79)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G79+H79)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G79-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H79-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M79" s="7" t="n"/>
@@ -27747,11 +27744,11 @@
         <v/>
       </c>
       <c r="K80" s="27">
-        <f>IF(I80="","",IF(OR(G80="",H80=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G80&gt;='설정'!$C$6),OR('설정'!$D$6="",G80&lt;'설정'!$D$6),OR('설정'!$E$6="",H80&gt;='설정'!$E$6),OR('설정'!$F$6="",H80&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G80&gt;='설정'!$C$7),OR('설정'!$D$7="",G80&lt;'설정'!$D$7),OR('설정'!$E$7="",H80&gt;='설정'!$E$7),OR('설정'!$F$7="",H80&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G80&gt;='설정'!$C$8),OR('설정'!$D$8="",G80&lt;'설정'!$D$8),OR('설정'!$E$8="",H80&gt;='설정'!$E$8),OR('설정'!$F$8="",H80&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I80="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G80&lt;&gt;"",H80&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G80&lt;&gt;"",N(G80)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G80&lt;&gt;"",H80&lt;&gt;""),(N(G80)+N(H80))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G80&lt;&gt;"",N(G80)&lt;='설정'!$E$6),AND(H80&lt;&gt;"",N(H80)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G80&lt;&gt;"",H80&lt;&gt;""),(N(G80)+N(H80))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G80&lt;&gt;"",H80&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G80&lt;&gt;"",N(G80)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G80&lt;&gt;"",H80&lt;&gt;""),(N(G80)+N(H80))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G80&lt;&gt;"",N(G80)&lt;='설정'!$E$7),AND(H80&lt;&gt;"",N(H80)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G80&lt;&gt;"",H80&lt;&gt;""),(N(G80)+N(H80))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G80&lt;&gt;"",H80&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G80&lt;&gt;"",N(G80)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G80&lt;&gt;"",H80&lt;&gt;""),(N(G80)+N(H80))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G80&lt;&gt;"",N(G80)&lt;='설정'!$E$8),AND(H80&lt;&gt;"",N(H80)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G80&lt;&gt;"",H80&lt;&gt;""),(N(G80)+N(H80))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L80" s="29">
-        <f>IF(OR(G80="",H80=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G80-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H80-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G80="",H80=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G80-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G80+H80)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G80+H80)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G80-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H80-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M80" s="7" t="n"/>
@@ -27810,11 +27807,11 @@
         <v/>
       </c>
       <c r="K81" s="27">
-        <f>IF(I81="","",IF(OR(G81="",H81=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G81&gt;='설정'!$C$6),OR('설정'!$D$6="",G81&lt;'설정'!$D$6),OR('설정'!$E$6="",H81&gt;='설정'!$E$6),OR('설정'!$F$6="",H81&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G81&gt;='설정'!$C$7),OR('설정'!$D$7="",G81&lt;'설정'!$D$7),OR('설정'!$E$7="",H81&gt;='설정'!$E$7),OR('설정'!$F$7="",H81&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G81&gt;='설정'!$C$8),OR('설정'!$D$8="",G81&lt;'설정'!$D$8),OR('설정'!$E$8="",H81&gt;='설정'!$E$8),OR('설정'!$F$8="",H81&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I81="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G81&lt;&gt;"",H81&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G81&lt;&gt;"",N(G81)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G81&lt;&gt;"",H81&lt;&gt;""),(N(G81)+N(H81))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G81&lt;&gt;"",N(G81)&lt;='설정'!$E$6),AND(H81&lt;&gt;"",N(H81)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G81&lt;&gt;"",H81&lt;&gt;""),(N(G81)+N(H81))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G81&lt;&gt;"",H81&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G81&lt;&gt;"",N(G81)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G81&lt;&gt;"",H81&lt;&gt;""),(N(G81)+N(H81))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G81&lt;&gt;"",N(G81)&lt;='설정'!$E$7),AND(H81&lt;&gt;"",N(H81)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G81&lt;&gt;"",H81&lt;&gt;""),(N(G81)+N(H81))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G81&lt;&gt;"",H81&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G81&lt;&gt;"",N(G81)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G81&lt;&gt;"",H81&lt;&gt;""),(N(G81)+N(H81))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G81&lt;&gt;"",N(G81)&lt;='설정'!$E$8),AND(H81&lt;&gt;"",N(H81)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G81&lt;&gt;"",H81&lt;&gt;""),(N(G81)+N(H81))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L81" s="29">
-        <f>IF(OR(G81="",H81=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G81-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H81-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G81="",H81=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G81-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G81+H81)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G81+H81)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G81-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H81-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M81" s="7" t="n"/>
@@ -27873,11 +27870,11 @@
         <v/>
       </c>
       <c r="K82" s="27">
-        <f>IF(I82="","",IF(OR(G82="",H82=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G82&gt;='설정'!$C$6),OR('설정'!$D$6="",G82&lt;'설정'!$D$6),OR('설정'!$E$6="",H82&gt;='설정'!$E$6),OR('설정'!$F$6="",H82&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G82&gt;='설정'!$C$7),OR('설정'!$D$7="",G82&lt;'설정'!$D$7),OR('설정'!$E$7="",H82&gt;='설정'!$E$7),OR('설정'!$F$7="",H82&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G82&gt;='설정'!$C$8),OR('설정'!$D$8="",G82&lt;'설정'!$D$8),OR('설정'!$E$8="",H82&gt;='설정'!$E$8),OR('설정'!$F$8="",H82&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I82="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G82&lt;&gt;"",H82&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G82&lt;&gt;"",N(G82)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G82&lt;&gt;"",H82&lt;&gt;""),(N(G82)+N(H82))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G82&lt;&gt;"",N(G82)&lt;='설정'!$E$6),AND(H82&lt;&gt;"",N(H82)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G82&lt;&gt;"",H82&lt;&gt;""),(N(G82)+N(H82))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G82&lt;&gt;"",H82&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G82&lt;&gt;"",N(G82)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G82&lt;&gt;"",H82&lt;&gt;""),(N(G82)+N(H82))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G82&lt;&gt;"",N(G82)&lt;='설정'!$E$7),AND(H82&lt;&gt;"",N(H82)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G82&lt;&gt;"",H82&lt;&gt;""),(N(G82)+N(H82))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G82&lt;&gt;"",H82&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G82&lt;&gt;"",N(G82)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G82&lt;&gt;"",H82&lt;&gt;""),(N(G82)+N(H82))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G82&lt;&gt;"",N(G82)&lt;='설정'!$E$8),AND(H82&lt;&gt;"",N(H82)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G82&lt;&gt;"",H82&lt;&gt;""),(N(G82)+N(H82))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L82" s="29">
-        <f>IF(OR(G82="",H82=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G82-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H82-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G82="",H82=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G82-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G82+H82)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G82+H82)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G82-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H82-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M82" s="7" t="n"/>
@@ -27936,11 +27933,11 @@
         <v/>
       </c>
       <c r="K83" s="27">
-        <f>IF(I83="","",IF(OR(G83="",H83=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G83&gt;='설정'!$C$6),OR('설정'!$D$6="",G83&lt;'설정'!$D$6),OR('설정'!$E$6="",H83&gt;='설정'!$E$6),OR('설정'!$F$6="",H83&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G83&gt;='설정'!$C$7),OR('설정'!$D$7="",G83&lt;'설정'!$D$7),OR('설정'!$E$7="",H83&gt;='설정'!$E$7),OR('설정'!$F$7="",H83&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G83&gt;='설정'!$C$8),OR('설정'!$D$8="",G83&lt;'설정'!$D$8),OR('설정'!$E$8="",H83&gt;='설정'!$E$8),OR('설정'!$F$8="",H83&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I83="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G83&lt;&gt;"",H83&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G83&lt;&gt;"",N(G83)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G83&lt;&gt;"",H83&lt;&gt;""),(N(G83)+N(H83))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G83&lt;&gt;"",N(G83)&lt;='설정'!$E$6),AND(H83&lt;&gt;"",N(H83)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G83&lt;&gt;"",H83&lt;&gt;""),(N(G83)+N(H83))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G83&lt;&gt;"",H83&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G83&lt;&gt;"",N(G83)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G83&lt;&gt;"",H83&lt;&gt;""),(N(G83)+N(H83))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G83&lt;&gt;"",N(G83)&lt;='설정'!$E$7),AND(H83&lt;&gt;"",N(H83)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G83&lt;&gt;"",H83&lt;&gt;""),(N(G83)+N(H83))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G83&lt;&gt;"",H83&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G83&lt;&gt;"",N(G83)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G83&lt;&gt;"",H83&lt;&gt;""),(N(G83)+N(H83))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G83&lt;&gt;"",N(G83)&lt;='설정'!$E$8),AND(H83&lt;&gt;"",N(H83)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G83&lt;&gt;"",H83&lt;&gt;""),(N(G83)+N(H83))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L83" s="29">
-        <f>IF(OR(G83="",H83=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G83-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H83-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G83="",H83=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G83-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G83+H83)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G83+H83)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G83-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H83-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M83" s="7" t="n"/>
@@ -27999,11 +27996,11 @@
         <v/>
       </c>
       <c r="K84" s="27">
-        <f>IF(I84="","",IF(OR(G84="",H84=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G84&gt;='설정'!$C$6),OR('설정'!$D$6="",G84&lt;'설정'!$D$6),OR('설정'!$E$6="",H84&gt;='설정'!$E$6),OR('설정'!$F$6="",H84&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G84&gt;='설정'!$C$7),OR('설정'!$D$7="",G84&lt;'설정'!$D$7),OR('설정'!$E$7="",H84&gt;='설정'!$E$7),OR('설정'!$F$7="",H84&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G84&gt;='설정'!$C$8),OR('설정'!$D$8="",G84&lt;'설정'!$D$8),OR('설정'!$E$8="",H84&gt;='설정'!$E$8),OR('설정'!$F$8="",H84&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I84="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G84&lt;&gt;"",H84&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G84&lt;&gt;"",N(G84)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G84&lt;&gt;"",H84&lt;&gt;""),(N(G84)+N(H84))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G84&lt;&gt;"",N(G84)&lt;='설정'!$E$6),AND(H84&lt;&gt;"",N(H84)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G84&lt;&gt;"",H84&lt;&gt;""),(N(G84)+N(H84))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G84&lt;&gt;"",H84&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G84&lt;&gt;"",N(G84)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G84&lt;&gt;"",H84&lt;&gt;""),(N(G84)+N(H84))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G84&lt;&gt;"",N(G84)&lt;='설정'!$E$7),AND(H84&lt;&gt;"",N(H84)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G84&lt;&gt;"",H84&lt;&gt;""),(N(G84)+N(H84))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G84&lt;&gt;"",H84&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G84&lt;&gt;"",N(G84)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G84&lt;&gt;"",H84&lt;&gt;""),(N(G84)+N(H84))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G84&lt;&gt;"",N(G84)&lt;='설정'!$E$8),AND(H84&lt;&gt;"",N(H84)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G84&lt;&gt;"",H84&lt;&gt;""),(N(G84)+N(H84))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L84" s="29">
-        <f>IF(OR(G84="",H84=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G84-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H84-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G84="",H84=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G84-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G84+H84)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G84+H84)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G84-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H84-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M84" s="7" t="n"/>
@@ -28062,11 +28059,11 @@
         <v/>
       </c>
       <c r="K85" s="27">
-        <f>IF(I85="","",IF(OR(G85="",H85=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G85&gt;='설정'!$C$6),OR('설정'!$D$6="",G85&lt;'설정'!$D$6),OR('설정'!$E$6="",H85&gt;='설정'!$E$6),OR('설정'!$F$6="",H85&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G85&gt;='설정'!$C$7),OR('설정'!$D$7="",G85&lt;'설정'!$D$7),OR('설정'!$E$7="",H85&gt;='설정'!$E$7),OR('설정'!$F$7="",H85&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G85&gt;='설정'!$C$8),OR('설정'!$D$8="",G85&lt;'설정'!$D$8),OR('설정'!$E$8="",H85&gt;='설정'!$E$8),OR('설정'!$F$8="",H85&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I85="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G85&lt;&gt;"",H85&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G85&lt;&gt;"",N(G85)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G85&lt;&gt;"",H85&lt;&gt;""),(N(G85)+N(H85))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G85&lt;&gt;"",N(G85)&lt;='설정'!$E$6),AND(H85&lt;&gt;"",N(H85)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G85&lt;&gt;"",H85&lt;&gt;""),(N(G85)+N(H85))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G85&lt;&gt;"",H85&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G85&lt;&gt;"",N(G85)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G85&lt;&gt;"",H85&lt;&gt;""),(N(G85)+N(H85))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G85&lt;&gt;"",N(G85)&lt;='설정'!$E$7),AND(H85&lt;&gt;"",N(H85)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G85&lt;&gt;"",H85&lt;&gt;""),(N(G85)+N(H85))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G85&lt;&gt;"",H85&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G85&lt;&gt;"",N(G85)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G85&lt;&gt;"",H85&lt;&gt;""),(N(G85)+N(H85))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G85&lt;&gt;"",N(G85)&lt;='설정'!$E$8),AND(H85&lt;&gt;"",N(H85)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G85&lt;&gt;"",H85&lt;&gt;""),(N(G85)+N(H85))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L85" s="29">
-        <f>IF(OR(G85="",H85=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G85-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H85-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G85="",H85=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G85-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G85+H85)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G85+H85)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G85-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H85-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M85" s="7" t="n"/>
@@ -28125,11 +28122,11 @@
         <v/>
       </c>
       <c r="K86" s="27">
-        <f>IF(I86="","",IF(OR(G86="",H86=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G86&gt;='설정'!$C$6),OR('설정'!$D$6="",G86&lt;'설정'!$D$6),OR('설정'!$E$6="",H86&gt;='설정'!$E$6),OR('설정'!$F$6="",H86&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G86&gt;='설정'!$C$7),OR('설정'!$D$7="",G86&lt;'설정'!$D$7),OR('설정'!$E$7="",H86&gt;='설정'!$E$7),OR('설정'!$F$7="",H86&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G86&gt;='설정'!$C$8),OR('설정'!$D$8="",G86&lt;'설정'!$D$8),OR('설정'!$E$8="",H86&gt;='설정'!$E$8),OR('설정'!$F$8="",H86&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I86="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G86&lt;&gt;"",H86&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G86&lt;&gt;"",N(G86)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G86&lt;&gt;"",H86&lt;&gt;""),(N(G86)+N(H86))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G86&lt;&gt;"",N(G86)&lt;='설정'!$E$6),AND(H86&lt;&gt;"",N(H86)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G86&lt;&gt;"",H86&lt;&gt;""),(N(G86)+N(H86))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G86&lt;&gt;"",H86&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G86&lt;&gt;"",N(G86)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G86&lt;&gt;"",H86&lt;&gt;""),(N(G86)+N(H86))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G86&lt;&gt;"",N(G86)&lt;='설정'!$E$7),AND(H86&lt;&gt;"",N(H86)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G86&lt;&gt;"",H86&lt;&gt;""),(N(G86)+N(H86))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G86&lt;&gt;"",H86&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G86&lt;&gt;"",N(G86)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G86&lt;&gt;"",H86&lt;&gt;""),(N(G86)+N(H86))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G86&lt;&gt;"",N(G86)&lt;='설정'!$E$8),AND(H86&lt;&gt;"",N(H86)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G86&lt;&gt;"",H86&lt;&gt;""),(N(G86)+N(H86))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L86" s="29">
-        <f>IF(OR(G86="",H86=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G86-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H86-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G86="",H86=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G86-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G86+H86)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G86+H86)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G86-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H86-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M86" s="7" t="n"/>
@@ -28188,11 +28185,11 @@
         <v/>
       </c>
       <c r="K87" s="27">
-        <f>IF(I87="","",IF(OR(G87="",H87=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G87&gt;='설정'!$C$6),OR('설정'!$D$6="",G87&lt;'설정'!$D$6),OR('설정'!$E$6="",H87&gt;='설정'!$E$6),OR('설정'!$F$6="",H87&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G87&gt;='설정'!$C$7),OR('설정'!$D$7="",G87&lt;'설정'!$D$7),OR('설정'!$E$7="",H87&gt;='설정'!$E$7),OR('설정'!$F$7="",H87&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G87&gt;='설정'!$C$8),OR('설정'!$D$8="",G87&lt;'설정'!$D$8),OR('설정'!$E$8="",H87&gt;='설정'!$E$8),OR('설정'!$F$8="",H87&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I87="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G87&lt;&gt;"",H87&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G87&lt;&gt;"",N(G87)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G87&lt;&gt;"",H87&lt;&gt;""),(N(G87)+N(H87))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G87&lt;&gt;"",N(G87)&lt;='설정'!$E$6),AND(H87&lt;&gt;"",N(H87)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G87&lt;&gt;"",H87&lt;&gt;""),(N(G87)+N(H87))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G87&lt;&gt;"",H87&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G87&lt;&gt;"",N(G87)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G87&lt;&gt;"",H87&lt;&gt;""),(N(G87)+N(H87))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G87&lt;&gt;"",N(G87)&lt;='설정'!$E$7),AND(H87&lt;&gt;"",N(H87)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G87&lt;&gt;"",H87&lt;&gt;""),(N(G87)+N(H87))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G87&lt;&gt;"",H87&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G87&lt;&gt;"",N(G87)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G87&lt;&gt;"",H87&lt;&gt;""),(N(G87)+N(H87))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G87&lt;&gt;"",N(G87)&lt;='설정'!$E$8),AND(H87&lt;&gt;"",N(H87)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G87&lt;&gt;"",H87&lt;&gt;""),(N(G87)+N(H87))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L87" s="29">
-        <f>IF(OR(G87="",H87=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G87-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H87-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G87="",H87=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G87-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G87+H87)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G87+H87)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G87-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H87-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M87" s="7" t="n"/>
@@ -28251,11 +28248,11 @@
         <v/>
       </c>
       <c r="K88" s="27">
-        <f>IF(I88="","",IF(OR(G88="",H88=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G88&gt;='설정'!$C$6),OR('설정'!$D$6="",G88&lt;'설정'!$D$6),OR('설정'!$E$6="",H88&gt;='설정'!$E$6),OR('설정'!$F$6="",H88&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G88&gt;='설정'!$C$7),OR('설정'!$D$7="",G88&lt;'설정'!$D$7),OR('설정'!$E$7="",H88&gt;='설정'!$E$7),OR('설정'!$F$7="",H88&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G88&gt;='설정'!$C$8),OR('설정'!$D$8="",G88&lt;'설정'!$D$8),OR('설정'!$E$8="",H88&gt;='설정'!$E$8),OR('설정'!$F$8="",H88&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I88="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G88&lt;&gt;"",H88&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G88&lt;&gt;"",N(G88)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G88&lt;&gt;"",H88&lt;&gt;""),(N(G88)+N(H88))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G88&lt;&gt;"",N(G88)&lt;='설정'!$E$6),AND(H88&lt;&gt;"",N(H88)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G88&lt;&gt;"",H88&lt;&gt;""),(N(G88)+N(H88))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G88&lt;&gt;"",H88&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G88&lt;&gt;"",N(G88)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G88&lt;&gt;"",H88&lt;&gt;""),(N(G88)+N(H88))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G88&lt;&gt;"",N(G88)&lt;='설정'!$E$7),AND(H88&lt;&gt;"",N(H88)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G88&lt;&gt;"",H88&lt;&gt;""),(N(G88)+N(H88))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G88&lt;&gt;"",H88&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G88&lt;&gt;"",N(G88)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G88&lt;&gt;"",H88&lt;&gt;""),(N(G88)+N(H88))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G88&lt;&gt;"",N(G88)&lt;='설정'!$E$8),AND(H88&lt;&gt;"",N(H88)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G88&lt;&gt;"",H88&lt;&gt;""),(N(G88)+N(H88))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L88" s="29">
-        <f>IF(OR(G88="",H88=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G88-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H88-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G88="",H88=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G88-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G88+H88)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G88+H88)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G88-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H88-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M88" s="7" t="n"/>
@@ -28314,11 +28311,11 @@
         <v/>
       </c>
       <c r="K89" s="27">
-        <f>IF(I89="","",IF(OR(G89="",H89=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G89&gt;='설정'!$C$6),OR('설정'!$D$6="",G89&lt;'설정'!$D$6),OR('설정'!$E$6="",H89&gt;='설정'!$E$6),OR('설정'!$F$6="",H89&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G89&gt;='설정'!$C$7),OR('설정'!$D$7="",G89&lt;'설정'!$D$7),OR('설정'!$E$7="",H89&gt;='설정'!$E$7),OR('설정'!$F$7="",H89&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G89&gt;='설정'!$C$8),OR('설정'!$D$8="",G89&lt;'설정'!$D$8),OR('설정'!$E$8="",H89&gt;='설정'!$E$8),OR('설정'!$F$8="",H89&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I89="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G89&lt;&gt;"",H89&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G89&lt;&gt;"",N(G89)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G89&lt;&gt;"",H89&lt;&gt;""),(N(G89)+N(H89))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G89&lt;&gt;"",N(G89)&lt;='설정'!$E$6),AND(H89&lt;&gt;"",N(H89)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G89&lt;&gt;"",H89&lt;&gt;""),(N(G89)+N(H89))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G89&lt;&gt;"",H89&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G89&lt;&gt;"",N(G89)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G89&lt;&gt;"",H89&lt;&gt;""),(N(G89)+N(H89))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G89&lt;&gt;"",N(G89)&lt;='설정'!$E$7),AND(H89&lt;&gt;"",N(H89)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G89&lt;&gt;"",H89&lt;&gt;""),(N(G89)+N(H89))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G89&lt;&gt;"",H89&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G89&lt;&gt;"",N(G89)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G89&lt;&gt;"",H89&lt;&gt;""),(N(G89)+N(H89))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G89&lt;&gt;"",N(G89)&lt;='설정'!$E$8),AND(H89&lt;&gt;"",N(H89)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G89&lt;&gt;"",H89&lt;&gt;""),(N(G89)+N(H89))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L89" s="29">
-        <f>IF(OR(G89="",H89=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G89-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H89-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G89="",H89=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G89-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G89+H89)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G89+H89)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G89-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H89-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M89" s="7" t="n"/>
@@ -28377,11 +28374,11 @@
         <v/>
       </c>
       <c r="K90" s="27">
-        <f>IF(I90="","",IF(OR(G90="",H90=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G90&gt;='설정'!$C$6),OR('설정'!$D$6="",G90&lt;'설정'!$D$6),OR('설정'!$E$6="",H90&gt;='설정'!$E$6),OR('설정'!$F$6="",H90&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G90&gt;='설정'!$C$7),OR('설정'!$D$7="",G90&lt;'설정'!$D$7),OR('설정'!$E$7="",H90&gt;='설정'!$E$7),OR('설정'!$F$7="",H90&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G90&gt;='설정'!$C$8),OR('설정'!$D$8="",G90&lt;'설정'!$D$8),OR('설정'!$E$8="",H90&gt;='설정'!$E$8),OR('설정'!$F$8="",H90&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I90="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G90&lt;&gt;"",H90&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G90&lt;&gt;"",N(G90)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G90&lt;&gt;"",H90&lt;&gt;""),(N(G90)+N(H90))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G90&lt;&gt;"",N(G90)&lt;='설정'!$E$6),AND(H90&lt;&gt;"",N(H90)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G90&lt;&gt;"",H90&lt;&gt;""),(N(G90)+N(H90))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G90&lt;&gt;"",H90&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G90&lt;&gt;"",N(G90)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G90&lt;&gt;"",H90&lt;&gt;""),(N(G90)+N(H90))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G90&lt;&gt;"",N(G90)&lt;='설정'!$E$7),AND(H90&lt;&gt;"",N(H90)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G90&lt;&gt;"",H90&lt;&gt;""),(N(G90)+N(H90))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G90&lt;&gt;"",H90&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G90&lt;&gt;"",N(G90)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G90&lt;&gt;"",H90&lt;&gt;""),(N(G90)+N(H90))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G90&lt;&gt;"",N(G90)&lt;='설정'!$E$8),AND(H90&lt;&gt;"",N(H90)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G90&lt;&gt;"",H90&lt;&gt;""),(N(G90)+N(H90))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L90" s="29">
-        <f>IF(OR(G90="",H90=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G90-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H90-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G90="",H90=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G90-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G90+H90)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G90+H90)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G90-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H90-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M90" s="7" t="n"/>
@@ -28440,11 +28437,11 @@
         <v/>
       </c>
       <c r="K91" s="27">
-        <f>IF(I91="","",IF(OR(G91="",H91=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G91&gt;='설정'!$C$6),OR('설정'!$D$6="",G91&lt;'설정'!$D$6),OR('설정'!$E$6="",H91&gt;='설정'!$E$6),OR('설정'!$F$6="",H91&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G91&gt;='설정'!$C$7),OR('설정'!$D$7="",G91&lt;'설정'!$D$7),OR('설정'!$E$7="",H91&gt;='설정'!$E$7),OR('설정'!$F$7="",H91&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G91&gt;='설정'!$C$8),OR('설정'!$D$8="",G91&lt;'설정'!$D$8),OR('설정'!$E$8="",H91&gt;='설정'!$E$8),OR('설정'!$F$8="",H91&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I91="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G91&lt;&gt;"",H91&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G91&lt;&gt;"",N(G91)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G91&lt;&gt;"",H91&lt;&gt;""),(N(G91)+N(H91))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G91&lt;&gt;"",N(G91)&lt;='설정'!$E$6),AND(H91&lt;&gt;"",N(H91)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G91&lt;&gt;"",H91&lt;&gt;""),(N(G91)+N(H91))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G91&lt;&gt;"",H91&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G91&lt;&gt;"",N(G91)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G91&lt;&gt;"",H91&lt;&gt;""),(N(G91)+N(H91))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G91&lt;&gt;"",N(G91)&lt;='설정'!$E$7),AND(H91&lt;&gt;"",N(H91)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G91&lt;&gt;"",H91&lt;&gt;""),(N(G91)+N(H91))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G91&lt;&gt;"",H91&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G91&lt;&gt;"",N(G91)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G91&lt;&gt;"",H91&lt;&gt;""),(N(G91)+N(H91))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G91&lt;&gt;"",N(G91)&lt;='설정'!$E$8),AND(H91&lt;&gt;"",N(H91)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G91&lt;&gt;"",H91&lt;&gt;""),(N(G91)+N(H91))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L91" s="29">
-        <f>IF(OR(G91="",H91=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G91-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H91-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G91="",H91=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G91-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G91+H91)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G91+H91)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G91-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H91-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M91" s="7" t="n"/>
@@ -28503,11 +28500,11 @@
         <v/>
       </c>
       <c r="K92" s="27">
-        <f>IF(I92="","",IF(OR(G92="",H92=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G92&gt;='설정'!$C$6),OR('설정'!$D$6="",G92&lt;'설정'!$D$6),OR('설정'!$E$6="",H92&gt;='설정'!$E$6),OR('설정'!$F$6="",H92&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G92&gt;='설정'!$C$7),OR('설정'!$D$7="",G92&lt;'설정'!$D$7),OR('설정'!$E$7="",H92&gt;='설정'!$E$7),OR('설정'!$F$7="",H92&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G92&gt;='설정'!$C$8),OR('설정'!$D$8="",G92&lt;'설정'!$D$8),OR('설정'!$E$8="",H92&gt;='설정'!$E$8),OR('설정'!$F$8="",H92&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I92="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G92&lt;&gt;"",H92&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G92&lt;&gt;"",N(G92)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G92&lt;&gt;"",H92&lt;&gt;""),(N(G92)+N(H92))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G92&lt;&gt;"",N(G92)&lt;='설정'!$E$6),AND(H92&lt;&gt;"",N(H92)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G92&lt;&gt;"",H92&lt;&gt;""),(N(G92)+N(H92))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G92&lt;&gt;"",H92&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G92&lt;&gt;"",N(G92)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G92&lt;&gt;"",H92&lt;&gt;""),(N(G92)+N(H92))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G92&lt;&gt;"",N(G92)&lt;='설정'!$E$7),AND(H92&lt;&gt;"",N(H92)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G92&lt;&gt;"",H92&lt;&gt;""),(N(G92)+N(H92))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G92&lt;&gt;"",H92&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G92&lt;&gt;"",N(G92)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G92&lt;&gt;"",H92&lt;&gt;""),(N(G92)+N(H92))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G92&lt;&gt;"",N(G92)&lt;='설정'!$E$8),AND(H92&lt;&gt;"",N(H92)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G92&lt;&gt;"",H92&lt;&gt;""),(N(G92)+N(H92))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L92" s="29">
-        <f>IF(OR(G92="",H92=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G92-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H92-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G92="",H92=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G92-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G92+H92)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G92+H92)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G92-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H92-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M92" s="7" t="n"/>
@@ -28566,11 +28563,11 @@
         <v/>
       </c>
       <c r="K93" s="27">
-        <f>IF(I93="","",IF(OR(G93="",H93=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G93&gt;='설정'!$C$6),OR('설정'!$D$6="",G93&lt;'설정'!$D$6),OR('설정'!$E$6="",H93&gt;='설정'!$E$6),OR('설정'!$F$6="",H93&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G93&gt;='설정'!$C$7),OR('설정'!$D$7="",G93&lt;'설정'!$D$7),OR('설정'!$E$7="",H93&gt;='설정'!$E$7),OR('설정'!$F$7="",H93&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G93&gt;='설정'!$C$8),OR('설정'!$D$8="",G93&lt;'설정'!$D$8),OR('설정'!$E$8="",H93&gt;='설정'!$E$8),OR('설정'!$F$8="",H93&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I93="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G93&lt;&gt;"",H93&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G93&lt;&gt;"",N(G93)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G93&lt;&gt;"",H93&lt;&gt;""),(N(G93)+N(H93))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G93&lt;&gt;"",N(G93)&lt;='설정'!$E$6),AND(H93&lt;&gt;"",N(H93)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G93&lt;&gt;"",H93&lt;&gt;""),(N(G93)+N(H93))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G93&lt;&gt;"",H93&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G93&lt;&gt;"",N(G93)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G93&lt;&gt;"",H93&lt;&gt;""),(N(G93)+N(H93))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G93&lt;&gt;"",N(G93)&lt;='설정'!$E$7),AND(H93&lt;&gt;"",N(H93)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G93&lt;&gt;"",H93&lt;&gt;""),(N(G93)+N(H93))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G93&lt;&gt;"",H93&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G93&lt;&gt;"",N(G93)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G93&lt;&gt;"",H93&lt;&gt;""),(N(G93)+N(H93))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G93&lt;&gt;"",N(G93)&lt;='설정'!$E$8),AND(H93&lt;&gt;"",N(H93)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G93&lt;&gt;"",H93&lt;&gt;""),(N(G93)+N(H93))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L93" s="29">
-        <f>IF(OR(G93="",H93=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G93-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H93-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G93="",H93=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G93-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G93+H93)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G93+H93)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G93-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H93-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M93" s="7" t="n"/>
@@ -28629,11 +28626,11 @@
         <v/>
       </c>
       <c r="K94" s="27">
-        <f>IF(I94="","",IF(OR(G94="",H94=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G94&gt;='설정'!$C$6),OR('설정'!$D$6="",G94&lt;'설정'!$D$6),OR('설정'!$E$6="",H94&gt;='설정'!$E$6),OR('설정'!$F$6="",H94&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G94&gt;='설정'!$C$7),OR('설정'!$D$7="",G94&lt;'설정'!$D$7),OR('설정'!$E$7="",H94&gt;='설정'!$E$7),OR('설정'!$F$7="",H94&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G94&gt;='설정'!$C$8),OR('설정'!$D$8="",G94&lt;'설정'!$D$8),OR('설정'!$E$8="",H94&gt;='설정'!$E$8),OR('설정'!$F$8="",H94&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I94="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G94&lt;&gt;"",H94&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G94&lt;&gt;"",N(G94)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G94&lt;&gt;"",H94&lt;&gt;""),(N(G94)+N(H94))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G94&lt;&gt;"",N(G94)&lt;='설정'!$E$6),AND(H94&lt;&gt;"",N(H94)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G94&lt;&gt;"",H94&lt;&gt;""),(N(G94)+N(H94))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G94&lt;&gt;"",H94&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G94&lt;&gt;"",N(G94)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G94&lt;&gt;"",H94&lt;&gt;""),(N(G94)+N(H94))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G94&lt;&gt;"",N(G94)&lt;='설정'!$E$7),AND(H94&lt;&gt;"",N(H94)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G94&lt;&gt;"",H94&lt;&gt;""),(N(G94)+N(H94))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G94&lt;&gt;"",H94&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G94&lt;&gt;"",N(G94)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G94&lt;&gt;"",H94&lt;&gt;""),(N(G94)+N(H94))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G94&lt;&gt;"",N(G94)&lt;='설정'!$E$8),AND(H94&lt;&gt;"",N(H94)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G94&lt;&gt;"",H94&lt;&gt;""),(N(G94)+N(H94))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L94" s="29">
-        <f>IF(OR(G94="",H94=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G94-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H94-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G94="",H94=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G94-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G94+H94)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G94+H94)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G94-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H94-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M94" s="7" t="n"/>
@@ -28692,11 +28689,11 @@
         <v/>
       </c>
       <c r="K95" s="27">
-        <f>IF(I95="","",IF(OR(G95="",H95=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G95&gt;='설정'!$C$6),OR('설정'!$D$6="",G95&lt;'설정'!$D$6),OR('설정'!$E$6="",H95&gt;='설정'!$E$6),OR('설정'!$F$6="",H95&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G95&gt;='설정'!$C$7),OR('설정'!$D$7="",G95&lt;'설정'!$D$7),OR('설정'!$E$7="",H95&gt;='설정'!$E$7),OR('설정'!$F$7="",H95&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G95&gt;='설정'!$C$8),OR('설정'!$D$8="",G95&lt;'설정'!$D$8),OR('설정'!$E$8="",H95&gt;='설정'!$E$8),OR('설정'!$F$8="",H95&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I95="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G95&lt;&gt;"",H95&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G95&lt;&gt;"",N(G95)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G95&lt;&gt;"",H95&lt;&gt;""),(N(G95)+N(H95))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G95&lt;&gt;"",N(G95)&lt;='설정'!$E$6),AND(H95&lt;&gt;"",N(H95)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G95&lt;&gt;"",H95&lt;&gt;""),(N(G95)+N(H95))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G95&lt;&gt;"",H95&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G95&lt;&gt;"",N(G95)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G95&lt;&gt;"",H95&lt;&gt;""),(N(G95)+N(H95))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G95&lt;&gt;"",N(G95)&lt;='설정'!$E$7),AND(H95&lt;&gt;"",N(H95)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G95&lt;&gt;"",H95&lt;&gt;""),(N(G95)+N(H95))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G95&lt;&gt;"",H95&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G95&lt;&gt;"",N(G95)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G95&lt;&gt;"",H95&lt;&gt;""),(N(G95)+N(H95))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G95&lt;&gt;"",N(G95)&lt;='설정'!$E$8),AND(H95&lt;&gt;"",N(H95)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G95&lt;&gt;"",H95&lt;&gt;""),(N(G95)+N(H95))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L95" s="29">
-        <f>IF(OR(G95="",H95=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G95-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H95-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G95="",H95=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G95-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G95+H95)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G95+H95)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G95-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H95-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M95" s="7" t="n"/>
@@ -28755,11 +28752,11 @@
         <v/>
       </c>
       <c r="K96" s="27">
-        <f>IF(I96="","",IF(OR(G96="",H96=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G96&gt;='설정'!$C$6),OR('설정'!$D$6="",G96&lt;'설정'!$D$6),OR('설정'!$E$6="",H96&gt;='설정'!$E$6),OR('설정'!$F$6="",H96&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G96&gt;='설정'!$C$7),OR('설정'!$D$7="",G96&lt;'설정'!$D$7),OR('설정'!$E$7="",H96&gt;='설정'!$E$7),OR('설정'!$F$7="",H96&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G96&gt;='설정'!$C$8),OR('설정'!$D$8="",G96&lt;'설정'!$D$8),OR('설정'!$E$8="",H96&gt;='설정'!$E$8),OR('설정'!$F$8="",H96&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I96="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G96&lt;&gt;"",H96&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G96&lt;&gt;"",N(G96)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G96&lt;&gt;"",H96&lt;&gt;""),(N(G96)+N(H96))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G96&lt;&gt;"",N(G96)&lt;='설정'!$E$6),AND(H96&lt;&gt;"",N(H96)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G96&lt;&gt;"",H96&lt;&gt;""),(N(G96)+N(H96))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G96&lt;&gt;"",H96&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G96&lt;&gt;"",N(G96)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G96&lt;&gt;"",H96&lt;&gt;""),(N(G96)+N(H96))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G96&lt;&gt;"",N(G96)&lt;='설정'!$E$7),AND(H96&lt;&gt;"",N(H96)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G96&lt;&gt;"",H96&lt;&gt;""),(N(G96)+N(H96))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G96&lt;&gt;"",H96&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G96&lt;&gt;"",N(G96)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G96&lt;&gt;"",H96&lt;&gt;""),(N(G96)+N(H96))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G96&lt;&gt;"",N(G96)&lt;='설정'!$E$8),AND(H96&lt;&gt;"",N(H96)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G96&lt;&gt;"",H96&lt;&gt;""),(N(G96)+N(H96))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L96" s="29">
-        <f>IF(OR(G96="",H96=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G96-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H96-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G96="",H96=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G96-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G96+H96)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G96+H96)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G96-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H96-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M96" s="7" t="n"/>
@@ -28818,11 +28815,11 @@
         <v/>
       </c>
       <c r="K97" s="27">
-        <f>IF(I97="","",IF(OR(G97="",H97=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G97&gt;='설정'!$C$6),OR('설정'!$D$6="",G97&lt;'설정'!$D$6),OR('설정'!$E$6="",H97&gt;='설정'!$E$6),OR('설정'!$F$6="",H97&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G97&gt;='설정'!$C$7),OR('설정'!$D$7="",G97&lt;'설정'!$D$7),OR('설정'!$E$7="",H97&gt;='설정'!$E$7),OR('설정'!$F$7="",H97&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G97&gt;='설정'!$C$8),OR('설정'!$D$8="",G97&lt;'설정'!$D$8),OR('설정'!$E$8="",H97&gt;='설정'!$E$8),OR('설정'!$F$8="",H97&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I97="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G97&lt;&gt;"",H97&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G97&lt;&gt;"",N(G97)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G97&lt;&gt;"",H97&lt;&gt;""),(N(G97)+N(H97))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G97&lt;&gt;"",N(G97)&lt;='설정'!$E$6),AND(H97&lt;&gt;"",N(H97)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G97&lt;&gt;"",H97&lt;&gt;""),(N(G97)+N(H97))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G97&lt;&gt;"",H97&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G97&lt;&gt;"",N(G97)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G97&lt;&gt;"",H97&lt;&gt;""),(N(G97)+N(H97))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G97&lt;&gt;"",N(G97)&lt;='설정'!$E$7),AND(H97&lt;&gt;"",N(H97)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G97&lt;&gt;"",H97&lt;&gt;""),(N(G97)+N(H97))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G97&lt;&gt;"",H97&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G97&lt;&gt;"",N(G97)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G97&lt;&gt;"",H97&lt;&gt;""),(N(G97)+N(H97))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G97&lt;&gt;"",N(G97)&lt;='설정'!$E$8),AND(H97&lt;&gt;"",N(H97)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G97&lt;&gt;"",H97&lt;&gt;""),(N(G97)+N(H97))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L97" s="29">
-        <f>IF(OR(G97="",H97=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G97-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H97-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G97="",H97=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G97-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G97+H97)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G97+H97)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G97-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H97-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M97" s="7" t="n"/>
@@ -28881,11 +28878,11 @@
         <v/>
       </c>
       <c r="K98" s="27">
-        <f>IF(I98="","",IF(OR(G98="",H98=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G98&gt;='설정'!$C$6),OR('설정'!$D$6="",G98&lt;'설정'!$D$6),OR('설정'!$E$6="",H98&gt;='설정'!$E$6),OR('설정'!$F$6="",H98&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G98&gt;='설정'!$C$7),OR('설정'!$D$7="",G98&lt;'설정'!$D$7),OR('설정'!$E$7="",H98&gt;='설정'!$E$7),OR('설정'!$F$7="",H98&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G98&gt;='설정'!$C$8),OR('설정'!$D$8="",G98&lt;'설정'!$D$8),OR('설정'!$E$8="",H98&gt;='설정'!$E$8),OR('설정'!$F$8="",H98&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I98="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G98&lt;&gt;"",H98&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G98&lt;&gt;"",N(G98)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G98&lt;&gt;"",H98&lt;&gt;""),(N(G98)+N(H98))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G98&lt;&gt;"",N(G98)&lt;='설정'!$E$6),AND(H98&lt;&gt;"",N(H98)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G98&lt;&gt;"",H98&lt;&gt;""),(N(G98)+N(H98))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G98&lt;&gt;"",H98&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G98&lt;&gt;"",N(G98)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G98&lt;&gt;"",H98&lt;&gt;""),(N(G98)+N(H98))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G98&lt;&gt;"",N(G98)&lt;='설정'!$E$7),AND(H98&lt;&gt;"",N(H98)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G98&lt;&gt;"",H98&lt;&gt;""),(N(G98)+N(H98))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G98&lt;&gt;"",H98&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G98&lt;&gt;"",N(G98)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G98&lt;&gt;"",H98&lt;&gt;""),(N(G98)+N(H98))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G98&lt;&gt;"",N(G98)&lt;='설정'!$E$8),AND(H98&lt;&gt;"",N(H98)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G98&lt;&gt;"",H98&lt;&gt;""),(N(G98)+N(H98))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L98" s="29">
-        <f>IF(OR(G98="",H98=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G98-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H98-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G98="",H98=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G98-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G98+H98)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G98+H98)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G98-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H98-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M98" s="7" t="n"/>
@@ -28944,11 +28941,11 @@
         <v/>
       </c>
       <c r="K99" s="27">
-        <f>IF(I99="","",IF(OR(G99="",H99=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G99&gt;='설정'!$C$6),OR('설정'!$D$6="",G99&lt;'설정'!$D$6),OR('설정'!$E$6="",H99&gt;='설정'!$E$6),OR('설정'!$F$6="",H99&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G99&gt;='설정'!$C$7),OR('설정'!$D$7="",G99&lt;'설정'!$D$7),OR('설정'!$E$7="",H99&gt;='설정'!$E$7),OR('설정'!$F$7="",H99&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G99&gt;='설정'!$C$8),OR('설정'!$D$8="",G99&lt;'설정'!$D$8),OR('설정'!$E$8="",H99&gt;='설정'!$E$8),OR('설정'!$F$8="",H99&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I99="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G99&lt;&gt;"",H99&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G99&lt;&gt;"",N(G99)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G99&lt;&gt;"",H99&lt;&gt;""),(N(G99)+N(H99))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G99&lt;&gt;"",N(G99)&lt;='설정'!$E$6),AND(H99&lt;&gt;"",N(H99)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G99&lt;&gt;"",H99&lt;&gt;""),(N(G99)+N(H99))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G99&lt;&gt;"",H99&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G99&lt;&gt;"",N(G99)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G99&lt;&gt;"",H99&lt;&gt;""),(N(G99)+N(H99))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G99&lt;&gt;"",N(G99)&lt;='설정'!$E$7),AND(H99&lt;&gt;"",N(H99)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G99&lt;&gt;"",H99&lt;&gt;""),(N(G99)+N(H99))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G99&lt;&gt;"",H99&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G99&lt;&gt;"",N(G99)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G99&lt;&gt;"",H99&lt;&gt;""),(N(G99)+N(H99))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G99&lt;&gt;"",N(G99)&lt;='설정'!$E$8),AND(H99&lt;&gt;"",N(H99)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G99&lt;&gt;"",H99&lt;&gt;""),(N(G99)+N(H99))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L99" s="29">
-        <f>IF(OR(G99="",H99=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G99-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H99-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G99="",H99=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G99-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G99+H99)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G99+H99)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G99-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H99-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M99" s="7" t="n"/>
@@ -29007,11 +29004,11 @@
         <v/>
       </c>
       <c r="K100" s="27">
-        <f>IF(I100="","",IF(OR(G100="",H100=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G100&gt;='설정'!$C$6),OR('설정'!$D$6="",G100&lt;'설정'!$D$6),OR('설정'!$E$6="",H100&gt;='설정'!$E$6),OR('설정'!$F$6="",H100&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G100&gt;='설정'!$C$7),OR('설정'!$D$7="",G100&lt;'설정'!$D$7),OR('설정'!$E$7="",H100&gt;='설정'!$E$7),OR('설정'!$F$7="",H100&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G100&gt;='설정'!$C$8),OR('설정'!$D$8="",G100&lt;'설정'!$D$8),OR('설정'!$E$8="",H100&gt;='설정'!$E$8),OR('설정'!$F$8="",H100&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I100="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G100&lt;&gt;"",H100&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G100&lt;&gt;"",N(G100)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G100&lt;&gt;"",H100&lt;&gt;""),(N(G100)+N(H100))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G100&lt;&gt;"",N(G100)&lt;='설정'!$E$6),AND(H100&lt;&gt;"",N(H100)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G100&lt;&gt;"",H100&lt;&gt;""),(N(G100)+N(H100))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G100&lt;&gt;"",H100&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G100&lt;&gt;"",N(G100)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G100&lt;&gt;"",H100&lt;&gt;""),(N(G100)+N(H100))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G100&lt;&gt;"",N(G100)&lt;='설정'!$E$7),AND(H100&lt;&gt;"",N(H100)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G100&lt;&gt;"",H100&lt;&gt;""),(N(G100)+N(H100))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G100&lt;&gt;"",H100&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G100&lt;&gt;"",N(G100)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G100&lt;&gt;"",H100&lt;&gt;""),(N(G100)+N(H100))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G100&lt;&gt;"",N(G100)&lt;='설정'!$E$8),AND(H100&lt;&gt;"",N(H100)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G100&lt;&gt;"",H100&lt;&gt;""),(N(G100)+N(H100))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L100" s="29">
-        <f>IF(OR(G100="",H100=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G100-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H100-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G100="",H100=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G100-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G100+H100)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G100+H100)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G100-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H100-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M100" s="7" t="n"/>
@@ -29070,11 +29067,11 @@
         <v/>
       </c>
       <c r="K101" s="27">
-        <f>IF(I101="","",IF(OR(G101="",H101=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G101&gt;='설정'!$C$6),OR('설정'!$D$6="",G101&lt;'설정'!$D$6),OR('설정'!$E$6="",H101&gt;='설정'!$E$6),OR('설정'!$F$6="",H101&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G101&gt;='설정'!$C$7),OR('설정'!$D$7="",G101&lt;'설정'!$D$7),OR('설정'!$E$7="",H101&gt;='설정'!$E$7),OR('설정'!$F$7="",H101&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G101&gt;='설정'!$C$8),OR('설정'!$D$8="",G101&lt;'설정'!$D$8),OR('설정'!$E$8="",H101&gt;='설정'!$E$8),OR('설정'!$F$8="",H101&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I101="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G101&lt;&gt;"",H101&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G101&lt;&gt;"",N(G101)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G101&lt;&gt;"",H101&lt;&gt;""),(N(G101)+N(H101))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G101&lt;&gt;"",N(G101)&lt;='설정'!$E$6),AND(H101&lt;&gt;"",N(H101)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G101&lt;&gt;"",H101&lt;&gt;""),(N(G101)+N(H101))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G101&lt;&gt;"",H101&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G101&lt;&gt;"",N(G101)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G101&lt;&gt;"",H101&lt;&gt;""),(N(G101)+N(H101))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G101&lt;&gt;"",N(G101)&lt;='설정'!$E$7),AND(H101&lt;&gt;"",N(H101)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G101&lt;&gt;"",H101&lt;&gt;""),(N(G101)+N(H101))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G101&lt;&gt;"",H101&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G101&lt;&gt;"",N(G101)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G101&lt;&gt;"",H101&lt;&gt;""),(N(G101)+N(H101))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G101&lt;&gt;"",N(G101)&lt;='설정'!$E$8),AND(H101&lt;&gt;"",N(H101)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G101&lt;&gt;"",H101&lt;&gt;""),(N(G101)+N(H101))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L101" s="29">
-        <f>IF(OR(G101="",H101=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G101-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H101-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G101="",H101=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G101-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G101+H101)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G101+H101)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G101-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H101-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M101" s="7" t="n"/>
@@ -29133,11 +29130,11 @@
         <v/>
       </c>
       <c r="K102" s="27">
-        <f>IF(I102="","",IF(OR(G102="",H102=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G102&gt;='설정'!$C$6),OR('설정'!$D$6="",G102&lt;'설정'!$D$6),OR('설정'!$E$6="",H102&gt;='설정'!$E$6),OR('설정'!$F$6="",H102&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G102&gt;='설정'!$C$7),OR('설정'!$D$7="",G102&lt;'설정'!$D$7),OR('설정'!$E$7="",H102&gt;='설정'!$E$7),OR('설정'!$F$7="",H102&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G102&gt;='설정'!$C$8),OR('설정'!$D$8="",G102&lt;'설정'!$D$8),OR('설정'!$E$8="",H102&gt;='설정'!$E$8),OR('설정'!$F$8="",H102&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I102="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G102&lt;&gt;"",H102&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G102&lt;&gt;"",N(G102)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G102&lt;&gt;"",H102&lt;&gt;""),(N(G102)+N(H102))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G102&lt;&gt;"",N(G102)&lt;='설정'!$E$6),AND(H102&lt;&gt;"",N(H102)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G102&lt;&gt;"",H102&lt;&gt;""),(N(G102)+N(H102))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G102&lt;&gt;"",H102&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G102&lt;&gt;"",N(G102)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G102&lt;&gt;"",H102&lt;&gt;""),(N(G102)+N(H102))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G102&lt;&gt;"",N(G102)&lt;='설정'!$E$7),AND(H102&lt;&gt;"",N(H102)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G102&lt;&gt;"",H102&lt;&gt;""),(N(G102)+N(H102))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G102&lt;&gt;"",H102&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G102&lt;&gt;"",N(G102)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G102&lt;&gt;"",H102&lt;&gt;""),(N(G102)+N(H102))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G102&lt;&gt;"",N(G102)&lt;='설정'!$E$8),AND(H102&lt;&gt;"",N(H102)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G102&lt;&gt;"",H102&lt;&gt;""),(N(G102)+N(H102))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L102" s="29">
-        <f>IF(OR(G102="",H102=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G102-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H102-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G102="",H102=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G102-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G102+H102)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G102+H102)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G102-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H102-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M102" s="7" t="n"/>
@@ -29196,11 +29193,11 @@
         <v/>
       </c>
       <c r="K103" s="27">
-        <f>IF(I103="","",IF(OR(G103="",H103=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G103&gt;='설정'!$C$6),OR('설정'!$D$6="",G103&lt;'설정'!$D$6),OR('설정'!$E$6="",H103&gt;='설정'!$E$6),OR('설정'!$F$6="",H103&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G103&gt;='설정'!$C$7),OR('설정'!$D$7="",G103&lt;'설정'!$D$7),OR('설정'!$E$7="",H103&gt;='설정'!$E$7),OR('설정'!$F$7="",H103&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G103&gt;='설정'!$C$8),OR('설정'!$D$8="",G103&lt;'설정'!$D$8),OR('설정'!$E$8="",H103&gt;='설정'!$E$8),OR('설정'!$F$8="",H103&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I103="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G103&lt;&gt;"",H103&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G103&lt;&gt;"",N(G103)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G103&lt;&gt;"",H103&lt;&gt;""),(N(G103)+N(H103))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G103&lt;&gt;"",N(G103)&lt;='설정'!$E$6),AND(H103&lt;&gt;"",N(H103)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G103&lt;&gt;"",H103&lt;&gt;""),(N(G103)+N(H103))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G103&lt;&gt;"",H103&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G103&lt;&gt;"",N(G103)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G103&lt;&gt;"",H103&lt;&gt;""),(N(G103)+N(H103))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G103&lt;&gt;"",N(G103)&lt;='설정'!$E$7),AND(H103&lt;&gt;"",N(H103)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G103&lt;&gt;"",H103&lt;&gt;""),(N(G103)+N(H103))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G103&lt;&gt;"",H103&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G103&lt;&gt;"",N(G103)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G103&lt;&gt;"",H103&lt;&gt;""),(N(G103)+N(H103))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G103&lt;&gt;"",N(G103)&lt;='설정'!$E$8),AND(H103&lt;&gt;"",N(H103)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G103&lt;&gt;"",H103&lt;&gt;""),(N(G103)+N(H103))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L103" s="29">
-        <f>IF(OR(G103="",H103=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G103-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H103-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G103="",H103=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G103-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G103+H103)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G103+H103)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G103-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H103-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M103" s="7" t="n"/>
@@ -29259,11 +29256,11 @@
         <v/>
       </c>
       <c r="K104" s="27">
-        <f>IF(I104="","",IF(OR(G104="",H104=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G104&gt;='설정'!$C$6),OR('설정'!$D$6="",G104&lt;'설정'!$D$6),OR('설정'!$E$6="",H104&gt;='설정'!$E$6),OR('설정'!$F$6="",H104&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G104&gt;='설정'!$C$7),OR('설정'!$D$7="",G104&lt;'설정'!$D$7),OR('설정'!$E$7="",H104&gt;='설정'!$E$7),OR('설정'!$F$7="",H104&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G104&gt;='설정'!$C$8),OR('설정'!$D$8="",G104&lt;'설정'!$D$8),OR('설정'!$E$8="",H104&gt;='설정'!$E$8),OR('설정'!$F$8="",H104&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I104="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G104&lt;&gt;"",H104&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G104&lt;&gt;"",N(G104)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G104&lt;&gt;"",H104&lt;&gt;""),(N(G104)+N(H104))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G104&lt;&gt;"",N(G104)&lt;='설정'!$E$6),AND(H104&lt;&gt;"",N(H104)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G104&lt;&gt;"",H104&lt;&gt;""),(N(G104)+N(H104))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G104&lt;&gt;"",H104&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G104&lt;&gt;"",N(G104)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G104&lt;&gt;"",H104&lt;&gt;""),(N(G104)+N(H104))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G104&lt;&gt;"",N(G104)&lt;='설정'!$E$7),AND(H104&lt;&gt;"",N(H104)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G104&lt;&gt;"",H104&lt;&gt;""),(N(G104)+N(H104))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G104&lt;&gt;"",H104&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G104&lt;&gt;"",N(G104)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G104&lt;&gt;"",H104&lt;&gt;""),(N(G104)+N(H104))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G104&lt;&gt;"",N(G104)&lt;='설정'!$E$8),AND(H104&lt;&gt;"",N(H104)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G104&lt;&gt;"",H104&lt;&gt;""),(N(G104)+N(H104))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L104" s="29">
-        <f>IF(OR(G104="",H104=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G104-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H104-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G104="",H104=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G104-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G104+H104)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G104+H104)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G104-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H104-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M104" s="7" t="n"/>
@@ -29322,11 +29319,11 @@
         <v/>
       </c>
       <c r="K105" s="27">
-        <f>IF(I105="","",IF(OR(G105="",H105=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G105&gt;='설정'!$C$6),OR('설정'!$D$6="",G105&lt;'설정'!$D$6),OR('설정'!$E$6="",H105&gt;='설정'!$E$6),OR('설정'!$F$6="",H105&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G105&gt;='설정'!$C$7),OR('설정'!$D$7="",G105&lt;'설정'!$D$7),OR('설정'!$E$7="",H105&gt;='설정'!$E$7),OR('설정'!$F$7="",H105&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G105&gt;='설정'!$C$8),OR('설정'!$D$8="",G105&lt;'설정'!$D$8),OR('설정'!$E$8="",H105&gt;='설정'!$E$8),OR('설정'!$F$8="",H105&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I105="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G105&lt;&gt;"",H105&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G105&lt;&gt;"",N(G105)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G105&lt;&gt;"",H105&lt;&gt;""),(N(G105)+N(H105))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G105&lt;&gt;"",N(G105)&lt;='설정'!$E$6),AND(H105&lt;&gt;"",N(H105)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G105&lt;&gt;"",H105&lt;&gt;""),(N(G105)+N(H105))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G105&lt;&gt;"",H105&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G105&lt;&gt;"",N(G105)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G105&lt;&gt;"",H105&lt;&gt;""),(N(G105)+N(H105))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G105&lt;&gt;"",N(G105)&lt;='설정'!$E$7),AND(H105&lt;&gt;"",N(H105)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G105&lt;&gt;"",H105&lt;&gt;""),(N(G105)+N(H105))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G105&lt;&gt;"",H105&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G105&lt;&gt;"",N(G105)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G105&lt;&gt;"",H105&lt;&gt;""),(N(G105)+N(H105))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G105&lt;&gt;"",N(G105)&lt;='설정'!$E$8),AND(H105&lt;&gt;"",N(H105)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G105&lt;&gt;"",H105&lt;&gt;""),(N(G105)+N(H105))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L105" s="29">
-        <f>IF(OR(G105="",H105=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G105-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H105-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G105="",H105=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G105-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G105+H105)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G105+H105)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G105-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H105-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M105" s="7" t="n"/>
@@ -29385,11 +29382,11 @@
         <v/>
       </c>
       <c r="K106" s="27">
-        <f>IF(I106="","",IF(OR(G106="",H106=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G106&gt;='설정'!$C$6),OR('설정'!$D$6="",G106&lt;'설정'!$D$6),OR('설정'!$E$6="",H106&gt;='설정'!$E$6),OR('설정'!$F$6="",H106&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G106&gt;='설정'!$C$7),OR('설정'!$D$7="",G106&lt;'설정'!$D$7),OR('설정'!$E$7="",H106&gt;='설정'!$E$7),OR('설정'!$F$7="",H106&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G106&gt;='설정'!$C$8),OR('설정'!$D$8="",G106&lt;'설정'!$D$8),OR('설정'!$E$8="",H106&gt;='설정'!$E$8),OR('설정'!$F$8="",H106&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I106="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G106&lt;&gt;"",H106&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G106&lt;&gt;"",N(G106)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G106&lt;&gt;"",H106&lt;&gt;""),(N(G106)+N(H106))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G106&lt;&gt;"",N(G106)&lt;='설정'!$E$6),AND(H106&lt;&gt;"",N(H106)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G106&lt;&gt;"",H106&lt;&gt;""),(N(G106)+N(H106))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G106&lt;&gt;"",H106&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G106&lt;&gt;"",N(G106)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G106&lt;&gt;"",H106&lt;&gt;""),(N(G106)+N(H106))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G106&lt;&gt;"",N(G106)&lt;='설정'!$E$7),AND(H106&lt;&gt;"",N(H106)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G106&lt;&gt;"",H106&lt;&gt;""),(N(G106)+N(H106))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G106&lt;&gt;"",H106&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G106&lt;&gt;"",N(G106)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G106&lt;&gt;"",H106&lt;&gt;""),(N(G106)+N(H106))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G106&lt;&gt;"",N(G106)&lt;='설정'!$E$8),AND(H106&lt;&gt;"",N(H106)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G106&lt;&gt;"",H106&lt;&gt;""),(N(G106)+N(H106))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L106" s="29">
-        <f>IF(OR(G106="",H106=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G106-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H106-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G106="",H106=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G106-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G106+H106)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G106+H106)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G106-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H106-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M106" s="7" t="n"/>
@@ -29448,11 +29445,11 @@
         <v/>
       </c>
       <c r="K107" s="27">
-        <f>IF(I107="","",IF(OR(G107="",H107=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G107&gt;='설정'!$C$6),OR('설정'!$D$6="",G107&lt;'설정'!$D$6),OR('설정'!$E$6="",H107&gt;='설정'!$E$6),OR('설정'!$F$6="",H107&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G107&gt;='설정'!$C$7),OR('설정'!$D$7="",G107&lt;'설정'!$D$7),OR('설정'!$E$7="",H107&gt;='설정'!$E$7),OR('설정'!$F$7="",H107&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G107&gt;='설정'!$C$8),OR('설정'!$D$8="",G107&lt;'설정'!$D$8),OR('설정'!$E$8="",H107&gt;='설정'!$E$8),OR('설정'!$F$8="",H107&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I107="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G107&lt;&gt;"",H107&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G107&lt;&gt;"",N(G107)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G107&lt;&gt;"",H107&lt;&gt;""),(N(G107)+N(H107))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G107&lt;&gt;"",N(G107)&lt;='설정'!$E$6),AND(H107&lt;&gt;"",N(H107)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G107&lt;&gt;"",H107&lt;&gt;""),(N(G107)+N(H107))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G107&lt;&gt;"",H107&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G107&lt;&gt;"",N(G107)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G107&lt;&gt;"",H107&lt;&gt;""),(N(G107)+N(H107))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G107&lt;&gt;"",N(G107)&lt;='설정'!$E$7),AND(H107&lt;&gt;"",N(H107)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G107&lt;&gt;"",H107&lt;&gt;""),(N(G107)+N(H107))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G107&lt;&gt;"",H107&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G107&lt;&gt;"",N(G107)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G107&lt;&gt;"",H107&lt;&gt;""),(N(G107)+N(H107))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G107&lt;&gt;"",N(G107)&lt;='설정'!$E$8),AND(H107&lt;&gt;"",N(H107)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G107&lt;&gt;"",H107&lt;&gt;""),(N(G107)+N(H107))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L107" s="29">
-        <f>IF(OR(G107="",H107=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G107-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H107-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G107="",H107=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G107-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G107+H107)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G107+H107)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G107-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H107-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M107" s="7" t="n"/>
@@ -29511,11 +29508,11 @@
         <v/>
       </c>
       <c r="K108" s="27">
-        <f>IF(I108="","",IF(OR(G108="",H108=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G108&gt;='설정'!$C$6),OR('설정'!$D$6="",G108&lt;'설정'!$D$6),OR('설정'!$E$6="",H108&gt;='설정'!$E$6),OR('설정'!$F$6="",H108&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G108&gt;='설정'!$C$7),OR('설정'!$D$7="",G108&lt;'설정'!$D$7),OR('설정'!$E$7="",H108&gt;='설정'!$E$7),OR('설정'!$F$7="",H108&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G108&gt;='설정'!$C$8),OR('설정'!$D$8="",G108&lt;'설정'!$D$8),OR('설정'!$E$8="",H108&gt;='설정'!$E$8),OR('설정'!$F$8="",H108&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I108="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G108&lt;&gt;"",H108&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G108&lt;&gt;"",N(G108)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G108&lt;&gt;"",H108&lt;&gt;""),(N(G108)+N(H108))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G108&lt;&gt;"",N(G108)&lt;='설정'!$E$6),AND(H108&lt;&gt;"",N(H108)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G108&lt;&gt;"",H108&lt;&gt;""),(N(G108)+N(H108))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G108&lt;&gt;"",H108&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G108&lt;&gt;"",N(G108)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G108&lt;&gt;"",H108&lt;&gt;""),(N(G108)+N(H108))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G108&lt;&gt;"",N(G108)&lt;='설정'!$E$7),AND(H108&lt;&gt;"",N(H108)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G108&lt;&gt;"",H108&lt;&gt;""),(N(G108)+N(H108))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G108&lt;&gt;"",H108&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G108&lt;&gt;"",N(G108)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G108&lt;&gt;"",H108&lt;&gt;""),(N(G108)+N(H108))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G108&lt;&gt;"",N(G108)&lt;='설정'!$E$8),AND(H108&lt;&gt;"",N(H108)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G108&lt;&gt;"",H108&lt;&gt;""),(N(G108)+N(H108))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L108" s="29">
-        <f>IF(OR(G108="",H108=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G108-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H108-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G108="",H108=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G108-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G108+H108)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G108+H108)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G108-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H108-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M108" s="7" t="n"/>
@@ -29574,11 +29571,11 @@
         <v/>
       </c>
       <c r="K109" s="27">
-        <f>IF(I109="","",IF(OR(G109="",H109=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G109&gt;='설정'!$C$6),OR('설정'!$D$6="",G109&lt;'설정'!$D$6),OR('설정'!$E$6="",H109&gt;='설정'!$E$6),OR('설정'!$F$6="",H109&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G109&gt;='설정'!$C$7),OR('설정'!$D$7="",G109&lt;'설정'!$D$7),OR('설정'!$E$7="",H109&gt;='설정'!$E$7),OR('설정'!$F$7="",H109&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G109&gt;='설정'!$C$8),OR('설정'!$D$8="",G109&lt;'설정'!$D$8),OR('설정'!$E$8="",H109&gt;='설정'!$E$8),OR('설정'!$F$8="",H109&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I109="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G109&lt;&gt;"",H109&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G109&lt;&gt;"",N(G109)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G109&lt;&gt;"",H109&lt;&gt;""),(N(G109)+N(H109))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G109&lt;&gt;"",N(G109)&lt;='설정'!$E$6),AND(H109&lt;&gt;"",N(H109)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G109&lt;&gt;"",H109&lt;&gt;""),(N(G109)+N(H109))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G109&lt;&gt;"",H109&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G109&lt;&gt;"",N(G109)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G109&lt;&gt;"",H109&lt;&gt;""),(N(G109)+N(H109))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G109&lt;&gt;"",N(G109)&lt;='설정'!$E$7),AND(H109&lt;&gt;"",N(H109)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G109&lt;&gt;"",H109&lt;&gt;""),(N(G109)+N(H109))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G109&lt;&gt;"",H109&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G109&lt;&gt;"",N(G109)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G109&lt;&gt;"",H109&lt;&gt;""),(N(G109)+N(H109))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G109&lt;&gt;"",N(G109)&lt;='설정'!$E$8),AND(H109&lt;&gt;"",N(H109)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G109&lt;&gt;"",H109&lt;&gt;""),(N(G109)+N(H109))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L109" s="29">
-        <f>IF(OR(G109="",H109=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G109-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H109-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G109="",H109=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G109-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G109+H109)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G109+H109)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G109-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H109-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M109" s="7" t="n"/>
@@ -29637,11 +29634,11 @@
         <v/>
       </c>
       <c r="K110" s="27">
-        <f>IF(I110="","",IF(OR(G110="",H110=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G110&gt;='설정'!$C$6),OR('설정'!$D$6="",G110&lt;'설정'!$D$6),OR('설정'!$E$6="",H110&gt;='설정'!$E$6),OR('설정'!$F$6="",H110&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G110&gt;='설정'!$C$7),OR('설정'!$D$7="",G110&lt;'설정'!$D$7),OR('설정'!$E$7="",H110&gt;='설정'!$E$7),OR('설정'!$F$7="",H110&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G110&gt;='설정'!$C$8),OR('설정'!$D$8="",G110&lt;'설정'!$D$8),OR('설정'!$E$8="",H110&gt;='설정'!$E$8),OR('설정'!$F$8="",H110&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I110="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G110&lt;&gt;"",H110&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G110&lt;&gt;"",N(G110)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G110&lt;&gt;"",H110&lt;&gt;""),(N(G110)+N(H110))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G110&lt;&gt;"",N(G110)&lt;='설정'!$E$6),AND(H110&lt;&gt;"",N(H110)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G110&lt;&gt;"",H110&lt;&gt;""),(N(G110)+N(H110))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G110&lt;&gt;"",H110&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G110&lt;&gt;"",N(G110)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G110&lt;&gt;"",H110&lt;&gt;""),(N(G110)+N(H110))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G110&lt;&gt;"",N(G110)&lt;='설정'!$E$7),AND(H110&lt;&gt;"",N(H110)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G110&lt;&gt;"",H110&lt;&gt;""),(N(G110)+N(H110))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G110&lt;&gt;"",H110&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G110&lt;&gt;"",N(G110)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G110&lt;&gt;"",H110&lt;&gt;""),(N(G110)+N(H110))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G110&lt;&gt;"",N(G110)&lt;='설정'!$E$8),AND(H110&lt;&gt;"",N(H110)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G110&lt;&gt;"",H110&lt;&gt;""),(N(G110)+N(H110))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L110" s="29">
-        <f>IF(OR(G110="",H110=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G110-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H110-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G110="",H110=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G110-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G110+H110)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G110+H110)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G110-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H110-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M110" s="7" t="n"/>
@@ -29700,11 +29697,11 @@
         <v/>
       </c>
       <c r="K111" s="27">
-        <f>IF(I111="","",IF(OR(G111="",H111=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G111&gt;='설정'!$C$6),OR('설정'!$D$6="",G111&lt;'설정'!$D$6),OR('설정'!$E$6="",H111&gt;='설정'!$E$6),OR('설정'!$F$6="",H111&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G111&gt;='설정'!$C$7),OR('설정'!$D$7="",G111&lt;'설정'!$D$7),OR('설정'!$E$7="",H111&gt;='설정'!$E$7),OR('설정'!$F$7="",H111&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G111&gt;='설정'!$C$8),OR('설정'!$D$8="",G111&lt;'설정'!$D$8),OR('설정'!$E$8="",H111&gt;='설정'!$E$8),OR('설정'!$F$8="",H111&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I111="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G111&lt;&gt;"",H111&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G111&lt;&gt;"",N(G111)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G111&lt;&gt;"",H111&lt;&gt;""),(N(G111)+N(H111))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G111&lt;&gt;"",N(G111)&lt;='설정'!$E$6),AND(H111&lt;&gt;"",N(H111)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G111&lt;&gt;"",H111&lt;&gt;""),(N(G111)+N(H111))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G111&lt;&gt;"",H111&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G111&lt;&gt;"",N(G111)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G111&lt;&gt;"",H111&lt;&gt;""),(N(G111)+N(H111))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G111&lt;&gt;"",N(G111)&lt;='설정'!$E$7),AND(H111&lt;&gt;"",N(H111)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G111&lt;&gt;"",H111&lt;&gt;""),(N(G111)+N(H111))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G111&lt;&gt;"",H111&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G111&lt;&gt;"",N(G111)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G111&lt;&gt;"",H111&lt;&gt;""),(N(G111)+N(H111))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G111&lt;&gt;"",N(G111)&lt;='설정'!$E$8),AND(H111&lt;&gt;"",N(H111)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G111&lt;&gt;"",H111&lt;&gt;""),(N(G111)+N(H111))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L111" s="29">
-        <f>IF(OR(G111="",H111=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G111-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H111-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G111="",H111=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G111-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G111+H111)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G111+H111)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G111-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H111-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M111" s="7" t="n"/>
@@ -29763,11 +29760,11 @@
         <v/>
       </c>
       <c r="K112" s="27">
-        <f>IF(I112="","",IF(OR(G112="",H112=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G112&gt;='설정'!$C$6),OR('설정'!$D$6="",G112&lt;'설정'!$D$6),OR('설정'!$E$6="",H112&gt;='설정'!$E$6),OR('설정'!$F$6="",H112&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G112&gt;='설정'!$C$7),OR('설정'!$D$7="",G112&lt;'설정'!$D$7),OR('설정'!$E$7="",H112&gt;='설정'!$E$7),OR('설정'!$F$7="",H112&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G112&gt;='설정'!$C$8),OR('설정'!$D$8="",G112&lt;'설정'!$D$8),OR('설정'!$E$8="",H112&gt;='설정'!$E$8),OR('설정'!$F$8="",H112&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I112="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G112&lt;&gt;"",H112&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G112&lt;&gt;"",N(G112)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G112&lt;&gt;"",H112&lt;&gt;""),(N(G112)+N(H112))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G112&lt;&gt;"",N(G112)&lt;='설정'!$E$6),AND(H112&lt;&gt;"",N(H112)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G112&lt;&gt;"",H112&lt;&gt;""),(N(G112)+N(H112))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G112&lt;&gt;"",H112&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G112&lt;&gt;"",N(G112)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G112&lt;&gt;"",H112&lt;&gt;""),(N(G112)+N(H112))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G112&lt;&gt;"",N(G112)&lt;='설정'!$E$7),AND(H112&lt;&gt;"",N(H112)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G112&lt;&gt;"",H112&lt;&gt;""),(N(G112)+N(H112))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G112&lt;&gt;"",H112&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G112&lt;&gt;"",N(G112)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G112&lt;&gt;"",H112&lt;&gt;""),(N(G112)+N(H112))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G112&lt;&gt;"",N(G112)&lt;='설정'!$E$8),AND(H112&lt;&gt;"",N(H112)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G112&lt;&gt;"",H112&lt;&gt;""),(N(G112)+N(H112))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L112" s="29">
-        <f>IF(OR(G112="",H112=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G112-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H112-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G112="",H112=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G112-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G112+H112)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G112+H112)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G112-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H112-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M112" s="7" t="n"/>
@@ -29826,11 +29823,11 @@
         <v/>
       </c>
       <c r="K113" s="27">
-        <f>IF(I113="","",IF(OR(G113="",H113=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G113&gt;='설정'!$C$6),OR('설정'!$D$6="",G113&lt;'설정'!$D$6),OR('설정'!$E$6="",H113&gt;='설정'!$E$6),OR('설정'!$F$6="",H113&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G113&gt;='설정'!$C$7),OR('설정'!$D$7="",G113&lt;'설정'!$D$7),OR('설정'!$E$7="",H113&gt;='설정'!$E$7),OR('설정'!$F$7="",H113&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G113&gt;='설정'!$C$8),OR('설정'!$D$8="",G113&lt;'설정'!$D$8),OR('설정'!$E$8="",H113&gt;='설정'!$E$8),OR('설정'!$F$8="",H113&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I113="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G113&lt;&gt;"",H113&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G113&lt;&gt;"",N(G113)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G113&lt;&gt;"",H113&lt;&gt;""),(N(G113)+N(H113))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G113&lt;&gt;"",N(G113)&lt;='설정'!$E$6),AND(H113&lt;&gt;"",N(H113)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G113&lt;&gt;"",H113&lt;&gt;""),(N(G113)+N(H113))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G113&lt;&gt;"",H113&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G113&lt;&gt;"",N(G113)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G113&lt;&gt;"",H113&lt;&gt;""),(N(G113)+N(H113))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G113&lt;&gt;"",N(G113)&lt;='설정'!$E$7),AND(H113&lt;&gt;"",N(H113)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G113&lt;&gt;"",H113&lt;&gt;""),(N(G113)+N(H113))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G113&lt;&gt;"",H113&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G113&lt;&gt;"",N(G113)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G113&lt;&gt;"",H113&lt;&gt;""),(N(G113)+N(H113))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G113&lt;&gt;"",N(G113)&lt;='설정'!$E$8),AND(H113&lt;&gt;"",N(H113)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G113&lt;&gt;"",H113&lt;&gt;""),(N(G113)+N(H113))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L113" s="29">
-        <f>IF(OR(G113="",H113=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G113-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H113-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G113="",H113=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G113-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G113+H113)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G113+H113)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G113-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H113-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M113" s="7" t="n"/>
@@ -29889,11 +29886,11 @@
         <v/>
       </c>
       <c r="K114" s="27">
-        <f>IF(I114="","",IF(OR(G114="",H114=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G114&gt;='설정'!$C$6),OR('설정'!$D$6="",G114&lt;'설정'!$D$6),OR('설정'!$E$6="",H114&gt;='설정'!$E$6),OR('설정'!$F$6="",H114&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G114&gt;='설정'!$C$7),OR('설정'!$D$7="",G114&lt;'설정'!$D$7),OR('설정'!$E$7="",H114&gt;='설정'!$E$7),OR('설정'!$F$7="",H114&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G114&gt;='설정'!$C$8),OR('설정'!$D$8="",G114&lt;'설정'!$D$8),OR('설정'!$E$8="",H114&gt;='설정'!$E$8),OR('설정'!$F$8="",H114&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I114="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G114&lt;&gt;"",H114&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G114&lt;&gt;"",N(G114)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G114&lt;&gt;"",H114&lt;&gt;""),(N(G114)+N(H114))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G114&lt;&gt;"",N(G114)&lt;='설정'!$E$6),AND(H114&lt;&gt;"",N(H114)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G114&lt;&gt;"",H114&lt;&gt;""),(N(G114)+N(H114))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G114&lt;&gt;"",H114&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G114&lt;&gt;"",N(G114)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G114&lt;&gt;"",H114&lt;&gt;""),(N(G114)+N(H114))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G114&lt;&gt;"",N(G114)&lt;='설정'!$E$7),AND(H114&lt;&gt;"",N(H114)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G114&lt;&gt;"",H114&lt;&gt;""),(N(G114)+N(H114))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G114&lt;&gt;"",H114&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G114&lt;&gt;"",N(G114)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G114&lt;&gt;"",H114&lt;&gt;""),(N(G114)+N(H114))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G114&lt;&gt;"",N(G114)&lt;='설정'!$E$8),AND(H114&lt;&gt;"",N(H114)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G114&lt;&gt;"",H114&lt;&gt;""),(N(G114)+N(H114))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L114" s="29">
-        <f>IF(OR(G114="",H114=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G114-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H114-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G114="",H114=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G114-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G114+H114)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G114+H114)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G114-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H114-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M114" s="7" t="n"/>
@@ -29952,11 +29949,11 @@
         <v/>
       </c>
       <c r="K115" s="27">
-        <f>IF(I115="","",IF(OR(G115="",H115=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G115&gt;='설정'!$C$6),OR('설정'!$D$6="",G115&lt;'설정'!$D$6),OR('설정'!$E$6="",H115&gt;='설정'!$E$6),OR('설정'!$F$6="",H115&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G115&gt;='설정'!$C$7),OR('설정'!$D$7="",G115&lt;'설정'!$D$7),OR('설정'!$E$7="",H115&gt;='설정'!$E$7),OR('설정'!$F$7="",H115&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G115&gt;='설정'!$C$8),OR('설정'!$D$8="",G115&lt;'설정'!$D$8),OR('설정'!$E$8="",H115&gt;='설정'!$E$8),OR('설정'!$F$8="",H115&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I115="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G115&lt;&gt;"",H115&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G115&lt;&gt;"",N(G115)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G115&lt;&gt;"",H115&lt;&gt;""),(N(G115)+N(H115))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G115&lt;&gt;"",N(G115)&lt;='설정'!$E$6),AND(H115&lt;&gt;"",N(H115)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G115&lt;&gt;"",H115&lt;&gt;""),(N(G115)+N(H115))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G115&lt;&gt;"",H115&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G115&lt;&gt;"",N(G115)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G115&lt;&gt;"",H115&lt;&gt;""),(N(G115)+N(H115))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G115&lt;&gt;"",N(G115)&lt;='설정'!$E$7),AND(H115&lt;&gt;"",N(H115)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G115&lt;&gt;"",H115&lt;&gt;""),(N(G115)+N(H115))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G115&lt;&gt;"",H115&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G115&lt;&gt;"",N(G115)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G115&lt;&gt;"",H115&lt;&gt;""),(N(G115)+N(H115))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G115&lt;&gt;"",N(G115)&lt;='설정'!$E$8),AND(H115&lt;&gt;"",N(H115)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G115&lt;&gt;"",H115&lt;&gt;""),(N(G115)+N(H115))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L115" s="29">
-        <f>IF(OR(G115="",H115=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G115-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H115-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G115="",H115=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G115-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G115+H115)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G115+H115)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G115-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H115-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M115" s="7" t="n"/>
@@ -30015,11 +30012,11 @@
         <v/>
       </c>
       <c r="K116" s="27">
-        <f>IF(I116="","",IF(OR(G116="",H116=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G116&gt;='설정'!$C$6),OR('설정'!$D$6="",G116&lt;'설정'!$D$6),OR('설정'!$E$6="",H116&gt;='설정'!$E$6),OR('설정'!$F$6="",H116&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G116&gt;='설정'!$C$7),OR('설정'!$D$7="",G116&lt;'설정'!$D$7),OR('설정'!$E$7="",H116&gt;='설정'!$E$7),OR('설정'!$F$7="",H116&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G116&gt;='설정'!$C$8),OR('설정'!$D$8="",G116&lt;'설정'!$D$8),OR('설정'!$E$8="",H116&gt;='설정'!$E$8),OR('설정'!$F$8="",H116&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I116="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G116&lt;&gt;"",H116&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G116&lt;&gt;"",N(G116)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G116&lt;&gt;"",H116&lt;&gt;""),(N(G116)+N(H116))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G116&lt;&gt;"",N(G116)&lt;='설정'!$E$6),AND(H116&lt;&gt;"",N(H116)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G116&lt;&gt;"",H116&lt;&gt;""),(N(G116)+N(H116))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G116&lt;&gt;"",H116&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G116&lt;&gt;"",N(G116)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G116&lt;&gt;"",H116&lt;&gt;""),(N(G116)+N(H116))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G116&lt;&gt;"",N(G116)&lt;='설정'!$E$7),AND(H116&lt;&gt;"",N(H116)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G116&lt;&gt;"",H116&lt;&gt;""),(N(G116)+N(H116))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G116&lt;&gt;"",H116&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G116&lt;&gt;"",N(G116)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G116&lt;&gt;"",H116&lt;&gt;""),(N(G116)+N(H116))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G116&lt;&gt;"",N(G116)&lt;='설정'!$E$8),AND(H116&lt;&gt;"",N(H116)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G116&lt;&gt;"",H116&lt;&gt;""),(N(G116)+N(H116))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L116" s="29">
-        <f>IF(OR(G116="",H116=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G116-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H116-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G116="",H116=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G116-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G116+H116)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G116+H116)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G116-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H116-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M116" s="7" t="n"/>
@@ -30078,11 +30075,11 @@
         <v/>
       </c>
       <c r="K117" s="27">
-        <f>IF(I117="","",IF(OR(G117="",H117=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G117&gt;='설정'!$C$6),OR('설정'!$D$6="",G117&lt;'설정'!$D$6),OR('설정'!$E$6="",H117&gt;='설정'!$E$6),OR('설정'!$F$6="",H117&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G117&gt;='설정'!$C$7),OR('설정'!$D$7="",G117&lt;'설정'!$D$7),OR('설정'!$E$7="",H117&gt;='설정'!$E$7),OR('설정'!$F$7="",H117&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G117&gt;='설정'!$C$8),OR('설정'!$D$8="",G117&lt;'설정'!$D$8),OR('설정'!$E$8="",H117&gt;='설정'!$E$8),OR('설정'!$F$8="",H117&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I117="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G117&lt;&gt;"",H117&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G117&lt;&gt;"",N(G117)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G117&lt;&gt;"",H117&lt;&gt;""),(N(G117)+N(H117))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G117&lt;&gt;"",N(G117)&lt;='설정'!$E$6),AND(H117&lt;&gt;"",N(H117)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G117&lt;&gt;"",H117&lt;&gt;""),(N(G117)+N(H117))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G117&lt;&gt;"",H117&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G117&lt;&gt;"",N(G117)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G117&lt;&gt;"",H117&lt;&gt;""),(N(G117)+N(H117))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G117&lt;&gt;"",N(G117)&lt;='설정'!$E$7),AND(H117&lt;&gt;"",N(H117)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G117&lt;&gt;"",H117&lt;&gt;""),(N(G117)+N(H117))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G117&lt;&gt;"",H117&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G117&lt;&gt;"",N(G117)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G117&lt;&gt;"",H117&lt;&gt;""),(N(G117)+N(H117))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G117&lt;&gt;"",N(G117)&lt;='설정'!$E$8),AND(H117&lt;&gt;"",N(H117)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G117&lt;&gt;"",H117&lt;&gt;""),(N(G117)+N(H117))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L117" s="29">
-        <f>IF(OR(G117="",H117=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G117-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H117-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G117="",H117=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G117-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G117+H117)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G117+H117)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G117-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H117-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M117" s="7" t="n"/>
@@ -30141,11 +30138,11 @@
         <v/>
       </c>
       <c r="K118" s="27">
-        <f>IF(I118="","",IF(OR(G118="",H118=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G118&gt;='설정'!$C$6),OR('설정'!$D$6="",G118&lt;'설정'!$D$6),OR('설정'!$E$6="",H118&gt;='설정'!$E$6),OR('설정'!$F$6="",H118&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G118&gt;='설정'!$C$7),OR('설정'!$D$7="",G118&lt;'설정'!$D$7),OR('설정'!$E$7="",H118&gt;='설정'!$E$7),OR('설정'!$F$7="",H118&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G118&gt;='설정'!$C$8),OR('설정'!$D$8="",G118&lt;'설정'!$D$8),OR('설정'!$E$8="",H118&gt;='설정'!$E$8),OR('설정'!$F$8="",H118&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I118="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G118&lt;&gt;"",H118&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G118&lt;&gt;"",N(G118)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G118&lt;&gt;"",H118&lt;&gt;""),(N(G118)+N(H118))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G118&lt;&gt;"",N(G118)&lt;='설정'!$E$6),AND(H118&lt;&gt;"",N(H118)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G118&lt;&gt;"",H118&lt;&gt;""),(N(G118)+N(H118))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G118&lt;&gt;"",H118&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G118&lt;&gt;"",N(G118)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G118&lt;&gt;"",H118&lt;&gt;""),(N(G118)+N(H118))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G118&lt;&gt;"",N(G118)&lt;='설정'!$E$7),AND(H118&lt;&gt;"",N(H118)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G118&lt;&gt;"",H118&lt;&gt;""),(N(G118)+N(H118))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G118&lt;&gt;"",H118&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G118&lt;&gt;"",N(G118)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G118&lt;&gt;"",H118&lt;&gt;""),(N(G118)+N(H118))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G118&lt;&gt;"",N(G118)&lt;='설정'!$E$8),AND(H118&lt;&gt;"",N(H118)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G118&lt;&gt;"",H118&lt;&gt;""),(N(G118)+N(H118))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L118" s="29">
-        <f>IF(OR(G118="",H118=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G118-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H118-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G118="",H118=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G118-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G118+H118)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G118+H118)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G118-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H118-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M118" s="7" t="n"/>
@@ -30204,11 +30201,11 @@
         <v/>
       </c>
       <c r="K119" s="27">
-        <f>IF(I119="","",IF(OR(G119="",H119=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G119&gt;='설정'!$C$6),OR('설정'!$D$6="",G119&lt;'설정'!$D$6),OR('설정'!$E$6="",H119&gt;='설정'!$E$6),OR('설정'!$F$6="",H119&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G119&gt;='설정'!$C$7),OR('설정'!$D$7="",G119&lt;'설정'!$D$7),OR('설정'!$E$7="",H119&gt;='설정'!$E$7),OR('설정'!$F$7="",H119&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G119&gt;='설정'!$C$8),OR('설정'!$D$8="",G119&lt;'설정'!$D$8),OR('설정'!$E$8="",H119&gt;='설정'!$E$8),OR('설정'!$F$8="",H119&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I119="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G119&lt;&gt;"",H119&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G119&lt;&gt;"",N(G119)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G119&lt;&gt;"",H119&lt;&gt;""),(N(G119)+N(H119))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G119&lt;&gt;"",N(G119)&lt;='설정'!$E$6),AND(H119&lt;&gt;"",N(H119)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G119&lt;&gt;"",H119&lt;&gt;""),(N(G119)+N(H119))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G119&lt;&gt;"",H119&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G119&lt;&gt;"",N(G119)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G119&lt;&gt;"",H119&lt;&gt;""),(N(G119)+N(H119))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G119&lt;&gt;"",N(G119)&lt;='설정'!$E$7),AND(H119&lt;&gt;"",N(H119)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G119&lt;&gt;"",H119&lt;&gt;""),(N(G119)+N(H119))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G119&lt;&gt;"",H119&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G119&lt;&gt;"",N(G119)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G119&lt;&gt;"",H119&lt;&gt;""),(N(G119)+N(H119))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G119&lt;&gt;"",N(G119)&lt;='설정'!$E$8),AND(H119&lt;&gt;"",N(H119)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G119&lt;&gt;"",H119&lt;&gt;""),(N(G119)+N(H119))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L119" s="29">
-        <f>IF(OR(G119="",H119=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G119-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H119-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G119="",H119=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G119-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G119+H119)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G119+H119)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G119-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H119-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M119" s="7" t="n"/>
@@ -30267,11 +30264,11 @@
         <v/>
       </c>
       <c r="K120" s="27">
-        <f>IF(I120="","",IF(OR(G120="",H120=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G120&gt;='설정'!$C$6),OR('설정'!$D$6="",G120&lt;'설정'!$D$6),OR('설정'!$E$6="",H120&gt;='설정'!$E$6),OR('설정'!$F$6="",H120&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G120&gt;='설정'!$C$7),OR('설정'!$D$7="",G120&lt;'설정'!$D$7),OR('설정'!$E$7="",H120&gt;='설정'!$E$7),OR('설정'!$F$7="",H120&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G120&gt;='설정'!$C$8),OR('설정'!$D$8="",G120&lt;'설정'!$D$8),OR('설정'!$E$8="",H120&gt;='설정'!$E$8),OR('설정'!$F$8="",H120&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I120="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G120&lt;&gt;"",H120&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G120&lt;&gt;"",N(G120)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G120&lt;&gt;"",H120&lt;&gt;""),(N(G120)+N(H120))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G120&lt;&gt;"",N(G120)&lt;='설정'!$E$6),AND(H120&lt;&gt;"",N(H120)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G120&lt;&gt;"",H120&lt;&gt;""),(N(G120)+N(H120))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G120&lt;&gt;"",H120&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G120&lt;&gt;"",N(G120)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G120&lt;&gt;"",H120&lt;&gt;""),(N(G120)+N(H120))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G120&lt;&gt;"",N(G120)&lt;='설정'!$E$7),AND(H120&lt;&gt;"",N(H120)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G120&lt;&gt;"",H120&lt;&gt;""),(N(G120)+N(H120))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G120&lt;&gt;"",H120&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G120&lt;&gt;"",N(G120)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G120&lt;&gt;"",H120&lt;&gt;""),(N(G120)+N(H120))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G120&lt;&gt;"",N(G120)&lt;='설정'!$E$8),AND(H120&lt;&gt;"",N(H120)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G120&lt;&gt;"",H120&lt;&gt;""),(N(G120)+N(H120))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L120" s="29">
-        <f>IF(OR(G120="",H120=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G120-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H120-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G120="",H120=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G120-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G120+H120)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G120+H120)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G120-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H120-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M120" s="7" t="n"/>
@@ -30330,11 +30327,11 @@
         <v/>
       </c>
       <c r="K121" s="27">
-        <f>IF(I121="","",IF(OR(G121="",H121=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G121&gt;='설정'!$C$6),OR('설정'!$D$6="",G121&lt;'설정'!$D$6),OR('설정'!$E$6="",H121&gt;='설정'!$E$6),OR('설정'!$F$6="",H121&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G121&gt;='설정'!$C$7),OR('설정'!$D$7="",G121&lt;'설정'!$D$7),OR('설정'!$E$7="",H121&gt;='설정'!$E$7),OR('설정'!$F$7="",H121&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G121&gt;='설정'!$C$8),OR('설정'!$D$8="",G121&lt;'설정'!$D$8),OR('설정'!$E$8="",H121&gt;='설정'!$E$8),OR('설정'!$F$8="",H121&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I121="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G121&lt;&gt;"",H121&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G121&lt;&gt;"",N(G121)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G121&lt;&gt;"",H121&lt;&gt;""),(N(G121)+N(H121))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G121&lt;&gt;"",N(G121)&lt;='설정'!$E$6),AND(H121&lt;&gt;"",N(H121)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G121&lt;&gt;"",H121&lt;&gt;""),(N(G121)+N(H121))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G121&lt;&gt;"",H121&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G121&lt;&gt;"",N(G121)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G121&lt;&gt;"",H121&lt;&gt;""),(N(G121)+N(H121))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G121&lt;&gt;"",N(G121)&lt;='설정'!$E$7),AND(H121&lt;&gt;"",N(H121)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G121&lt;&gt;"",H121&lt;&gt;""),(N(G121)+N(H121))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G121&lt;&gt;"",H121&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G121&lt;&gt;"",N(G121)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G121&lt;&gt;"",H121&lt;&gt;""),(N(G121)+N(H121))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G121&lt;&gt;"",N(G121)&lt;='설정'!$E$8),AND(H121&lt;&gt;"",N(H121)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G121&lt;&gt;"",H121&lt;&gt;""),(N(G121)+N(H121))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L121" s="29">
-        <f>IF(OR(G121="",H121=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G121-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H121-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G121="",H121=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G121-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G121+H121)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G121+H121)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G121-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H121-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M121" s="7" t="n"/>
@@ -30393,11 +30390,11 @@
         <v/>
       </c>
       <c r="K122" s="27">
-        <f>IF(I122="","",IF(OR(G122="",H122=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G122&gt;='설정'!$C$6),OR('설정'!$D$6="",G122&lt;'설정'!$D$6),OR('설정'!$E$6="",H122&gt;='설정'!$E$6),OR('설정'!$F$6="",H122&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G122&gt;='설정'!$C$7),OR('설정'!$D$7="",G122&lt;'설정'!$D$7),OR('설정'!$E$7="",H122&gt;='설정'!$E$7),OR('설정'!$F$7="",H122&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G122&gt;='설정'!$C$8),OR('설정'!$D$8="",G122&lt;'설정'!$D$8),OR('설정'!$E$8="",H122&gt;='설정'!$E$8),OR('설정'!$F$8="",H122&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I122="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G122&lt;&gt;"",H122&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G122&lt;&gt;"",N(G122)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G122&lt;&gt;"",H122&lt;&gt;""),(N(G122)+N(H122))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G122&lt;&gt;"",N(G122)&lt;='설정'!$E$6),AND(H122&lt;&gt;"",N(H122)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G122&lt;&gt;"",H122&lt;&gt;""),(N(G122)+N(H122))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G122&lt;&gt;"",H122&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G122&lt;&gt;"",N(G122)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G122&lt;&gt;"",H122&lt;&gt;""),(N(G122)+N(H122))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G122&lt;&gt;"",N(G122)&lt;='설정'!$E$7),AND(H122&lt;&gt;"",N(H122)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G122&lt;&gt;"",H122&lt;&gt;""),(N(G122)+N(H122))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G122&lt;&gt;"",H122&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G122&lt;&gt;"",N(G122)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G122&lt;&gt;"",H122&lt;&gt;""),(N(G122)+N(H122))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G122&lt;&gt;"",N(G122)&lt;='설정'!$E$8),AND(H122&lt;&gt;"",N(H122)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G122&lt;&gt;"",H122&lt;&gt;""),(N(G122)+N(H122))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L122" s="29">
-        <f>IF(OR(G122="",H122=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G122-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H122-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G122="",H122=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G122-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G122+H122)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G122+H122)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G122-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H122-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M122" s="7" t="n"/>
@@ -30456,11 +30453,11 @@
         <v/>
       </c>
       <c r="K123" s="27">
-        <f>IF(I123="","",IF(OR(G123="",H123=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G123&gt;='설정'!$C$6),OR('설정'!$D$6="",G123&lt;'설정'!$D$6),OR('설정'!$E$6="",H123&gt;='설정'!$E$6),OR('설정'!$F$6="",H123&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G123&gt;='설정'!$C$7),OR('설정'!$D$7="",G123&lt;'설정'!$D$7),OR('설정'!$E$7="",H123&gt;='설정'!$E$7),OR('설정'!$F$7="",H123&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G123&gt;='설정'!$C$8),OR('설정'!$D$8="",G123&lt;'설정'!$D$8),OR('설정'!$E$8="",H123&gt;='설정'!$E$8),OR('설정'!$F$8="",H123&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I123="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G123&lt;&gt;"",H123&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G123&lt;&gt;"",N(G123)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G123&lt;&gt;"",H123&lt;&gt;""),(N(G123)+N(H123))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G123&lt;&gt;"",N(G123)&lt;='설정'!$E$6),AND(H123&lt;&gt;"",N(H123)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G123&lt;&gt;"",H123&lt;&gt;""),(N(G123)+N(H123))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G123&lt;&gt;"",H123&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G123&lt;&gt;"",N(G123)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G123&lt;&gt;"",H123&lt;&gt;""),(N(G123)+N(H123))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G123&lt;&gt;"",N(G123)&lt;='설정'!$E$7),AND(H123&lt;&gt;"",N(H123)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G123&lt;&gt;"",H123&lt;&gt;""),(N(G123)+N(H123))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G123&lt;&gt;"",H123&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G123&lt;&gt;"",N(G123)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G123&lt;&gt;"",H123&lt;&gt;""),(N(G123)+N(H123))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G123&lt;&gt;"",N(G123)&lt;='설정'!$E$8),AND(H123&lt;&gt;"",N(H123)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G123&lt;&gt;"",H123&lt;&gt;""),(N(G123)+N(H123))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L123" s="29">
-        <f>IF(OR(G123="",H123=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G123-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H123-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G123="",H123=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G123-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G123+H123)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G123+H123)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G123-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H123-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M123" s="7" t="n"/>
@@ -30519,11 +30516,11 @@
         <v/>
       </c>
       <c r="K124" s="27">
-        <f>IF(I124="","",IF(OR(G124="",H124=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G124&gt;='설정'!$C$6),OR('설정'!$D$6="",G124&lt;'설정'!$D$6),OR('설정'!$E$6="",H124&gt;='설정'!$E$6),OR('설정'!$F$6="",H124&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G124&gt;='설정'!$C$7),OR('설정'!$D$7="",G124&lt;'설정'!$D$7),OR('설정'!$E$7="",H124&gt;='설정'!$E$7),OR('설정'!$F$7="",H124&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G124&gt;='설정'!$C$8),OR('설정'!$D$8="",G124&lt;'설정'!$D$8),OR('설정'!$E$8="",H124&gt;='설정'!$E$8),OR('설정'!$F$8="",H124&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I124="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G124&lt;&gt;"",H124&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G124&lt;&gt;"",N(G124)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G124&lt;&gt;"",H124&lt;&gt;""),(N(G124)+N(H124))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G124&lt;&gt;"",N(G124)&lt;='설정'!$E$6),AND(H124&lt;&gt;"",N(H124)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G124&lt;&gt;"",H124&lt;&gt;""),(N(G124)+N(H124))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G124&lt;&gt;"",H124&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G124&lt;&gt;"",N(G124)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G124&lt;&gt;"",H124&lt;&gt;""),(N(G124)+N(H124))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G124&lt;&gt;"",N(G124)&lt;='설정'!$E$7),AND(H124&lt;&gt;"",N(H124)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G124&lt;&gt;"",H124&lt;&gt;""),(N(G124)+N(H124))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G124&lt;&gt;"",H124&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G124&lt;&gt;"",N(G124)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G124&lt;&gt;"",H124&lt;&gt;""),(N(G124)+N(H124))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G124&lt;&gt;"",N(G124)&lt;='설정'!$E$8),AND(H124&lt;&gt;"",N(H124)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G124&lt;&gt;"",H124&lt;&gt;""),(N(G124)+N(H124))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L124" s="29">
-        <f>IF(OR(G124="",H124=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G124-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H124-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G124="",H124=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G124-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G124+H124)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G124+H124)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G124-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H124-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M124" s="7" t="n"/>
@@ -30582,11 +30579,11 @@
         <v/>
       </c>
       <c r="K125" s="27">
-        <f>IF(I125="","",IF(OR(G125="",H125=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G125&gt;='설정'!$C$6),OR('설정'!$D$6="",G125&lt;'설정'!$D$6),OR('설정'!$E$6="",H125&gt;='설정'!$E$6),OR('설정'!$F$6="",H125&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G125&gt;='설정'!$C$7),OR('설정'!$D$7="",G125&lt;'설정'!$D$7),OR('설정'!$E$7="",H125&gt;='설정'!$E$7),OR('설정'!$F$7="",H125&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G125&gt;='설정'!$C$8),OR('설정'!$D$8="",G125&lt;'설정'!$D$8),OR('설정'!$E$8="",H125&gt;='설정'!$E$8),OR('설정'!$F$8="",H125&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I125="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G125&lt;&gt;"",H125&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G125&lt;&gt;"",N(G125)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G125&lt;&gt;"",H125&lt;&gt;""),(N(G125)+N(H125))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G125&lt;&gt;"",N(G125)&lt;='설정'!$E$6),AND(H125&lt;&gt;"",N(H125)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G125&lt;&gt;"",H125&lt;&gt;""),(N(G125)+N(H125))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G125&lt;&gt;"",H125&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G125&lt;&gt;"",N(G125)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G125&lt;&gt;"",H125&lt;&gt;""),(N(G125)+N(H125))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G125&lt;&gt;"",N(G125)&lt;='설정'!$E$7),AND(H125&lt;&gt;"",N(H125)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G125&lt;&gt;"",H125&lt;&gt;""),(N(G125)+N(H125))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G125&lt;&gt;"",H125&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G125&lt;&gt;"",N(G125)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G125&lt;&gt;"",H125&lt;&gt;""),(N(G125)+N(H125))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G125&lt;&gt;"",N(G125)&lt;='설정'!$E$8),AND(H125&lt;&gt;"",N(H125)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G125&lt;&gt;"",H125&lt;&gt;""),(N(G125)+N(H125))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L125" s="29">
-        <f>IF(OR(G125="",H125=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G125-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H125-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G125="",H125=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G125-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G125+H125)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G125+H125)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G125-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H125-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M125" s="7" t="n"/>
@@ -30645,11 +30642,11 @@
         <v/>
       </c>
       <c r="K126" s="27">
-        <f>IF(I126="","",IF(OR(G126="",H126=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G126&gt;='설정'!$C$6),OR('설정'!$D$6="",G126&lt;'설정'!$D$6),OR('설정'!$E$6="",H126&gt;='설정'!$E$6),OR('설정'!$F$6="",H126&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G126&gt;='설정'!$C$7),OR('설정'!$D$7="",G126&lt;'설정'!$D$7),OR('설정'!$E$7="",H126&gt;='설정'!$E$7),OR('설정'!$F$7="",H126&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G126&gt;='설정'!$C$8),OR('설정'!$D$8="",G126&lt;'설정'!$D$8),OR('설정'!$E$8="",H126&gt;='설정'!$E$8),OR('설정'!$F$8="",H126&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I126="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G126&lt;&gt;"",H126&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G126&lt;&gt;"",N(G126)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G126&lt;&gt;"",H126&lt;&gt;""),(N(G126)+N(H126))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G126&lt;&gt;"",N(G126)&lt;='설정'!$E$6),AND(H126&lt;&gt;"",N(H126)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G126&lt;&gt;"",H126&lt;&gt;""),(N(G126)+N(H126))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G126&lt;&gt;"",H126&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G126&lt;&gt;"",N(G126)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G126&lt;&gt;"",H126&lt;&gt;""),(N(G126)+N(H126))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G126&lt;&gt;"",N(G126)&lt;='설정'!$E$7),AND(H126&lt;&gt;"",N(H126)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G126&lt;&gt;"",H126&lt;&gt;""),(N(G126)+N(H126))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G126&lt;&gt;"",H126&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G126&lt;&gt;"",N(G126)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G126&lt;&gt;"",H126&lt;&gt;""),(N(G126)+N(H126))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G126&lt;&gt;"",N(G126)&lt;='설정'!$E$8),AND(H126&lt;&gt;"",N(H126)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G126&lt;&gt;"",H126&lt;&gt;""),(N(G126)+N(H126))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L126" s="29">
-        <f>IF(OR(G126="",H126=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G126-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H126-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G126="",H126=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G126-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G126+H126)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G126+H126)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G126-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H126-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M126" s="7" t="n"/>
@@ -30708,11 +30705,11 @@
         <v/>
       </c>
       <c r="K127" s="27">
-        <f>IF(I127="","",IF(OR(G127="",H127=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G127&gt;='설정'!$C$6),OR('설정'!$D$6="",G127&lt;'설정'!$D$6),OR('설정'!$E$6="",H127&gt;='설정'!$E$6),OR('설정'!$F$6="",H127&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G127&gt;='설정'!$C$7),OR('설정'!$D$7="",G127&lt;'설정'!$D$7),OR('설정'!$E$7="",H127&gt;='설정'!$E$7),OR('설정'!$F$7="",H127&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G127&gt;='설정'!$C$8),OR('설정'!$D$8="",G127&lt;'설정'!$D$8),OR('설정'!$E$8="",H127&gt;='설정'!$E$8),OR('설정'!$F$8="",H127&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I127="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G127&lt;&gt;"",H127&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G127&lt;&gt;"",N(G127)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G127&lt;&gt;"",H127&lt;&gt;""),(N(G127)+N(H127))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G127&lt;&gt;"",N(G127)&lt;='설정'!$E$6),AND(H127&lt;&gt;"",N(H127)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G127&lt;&gt;"",H127&lt;&gt;""),(N(G127)+N(H127))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G127&lt;&gt;"",H127&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G127&lt;&gt;"",N(G127)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G127&lt;&gt;"",H127&lt;&gt;""),(N(G127)+N(H127))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G127&lt;&gt;"",N(G127)&lt;='설정'!$E$7),AND(H127&lt;&gt;"",N(H127)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G127&lt;&gt;"",H127&lt;&gt;""),(N(G127)+N(H127))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G127&lt;&gt;"",H127&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G127&lt;&gt;"",N(G127)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G127&lt;&gt;"",H127&lt;&gt;""),(N(G127)+N(H127))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G127&lt;&gt;"",N(G127)&lt;='설정'!$E$8),AND(H127&lt;&gt;"",N(H127)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G127&lt;&gt;"",H127&lt;&gt;""),(N(G127)+N(H127))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L127" s="29">
-        <f>IF(OR(G127="",H127=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G127-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H127-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G127="",H127=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G127-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G127+H127)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G127+H127)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G127-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H127-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M127" s="7" t="n"/>
@@ -30771,11 +30768,11 @@
         <v/>
       </c>
       <c r="K128" s="27">
-        <f>IF(I128="","",IF(OR(G128="",H128=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G128&gt;='설정'!$C$6),OR('설정'!$D$6="",G128&lt;'설정'!$D$6),OR('설정'!$E$6="",H128&gt;='설정'!$E$6),OR('설정'!$F$6="",H128&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G128&gt;='설정'!$C$7),OR('설정'!$D$7="",G128&lt;'설정'!$D$7),OR('설정'!$E$7="",H128&gt;='설정'!$E$7),OR('설정'!$F$7="",H128&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G128&gt;='설정'!$C$8),OR('설정'!$D$8="",G128&lt;'설정'!$D$8),OR('설정'!$E$8="",H128&gt;='설정'!$E$8),OR('설정'!$F$8="",H128&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I128="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G128&lt;&gt;"",H128&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G128&lt;&gt;"",N(G128)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G128&lt;&gt;"",H128&lt;&gt;""),(N(G128)+N(H128))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G128&lt;&gt;"",N(G128)&lt;='설정'!$E$6),AND(H128&lt;&gt;"",N(H128)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G128&lt;&gt;"",H128&lt;&gt;""),(N(G128)+N(H128))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G128&lt;&gt;"",H128&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G128&lt;&gt;"",N(G128)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G128&lt;&gt;"",H128&lt;&gt;""),(N(G128)+N(H128))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G128&lt;&gt;"",N(G128)&lt;='설정'!$E$7),AND(H128&lt;&gt;"",N(H128)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G128&lt;&gt;"",H128&lt;&gt;""),(N(G128)+N(H128))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G128&lt;&gt;"",H128&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G128&lt;&gt;"",N(G128)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G128&lt;&gt;"",H128&lt;&gt;""),(N(G128)+N(H128))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G128&lt;&gt;"",N(G128)&lt;='설정'!$E$8),AND(H128&lt;&gt;"",N(H128)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G128&lt;&gt;"",H128&lt;&gt;""),(N(G128)+N(H128))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L128" s="29">
-        <f>IF(OR(G128="",H128=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G128-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H128-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G128="",H128=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G128-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G128+H128)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G128+H128)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G128-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H128-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M128" s="7" t="n"/>
@@ -30834,11 +30831,11 @@
         <v/>
       </c>
       <c r="K129" s="27">
-        <f>IF(I129="","",IF(OR(G129="",H129=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G129&gt;='설정'!$C$6),OR('설정'!$D$6="",G129&lt;'설정'!$D$6),OR('설정'!$E$6="",H129&gt;='설정'!$E$6),OR('설정'!$F$6="",H129&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G129&gt;='설정'!$C$7),OR('설정'!$D$7="",G129&lt;'설정'!$D$7),OR('설정'!$E$7="",H129&gt;='설정'!$E$7),OR('설정'!$F$7="",H129&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G129&gt;='설정'!$C$8),OR('설정'!$D$8="",G129&lt;'설정'!$D$8),OR('설정'!$E$8="",H129&gt;='설정'!$E$8),OR('설정'!$F$8="",H129&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I129="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G129&lt;&gt;"",H129&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G129&lt;&gt;"",N(G129)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G129&lt;&gt;"",H129&lt;&gt;""),(N(G129)+N(H129))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G129&lt;&gt;"",N(G129)&lt;='설정'!$E$6),AND(H129&lt;&gt;"",N(H129)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G129&lt;&gt;"",H129&lt;&gt;""),(N(G129)+N(H129))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G129&lt;&gt;"",H129&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G129&lt;&gt;"",N(G129)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G129&lt;&gt;"",H129&lt;&gt;""),(N(G129)+N(H129))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G129&lt;&gt;"",N(G129)&lt;='설정'!$E$7),AND(H129&lt;&gt;"",N(H129)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G129&lt;&gt;"",H129&lt;&gt;""),(N(G129)+N(H129))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G129&lt;&gt;"",H129&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G129&lt;&gt;"",N(G129)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G129&lt;&gt;"",H129&lt;&gt;""),(N(G129)+N(H129))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G129&lt;&gt;"",N(G129)&lt;='설정'!$E$8),AND(H129&lt;&gt;"",N(H129)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G129&lt;&gt;"",H129&lt;&gt;""),(N(G129)+N(H129))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L129" s="29">
-        <f>IF(OR(G129="",H129=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G129-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H129-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G129="",H129=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G129-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G129+H129)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G129+H129)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G129-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H129-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M129" s="7" t="n"/>
@@ -30897,11 +30894,11 @@
         <v/>
       </c>
       <c r="K130" s="27">
-        <f>IF(I130="","",IF(OR(G130="",H130=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G130&gt;='설정'!$C$6),OR('설정'!$D$6="",G130&lt;'설정'!$D$6),OR('설정'!$E$6="",H130&gt;='설정'!$E$6),OR('설정'!$F$6="",H130&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G130&gt;='설정'!$C$7),OR('설정'!$D$7="",G130&lt;'설정'!$D$7),OR('설정'!$E$7="",H130&gt;='설정'!$E$7),OR('설정'!$F$7="",H130&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G130&gt;='설정'!$C$8),OR('설정'!$D$8="",G130&lt;'설정'!$D$8),OR('설정'!$E$8="",H130&gt;='설정'!$E$8),OR('설정'!$F$8="",H130&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I130="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G130&lt;&gt;"",H130&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G130&lt;&gt;"",N(G130)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G130&lt;&gt;"",H130&lt;&gt;""),(N(G130)+N(H130))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G130&lt;&gt;"",N(G130)&lt;='설정'!$E$6),AND(H130&lt;&gt;"",N(H130)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G130&lt;&gt;"",H130&lt;&gt;""),(N(G130)+N(H130))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G130&lt;&gt;"",H130&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G130&lt;&gt;"",N(G130)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G130&lt;&gt;"",H130&lt;&gt;""),(N(G130)+N(H130))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G130&lt;&gt;"",N(G130)&lt;='설정'!$E$7),AND(H130&lt;&gt;"",N(H130)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G130&lt;&gt;"",H130&lt;&gt;""),(N(G130)+N(H130))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G130&lt;&gt;"",H130&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G130&lt;&gt;"",N(G130)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G130&lt;&gt;"",H130&lt;&gt;""),(N(G130)+N(H130))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G130&lt;&gt;"",N(G130)&lt;='설정'!$E$8),AND(H130&lt;&gt;"",N(H130)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G130&lt;&gt;"",H130&lt;&gt;""),(N(G130)+N(H130))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L130" s="29">
-        <f>IF(OR(G130="",H130=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G130-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H130-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G130="",H130=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G130-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G130+H130)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G130+H130)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G130-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H130-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M130" s="7" t="n"/>
@@ -30960,11 +30957,11 @@
         <v/>
       </c>
       <c r="K131" s="27">
-        <f>IF(I131="","",IF(OR(G131="",H131=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G131&gt;='설정'!$C$6),OR('설정'!$D$6="",G131&lt;'설정'!$D$6),OR('설정'!$E$6="",H131&gt;='설정'!$E$6),OR('설정'!$F$6="",H131&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G131&gt;='설정'!$C$7),OR('설정'!$D$7="",G131&lt;'설정'!$D$7),OR('설정'!$E$7="",H131&gt;='설정'!$E$7),OR('설정'!$F$7="",H131&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G131&gt;='설정'!$C$8),OR('설정'!$D$8="",G131&lt;'설정'!$D$8),OR('설정'!$E$8="",H131&gt;='설정'!$E$8),OR('설정'!$F$8="",H131&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I131="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G131&lt;&gt;"",H131&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G131&lt;&gt;"",N(G131)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G131&lt;&gt;"",H131&lt;&gt;""),(N(G131)+N(H131))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G131&lt;&gt;"",N(G131)&lt;='설정'!$E$6),AND(H131&lt;&gt;"",N(H131)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G131&lt;&gt;"",H131&lt;&gt;""),(N(G131)+N(H131))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G131&lt;&gt;"",H131&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G131&lt;&gt;"",N(G131)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G131&lt;&gt;"",H131&lt;&gt;""),(N(G131)+N(H131))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G131&lt;&gt;"",N(G131)&lt;='설정'!$E$7),AND(H131&lt;&gt;"",N(H131)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G131&lt;&gt;"",H131&lt;&gt;""),(N(G131)+N(H131))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G131&lt;&gt;"",H131&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G131&lt;&gt;"",N(G131)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G131&lt;&gt;"",H131&lt;&gt;""),(N(G131)+N(H131))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G131&lt;&gt;"",N(G131)&lt;='설정'!$E$8),AND(H131&lt;&gt;"",N(H131)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G131&lt;&gt;"",H131&lt;&gt;""),(N(G131)+N(H131))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L131" s="29">
-        <f>IF(OR(G131="",H131=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G131-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H131-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G131="",H131=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G131-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G131+H131)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G131+H131)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G131-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H131-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M131" s="7" t="n"/>
@@ -31023,11 +31020,11 @@
         <v/>
       </c>
       <c r="K132" s="27">
-        <f>IF(I132="","",IF(OR(G132="",H132=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G132&gt;='설정'!$C$6),OR('설정'!$D$6="",G132&lt;'설정'!$D$6),OR('설정'!$E$6="",H132&gt;='설정'!$E$6),OR('설정'!$F$6="",H132&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G132&gt;='설정'!$C$7),OR('설정'!$D$7="",G132&lt;'설정'!$D$7),OR('설정'!$E$7="",H132&gt;='설정'!$E$7),OR('설정'!$F$7="",H132&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G132&gt;='설정'!$C$8),OR('설정'!$D$8="",G132&lt;'설정'!$D$8),OR('설정'!$E$8="",H132&gt;='설정'!$E$8),OR('설정'!$F$8="",H132&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I132="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G132&lt;&gt;"",H132&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G132&lt;&gt;"",N(G132)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G132&lt;&gt;"",H132&lt;&gt;""),(N(G132)+N(H132))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G132&lt;&gt;"",N(G132)&lt;='설정'!$E$6),AND(H132&lt;&gt;"",N(H132)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G132&lt;&gt;"",H132&lt;&gt;""),(N(G132)+N(H132))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G132&lt;&gt;"",H132&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G132&lt;&gt;"",N(G132)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G132&lt;&gt;"",H132&lt;&gt;""),(N(G132)+N(H132))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G132&lt;&gt;"",N(G132)&lt;='설정'!$E$7),AND(H132&lt;&gt;"",N(H132)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G132&lt;&gt;"",H132&lt;&gt;""),(N(G132)+N(H132))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G132&lt;&gt;"",H132&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G132&lt;&gt;"",N(G132)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G132&lt;&gt;"",H132&lt;&gt;""),(N(G132)+N(H132))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G132&lt;&gt;"",N(G132)&lt;='설정'!$E$8),AND(H132&lt;&gt;"",N(H132)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G132&lt;&gt;"",H132&lt;&gt;""),(N(G132)+N(H132))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L132" s="29">
-        <f>IF(OR(G132="",H132=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G132-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H132-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G132="",H132=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G132-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G132+H132)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G132+H132)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G132-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H132-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M132" s="7" t="n"/>
@@ -31086,11 +31083,11 @@
         <v/>
       </c>
       <c r="K133" s="27">
-        <f>IF(I133="","",IF(OR(G133="",H133=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G133&gt;='설정'!$C$6),OR('설정'!$D$6="",G133&lt;'설정'!$D$6),OR('설정'!$E$6="",H133&gt;='설정'!$E$6),OR('설정'!$F$6="",H133&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G133&gt;='설정'!$C$7),OR('설정'!$D$7="",G133&lt;'설정'!$D$7),OR('설정'!$E$7="",H133&gt;='설정'!$E$7),OR('설정'!$F$7="",H133&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G133&gt;='설정'!$C$8),OR('설정'!$D$8="",G133&lt;'설정'!$D$8),OR('설정'!$E$8="",H133&gt;='설정'!$E$8),OR('설정'!$F$8="",H133&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I133="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G133&lt;&gt;"",H133&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G133&lt;&gt;"",N(G133)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G133&lt;&gt;"",H133&lt;&gt;""),(N(G133)+N(H133))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G133&lt;&gt;"",N(G133)&lt;='설정'!$E$6),AND(H133&lt;&gt;"",N(H133)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G133&lt;&gt;"",H133&lt;&gt;""),(N(G133)+N(H133))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G133&lt;&gt;"",H133&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G133&lt;&gt;"",N(G133)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G133&lt;&gt;"",H133&lt;&gt;""),(N(G133)+N(H133))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G133&lt;&gt;"",N(G133)&lt;='설정'!$E$7),AND(H133&lt;&gt;"",N(H133)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G133&lt;&gt;"",H133&lt;&gt;""),(N(G133)+N(H133))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G133&lt;&gt;"",H133&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G133&lt;&gt;"",N(G133)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G133&lt;&gt;"",H133&lt;&gt;""),(N(G133)+N(H133))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G133&lt;&gt;"",N(G133)&lt;='설정'!$E$8),AND(H133&lt;&gt;"",N(H133)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G133&lt;&gt;"",H133&lt;&gt;""),(N(G133)+N(H133))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L133" s="29">
-        <f>IF(OR(G133="",H133=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G133-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H133-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G133="",H133=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G133-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G133+H133)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G133+H133)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G133-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H133-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M133" s="7" t="n"/>
@@ -31149,11 +31146,11 @@
         <v/>
       </c>
       <c r="K134" s="27">
-        <f>IF(I134="","",IF(OR(G134="",H134=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G134&gt;='설정'!$C$6),OR('설정'!$D$6="",G134&lt;'설정'!$D$6),OR('설정'!$E$6="",H134&gt;='설정'!$E$6),OR('설정'!$F$6="",H134&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G134&gt;='설정'!$C$7),OR('설정'!$D$7="",G134&lt;'설정'!$D$7),OR('설정'!$E$7="",H134&gt;='설정'!$E$7),OR('설정'!$F$7="",H134&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G134&gt;='설정'!$C$8),OR('설정'!$D$8="",G134&lt;'설정'!$D$8),OR('설정'!$E$8="",H134&gt;='설정'!$E$8),OR('설정'!$F$8="",H134&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I134="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G134&lt;&gt;"",H134&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G134&lt;&gt;"",N(G134)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G134&lt;&gt;"",H134&lt;&gt;""),(N(G134)+N(H134))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G134&lt;&gt;"",N(G134)&lt;='설정'!$E$6),AND(H134&lt;&gt;"",N(H134)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G134&lt;&gt;"",H134&lt;&gt;""),(N(G134)+N(H134))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G134&lt;&gt;"",H134&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G134&lt;&gt;"",N(G134)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G134&lt;&gt;"",H134&lt;&gt;""),(N(G134)+N(H134))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G134&lt;&gt;"",N(G134)&lt;='설정'!$E$7),AND(H134&lt;&gt;"",N(H134)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G134&lt;&gt;"",H134&lt;&gt;""),(N(G134)+N(H134))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G134&lt;&gt;"",H134&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G134&lt;&gt;"",N(G134)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G134&lt;&gt;"",H134&lt;&gt;""),(N(G134)+N(H134))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G134&lt;&gt;"",N(G134)&lt;='설정'!$E$8),AND(H134&lt;&gt;"",N(H134)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G134&lt;&gt;"",H134&lt;&gt;""),(N(G134)+N(H134))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L134" s="29">
-        <f>IF(OR(G134="",H134=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G134-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H134-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G134="",H134=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G134-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G134+H134)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G134+H134)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G134-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H134-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M134" s="7" t="n"/>
@@ -31212,11 +31209,11 @@
         <v/>
       </c>
       <c r="K135" s="27">
-        <f>IF(I135="","",IF(OR(G135="",H135=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G135&gt;='설정'!$C$6),OR('설정'!$D$6="",G135&lt;'설정'!$D$6),OR('설정'!$E$6="",H135&gt;='설정'!$E$6),OR('설정'!$F$6="",H135&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G135&gt;='설정'!$C$7),OR('설정'!$D$7="",G135&lt;'설정'!$D$7),OR('설정'!$E$7="",H135&gt;='설정'!$E$7),OR('설정'!$F$7="",H135&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G135&gt;='설정'!$C$8),OR('설정'!$D$8="",G135&lt;'설정'!$D$8),OR('설정'!$E$8="",H135&gt;='설정'!$E$8),OR('설정'!$F$8="",H135&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I135="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G135&lt;&gt;"",H135&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G135&lt;&gt;"",N(G135)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G135&lt;&gt;"",H135&lt;&gt;""),(N(G135)+N(H135))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G135&lt;&gt;"",N(G135)&lt;='설정'!$E$6),AND(H135&lt;&gt;"",N(H135)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G135&lt;&gt;"",H135&lt;&gt;""),(N(G135)+N(H135))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G135&lt;&gt;"",H135&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G135&lt;&gt;"",N(G135)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G135&lt;&gt;"",H135&lt;&gt;""),(N(G135)+N(H135))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G135&lt;&gt;"",N(G135)&lt;='설정'!$E$7),AND(H135&lt;&gt;"",N(H135)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G135&lt;&gt;"",H135&lt;&gt;""),(N(G135)+N(H135))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G135&lt;&gt;"",H135&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G135&lt;&gt;"",N(G135)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G135&lt;&gt;"",H135&lt;&gt;""),(N(G135)+N(H135))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G135&lt;&gt;"",N(G135)&lt;='설정'!$E$8),AND(H135&lt;&gt;"",N(H135)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G135&lt;&gt;"",H135&lt;&gt;""),(N(G135)+N(H135))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L135" s="29">
-        <f>IF(OR(G135="",H135=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G135-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H135-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G135="",H135=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G135-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G135+H135)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G135+H135)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G135-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H135-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M135" s="7" t="n"/>
@@ -31275,11 +31272,11 @@
         <v/>
       </c>
       <c r="K136" s="27">
-        <f>IF(I136="","",IF(OR(G136="",H136=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G136&gt;='설정'!$C$6),OR('설정'!$D$6="",G136&lt;'설정'!$D$6),OR('설정'!$E$6="",H136&gt;='설정'!$E$6),OR('설정'!$F$6="",H136&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G136&gt;='설정'!$C$7),OR('설정'!$D$7="",G136&lt;'설정'!$D$7),OR('설정'!$E$7="",H136&gt;='설정'!$E$7),OR('설정'!$F$7="",H136&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G136&gt;='설정'!$C$8),OR('설정'!$D$8="",G136&lt;'설정'!$D$8),OR('설정'!$E$8="",H136&gt;='설정'!$E$8),OR('설정'!$F$8="",H136&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I136="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G136&lt;&gt;"",H136&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G136&lt;&gt;"",N(G136)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G136&lt;&gt;"",H136&lt;&gt;""),(N(G136)+N(H136))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G136&lt;&gt;"",N(G136)&lt;='설정'!$E$6),AND(H136&lt;&gt;"",N(H136)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G136&lt;&gt;"",H136&lt;&gt;""),(N(G136)+N(H136))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G136&lt;&gt;"",H136&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G136&lt;&gt;"",N(G136)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G136&lt;&gt;"",H136&lt;&gt;""),(N(G136)+N(H136))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G136&lt;&gt;"",N(G136)&lt;='설정'!$E$7),AND(H136&lt;&gt;"",N(H136)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G136&lt;&gt;"",H136&lt;&gt;""),(N(G136)+N(H136))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G136&lt;&gt;"",H136&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G136&lt;&gt;"",N(G136)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G136&lt;&gt;"",H136&lt;&gt;""),(N(G136)+N(H136))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G136&lt;&gt;"",N(G136)&lt;='설정'!$E$8),AND(H136&lt;&gt;"",N(H136)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G136&lt;&gt;"",H136&lt;&gt;""),(N(G136)+N(H136))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L136" s="29">
-        <f>IF(OR(G136="",H136=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G136-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H136-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G136="",H136=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G136-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G136+H136)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G136+H136)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G136-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H136-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M136" s="7" t="n"/>
@@ -31338,11 +31335,11 @@
         <v/>
       </c>
       <c r="K137" s="27">
-        <f>IF(I137="","",IF(OR(G137="",H137=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G137&gt;='설정'!$C$6),OR('설정'!$D$6="",G137&lt;'설정'!$D$6),OR('설정'!$E$6="",H137&gt;='설정'!$E$6),OR('설정'!$F$6="",H137&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G137&gt;='설정'!$C$7),OR('설정'!$D$7="",G137&lt;'설정'!$D$7),OR('설정'!$E$7="",H137&gt;='설정'!$E$7),OR('설정'!$F$7="",H137&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G137&gt;='설정'!$C$8),OR('설정'!$D$8="",G137&lt;'설정'!$D$8),OR('설정'!$E$8="",H137&gt;='설정'!$E$8),OR('설정'!$F$8="",H137&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I137="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G137&lt;&gt;"",H137&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G137&lt;&gt;"",N(G137)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G137&lt;&gt;"",H137&lt;&gt;""),(N(G137)+N(H137))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G137&lt;&gt;"",N(G137)&lt;='설정'!$E$6),AND(H137&lt;&gt;"",N(H137)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G137&lt;&gt;"",H137&lt;&gt;""),(N(G137)+N(H137))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G137&lt;&gt;"",H137&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G137&lt;&gt;"",N(G137)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G137&lt;&gt;"",H137&lt;&gt;""),(N(G137)+N(H137))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G137&lt;&gt;"",N(G137)&lt;='설정'!$E$7),AND(H137&lt;&gt;"",N(H137)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G137&lt;&gt;"",H137&lt;&gt;""),(N(G137)+N(H137))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G137&lt;&gt;"",H137&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G137&lt;&gt;"",N(G137)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G137&lt;&gt;"",H137&lt;&gt;""),(N(G137)+N(H137))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G137&lt;&gt;"",N(G137)&lt;='설정'!$E$8),AND(H137&lt;&gt;"",N(H137)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G137&lt;&gt;"",H137&lt;&gt;""),(N(G137)+N(H137))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L137" s="29">
-        <f>IF(OR(G137="",H137=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G137-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H137-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G137="",H137=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G137-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G137+H137)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G137+H137)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G137-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H137-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M137" s="7" t="n"/>
@@ -31401,11 +31398,11 @@
         <v/>
       </c>
       <c r="K138" s="27">
-        <f>IF(I138="","",IF(OR(G138="",H138=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G138&gt;='설정'!$C$6),OR('설정'!$D$6="",G138&lt;'설정'!$D$6),OR('설정'!$E$6="",H138&gt;='설정'!$E$6),OR('설정'!$F$6="",H138&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G138&gt;='설정'!$C$7),OR('설정'!$D$7="",G138&lt;'설정'!$D$7),OR('설정'!$E$7="",H138&gt;='설정'!$E$7),OR('설정'!$F$7="",H138&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G138&gt;='설정'!$C$8),OR('설정'!$D$8="",G138&lt;'설정'!$D$8),OR('설정'!$E$8="",H138&gt;='설정'!$E$8),OR('설정'!$F$8="",H138&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I138="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G138&lt;&gt;"",H138&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G138&lt;&gt;"",N(G138)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G138&lt;&gt;"",H138&lt;&gt;""),(N(G138)+N(H138))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G138&lt;&gt;"",N(G138)&lt;='설정'!$E$6),AND(H138&lt;&gt;"",N(H138)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G138&lt;&gt;"",H138&lt;&gt;""),(N(G138)+N(H138))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G138&lt;&gt;"",H138&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G138&lt;&gt;"",N(G138)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G138&lt;&gt;"",H138&lt;&gt;""),(N(G138)+N(H138))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G138&lt;&gt;"",N(G138)&lt;='설정'!$E$7),AND(H138&lt;&gt;"",N(H138)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G138&lt;&gt;"",H138&lt;&gt;""),(N(G138)+N(H138))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G138&lt;&gt;"",H138&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G138&lt;&gt;"",N(G138)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G138&lt;&gt;"",H138&lt;&gt;""),(N(G138)+N(H138))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G138&lt;&gt;"",N(G138)&lt;='설정'!$E$8),AND(H138&lt;&gt;"",N(H138)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G138&lt;&gt;"",H138&lt;&gt;""),(N(G138)+N(H138))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L138" s="29">
-        <f>IF(OR(G138="",H138=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G138-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H138-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G138="",H138=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G138-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G138+H138)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G138+H138)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G138-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H138-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M138" s="7" t="n"/>
@@ -31464,11 +31461,11 @@
         <v/>
       </c>
       <c r="K139" s="27">
-        <f>IF(I139="","",IF(OR(G139="",H139=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G139&gt;='설정'!$C$6),OR('설정'!$D$6="",G139&lt;'설정'!$D$6),OR('설정'!$E$6="",H139&gt;='설정'!$E$6),OR('설정'!$F$6="",H139&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G139&gt;='설정'!$C$7),OR('설정'!$D$7="",G139&lt;'설정'!$D$7),OR('설정'!$E$7="",H139&gt;='설정'!$E$7),OR('설정'!$F$7="",H139&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G139&gt;='설정'!$C$8),OR('설정'!$D$8="",G139&lt;'설정'!$D$8),OR('설정'!$E$8="",H139&gt;='설정'!$E$8),OR('설정'!$F$8="",H139&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I139="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G139&lt;&gt;"",H139&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G139&lt;&gt;"",N(G139)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G139&lt;&gt;"",H139&lt;&gt;""),(N(G139)+N(H139))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G139&lt;&gt;"",N(G139)&lt;='설정'!$E$6),AND(H139&lt;&gt;"",N(H139)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G139&lt;&gt;"",H139&lt;&gt;""),(N(G139)+N(H139))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G139&lt;&gt;"",H139&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G139&lt;&gt;"",N(G139)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G139&lt;&gt;"",H139&lt;&gt;""),(N(G139)+N(H139))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G139&lt;&gt;"",N(G139)&lt;='설정'!$E$7),AND(H139&lt;&gt;"",N(H139)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G139&lt;&gt;"",H139&lt;&gt;""),(N(G139)+N(H139))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G139&lt;&gt;"",H139&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G139&lt;&gt;"",N(G139)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G139&lt;&gt;"",H139&lt;&gt;""),(N(G139)+N(H139))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G139&lt;&gt;"",N(G139)&lt;='설정'!$E$8),AND(H139&lt;&gt;"",N(H139)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G139&lt;&gt;"",H139&lt;&gt;""),(N(G139)+N(H139))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L139" s="29">
-        <f>IF(OR(G139="",H139=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G139-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H139-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G139="",H139=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G139-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G139+H139)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G139+H139)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G139-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H139-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M139" s="7" t="n"/>
@@ -31527,11 +31524,11 @@
         <v/>
       </c>
       <c r="K140" s="27">
-        <f>IF(I140="","",IF(OR(G140="",H140=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G140&gt;='설정'!$C$6),OR('설정'!$D$6="",G140&lt;'설정'!$D$6),OR('설정'!$E$6="",H140&gt;='설정'!$E$6),OR('설정'!$F$6="",H140&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G140&gt;='설정'!$C$7),OR('설정'!$D$7="",G140&lt;'설정'!$D$7),OR('설정'!$E$7="",H140&gt;='설정'!$E$7),OR('설정'!$F$7="",H140&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G140&gt;='설정'!$C$8),OR('설정'!$D$8="",G140&lt;'설정'!$D$8),OR('설정'!$E$8="",H140&gt;='설정'!$E$8),OR('설정'!$F$8="",H140&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I140="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G140&lt;&gt;"",H140&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G140&lt;&gt;"",N(G140)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G140&lt;&gt;"",H140&lt;&gt;""),(N(G140)+N(H140))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G140&lt;&gt;"",N(G140)&lt;='설정'!$E$6),AND(H140&lt;&gt;"",N(H140)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G140&lt;&gt;"",H140&lt;&gt;""),(N(G140)+N(H140))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G140&lt;&gt;"",H140&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G140&lt;&gt;"",N(G140)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G140&lt;&gt;"",H140&lt;&gt;""),(N(G140)+N(H140))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G140&lt;&gt;"",N(G140)&lt;='설정'!$E$7),AND(H140&lt;&gt;"",N(H140)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G140&lt;&gt;"",H140&lt;&gt;""),(N(G140)+N(H140))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G140&lt;&gt;"",H140&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G140&lt;&gt;"",N(G140)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G140&lt;&gt;"",H140&lt;&gt;""),(N(G140)+N(H140))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G140&lt;&gt;"",N(G140)&lt;='설정'!$E$8),AND(H140&lt;&gt;"",N(H140)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G140&lt;&gt;"",H140&lt;&gt;""),(N(G140)+N(H140))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L140" s="29">
-        <f>IF(OR(G140="",H140=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G140-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H140-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G140="",H140=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G140-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G140+H140)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G140+H140)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G140-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H140-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M140" s="7" t="n"/>
@@ -31590,11 +31587,11 @@
         <v/>
       </c>
       <c r="K141" s="27">
-        <f>IF(I141="","",IF(OR(G141="",H141=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G141&gt;='설정'!$C$6),OR('설정'!$D$6="",G141&lt;'설정'!$D$6),OR('설정'!$E$6="",H141&gt;='설정'!$E$6),OR('설정'!$F$6="",H141&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G141&gt;='설정'!$C$7),OR('설정'!$D$7="",G141&lt;'설정'!$D$7),OR('설정'!$E$7="",H141&gt;='설정'!$E$7),OR('설정'!$F$7="",H141&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G141&gt;='설정'!$C$8),OR('설정'!$D$8="",G141&lt;'설정'!$D$8),OR('설정'!$E$8="",H141&gt;='설정'!$E$8),OR('설정'!$F$8="",H141&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I141="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G141&lt;&gt;"",H141&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G141&lt;&gt;"",N(G141)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G141&lt;&gt;"",H141&lt;&gt;""),(N(G141)+N(H141))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G141&lt;&gt;"",N(G141)&lt;='설정'!$E$6),AND(H141&lt;&gt;"",N(H141)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G141&lt;&gt;"",H141&lt;&gt;""),(N(G141)+N(H141))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G141&lt;&gt;"",H141&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G141&lt;&gt;"",N(G141)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G141&lt;&gt;"",H141&lt;&gt;""),(N(G141)+N(H141))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G141&lt;&gt;"",N(G141)&lt;='설정'!$E$7),AND(H141&lt;&gt;"",N(H141)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G141&lt;&gt;"",H141&lt;&gt;""),(N(G141)+N(H141))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G141&lt;&gt;"",H141&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G141&lt;&gt;"",N(G141)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G141&lt;&gt;"",H141&lt;&gt;""),(N(G141)+N(H141))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G141&lt;&gt;"",N(G141)&lt;='설정'!$E$8),AND(H141&lt;&gt;"",N(H141)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G141&lt;&gt;"",H141&lt;&gt;""),(N(G141)+N(H141))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L141" s="29">
-        <f>IF(OR(G141="",H141=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G141-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H141-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G141="",H141=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G141-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G141+H141)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G141+H141)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G141-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H141-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M141" s="7" t="n"/>
@@ -31653,11 +31650,11 @@
         <v/>
       </c>
       <c r="K142" s="27">
-        <f>IF(I142="","",IF(OR(G142="",H142=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G142&gt;='설정'!$C$6),OR('설정'!$D$6="",G142&lt;'설정'!$D$6),OR('설정'!$E$6="",H142&gt;='설정'!$E$6),OR('설정'!$F$6="",H142&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G142&gt;='설정'!$C$7),OR('설정'!$D$7="",G142&lt;'설정'!$D$7),OR('설정'!$E$7="",H142&gt;='설정'!$E$7),OR('설정'!$F$7="",H142&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G142&gt;='설정'!$C$8),OR('설정'!$D$8="",G142&lt;'설정'!$D$8),OR('설정'!$E$8="",H142&gt;='설정'!$E$8),OR('설정'!$F$8="",H142&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I142="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G142&lt;&gt;"",H142&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G142&lt;&gt;"",N(G142)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G142&lt;&gt;"",H142&lt;&gt;""),(N(G142)+N(H142))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G142&lt;&gt;"",N(G142)&lt;='설정'!$E$6),AND(H142&lt;&gt;"",N(H142)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G142&lt;&gt;"",H142&lt;&gt;""),(N(G142)+N(H142))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G142&lt;&gt;"",H142&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G142&lt;&gt;"",N(G142)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G142&lt;&gt;"",H142&lt;&gt;""),(N(G142)+N(H142))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G142&lt;&gt;"",N(G142)&lt;='설정'!$E$7),AND(H142&lt;&gt;"",N(H142)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G142&lt;&gt;"",H142&lt;&gt;""),(N(G142)+N(H142))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G142&lt;&gt;"",H142&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G142&lt;&gt;"",N(G142)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G142&lt;&gt;"",H142&lt;&gt;""),(N(G142)+N(H142))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G142&lt;&gt;"",N(G142)&lt;='설정'!$E$8),AND(H142&lt;&gt;"",N(H142)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G142&lt;&gt;"",H142&lt;&gt;""),(N(G142)+N(H142))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L142" s="29">
-        <f>IF(OR(G142="",H142=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G142-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H142-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G142="",H142=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G142-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G142+H142)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G142+H142)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G142-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H142-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M142" s="7" t="n"/>
@@ -31716,11 +31713,11 @@
         <v/>
       </c>
       <c r="K143" s="27">
-        <f>IF(I143="","",IF(OR(G143="",H143=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G143&gt;='설정'!$C$6),OR('설정'!$D$6="",G143&lt;'설정'!$D$6),OR('설정'!$E$6="",H143&gt;='설정'!$E$6),OR('설정'!$F$6="",H143&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G143&gt;='설정'!$C$7),OR('설정'!$D$7="",G143&lt;'설정'!$D$7),OR('설정'!$E$7="",H143&gt;='설정'!$E$7),OR('설정'!$F$7="",H143&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G143&gt;='설정'!$C$8),OR('설정'!$D$8="",G143&lt;'설정'!$D$8),OR('설정'!$E$8="",H143&gt;='설정'!$E$8),OR('설정'!$F$8="",H143&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I143="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G143&lt;&gt;"",H143&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G143&lt;&gt;"",N(G143)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G143&lt;&gt;"",H143&lt;&gt;""),(N(G143)+N(H143))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G143&lt;&gt;"",N(G143)&lt;='설정'!$E$6),AND(H143&lt;&gt;"",N(H143)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G143&lt;&gt;"",H143&lt;&gt;""),(N(G143)+N(H143))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G143&lt;&gt;"",H143&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G143&lt;&gt;"",N(G143)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G143&lt;&gt;"",H143&lt;&gt;""),(N(G143)+N(H143))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G143&lt;&gt;"",N(G143)&lt;='설정'!$E$7),AND(H143&lt;&gt;"",N(H143)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G143&lt;&gt;"",H143&lt;&gt;""),(N(G143)+N(H143))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G143&lt;&gt;"",H143&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G143&lt;&gt;"",N(G143)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G143&lt;&gt;"",H143&lt;&gt;""),(N(G143)+N(H143))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G143&lt;&gt;"",N(G143)&lt;='설정'!$E$8),AND(H143&lt;&gt;"",N(H143)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G143&lt;&gt;"",H143&lt;&gt;""),(N(G143)+N(H143))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L143" s="29">
-        <f>IF(OR(G143="",H143=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G143-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H143-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G143="",H143=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G143-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G143+H143)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G143+H143)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G143-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H143-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M143" s="7" t="n"/>
@@ -31779,11 +31776,11 @@
         <v/>
       </c>
       <c r="K144" s="27">
-        <f>IF(I144="","",IF(OR(G144="",H144=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G144&gt;='설정'!$C$6),OR('설정'!$D$6="",G144&lt;'설정'!$D$6),OR('설정'!$E$6="",H144&gt;='설정'!$E$6),OR('설정'!$F$6="",H144&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G144&gt;='설정'!$C$7),OR('설정'!$D$7="",G144&lt;'설정'!$D$7),OR('설정'!$E$7="",H144&gt;='설정'!$E$7),OR('설정'!$F$7="",H144&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G144&gt;='설정'!$C$8),OR('설정'!$D$8="",G144&lt;'설정'!$D$8),OR('설정'!$E$8="",H144&gt;='설정'!$E$8),OR('설정'!$F$8="",H144&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I144="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G144&lt;&gt;"",H144&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G144&lt;&gt;"",N(G144)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G144&lt;&gt;"",H144&lt;&gt;""),(N(G144)+N(H144))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G144&lt;&gt;"",N(G144)&lt;='설정'!$E$6),AND(H144&lt;&gt;"",N(H144)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G144&lt;&gt;"",H144&lt;&gt;""),(N(G144)+N(H144))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G144&lt;&gt;"",H144&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G144&lt;&gt;"",N(G144)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G144&lt;&gt;"",H144&lt;&gt;""),(N(G144)+N(H144))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G144&lt;&gt;"",N(G144)&lt;='설정'!$E$7),AND(H144&lt;&gt;"",N(H144)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G144&lt;&gt;"",H144&lt;&gt;""),(N(G144)+N(H144))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G144&lt;&gt;"",H144&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G144&lt;&gt;"",N(G144)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G144&lt;&gt;"",H144&lt;&gt;""),(N(G144)+N(H144))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G144&lt;&gt;"",N(G144)&lt;='설정'!$E$8),AND(H144&lt;&gt;"",N(H144)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G144&lt;&gt;"",H144&lt;&gt;""),(N(G144)+N(H144))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L144" s="29">
-        <f>IF(OR(G144="",H144=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G144-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H144-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G144="",H144=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G144-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G144+H144)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G144+H144)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G144-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H144-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M144" s="7" t="n"/>
@@ -31842,11 +31839,11 @@
         <v/>
       </c>
       <c r="K145" s="27">
-        <f>IF(I145="","",IF(OR(G145="",H145=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G145&gt;='설정'!$C$6),OR('설정'!$D$6="",G145&lt;'설정'!$D$6),OR('설정'!$E$6="",H145&gt;='설정'!$E$6),OR('설정'!$F$6="",H145&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G145&gt;='설정'!$C$7),OR('설정'!$D$7="",G145&lt;'설정'!$D$7),OR('설정'!$E$7="",H145&gt;='설정'!$E$7),OR('설정'!$F$7="",H145&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G145&gt;='설정'!$C$8),OR('설정'!$D$8="",G145&lt;'설정'!$D$8),OR('설정'!$E$8="",H145&gt;='설정'!$E$8),OR('설정'!$F$8="",H145&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I145="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G145&lt;&gt;"",H145&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G145&lt;&gt;"",N(G145)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G145&lt;&gt;"",H145&lt;&gt;""),(N(G145)+N(H145))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G145&lt;&gt;"",N(G145)&lt;='설정'!$E$6),AND(H145&lt;&gt;"",N(H145)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G145&lt;&gt;"",H145&lt;&gt;""),(N(G145)+N(H145))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G145&lt;&gt;"",H145&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G145&lt;&gt;"",N(G145)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G145&lt;&gt;"",H145&lt;&gt;""),(N(G145)+N(H145))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G145&lt;&gt;"",N(G145)&lt;='설정'!$E$7),AND(H145&lt;&gt;"",N(H145)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G145&lt;&gt;"",H145&lt;&gt;""),(N(G145)+N(H145))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G145&lt;&gt;"",H145&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G145&lt;&gt;"",N(G145)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G145&lt;&gt;"",H145&lt;&gt;""),(N(G145)+N(H145))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G145&lt;&gt;"",N(G145)&lt;='설정'!$E$8),AND(H145&lt;&gt;"",N(H145)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G145&lt;&gt;"",H145&lt;&gt;""),(N(G145)+N(H145))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L145" s="29">
-        <f>IF(OR(G145="",H145=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G145-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H145-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G145="",H145=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G145-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G145+H145)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G145+H145)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G145-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H145-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M145" s="7" t="n"/>
@@ -31905,11 +31902,11 @@
         <v/>
       </c>
       <c r="K146" s="27">
-        <f>IF(I146="","",IF(OR(G146="",H146=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G146&gt;='설정'!$C$6),OR('설정'!$D$6="",G146&lt;'설정'!$D$6),OR('설정'!$E$6="",H146&gt;='설정'!$E$6),OR('설정'!$F$6="",H146&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G146&gt;='설정'!$C$7),OR('설정'!$D$7="",G146&lt;'설정'!$D$7),OR('설정'!$E$7="",H146&gt;='설정'!$E$7),OR('설정'!$F$7="",H146&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G146&gt;='설정'!$C$8),OR('설정'!$D$8="",G146&lt;'설정'!$D$8),OR('설정'!$E$8="",H146&gt;='설정'!$E$8),OR('설정'!$F$8="",H146&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I146="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G146&lt;&gt;"",H146&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G146&lt;&gt;"",N(G146)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G146&lt;&gt;"",H146&lt;&gt;""),(N(G146)+N(H146))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G146&lt;&gt;"",N(G146)&lt;='설정'!$E$6),AND(H146&lt;&gt;"",N(H146)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G146&lt;&gt;"",H146&lt;&gt;""),(N(G146)+N(H146))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G146&lt;&gt;"",H146&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G146&lt;&gt;"",N(G146)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G146&lt;&gt;"",H146&lt;&gt;""),(N(G146)+N(H146))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G146&lt;&gt;"",N(G146)&lt;='설정'!$E$7),AND(H146&lt;&gt;"",N(H146)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G146&lt;&gt;"",H146&lt;&gt;""),(N(G146)+N(H146))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G146&lt;&gt;"",H146&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G146&lt;&gt;"",N(G146)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G146&lt;&gt;"",H146&lt;&gt;""),(N(G146)+N(H146))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G146&lt;&gt;"",N(G146)&lt;='설정'!$E$8),AND(H146&lt;&gt;"",N(H146)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G146&lt;&gt;"",H146&lt;&gt;""),(N(G146)+N(H146))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L146" s="29">
-        <f>IF(OR(G146="",H146=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G146-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H146-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G146="",H146=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G146-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G146+H146)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G146+H146)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G146-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H146-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M146" s="7" t="n"/>
@@ -31968,11 +31965,11 @@
         <v/>
       </c>
       <c r="K147" s="27">
-        <f>IF(I147="","",IF(OR(G147="",H147=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G147&gt;='설정'!$C$6),OR('설정'!$D$6="",G147&lt;'설정'!$D$6),OR('설정'!$E$6="",H147&gt;='설정'!$E$6),OR('설정'!$F$6="",H147&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G147&gt;='설정'!$C$7),OR('설정'!$D$7="",G147&lt;'설정'!$D$7),OR('설정'!$E$7="",H147&gt;='설정'!$E$7),OR('설정'!$F$7="",H147&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G147&gt;='설정'!$C$8),OR('설정'!$D$8="",G147&lt;'설정'!$D$8),OR('설정'!$E$8="",H147&gt;='설정'!$E$8),OR('설정'!$F$8="",H147&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I147="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G147&lt;&gt;"",H147&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G147&lt;&gt;"",N(G147)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G147&lt;&gt;"",H147&lt;&gt;""),(N(G147)+N(H147))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G147&lt;&gt;"",N(G147)&lt;='설정'!$E$6),AND(H147&lt;&gt;"",N(H147)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G147&lt;&gt;"",H147&lt;&gt;""),(N(G147)+N(H147))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G147&lt;&gt;"",H147&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G147&lt;&gt;"",N(G147)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G147&lt;&gt;"",H147&lt;&gt;""),(N(G147)+N(H147))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G147&lt;&gt;"",N(G147)&lt;='설정'!$E$7),AND(H147&lt;&gt;"",N(H147)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G147&lt;&gt;"",H147&lt;&gt;""),(N(G147)+N(H147))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G147&lt;&gt;"",H147&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G147&lt;&gt;"",N(G147)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G147&lt;&gt;"",H147&lt;&gt;""),(N(G147)+N(H147))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G147&lt;&gt;"",N(G147)&lt;='설정'!$E$8),AND(H147&lt;&gt;"",N(H147)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G147&lt;&gt;"",H147&lt;&gt;""),(N(G147)+N(H147))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L147" s="29">
-        <f>IF(OR(G147="",H147=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G147-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H147-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G147="",H147=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G147-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G147+H147)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G147+H147)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G147-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H147-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M147" s="7" t="n"/>
@@ -32031,11 +32028,11 @@
         <v/>
       </c>
       <c r="K148" s="27">
-        <f>IF(I148="","",IF(OR(G148="",H148=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G148&gt;='설정'!$C$6),OR('설정'!$D$6="",G148&lt;'설정'!$D$6),OR('설정'!$E$6="",H148&gt;='설정'!$E$6),OR('설정'!$F$6="",H148&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G148&gt;='설정'!$C$7),OR('설정'!$D$7="",G148&lt;'설정'!$D$7),OR('설정'!$E$7="",H148&gt;='설정'!$E$7),OR('설정'!$F$7="",H148&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G148&gt;='설정'!$C$8),OR('설정'!$D$8="",G148&lt;'설정'!$D$8),OR('설정'!$E$8="",H148&gt;='설정'!$E$8),OR('설정'!$F$8="",H148&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I148="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G148&lt;&gt;"",H148&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G148&lt;&gt;"",N(G148)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G148&lt;&gt;"",H148&lt;&gt;""),(N(G148)+N(H148))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G148&lt;&gt;"",N(G148)&lt;='설정'!$E$6),AND(H148&lt;&gt;"",N(H148)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G148&lt;&gt;"",H148&lt;&gt;""),(N(G148)+N(H148))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G148&lt;&gt;"",H148&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G148&lt;&gt;"",N(G148)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G148&lt;&gt;"",H148&lt;&gt;""),(N(G148)+N(H148))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G148&lt;&gt;"",N(G148)&lt;='설정'!$E$7),AND(H148&lt;&gt;"",N(H148)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G148&lt;&gt;"",H148&lt;&gt;""),(N(G148)+N(H148))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G148&lt;&gt;"",H148&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G148&lt;&gt;"",N(G148)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G148&lt;&gt;"",H148&lt;&gt;""),(N(G148)+N(H148))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G148&lt;&gt;"",N(G148)&lt;='설정'!$E$8),AND(H148&lt;&gt;"",N(H148)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G148&lt;&gt;"",H148&lt;&gt;""),(N(G148)+N(H148))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L148" s="29">
-        <f>IF(OR(G148="",H148=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G148-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H148-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G148="",H148=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G148-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G148+H148)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G148+H148)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G148-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H148-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M148" s="7" t="n"/>
@@ -32094,11 +32091,11 @@
         <v/>
       </c>
       <c r="K149" s="27">
-        <f>IF(I149="","",IF(OR(G149="",H149=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G149&gt;='설정'!$C$6),OR('설정'!$D$6="",G149&lt;'설정'!$D$6),OR('설정'!$E$6="",H149&gt;='설정'!$E$6),OR('설정'!$F$6="",H149&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G149&gt;='설정'!$C$7),OR('설정'!$D$7="",G149&lt;'설정'!$D$7),OR('설정'!$E$7="",H149&gt;='설정'!$E$7),OR('설정'!$F$7="",H149&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G149&gt;='설정'!$C$8),OR('설정'!$D$8="",G149&lt;'설정'!$D$8),OR('설정'!$E$8="",H149&gt;='설정'!$E$8),OR('설정'!$F$8="",H149&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I149="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G149&lt;&gt;"",H149&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G149&lt;&gt;"",N(G149)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G149&lt;&gt;"",H149&lt;&gt;""),(N(G149)+N(H149))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G149&lt;&gt;"",N(G149)&lt;='설정'!$E$6),AND(H149&lt;&gt;"",N(H149)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G149&lt;&gt;"",H149&lt;&gt;""),(N(G149)+N(H149))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G149&lt;&gt;"",H149&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G149&lt;&gt;"",N(G149)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G149&lt;&gt;"",H149&lt;&gt;""),(N(G149)+N(H149))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G149&lt;&gt;"",N(G149)&lt;='설정'!$E$7),AND(H149&lt;&gt;"",N(H149)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G149&lt;&gt;"",H149&lt;&gt;""),(N(G149)+N(H149))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G149&lt;&gt;"",H149&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G149&lt;&gt;"",N(G149)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G149&lt;&gt;"",H149&lt;&gt;""),(N(G149)+N(H149))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G149&lt;&gt;"",N(G149)&lt;='설정'!$E$8),AND(H149&lt;&gt;"",N(H149)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G149&lt;&gt;"",H149&lt;&gt;""),(N(G149)+N(H149))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L149" s="29">
-        <f>IF(OR(G149="",H149=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G149-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H149-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G149="",H149=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G149-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G149+H149)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G149+H149)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G149-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H149-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M149" s="7" t="n"/>
@@ -32157,11 +32154,11 @@
         <v/>
       </c>
       <c r="K150" s="27">
-        <f>IF(I150="","",IF(OR(G150="",H150=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G150&gt;='설정'!$C$6),OR('설정'!$D$6="",G150&lt;'설정'!$D$6),OR('설정'!$E$6="",H150&gt;='설정'!$E$6),OR('설정'!$F$6="",H150&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G150&gt;='설정'!$C$7),OR('설정'!$D$7="",G150&lt;'설정'!$D$7),OR('설정'!$E$7="",H150&gt;='설정'!$E$7),OR('설정'!$F$7="",H150&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G150&gt;='설정'!$C$8),OR('설정'!$D$8="",G150&lt;'설정'!$D$8),OR('설정'!$E$8="",H150&gt;='설정'!$E$8),OR('설정'!$F$8="",H150&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I150="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G150&lt;&gt;"",H150&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G150&lt;&gt;"",N(G150)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G150&lt;&gt;"",H150&lt;&gt;""),(N(G150)+N(H150))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G150&lt;&gt;"",N(G150)&lt;='설정'!$E$6),AND(H150&lt;&gt;"",N(H150)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G150&lt;&gt;"",H150&lt;&gt;""),(N(G150)+N(H150))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G150&lt;&gt;"",H150&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G150&lt;&gt;"",N(G150)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G150&lt;&gt;"",H150&lt;&gt;""),(N(G150)+N(H150))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G150&lt;&gt;"",N(G150)&lt;='설정'!$E$7),AND(H150&lt;&gt;"",N(H150)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G150&lt;&gt;"",H150&lt;&gt;""),(N(G150)+N(H150))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G150&lt;&gt;"",H150&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G150&lt;&gt;"",N(G150)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G150&lt;&gt;"",H150&lt;&gt;""),(N(G150)+N(H150))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G150&lt;&gt;"",N(G150)&lt;='설정'!$E$8),AND(H150&lt;&gt;"",N(H150)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G150&lt;&gt;"",H150&lt;&gt;""),(N(G150)+N(H150))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L150" s="29">
-        <f>IF(OR(G150="",H150=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G150-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H150-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G150="",H150=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G150-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G150+H150)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G150+H150)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G150-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H150-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M150" s="7" t="n"/>
@@ -32220,11 +32217,11 @@
         <v/>
       </c>
       <c r="K151" s="27">
-        <f>IF(I151="","",IF(OR(G151="",H151=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G151&gt;='설정'!$C$6),OR('설정'!$D$6="",G151&lt;'설정'!$D$6),OR('설정'!$E$6="",H151&gt;='설정'!$E$6),OR('설정'!$F$6="",H151&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G151&gt;='설정'!$C$7),OR('설정'!$D$7="",G151&lt;'설정'!$D$7),OR('설정'!$E$7="",H151&gt;='설정'!$E$7),OR('설정'!$F$7="",H151&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G151&gt;='설정'!$C$8),OR('설정'!$D$8="",G151&lt;'설정'!$D$8),OR('설정'!$E$8="",H151&gt;='설정'!$E$8),OR('설정'!$F$8="",H151&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I151="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G151&lt;&gt;"",H151&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G151&lt;&gt;"",N(G151)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G151&lt;&gt;"",H151&lt;&gt;""),(N(G151)+N(H151))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G151&lt;&gt;"",N(G151)&lt;='설정'!$E$6),AND(H151&lt;&gt;"",N(H151)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G151&lt;&gt;"",H151&lt;&gt;""),(N(G151)+N(H151))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G151&lt;&gt;"",H151&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G151&lt;&gt;"",N(G151)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G151&lt;&gt;"",H151&lt;&gt;""),(N(G151)+N(H151))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G151&lt;&gt;"",N(G151)&lt;='설정'!$E$7),AND(H151&lt;&gt;"",N(H151)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G151&lt;&gt;"",H151&lt;&gt;""),(N(G151)+N(H151))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G151&lt;&gt;"",H151&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G151&lt;&gt;"",N(G151)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G151&lt;&gt;"",H151&lt;&gt;""),(N(G151)+N(H151))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G151&lt;&gt;"",N(G151)&lt;='설정'!$E$8),AND(H151&lt;&gt;"",N(H151)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G151&lt;&gt;"",H151&lt;&gt;""),(N(G151)+N(H151))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L151" s="29">
-        <f>IF(OR(G151="",H151=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G151-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H151-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G151="",H151=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G151-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G151+H151)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G151+H151)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G151-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H151-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M151" s="7" t="n"/>
@@ -32283,11 +32280,11 @@
         <v/>
       </c>
       <c r="K152" s="27">
-        <f>IF(I152="","",IF(OR(G152="",H152=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G152&gt;='설정'!$C$6),OR('설정'!$D$6="",G152&lt;'설정'!$D$6),OR('설정'!$E$6="",H152&gt;='설정'!$E$6),OR('설정'!$F$6="",H152&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G152&gt;='설정'!$C$7),OR('설정'!$D$7="",G152&lt;'설정'!$D$7),OR('설정'!$E$7="",H152&gt;='설정'!$E$7),OR('설정'!$F$7="",H152&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G152&gt;='설정'!$C$8),OR('설정'!$D$8="",G152&lt;'설정'!$D$8),OR('설정'!$E$8="",H152&gt;='설정'!$E$8),OR('설정'!$F$8="",H152&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I152="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G152&lt;&gt;"",H152&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G152&lt;&gt;"",N(G152)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G152&lt;&gt;"",H152&lt;&gt;""),(N(G152)+N(H152))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G152&lt;&gt;"",N(G152)&lt;='설정'!$E$6),AND(H152&lt;&gt;"",N(H152)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G152&lt;&gt;"",H152&lt;&gt;""),(N(G152)+N(H152))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G152&lt;&gt;"",H152&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G152&lt;&gt;"",N(G152)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G152&lt;&gt;"",H152&lt;&gt;""),(N(G152)+N(H152))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G152&lt;&gt;"",N(G152)&lt;='설정'!$E$7),AND(H152&lt;&gt;"",N(H152)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G152&lt;&gt;"",H152&lt;&gt;""),(N(G152)+N(H152))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G152&lt;&gt;"",H152&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G152&lt;&gt;"",N(G152)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G152&lt;&gt;"",H152&lt;&gt;""),(N(G152)+N(H152))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G152&lt;&gt;"",N(G152)&lt;='설정'!$E$8),AND(H152&lt;&gt;"",N(H152)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G152&lt;&gt;"",H152&lt;&gt;""),(N(G152)+N(H152))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L152" s="29">
-        <f>IF(OR(G152="",H152=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G152-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H152-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G152="",H152=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G152-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G152+H152)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G152+H152)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G152-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H152-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M152" s="7" t="n"/>
@@ -32346,11 +32343,11 @@
         <v/>
       </c>
       <c r="K153" s="27">
-        <f>IF(I153="","",IF(OR(G153="",H153=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G153&gt;='설정'!$C$6),OR('설정'!$D$6="",G153&lt;'설정'!$D$6),OR('설정'!$E$6="",H153&gt;='설정'!$E$6),OR('설정'!$F$6="",H153&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G153&gt;='설정'!$C$7),OR('설정'!$D$7="",G153&lt;'설정'!$D$7),OR('설정'!$E$7="",H153&gt;='설정'!$E$7),OR('설정'!$F$7="",H153&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G153&gt;='설정'!$C$8),OR('설정'!$D$8="",G153&lt;'설정'!$D$8),OR('설정'!$E$8="",H153&gt;='설정'!$E$8),OR('설정'!$F$8="",H153&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I153="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G153&lt;&gt;"",H153&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G153&lt;&gt;"",N(G153)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G153&lt;&gt;"",H153&lt;&gt;""),(N(G153)+N(H153))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G153&lt;&gt;"",N(G153)&lt;='설정'!$E$6),AND(H153&lt;&gt;"",N(H153)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G153&lt;&gt;"",H153&lt;&gt;""),(N(G153)+N(H153))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G153&lt;&gt;"",H153&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G153&lt;&gt;"",N(G153)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G153&lt;&gt;"",H153&lt;&gt;""),(N(G153)+N(H153))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G153&lt;&gt;"",N(G153)&lt;='설정'!$E$7),AND(H153&lt;&gt;"",N(H153)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G153&lt;&gt;"",H153&lt;&gt;""),(N(G153)+N(H153))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G153&lt;&gt;"",H153&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G153&lt;&gt;"",N(G153)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G153&lt;&gt;"",H153&lt;&gt;""),(N(G153)+N(H153))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G153&lt;&gt;"",N(G153)&lt;='설정'!$E$8),AND(H153&lt;&gt;"",N(H153)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G153&lt;&gt;"",H153&lt;&gt;""),(N(G153)+N(H153))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L153" s="29">
-        <f>IF(OR(G153="",H153=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G153-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H153-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G153="",H153=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G153-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G153+H153)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G153+H153)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G153-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H153-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M153" s="7" t="n"/>
@@ -32409,11 +32406,11 @@
         <v/>
       </c>
       <c r="K154" s="27">
-        <f>IF(I154="","",IF(OR(G154="",H154=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G154&gt;='설정'!$C$6),OR('설정'!$D$6="",G154&lt;'설정'!$D$6),OR('설정'!$E$6="",H154&gt;='설정'!$E$6),OR('설정'!$F$6="",H154&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G154&gt;='설정'!$C$7),OR('설정'!$D$7="",G154&lt;'설정'!$D$7),OR('설정'!$E$7="",H154&gt;='설정'!$E$7),OR('설정'!$F$7="",H154&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G154&gt;='설정'!$C$8),OR('설정'!$D$8="",G154&lt;'설정'!$D$8),OR('설정'!$E$8="",H154&gt;='설정'!$E$8),OR('설정'!$F$8="",H154&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I154="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G154&lt;&gt;"",H154&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G154&lt;&gt;"",N(G154)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G154&lt;&gt;"",H154&lt;&gt;""),(N(G154)+N(H154))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G154&lt;&gt;"",N(G154)&lt;='설정'!$E$6),AND(H154&lt;&gt;"",N(H154)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G154&lt;&gt;"",H154&lt;&gt;""),(N(G154)+N(H154))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G154&lt;&gt;"",H154&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G154&lt;&gt;"",N(G154)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G154&lt;&gt;"",H154&lt;&gt;""),(N(G154)+N(H154))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G154&lt;&gt;"",N(G154)&lt;='설정'!$E$7),AND(H154&lt;&gt;"",N(H154)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G154&lt;&gt;"",H154&lt;&gt;""),(N(G154)+N(H154))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G154&lt;&gt;"",H154&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G154&lt;&gt;"",N(G154)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G154&lt;&gt;"",H154&lt;&gt;""),(N(G154)+N(H154))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G154&lt;&gt;"",N(G154)&lt;='설정'!$E$8),AND(H154&lt;&gt;"",N(H154)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G154&lt;&gt;"",H154&lt;&gt;""),(N(G154)+N(H154))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L154" s="29">
-        <f>IF(OR(G154="",H154=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G154-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H154-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G154="",H154=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G154-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G154+H154)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G154+H154)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G154-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H154-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M154" s="7" t="n"/>
@@ -32472,11 +32469,11 @@
         <v/>
       </c>
       <c r="K155" s="27">
-        <f>IF(I155="","",IF(OR(G155="",H155=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G155&gt;='설정'!$C$6),OR('설정'!$D$6="",G155&lt;'설정'!$D$6),OR('설정'!$E$6="",H155&gt;='설정'!$E$6),OR('설정'!$F$6="",H155&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G155&gt;='설정'!$C$7),OR('설정'!$D$7="",G155&lt;'설정'!$D$7),OR('설정'!$E$7="",H155&gt;='설정'!$E$7),OR('설정'!$F$7="",H155&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G155&gt;='설정'!$C$8),OR('설정'!$D$8="",G155&lt;'설정'!$D$8),OR('설정'!$E$8="",H155&gt;='설정'!$E$8),OR('설정'!$F$8="",H155&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I155="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G155&lt;&gt;"",H155&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G155&lt;&gt;"",N(G155)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G155&lt;&gt;"",H155&lt;&gt;""),(N(G155)+N(H155))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G155&lt;&gt;"",N(G155)&lt;='설정'!$E$6),AND(H155&lt;&gt;"",N(H155)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G155&lt;&gt;"",H155&lt;&gt;""),(N(G155)+N(H155))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G155&lt;&gt;"",H155&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G155&lt;&gt;"",N(G155)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G155&lt;&gt;"",H155&lt;&gt;""),(N(G155)+N(H155))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G155&lt;&gt;"",N(G155)&lt;='설정'!$E$7),AND(H155&lt;&gt;"",N(H155)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G155&lt;&gt;"",H155&lt;&gt;""),(N(G155)+N(H155))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G155&lt;&gt;"",H155&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G155&lt;&gt;"",N(G155)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G155&lt;&gt;"",H155&lt;&gt;""),(N(G155)+N(H155))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G155&lt;&gt;"",N(G155)&lt;='설정'!$E$8),AND(H155&lt;&gt;"",N(H155)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G155&lt;&gt;"",H155&lt;&gt;""),(N(G155)+N(H155))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L155" s="29">
-        <f>IF(OR(G155="",H155=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G155-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H155-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G155="",H155=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G155-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G155+H155)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G155+H155)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G155-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H155-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M155" s="7" t="n"/>
@@ -32535,11 +32532,11 @@
         <v/>
       </c>
       <c r="K156" s="27">
-        <f>IF(I156="","",IF(OR(G156="",H156=""),'설정'!$B$9,IF(AND(OR('설정'!$C$6="",G156&gt;='설정'!$C$6),OR('설정'!$D$6="",G156&lt;'설정'!$D$6),OR('설정'!$E$6="",H156&gt;='설정'!$E$6),OR('설정'!$F$6="",H156&lt;'설정'!$F$6)),'설정'!$B$6,IF(AND(OR('설정'!$C$7="",G156&gt;='설정'!$C$7),OR('설정'!$D$7="",G156&lt;'설정'!$D$7),OR('설정'!$E$7="",H156&gt;='설정'!$E$7),OR('설정'!$F$7="",H156&lt;'설정'!$F$7)),'설정'!$B$7,IF(AND(OR('설정'!$C$8="",G156&gt;='설정'!$C$8),OR('설정'!$D$8="",G156&lt;'설정'!$D$8),OR('설정'!$E$8="",H156&gt;='설정'!$E$8),OR('설정'!$F$8="",H156&lt;'설정'!$F$8)),'설정'!$B$8,'설정'!$B$9)))))</f>
+        <f>IF(I156="","",IF(IF(COUNT('설정'!$C$6:$F$6)=0,AND(G156&lt;&gt;"",H156&lt;&gt;""),OR(AND('설정'!$C$6&lt;&gt;"",G156&lt;&gt;"",N(G156)&gt;='설정'!$C$6),AND('설정'!$D$6&lt;&gt;"",AND(G156&lt;&gt;"",H156&lt;&gt;""),(N(G156)+N(H156))&gt;='설정'!$D$6),AND('설정'!$E$6&lt;&gt;"",OR(AND(G156&lt;&gt;"",N(G156)&lt;='설정'!$E$6),AND(H156&lt;&gt;"",N(H156)&lt;='설정'!$E$6))),AND('설정'!$F$6&lt;&gt;"",AND(G156&lt;&gt;"",H156&lt;&gt;""),(N(G156)+N(H156))&lt;='설정'!$F$6))),'설정'!$B$6,IF(IF(COUNT('설정'!$C$7:$F$7)=0,AND(G156&lt;&gt;"",H156&lt;&gt;""),OR(AND('설정'!$C$7&lt;&gt;"",G156&lt;&gt;"",N(G156)&gt;='설정'!$C$7),AND('설정'!$D$7&lt;&gt;"",AND(G156&lt;&gt;"",H156&lt;&gt;""),(N(G156)+N(H156))&gt;='설정'!$D$7),AND('설정'!$E$7&lt;&gt;"",OR(AND(G156&lt;&gt;"",N(G156)&lt;='설정'!$E$7),AND(H156&lt;&gt;"",N(H156)&lt;='설정'!$E$7))),AND('설정'!$F$7&lt;&gt;"",AND(G156&lt;&gt;"",H156&lt;&gt;""),(N(G156)+N(H156))&lt;='설정'!$F$7))),'설정'!$B$7,IF(IF(COUNT('설정'!$C$8:$F$8)=0,AND(G156&lt;&gt;"",H156&lt;&gt;""),OR(AND('설정'!$C$8&lt;&gt;"",G156&lt;&gt;"",N(G156)&gt;='설정'!$C$8),AND('설정'!$D$8&lt;&gt;"",AND(G156&lt;&gt;"",H156&lt;&gt;""),(N(G156)+N(H156))&gt;='설정'!$D$8),AND('설정'!$E$8&lt;&gt;"",OR(AND(G156&lt;&gt;"",N(G156)&lt;='설정'!$E$8),AND(H156&lt;&gt;"",N(H156)&lt;='설정'!$E$8))),AND('설정'!$F$8&lt;&gt;"",AND(G156&lt;&gt;"",H156&lt;&gt;""),(N(G156)+N(H156))&lt;='설정'!$F$8))),'설정'!$B$8,'설정'!$B$9))))</f>
         <v/>
       </c>
       <c r="L156" s="29">
-        <f>IF(OR(G156="",H156=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$D$8)*(ABS(G156-'설정'!$C$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$F$8)*(ABS(H156-'설정'!$E$6:$F$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
+        <f>IF(OR(G156="",H156=""),"",IF(SUMPRODUCT(ISNUMBER('설정'!$C$6:$C$8)*(ABS(G156-'설정'!$C$6:$C$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$D$6:$D$8)*(ABS((G156+H156)-'설정'!$D$6:$D$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$F$6:$F$8)*(ABS((G156+H156)-'설정'!$F$6:$F$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(G156-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))+SUMPRODUCT(ISNUMBER('설정'!$E$6:$E$8)*(ABS(H156-'설정'!$E$6:$E$8)&lt;='설정'!$C$15))&gt;0,"경계",""))</f>
         <v/>
       </c>
       <c r="M156" s="7" t="n"/>

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -874,7 +874,7 @@
           <t>· 점수(100점 만점)로 판정. 한 줄 안의 조건은 '하나라도' 맞으면 그 반(또는)
 · 위 순위부터 차례로 확인해 처음 맞는 반에 배정, 조건이 모두 빈 줄은 '나머지'
 · 합계 = 공수1 + 공수2, 한 과목 이하 = 공수1·공수2 중 하나라도 그 점수 이하
-· 예) TF1반: 공수1 51점 이상 또는 합계 120점 이상</t>
+· 예) TF1반: 공수1 55점 이상 또는 합계 115점 이상</t>
         </is>
       </c>
     </row>
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -41471,7 +41471,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>변별도 = TF1반 정답률 − TF3반 정답률(자동배정 기준, 0.3 이상이면 상·하위를 잘 가르는 문항). 객관식은 선지별 선택 인원으로 매력적 오답을 확인하세요.</t>
+          <t>변별도 = TF1반 정답률 − HF반 정답률(자동배정 기준, 0.3 이상이면 상·하위를 잘 가르는 문항). 객관식은 선지별 선택 인원으로 매력적 오답을 확인하세요.</t>
         </is>
       </c>
     </row>
@@ -41626,7 +41626,7 @@
         <v/>
       </c>
       <c r="M6" s="43">
-        <f>IF(OR(J6="",L6=""),"",J6-L6)</f>
+        <f>IF(OR(J6="",K6=""),"",J6-K6)</f>
         <v/>
       </c>
       <c r="N6" s="39">
@@ -41704,7 +41704,7 @@
         <v/>
       </c>
       <c r="M7" s="43">
-        <f>IF(OR(J7="",L7=""),"",J7-L7)</f>
+        <f>IF(OR(J7="",K7=""),"",J7-K7)</f>
         <v/>
       </c>
       <c r="N7" s="39">
@@ -41782,7 +41782,7 @@
         <v/>
       </c>
       <c r="M8" s="43">
-        <f>IF(OR(J8="",L8=""),"",J8-L8)</f>
+        <f>IF(OR(J8="",K8=""),"",J8-K8)</f>
         <v/>
       </c>
       <c r="N8" s="39">
@@ -41860,7 +41860,7 @@
         <v/>
       </c>
       <c r="M9" s="43">
-        <f>IF(OR(J9="",L9=""),"",J9-L9)</f>
+        <f>IF(OR(J9="",K9=""),"",J9-K9)</f>
         <v/>
       </c>
       <c r="N9" s="39">
@@ -41938,7 +41938,7 @@
         <v/>
       </c>
       <c r="M10" s="43">
-        <f>IF(OR(J10="",L10=""),"",J10-L10)</f>
+        <f>IF(OR(J10="",K10=""),"",J10-K10)</f>
         <v/>
       </c>
       <c r="N10" s="39">
@@ -42016,7 +42016,7 @@
         <v/>
       </c>
       <c r="M11" s="43">
-        <f>IF(OR(J11="",L11=""),"",J11-L11)</f>
+        <f>IF(OR(J11="",K11=""),"",J11-K11)</f>
         <v/>
       </c>
       <c r="N11" s="39">
@@ -42094,7 +42094,7 @@
         <v/>
       </c>
       <c r="M12" s="43">
-        <f>IF(OR(J12="",L12=""),"",J12-L12)</f>
+        <f>IF(OR(J12="",K12=""),"",J12-K12)</f>
         <v/>
       </c>
       <c r="N12" s="39">
@@ -42172,7 +42172,7 @@
         <v/>
       </c>
       <c r="M13" s="43">
-        <f>IF(OR(J13="",L13=""),"",J13-L13)</f>
+        <f>IF(OR(J13="",K13=""),"",J13-K13)</f>
         <v/>
       </c>
       <c r="N13" s="39">
@@ -42250,7 +42250,7 @@
         <v/>
       </c>
       <c r="M14" s="43">
-        <f>IF(OR(J14="",L14=""),"",J14-L14)</f>
+        <f>IF(OR(J14="",K14=""),"",J14-K14)</f>
         <v/>
       </c>
       <c r="N14" s="39">
@@ -42328,7 +42328,7 @@
         <v/>
       </c>
       <c r="M15" s="43">
-        <f>IF(OR(J15="",L15=""),"",J15-L15)</f>
+        <f>IF(OR(J15="",K15=""),"",J15-K15)</f>
         <v/>
       </c>
       <c r="N15" s="39">
@@ -42406,7 +42406,7 @@
         <v/>
       </c>
       <c r="M16" s="43">
-        <f>IF(OR(J16="",L16=""),"",J16-L16)</f>
+        <f>IF(OR(J16="",K16=""),"",J16-K16)</f>
         <v/>
       </c>
       <c r="N16" s="39">
@@ -42484,7 +42484,7 @@
         <v/>
       </c>
       <c r="M17" s="43">
-        <f>IF(OR(J17="",L17=""),"",J17-L17)</f>
+        <f>IF(OR(J17="",K17=""),"",J17-K17)</f>
         <v/>
       </c>
       <c r="N17" s="39">
@@ -42562,7 +42562,7 @@
         <v/>
       </c>
       <c r="M18" s="43">
-        <f>IF(OR(J18="",L18=""),"",J18-L18)</f>
+        <f>IF(OR(J18="",K18=""),"",J18-K18)</f>
         <v/>
       </c>
       <c r="N18" s="39">
@@ -42640,7 +42640,7 @@
         <v/>
       </c>
       <c r="M19" s="43">
-        <f>IF(OR(J19="",L19=""),"",J19-L19)</f>
+        <f>IF(OR(J19="",K19=""),"",J19-K19)</f>
         <v/>
       </c>
       <c r="N19" s="39">
@@ -42718,7 +42718,7 @@
         <v/>
       </c>
       <c r="M20" s="43">
-        <f>IF(OR(J20="",L20=""),"",J20-L20)</f>
+        <f>IF(OR(J20="",K20=""),"",J20-K20)</f>
         <v/>
       </c>
       <c r="N20" s="39">
@@ -42801,7 +42801,7 @@
         <v/>
       </c>
       <c r="M21" s="43">
-        <f>IF(OR(J21="",L21=""),"",J21-L21)</f>
+        <f>IF(OR(J21="",K21=""),"",J21-K21)</f>
         <v/>
       </c>
       <c r="N21" s="39">
@@ -42884,7 +42884,7 @@
         <v/>
       </c>
       <c r="M22" s="43">
-        <f>IF(OR(J22="",L22=""),"",J22-L22)</f>
+        <f>IF(OR(J22="",K22=""),"",J22-K22)</f>
         <v/>
       </c>
       <c r="N22" s="39">
@@ -42967,7 +42967,7 @@
         <v/>
       </c>
       <c r="M23" s="43">
-        <f>IF(OR(J23="",L23=""),"",J23-L23)</f>
+        <f>IF(OR(J23="",K23=""),"",J23-K23)</f>
         <v/>
       </c>
       <c r="N23" s="39">
@@ -43050,7 +43050,7 @@
         <v/>
       </c>
       <c r="M24" s="43">
-        <f>IF(OR(J24="",L24=""),"",J24-L24)</f>
+        <f>IF(OR(J24="",K24=""),"",J24-K24)</f>
         <v/>
       </c>
       <c r="N24" s="39">
@@ -43133,7 +43133,7 @@
         <v/>
       </c>
       <c r="M25" s="43">
-        <f>IF(OR(J25="",L25=""),"",J25-L25)</f>
+        <f>IF(OR(J25="",K25=""),"",J25-K25)</f>
         <v/>
       </c>
       <c r="N25" s="39">
@@ -43317,7 +43317,7 @@
         <v/>
       </c>
       <c r="M30" s="43">
-        <f>IF(OR(J30="",L30=""),"",J30-L30)</f>
+        <f>IF(OR(J30="",K30=""),"",J30-K30)</f>
         <v/>
       </c>
       <c r="N30" s="39">
@@ -43395,7 +43395,7 @@
         <v/>
       </c>
       <c r="M31" s="43">
-        <f>IF(OR(J31="",L31=""),"",J31-L31)</f>
+        <f>IF(OR(J31="",K31=""),"",J31-K31)</f>
         <v/>
       </c>
       <c r="N31" s="39">
@@ -43473,7 +43473,7 @@
         <v/>
       </c>
       <c r="M32" s="43">
-        <f>IF(OR(J32="",L32=""),"",J32-L32)</f>
+        <f>IF(OR(J32="",K32=""),"",J32-K32)</f>
         <v/>
       </c>
       <c r="N32" s="39">
@@ -43551,7 +43551,7 @@
         <v/>
       </c>
       <c r="M33" s="43">
-        <f>IF(OR(J33="",L33=""),"",J33-L33)</f>
+        <f>IF(OR(J33="",K33=""),"",J33-K33)</f>
         <v/>
       </c>
       <c r="N33" s="39">
@@ -43629,7 +43629,7 @@
         <v/>
       </c>
       <c r="M34" s="43">
-        <f>IF(OR(J34="",L34=""),"",J34-L34)</f>
+        <f>IF(OR(J34="",K34=""),"",J34-K34)</f>
         <v/>
       </c>
       <c r="N34" s="39">
@@ -43707,7 +43707,7 @@
         <v/>
       </c>
       <c r="M35" s="43">
-        <f>IF(OR(J35="",L35=""),"",J35-L35)</f>
+        <f>IF(OR(J35="",K35=""),"",J35-K35)</f>
         <v/>
       </c>
       <c r="N35" s="39">
@@ -43785,7 +43785,7 @@
         <v/>
       </c>
       <c r="M36" s="43">
-        <f>IF(OR(J36="",L36=""),"",J36-L36)</f>
+        <f>IF(OR(J36="",K36=""),"",J36-K36)</f>
         <v/>
       </c>
       <c r="N36" s="39">
@@ -43863,7 +43863,7 @@
         <v/>
       </c>
       <c r="M37" s="43">
-        <f>IF(OR(J37="",L37=""),"",J37-L37)</f>
+        <f>IF(OR(J37="",K37=""),"",J37-K37)</f>
         <v/>
       </c>
       <c r="N37" s="39">
@@ -43941,7 +43941,7 @@
         <v/>
       </c>
       <c r="M38" s="43">
-        <f>IF(OR(J38="",L38=""),"",J38-L38)</f>
+        <f>IF(OR(J38="",K38=""),"",J38-K38)</f>
         <v/>
       </c>
       <c r="N38" s="39">
@@ -44019,7 +44019,7 @@
         <v/>
       </c>
       <c r="M39" s="43">
-        <f>IF(OR(J39="",L39=""),"",J39-L39)</f>
+        <f>IF(OR(J39="",K39=""),"",J39-K39)</f>
         <v/>
       </c>
       <c r="N39" s="39">
@@ -44097,7 +44097,7 @@
         <v/>
       </c>
       <c r="M40" s="43">
-        <f>IF(OR(J40="",L40=""),"",J40-L40)</f>
+        <f>IF(OR(J40="",K40=""),"",J40-K40)</f>
         <v/>
       </c>
       <c r="N40" s="39">
@@ -44175,7 +44175,7 @@
         <v/>
       </c>
       <c r="M41" s="43">
-        <f>IF(OR(J41="",L41=""),"",J41-L41)</f>
+        <f>IF(OR(J41="",K41=""),"",J41-K41)</f>
         <v/>
       </c>
       <c r="N41" s="39">
@@ -44253,7 +44253,7 @@
         <v/>
       </c>
       <c r="M42" s="43">
-        <f>IF(OR(J42="",L42=""),"",J42-L42)</f>
+        <f>IF(OR(J42="",K42=""),"",J42-K42)</f>
         <v/>
       </c>
       <c r="N42" s="39">
@@ -44331,7 +44331,7 @@
         <v/>
       </c>
       <c r="M43" s="43">
-        <f>IF(OR(J43="",L43=""),"",J43-L43)</f>
+        <f>IF(OR(J43="",K43=""),"",J43-K43)</f>
         <v/>
       </c>
       <c r="N43" s="39">
@@ -44409,7 +44409,7 @@
         <v/>
       </c>
       <c r="M44" s="43">
-        <f>IF(OR(J44="",L44=""),"",J44-L44)</f>
+        <f>IF(OR(J44="",K44=""),"",J44-K44)</f>
         <v/>
       </c>
       <c r="N44" s="39">
@@ -44492,7 +44492,7 @@
         <v/>
       </c>
       <c r="M45" s="43">
-        <f>IF(OR(J45="",L45=""),"",J45-L45)</f>
+        <f>IF(OR(J45="",K45=""),"",J45-K45)</f>
         <v/>
       </c>
       <c r="N45" s="39">
@@ -44575,7 +44575,7 @@
         <v/>
       </c>
       <c r="M46" s="43">
-        <f>IF(OR(J46="",L46=""),"",J46-L46)</f>
+        <f>IF(OR(J46="",K46=""),"",J46-K46)</f>
         <v/>
       </c>
       <c r="N46" s="39">
@@ -44658,7 +44658,7 @@
         <v/>
       </c>
       <c r="M47" s="43">
-        <f>IF(OR(J47="",L47=""),"",J47-L47)</f>
+        <f>IF(OR(J47="",K47=""),"",J47-K47)</f>
         <v/>
       </c>
       <c r="N47" s="39">
@@ -44741,7 +44741,7 @@
         <v/>
       </c>
       <c r="M48" s="43">
-        <f>IF(OR(J48="",L48=""),"",J48-L48)</f>
+        <f>IF(OR(J48="",K48=""),"",J48-K48)</f>
         <v/>
       </c>
       <c r="N48" s="39">
@@ -44824,7 +44824,7 @@
         <v/>
       </c>
       <c r="M49" s="43">
-        <f>IF(OR(J49="",L49=""),"",J49-L49)</f>
+        <f>IF(OR(J49="",K49=""),"",J49-K49)</f>
         <v/>
       </c>
       <c r="N49" s="39">

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -23006,7 +23006,7 @@
       <c r="M7" s="7" t="n"/>
       <c r="N7" s="7" t="n"/>
       <c r="O7" s="27">
-        <f>IF(M7&lt;&gt;"",M7,K7)</f>
+        <f>IF(M7&lt;&gt;"",M7,IF(OR(K7='설정'!$B$6,K7='설정'!$B$8),SUBSTITUTE(K7,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G7)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G7)),"화목","반")),K7))</f>
         <v/>
       </c>
       <c r="P7" s="30">
@@ -23026,23 +23026,23 @@
         <v/>
       </c>
       <c r="U7" s="27">
-        <f>COUNTIF($O$7:$O$156,S7)</f>
+        <f>COUNTIF($O$7:$O$156,SUBSTITUTE(S7,"반","")&amp;"*")</f>
         <v/>
       </c>
       <c r="V7" s="32">
-        <f>IFERROR(AVERAGEIF($O$7:$O$156,S7,$G$7:$G$156),"")</f>
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,SUBSTITUTE(S7,"반","")&amp;"*",$G$7:$G$156),"")</f>
         <v/>
       </c>
       <c r="W7" s="32">
-        <f>IFERROR(AVERAGEIF($O$7:$O$156,S7,$H$7:$H$156),"")</f>
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,SUBSTITUTE(S7,"반","")&amp;"*",$H$7:$H$156),"")</f>
         <v/>
       </c>
       <c r="X7" s="10">
-        <f>COUNTIFS($O$7:$O$156,S7,$D$7:$D$156,"재원")</f>
+        <f>COUNTIFS($O$7:$O$156,SUBSTITUTE(S7,"반","")&amp;"*",$D$7:$D$156,"재원")</f>
         <v/>
       </c>
       <c r="Y7" s="10">
-        <f>COUNTIFS($O$7:$O$156,S7,$D$7:$D$156,"외부")</f>
+        <f>COUNTIFS($O$7:$O$156,SUBSTITUTE(S7,"반","")&amp;"*",$D$7:$D$156,"외부")</f>
         <v/>
       </c>
     </row>
@@ -23097,7 +23097,7 @@
       <c r="M8" s="7" t="n"/>
       <c r="N8" s="7" t="n"/>
       <c r="O8" s="27">
-        <f>IF(M8&lt;&gt;"",M8,K8)</f>
+        <f>IF(M8&lt;&gt;"",M8,IF(OR(K8='설정'!$B$6,K8='설정'!$B$8),SUBSTITUTE(K8,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G8)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G8)),"화목","반")),K8))</f>
         <v/>
       </c>
       <c r="P8" s="30">
@@ -23117,23 +23117,23 @@
         <v/>
       </c>
       <c r="U8" s="27">
-        <f>COUNTIF($O$7:$O$156,S8)</f>
+        <f>COUNTIF($O$7:$O$156,SUBSTITUTE(S8,"반","")&amp;"*")</f>
         <v/>
       </c>
       <c r="V8" s="32">
-        <f>IFERROR(AVERAGEIF($O$7:$O$156,S8,$G$7:$G$156),"")</f>
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,SUBSTITUTE(S8,"반","")&amp;"*",$G$7:$G$156),"")</f>
         <v/>
       </c>
       <c r="W8" s="32">
-        <f>IFERROR(AVERAGEIF($O$7:$O$156,S8,$H$7:$H$156),"")</f>
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,SUBSTITUTE(S8,"반","")&amp;"*",$H$7:$H$156),"")</f>
         <v/>
       </c>
       <c r="X8" s="10">
-        <f>COUNTIFS($O$7:$O$156,S8,$D$7:$D$156,"재원")</f>
+        <f>COUNTIFS($O$7:$O$156,SUBSTITUTE(S8,"반","")&amp;"*",$D$7:$D$156,"재원")</f>
         <v/>
       </c>
       <c r="Y8" s="10">
-        <f>COUNTIFS($O$7:$O$156,S8,$D$7:$D$156,"외부")</f>
+        <f>COUNTIFS($O$7:$O$156,SUBSTITUTE(S8,"반","")&amp;"*",$D$7:$D$156,"외부")</f>
         <v/>
       </c>
     </row>
@@ -23188,7 +23188,7 @@
       <c r="M9" s="7" t="n"/>
       <c r="N9" s="7" t="n"/>
       <c r="O9" s="27">
-        <f>IF(M9&lt;&gt;"",M9,K9)</f>
+        <f>IF(M9&lt;&gt;"",M9,IF(OR(K9='설정'!$B$6,K9='설정'!$B$8),SUBSTITUTE(K9,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G9)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G9)),"화목","반")),K9))</f>
         <v/>
       </c>
       <c r="P9" s="30">
@@ -23208,23 +23208,23 @@
         <v/>
       </c>
       <c r="U9" s="27">
-        <f>COUNTIF($O$7:$O$156,S9)</f>
+        <f>COUNTIF($O$7:$O$156,SUBSTITUTE(S9,"반","")&amp;"*")</f>
         <v/>
       </c>
       <c r="V9" s="32">
-        <f>IFERROR(AVERAGEIF($O$7:$O$156,S9,$G$7:$G$156),"")</f>
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,SUBSTITUTE(S9,"반","")&amp;"*",$G$7:$G$156),"")</f>
         <v/>
       </c>
       <c r="W9" s="32">
-        <f>IFERROR(AVERAGEIF($O$7:$O$156,S9,$H$7:$H$156),"")</f>
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,SUBSTITUTE(S9,"반","")&amp;"*",$H$7:$H$156),"")</f>
         <v/>
       </c>
       <c r="X9" s="10">
-        <f>COUNTIFS($O$7:$O$156,S9,$D$7:$D$156,"재원")</f>
+        <f>COUNTIFS($O$7:$O$156,SUBSTITUTE(S9,"반","")&amp;"*",$D$7:$D$156,"재원")</f>
         <v/>
       </c>
       <c r="Y9" s="10">
-        <f>COUNTIFS($O$7:$O$156,S9,$D$7:$D$156,"외부")</f>
+        <f>COUNTIFS($O$7:$O$156,SUBSTITUTE(S9,"반","")&amp;"*",$D$7:$D$156,"외부")</f>
         <v/>
       </c>
     </row>
@@ -23279,7 +23279,7 @@
       <c r="M10" s="7" t="n"/>
       <c r="N10" s="7" t="n"/>
       <c r="O10" s="27">
-        <f>IF(M10&lt;&gt;"",M10,K10)</f>
+        <f>IF(M10&lt;&gt;"",M10,IF(OR(K10='설정'!$B$6,K10='설정'!$B$8),SUBSTITUTE(K10,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G10)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G10)),"화목","반")),K10))</f>
         <v/>
       </c>
       <c r="P10" s="30">
@@ -23299,23 +23299,23 @@
         <v/>
       </c>
       <c r="U10" s="27">
-        <f>COUNTIF($O$7:$O$156,S10)</f>
+        <f>COUNTIF($O$7:$O$156,SUBSTITUTE(S10,"반","")&amp;"*")</f>
         <v/>
       </c>
       <c r="V10" s="32">
-        <f>IFERROR(AVERAGEIF($O$7:$O$156,S10,$G$7:$G$156),"")</f>
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,SUBSTITUTE(S10,"반","")&amp;"*",$G$7:$G$156),"")</f>
         <v/>
       </c>
       <c r="W10" s="32">
-        <f>IFERROR(AVERAGEIF($O$7:$O$156,S10,$H$7:$H$156),"")</f>
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,SUBSTITUTE(S10,"반","")&amp;"*",$H$7:$H$156),"")</f>
         <v/>
       </c>
       <c r="X10" s="10">
-        <f>COUNTIFS($O$7:$O$156,S10,$D$7:$D$156,"재원")</f>
+        <f>COUNTIFS($O$7:$O$156,SUBSTITUTE(S10,"반","")&amp;"*",$D$7:$D$156,"재원")</f>
         <v/>
       </c>
       <c r="Y10" s="10">
-        <f>COUNTIFS($O$7:$O$156,S10,$D$7:$D$156,"외부")</f>
+        <f>COUNTIFS($O$7:$O$156,SUBSTITUTE(S10,"반","")&amp;"*",$D$7:$D$156,"외부")</f>
         <v/>
       </c>
     </row>
@@ -23370,7 +23370,7 @@
       <c r="M11" s="7" t="n"/>
       <c r="N11" s="7" t="n"/>
       <c r="O11" s="27">
-        <f>IF(M11&lt;&gt;"",M11,K11)</f>
+        <f>IF(M11&lt;&gt;"",M11,IF(OR(K11='설정'!$B$6,K11='설정'!$B$8),SUBSTITUTE(K11,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G11)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G11)),"화목","반")),K11))</f>
         <v/>
       </c>
       <c r="P11" s="30">
@@ -23462,7 +23462,7 @@
       <c r="M12" s="7" t="n"/>
       <c r="N12" s="7" t="n"/>
       <c r="O12" s="27">
-        <f>IF(M12&lt;&gt;"",M12,K12)</f>
+        <f>IF(M12&lt;&gt;"",M12,IF(OR(K12='설정'!$B$6,K12='설정'!$B$8),SUBSTITUTE(K12,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G12)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G12)),"화목","반")),K12))</f>
         <v/>
       </c>
       <c r="P12" s="30">
@@ -23525,7 +23525,7 @@
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n"/>
       <c r="O13" s="27">
-        <f>IF(M13&lt;&gt;"",M13,K13)</f>
+        <f>IF(M13&lt;&gt;"",M13,IF(OR(K13='설정'!$B$6,K13='설정'!$B$8),SUBSTITUTE(K13,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G13)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G13)),"화목","반")),K13))</f>
         <v/>
       </c>
       <c r="P13" s="30">
@@ -23540,6 +23540,7 @@
         <is>
           <t>· 자동배정은 '설정' ①의 기준(공수1 점수·한 과목 점수·합계)
 · 경계 = 과목 점수나 합계가 기준 점수와 경계 범위 이내
+· 공통수학반(최종): TF1·TF2는 현재 등원 요일에 따라 월금/화목 반(예: TF1월금, TF2화목)
 · 공통수학반·선행반은 목록에서 고르거나 직접 입력('설정' ⑥·⑦에 반 소개 추가 가능)
 · 환산총점·석차는 참고용</t>
         </is>
@@ -23596,7 +23597,7 @@
       <c r="M14" s="7" t="n"/>
       <c r="N14" s="7" t="n"/>
       <c r="O14" s="27">
-        <f>IF(M14&lt;&gt;"",M14,K14)</f>
+        <f>IF(M14&lt;&gt;"",M14,IF(OR(K14='설정'!$B$6,K14='설정'!$B$8),SUBSTITUTE(K14,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G14)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G14)),"화목","반")),K14))</f>
         <v/>
       </c>
       <c r="P14" s="30">
@@ -23659,7 +23660,7 @@
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
       <c r="O15" s="27">
-        <f>IF(M15&lt;&gt;"",M15,K15)</f>
+        <f>IF(M15&lt;&gt;"",M15,IF(OR(K15='설정'!$B$6,K15='설정'!$B$8),SUBSTITUTE(K15,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G15)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G15)),"화목","반")),K15))</f>
         <v/>
       </c>
       <c r="P15" s="30">
@@ -23722,7 +23723,7 @@
       <c r="M16" s="7" t="n"/>
       <c r="N16" s="7" t="n"/>
       <c r="O16" s="27">
-        <f>IF(M16&lt;&gt;"",M16,K16)</f>
+        <f>IF(M16&lt;&gt;"",M16,IF(OR(K16='설정'!$B$6,K16='설정'!$B$8),SUBSTITUTE(K16,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G16)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G16)),"화목","반")),K16))</f>
         <v/>
       </c>
       <c r="P16" s="30">
@@ -23785,7 +23786,7 @@
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="7" t="n"/>
       <c r="O17" s="27">
-        <f>IF(M17&lt;&gt;"",M17,K17)</f>
+        <f>IF(M17&lt;&gt;"",M17,IF(OR(K17='설정'!$B$6,K17='설정'!$B$8),SUBSTITUTE(K17,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G17)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G17)),"화목","반")),K17))</f>
         <v/>
       </c>
       <c r="P17" s="30">
@@ -23848,7 +23849,7 @@
       <c r="M18" s="7" t="n"/>
       <c r="N18" s="7" t="n"/>
       <c r="O18" s="27">
-        <f>IF(M18&lt;&gt;"",M18,K18)</f>
+        <f>IF(M18&lt;&gt;"",M18,IF(OR(K18='설정'!$B$6,K18='설정'!$B$8),SUBSTITUTE(K18,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G18)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G18)),"화목","반")),K18))</f>
         <v/>
       </c>
       <c r="P18" s="30">
@@ -23911,7 +23912,7 @@
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n"/>
       <c r="O19" s="27">
-        <f>IF(M19&lt;&gt;"",M19,K19)</f>
+        <f>IF(M19&lt;&gt;"",M19,IF(OR(K19='설정'!$B$6,K19='설정'!$B$8),SUBSTITUTE(K19,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G19)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G19)),"화목","반")),K19))</f>
         <v/>
       </c>
       <c r="P19" s="30">
@@ -23974,7 +23975,7 @@
       <c r="M20" s="7" t="n"/>
       <c r="N20" s="7" t="n"/>
       <c r="O20" s="27">
-        <f>IF(M20&lt;&gt;"",M20,K20)</f>
+        <f>IF(M20&lt;&gt;"",M20,IF(OR(K20='설정'!$B$6,K20='설정'!$B$8),SUBSTITUTE(K20,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G20)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G20)),"화목","반")),K20))</f>
         <v/>
       </c>
       <c r="P20" s="30">
@@ -23984,6 +23985,11 @@
       <c r="Q20" s="10">
         <f>IF(J20="","",J20+ROW()/100000)</f>
         <v/>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t>요일반별 인원 (최종 기준)</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -24037,7 +24043,7 @@
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n"/>
       <c r="O21" s="27">
-        <f>IF(M21&lt;&gt;"",M21,K21)</f>
+        <f>IF(M21&lt;&gt;"",M21,IF(OR(K21='설정'!$B$6,K21='설정'!$B$8),SUBSTITUTE(K21,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G21)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G21)),"화목","반")),K21))</f>
         <v/>
       </c>
       <c r="P21" s="30">
@@ -24047,6 +24053,28 @@
       <c r="Q21" s="10">
         <f>IF(J21="","",J21+ROW()/100000)</f>
         <v/>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>반</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>인원</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>공수1
+평균</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>공수2
+평균</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -24100,7 +24128,7 @@
       <c r="M22" s="7" t="n"/>
       <c r="N22" s="7" t="n"/>
       <c r="O22" s="27">
-        <f>IF(M22&lt;&gt;"",M22,K22)</f>
+        <f>IF(M22&lt;&gt;"",M22,IF(OR(K22='설정'!$B$6,K22='설정'!$B$8),SUBSTITUTE(K22,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G22)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G22)),"화목","반")),K22))</f>
         <v/>
       </c>
       <c r="P22" s="30">
@@ -24109,6 +24137,22 @@
       </c>
       <c r="Q22" s="10">
         <f>IF(J22="","",J22+ROW()/100000)</f>
+        <v/>
+      </c>
+      <c r="S22" s="31">
+        <f>SUBSTITUTE('설정'!$B$6,"반","")&amp;"월금"</f>
+        <v/>
+      </c>
+      <c r="T22" s="27">
+        <f>COUNTIF($O$7:$O$156,S22)</f>
+        <v/>
+      </c>
+      <c r="U22" s="32">
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,S22,$G$7:$G$156),"")</f>
+        <v/>
+      </c>
+      <c r="V22" s="32">
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,S22,$H$7:$H$156),"")</f>
         <v/>
       </c>
     </row>
@@ -24163,7 +24207,7 @@
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n"/>
       <c r="O23" s="27">
-        <f>IF(M23&lt;&gt;"",M23,K23)</f>
+        <f>IF(M23&lt;&gt;"",M23,IF(OR(K23='설정'!$B$6,K23='설정'!$B$8),SUBSTITUTE(K23,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G23)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G23)),"화목","반")),K23))</f>
         <v/>
       </c>
       <c r="P23" s="30">
@@ -24172,6 +24216,22 @@
       </c>
       <c r="Q23" s="10">
         <f>IF(J23="","",J23+ROW()/100000)</f>
+        <v/>
+      </c>
+      <c r="S23" s="31">
+        <f>SUBSTITUTE('설정'!$B$6,"반","")&amp;"화목"</f>
+        <v/>
+      </c>
+      <c r="T23" s="27">
+        <f>COUNTIF($O$7:$O$156,S23)</f>
+        <v/>
+      </c>
+      <c r="U23" s="32">
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,S23,$G$7:$G$156),"")</f>
+        <v/>
+      </c>
+      <c r="V23" s="32">
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,S23,$H$7:$H$156),"")</f>
         <v/>
       </c>
     </row>
@@ -24226,7 +24286,7 @@
       <c r="M24" s="7" t="n"/>
       <c r="N24" s="7" t="n"/>
       <c r="O24" s="27">
-        <f>IF(M24&lt;&gt;"",M24,K24)</f>
+        <f>IF(M24&lt;&gt;"",M24,IF(OR(K24='설정'!$B$6,K24='설정'!$B$8),SUBSTITUTE(K24,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G24)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G24)),"화목","반")),K24))</f>
         <v/>
       </c>
       <c r="P24" s="30">
@@ -24235,6 +24295,22 @@
       </c>
       <c r="Q24" s="10">
         <f>IF(J24="","",J24+ROW()/100000)</f>
+        <v/>
+      </c>
+      <c r="S24" s="34">
+        <f>SUBSTITUTE('설정'!$B$8,"반","")&amp;"월금"</f>
+        <v/>
+      </c>
+      <c r="T24" s="27">
+        <f>COUNTIF($O$7:$O$156,S24)</f>
+        <v/>
+      </c>
+      <c r="U24" s="32">
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,S24,$G$7:$G$156),"")</f>
+        <v/>
+      </c>
+      <c r="V24" s="32">
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,S24,$H$7:$H$156),"")</f>
         <v/>
       </c>
     </row>
@@ -24289,7 +24365,7 @@
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
       <c r="O25" s="27">
-        <f>IF(M25&lt;&gt;"",M25,K25)</f>
+        <f>IF(M25&lt;&gt;"",M25,IF(OR(K25='설정'!$B$6,K25='설정'!$B$8),SUBSTITUTE(K25,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G25)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G25)),"화목","반")),K25))</f>
         <v/>
       </c>
       <c r="P25" s="30">
@@ -24298,6 +24374,22 @@
       </c>
       <c r="Q25" s="10">
         <f>IF(J25="","",J25+ROW()/100000)</f>
+        <v/>
+      </c>
+      <c r="S25" s="34">
+        <f>SUBSTITUTE('설정'!$B$8,"반","")&amp;"화목"</f>
+        <v/>
+      </c>
+      <c r="T25" s="27">
+        <f>COUNTIF($O$7:$O$156,S25)</f>
+        <v/>
+      </c>
+      <c r="U25" s="32">
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,S25,$G$7:$G$156),"")</f>
+        <v/>
+      </c>
+      <c r="V25" s="32">
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,S25,$H$7:$H$156),"")</f>
         <v/>
       </c>
     </row>
@@ -24352,7 +24444,7 @@
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="7" t="n"/>
       <c r="O26" s="27">
-        <f>IF(M26&lt;&gt;"",M26,K26)</f>
+        <f>IF(M26&lt;&gt;"",M26,IF(OR(K26='설정'!$B$6,K26='설정'!$B$8),SUBSTITUTE(K26,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G26)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G26)),"화목","반")),K26))</f>
         <v/>
       </c>
       <c r="P26" s="30">
@@ -24415,7 +24507,7 @@
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
       <c r="O27" s="27">
-        <f>IF(M27&lt;&gt;"",M27,K27)</f>
+        <f>IF(M27&lt;&gt;"",M27,IF(OR(K27='설정'!$B$6,K27='설정'!$B$8),SUBSTITUTE(K27,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G27)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G27)),"화목","반")),K27))</f>
         <v/>
       </c>
       <c r="P27" s="30">
@@ -24478,7 +24570,7 @@
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="7" t="n"/>
       <c r="O28" s="27">
-        <f>IF(M28&lt;&gt;"",M28,K28)</f>
+        <f>IF(M28&lt;&gt;"",M28,IF(OR(K28='설정'!$B$6,K28='설정'!$B$8),SUBSTITUTE(K28,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G28)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G28)),"화목","반")),K28))</f>
         <v/>
       </c>
       <c r="P28" s="30">
@@ -24541,7 +24633,7 @@
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
       <c r="O29" s="27">
-        <f>IF(M29&lt;&gt;"",M29,K29)</f>
+        <f>IF(M29&lt;&gt;"",M29,IF(OR(K29='설정'!$B$6,K29='설정'!$B$8),SUBSTITUTE(K29,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G29)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G29)),"화목","반")),K29))</f>
         <v/>
       </c>
       <c r="P29" s="30">
@@ -24604,7 +24696,7 @@
       <c r="M30" s="7" t="n"/>
       <c r="N30" s="7" t="n"/>
       <c r="O30" s="27">
-        <f>IF(M30&lt;&gt;"",M30,K30)</f>
+        <f>IF(M30&lt;&gt;"",M30,IF(OR(K30='설정'!$B$6,K30='설정'!$B$8),SUBSTITUTE(K30,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G30)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G30)),"화목","반")),K30))</f>
         <v/>
       </c>
       <c r="P30" s="30">
@@ -24667,7 +24759,7 @@
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n"/>
       <c r="O31" s="27">
-        <f>IF(M31&lt;&gt;"",M31,K31)</f>
+        <f>IF(M31&lt;&gt;"",M31,IF(OR(K31='설정'!$B$6,K31='설정'!$B$8),SUBSTITUTE(K31,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G31)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G31)),"화목","반")),K31))</f>
         <v/>
       </c>
       <c r="P31" s="30">
@@ -24730,7 +24822,7 @@
       <c r="M32" s="7" t="n"/>
       <c r="N32" s="7" t="n"/>
       <c r="O32" s="27">
-        <f>IF(M32&lt;&gt;"",M32,K32)</f>
+        <f>IF(M32&lt;&gt;"",M32,IF(OR(K32='설정'!$B$6,K32='설정'!$B$8),SUBSTITUTE(K32,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G32)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G32)),"화목","반")),K32))</f>
         <v/>
       </c>
       <c r="P32" s="30">
@@ -24793,7 +24885,7 @@
       <c r="M33" s="7" t="n"/>
       <c r="N33" s="7" t="n"/>
       <c r="O33" s="27">
-        <f>IF(M33&lt;&gt;"",M33,K33)</f>
+        <f>IF(M33&lt;&gt;"",M33,IF(OR(K33='설정'!$B$6,K33='설정'!$B$8),SUBSTITUTE(K33,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G33)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G33)),"화목","반")),K33))</f>
         <v/>
       </c>
       <c r="P33" s="30">
@@ -24856,7 +24948,7 @@
       <c r="M34" s="7" t="n"/>
       <c r="N34" s="7" t="n"/>
       <c r="O34" s="27">
-        <f>IF(M34&lt;&gt;"",M34,K34)</f>
+        <f>IF(M34&lt;&gt;"",M34,IF(OR(K34='설정'!$B$6,K34='설정'!$B$8),SUBSTITUTE(K34,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G34)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G34)),"화목","반")),K34))</f>
         <v/>
       </c>
       <c r="P34" s="30">
@@ -24919,7 +25011,7 @@
       <c r="M35" s="7" t="n"/>
       <c r="N35" s="7" t="n"/>
       <c r="O35" s="27">
-        <f>IF(M35&lt;&gt;"",M35,K35)</f>
+        <f>IF(M35&lt;&gt;"",M35,IF(OR(K35='설정'!$B$6,K35='설정'!$B$8),SUBSTITUTE(K35,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G35)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G35)),"화목","반")),K35))</f>
         <v/>
       </c>
       <c r="P35" s="30">
@@ -24982,7 +25074,7 @@
       <c r="M36" s="7" t="n"/>
       <c r="N36" s="7" t="n"/>
       <c r="O36" s="27">
-        <f>IF(M36&lt;&gt;"",M36,K36)</f>
+        <f>IF(M36&lt;&gt;"",M36,IF(OR(K36='설정'!$B$6,K36='설정'!$B$8),SUBSTITUTE(K36,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G36)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G36)),"화목","반")),K36))</f>
         <v/>
       </c>
       <c r="P36" s="30">
@@ -25045,7 +25137,7 @@
       <c r="M37" s="7" t="n"/>
       <c r="N37" s="7" t="n"/>
       <c r="O37" s="27">
-        <f>IF(M37&lt;&gt;"",M37,K37)</f>
+        <f>IF(M37&lt;&gt;"",M37,IF(OR(K37='설정'!$B$6,K37='설정'!$B$8),SUBSTITUTE(K37,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G37)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G37)),"화목","반")),K37))</f>
         <v/>
       </c>
       <c r="P37" s="30">
@@ -25108,7 +25200,7 @@
       <c r="M38" s="7" t="n"/>
       <c r="N38" s="7" t="n"/>
       <c r="O38" s="27">
-        <f>IF(M38&lt;&gt;"",M38,K38)</f>
+        <f>IF(M38&lt;&gt;"",M38,IF(OR(K38='설정'!$B$6,K38='설정'!$B$8),SUBSTITUTE(K38,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G38)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G38)),"화목","반")),K38))</f>
         <v/>
       </c>
       <c r="P38" s="30">
@@ -25171,7 +25263,7 @@
       <c r="M39" s="7" t="n"/>
       <c r="N39" s="7" t="n"/>
       <c r="O39" s="27">
-        <f>IF(M39&lt;&gt;"",M39,K39)</f>
+        <f>IF(M39&lt;&gt;"",M39,IF(OR(K39='설정'!$B$6,K39='설정'!$B$8),SUBSTITUTE(K39,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G39)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G39)),"화목","반")),K39))</f>
         <v/>
       </c>
       <c r="P39" s="30">
@@ -25234,7 +25326,7 @@
       <c r="M40" s="7" t="n"/>
       <c r="N40" s="7" t="n"/>
       <c r="O40" s="27">
-        <f>IF(M40&lt;&gt;"",M40,K40)</f>
+        <f>IF(M40&lt;&gt;"",M40,IF(OR(K40='설정'!$B$6,K40='설정'!$B$8),SUBSTITUTE(K40,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G40)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G40)),"화목","반")),K40))</f>
         <v/>
       </c>
       <c r="P40" s="30">
@@ -25297,7 +25389,7 @@
       <c r="M41" s="7" t="n"/>
       <c r="N41" s="7" t="n"/>
       <c r="O41" s="27">
-        <f>IF(M41&lt;&gt;"",M41,K41)</f>
+        <f>IF(M41&lt;&gt;"",M41,IF(OR(K41='설정'!$B$6,K41='설정'!$B$8),SUBSTITUTE(K41,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G41)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G41)),"화목","반")),K41))</f>
         <v/>
       </c>
       <c r="P41" s="30">
@@ -25360,7 +25452,7 @@
       <c r="M42" s="7" t="n"/>
       <c r="N42" s="7" t="n"/>
       <c r="O42" s="27">
-        <f>IF(M42&lt;&gt;"",M42,K42)</f>
+        <f>IF(M42&lt;&gt;"",M42,IF(OR(K42='설정'!$B$6,K42='설정'!$B$8),SUBSTITUTE(K42,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G42)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G42)),"화목","반")),K42))</f>
         <v/>
       </c>
       <c r="P42" s="30">
@@ -25423,7 +25515,7 @@
       <c r="M43" s="7" t="n"/>
       <c r="N43" s="7" t="n"/>
       <c r="O43" s="27">
-        <f>IF(M43&lt;&gt;"",M43,K43)</f>
+        <f>IF(M43&lt;&gt;"",M43,IF(OR(K43='설정'!$B$6,K43='설정'!$B$8),SUBSTITUTE(K43,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G43)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G43)),"화목","반")),K43))</f>
         <v/>
       </c>
       <c r="P43" s="30">
@@ -25486,7 +25578,7 @@
       <c r="M44" s="7" t="n"/>
       <c r="N44" s="7" t="n"/>
       <c r="O44" s="27">
-        <f>IF(M44&lt;&gt;"",M44,K44)</f>
+        <f>IF(M44&lt;&gt;"",M44,IF(OR(K44='설정'!$B$6,K44='설정'!$B$8),SUBSTITUTE(K44,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G44)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G44)),"화목","반")),K44))</f>
         <v/>
       </c>
       <c r="P44" s="30">
@@ -25549,7 +25641,7 @@
       <c r="M45" s="7" t="n"/>
       <c r="N45" s="7" t="n"/>
       <c r="O45" s="27">
-        <f>IF(M45&lt;&gt;"",M45,K45)</f>
+        <f>IF(M45&lt;&gt;"",M45,IF(OR(K45='설정'!$B$6,K45='설정'!$B$8),SUBSTITUTE(K45,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G45)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G45)),"화목","반")),K45))</f>
         <v/>
       </c>
       <c r="P45" s="30">
@@ -25612,7 +25704,7 @@
       <c r="M46" s="7" t="n"/>
       <c r="N46" s="7" t="n"/>
       <c r="O46" s="27">
-        <f>IF(M46&lt;&gt;"",M46,K46)</f>
+        <f>IF(M46&lt;&gt;"",M46,IF(OR(K46='설정'!$B$6,K46='설정'!$B$8),SUBSTITUTE(K46,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G46)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G46)),"화목","반")),K46))</f>
         <v/>
       </c>
       <c r="P46" s="30">
@@ -25675,7 +25767,7 @@
       <c r="M47" s="7" t="n"/>
       <c r="N47" s="7" t="n"/>
       <c r="O47" s="27">
-        <f>IF(M47&lt;&gt;"",M47,K47)</f>
+        <f>IF(M47&lt;&gt;"",M47,IF(OR(K47='설정'!$B$6,K47='설정'!$B$8),SUBSTITUTE(K47,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G47)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G47)),"화목","반")),K47))</f>
         <v/>
       </c>
       <c r="P47" s="30">
@@ -25738,7 +25830,7 @@
       <c r="M48" s="7" t="n"/>
       <c r="N48" s="7" t="n"/>
       <c r="O48" s="27">
-        <f>IF(M48&lt;&gt;"",M48,K48)</f>
+        <f>IF(M48&lt;&gt;"",M48,IF(OR(K48='설정'!$B$6,K48='설정'!$B$8),SUBSTITUTE(K48,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G48)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G48)),"화목","반")),K48))</f>
         <v/>
       </c>
       <c r="P48" s="30">
@@ -25801,7 +25893,7 @@
       <c r="M49" s="7" t="n"/>
       <c r="N49" s="7" t="n"/>
       <c r="O49" s="27">
-        <f>IF(M49&lt;&gt;"",M49,K49)</f>
+        <f>IF(M49&lt;&gt;"",M49,IF(OR(K49='설정'!$B$6,K49='설정'!$B$8),SUBSTITUTE(K49,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G49)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G49)),"화목","반")),K49))</f>
         <v/>
       </c>
       <c r="P49" s="30">
@@ -25864,7 +25956,7 @@
       <c r="M50" s="7" t="n"/>
       <c r="N50" s="7" t="n"/>
       <c r="O50" s="27">
-        <f>IF(M50&lt;&gt;"",M50,K50)</f>
+        <f>IF(M50&lt;&gt;"",M50,IF(OR(K50='설정'!$B$6,K50='설정'!$B$8),SUBSTITUTE(K50,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G50)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G50)),"화목","반")),K50))</f>
         <v/>
       </c>
       <c r="P50" s="30">
@@ -25927,7 +26019,7 @@
       <c r="M51" s="7" t="n"/>
       <c r="N51" s="7" t="n"/>
       <c r="O51" s="27">
-        <f>IF(M51&lt;&gt;"",M51,K51)</f>
+        <f>IF(M51&lt;&gt;"",M51,IF(OR(K51='설정'!$B$6,K51='설정'!$B$8),SUBSTITUTE(K51,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G51)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G51)),"화목","반")),K51))</f>
         <v/>
       </c>
       <c r="P51" s="30">
@@ -25990,7 +26082,7 @@
       <c r="M52" s="7" t="n"/>
       <c r="N52" s="7" t="n"/>
       <c r="O52" s="27">
-        <f>IF(M52&lt;&gt;"",M52,K52)</f>
+        <f>IF(M52&lt;&gt;"",M52,IF(OR(K52='설정'!$B$6,K52='설정'!$B$8),SUBSTITUTE(K52,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G52)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G52)),"화목","반")),K52))</f>
         <v/>
       </c>
       <c r="P52" s="30">
@@ -26053,7 +26145,7 @@
       <c r="M53" s="7" t="n"/>
       <c r="N53" s="7" t="n"/>
       <c r="O53" s="27">
-        <f>IF(M53&lt;&gt;"",M53,K53)</f>
+        <f>IF(M53&lt;&gt;"",M53,IF(OR(K53='설정'!$B$6,K53='설정'!$B$8),SUBSTITUTE(K53,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G53)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G53)),"화목","반")),K53))</f>
         <v/>
       </c>
       <c r="P53" s="30">
@@ -26116,7 +26208,7 @@
       <c r="M54" s="7" t="n"/>
       <c r="N54" s="7" t="n"/>
       <c r="O54" s="27">
-        <f>IF(M54&lt;&gt;"",M54,K54)</f>
+        <f>IF(M54&lt;&gt;"",M54,IF(OR(K54='설정'!$B$6,K54='설정'!$B$8),SUBSTITUTE(K54,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G54)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G54)),"화목","반")),K54))</f>
         <v/>
       </c>
       <c r="P54" s="30">
@@ -26179,7 +26271,7 @@
       <c r="M55" s="7" t="n"/>
       <c r="N55" s="7" t="n"/>
       <c r="O55" s="27">
-        <f>IF(M55&lt;&gt;"",M55,K55)</f>
+        <f>IF(M55&lt;&gt;"",M55,IF(OR(K55='설정'!$B$6,K55='설정'!$B$8),SUBSTITUTE(K55,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G55)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G55)),"화목","반")),K55))</f>
         <v/>
       </c>
       <c r="P55" s="30">
@@ -26242,7 +26334,7 @@
       <c r="M56" s="7" t="n"/>
       <c r="N56" s="7" t="n"/>
       <c r="O56" s="27">
-        <f>IF(M56&lt;&gt;"",M56,K56)</f>
+        <f>IF(M56&lt;&gt;"",M56,IF(OR(K56='설정'!$B$6,K56='설정'!$B$8),SUBSTITUTE(K56,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G56)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G56)),"화목","반")),K56))</f>
         <v/>
       </c>
       <c r="P56" s="30">
@@ -26305,7 +26397,7 @@
       <c r="M57" s="7" t="n"/>
       <c r="N57" s="7" t="n"/>
       <c r="O57" s="27">
-        <f>IF(M57&lt;&gt;"",M57,K57)</f>
+        <f>IF(M57&lt;&gt;"",M57,IF(OR(K57='설정'!$B$6,K57='설정'!$B$8),SUBSTITUTE(K57,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G57)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G57)),"화목","반")),K57))</f>
         <v/>
       </c>
       <c r="P57" s="30">
@@ -26368,7 +26460,7 @@
       <c r="M58" s="7" t="n"/>
       <c r="N58" s="7" t="n"/>
       <c r="O58" s="27">
-        <f>IF(M58&lt;&gt;"",M58,K58)</f>
+        <f>IF(M58&lt;&gt;"",M58,IF(OR(K58='설정'!$B$6,K58='설정'!$B$8),SUBSTITUTE(K58,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G58)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G58)),"화목","반")),K58))</f>
         <v/>
       </c>
       <c r="P58" s="30">
@@ -26431,7 +26523,7 @@
       <c r="M59" s="7" t="n"/>
       <c r="N59" s="7" t="n"/>
       <c r="O59" s="27">
-        <f>IF(M59&lt;&gt;"",M59,K59)</f>
+        <f>IF(M59&lt;&gt;"",M59,IF(OR(K59='설정'!$B$6,K59='설정'!$B$8),SUBSTITUTE(K59,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G59)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G59)),"화목","반")),K59))</f>
         <v/>
       </c>
       <c r="P59" s="30">
@@ -26494,7 +26586,7 @@
       <c r="M60" s="7" t="n"/>
       <c r="N60" s="7" t="n"/>
       <c r="O60" s="27">
-        <f>IF(M60&lt;&gt;"",M60,K60)</f>
+        <f>IF(M60&lt;&gt;"",M60,IF(OR(K60='설정'!$B$6,K60='설정'!$B$8),SUBSTITUTE(K60,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G60)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G60)),"화목","반")),K60))</f>
         <v/>
       </c>
       <c r="P60" s="30">
@@ -26557,7 +26649,7 @@
       <c r="M61" s="7" t="n"/>
       <c r="N61" s="7" t="n"/>
       <c r="O61" s="27">
-        <f>IF(M61&lt;&gt;"",M61,K61)</f>
+        <f>IF(M61&lt;&gt;"",M61,IF(OR(K61='설정'!$B$6,K61='설정'!$B$8),SUBSTITUTE(K61,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G61)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G61)),"화목","반")),K61))</f>
         <v/>
       </c>
       <c r="P61" s="30">
@@ -26620,7 +26712,7 @@
       <c r="M62" s="7" t="n"/>
       <c r="N62" s="7" t="n"/>
       <c r="O62" s="27">
-        <f>IF(M62&lt;&gt;"",M62,K62)</f>
+        <f>IF(M62&lt;&gt;"",M62,IF(OR(K62='설정'!$B$6,K62='설정'!$B$8),SUBSTITUTE(K62,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G62)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G62)),"화목","반")),K62))</f>
         <v/>
       </c>
       <c r="P62" s="30">
@@ -26683,7 +26775,7 @@
       <c r="M63" s="7" t="n"/>
       <c r="N63" s="7" t="n"/>
       <c r="O63" s="27">
-        <f>IF(M63&lt;&gt;"",M63,K63)</f>
+        <f>IF(M63&lt;&gt;"",M63,IF(OR(K63='설정'!$B$6,K63='설정'!$B$8),SUBSTITUTE(K63,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G63)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G63)),"화목","반")),K63))</f>
         <v/>
       </c>
       <c r="P63" s="30">
@@ -26746,7 +26838,7 @@
       <c r="M64" s="7" t="n"/>
       <c r="N64" s="7" t="n"/>
       <c r="O64" s="27">
-        <f>IF(M64&lt;&gt;"",M64,K64)</f>
+        <f>IF(M64&lt;&gt;"",M64,IF(OR(K64='설정'!$B$6,K64='설정'!$B$8),SUBSTITUTE(K64,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G64)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G64)),"화목","반")),K64))</f>
         <v/>
       </c>
       <c r="P64" s="30">
@@ -26809,7 +26901,7 @@
       <c r="M65" s="7" t="n"/>
       <c r="N65" s="7" t="n"/>
       <c r="O65" s="27">
-        <f>IF(M65&lt;&gt;"",M65,K65)</f>
+        <f>IF(M65&lt;&gt;"",M65,IF(OR(K65='설정'!$B$6,K65='설정'!$B$8),SUBSTITUTE(K65,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G65)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G65)),"화목","반")),K65))</f>
         <v/>
       </c>
       <c r="P65" s="30">
@@ -26872,7 +26964,7 @@
       <c r="M66" s="7" t="n"/>
       <c r="N66" s="7" t="n"/>
       <c r="O66" s="27">
-        <f>IF(M66&lt;&gt;"",M66,K66)</f>
+        <f>IF(M66&lt;&gt;"",M66,IF(OR(K66='설정'!$B$6,K66='설정'!$B$8),SUBSTITUTE(K66,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G66)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G66)),"화목","반")),K66))</f>
         <v/>
       </c>
       <c r="P66" s="30">
@@ -26935,7 +27027,7 @@
       <c r="M67" s="7" t="n"/>
       <c r="N67" s="7" t="n"/>
       <c r="O67" s="27">
-        <f>IF(M67&lt;&gt;"",M67,K67)</f>
+        <f>IF(M67&lt;&gt;"",M67,IF(OR(K67='설정'!$B$6,K67='설정'!$B$8),SUBSTITUTE(K67,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G67)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G67)),"화목","반")),K67))</f>
         <v/>
       </c>
       <c r="P67" s="30">
@@ -26998,7 +27090,7 @@
       <c r="M68" s="7" t="n"/>
       <c r="N68" s="7" t="n"/>
       <c r="O68" s="27">
-        <f>IF(M68&lt;&gt;"",M68,K68)</f>
+        <f>IF(M68&lt;&gt;"",M68,IF(OR(K68='설정'!$B$6,K68='설정'!$B$8),SUBSTITUTE(K68,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G68)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G68)),"화목","반")),K68))</f>
         <v/>
       </c>
       <c r="P68" s="30">
@@ -27061,7 +27153,7 @@
       <c r="M69" s="7" t="n"/>
       <c r="N69" s="7" t="n"/>
       <c r="O69" s="27">
-        <f>IF(M69&lt;&gt;"",M69,K69)</f>
+        <f>IF(M69&lt;&gt;"",M69,IF(OR(K69='설정'!$B$6,K69='설정'!$B$8),SUBSTITUTE(K69,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G69)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G69)),"화목","반")),K69))</f>
         <v/>
       </c>
       <c r="P69" s="30">
@@ -27124,7 +27216,7 @@
       <c r="M70" s="7" t="n"/>
       <c r="N70" s="7" t="n"/>
       <c r="O70" s="27">
-        <f>IF(M70&lt;&gt;"",M70,K70)</f>
+        <f>IF(M70&lt;&gt;"",M70,IF(OR(K70='설정'!$B$6,K70='설정'!$B$8),SUBSTITUTE(K70,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G70)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G70)),"화목","반")),K70))</f>
         <v/>
       </c>
       <c r="P70" s="30">
@@ -27187,7 +27279,7 @@
       <c r="M71" s="7" t="n"/>
       <c r="N71" s="7" t="n"/>
       <c r="O71" s="27">
-        <f>IF(M71&lt;&gt;"",M71,K71)</f>
+        <f>IF(M71&lt;&gt;"",M71,IF(OR(K71='설정'!$B$6,K71='설정'!$B$8),SUBSTITUTE(K71,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G71)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G71)),"화목","반")),K71))</f>
         <v/>
       </c>
       <c r="P71" s="30">
@@ -27250,7 +27342,7 @@
       <c r="M72" s="7" t="n"/>
       <c r="N72" s="7" t="n"/>
       <c r="O72" s="27">
-        <f>IF(M72&lt;&gt;"",M72,K72)</f>
+        <f>IF(M72&lt;&gt;"",M72,IF(OR(K72='설정'!$B$6,K72='설정'!$B$8),SUBSTITUTE(K72,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G72)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G72)),"화목","반")),K72))</f>
         <v/>
       </c>
       <c r="P72" s="30">
@@ -27313,7 +27405,7 @@
       <c r="M73" s="7" t="n"/>
       <c r="N73" s="7" t="n"/>
       <c r="O73" s="27">
-        <f>IF(M73&lt;&gt;"",M73,K73)</f>
+        <f>IF(M73&lt;&gt;"",M73,IF(OR(K73='설정'!$B$6,K73='설정'!$B$8),SUBSTITUTE(K73,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G73)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G73)),"화목","반")),K73))</f>
         <v/>
       </c>
       <c r="P73" s="30">
@@ -27376,7 +27468,7 @@
       <c r="M74" s="7" t="n"/>
       <c r="N74" s="7" t="n"/>
       <c r="O74" s="27">
-        <f>IF(M74&lt;&gt;"",M74,K74)</f>
+        <f>IF(M74&lt;&gt;"",M74,IF(OR(K74='설정'!$B$6,K74='설정'!$B$8),SUBSTITUTE(K74,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G74)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G74)),"화목","반")),K74))</f>
         <v/>
       </c>
       <c r="P74" s="30">
@@ -27439,7 +27531,7 @@
       <c r="M75" s="7" t="n"/>
       <c r="N75" s="7" t="n"/>
       <c r="O75" s="27">
-        <f>IF(M75&lt;&gt;"",M75,K75)</f>
+        <f>IF(M75&lt;&gt;"",M75,IF(OR(K75='설정'!$B$6,K75='설정'!$B$8),SUBSTITUTE(K75,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G75)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G75)),"화목","반")),K75))</f>
         <v/>
       </c>
       <c r="P75" s="30">
@@ -27502,7 +27594,7 @@
       <c r="M76" s="7" t="n"/>
       <c r="N76" s="7" t="n"/>
       <c r="O76" s="27">
-        <f>IF(M76&lt;&gt;"",M76,K76)</f>
+        <f>IF(M76&lt;&gt;"",M76,IF(OR(K76='설정'!$B$6,K76='설정'!$B$8),SUBSTITUTE(K76,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G76)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G76)),"화목","반")),K76))</f>
         <v/>
       </c>
       <c r="P76" s="30">
@@ -27565,7 +27657,7 @@
       <c r="M77" s="7" t="n"/>
       <c r="N77" s="7" t="n"/>
       <c r="O77" s="27">
-        <f>IF(M77&lt;&gt;"",M77,K77)</f>
+        <f>IF(M77&lt;&gt;"",M77,IF(OR(K77='설정'!$B$6,K77='설정'!$B$8),SUBSTITUTE(K77,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G77)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G77)),"화목","반")),K77))</f>
         <v/>
       </c>
       <c r="P77" s="30">
@@ -27628,7 +27720,7 @@
       <c r="M78" s="7" t="n"/>
       <c r="N78" s="7" t="n"/>
       <c r="O78" s="27">
-        <f>IF(M78&lt;&gt;"",M78,K78)</f>
+        <f>IF(M78&lt;&gt;"",M78,IF(OR(K78='설정'!$B$6,K78='설정'!$B$8),SUBSTITUTE(K78,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G78)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G78)),"화목","반")),K78))</f>
         <v/>
       </c>
       <c r="P78" s="30">
@@ -27691,7 +27783,7 @@
       <c r="M79" s="7" t="n"/>
       <c r="N79" s="7" t="n"/>
       <c r="O79" s="27">
-        <f>IF(M79&lt;&gt;"",M79,K79)</f>
+        <f>IF(M79&lt;&gt;"",M79,IF(OR(K79='설정'!$B$6,K79='설정'!$B$8),SUBSTITUTE(K79,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G79)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G79)),"화목","반")),K79))</f>
         <v/>
       </c>
       <c r="P79" s="30">
@@ -27754,7 +27846,7 @@
       <c r="M80" s="7" t="n"/>
       <c r="N80" s="7" t="n"/>
       <c r="O80" s="27">
-        <f>IF(M80&lt;&gt;"",M80,K80)</f>
+        <f>IF(M80&lt;&gt;"",M80,IF(OR(K80='설정'!$B$6,K80='설정'!$B$8),SUBSTITUTE(K80,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G80)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G80)),"화목","반")),K80))</f>
         <v/>
       </c>
       <c r="P80" s="30">
@@ -27817,7 +27909,7 @@
       <c r="M81" s="7" t="n"/>
       <c r="N81" s="7" t="n"/>
       <c r="O81" s="27">
-        <f>IF(M81&lt;&gt;"",M81,K81)</f>
+        <f>IF(M81&lt;&gt;"",M81,IF(OR(K81='설정'!$B$6,K81='설정'!$B$8),SUBSTITUTE(K81,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G81)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G81)),"화목","반")),K81))</f>
         <v/>
       </c>
       <c r="P81" s="30">
@@ -27880,7 +27972,7 @@
       <c r="M82" s="7" t="n"/>
       <c r="N82" s="7" t="n"/>
       <c r="O82" s="27">
-        <f>IF(M82&lt;&gt;"",M82,K82)</f>
+        <f>IF(M82&lt;&gt;"",M82,IF(OR(K82='설정'!$B$6,K82='설정'!$B$8),SUBSTITUTE(K82,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G82)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G82)),"화목","반")),K82))</f>
         <v/>
       </c>
       <c r="P82" s="30">
@@ -27943,7 +28035,7 @@
       <c r="M83" s="7" t="n"/>
       <c r="N83" s="7" t="n"/>
       <c r="O83" s="27">
-        <f>IF(M83&lt;&gt;"",M83,K83)</f>
+        <f>IF(M83&lt;&gt;"",M83,IF(OR(K83='설정'!$B$6,K83='설정'!$B$8),SUBSTITUTE(K83,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G83)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G83)),"화목","반")),K83))</f>
         <v/>
       </c>
       <c r="P83" s="30">
@@ -28006,7 +28098,7 @@
       <c r="M84" s="7" t="n"/>
       <c r="N84" s="7" t="n"/>
       <c r="O84" s="27">
-        <f>IF(M84&lt;&gt;"",M84,K84)</f>
+        <f>IF(M84&lt;&gt;"",M84,IF(OR(K84='설정'!$B$6,K84='설정'!$B$8),SUBSTITUTE(K84,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G84)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G84)),"화목","반")),K84))</f>
         <v/>
       </c>
       <c r="P84" s="30">
@@ -28069,7 +28161,7 @@
       <c r="M85" s="7" t="n"/>
       <c r="N85" s="7" t="n"/>
       <c r="O85" s="27">
-        <f>IF(M85&lt;&gt;"",M85,K85)</f>
+        <f>IF(M85&lt;&gt;"",M85,IF(OR(K85='설정'!$B$6,K85='설정'!$B$8),SUBSTITUTE(K85,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G85)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G85)),"화목","반")),K85))</f>
         <v/>
       </c>
       <c r="P85" s="30">
@@ -28132,7 +28224,7 @@
       <c r="M86" s="7" t="n"/>
       <c r="N86" s="7" t="n"/>
       <c r="O86" s="27">
-        <f>IF(M86&lt;&gt;"",M86,K86)</f>
+        <f>IF(M86&lt;&gt;"",M86,IF(OR(K86='설정'!$B$6,K86='설정'!$B$8),SUBSTITUTE(K86,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G86)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G86)),"화목","반")),K86))</f>
         <v/>
       </c>
       <c r="P86" s="30">
@@ -28195,7 +28287,7 @@
       <c r="M87" s="7" t="n"/>
       <c r="N87" s="7" t="n"/>
       <c r="O87" s="27">
-        <f>IF(M87&lt;&gt;"",M87,K87)</f>
+        <f>IF(M87&lt;&gt;"",M87,IF(OR(K87='설정'!$B$6,K87='설정'!$B$8),SUBSTITUTE(K87,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G87)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G87)),"화목","반")),K87))</f>
         <v/>
       </c>
       <c r="P87" s="30">
@@ -28258,7 +28350,7 @@
       <c r="M88" s="7" t="n"/>
       <c r="N88" s="7" t="n"/>
       <c r="O88" s="27">
-        <f>IF(M88&lt;&gt;"",M88,K88)</f>
+        <f>IF(M88&lt;&gt;"",M88,IF(OR(K88='설정'!$B$6,K88='설정'!$B$8),SUBSTITUTE(K88,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G88)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G88)),"화목","반")),K88))</f>
         <v/>
       </c>
       <c r="P88" s="30">
@@ -28321,7 +28413,7 @@
       <c r="M89" s="7" t="n"/>
       <c r="N89" s="7" t="n"/>
       <c r="O89" s="27">
-        <f>IF(M89&lt;&gt;"",M89,K89)</f>
+        <f>IF(M89&lt;&gt;"",M89,IF(OR(K89='설정'!$B$6,K89='설정'!$B$8),SUBSTITUTE(K89,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G89)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G89)),"화목","반")),K89))</f>
         <v/>
       </c>
       <c r="P89" s="30">
@@ -28384,7 +28476,7 @@
       <c r="M90" s="7" t="n"/>
       <c r="N90" s="7" t="n"/>
       <c r="O90" s="27">
-        <f>IF(M90&lt;&gt;"",M90,K90)</f>
+        <f>IF(M90&lt;&gt;"",M90,IF(OR(K90='설정'!$B$6,K90='설정'!$B$8),SUBSTITUTE(K90,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G90)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G90)),"화목","반")),K90))</f>
         <v/>
       </c>
       <c r="P90" s="30">
@@ -28447,7 +28539,7 @@
       <c r="M91" s="7" t="n"/>
       <c r="N91" s="7" t="n"/>
       <c r="O91" s="27">
-        <f>IF(M91&lt;&gt;"",M91,K91)</f>
+        <f>IF(M91&lt;&gt;"",M91,IF(OR(K91='설정'!$B$6,K91='설정'!$B$8),SUBSTITUTE(K91,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G91)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G91)),"화목","반")),K91))</f>
         <v/>
       </c>
       <c r="P91" s="30">
@@ -28510,7 +28602,7 @@
       <c r="M92" s="7" t="n"/>
       <c r="N92" s="7" t="n"/>
       <c r="O92" s="27">
-        <f>IF(M92&lt;&gt;"",M92,K92)</f>
+        <f>IF(M92&lt;&gt;"",M92,IF(OR(K92='설정'!$B$6,K92='설정'!$B$8),SUBSTITUTE(K92,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G92)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G92)),"화목","반")),K92))</f>
         <v/>
       </c>
       <c r="P92" s="30">
@@ -28573,7 +28665,7 @@
       <c r="M93" s="7" t="n"/>
       <c r="N93" s="7" t="n"/>
       <c r="O93" s="27">
-        <f>IF(M93&lt;&gt;"",M93,K93)</f>
+        <f>IF(M93&lt;&gt;"",M93,IF(OR(K93='설정'!$B$6,K93='설정'!$B$8),SUBSTITUTE(K93,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G93)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G93)),"화목","반")),K93))</f>
         <v/>
       </c>
       <c r="P93" s="30">
@@ -28636,7 +28728,7 @@
       <c r="M94" s="7" t="n"/>
       <c r="N94" s="7" t="n"/>
       <c r="O94" s="27">
-        <f>IF(M94&lt;&gt;"",M94,K94)</f>
+        <f>IF(M94&lt;&gt;"",M94,IF(OR(K94='설정'!$B$6,K94='설정'!$B$8),SUBSTITUTE(K94,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G94)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G94)),"화목","반")),K94))</f>
         <v/>
       </c>
       <c r="P94" s="30">
@@ -28699,7 +28791,7 @@
       <c r="M95" s="7" t="n"/>
       <c r="N95" s="7" t="n"/>
       <c r="O95" s="27">
-        <f>IF(M95&lt;&gt;"",M95,K95)</f>
+        <f>IF(M95&lt;&gt;"",M95,IF(OR(K95='설정'!$B$6,K95='설정'!$B$8),SUBSTITUTE(K95,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G95)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G95)),"화목","반")),K95))</f>
         <v/>
       </c>
       <c r="P95" s="30">
@@ -28762,7 +28854,7 @@
       <c r="M96" s="7" t="n"/>
       <c r="N96" s="7" t="n"/>
       <c r="O96" s="27">
-        <f>IF(M96&lt;&gt;"",M96,K96)</f>
+        <f>IF(M96&lt;&gt;"",M96,IF(OR(K96='설정'!$B$6,K96='설정'!$B$8),SUBSTITUTE(K96,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G96)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G96)),"화목","반")),K96))</f>
         <v/>
       </c>
       <c r="P96" s="30">
@@ -28825,7 +28917,7 @@
       <c r="M97" s="7" t="n"/>
       <c r="N97" s="7" t="n"/>
       <c r="O97" s="27">
-        <f>IF(M97&lt;&gt;"",M97,K97)</f>
+        <f>IF(M97&lt;&gt;"",M97,IF(OR(K97='설정'!$B$6,K97='설정'!$B$8),SUBSTITUTE(K97,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G97)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G97)),"화목","반")),K97))</f>
         <v/>
       </c>
       <c r="P97" s="30">
@@ -28888,7 +28980,7 @@
       <c r="M98" s="7" t="n"/>
       <c r="N98" s="7" t="n"/>
       <c r="O98" s="27">
-        <f>IF(M98&lt;&gt;"",M98,K98)</f>
+        <f>IF(M98&lt;&gt;"",M98,IF(OR(K98='설정'!$B$6,K98='설정'!$B$8),SUBSTITUTE(K98,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G98)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G98)),"화목","반")),K98))</f>
         <v/>
       </c>
       <c r="P98" s="30">
@@ -28951,7 +29043,7 @@
       <c r="M99" s="7" t="n"/>
       <c r="N99" s="7" t="n"/>
       <c r="O99" s="27">
-        <f>IF(M99&lt;&gt;"",M99,K99)</f>
+        <f>IF(M99&lt;&gt;"",M99,IF(OR(K99='설정'!$B$6,K99='설정'!$B$8),SUBSTITUTE(K99,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G99)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G99)),"화목","반")),K99))</f>
         <v/>
       </c>
       <c r="P99" s="30">
@@ -29014,7 +29106,7 @@
       <c r="M100" s="7" t="n"/>
       <c r="N100" s="7" t="n"/>
       <c r="O100" s="27">
-        <f>IF(M100&lt;&gt;"",M100,K100)</f>
+        <f>IF(M100&lt;&gt;"",M100,IF(OR(K100='설정'!$B$6,K100='설정'!$B$8),SUBSTITUTE(K100,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G100)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G100)),"화목","반")),K100))</f>
         <v/>
       </c>
       <c r="P100" s="30">
@@ -29077,7 +29169,7 @@
       <c r="M101" s="7" t="n"/>
       <c r="N101" s="7" t="n"/>
       <c r="O101" s="27">
-        <f>IF(M101&lt;&gt;"",M101,K101)</f>
+        <f>IF(M101&lt;&gt;"",M101,IF(OR(K101='설정'!$B$6,K101='설정'!$B$8),SUBSTITUTE(K101,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G101)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G101)),"화목","반")),K101))</f>
         <v/>
       </c>
       <c r="P101" s="30">
@@ -29140,7 +29232,7 @@
       <c r="M102" s="7" t="n"/>
       <c r="N102" s="7" t="n"/>
       <c r="O102" s="27">
-        <f>IF(M102&lt;&gt;"",M102,K102)</f>
+        <f>IF(M102&lt;&gt;"",M102,IF(OR(K102='설정'!$B$6,K102='설정'!$B$8),SUBSTITUTE(K102,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G102)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G102)),"화목","반")),K102))</f>
         <v/>
       </c>
       <c r="P102" s="30">
@@ -29203,7 +29295,7 @@
       <c r="M103" s="7" t="n"/>
       <c r="N103" s="7" t="n"/>
       <c r="O103" s="27">
-        <f>IF(M103&lt;&gt;"",M103,K103)</f>
+        <f>IF(M103&lt;&gt;"",M103,IF(OR(K103='설정'!$B$6,K103='설정'!$B$8),SUBSTITUTE(K103,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G103)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G103)),"화목","반")),K103))</f>
         <v/>
       </c>
       <c r="P103" s="30">
@@ -29266,7 +29358,7 @@
       <c r="M104" s="7" t="n"/>
       <c r="N104" s="7" t="n"/>
       <c r="O104" s="27">
-        <f>IF(M104&lt;&gt;"",M104,K104)</f>
+        <f>IF(M104&lt;&gt;"",M104,IF(OR(K104='설정'!$B$6,K104='설정'!$B$8),SUBSTITUTE(K104,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G104)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G104)),"화목","반")),K104))</f>
         <v/>
       </c>
       <c r="P104" s="30">
@@ -29329,7 +29421,7 @@
       <c r="M105" s="7" t="n"/>
       <c r="N105" s="7" t="n"/>
       <c r="O105" s="27">
-        <f>IF(M105&lt;&gt;"",M105,K105)</f>
+        <f>IF(M105&lt;&gt;"",M105,IF(OR(K105='설정'!$B$6,K105='설정'!$B$8),SUBSTITUTE(K105,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G105)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G105)),"화목","반")),K105))</f>
         <v/>
       </c>
       <c r="P105" s="30">
@@ -29392,7 +29484,7 @@
       <c r="M106" s="7" t="n"/>
       <c r="N106" s="7" t="n"/>
       <c r="O106" s="27">
-        <f>IF(M106&lt;&gt;"",M106,K106)</f>
+        <f>IF(M106&lt;&gt;"",M106,IF(OR(K106='설정'!$B$6,K106='설정'!$B$8),SUBSTITUTE(K106,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G106)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G106)),"화목","반")),K106))</f>
         <v/>
       </c>
       <c r="P106" s="30">
@@ -29455,7 +29547,7 @@
       <c r="M107" s="7" t="n"/>
       <c r="N107" s="7" t="n"/>
       <c r="O107" s="27">
-        <f>IF(M107&lt;&gt;"",M107,K107)</f>
+        <f>IF(M107&lt;&gt;"",M107,IF(OR(K107='설정'!$B$6,K107='설정'!$B$8),SUBSTITUTE(K107,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G107)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G107)),"화목","반")),K107))</f>
         <v/>
       </c>
       <c r="P107" s="30">
@@ -29518,7 +29610,7 @@
       <c r="M108" s="7" t="n"/>
       <c r="N108" s="7" t="n"/>
       <c r="O108" s="27">
-        <f>IF(M108&lt;&gt;"",M108,K108)</f>
+        <f>IF(M108&lt;&gt;"",M108,IF(OR(K108='설정'!$B$6,K108='설정'!$B$8),SUBSTITUTE(K108,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G108)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G108)),"화목","반")),K108))</f>
         <v/>
       </c>
       <c r="P108" s="30">
@@ -29581,7 +29673,7 @@
       <c r="M109" s="7" t="n"/>
       <c r="N109" s="7" t="n"/>
       <c r="O109" s="27">
-        <f>IF(M109&lt;&gt;"",M109,K109)</f>
+        <f>IF(M109&lt;&gt;"",M109,IF(OR(K109='설정'!$B$6,K109='설정'!$B$8),SUBSTITUTE(K109,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G109)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G109)),"화목","반")),K109))</f>
         <v/>
       </c>
       <c r="P109" s="30">
@@ -29644,7 +29736,7 @@
       <c r="M110" s="7" t="n"/>
       <c r="N110" s="7" t="n"/>
       <c r="O110" s="27">
-        <f>IF(M110&lt;&gt;"",M110,K110)</f>
+        <f>IF(M110&lt;&gt;"",M110,IF(OR(K110='설정'!$B$6,K110='설정'!$B$8),SUBSTITUTE(K110,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G110)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G110)),"화목","반")),K110))</f>
         <v/>
       </c>
       <c r="P110" s="30">
@@ -29707,7 +29799,7 @@
       <c r="M111" s="7" t="n"/>
       <c r="N111" s="7" t="n"/>
       <c r="O111" s="27">
-        <f>IF(M111&lt;&gt;"",M111,K111)</f>
+        <f>IF(M111&lt;&gt;"",M111,IF(OR(K111='설정'!$B$6,K111='설정'!$B$8),SUBSTITUTE(K111,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G111)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G111)),"화목","반")),K111))</f>
         <v/>
       </c>
       <c r="P111" s="30">
@@ -29770,7 +29862,7 @@
       <c r="M112" s="7" t="n"/>
       <c r="N112" s="7" t="n"/>
       <c r="O112" s="27">
-        <f>IF(M112&lt;&gt;"",M112,K112)</f>
+        <f>IF(M112&lt;&gt;"",M112,IF(OR(K112='설정'!$B$6,K112='설정'!$B$8),SUBSTITUTE(K112,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G112)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G112)),"화목","반")),K112))</f>
         <v/>
       </c>
       <c r="P112" s="30">
@@ -29833,7 +29925,7 @@
       <c r="M113" s="7" t="n"/>
       <c r="N113" s="7" t="n"/>
       <c r="O113" s="27">
-        <f>IF(M113&lt;&gt;"",M113,K113)</f>
+        <f>IF(M113&lt;&gt;"",M113,IF(OR(K113='설정'!$B$6,K113='설정'!$B$8),SUBSTITUTE(K113,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G113)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G113)),"화목","반")),K113))</f>
         <v/>
       </c>
       <c r="P113" s="30">
@@ -29896,7 +29988,7 @@
       <c r="M114" s="7" t="n"/>
       <c r="N114" s="7" t="n"/>
       <c r="O114" s="27">
-        <f>IF(M114&lt;&gt;"",M114,K114)</f>
+        <f>IF(M114&lt;&gt;"",M114,IF(OR(K114='설정'!$B$6,K114='설정'!$B$8),SUBSTITUTE(K114,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G114)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G114)),"화목","반")),K114))</f>
         <v/>
       </c>
       <c r="P114" s="30">
@@ -29959,7 +30051,7 @@
       <c r="M115" s="7" t="n"/>
       <c r="N115" s="7" t="n"/>
       <c r="O115" s="27">
-        <f>IF(M115&lt;&gt;"",M115,K115)</f>
+        <f>IF(M115&lt;&gt;"",M115,IF(OR(K115='설정'!$B$6,K115='설정'!$B$8),SUBSTITUTE(K115,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G115)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G115)),"화목","반")),K115))</f>
         <v/>
       </c>
       <c r="P115" s="30">
@@ -30022,7 +30114,7 @@
       <c r="M116" s="7" t="n"/>
       <c r="N116" s="7" t="n"/>
       <c r="O116" s="27">
-        <f>IF(M116&lt;&gt;"",M116,K116)</f>
+        <f>IF(M116&lt;&gt;"",M116,IF(OR(K116='설정'!$B$6,K116='설정'!$B$8),SUBSTITUTE(K116,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G116)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G116)),"화목","반")),K116))</f>
         <v/>
       </c>
       <c r="P116" s="30">
@@ -30085,7 +30177,7 @@
       <c r="M117" s="7" t="n"/>
       <c r="N117" s="7" t="n"/>
       <c r="O117" s="27">
-        <f>IF(M117&lt;&gt;"",M117,K117)</f>
+        <f>IF(M117&lt;&gt;"",M117,IF(OR(K117='설정'!$B$6,K117='설정'!$B$8),SUBSTITUTE(K117,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G117)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G117)),"화목","반")),K117))</f>
         <v/>
       </c>
       <c r="P117" s="30">
@@ -30148,7 +30240,7 @@
       <c r="M118" s="7" t="n"/>
       <c r="N118" s="7" t="n"/>
       <c r="O118" s="27">
-        <f>IF(M118&lt;&gt;"",M118,K118)</f>
+        <f>IF(M118&lt;&gt;"",M118,IF(OR(K118='설정'!$B$6,K118='설정'!$B$8),SUBSTITUTE(K118,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G118)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G118)),"화목","반")),K118))</f>
         <v/>
       </c>
       <c r="P118" s="30">
@@ -30211,7 +30303,7 @@
       <c r="M119" s="7" t="n"/>
       <c r="N119" s="7" t="n"/>
       <c r="O119" s="27">
-        <f>IF(M119&lt;&gt;"",M119,K119)</f>
+        <f>IF(M119&lt;&gt;"",M119,IF(OR(K119='설정'!$B$6,K119='설정'!$B$8),SUBSTITUTE(K119,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G119)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G119)),"화목","반")),K119))</f>
         <v/>
       </c>
       <c r="P119" s="30">
@@ -30274,7 +30366,7 @@
       <c r="M120" s="7" t="n"/>
       <c r="N120" s="7" t="n"/>
       <c r="O120" s="27">
-        <f>IF(M120&lt;&gt;"",M120,K120)</f>
+        <f>IF(M120&lt;&gt;"",M120,IF(OR(K120='설정'!$B$6,K120='설정'!$B$8),SUBSTITUTE(K120,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G120)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G120)),"화목","반")),K120))</f>
         <v/>
       </c>
       <c r="P120" s="30">
@@ -30337,7 +30429,7 @@
       <c r="M121" s="7" t="n"/>
       <c r="N121" s="7" t="n"/>
       <c r="O121" s="27">
-        <f>IF(M121&lt;&gt;"",M121,K121)</f>
+        <f>IF(M121&lt;&gt;"",M121,IF(OR(K121='설정'!$B$6,K121='설정'!$B$8),SUBSTITUTE(K121,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G121)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G121)),"화목","반")),K121))</f>
         <v/>
       </c>
       <c r="P121" s="30">
@@ -30400,7 +30492,7 @@
       <c r="M122" s="7" t="n"/>
       <c r="N122" s="7" t="n"/>
       <c r="O122" s="27">
-        <f>IF(M122&lt;&gt;"",M122,K122)</f>
+        <f>IF(M122&lt;&gt;"",M122,IF(OR(K122='설정'!$B$6,K122='설정'!$B$8),SUBSTITUTE(K122,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G122)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G122)),"화목","반")),K122))</f>
         <v/>
       </c>
       <c r="P122" s="30">
@@ -30463,7 +30555,7 @@
       <c r="M123" s="7" t="n"/>
       <c r="N123" s="7" t="n"/>
       <c r="O123" s="27">
-        <f>IF(M123&lt;&gt;"",M123,K123)</f>
+        <f>IF(M123&lt;&gt;"",M123,IF(OR(K123='설정'!$B$6,K123='설정'!$B$8),SUBSTITUTE(K123,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G123)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G123)),"화목","반")),K123))</f>
         <v/>
       </c>
       <c r="P123" s="30">
@@ -30526,7 +30618,7 @@
       <c r="M124" s="7" t="n"/>
       <c r="N124" s="7" t="n"/>
       <c r="O124" s="27">
-        <f>IF(M124&lt;&gt;"",M124,K124)</f>
+        <f>IF(M124&lt;&gt;"",M124,IF(OR(K124='설정'!$B$6,K124='설정'!$B$8),SUBSTITUTE(K124,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G124)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G124)),"화목","반")),K124))</f>
         <v/>
       </c>
       <c r="P124" s="30">
@@ -30589,7 +30681,7 @@
       <c r="M125" s="7" t="n"/>
       <c r="N125" s="7" t="n"/>
       <c r="O125" s="27">
-        <f>IF(M125&lt;&gt;"",M125,K125)</f>
+        <f>IF(M125&lt;&gt;"",M125,IF(OR(K125='설정'!$B$6,K125='설정'!$B$8),SUBSTITUTE(K125,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G125)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G125)),"화목","반")),K125))</f>
         <v/>
       </c>
       <c r="P125" s="30">
@@ -30652,7 +30744,7 @@
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="n"/>
       <c r="O126" s="27">
-        <f>IF(M126&lt;&gt;"",M126,K126)</f>
+        <f>IF(M126&lt;&gt;"",M126,IF(OR(K126='설정'!$B$6,K126='설정'!$B$8),SUBSTITUTE(K126,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G126)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G126)),"화목","반")),K126))</f>
         <v/>
       </c>
       <c r="P126" s="30">
@@ -30715,7 +30807,7 @@
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="n"/>
       <c r="O127" s="27">
-        <f>IF(M127&lt;&gt;"",M127,K127)</f>
+        <f>IF(M127&lt;&gt;"",M127,IF(OR(K127='설정'!$B$6,K127='설정'!$B$8),SUBSTITUTE(K127,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G127)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G127)),"화목","반")),K127))</f>
         <v/>
       </c>
       <c r="P127" s="30">
@@ -30778,7 +30870,7 @@
       <c r="M128" s="7" t="n"/>
       <c r="N128" s="7" t="n"/>
       <c r="O128" s="27">
-        <f>IF(M128&lt;&gt;"",M128,K128)</f>
+        <f>IF(M128&lt;&gt;"",M128,IF(OR(K128='설정'!$B$6,K128='설정'!$B$8),SUBSTITUTE(K128,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G128)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G128)),"화목","반")),K128))</f>
         <v/>
       </c>
       <c r="P128" s="30">
@@ -30841,7 +30933,7 @@
       <c r="M129" s="7" t="n"/>
       <c r="N129" s="7" t="n"/>
       <c r="O129" s="27">
-        <f>IF(M129&lt;&gt;"",M129,K129)</f>
+        <f>IF(M129&lt;&gt;"",M129,IF(OR(K129='설정'!$B$6,K129='설정'!$B$8),SUBSTITUTE(K129,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G129)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G129)),"화목","반")),K129))</f>
         <v/>
       </c>
       <c r="P129" s="30">
@@ -30904,7 +30996,7 @@
       <c r="M130" s="7" t="n"/>
       <c r="N130" s="7" t="n"/>
       <c r="O130" s="27">
-        <f>IF(M130&lt;&gt;"",M130,K130)</f>
+        <f>IF(M130&lt;&gt;"",M130,IF(OR(K130='설정'!$B$6,K130='설정'!$B$8),SUBSTITUTE(K130,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G130)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G130)),"화목","반")),K130))</f>
         <v/>
       </c>
       <c r="P130" s="30">
@@ -30967,7 +31059,7 @@
       <c r="M131" s="7" t="n"/>
       <c r="N131" s="7" t="n"/>
       <c r="O131" s="27">
-        <f>IF(M131&lt;&gt;"",M131,K131)</f>
+        <f>IF(M131&lt;&gt;"",M131,IF(OR(K131='설정'!$B$6,K131='설정'!$B$8),SUBSTITUTE(K131,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G131)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G131)),"화목","반")),K131))</f>
         <v/>
       </c>
       <c r="P131" s="30">
@@ -31030,7 +31122,7 @@
       <c r="M132" s="7" t="n"/>
       <c r="N132" s="7" t="n"/>
       <c r="O132" s="27">
-        <f>IF(M132&lt;&gt;"",M132,K132)</f>
+        <f>IF(M132&lt;&gt;"",M132,IF(OR(K132='설정'!$B$6,K132='설정'!$B$8),SUBSTITUTE(K132,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G132)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G132)),"화목","반")),K132))</f>
         <v/>
       </c>
       <c r="P132" s="30">
@@ -31093,7 +31185,7 @@
       <c r="M133" s="7" t="n"/>
       <c r="N133" s="7" t="n"/>
       <c r="O133" s="27">
-        <f>IF(M133&lt;&gt;"",M133,K133)</f>
+        <f>IF(M133&lt;&gt;"",M133,IF(OR(K133='설정'!$B$6,K133='설정'!$B$8),SUBSTITUTE(K133,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G133)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G133)),"화목","반")),K133))</f>
         <v/>
       </c>
       <c r="P133" s="30">
@@ -31156,7 +31248,7 @@
       <c r="M134" s="7" t="n"/>
       <c r="N134" s="7" t="n"/>
       <c r="O134" s="27">
-        <f>IF(M134&lt;&gt;"",M134,K134)</f>
+        <f>IF(M134&lt;&gt;"",M134,IF(OR(K134='설정'!$B$6,K134='설정'!$B$8),SUBSTITUTE(K134,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G134)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G134)),"화목","반")),K134))</f>
         <v/>
       </c>
       <c r="P134" s="30">
@@ -31219,7 +31311,7 @@
       <c r="M135" s="7" t="n"/>
       <c r="N135" s="7" t="n"/>
       <c r="O135" s="27">
-        <f>IF(M135&lt;&gt;"",M135,K135)</f>
+        <f>IF(M135&lt;&gt;"",M135,IF(OR(K135='설정'!$B$6,K135='설정'!$B$8),SUBSTITUTE(K135,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G135)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G135)),"화목","반")),K135))</f>
         <v/>
       </c>
       <c r="P135" s="30">
@@ -31282,7 +31374,7 @@
       <c r="M136" s="7" t="n"/>
       <c r="N136" s="7" t="n"/>
       <c r="O136" s="27">
-        <f>IF(M136&lt;&gt;"",M136,K136)</f>
+        <f>IF(M136&lt;&gt;"",M136,IF(OR(K136='설정'!$B$6,K136='설정'!$B$8),SUBSTITUTE(K136,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G136)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G136)),"화목","반")),K136))</f>
         <v/>
       </c>
       <c r="P136" s="30">
@@ -31345,7 +31437,7 @@
       <c r="M137" s="7" t="n"/>
       <c r="N137" s="7" t="n"/>
       <c r="O137" s="27">
-        <f>IF(M137&lt;&gt;"",M137,K137)</f>
+        <f>IF(M137&lt;&gt;"",M137,IF(OR(K137='설정'!$B$6,K137='설정'!$B$8),SUBSTITUTE(K137,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G137)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G137)),"화목","반")),K137))</f>
         <v/>
       </c>
       <c r="P137" s="30">
@@ -31408,7 +31500,7 @@
       <c r="M138" s="7" t="n"/>
       <c r="N138" s="7" t="n"/>
       <c r="O138" s="27">
-        <f>IF(M138&lt;&gt;"",M138,K138)</f>
+        <f>IF(M138&lt;&gt;"",M138,IF(OR(K138='설정'!$B$6,K138='설정'!$B$8),SUBSTITUTE(K138,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G138)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G138)),"화목","반")),K138))</f>
         <v/>
       </c>
       <c r="P138" s="30">
@@ -31471,7 +31563,7 @@
       <c r="M139" s="7" t="n"/>
       <c r="N139" s="7" t="n"/>
       <c r="O139" s="27">
-        <f>IF(M139&lt;&gt;"",M139,K139)</f>
+        <f>IF(M139&lt;&gt;"",M139,IF(OR(K139='설정'!$B$6,K139='설정'!$B$8),SUBSTITUTE(K139,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G139)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G139)),"화목","반")),K139))</f>
         <v/>
       </c>
       <c r="P139" s="30">
@@ -31534,7 +31626,7 @@
       <c r="M140" s="7" t="n"/>
       <c r="N140" s="7" t="n"/>
       <c r="O140" s="27">
-        <f>IF(M140&lt;&gt;"",M140,K140)</f>
+        <f>IF(M140&lt;&gt;"",M140,IF(OR(K140='설정'!$B$6,K140='설정'!$B$8),SUBSTITUTE(K140,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G140)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G140)),"화목","반")),K140))</f>
         <v/>
       </c>
       <c r="P140" s="30">
@@ -31597,7 +31689,7 @@
       <c r="M141" s="7" t="n"/>
       <c r="N141" s="7" t="n"/>
       <c r="O141" s="27">
-        <f>IF(M141&lt;&gt;"",M141,K141)</f>
+        <f>IF(M141&lt;&gt;"",M141,IF(OR(K141='설정'!$B$6,K141='설정'!$B$8),SUBSTITUTE(K141,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G141)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G141)),"화목","반")),K141))</f>
         <v/>
       </c>
       <c r="P141" s="30">
@@ -31660,7 +31752,7 @@
       <c r="M142" s="7" t="n"/>
       <c r="N142" s="7" t="n"/>
       <c r="O142" s="27">
-        <f>IF(M142&lt;&gt;"",M142,K142)</f>
+        <f>IF(M142&lt;&gt;"",M142,IF(OR(K142='설정'!$B$6,K142='설정'!$B$8),SUBSTITUTE(K142,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G142)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G142)),"화목","반")),K142))</f>
         <v/>
       </c>
       <c r="P142" s="30">
@@ -31723,7 +31815,7 @@
       <c r="M143" s="7" t="n"/>
       <c r="N143" s="7" t="n"/>
       <c r="O143" s="27">
-        <f>IF(M143&lt;&gt;"",M143,K143)</f>
+        <f>IF(M143&lt;&gt;"",M143,IF(OR(K143='설정'!$B$6,K143='설정'!$B$8),SUBSTITUTE(K143,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G143)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G143)),"화목","반")),K143))</f>
         <v/>
       </c>
       <c r="P143" s="30">
@@ -31786,7 +31878,7 @@
       <c r="M144" s="7" t="n"/>
       <c r="N144" s="7" t="n"/>
       <c r="O144" s="27">
-        <f>IF(M144&lt;&gt;"",M144,K144)</f>
+        <f>IF(M144&lt;&gt;"",M144,IF(OR(K144='설정'!$B$6,K144='설정'!$B$8),SUBSTITUTE(K144,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G144)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G144)),"화목","반")),K144))</f>
         <v/>
       </c>
       <c r="P144" s="30">
@@ -31849,7 +31941,7 @@
       <c r="M145" s="7" t="n"/>
       <c r="N145" s="7" t="n"/>
       <c r="O145" s="27">
-        <f>IF(M145&lt;&gt;"",M145,K145)</f>
+        <f>IF(M145&lt;&gt;"",M145,IF(OR(K145='설정'!$B$6,K145='설정'!$B$8),SUBSTITUTE(K145,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G145)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G145)),"화목","반")),K145))</f>
         <v/>
       </c>
       <c r="P145" s="30">
@@ -31912,7 +32004,7 @@
       <c r="M146" s="7" t="n"/>
       <c r="N146" s="7" t="n"/>
       <c r="O146" s="27">
-        <f>IF(M146&lt;&gt;"",M146,K146)</f>
+        <f>IF(M146&lt;&gt;"",M146,IF(OR(K146='설정'!$B$6,K146='설정'!$B$8),SUBSTITUTE(K146,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G146)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G146)),"화목","반")),K146))</f>
         <v/>
       </c>
       <c r="P146" s="30">
@@ -31975,7 +32067,7 @@
       <c r="M147" s="7" t="n"/>
       <c r="N147" s="7" t="n"/>
       <c r="O147" s="27">
-        <f>IF(M147&lt;&gt;"",M147,K147)</f>
+        <f>IF(M147&lt;&gt;"",M147,IF(OR(K147='설정'!$B$6,K147='설정'!$B$8),SUBSTITUTE(K147,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G147)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G147)),"화목","반")),K147))</f>
         <v/>
       </c>
       <c r="P147" s="30">
@@ -32038,7 +32130,7 @@
       <c r="M148" s="7" t="n"/>
       <c r="N148" s="7" t="n"/>
       <c r="O148" s="27">
-        <f>IF(M148&lt;&gt;"",M148,K148)</f>
+        <f>IF(M148&lt;&gt;"",M148,IF(OR(K148='설정'!$B$6,K148='설정'!$B$8),SUBSTITUTE(K148,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G148)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G148)),"화목","반")),K148))</f>
         <v/>
       </c>
       <c r="P148" s="30">
@@ -32101,7 +32193,7 @@
       <c r="M149" s="7" t="n"/>
       <c r="N149" s="7" t="n"/>
       <c r="O149" s="27">
-        <f>IF(M149&lt;&gt;"",M149,K149)</f>
+        <f>IF(M149&lt;&gt;"",M149,IF(OR(K149='설정'!$B$6,K149='설정'!$B$8),SUBSTITUTE(K149,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G149)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G149)),"화목","반")),K149))</f>
         <v/>
       </c>
       <c r="P149" s="30">
@@ -32164,7 +32256,7 @@
       <c r="M150" s="7" t="n"/>
       <c r="N150" s="7" t="n"/>
       <c r="O150" s="27">
-        <f>IF(M150&lt;&gt;"",M150,K150)</f>
+        <f>IF(M150&lt;&gt;"",M150,IF(OR(K150='설정'!$B$6,K150='설정'!$B$8),SUBSTITUTE(K150,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G150)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G150)),"화목","반")),K150))</f>
         <v/>
       </c>
       <c r="P150" s="30">
@@ -32227,7 +32319,7 @@
       <c r="M151" s="7" t="n"/>
       <c r="N151" s="7" t="n"/>
       <c r="O151" s="27">
-        <f>IF(M151&lt;&gt;"",M151,K151)</f>
+        <f>IF(M151&lt;&gt;"",M151,IF(OR(K151='설정'!$B$6,K151='설정'!$B$8),SUBSTITUTE(K151,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G151)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G151)),"화목","반")),K151))</f>
         <v/>
       </c>
       <c r="P151" s="30">
@@ -32290,7 +32382,7 @@
       <c r="M152" s="7" t="n"/>
       <c r="N152" s="7" t="n"/>
       <c r="O152" s="27">
-        <f>IF(M152&lt;&gt;"",M152,K152)</f>
+        <f>IF(M152&lt;&gt;"",M152,IF(OR(K152='설정'!$B$6,K152='설정'!$B$8),SUBSTITUTE(K152,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G152)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G152)),"화목","반")),K152))</f>
         <v/>
       </c>
       <c r="P152" s="30">
@@ -32353,7 +32445,7 @@
       <c r="M153" s="7" t="n"/>
       <c r="N153" s="7" t="n"/>
       <c r="O153" s="27">
-        <f>IF(M153&lt;&gt;"",M153,K153)</f>
+        <f>IF(M153&lt;&gt;"",M153,IF(OR(K153='설정'!$B$6,K153='설정'!$B$8),SUBSTITUTE(K153,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G153)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G153)),"화목","반")),K153))</f>
         <v/>
       </c>
       <c r="P153" s="30">
@@ -32416,7 +32508,7 @@
       <c r="M154" s="7" t="n"/>
       <c r="N154" s="7" t="n"/>
       <c r="O154" s="27">
-        <f>IF(M154&lt;&gt;"",M154,K154)</f>
+        <f>IF(M154&lt;&gt;"",M154,IF(OR(K154='설정'!$B$6,K154='설정'!$B$8),SUBSTITUTE(K154,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G154)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G154)),"화목","반")),K154))</f>
         <v/>
       </c>
       <c r="P154" s="30">
@@ -32479,7 +32571,7 @@
       <c r="M155" s="7" t="n"/>
       <c r="N155" s="7" t="n"/>
       <c r="O155" s="27">
-        <f>IF(M155&lt;&gt;"",M155,K155)</f>
+        <f>IF(M155&lt;&gt;"",M155,IF(OR(K155='설정'!$B$6,K155='설정'!$B$8),SUBSTITUTE(K155,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G155)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G155)),"화목","반")),K155))</f>
         <v/>
       </c>
       <c r="P155" s="30">
@@ -32542,7 +32634,7 @@
       <c r="M156" s="7" t="n"/>
       <c r="N156" s="7" t="n"/>
       <c r="O156" s="27">
-        <f>IF(M156&lt;&gt;"",M156,K156)</f>
+        <f>IF(M156&lt;&gt;"",M156,IF(OR(K156='설정'!$B$6,K156='설정'!$B$8),SUBSTITUTE(K156,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G156)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G156)),"화목","반")),K156))</f>
         <v/>
       </c>
       <c r="P156" s="30">
@@ -32567,30 +32659,30 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:K156">
     <cfRule type="expression" priority="2" dxfId="3">
-      <formula>AND($K7&lt;&gt;"",$K7='설정'!$B$6)</formula>
+      <formula>AND($K7&lt;&gt;"",LEFT($K7,LEN(SUBSTITUTE('설정'!$B$6,"반","")))=SUBSTITUTE('설정'!$B$6,"반",""))</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="4">
-      <formula>AND($K7&lt;&gt;"",$K7='설정'!$B$7)</formula>
+      <formula>AND($K7&lt;&gt;"",LEFT($K7,LEN(SUBSTITUTE('설정'!$B$7,"반","")))=SUBSTITUTE('설정'!$B$7,"반",""))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="5">
-      <formula>AND($K7&lt;&gt;"",$K7='설정'!$B$8)</formula>
+      <formula>AND($K7&lt;&gt;"",LEFT($K7,LEN(SUBSTITUTE('설정'!$B$8,"반","")))=SUBSTITUTE('설정'!$B$8,"반",""))</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="6">
-      <formula>AND($K7&lt;&gt;"",$K7='설정'!$B$9)</formula>
+      <formula>AND($K7&lt;&gt;"",LEFT($K7,LEN(SUBSTITUTE('설정'!$B$9,"반","")))=SUBSTITUTE('설정'!$B$9,"반",""))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O7:O156">
     <cfRule type="expression" priority="6" dxfId="3">
-      <formula>AND($O7&lt;&gt;"",$O7='설정'!$B$6)</formula>
+      <formula>AND($O7&lt;&gt;"",LEFT($O7,LEN(SUBSTITUTE('설정'!$B$6,"반","")))=SUBSTITUTE('설정'!$B$6,"반",""))</formula>
     </cfRule>
     <cfRule type="expression" priority="7" dxfId="4">
-      <formula>AND($O7&lt;&gt;"",$O7='설정'!$B$7)</formula>
+      <formula>AND($O7&lt;&gt;"",LEFT($O7,LEN(SUBSTITUTE('설정'!$B$7,"반","")))=SUBSTITUTE('설정'!$B$7,"반",""))</formula>
     </cfRule>
     <cfRule type="expression" priority="8" dxfId="5">
-      <formula>AND($O7&lt;&gt;"",$O7='설정'!$B$8)</formula>
+      <formula>AND($O7&lt;&gt;"",LEFT($O7,LEN(SUBSTITUTE('설정'!$B$8,"반","")))=SUBSTITUTE('설정'!$B$8,"반",""))</formula>
     </cfRule>
     <cfRule type="expression" priority="9" dxfId="6">
-      <formula>AND($O7&lt;&gt;"",$O7='설정'!$B$9)</formula>
+      <formula>AND($O7&lt;&gt;"",LEFT($O7,LEN(SUBSTITUTE('설정'!$B$9,"반","")))=SUBSTITUTE('설정'!$B$9,"반",""))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -951,6 +951,23 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>학교 지정</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>TF1월</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>학생명단 '자사/일반' 칸에 학교가 적힌 학생은 점수와 관계없이 이 반 (비우면 적용 안 함)</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1648,7 @@
       <c r="B69" s="16" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="37">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B49:E49"/>
     <mergeCell ref="B65:E65"/>
@@ -1658,6 +1675,7 @@
     <mergeCell ref="B58:E58"/>
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="B39:E39"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="B60:E60"/>
     <mergeCell ref="B67:E67"/>
     <mergeCell ref="C9:F9"/>
@@ -23006,7 +23024,7 @@
       <c r="M7" s="7" t="n"/>
       <c r="N7" s="7" t="n"/>
       <c r="O7" s="27">
-        <f>IF(M7&lt;&gt;"",M7,IF(OR(K7='설정'!$B$6,K7='설정'!$B$8),SUBSTITUTE(K7,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G7)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G7)),"화목","반")),K7))</f>
+        <f>IF(M7&lt;&gt;"",M7,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K7&lt;&gt;""),'설정'!$B$10,IF(OR(K7='설정'!$B$6,K7='설정'!$B$8),SUBSTITUTE(K7,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G7)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G7)),"화목","반")),K7)))</f>
         <v/>
       </c>
       <c r="P7" s="30">
@@ -23097,7 +23115,7 @@
       <c r="M8" s="7" t="n"/>
       <c r="N8" s="7" t="n"/>
       <c r="O8" s="27">
-        <f>IF(M8&lt;&gt;"",M8,IF(OR(K8='설정'!$B$6,K8='설정'!$B$8),SUBSTITUTE(K8,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G8)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G8)),"화목","반")),K8))</f>
+        <f>IF(M8&lt;&gt;"",M8,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K8&lt;&gt;""),'설정'!$B$10,IF(OR(K8='설정'!$B$6,K8='설정'!$B$8),SUBSTITUTE(K8,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G8)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G8)),"화목","반")),K8)))</f>
         <v/>
       </c>
       <c r="P8" s="30">
@@ -23188,7 +23206,7 @@
       <c r="M9" s="7" t="n"/>
       <c r="N9" s="7" t="n"/>
       <c r="O9" s="27">
-        <f>IF(M9&lt;&gt;"",M9,IF(OR(K9='설정'!$B$6,K9='설정'!$B$8),SUBSTITUTE(K9,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G9)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G9)),"화목","반")),K9))</f>
+        <f>IF(M9&lt;&gt;"",M9,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K9&lt;&gt;""),'설정'!$B$10,IF(OR(K9='설정'!$B$6,K9='설정'!$B$8),SUBSTITUTE(K9,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G9)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G9)),"화목","반")),K9)))</f>
         <v/>
       </c>
       <c r="P9" s="30">
@@ -23279,7 +23297,7 @@
       <c r="M10" s="7" t="n"/>
       <c r="N10" s="7" t="n"/>
       <c r="O10" s="27">
-        <f>IF(M10&lt;&gt;"",M10,IF(OR(K10='설정'!$B$6,K10='설정'!$B$8),SUBSTITUTE(K10,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G10)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G10)),"화목","반")),K10))</f>
+        <f>IF(M10&lt;&gt;"",M10,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K10&lt;&gt;""),'설정'!$B$10,IF(OR(K10='설정'!$B$6,K10='설정'!$B$8),SUBSTITUTE(K10,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G10)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G10)),"화목","반")),K10)))</f>
         <v/>
       </c>
       <c r="P10" s="30">
@@ -23370,7 +23388,7 @@
       <c r="M11" s="7" t="n"/>
       <c r="N11" s="7" t="n"/>
       <c r="O11" s="27">
-        <f>IF(M11&lt;&gt;"",M11,IF(OR(K11='설정'!$B$6,K11='설정'!$B$8),SUBSTITUTE(K11,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G11)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G11)),"화목","반")),K11))</f>
+        <f>IF(M11&lt;&gt;"",M11,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K11&lt;&gt;""),'설정'!$B$10,IF(OR(K11='설정'!$B$6,K11='설정'!$B$8),SUBSTITUTE(K11,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G11)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G11)),"화목","반")),K11)))</f>
         <v/>
       </c>
       <c r="P11" s="30">
@@ -23462,7 +23480,7 @@
       <c r="M12" s="7" t="n"/>
       <c r="N12" s="7" t="n"/>
       <c r="O12" s="27">
-        <f>IF(M12&lt;&gt;"",M12,IF(OR(K12='설정'!$B$6,K12='설정'!$B$8),SUBSTITUTE(K12,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G12)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G12)),"화목","반")),K12))</f>
+        <f>IF(M12&lt;&gt;"",M12,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K12&lt;&gt;""),'설정'!$B$10,IF(OR(K12='설정'!$B$6,K12='설정'!$B$8),SUBSTITUTE(K12,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G12)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G12)),"화목","반")),K12)))</f>
         <v/>
       </c>
       <c r="P12" s="30">
@@ -23525,7 +23543,7 @@
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n"/>
       <c r="O13" s="27">
-        <f>IF(M13&lt;&gt;"",M13,IF(OR(K13='설정'!$B$6,K13='설정'!$B$8),SUBSTITUTE(K13,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G13)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G13)),"화목","반")),K13))</f>
+        <f>IF(M13&lt;&gt;"",M13,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K13&lt;&gt;""),'설정'!$B$10,IF(OR(K13='설정'!$B$6,K13='설정'!$B$8),SUBSTITUTE(K13,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G13)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G13)),"화목","반")),K13)))</f>
         <v/>
       </c>
       <c r="P13" s="30">
@@ -23540,7 +23558,7 @@
         <is>
           <t>· 자동배정은 '설정' ①의 기준(공수1 점수·한 과목 점수·합계)
 · 경계 = 과목 점수나 합계가 기준 점수와 경계 범위 이내
-· 공통수학반(최종): TF1·TF2는 현재 등원 요일에 따라 월금/화목 반(예: TF1월금, TF2화목)
+· 공통수학반(최종): '자사/일반'에 학교가 적힌 학생은 '설정' B10 반, 그 외 TF1·TF2는 등원 요일에 따라 월금/화목
 · 공통수학반·선행반은 목록에서 고르거나 직접 입력('설정' ⑥·⑦에 반 소개 추가 가능)
 · 환산총점·석차는 참고용</t>
         </is>
@@ -23597,7 +23615,7 @@
       <c r="M14" s="7" t="n"/>
       <c r="N14" s="7" t="n"/>
       <c r="O14" s="27">
-        <f>IF(M14&lt;&gt;"",M14,IF(OR(K14='설정'!$B$6,K14='설정'!$B$8),SUBSTITUTE(K14,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G14)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G14)),"화목","반")),K14))</f>
+        <f>IF(M14&lt;&gt;"",M14,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K14&lt;&gt;""),'설정'!$B$10,IF(OR(K14='설정'!$B$6,K14='설정'!$B$8),SUBSTITUTE(K14,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G14)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G14)),"화목","반")),K14)))</f>
         <v/>
       </c>
       <c r="P14" s="30">
@@ -23660,7 +23678,7 @@
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
       <c r="O15" s="27">
-        <f>IF(M15&lt;&gt;"",M15,IF(OR(K15='설정'!$B$6,K15='설정'!$B$8),SUBSTITUTE(K15,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G15)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G15)),"화목","반")),K15))</f>
+        <f>IF(M15&lt;&gt;"",M15,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K15&lt;&gt;""),'설정'!$B$10,IF(OR(K15='설정'!$B$6,K15='설정'!$B$8),SUBSTITUTE(K15,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G15)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G15)),"화목","반")),K15)))</f>
         <v/>
       </c>
       <c r="P15" s="30">
@@ -23723,7 +23741,7 @@
       <c r="M16" s="7" t="n"/>
       <c r="N16" s="7" t="n"/>
       <c r="O16" s="27">
-        <f>IF(M16&lt;&gt;"",M16,IF(OR(K16='설정'!$B$6,K16='설정'!$B$8),SUBSTITUTE(K16,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G16)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G16)),"화목","반")),K16))</f>
+        <f>IF(M16&lt;&gt;"",M16,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K16&lt;&gt;""),'설정'!$B$10,IF(OR(K16='설정'!$B$6,K16='설정'!$B$8),SUBSTITUTE(K16,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G16)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G16)),"화목","반")),K16)))</f>
         <v/>
       </c>
       <c r="P16" s="30">
@@ -23786,7 +23804,7 @@
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="7" t="n"/>
       <c r="O17" s="27">
-        <f>IF(M17&lt;&gt;"",M17,IF(OR(K17='설정'!$B$6,K17='설정'!$B$8),SUBSTITUTE(K17,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G17)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G17)),"화목","반")),K17))</f>
+        <f>IF(M17&lt;&gt;"",M17,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K17&lt;&gt;""),'설정'!$B$10,IF(OR(K17='설정'!$B$6,K17='설정'!$B$8),SUBSTITUTE(K17,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G17)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G17)),"화목","반")),K17)))</f>
         <v/>
       </c>
       <c r="P17" s="30">
@@ -23849,7 +23867,7 @@
       <c r="M18" s="7" t="n"/>
       <c r="N18" s="7" t="n"/>
       <c r="O18" s="27">
-        <f>IF(M18&lt;&gt;"",M18,IF(OR(K18='설정'!$B$6,K18='설정'!$B$8),SUBSTITUTE(K18,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G18)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G18)),"화목","반")),K18))</f>
+        <f>IF(M18&lt;&gt;"",M18,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K18&lt;&gt;""),'설정'!$B$10,IF(OR(K18='설정'!$B$6,K18='설정'!$B$8),SUBSTITUTE(K18,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G18)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G18)),"화목","반")),K18)))</f>
         <v/>
       </c>
       <c r="P18" s="30">
@@ -23912,7 +23930,7 @@
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n"/>
       <c r="O19" s="27">
-        <f>IF(M19&lt;&gt;"",M19,IF(OR(K19='설정'!$B$6,K19='설정'!$B$8),SUBSTITUTE(K19,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G19)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G19)),"화목","반")),K19))</f>
+        <f>IF(M19&lt;&gt;"",M19,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K19&lt;&gt;""),'설정'!$B$10,IF(OR(K19='설정'!$B$6,K19='설정'!$B$8),SUBSTITUTE(K19,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G19)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G19)),"화목","반")),K19)))</f>
         <v/>
       </c>
       <c r="P19" s="30">
@@ -23975,7 +23993,7 @@
       <c r="M20" s="7" t="n"/>
       <c r="N20" s="7" t="n"/>
       <c r="O20" s="27">
-        <f>IF(M20&lt;&gt;"",M20,IF(OR(K20='설정'!$B$6,K20='설정'!$B$8),SUBSTITUTE(K20,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G20)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G20)),"화목","반")),K20))</f>
+        <f>IF(M20&lt;&gt;"",M20,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K20&lt;&gt;""),'설정'!$B$10,IF(OR(K20='설정'!$B$6,K20='설정'!$B$8),SUBSTITUTE(K20,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G20)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G20)),"화목","반")),K20)))</f>
         <v/>
       </c>
       <c r="P20" s="30">
@@ -24043,7 +24061,7 @@
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n"/>
       <c r="O21" s="27">
-        <f>IF(M21&lt;&gt;"",M21,IF(OR(K21='설정'!$B$6,K21='설정'!$B$8),SUBSTITUTE(K21,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G21)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G21)),"화목","반")),K21))</f>
+        <f>IF(M21&lt;&gt;"",M21,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K21&lt;&gt;""),'설정'!$B$10,IF(OR(K21='설정'!$B$6,K21='설정'!$B$8),SUBSTITUTE(K21,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G21)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G21)),"화목","반")),K21)))</f>
         <v/>
       </c>
       <c r="P21" s="30">
@@ -24128,7 +24146,7 @@
       <c r="M22" s="7" t="n"/>
       <c r="N22" s="7" t="n"/>
       <c r="O22" s="27">
-        <f>IF(M22&lt;&gt;"",M22,IF(OR(K22='설정'!$B$6,K22='설정'!$B$8),SUBSTITUTE(K22,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G22)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G22)),"화목","반")),K22))</f>
+        <f>IF(M22&lt;&gt;"",M22,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K22&lt;&gt;""),'설정'!$B$10,IF(OR(K22='설정'!$B$6,K22='설정'!$B$8),SUBSTITUTE(K22,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G22)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G22)),"화목","반")),K22)))</f>
         <v/>
       </c>
       <c r="P22" s="30">
@@ -24140,7 +24158,7 @@
         <v/>
       </c>
       <c r="S22" s="31">
-        <f>SUBSTITUTE('설정'!$B$6,"반","")&amp;"월금"</f>
+        <f>IF('설정'!$B$10="","-",'설정'!$B$10)</f>
         <v/>
       </c>
       <c r="T22" s="27">
@@ -24207,7 +24225,7 @@
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n"/>
       <c r="O23" s="27">
-        <f>IF(M23&lt;&gt;"",M23,IF(OR(K23='설정'!$B$6,K23='설정'!$B$8),SUBSTITUTE(K23,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G23)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G23)),"화목","반")),K23))</f>
+        <f>IF(M23&lt;&gt;"",M23,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K23&lt;&gt;""),'설정'!$B$10,IF(OR(K23='설정'!$B$6,K23='설정'!$B$8),SUBSTITUTE(K23,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G23)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G23)),"화목","반")),K23)))</f>
         <v/>
       </c>
       <c r="P23" s="30">
@@ -24219,7 +24237,7 @@
         <v/>
       </c>
       <c r="S23" s="31">
-        <f>SUBSTITUTE('설정'!$B$6,"반","")&amp;"화목"</f>
+        <f>SUBSTITUTE('설정'!$B$6,"반","")&amp;"월금"</f>
         <v/>
       </c>
       <c r="T23" s="27">
@@ -24286,7 +24304,7 @@
       <c r="M24" s="7" t="n"/>
       <c r="N24" s="7" t="n"/>
       <c r="O24" s="27">
-        <f>IF(M24&lt;&gt;"",M24,IF(OR(K24='설정'!$B$6,K24='설정'!$B$8),SUBSTITUTE(K24,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G24)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G24)),"화목","반")),K24))</f>
+        <f>IF(M24&lt;&gt;"",M24,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K24&lt;&gt;""),'설정'!$B$10,IF(OR(K24='설정'!$B$6,K24='설정'!$B$8),SUBSTITUTE(K24,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G24)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G24)),"화목","반")),K24)))</f>
         <v/>
       </c>
       <c r="P24" s="30">
@@ -24297,8 +24315,8 @@
         <f>IF(J24="","",J24+ROW()/100000)</f>
         <v/>
       </c>
-      <c r="S24" s="34">
-        <f>SUBSTITUTE('설정'!$B$8,"반","")&amp;"월금"</f>
+      <c r="S24" s="31">
+        <f>SUBSTITUTE('설정'!$B$6,"반","")&amp;"화목"</f>
         <v/>
       </c>
       <c r="T24" s="27">
@@ -24365,7 +24383,7 @@
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
       <c r="O25" s="27">
-        <f>IF(M25&lt;&gt;"",M25,IF(OR(K25='설정'!$B$6,K25='설정'!$B$8),SUBSTITUTE(K25,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G25)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G25)),"화목","반")),K25))</f>
+        <f>IF(M25&lt;&gt;"",M25,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K25&lt;&gt;""),'설정'!$B$10,IF(OR(K25='설정'!$B$6,K25='설정'!$B$8),SUBSTITUTE(K25,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G25)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G25)),"화목","반")),K25)))</f>
         <v/>
       </c>
       <c r="P25" s="30">
@@ -24377,7 +24395,7 @@
         <v/>
       </c>
       <c r="S25" s="34">
-        <f>SUBSTITUTE('설정'!$B$8,"반","")&amp;"화목"</f>
+        <f>SUBSTITUTE('설정'!$B$8,"반","")&amp;"월금"</f>
         <v/>
       </c>
       <c r="T25" s="27">
@@ -24444,7 +24462,7 @@
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="7" t="n"/>
       <c r="O26" s="27">
-        <f>IF(M26&lt;&gt;"",M26,IF(OR(K26='설정'!$B$6,K26='설정'!$B$8),SUBSTITUTE(K26,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G26)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G26)),"화목","반")),K26))</f>
+        <f>IF(M26&lt;&gt;"",M26,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K26&lt;&gt;""),'설정'!$B$10,IF(OR(K26='설정'!$B$6,K26='설정'!$B$8),SUBSTITUTE(K26,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G26)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G26)),"화목","반")),K26)))</f>
         <v/>
       </c>
       <c r="P26" s="30">
@@ -24453,6 +24471,22 @@
       </c>
       <c r="Q26" s="10">
         <f>IF(J26="","",J26+ROW()/100000)</f>
+        <v/>
+      </c>
+      <c r="S26" s="34">
+        <f>SUBSTITUTE('설정'!$B$8,"반","")&amp;"화목"</f>
+        <v/>
+      </c>
+      <c r="T26" s="27">
+        <f>COUNTIF($O$7:$O$156,S26)</f>
+        <v/>
+      </c>
+      <c r="U26" s="32">
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,S26,$G$7:$G$156),"")</f>
+        <v/>
+      </c>
+      <c r="V26" s="32">
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,S26,$H$7:$H$156),"")</f>
         <v/>
       </c>
     </row>
@@ -24507,7 +24541,7 @@
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
       <c r="O27" s="27">
-        <f>IF(M27&lt;&gt;"",M27,IF(OR(K27='설정'!$B$6,K27='설정'!$B$8),SUBSTITUTE(K27,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G27)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G27)),"화목","반")),K27))</f>
+        <f>IF(M27&lt;&gt;"",M27,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K27&lt;&gt;""),'설정'!$B$10,IF(OR(K27='설정'!$B$6,K27='설정'!$B$8),SUBSTITUTE(K27,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G27)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G27)),"화목","반")),K27)))</f>
         <v/>
       </c>
       <c r="P27" s="30">
@@ -24570,7 +24604,7 @@
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="7" t="n"/>
       <c r="O28" s="27">
-        <f>IF(M28&lt;&gt;"",M28,IF(OR(K28='설정'!$B$6,K28='설정'!$B$8),SUBSTITUTE(K28,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G28)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G28)),"화목","반")),K28))</f>
+        <f>IF(M28&lt;&gt;"",M28,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K28&lt;&gt;""),'설정'!$B$10,IF(OR(K28='설정'!$B$6,K28='설정'!$B$8),SUBSTITUTE(K28,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G28)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G28)),"화목","반")),K28)))</f>
         <v/>
       </c>
       <c r="P28" s="30">
@@ -24633,7 +24667,7 @@
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
       <c r="O29" s="27">
-        <f>IF(M29&lt;&gt;"",M29,IF(OR(K29='설정'!$B$6,K29='설정'!$B$8),SUBSTITUTE(K29,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G29)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G29)),"화목","반")),K29))</f>
+        <f>IF(M29&lt;&gt;"",M29,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K29&lt;&gt;""),'설정'!$B$10,IF(OR(K29='설정'!$B$6,K29='설정'!$B$8),SUBSTITUTE(K29,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G29)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G29)),"화목","반")),K29)))</f>
         <v/>
       </c>
       <c r="P29" s="30">
@@ -24696,7 +24730,7 @@
       <c r="M30" s="7" t="n"/>
       <c r="N30" s="7" t="n"/>
       <c r="O30" s="27">
-        <f>IF(M30&lt;&gt;"",M30,IF(OR(K30='설정'!$B$6,K30='설정'!$B$8),SUBSTITUTE(K30,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G30)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G30)),"화목","반")),K30))</f>
+        <f>IF(M30&lt;&gt;"",M30,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K30&lt;&gt;""),'설정'!$B$10,IF(OR(K30='설정'!$B$6,K30='설정'!$B$8),SUBSTITUTE(K30,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G30)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G30)),"화목","반")),K30)))</f>
         <v/>
       </c>
       <c r="P30" s="30">
@@ -24759,7 +24793,7 @@
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n"/>
       <c r="O31" s="27">
-        <f>IF(M31&lt;&gt;"",M31,IF(OR(K31='설정'!$B$6,K31='설정'!$B$8),SUBSTITUTE(K31,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G31)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G31)),"화목","반")),K31))</f>
+        <f>IF(M31&lt;&gt;"",M31,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K31&lt;&gt;""),'설정'!$B$10,IF(OR(K31='설정'!$B$6,K31='설정'!$B$8),SUBSTITUTE(K31,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G31)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G31)),"화목","반")),K31)))</f>
         <v/>
       </c>
       <c r="P31" s="30">
@@ -24822,7 +24856,7 @@
       <c r="M32" s="7" t="n"/>
       <c r="N32" s="7" t="n"/>
       <c r="O32" s="27">
-        <f>IF(M32&lt;&gt;"",M32,IF(OR(K32='설정'!$B$6,K32='설정'!$B$8),SUBSTITUTE(K32,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G32)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G32)),"화목","반")),K32))</f>
+        <f>IF(M32&lt;&gt;"",M32,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K32&lt;&gt;""),'설정'!$B$10,IF(OR(K32='설정'!$B$6,K32='설정'!$B$8),SUBSTITUTE(K32,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G32)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G32)),"화목","반")),K32)))</f>
         <v/>
       </c>
       <c r="P32" s="30">
@@ -24885,7 +24919,7 @@
       <c r="M33" s="7" t="n"/>
       <c r="N33" s="7" t="n"/>
       <c r="O33" s="27">
-        <f>IF(M33&lt;&gt;"",M33,IF(OR(K33='설정'!$B$6,K33='설정'!$B$8),SUBSTITUTE(K33,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G33)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G33)),"화목","반")),K33))</f>
+        <f>IF(M33&lt;&gt;"",M33,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K33&lt;&gt;""),'설정'!$B$10,IF(OR(K33='설정'!$B$6,K33='설정'!$B$8),SUBSTITUTE(K33,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G33)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G33)),"화목","반")),K33)))</f>
         <v/>
       </c>
       <c r="P33" s="30">
@@ -24948,7 +24982,7 @@
       <c r="M34" s="7" t="n"/>
       <c r="N34" s="7" t="n"/>
       <c r="O34" s="27">
-        <f>IF(M34&lt;&gt;"",M34,IF(OR(K34='설정'!$B$6,K34='설정'!$B$8),SUBSTITUTE(K34,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G34)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G34)),"화목","반")),K34))</f>
+        <f>IF(M34&lt;&gt;"",M34,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K34&lt;&gt;""),'설정'!$B$10,IF(OR(K34='설정'!$B$6,K34='설정'!$B$8),SUBSTITUTE(K34,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G34)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G34)),"화목","반")),K34)))</f>
         <v/>
       </c>
       <c r="P34" s="30">
@@ -25011,7 +25045,7 @@
       <c r="M35" s="7" t="n"/>
       <c r="N35" s="7" t="n"/>
       <c r="O35" s="27">
-        <f>IF(M35&lt;&gt;"",M35,IF(OR(K35='설정'!$B$6,K35='설정'!$B$8),SUBSTITUTE(K35,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G35)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G35)),"화목","반")),K35))</f>
+        <f>IF(M35&lt;&gt;"",M35,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K35&lt;&gt;""),'설정'!$B$10,IF(OR(K35='설정'!$B$6,K35='설정'!$B$8),SUBSTITUTE(K35,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G35)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G35)),"화목","반")),K35)))</f>
         <v/>
       </c>
       <c r="P35" s="30">
@@ -25074,7 +25108,7 @@
       <c r="M36" s="7" t="n"/>
       <c r="N36" s="7" t="n"/>
       <c r="O36" s="27">
-        <f>IF(M36&lt;&gt;"",M36,IF(OR(K36='설정'!$B$6,K36='설정'!$B$8),SUBSTITUTE(K36,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G36)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G36)),"화목","반")),K36))</f>
+        <f>IF(M36&lt;&gt;"",M36,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K36&lt;&gt;""),'설정'!$B$10,IF(OR(K36='설정'!$B$6,K36='설정'!$B$8),SUBSTITUTE(K36,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G36)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G36)),"화목","반")),K36)))</f>
         <v/>
       </c>
       <c r="P36" s="30">
@@ -25137,7 +25171,7 @@
       <c r="M37" s="7" t="n"/>
       <c r="N37" s="7" t="n"/>
       <c r="O37" s="27">
-        <f>IF(M37&lt;&gt;"",M37,IF(OR(K37='설정'!$B$6,K37='설정'!$B$8),SUBSTITUTE(K37,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G37)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G37)),"화목","반")),K37))</f>
+        <f>IF(M37&lt;&gt;"",M37,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K37&lt;&gt;""),'설정'!$B$10,IF(OR(K37='설정'!$B$6,K37='설정'!$B$8),SUBSTITUTE(K37,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G37)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G37)),"화목","반")),K37)))</f>
         <v/>
       </c>
       <c r="P37" s="30">
@@ -25200,7 +25234,7 @@
       <c r="M38" s="7" t="n"/>
       <c r="N38" s="7" t="n"/>
       <c r="O38" s="27">
-        <f>IF(M38&lt;&gt;"",M38,IF(OR(K38='설정'!$B$6,K38='설정'!$B$8),SUBSTITUTE(K38,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G38)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G38)),"화목","반")),K38))</f>
+        <f>IF(M38&lt;&gt;"",M38,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K38&lt;&gt;""),'설정'!$B$10,IF(OR(K38='설정'!$B$6,K38='설정'!$B$8),SUBSTITUTE(K38,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G38)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G38)),"화목","반")),K38)))</f>
         <v/>
       </c>
       <c r="P38" s="30">
@@ -25263,7 +25297,7 @@
       <c r="M39" s="7" t="n"/>
       <c r="N39" s="7" t="n"/>
       <c r="O39" s="27">
-        <f>IF(M39&lt;&gt;"",M39,IF(OR(K39='설정'!$B$6,K39='설정'!$B$8),SUBSTITUTE(K39,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G39)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G39)),"화목","반")),K39))</f>
+        <f>IF(M39&lt;&gt;"",M39,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K39&lt;&gt;""),'설정'!$B$10,IF(OR(K39='설정'!$B$6,K39='설정'!$B$8),SUBSTITUTE(K39,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G39)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G39)),"화목","반")),K39)))</f>
         <v/>
       </c>
       <c r="P39" s="30">
@@ -25326,7 +25360,7 @@
       <c r="M40" s="7" t="n"/>
       <c r="N40" s="7" t="n"/>
       <c r="O40" s="27">
-        <f>IF(M40&lt;&gt;"",M40,IF(OR(K40='설정'!$B$6,K40='설정'!$B$8),SUBSTITUTE(K40,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G40)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G40)),"화목","반")),K40))</f>
+        <f>IF(M40&lt;&gt;"",M40,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K40&lt;&gt;""),'설정'!$B$10,IF(OR(K40='설정'!$B$6,K40='설정'!$B$8),SUBSTITUTE(K40,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G40)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G40)),"화목","반")),K40)))</f>
         <v/>
       </c>
       <c r="P40" s="30">
@@ -25389,7 +25423,7 @@
       <c r="M41" s="7" t="n"/>
       <c r="N41" s="7" t="n"/>
       <c r="O41" s="27">
-        <f>IF(M41&lt;&gt;"",M41,IF(OR(K41='설정'!$B$6,K41='설정'!$B$8),SUBSTITUTE(K41,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G41)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G41)),"화목","반")),K41))</f>
+        <f>IF(M41&lt;&gt;"",M41,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K41&lt;&gt;""),'설정'!$B$10,IF(OR(K41='설정'!$B$6,K41='설정'!$B$8),SUBSTITUTE(K41,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G41)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G41)),"화목","반")),K41)))</f>
         <v/>
       </c>
       <c r="P41" s="30">
@@ -25452,7 +25486,7 @@
       <c r="M42" s="7" t="n"/>
       <c r="N42" s="7" t="n"/>
       <c r="O42" s="27">
-        <f>IF(M42&lt;&gt;"",M42,IF(OR(K42='설정'!$B$6,K42='설정'!$B$8),SUBSTITUTE(K42,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G42)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G42)),"화목","반")),K42))</f>
+        <f>IF(M42&lt;&gt;"",M42,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K42&lt;&gt;""),'설정'!$B$10,IF(OR(K42='설정'!$B$6,K42='설정'!$B$8),SUBSTITUTE(K42,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G42)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G42)),"화목","반")),K42)))</f>
         <v/>
       </c>
       <c r="P42" s="30">
@@ -25515,7 +25549,7 @@
       <c r="M43" s="7" t="n"/>
       <c r="N43" s="7" t="n"/>
       <c r="O43" s="27">
-        <f>IF(M43&lt;&gt;"",M43,IF(OR(K43='설정'!$B$6,K43='설정'!$B$8),SUBSTITUTE(K43,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G43)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G43)),"화목","반")),K43))</f>
+        <f>IF(M43&lt;&gt;"",M43,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K43&lt;&gt;""),'설정'!$B$10,IF(OR(K43='설정'!$B$6,K43='설정'!$B$8),SUBSTITUTE(K43,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G43)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G43)),"화목","반")),K43)))</f>
         <v/>
       </c>
       <c r="P43" s="30">
@@ -25578,7 +25612,7 @@
       <c r="M44" s="7" t="n"/>
       <c r="N44" s="7" t="n"/>
       <c r="O44" s="27">
-        <f>IF(M44&lt;&gt;"",M44,IF(OR(K44='설정'!$B$6,K44='설정'!$B$8),SUBSTITUTE(K44,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G44)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G44)),"화목","반")),K44))</f>
+        <f>IF(M44&lt;&gt;"",M44,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K44&lt;&gt;""),'설정'!$B$10,IF(OR(K44='설정'!$B$6,K44='설정'!$B$8),SUBSTITUTE(K44,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G44)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G44)),"화목","반")),K44)))</f>
         <v/>
       </c>
       <c r="P44" s="30">
@@ -25641,7 +25675,7 @@
       <c r="M45" s="7" t="n"/>
       <c r="N45" s="7" t="n"/>
       <c r="O45" s="27">
-        <f>IF(M45&lt;&gt;"",M45,IF(OR(K45='설정'!$B$6,K45='설정'!$B$8),SUBSTITUTE(K45,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G45)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G45)),"화목","반")),K45))</f>
+        <f>IF(M45&lt;&gt;"",M45,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K45&lt;&gt;""),'설정'!$B$10,IF(OR(K45='설정'!$B$6,K45='설정'!$B$8),SUBSTITUTE(K45,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G45)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G45)),"화목","반")),K45)))</f>
         <v/>
       </c>
       <c r="P45" s="30">
@@ -25704,7 +25738,7 @@
       <c r="M46" s="7" t="n"/>
       <c r="N46" s="7" t="n"/>
       <c r="O46" s="27">
-        <f>IF(M46&lt;&gt;"",M46,IF(OR(K46='설정'!$B$6,K46='설정'!$B$8),SUBSTITUTE(K46,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G46)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G46)),"화목","반")),K46))</f>
+        <f>IF(M46&lt;&gt;"",M46,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K46&lt;&gt;""),'설정'!$B$10,IF(OR(K46='설정'!$B$6,K46='설정'!$B$8),SUBSTITUTE(K46,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G46)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G46)),"화목","반")),K46)))</f>
         <v/>
       </c>
       <c r="P46" s="30">
@@ -25767,7 +25801,7 @@
       <c r="M47" s="7" t="n"/>
       <c r="N47" s="7" t="n"/>
       <c r="O47" s="27">
-        <f>IF(M47&lt;&gt;"",M47,IF(OR(K47='설정'!$B$6,K47='설정'!$B$8),SUBSTITUTE(K47,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G47)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G47)),"화목","반")),K47))</f>
+        <f>IF(M47&lt;&gt;"",M47,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K47&lt;&gt;""),'설정'!$B$10,IF(OR(K47='설정'!$B$6,K47='설정'!$B$8),SUBSTITUTE(K47,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G47)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G47)),"화목","반")),K47)))</f>
         <v/>
       </c>
       <c r="P47" s="30">
@@ -25830,7 +25864,7 @@
       <c r="M48" s="7" t="n"/>
       <c r="N48" s="7" t="n"/>
       <c r="O48" s="27">
-        <f>IF(M48&lt;&gt;"",M48,IF(OR(K48='설정'!$B$6,K48='설정'!$B$8),SUBSTITUTE(K48,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G48)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G48)),"화목","반")),K48))</f>
+        <f>IF(M48&lt;&gt;"",M48,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K48&lt;&gt;""),'설정'!$B$10,IF(OR(K48='설정'!$B$6,K48='설정'!$B$8),SUBSTITUTE(K48,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G48)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G48)),"화목","반")),K48)))</f>
         <v/>
       </c>
       <c r="P48" s="30">
@@ -25893,7 +25927,7 @@
       <c r="M49" s="7" t="n"/>
       <c r="N49" s="7" t="n"/>
       <c r="O49" s="27">
-        <f>IF(M49&lt;&gt;"",M49,IF(OR(K49='설정'!$B$6,K49='설정'!$B$8),SUBSTITUTE(K49,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G49)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G49)),"화목","반")),K49))</f>
+        <f>IF(M49&lt;&gt;"",M49,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K49&lt;&gt;""),'설정'!$B$10,IF(OR(K49='설정'!$B$6,K49='설정'!$B$8),SUBSTITUTE(K49,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G49)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G49)),"화목","반")),K49)))</f>
         <v/>
       </c>
       <c r="P49" s="30">
@@ -25956,7 +25990,7 @@
       <c r="M50" s="7" t="n"/>
       <c r="N50" s="7" t="n"/>
       <c r="O50" s="27">
-        <f>IF(M50&lt;&gt;"",M50,IF(OR(K50='설정'!$B$6,K50='설정'!$B$8),SUBSTITUTE(K50,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G50)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G50)),"화목","반")),K50))</f>
+        <f>IF(M50&lt;&gt;"",M50,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K50&lt;&gt;""),'설정'!$B$10,IF(OR(K50='설정'!$B$6,K50='설정'!$B$8),SUBSTITUTE(K50,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G50)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G50)),"화목","반")),K50)))</f>
         <v/>
       </c>
       <c r="P50" s="30">
@@ -26019,7 +26053,7 @@
       <c r="M51" s="7" t="n"/>
       <c r="N51" s="7" t="n"/>
       <c r="O51" s="27">
-        <f>IF(M51&lt;&gt;"",M51,IF(OR(K51='설정'!$B$6,K51='설정'!$B$8),SUBSTITUTE(K51,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G51)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G51)),"화목","반")),K51))</f>
+        <f>IF(M51&lt;&gt;"",M51,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K51&lt;&gt;""),'설정'!$B$10,IF(OR(K51='설정'!$B$6,K51='설정'!$B$8),SUBSTITUTE(K51,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G51)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G51)),"화목","반")),K51)))</f>
         <v/>
       </c>
       <c r="P51" s="30">
@@ -26082,7 +26116,7 @@
       <c r="M52" s="7" t="n"/>
       <c r="N52" s="7" t="n"/>
       <c r="O52" s="27">
-        <f>IF(M52&lt;&gt;"",M52,IF(OR(K52='설정'!$B$6,K52='설정'!$B$8),SUBSTITUTE(K52,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G52)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G52)),"화목","반")),K52))</f>
+        <f>IF(M52&lt;&gt;"",M52,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K52&lt;&gt;""),'설정'!$B$10,IF(OR(K52='설정'!$B$6,K52='설정'!$B$8),SUBSTITUTE(K52,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G52)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G52)),"화목","반")),K52)))</f>
         <v/>
       </c>
       <c r="P52" s="30">
@@ -26145,7 +26179,7 @@
       <c r="M53" s="7" t="n"/>
       <c r="N53" s="7" t="n"/>
       <c r="O53" s="27">
-        <f>IF(M53&lt;&gt;"",M53,IF(OR(K53='설정'!$B$6,K53='설정'!$B$8),SUBSTITUTE(K53,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G53)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G53)),"화목","반")),K53))</f>
+        <f>IF(M53&lt;&gt;"",M53,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K53&lt;&gt;""),'설정'!$B$10,IF(OR(K53='설정'!$B$6,K53='설정'!$B$8),SUBSTITUTE(K53,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G53)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G53)),"화목","반")),K53)))</f>
         <v/>
       </c>
       <c r="P53" s="30">
@@ -26208,7 +26242,7 @@
       <c r="M54" s="7" t="n"/>
       <c r="N54" s="7" t="n"/>
       <c r="O54" s="27">
-        <f>IF(M54&lt;&gt;"",M54,IF(OR(K54='설정'!$B$6,K54='설정'!$B$8),SUBSTITUTE(K54,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G54)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G54)),"화목","반")),K54))</f>
+        <f>IF(M54&lt;&gt;"",M54,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K54&lt;&gt;""),'설정'!$B$10,IF(OR(K54='설정'!$B$6,K54='설정'!$B$8),SUBSTITUTE(K54,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G54)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G54)),"화목","반")),K54)))</f>
         <v/>
       </c>
       <c r="P54" s="30">
@@ -26271,7 +26305,7 @@
       <c r="M55" s="7" t="n"/>
       <c r="N55" s="7" t="n"/>
       <c r="O55" s="27">
-        <f>IF(M55&lt;&gt;"",M55,IF(OR(K55='설정'!$B$6,K55='설정'!$B$8),SUBSTITUTE(K55,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G55)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G55)),"화목","반")),K55))</f>
+        <f>IF(M55&lt;&gt;"",M55,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K55&lt;&gt;""),'설정'!$B$10,IF(OR(K55='설정'!$B$6,K55='설정'!$B$8),SUBSTITUTE(K55,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G55)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G55)),"화목","반")),K55)))</f>
         <v/>
       </c>
       <c r="P55" s="30">
@@ -26334,7 +26368,7 @@
       <c r="M56" s="7" t="n"/>
       <c r="N56" s="7" t="n"/>
       <c r="O56" s="27">
-        <f>IF(M56&lt;&gt;"",M56,IF(OR(K56='설정'!$B$6,K56='설정'!$B$8),SUBSTITUTE(K56,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G56)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G56)),"화목","반")),K56))</f>
+        <f>IF(M56&lt;&gt;"",M56,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K56&lt;&gt;""),'설정'!$B$10,IF(OR(K56='설정'!$B$6,K56='설정'!$B$8),SUBSTITUTE(K56,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G56)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G56)),"화목","반")),K56)))</f>
         <v/>
       </c>
       <c r="P56" s="30">
@@ -26397,7 +26431,7 @@
       <c r="M57" s="7" t="n"/>
       <c r="N57" s="7" t="n"/>
       <c r="O57" s="27">
-        <f>IF(M57&lt;&gt;"",M57,IF(OR(K57='설정'!$B$6,K57='설정'!$B$8),SUBSTITUTE(K57,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G57)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G57)),"화목","반")),K57))</f>
+        <f>IF(M57&lt;&gt;"",M57,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K57&lt;&gt;""),'설정'!$B$10,IF(OR(K57='설정'!$B$6,K57='설정'!$B$8),SUBSTITUTE(K57,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G57)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G57)),"화목","반")),K57)))</f>
         <v/>
       </c>
       <c r="P57" s="30">
@@ -26460,7 +26494,7 @@
       <c r="M58" s="7" t="n"/>
       <c r="N58" s="7" t="n"/>
       <c r="O58" s="27">
-        <f>IF(M58&lt;&gt;"",M58,IF(OR(K58='설정'!$B$6,K58='설정'!$B$8),SUBSTITUTE(K58,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G58)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G58)),"화목","반")),K58))</f>
+        <f>IF(M58&lt;&gt;"",M58,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K58&lt;&gt;""),'설정'!$B$10,IF(OR(K58='설정'!$B$6,K58='설정'!$B$8),SUBSTITUTE(K58,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G58)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G58)),"화목","반")),K58)))</f>
         <v/>
       </c>
       <c r="P58" s="30">
@@ -26523,7 +26557,7 @@
       <c r="M59" s="7" t="n"/>
       <c r="N59" s="7" t="n"/>
       <c r="O59" s="27">
-        <f>IF(M59&lt;&gt;"",M59,IF(OR(K59='설정'!$B$6,K59='설정'!$B$8),SUBSTITUTE(K59,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G59)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G59)),"화목","반")),K59))</f>
+        <f>IF(M59&lt;&gt;"",M59,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K59&lt;&gt;""),'설정'!$B$10,IF(OR(K59='설정'!$B$6,K59='설정'!$B$8),SUBSTITUTE(K59,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G59)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G59)),"화목","반")),K59)))</f>
         <v/>
       </c>
       <c r="P59" s="30">
@@ -26586,7 +26620,7 @@
       <c r="M60" s="7" t="n"/>
       <c r="N60" s="7" t="n"/>
       <c r="O60" s="27">
-        <f>IF(M60&lt;&gt;"",M60,IF(OR(K60='설정'!$B$6,K60='설정'!$B$8),SUBSTITUTE(K60,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G60)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G60)),"화목","반")),K60))</f>
+        <f>IF(M60&lt;&gt;"",M60,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K60&lt;&gt;""),'설정'!$B$10,IF(OR(K60='설정'!$B$6,K60='설정'!$B$8),SUBSTITUTE(K60,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G60)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G60)),"화목","반")),K60)))</f>
         <v/>
       </c>
       <c r="P60" s="30">
@@ -26649,7 +26683,7 @@
       <c r="M61" s="7" t="n"/>
       <c r="N61" s="7" t="n"/>
       <c r="O61" s="27">
-        <f>IF(M61&lt;&gt;"",M61,IF(OR(K61='설정'!$B$6,K61='설정'!$B$8),SUBSTITUTE(K61,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G61)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G61)),"화목","반")),K61))</f>
+        <f>IF(M61&lt;&gt;"",M61,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K61&lt;&gt;""),'설정'!$B$10,IF(OR(K61='설정'!$B$6,K61='설정'!$B$8),SUBSTITUTE(K61,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G61)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G61)),"화목","반")),K61)))</f>
         <v/>
       </c>
       <c r="P61" s="30">
@@ -26712,7 +26746,7 @@
       <c r="M62" s="7" t="n"/>
       <c r="N62" s="7" t="n"/>
       <c r="O62" s="27">
-        <f>IF(M62&lt;&gt;"",M62,IF(OR(K62='설정'!$B$6,K62='설정'!$B$8),SUBSTITUTE(K62,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G62)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G62)),"화목","반")),K62))</f>
+        <f>IF(M62&lt;&gt;"",M62,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K62&lt;&gt;""),'설정'!$B$10,IF(OR(K62='설정'!$B$6,K62='설정'!$B$8),SUBSTITUTE(K62,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G62)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G62)),"화목","반")),K62)))</f>
         <v/>
       </c>
       <c r="P62" s="30">
@@ -26775,7 +26809,7 @@
       <c r="M63" s="7" t="n"/>
       <c r="N63" s="7" t="n"/>
       <c r="O63" s="27">
-        <f>IF(M63&lt;&gt;"",M63,IF(OR(K63='설정'!$B$6,K63='설정'!$B$8),SUBSTITUTE(K63,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G63)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G63)),"화목","반")),K63))</f>
+        <f>IF(M63&lt;&gt;"",M63,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K63&lt;&gt;""),'설정'!$B$10,IF(OR(K63='설정'!$B$6,K63='설정'!$B$8),SUBSTITUTE(K63,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G63)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G63)),"화목","반")),K63)))</f>
         <v/>
       </c>
       <c r="P63" s="30">
@@ -26838,7 +26872,7 @@
       <c r="M64" s="7" t="n"/>
       <c r="N64" s="7" t="n"/>
       <c r="O64" s="27">
-        <f>IF(M64&lt;&gt;"",M64,IF(OR(K64='설정'!$B$6,K64='설정'!$B$8),SUBSTITUTE(K64,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G64)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G64)),"화목","반")),K64))</f>
+        <f>IF(M64&lt;&gt;"",M64,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K64&lt;&gt;""),'설정'!$B$10,IF(OR(K64='설정'!$B$6,K64='설정'!$B$8),SUBSTITUTE(K64,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G64)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G64)),"화목","반")),K64)))</f>
         <v/>
       </c>
       <c r="P64" s="30">
@@ -26901,7 +26935,7 @@
       <c r="M65" s="7" t="n"/>
       <c r="N65" s="7" t="n"/>
       <c r="O65" s="27">
-        <f>IF(M65&lt;&gt;"",M65,IF(OR(K65='설정'!$B$6,K65='설정'!$B$8),SUBSTITUTE(K65,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G65)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G65)),"화목","반")),K65))</f>
+        <f>IF(M65&lt;&gt;"",M65,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K65&lt;&gt;""),'설정'!$B$10,IF(OR(K65='설정'!$B$6,K65='설정'!$B$8),SUBSTITUTE(K65,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G65)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G65)),"화목","반")),K65)))</f>
         <v/>
       </c>
       <c r="P65" s="30">
@@ -26964,7 +26998,7 @@
       <c r="M66" s="7" t="n"/>
       <c r="N66" s="7" t="n"/>
       <c r="O66" s="27">
-        <f>IF(M66&lt;&gt;"",M66,IF(OR(K66='설정'!$B$6,K66='설정'!$B$8),SUBSTITUTE(K66,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G66)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G66)),"화목","반")),K66))</f>
+        <f>IF(M66&lt;&gt;"",M66,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K66&lt;&gt;""),'설정'!$B$10,IF(OR(K66='설정'!$B$6,K66='설정'!$B$8),SUBSTITUTE(K66,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G66)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G66)),"화목","반")),K66)))</f>
         <v/>
       </c>
       <c r="P66" s="30">
@@ -27027,7 +27061,7 @@
       <c r="M67" s="7" t="n"/>
       <c r="N67" s="7" t="n"/>
       <c r="O67" s="27">
-        <f>IF(M67&lt;&gt;"",M67,IF(OR(K67='설정'!$B$6,K67='설정'!$B$8),SUBSTITUTE(K67,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G67)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G67)),"화목","반")),K67))</f>
+        <f>IF(M67&lt;&gt;"",M67,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K67&lt;&gt;""),'설정'!$B$10,IF(OR(K67='설정'!$B$6,K67='설정'!$B$8),SUBSTITUTE(K67,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G67)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G67)),"화목","반")),K67)))</f>
         <v/>
       </c>
       <c r="P67" s="30">
@@ -27090,7 +27124,7 @@
       <c r="M68" s="7" t="n"/>
       <c r="N68" s="7" t="n"/>
       <c r="O68" s="27">
-        <f>IF(M68&lt;&gt;"",M68,IF(OR(K68='설정'!$B$6,K68='설정'!$B$8),SUBSTITUTE(K68,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G68)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G68)),"화목","반")),K68))</f>
+        <f>IF(M68&lt;&gt;"",M68,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K68&lt;&gt;""),'설정'!$B$10,IF(OR(K68='설정'!$B$6,K68='설정'!$B$8),SUBSTITUTE(K68,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G68)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G68)),"화목","반")),K68)))</f>
         <v/>
       </c>
       <c r="P68" s="30">
@@ -27153,7 +27187,7 @@
       <c r="M69" s="7" t="n"/>
       <c r="N69" s="7" t="n"/>
       <c r="O69" s="27">
-        <f>IF(M69&lt;&gt;"",M69,IF(OR(K69='설정'!$B$6,K69='설정'!$B$8),SUBSTITUTE(K69,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G69)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G69)),"화목","반")),K69))</f>
+        <f>IF(M69&lt;&gt;"",M69,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K69&lt;&gt;""),'설정'!$B$10,IF(OR(K69='설정'!$B$6,K69='설정'!$B$8),SUBSTITUTE(K69,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G69)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G69)),"화목","반")),K69)))</f>
         <v/>
       </c>
       <c r="P69" s="30">
@@ -27216,7 +27250,7 @@
       <c r="M70" s="7" t="n"/>
       <c r="N70" s="7" t="n"/>
       <c r="O70" s="27">
-        <f>IF(M70&lt;&gt;"",M70,IF(OR(K70='설정'!$B$6,K70='설정'!$B$8),SUBSTITUTE(K70,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G70)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G70)),"화목","반")),K70))</f>
+        <f>IF(M70&lt;&gt;"",M70,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K70&lt;&gt;""),'설정'!$B$10,IF(OR(K70='설정'!$B$6,K70='설정'!$B$8),SUBSTITUTE(K70,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G70)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G70)),"화목","반")),K70)))</f>
         <v/>
       </c>
       <c r="P70" s="30">
@@ -27279,7 +27313,7 @@
       <c r="M71" s="7" t="n"/>
       <c r="N71" s="7" t="n"/>
       <c r="O71" s="27">
-        <f>IF(M71&lt;&gt;"",M71,IF(OR(K71='설정'!$B$6,K71='설정'!$B$8),SUBSTITUTE(K71,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G71)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G71)),"화목","반")),K71))</f>
+        <f>IF(M71&lt;&gt;"",M71,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K71&lt;&gt;""),'설정'!$B$10,IF(OR(K71='설정'!$B$6,K71='설정'!$B$8),SUBSTITUTE(K71,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G71)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G71)),"화목","반")),K71)))</f>
         <v/>
       </c>
       <c r="P71" s="30">
@@ -27342,7 +27376,7 @@
       <c r="M72" s="7" t="n"/>
       <c r="N72" s="7" t="n"/>
       <c r="O72" s="27">
-        <f>IF(M72&lt;&gt;"",M72,IF(OR(K72='설정'!$B$6,K72='설정'!$B$8),SUBSTITUTE(K72,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G72)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G72)),"화목","반")),K72))</f>
+        <f>IF(M72&lt;&gt;"",M72,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K72&lt;&gt;""),'설정'!$B$10,IF(OR(K72='설정'!$B$6,K72='설정'!$B$8),SUBSTITUTE(K72,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G72)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G72)),"화목","반")),K72)))</f>
         <v/>
       </c>
       <c r="P72" s="30">
@@ -27405,7 +27439,7 @@
       <c r="M73" s="7" t="n"/>
       <c r="N73" s="7" t="n"/>
       <c r="O73" s="27">
-        <f>IF(M73&lt;&gt;"",M73,IF(OR(K73='설정'!$B$6,K73='설정'!$B$8),SUBSTITUTE(K73,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G73)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G73)),"화목","반")),K73))</f>
+        <f>IF(M73&lt;&gt;"",M73,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K73&lt;&gt;""),'설정'!$B$10,IF(OR(K73='설정'!$B$6,K73='설정'!$B$8),SUBSTITUTE(K73,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G73)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G73)),"화목","반")),K73)))</f>
         <v/>
       </c>
       <c r="P73" s="30">
@@ -27468,7 +27502,7 @@
       <c r="M74" s="7" t="n"/>
       <c r="N74" s="7" t="n"/>
       <c r="O74" s="27">
-        <f>IF(M74&lt;&gt;"",M74,IF(OR(K74='설정'!$B$6,K74='설정'!$B$8),SUBSTITUTE(K74,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G74)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G74)),"화목","반")),K74))</f>
+        <f>IF(M74&lt;&gt;"",M74,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K74&lt;&gt;""),'설정'!$B$10,IF(OR(K74='설정'!$B$6,K74='설정'!$B$8),SUBSTITUTE(K74,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G74)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G74)),"화목","반")),K74)))</f>
         <v/>
       </c>
       <c r="P74" s="30">
@@ -27531,7 +27565,7 @@
       <c r="M75" s="7" t="n"/>
       <c r="N75" s="7" t="n"/>
       <c r="O75" s="27">
-        <f>IF(M75&lt;&gt;"",M75,IF(OR(K75='설정'!$B$6,K75='설정'!$B$8),SUBSTITUTE(K75,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G75)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G75)),"화목","반")),K75))</f>
+        <f>IF(M75&lt;&gt;"",M75,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K75&lt;&gt;""),'설정'!$B$10,IF(OR(K75='설정'!$B$6,K75='설정'!$B$8),SUBSTITUTE(K75,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G75)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G75)),"화목","반")),K75)))</f>
         <v/>
       </c>
       <c r="P75" s="30">
@@ -27594,7 +27628,7 @@
       <c r="M76" s="7" t="n"/>
       <c r="N76" s="7" t="n"/>
       <c r="O76" s="27">
-        <f>IF(M76&lt;&gt;"",M76,IF(OR(K76='설정'!$B$6,K76='설정'!$B$8),SUBSTITUTE(K76,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G76)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G76)),"화목","반")),K76))</f>
+        <f>IF(M76&lt;&gt;"",M76,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K76&lt;&gt;""),'설정'!$B$10,IF(OR(K76='설정'!$B$6,K76='설정'!$B$8),SUBSTITUTE(K76,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G76)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G76)),"화목","반")),K76)))</f>
         <v/>
       </c>
       <c r="P76" s="30">
@@ -27657,7 +27691,7 @@
       <c r="M77" s="7" t="n"/>
       <c r="N77" s="7" t="n"/>
       <c r="O77" s="27">
-        <f>IF(M77&lt;&gt;"",M77,IF(OR(K77='설정'!$B$6,K77='설정'!$B$8),SUBSTITUTE(K77,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G77)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G77)),"화목","반")),K77))</f>
+        <f>IF(M77&lt;&gt;"",M77,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K77&lt;&gt;""),'설정'!$B$10,IF(OR(K77='설정'!$B$6,K77='설정'!$B$8),SUBSTITUTE(K77,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G77)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G77)),"화목","반")),K77)))</f>
         <v/>
       </c>
       <c r="P77" s="30">
@@ -27720,7 +27754,7 @@
       <c r="M78" s="7" t="n"/>
       <c r="N78" s="7" t="n"/>
       <c r="O78" s="27">
-        <f>IF(M78&lt;&gt;"",M78,IF(OR(K78='설정'!$B$6,K78='설정'!$B$8),SUBSTITUTE(K78,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G78)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G78)),"화목","반")),K78))</f>
+        <f>IF(M78&lt;&gt;"",M78,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K78&lt;&gt;""),'설정'!$B$10,IF(OR(K78='설정'!$B$6,K78='설정'!$B$8),SUBSTITUTE(K78,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G78)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G78)),"화목","반")),K78)))</f>
         <v/>
       </c>
       <c r="P78" s="30">
@@ -27783,7 +27817,7 @@
       <c r="M79" s="7" t="n"/>
       <c r="N79" s="7" t="n"/>
       <c r="O79" s="27">
-        <f>IF(M79&lt;&gt;"",M79,IF(OR(K79='설정'!$B$6,K79='설정'!$B$8),SUBSTITUTE(K79,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G79)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G79)),"화목","반")),K79))</f>
+        <f>IF(M79&lt;&gt;"",M79,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K79&lt;&gt;""),'설정'!$B$10,IF(OR(K79='설정'!$B$6,K79='설정'!$B$8),SUBSTITUTE(K79,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G79)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G79)),"화목","반")),K79)))</f>
         <v/>
       </c>
       <c r="P79" s="30">
@@ -27846,7 +27880,7 @@
       <c r="M80" s="7" t="n"/>
       <c r="N80" s="7" t="n"/>
       <c r="O80" s="27">
-        <f>IF(M80&lt;&gt;"",M80,IF(OR(K80='설정'!$B$6,K80='설정'!$B$8),SUBSTITUTE(K80,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G80)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G80)),"화목","반")),K80))</f>
+        <f>IF(M80&lt;&gt;"",M80,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K80&lt;&gt;""),'설정'!$B$10,IF(OR(K80='설정'!$B$6,K80='설정'!$B$8),SUBSTITUTE(K80,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G80)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G80)),"화목","반")),K80)))</f>
         <v/>
       </c>
       <c r="P80" s="30">
@@ -27909,7 +27943,7 @@
       <c r="M81" s="7" t="n"/>
       <c r="N81" s="7" t="n"/>
       <c r="O81" s="27">
-        <f>IF(M81&lt;&gt;"",M81,IF(OR(K81='설정'!$B$6,K81='설정'!$B$8),SUBSTITUTE(K81,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G81)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G81)),"화목","반")),K81))</f>
+        <f>IF(M81&lt;&gt;"",M81,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K81&lt;&gt;""),'설정'!$B$10,IF(OR(K81='설정'!$B$6,K81='설정'!$B$8),SUBSTITUTE(K81,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G81)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G81)),"화목","반")),K81)))</f>
         <v/>
       </c>
       <c r="P81" s="30">
@@ -27972,7 +28006,7 @@
       <c r="M82" s="7" t="n"/>
       <c r="N82" s="7" t="n"/>
       <c r="O82" s="27">
-        <f>IF(M82&lt;&gt;"",M82,IF(OR(K82='설정'!$B$6,K82='설정'!$B$8),SUBSTITUTE(K82,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G82)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G82)),"화목","반")),K82))</f>
+        <f>IF(M82&lt;&gt;"",M82,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K82&lt;&gt;""),'설정'!$B$10,IF(OR(K82='설정'!$B$6,K82='설정'!$B$8),SUBSTITUTE(K82,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G82)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G82)),"화목","반")),K82)))</f>
         <v/>
       </c>
       <c r="P82" s="30">
@@ -28035,7 +28069,7 @@
       <c r="M83" s="7" t="n"/>
       <c r="N83" s="7" t="n"/>
       <c r="O83" s="27">
-        <f>IF(M83&lt;&gt;"",M83,IF(OR(K83='설정'!$B$6,K83='설정'!$B$8),SUBSTITUTE(K83,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G83)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G83)),"화목","반")),K83))</f>
+        <f>IF(M83&lt;&gt;"",M83,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K83&lt;&gt;""),'설정'!$B$10,IF(OR(K83='설정'!$B$6,K83='설정'!$B$8),SUBSTITUTE(K83,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G83)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G83)),"화목","반")),K83)))</f>
         <v/>
       </c>
       <c r="P83" s="30">
@@ -28098,7 +28132,7 @@
       <c r="M84" s="7" t="n"/>
       <c r="N84" s="7" t="n"/>
       <c r="O84" s="27">
-        <f>IF(M84&lt;&gt;"",M84,IF(OR(K84='설정'!$B$6,K84='설정'!$B$8),SUBSTITUTE(K84,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G84)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G84)),"화목","반")),K84))</f>
+        <f>IF(M84&lt;&gt;"",M84,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K84&lt;&gt;""),'설정'!$B$10,IF(OR(K84='설정'!$B$6,K84='설정'!$B$8),SUBSTITUTE(K84,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G84)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G84)),"화목","반")),K84)))</f>
         <v/>
       </c>
       <c r="P84" s="30">
@@ -28161,7 +28195,7 @@
       <c r="M85" s="7" t="n"/>
       <c r="N85" s="7" t="n"/>
       <c r="O85" s="27">
-        <f>IF(M85&lt;&gt;"",M85,IF(OR(K85='설정'!$B$6,K85='설정'!$B$8),SUBSTITUTE(K85,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G85)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G85)),"화목","반")),K85))</f>
+        <f>IF(M85&lt;&gt;"",M85,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K85&lt;&gt;""),'설정'!$B$10,IF(OR(K85='설정'!$B$6,K85='설정'!$B$8),SUBSTITUTE(K85,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G85)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G85)),"화목","반")),K85)))</f>
         <v/>
       </c>
       <c r="P85" s="30">
@@ -28224,7 +28258,7 @@
       <c r="M86" s="7" t="n"/>
       <c r="N86" s="7" t="n"/>
       <c r="O86" s="27">
-        <f>IF(M86&lt;&gt;"",M86,IF(OR(K86='설정'!$B$6,K86='설정'!$B$8),SUBSTITUTE(K86,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G86)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G86)),"화목","반")),K86))</f>
+        <f>IF(M86&lt;&gt;"",M86,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K86&lt;&gt;""),'설정'!$B$10,IF(OR(K86='설정'!$B$6,K86='설정'!$B$8),SUBSTITUTE(K86,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G86)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G86)),"화목","반")),K86)))</f>
         <v/>
       </c>
       <c r="P86" s="30">
@@ -28287,7 +28321,7 @@
       <c r="M87" s="7" t="n"/>
       <c r="N87" s="7" t="n"/>
       <c r="O87" s="27">
-        <f>IF(M87&lt;&gt;"",M87,IF(OR(K87='설정'!$B$6,K87='설정'!$B$8),SUBSTITUTE(K87,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G87)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G87)),"화목","반")),K87))</f>
+        <f>IF(M87&lt;&gt;"",M87,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K87&lt;&gt;""),'설정'!$B$10,IF(OR(K87='설정'!$B$6,K87='설정'!$B$8),SUBSTITUTE(K87,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G87)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G87)),"화목","반")),K87)))</f>
         <v/>
       </c>
       <c r="P87" s="30">
@@ -28350,7 +28384,7 @@
       <c r="M88" s="7" t="n"/>
       <c r="N88" s="7" t="n"/>
       <c r="O88" s="27">
-        <f>IF(M88&lt;&gt;"",M88,IF(OR(K88='설정'!$B$6,K88='설정'!$B$8),SUBSTITUTE(K88,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G88)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G88)),"화목","반")),K88))</f>
+        <f>IF(M88&lt;&gt;"",M88,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K88&lt;&gt;""),'설정'!$B$10,IF(OR(K88='설정'!$B$6,K88='설정'!$B$8),SUBSTITUTE(K88,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G88)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G88)),"화목","반")),K88)))</f>
         <v/>
       </c>
       <c r="P88" s="30">
@@ -28413,7 +28447,7 @@
       <c r="M89" s="7" t="n"/>
       <c r="N89" s="7" t="n"/>
       <c r="O89" s="27">
-        <f>IF(M89&lt;&gt;"",M89,IF(OR(K89='설정'!$B$6,K89='설정'!$B$8),SUBSTITUTE(K89,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G89)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G89)),"화목","반")),K89))</f>
+        <f>IF(M89&lt;&gt;"",M89,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K89&lt;&gt;""),'설정'!$B$10,IF(OR(K89='설정'!$B$6,K89='설정'!$B$8),SUBSTITUTE(K89,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G89)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G89)),"화목","반")),K89)))</f>
         <v/>
       </c>
       <c r="P89" s="30">
@@ -28476,7 +28510,7 @@
       <c r="M90" s="7" t="n"/>
       <c r="N90" s="7" t="n"/>
       <c r="O90" s="27">
-        <f>IF(M90&lt;&gt;"",M90,IF(OR(K90='설정'!$B$6,K90='설정'!$B$8),SUBSTITUTE(K90,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G90)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G90)),"화목","반")),K90))</f>
+        <f>IF(M90&lt;&gt;"",M90,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K90&lt;&gt;""),'설정'!$B$10,IF(OR(K90='설정'!$B$6,K90='설정'!$B$8),SUBSTITUTE(K90,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G90)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G90)),"화목","반")),K90)))</f>
         <v/>
       </c>
       <c r="P90" s="30">
@@ -28539,7 +28573,7 @@
       <c r="M91" s="7" t="n"/>
       <c r="N91" s="7" t="n"/>
       <c r="O91" s="27">
-        <f>IF(M91&lt;&gt;"",M91,IF(OR(K91='설정'!$B$6,K91='설정'!$B$8),SUBSTITUTE(K91,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G91)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G91)),"화목","반")),K91))</f>
+        <f>IF(M91&lt;&gt;"",M91,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K91&lt;&gt;""),'설정'!$B$10,IF(OR(K91='설정'!$B$6,K91='설정'!$B$8),SUBSTITUTE(K91,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G91)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G91)),"화목","반")),K91)))</f>
         <v/>
       </c>
       <c r="P91" s="30">
@@ -28602,7 +28636,7 @@
       <c r="M92" s="7" t="n"/>
       <c r="N92" s="7" t="n"/>
       <c r="O92" s="27">
-        <f>IF(M92&lt;&gt;"",M92,IF(OR(K92='설정'!$B$6,K92='설정'!$B$8),SUBSTITUTE(K92,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G92)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G92)),"화목","반")),K92))</f>
+        <f>IF(M92&lt;&gt;"",M92,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K92&lt;&gt;""),'설정'!$B$10,IF(OR(K92='설정'!$B$6,K92='설정'!$B$8),SUBSTITUTE(K92,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G92)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G92)),"화목","반")),K92)))</f>
         <v/>
       </c>
       <c r="P92" s="30">
@@ -28665,7 +28699,7 @@
       <c r="M93" s="7" t="n"/>
       <c r="N93" s="7" t="n"/>
       <c r="O93" s="27">
-        <f>IF(M93&lt;&gt;"",M93,IF(OR(K93='설정'!$B$6,K93='설정'!$B$8),SUBSTITUTE(K93,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G93)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G93)),"화목","반")),K93))</f>
+        <f>IF(M93&lt;&gt;"",M93,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K93&lt;&gt;""),'설정'!$B$10,IF(OR(K93='설정'!$B$6,K93='설정'!$B$8),SUBSTITUTE(K93,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G93)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G93)),"화목","반")),K93)))</f>
         <v/>
       </c>
       <c r="P93" s="30">
@@ -28728,7 +28762,7 @@
       <c r="M94" s="7" t="n"/>
       <c r="N94" s="7" t="n"/>
       <c r="O94" s="27">
-        <f>IF(M94&lt;&gt;"",M94,IF(OR(K94='설정'!$B$6,K94='설정'!$B$8),SUBSTITUTE(K94,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G94)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G94)),"화목","반")),K94))</f>
+        <f>IF(M94&lt;&gt;"",M94,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K94&lt;&gt;""),'설정'!$B$10,IF(OR(K94='설정'!$B$6,K94='설정'!$B$8),SUBSTITUTE(K94,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G94)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G94)),"화목","반")),K94)))</f>
         <v/>
       </c>
       <c r="P94" s="30">
@@ -28791,7 +28825,7 @@
       <c r="M95" s="7" t="n"/>
       <c r="N95" s="7" t="n"/>
       <c r="O95" s="27">
-        <f>IF(M95&lt;&gt;"",M95,IF(OR(K95='설정'!$B$6,K95='설정'!$B$8),SUBSTITUTE(K95,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G95)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G95)),"화목","반")),K95))</f>
+        <f>IF(M95&lt;&gt;"",M95,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K95&lt;&gt;""),'설정'!$B$10,IF(OR(K95='설정'!$B$6,K95='설정'!$B$8),SUBSTITUTE(K95,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G95)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G95)),"화목","반")),K95)))</f>
         <v/>
       </c>
       <c r="P95" s="30">
@@ -28854,7 +28888,7 @@
       <c r="M96" s="7" t="n"/>
       <c r="N96" s="7" t="n"/>
       <c r="O96" s="27">
-        <f>IF(M96&lt;&gt;"",M96,IF(OR(K96='설정'!$B$6,K96='설정'!$B$8),SUBSTITUTE(K96,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G96)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G96)),"화목","반")),K96))</f>
+        <f>IF(M96&lt;&gt;"",M96,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K96&lt;&gt;""),'설정'!$B$10,IF(OR(K96='설정'!$B$6,K96='설정'!$B$8),SUBSTITUTE(K96,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G96)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G96)),"화목","반")),K96)))</f>
         <v/>
       </c>
       <c r="P96" s="30">
@@ -28917,7 +28951,7 @@
       <c r="M97" s="7" t="n"/>
       <c r="N97" s="7" t="n"/>
       <c r="O97" s="27">
-        <f>IF(M97&lt;&gt;"",M97,IF(OR(K97='설정'!$B$6,K97='설정'!$B$8),SUBSTITUTE(K97,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G97)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G97)),"화목","반")),K97))</f>
+        <f>IF(M97&lt;&gt;"",M97,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K97&lt;&gt;""),'설정'!$B$10,IF(OR(K97='설정'!$B$6,K97='설정'!$B$8),SUBSTITUTE(K97,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G97)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G97)),"화목","반")),K97)))</f>
         <v/>
       </c>
       <c r="P97" s="30">
@@ -28980,7 +29014,7 @@
       <c r="M98" s="7" t="n"/>
       <c r="N98" s="7" t="n"/>
       <c r="O98" s="27">
-        <f>IF(M98&lt;&gt;"",M98,IF(OR(K98='설정'!$B$6,K98='설정'!$B$8),SUBSTITUTE(K98,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G98)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G98)),"화목","반")),K98))</f>
+        <f>IF(M98&lt;&gt;"",M98,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K98&lt;&gt;""),'설정'!$B$10,IF(OR(K98='설정'!$B$6,K98='설정'!$B$8),SUBSTITUTE(K98,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G98)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G98)),"화목","반")),K98)))</f>
         <v/>
       </c>
       <c r="P98" s="30">
@@ -29043,7 +29077,7 @@
       <c r="M99" s="7" t="n"/>
       <c r="N99" s="7" t="n"/>
       <c r="O99" s="27">
-        <f>IF(M99&lt;&gt;"",M99,IF(OR(K99='설정'!$B$6,K99='설정'!$B$8),SUBSTITUTE(K99,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G99)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G99)),"화목","반")),K99))</f>
+        <f>IF(M99&lt;&gt;"",M99,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K99&lt;&gt;""),'설정'!$B$10,IF(OR(K99='설정'!$B$6,K99='설정'!$B$8),SUBSTITUTE(K99,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G99)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G99)),"화목","반")),K99)))</f>
         <v/>
       </c>
       <c r="P99" s="30">
@@ -29106,7 +29140,7 @@
       <c r="M100" s="7" t="n"/>
       <c r="N100" s="7" t="n"/>
       <c r="O100" s="27">
-        <f>IF(M100&lt;&gt;"",M100,IF(OR(K100='설정'!$B$6,K100='설정'!$B$8),SUBSTITUTE(K100,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G100)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G100)),"화목","반")),K100))</f>
+        <f>IF(M100&lt;&gt;"",M100,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K100&lt;&gt;""),'설정'!$B$10,IF(OR(K100='설정'!$B$6,K100='설정'!$B$8),SUBSTITUTE(K100,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G100)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G100)),"화목","반")),K100)))</f>
         <v/>
       </c>
       <c r="P100" s="30">
@@ -29169,7 +29203,7 @@
       <c r="M101" s="7" t="n"/>
       <c r="N101" s="7" t="n"/>
       <c r="O101" s="27">
-        <f>IF(M101&lt;&gt;"",M101,IF(OR(K101='설정'!$B$6,K101='설정'!$B$8),SUBSTITUTE(K101,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G101)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G101)),"화목","반")),K101))</f>
+        <f>IF(M101&lt;&gt;"",M101,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K101&lt;&gt;""),'설정'!$B$10,IF(OR(K101='설정'!$B$6,K101='설정'!$B$8),SUBSTITUTE(K101,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G101)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G101)),"화목","반")),K101)))</f>
         <v/>
       </c>
       <c r="P101" s="30">
@@ -29232,7 +29266,7 @@
       <c r="M102" s="7" t="n"/>
       <c r="N102" s="7" t="n"/>
       <c r="O102" s="27">
-        <f>IF(M102&lt;&gt;"",M102,IF(OR(K102='설정'!$B$6,K102='설정'!$B$8),SUBSTITUTE(K102,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G102)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G102)),"화목","반")),K102))</f>
+        <f>IF(M102&lt;&gt;"",M102,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K102&lt;&gt;""),'설정'!$B$10,IF(OR(K102='설정'!$B$6,K102='설정'!$B$8),SUBSTITUTE(K102,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G102)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G102)),"화목","반")),K102)))</f>
         <v/>
       </c>
       <c r="P102" s="30">
@@ -29295,7 +29329,7 @@
       <c r="M103" s="7" t="n"/>
       <c r="N103" s="7" t="n"/>
       <c r="O103" s="27">
-        <f>IF(M103&lt;&gt;"",M103,IF(OR(K103='설정'!$B$6,K103='설정'!$B$8),SUBSTITUTE(K103,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G103)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G103)),"화목","반")),K103))</f>
+        <f>IF(M103&lt;&gt;"",M103,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K103&lt;&gt;""),'설정'!$B$10,IF(OR(K103='설정'!$B$6,K103='설정'!$B$8),SUBSTITUTE(K103,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G103)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G103)),"화목","반")),K103)))</f>
         <v/>
       </c>
       <c r="P103" s="30">
@@ -29358,7 +29392,7 @@
       <c r="M104" s="7" t="n"/>
       <c r="N104" s="7" t="n"/>
       <c r="O104" s="27">
-        <f>IF(M104&lt;&gt;"",M104,IF(OR(K104='설정'!$B$6,K104='설정'!$B$8),SUBSTITUTE(K104,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G104)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G104)),"화목","반")),K104))</f>
+        <f>IF(M104&lt;&gt;"",M104,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K104&lt;&gt;""),'설정'!$B$10,IF(OR(K104='설정'!$B$6,K104='설정'!$B$8),SUBSTITUTE(K104,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G104)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G104)),"화목","반")),K104)))</f>
         <v/>
       </c>
       <c r="P104" s="30">
@@ -29421,7 +29455,7 @@
       <c r="M105" s="7" t="n"/>
       <c r="N105" s="7" t="n"/>
       <c r="O105" s="27">
-        <f>IF(M105&lt;&gt;"",M105,IF(OR(K105='설정'!$B$6,K105='설정'!$B$8),SUBSTITUTE(K105,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G105)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G105)),"화목","반")),K105))</f>
+        <f>IF(M105&lt;&gt;"",M105,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K105&lt;&gt;""),'설정'!$B$10,IF(OR(K105='설정'!$B$6,K105='설정'!$B$8),SUBSTITUTE(K105,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G105)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G105)),"화목","반")),K105)))</f>
         <v/>
       </c>
       <c r="P105" s="30">
@@ -29484,7 +29518,7 @@
       <c r="M106" s="7" t="n"/>
       <c r="N106" s="7" t="n"/>
       <c r="O106" s="27">
-        <f>IF(M106&lt;&gt;"",M106,IF(OR(K106='설정'!$B$6,K106='설정'!$B$8),SUBSTITUTE(K106,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G106)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G106)),"화목","반")),K106))</f>
+        <f>IF(M106&lt;&gt;"",M106,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K106&lt;&gt;""),'설정'!$B$10,IF(OR(K106='설정'!$B$6,K106='설정'!$B$8),SUBSTITUTE(K106,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G106)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G106)),"화목","반")),K106)))</f>
         <v/>
       </c>
       <c r="P106" s="30">
@@ -29547,7 +29581,7 @@
       <c r="M107" s="7" t="n"/>
       <c r="N107" s="7" t="n"/>
       <c r="O107" s="27">
-        <f>IF(M107&lt;&gt;"",M107,IF(OR(K107='설정'!$B$6,K107='설정'!$B$8),SUBSTITUTE(K107,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G107)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G107)),"화목","반")),K107))</f>
+        <f>IF(M107&lt;&gt;"",M107,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K107&lt;&gt;""),'설정'!$B$10,IF(OR(K107='설정'!$B$6,K107='설정'!$B$8),SUBSTITUTE(K107,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G107)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G107)),"화목","반")),K107)))</f>
         <v/>
       </c>
       <c r="P107" s="30">
@@ -29610,7 +29644,7 @@
       <c r="M108" s="7" t="n"/>
       <c r="N108" s="7" t="n"/>
       <c r="O108" s="27">
-        <f>IF(M108&lt;&gt;"",M108,IF(OR(K108='설정'!$B$6,K108='설정'!$B$8),SUBSTITUTE(K108,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G108)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G108)),"화목","반")),K108))</f>
+        <f>IF(M108&lt;&gt;"",M108,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K108&lt;&gt;""),'설정'!$B$10,IF(OR(K108='설정'!$B$6,K108='설정'!$B$8),SUBSTITUTE(K108,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G108)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G108)),"화목","반")),K108)))</f>
         <v/>
       </c>
       <c r="P108" s="30">
@@ -29673,7 +29707,7 @@
       <c r="M109" s="7" t="n"/>
       <c r="N109" s="7" t="n"/>
       <c r="O109" s="27">
-        <f>IF(M109&lt;&gt;"",M109,IF(OR(K109='설정'!$B$6,K109='설정'!$B$8),SUBSTITUTE(K109,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G109)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G109)),"화목","반")),K109))</f>
+        <f>IF(M109&lt;&gt;"",M109,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K109&lt;&gt;""),'설정'!$B$10,IF(OR(K109='설정'!$B$6,K109='설정'!$B$8),SUBSTITUTE(K109,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G109)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G109)),"화목","반")),K109)))</f>
         <v/>
       </c>
       <c r="P109" s="30">
@@ -29736,7 +29770,7 @@
       <c r="M110" s="7" t="n"/>
       <c r="N110" s="7" t="n"/>
       <c r="O110" s="27">
-        <f>IF(M110&lt;&gt;"",M110,IF(OR(K110='설정'!$B$6,K110='설정'!$B$8),SUBSTITUTE(K110,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G110)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G110)),"화목","반")),K110))</f>
+        <f>IF(M110&lt;&gt;"",M110,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K110&lt;&gt;""),'설정'!$B$10,IF(OR(K110='설정'!$B$6,K110='설정'!$B$8),SUBSTITUTE(K110,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G110)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G110)),"화목","반")),K110)))</f>
         <v/>
       </c>
       <c r="P110" s="30">
@@ -29799,7 +29833,7 @@
       <c r="M111" s="7" t="n"/>
       <c r="N111" s="7" t="n"/>
       <c r="O111" s="27">
-        <f>IF(M111&lt;&gt;"",M111,IF(OR(K111='설정'!$B$6,K111='설정'!$B$8),SUBSTITUTE(K111,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G111)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G111)),"화목","반")),K111))</f>
+        <f>IF(M111&lt;&gt;"",M111,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K111&lt;&gt;""),'설정'!$B$10,IF(OR(K111='설정'!$B$6,K111='설정'!$B$8),SUBSTITUTE(K111,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G111)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G111)),"화목","반")),K111)))</f>
         <v/>
       </c>
       <c r="P111" s="30">
@@ -29862,7 +29896,7 @@
       <c r="M112" s="7" t="n"/>
       <c r="N112" s="7" t="n"/>
       <c r="O112" s="27">
-        <f>IF(M112&lt;&gt;"",M112,IF(OR(K112='설정'!$B$6,K112='설정'!$B$8),SUBSTITUTE(K112,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G112)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G112)),"화목","반")),K112))</f>
+        <f>IF(M112&lt;&gt;"",M112,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K112&lt;&gt;""),'설정'!$B$10,IF(OR(K112='설정'!$B$6,K112='설정'!$B$8),SUBSTITUTE(K112,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G112)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G112)),"화목","반")),K112)))</f>
         <v/>
       </c>
       <c r="P112" s="30">
@@ -29925,7 +29959,7 @@
       <c r="M113" s="7" t="n"/>
       <c r="N113" s="7" t="n"/>
       <c r="O113" s="27">
-        <f>IF(M113&lt;&gt;"",M113,IF(OR(K113='설정'!$B$6,K113='설정'!$B$8),SUBSTITUTE(K113,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G113)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G113)),"화목","반")),K113))</f>
+        <f>IF(M113&lt;&gt;"",M113,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K113&lt;&gt;""),'설정'!$B$10,IF(OR(K113='설정'!$B$6,K113='설정'!$B$8),SUBSTITUTE(K113,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G113)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G113)),"화목","반")),K113)))</f>
         <v/>
       </c>
       <c r="P113" s="30">
@@ -29988,7 +30022,7 @@
       <c r="M114" s="7" t="n"/>
       <c r="N114" s="7" t="n"/>
       <c r="O114" s="27">
-        <f>IF(M114&lt;&gt;"",M114,IF(OR(K114='설정'!$B$6,K114='설정'!$B$8),SUBSTITUTE(K114,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G114)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G114)),"화목","반")),K114))</f>
+        <f>IF(M114&lt;&gt;"",M114,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K114&lt;&gt;""),'설정'!$B$10,IF(OR(K114='설정'!$B$6,K114='설정'!$B$8),SUBSTITUTE(K114,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G114)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G114)),"화목","반")),K114)))</f>
         <v/>
       </c>
       <c r="P114" s="30">
@@ -30051,7 +30085,7 @@
       <c r="M115" s="7" t="n"/>
       <c r="N115" s="7" t="n"/>
       <c r="O115" s="27">
-        <f>IF(M115&lt;&gt;"",M115,IF(OR(K115='설정'!$B$6,K115='설정'!$B$8),SUBSTITUTE(K115,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G115)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G115)),"화목","반")),K115))</f>
+        <f>IF(M115&lt;&gt;"",M115,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K115&lt;&gt;""),'설정'!$B$10,IF(OR(K115='설정'!$B$6,K115='설정'!$B$8),SUBSTITUTE(K115,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G115)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G115)),"화목","반")),K115)))</f>
         <v/>
       </c>
       <c r="P115" s="30">
@@ -30114,7 +30148,7 @@
       <c r="M116" s="7" t="n"/>
       <c r="N116" s="7" t="n"/>
       <c r="O116" s="27">
-        <f>IF(M116&lt;&gt;"",M116,IF(OR(K116='설정'!$B$6,K116='설정'!$B$8),SUBSTITUTE(K116,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G116)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G116)),"화목","반")),K116))</f>
+        <f>IF(M116&lt;&gt;"",M116,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K116&lt;&gt;""),'설정'!$B$10,IF(OR(K116='설정'!$B$6,K116='설정'!$B$8),SUBSTITUTE(K116,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G116)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G116)),"화목","반")),K116)))</f>
         <v/>
       </c>
       <c r="P116" s="30">
@@ -30177,7 +30211,7 @@
       <c r="M117" s="7" t="n"/>
       <c r="N117" s="7" t="n"/>
       <c r="O117" s="27">
-        <f>IF(M117&lt;&gt;"",M117,IF(OR(K117='설정'!$B$6,K117='설정'!$B$8),SUBSTITUTE(K117,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G117)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G117)),"화목","반")),K117))</f>
+        <f>IF(M117&lt;&gt;"",M117,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K117&lt;&gt;""),'설정'!$B$10,IF(OR(K117='설정'!$B$6,K117='설정'!$B$8),SUBSTITUTE(K117,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G117)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G117)),"화목","반")),K117)))</f>
         <v/>
       </c>
       <c r="P117" s="30">
@@ -30240,7 +30274,7 @@
       <c r="M118" s="7" t="n"/>
       <c r="N118" s="7" t="n"/>
       <c r="O118" s="27">
-        <f>IF(M118&lt;&gt;"",M118,IF(OR(K118='설정'!$B$6,K118='설정'!$B$8),SUBSTITUTE(K118,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G118)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G118)),"화목","반")),K118))</f>
+        <f>IF(M118&lt;&gt;"",M118,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K118&lt;&gt;""),'설정'!$B$10,IF(OR(K118='설정'!$B$6,K118='설정'!$B$8),SUBSTITUTE(K118,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G118)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G118)),"화목","반")),K118)))</f>
         <v/>
       </c>
       <c r="P118" s="30">
@@ -30303,7 +30337,7 @@
       <c r="M119" s="7" t="n"/>
       <c r="N119" s="7" t="n"/>
       <c r="O119" s="27">
-        <f>IF(M119&lt;&gt;"",M119,IF(OR(K119='설정'!$B$6,K119='설정'!$B$8),SUBSTITUTE(K119,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G119)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G119)),"화목","반")),K119))</f>
+        <f>IF(M119&lt;&gt;"",M119,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K119&lt;&gt;""),'설정'!$B$10,IF(OR(K119='설정'!$B$6,K119='설정'!$B$8),SUBSTITUTE(K119,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G119)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G119)),"화목","반")),K119)))</f>
         <v/>
       </c>
       <c r="P119" s="30">
@@ -30366,7 +30400,7 @@
       <c r="M120" s="7" t="n"/>
       <c r="N120" s="7" t="n"/>
       <c r="O120" s="27">
-        <f>IF(M120&lt;&gt;"",M120,IF(OR(K120='설정'!$B$6,K120='설정'!$B$8),SUBSTITUTE(K120,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G120)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G120)),"화목","반")),K120))</f>
+        <f>IF(M120&lt;&gt;"",M120,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K120&lt;&gt;""),'설정'!$B$10,IF(OR(K120='설정'!$B$6,K120='설정'!$B$8),SUBSTITUTE(K120,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G120)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G120)),"화목","반")),K120)))</f>
         <v/>
       </c>
       <c r="P120" s="30">
@@ -30429,7 +30463,7 @@
       <c r="M121" s="7" t="n"/>
       <c r="N121" s="7" t="n"/>
       <c r="O121" s="27">
-        <f>IF(M121&lt;&gt;"",M121,IF(OR(K121='설정'!$B$6,K121='설정'!$B$8),SUBSTITUTE(K121,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G121)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G121)),"화목","반")),K121))</f>
+        <f>IF(M121&lt;&gt;"",M121,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K121&lt;&gt;""),'설정'!$B$10,IF(OR(K121='설정'!$B$6,K121='설정'!$B$8),SUBSTITUTE(K121,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G121)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G121)),"화목","반")),K121)))</f>
         <v/>
       </c>
       <c r="P121" s="30">
@@ -30492,7 +30526,7 @@
       <c r="M122" s="7" t="n"/>
       <c r="N122" s="7" t="n"/>
       <c r="O122" s="27">
-        <f>IF(M122&lt;&gt;"",M122,IF(OR(K122='설정'!$B$6,K122='설정'!$B$8),SUBSTITUTE(K122,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G122)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G122)),"화목","반")),K122))</f>
+        <f>IF(M122&lt;&gt;"",M122,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K122&lt;&gt;""),'설정'!$B$10,IF(OR(K122='설정'!$B$6,K122='설정'!$B$8),SUBSTITUTE(K122,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G122)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G122)),"화목","반")),K122)))</f>
         <v/>
       </c>
       <c r="P122" s="30">
@@ -30555,7 +30589,7 @@
       <c r="M123" s="7" t="n"/>
       <c r="N123" s="7" t="n"/>
       <c r="O123" s="27">
-        <f>IF(M123&lt;&gt;"",M123,IF(OR(K123='설정'!$B$6,K123='설정'!$B$8),SUBSTITUTE(K123,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G123)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G123)),"화목","반")),K123))</f>
+        <f>IF(M123&lt;&gt;"",M123,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K123&lt;&gt;""),'설정'!$B$10,IF(OR(K123='설정'!$B$6,K123='설정'!$B$8),SUBSTITUTE(K123,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G123)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G123)),"화목","반")),K123)))</f>
         <v/>
       </c>
       <c r="P123" s="30">
@@ -30618,7 +30652,7 @@
       <c r="M124" s="7" t="n"/>
       <c r="N124" s="7" t="n"/>
       <c r="O124" s="27">
-        <f>IF(M124&lt;&gt;"",M124,IF(OR(K124='설정'!$B$6,K124='설정'!$B$8),SUBSTITUTE(K124,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G124)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G124)),"화목","반")),K124))</f>
+        <f>IF(M124&lt;&gt;"",M124,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K124&lt;&gt;""),'설정'!$B$10,IF(OR(K124='설정'!$B$6,K124='설정'!$B$8),SUBSTITUTE(K124,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G124)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G124)),"화목","반")),K124)))</f>
         <v/>
       </c>
       <c r="P124" s="30">
@@ -30681,7 +30715,7 @@
       <c r="M125" s="7" t="n"/>
       <c r="N125" s="7" t="n"/>
       <c r="O125" s="27">
-        <f>IF(M125&lt;&gt;"",M125,IF(OR(K125='설정'!$B$6,K125='설정'!$B$8),SUBSTITUTE(K125,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G125)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G125)),"화목","반")),K125))</f>
+        <f>IF(M125&lt;&gt;"",M125,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K125&lt;&gt;""),'설정'!$B$10,IF(OR(K125='설정'!$B$6,K125='설정'!$B$8),SUBSTITUTE(K125,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G125)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G125)),"화목","반")),K125)))</f>
         <v/>
       </c>
       <c r="P125" s="30">
@@ -30744,7 +30778,7 @@
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="n"/>
       <c r="O126" s="27">
-        <f>IF(M126&lt;&gt;"",M126,IF(OR(K126='설정'!$B$6,K126='설정'!$B$8),SUBSTITUTE(K126,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G126)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G126)),"화목","반")),K126))</f>
+        <f>IF(M126&lt;&gt;"",M126,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K126&lt;&gt;""),'설정'!$B$10,IF(OR(K126='설정'!$B$6,K126='설정'!$B$8),SUBSTITUTE(K126,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G126)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G126)),"화목","반")),K126)))</f>
         <v/>
       </c>
       <c r="P126" s="30">
@@ -30807,7 +30841,7 @@
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="n"/>
       <c r="O127" s="27">
-        <f>IF(M127&lt;&gt;"",M127,IF(OR(K127='설정'!$B$6,K127='설정'!$B$8),SUBSTITUTE(K127,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G127)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G127)),"화목","반")),K127))</f>
+        <f>IF(M127&lt;&gt;"",M127,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K127&lt;&gt;""),'설정'!$B$10,IF(OR(K127='설정'!$B$6,K127='설정'!$B$8),SUBSTITUTE(K127,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G127)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G127)),"화목","반")),K127)))</f>
         <v/>
       </c>
       <c r="P127" s="30">
@@ -30870,7 +30904,7 @@
       <c r="M128" s="7" t="n"/>
       <c r="N128" s="7" t="n"/>
       <c r="O128" s="27">
-        <f>IF(M128&lt;&gt;"",M128,IF(OR(K128='설정'!$B$6,K128='설정'!$B$8),SUBSTITUTE(K128,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G128)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G128)),"화목","반")),K128))</f>
+        <f>IF(M128&lt;&gt;"",M128,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K128&lt;&gt;""),'설정'!$B$10,IF(OR(K128='설정'!$B$6,K128='설정'!$B$8),SUBSTITUTE(K128,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G128)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G128)),"화목","반")),K128)))</f>
         <v/>
       </c>
       <c r="P128" s="30">
@@ -30933,7 +30967,7 @@
       <c r="M129" s="7" t="n"/>
       <c r="N129" s="7" t="n"/>
       <c r="O129" s="27">
-        <f>IF(M129&lt;&gt;"",M129,IF(OR(K129='설정'!$B$6,K129='설정'!$B$8),SUBSTITUTE(K129,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G129)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G129)),"화목","반")),K129))</f>
+        <f>IF(M129&lt;&gt;"",M129,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K129&lt;&gt;""),'설정'!$B$10,IF(OR(K129='설정'!$B$6,K129='설정'!$B$8),SUBSTITUTE(K129,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G129)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G129)),"화목","반")),K129)))</f>
         <v/>
       </c>
       <c r="P129" s="30">
@@ -30996,7 +31030,7 @@
       <c r="M130" s="7" t="n"/>
       <c r="N130" s="7" t="n"/>
       <c r="O130" s="27">
-        <f>IF(M130&lt;&gt;"",M130,IF(OR(K130='설정'!$B$6,K130='설정'!$B$8),SUBSTITUTE(K130,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G130)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G130)),"화목","반")),K130))</f>
+        <f>IF(M130&lt;&gt;"",M130,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K130&lt;&gt;""),'설정'!$B$10,IF(OR(K130='설정'!$B$6,K130='설정'!$B$8),SUBSTITUTE(K130,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G130)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G130)),"화목","반")),K130)))</f>
         <v/>
       </c>
       <c r="P130" s="30">
@@ -31059,7 +31093,7 @@
       <c r="M131" s="7" t="n"/>
       <c r="N131" s="7" t="n"/>
       <c r="O131" s="27">
-        <f>IF(M131&lt;&gt;"",M131,IF(OR(K131='설정'!$B$6,K131='설정'!$B$8),SUBSTITUTE(K131,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G131)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G131)),"화목","반")),K131))</f>
+        <f>IF(M131&lt;&gt;"",M131,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K131&lt;&gt;""),'설정'!$B$10,IF(OR(K131='설정'!$B$6,K131='설정'!$B$8),SUBSTITUTE(K131,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G131)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G131)),"화목","반")),K131)))</f>
         <v/>
       </c>
       <c r="P131" s="30">
@@ -31122,7 +31156,7 @@
       <c r="M132" s="7" t="n"/>
       <c r="N132" s="7" t="n"/>
       <c r="O132" s="27">
-        <f>IF(M132&lt;&gt;"",M132,IF(OR(K132='설정'!$B$6,K132='설정'!$B$8),SUBSTITUTE(K132,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G132)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G132)),"화목","반")),K132))</f>
+        <f>IF(M132&lt;&gt;"",M132,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K132&lt;&gt;""),'설정'!$B$10,IF(OR(K132='설정'!$B$6,K132='설정'!$B$8),SUBSTITUTE(K132,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G132)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G132)),"화목","반")),K132)))</f>
         <v/>
       </c>
       <c r="P132" s="30">
@@ -31185,7 +31219,7 @@
       <c r="M133" s="7" t="n"/>
       <c r="N133" s="7" t="n"/>
       <c r="O133" s="27">
-        <f>IF(M133&lt;&gt;"",M133,IF(OR(K133='설정'!$B$6,K133='설정'!$B$8),SUBSTITUTE(K133,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G133)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G133)),"화목","반")),K133))</f>
+        <f>IF(M133&lt;&gt;"",M133,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K133&lt;&gt;""),'설정'!$B$10,IF(OR(K133='설정'!$B$6,K133='설정'!$B$8),SUBSTITUTE(K133,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G133)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G133)),"화목","반")),K133)))</f>
         <v/>
       </c>
       <c r="P133" s="30">
@@ -31248,7 +31282,7 @@
       <c r="M134" s="7" t="n"/>
       <c r="N134" s="7" t="n"/>
       <c r="O134" s="27">
-        <f>IF(M134&lt;&gt;"",M134,IF(OR(K134='설정'!$B$6,K134='설정'!$B$8),SUBSTITUTE(K134,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G134)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G134)),"화목","반")),K134))</f>
+        <f>IF(M134&lt;&gt;"",M134,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K134&lt;&gt;""),'설정'!$B$10,IF(OR(K134='설정'!$B$6,K134='설정'!$B$8),SUBSTITUTE(K134,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G134)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G134)),"화목","반")),K134)))</f>
         <v/>
       </c>
       <c r="P134" s="30">
@@ -31311,7 +31345,7 @@
       <c r="M135" s="7" t="n"/>
       <c r="N135" s="7" t="n"/>
       <c r="O135" s="27">
-        <f>IF(M135&lt;&gt;"",M135,IF(OR(K135='설정'!$B$6,K135='설정'!$B$8),SUBSTITUTE(K135,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G135)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G135)),"화목","반")),K135))</f>
+        <f>IF(M135&lt;&gt;"",M135,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K135&lt;&gt;""),'설정'!$B$10,IF(OR(K135='설정'!$B$6,K135='설정'!$B$8),SUBSTITUTE(K135,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G135)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G135)),"화목","반")),K135)))</f>
         <v/>
       </c>
       <c r="P135" s="30">
@@ -31374,7 +31408,7 @@
       <c r="M136" s="7" t="n"/>
       <c r="N136" s="7" t="n"/>
       <c r="O136" s="27">
-        <f>IF(M136&lt;&gt;"",M136,IF(OR(K136='설정'!$B$6,K136='설정'!$B$8),SUBSTITUTE(K136,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G136)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G136)),"화목","반")),K136))</f>
+        <f>IF(M136&lt;&gt;"",M136,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K136&lt;&gt;""),'설정'!$B$10,IF(OR(K136='설정'!$B$6,K136='설정'!$B$8),SUBSTITUTE(K136,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G136)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G136)),"화목","반")),K136)))</f>
         <v/>
       </c>
       <c r="P136" s="30">
@@ -31437,7 +31471,7 @@
       <c r="M137" s="7" t="n"/>
       <c r="N137" s="7" t="n"/>
       <c r="O137" s="27">
-        <f>IF(M137&lt;&gt;"",M137,IF(OR(K137='설정'!$B$6,K137='설정'!$B$8),SUBSTITUTE(K137,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G137)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G137)),"화목","반")),K137))</f>
+        <f>IF(M137&lt;&gt;"",M137,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K137&lt;&gt;""),'설정'!$B$10,IF(OR(K137='설정'!$B$6,K137='설정'!$B$8),SUBSTITUTE(K137,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G137)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G137)),"화목","반")),K137)))</f>
         <v/>
       </c>
       <c r="P137" s="30">
@@ -31500,7 +31534,7 @@
       <c r="M138" s="7" t="n"/>
       <c r="N138" s="7" t="n"/>
       <c r="O138" s="27">
-        <f>IF(M138&lt;&gt;"",M138,IF(OR(K138='설정'!$B$6,K138='설정'!$B$8),SUBSTITUTE(K138,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G138)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G138)),"화목","반")),K138))</f>
+        <f>IF(M138&lt;&gt;"",M138,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K138&lt;&gt;""),'설정'!$B$10,IF(OR(K138='설정'!$B$6,K138='설정'!$B$8),SUBSTITUTE(K138,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G138)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G138)),"화목","반")),K138)))</f>
         <v/>
       </c>
       <c r="P138" s="30">
@@ -31563,7 +31597,7 @@
       <c r="M139" s="7" t="n"/>
       <c r="N139" s="7" t="n"/>
       <c r="O139" s="27">
-        <f>IF(M139&lt;&gt;"",M139,IF(OR(K139='설정'!$B$6,K139='설정'!$B$8),SUBSTITUTE(K139,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G139)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G139)),"화목","반")),K139))</f>
+        <f>IF(M139&lt;&gt;"",M139,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K139&lt;&gt;""),'설정'!$B$10,IF(OR(K139='설정'!$B$6,K139='설정'!$B$8),SUBSTITUTE(K139,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G139)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G139)),"화목","반")),K139)))</f>
         <v/>
       </c>
       <c r="P139" s="30">
@@ -31626,7 +31660,7 @@
       <c r="M140" s="7" t="n"/>
       <c r="N140" s="7" t="n"/>
       <c r="O140" s="27">
-        <f>IF(M140&lt;&gt;"",M140,IF(OR(K140='설정'!$B$6,K140='설정'!$B$8),SUBSTITUTE(K140,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G140)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G140)),"화목","반")),K140))</f>
+        <f>IF(M140&lt;&gt;"",M140,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K140&lt;&gt;""),'설정'!$B$10,IF(OR(K140='설정'!$B$6,K140='설정'!$B$8),SUBSTITUTE(K140,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G140)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G140)),"화목","반")),K140)))</f>
         <v/>
       </c>
       <c r="P140" s="30">
@@ -31689,7 +31723,7 @@
       <c r="M141" s="7" t="n"/>
       <c r="N141" s="7" t="n"/>
       <c r="O141" s="27">
-        <f>IF(M141&lt;&gt;"",M141,IF(OR(K141='설정'!$B$6,K141='설정'!$B$8),SUBSTITUTE(K141,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G141)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G141)),"화목","반")),K141))</f>
+        <f>IF(M141&lt;&gt;"",M141,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K141&lt;&gt;""),'설정'!$B$10,IF(OR(K141='설정'!$B$6,K141='설정'!$B$8),SUBSTITUTE(K141,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G141)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G141)),"화목","반")),K141)))</f>
         <v/>
       </c>
       <c r="P141" s="30">
@@ -31752,7 +31786,7 @@
       <c r="M142" s="7" t="n"/>
       <c r="N142" s="7" t="n"/>
       <c r="O142" s="27">
-        <f>IF(M142&lt;&gt;"",M142,IF(OR(K142='설정'!$B$6,K142='설정'!$B$8),SUBSTITUTE(K142,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G142)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G142)),"화목","반")),K142))</f>
+        <f>IF(M142&lt;&gt;"",M142,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K142&lt;&gt;""),'설정'!$B$10,IF(OR(K142='설정'!$B$6,K142='설정'!$B$8),SUBSTITUTE(K142,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G142)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G142)),"화목","반")),K142)))</f>
         <v/>
       </c>
       <c r="P142" s="30">
@@ -31815,7 +31849,7 @@
       <c r="M143" s="7" t="n"/>
       <c r="N143" s="7" t="n"/>
       <c r="O143" s="27">
-        <f>IF(M143&lt;&gt;"",M143,IF(OR(K143='설정'!$B$6,K143='설정'!$B$8),SUBSTITUTE(K143,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G143)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G143)),"화목","반")),K143))</f>
+        <f>IF(M143&lt;&gt;"",M143,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K143&lt;&gt;""),'설정'!$B$10,IF(OR(K143='설정'!$B$6,K143='설정'!$B$8),SUBSTITUTE(K143,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G143)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G143)),"화목","반")),K143)))</f>
         <v/>
       </c>
       <c r="P143" s="30">
@@ -31878,7 +31912,7 @@
       <c r="M144" s="7" t="n"/>
       <c r="N144" s="7" t="n"/>
       <c r="O144" s="27">
-        <f>IF(M144&lt;&gt;"",M144,IF(OR(K144='설정'!$B$6,K144='설정'!$B$8),SUBSTITUTE(K144,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G144)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G144)),"화목","반")),K144))</f>
+        <f>IF(M144&lt;&gt;"",M144,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K144&lt;&gt;""),'설정'!$B$10,IF(OR(K144='설정'!$B$6,K144='설정'!$B$8),SUBSTITUTE(K144,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G144)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G144)),"화목","반")),K144)))</f>
         <v/>
       </c>
       <c r="P144" s="30">
@@ -31941,7 +31975,7 @@
       <c r="M145" s="7" t="n"/>
       <c r="N145" s="7" t="n"/>
       <c r="O145" s="27">
-        <f>IF(M145&lt;&gt;"",M145,IF(OR(K145='설정'!$B$6,K145='설정'!$B$8),SUBSTITUTE(K145,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G145)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G145)),"화목","반")),K145))</f>
+        <f>IF(M145&lt;&gt;"",M145,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K145&lt;&gt;""),'설정'!$B$10,IF(OR(K145='설정'!$B$6,K145='설정'!$B$8),SUBSTITUTE(K145,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G145)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G145)),"화목","반")),K145)))</f>
         <v/>
       </c>
       <c r="P145" s="30">
@@ -32004,7 +32038,7 @@
       <c r="M146" s="7" t="n"/>
       <c r="N146" s="7" t="n"/>
       <c r="O146" s="27">
-        <f>IF(M146&lt;&gt;"",M146,IF(OR(K146='설정'!$B$6,K146='설정'!$B$8),SUBSTITUTE(K146,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G146)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G146)),"화목","반")),K146))</f>
+        <f>IF(M146&lt;&gt;"",M146,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K146&lt;&gt;""),'설정'!$B$10,IF(OR(K146='설정'!$B$6,K146='설정'!$B$8),SUBSTITUTE(K146,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G146)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G146)),"화목","반")),K146)))</f>
         <v/>
       </c>
       <c r="P146" s="30">
@@ -32067,7 +32101,7 @@
       <c r="M147" s="7" t="n"/>
       <c r="N147" s="7" t="n"/>
       <c r="O147" s="27">
-        <f>IF(M147&lt;&gt;"",M147,IF(OR(K147='설정'!$B$6,K147='설정'!$B$8),SUBSTITUTE(K147,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G147)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G147)),"화목","반")),K147))</f>
+        <f>IF(M147&lt;&gt;"",M147,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K147&lt;&gt;""),'설정'!$B$10,IF(OR(K147='설정'!$B$6,K147='설정'!$B$8),SUBSTITUTE(K147,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G147)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G147)),"화목","반")),K147)))</f>
         <v/>
       </c>
       <c r="P147" s="30">
@@ -32130,7 +32164,7 @@
       <c r="M148" s="7" t="n"/>
       <c r="N148" s="7" t="n"/>
       <c r="O148" s="27">
-        <f>IF(M148&lt;&gt;"",M148,IF(OR(K148='설정'!$B$6,K148='설정'!$B$8),SUBSTITUTE(K148,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G148)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G148)),"화목","반")),K148))</f>
+        <f>IF(M148&lt;&gt;"",M148,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K148&lt;&gt;""),'설정'!$B$10,IF(OR(K148='설정'!$B$6,K148='설정'!$B$8),SUBSTITUTE(K148,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G148)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G148)),"화목","반")),K148)))</f>
         <v/>
       </c>
       <c r="P148" s="30">
@@ -32193,7 +32227,7 @@
       <c r="M149" s="7" t="n"/>
       <c r="N149" s="7" t="n"/>
       <c r="O149" s="27">
-        <f>IF(M149&lt;&gt;"",M149,IF(OR(K149='설정'!$B$6,K149='설정'!$B$8),SUBSTITUTE(K149,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G149)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G149)),"화목","반")),K149))</f>
+        <f>IF(M149&lt;&gt;"",M149,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K149&lt;&gt;""),'설정'!$B$10,IF(OR(K149='설정'!$B$6,K149='설정'!$B$8),SUBSTITUTE(K149,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G149)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G149)),"화목","반")),K149)))</f>
         <v/>
       </c>
       <c r="P149" s="30">
@@ -32256,7 +32290,7 @@
       <c r="M150" s="7" t="n"/>
       <c r="N150" s="7" t="n"/>
       <c r="O150" s="27">
-        <f>IF(M150&lt;&gt;"",M150,IF(OR(K150='설정'!$B$6,K150='설정'!$B$8),SUBSTITUTE(K150,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G150)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G150)),"화목","반")),K150))</f>
+        <f>IF(M150&lt;&gt;"",M150,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K150&lt;&gt;""),'설정'!$B$10,IF(OR(K150='설정'!$B$6,K150='설정'!$B$8),SUBSTITUTE(K150,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G150)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G150)),"화목","반")),K150)))</f>
         <v/>
       </c>
       <c r="P150" s="30">
@@ -32319,7 +32353,7 @@
       <c r="M151" s="7" t="n"/>
       <c r="N151" s="7" t="n"/>
       <c r="O151" s="27">
-        <f>IF(M151&lt;&gt;"",M151,IF(OR(K151='설정'!$B$6,K151='설정'!$B$8),SUBSTITUTE(K151,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G151)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G151)),"화목","반")),K151))</f>
+        <f>IF(M151&lt;&gt;"",M151,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K151&lt;&gt;""),'설정'!$B$10,IF(OR(K151='설정'!$B$6,K151='설정'!$B$8),SUBSTITUTE(K151,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G151)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G151)),"화목","반")),K151)))</f>
         <v/>
       </c>
       <c r="P151" s="30">
@@ -32382,7 +32416,7 @@
       <c r="M152" s="7" t="n"/>
       <c r="N152" s="7" t="n"/>
       <c r="O152" s="27">
-        <f>IF(M152&lt;&gt;"",M152,IF(OR(K152='설정'!$B$6,K152='설정'!$B$8),SUBSTITUTE(K152,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G152)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G152)),"화목","반")),K152))</f>
+        <f>IF(M152&lt;&gt;"",M152,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K152&lt;&gt;""),'설정'!$B$10,IF(OR(K152='설정'!$B$6,K152='설정'!$B$8),SUBSTITUTE(K152,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G152)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G152)),"화목","반")),K152)))</f>
         <v/>
       </c>
       <c r="P152" s="30">
@@ -32445,7 +32479,7 @@
       <c r="M153" s="7" t="n"/>
       <c r="N153" s="7" t="n"/>
       <c r="O153" s="27">
-        <f>IF(M153&lt;&gt;"",M153,IF(OR(K153='설정'!$B$6,K153='설정'!$B$8),SUBSTITUTE(K153,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G153)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G153)),"화목","반")),K153))</f>
+        <f>IF(M153&lt;&gt;"",M153,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K153&lt;&gt;""),'설정'!$B$10,IF(OR(K153='설정'!$B$6,K153='설정'!$B$8),SUBSTITUTE(K153,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G153)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G153)),"화목","반")),K153)))</f>
         <v/>
       </c>
       <c r="P153" s="30">
@@ -32508,7 +32542,7 @@
       <c r="M154" s="7" t="n"/>
       <c r="N154" s="7" t="n"/>
       <c r="O154" s="27">
-        <f>IF(M154&lt;&gt;"",M154,IF(OR(K154='설정'!$B$6,K154='설정'!$B$8),SUBSTITUTE(K154,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G154)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G154)),"화목","반")),K154))</f>
+        <f>IF(M154&lt;&gt;"",M154,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K154&lt;&gt;""),'설정'!$B$10,IF(OR(K154='설정'!$B$6,K154='설정'!$B$8),SUBSTITUTE(K154,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G154)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G154)),"화목","반")),K154)))</f>
         <v/>
       </c>
       <c r="P154" s="30">
@@ -32571,7 +32605,7 @@
       <c r="M155" s="7" t="n"/>
       <c r="N155" s="7" t="n"/>
       <c r="O155" s="27">
-        <f>IF(M155&lt;&gt;"",M155,IF(OR(K155='설정'!$B$6,K155='설정'!$B$8),SUBSTITUTE(K155,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G155)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G155)),"화목","반")),K155))</f>
+        <f>IF(M155&lt;&gt;"",M155,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K155&lt;&gt;""),'설정'!$B$10,IF(OR(K155='설정'!$B$6,K155='설정'!$B$8),SUBSTITUTE(K155,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G155)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G155)),"화목","반")),K155)))</f>
         <v/>
       </c>
       <c r="P155" s="30">
@@ -32634,7 +32668,7 @@
       <c r="M156" s="7" t="n"/>
       <c r="N156" s="7" t="n"/>
       <c r="O156" s="27">
-        <f>IF(M156&lt;&gt;"",M156,IF(OR(K156='설정'!$B$6,K156='설정'!$B$8),SUBSTITUTE(K156,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G156)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G156)),"화목","반")),K156))</f>
+        <f>IF(M156&lt;&gt;"",M156,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K156&lt;&gt;""),'설정'!$B$10,IF(OR(K156='설정'!$B$6,K156='설정'!$B$8),SUBSTITUTE(K156,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G156)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G156)),"화목","반")),K156)))</f>
         <v/>
       </c>
       <c r="P156" s="30">

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="164" formatCode="0.#"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -111,6 +111,11 @@
       <b val="1"/>
       <color rgb="00C55A11"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00C00000"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -246,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -352,6 +357,9 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -373,7 +381,7 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -959,7 +967,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>TF1월</t>
+          <t>TF자사</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -1580,8 +1588,15 @@
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="6" t="n"/>
-      <c r="B58" s="16" t="n"/>
+      <c r="A58" s="6">
+        <f>B10</f>
+        <v/>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>자사고·특목고 진학 예정 학생을 위한 반으로, 고교 내신과 심화 문항 해결력을 함께 준비합니다.</t>
+        </is>
+      </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
           <t>← 공통수학반이 더 있으면 반 이름과 소개를 추가</t>
@@ -23409,7 +23424,7 @@
         <v/>
       </c>
       <c r="U11" s="8">
-        <f>SUM(U7:U10)</f>
+        <f>COUNTIF($O$7:$O$156,"?*")</f>
         <v/>
       </c>
       <c r="V11" s="36">
@@ -23421,11 +23436,11 @@
         <v/>
       </c>
       <c r="X11" s="8">
-        <f>SUM(X7:X10)</f>
+        <f>COUNTIFS($O$7:$O$156,"?*",$D$7:$D$156,"재원")</f>
         <v/>
       </c>
       <c r="Y11" s="8">
-        <f>SUM(Y7:Y10)</f>
+        <f>COUNTIFS($O$7:$O$156,"?*",$D$7:$D$156,"외부")</f>
         <v/>
       </c>
     </row>
@@ -23489,6 +23504,10 @@
       </c>
       <c r="Q12" s="10">
         <f>IF(J12="","",J12+ROW()/100000)</f>
+        <v/>
+      </c>
+      <c r="S12" s="37">
+        <f>IF('설정'!$B$10="","","※ "&amp;'설정'!$B$10&amp;" "&amp;COUNTIF($O$7:$O$156,'설정'!$B$10)&amp;"명은 위 반별 인원에 없음(아래 요일반 표)")</f>
         <v/>
       </c>
     </row>
@@ -32862,7 +32881,7 @@
         <f>IF($N7="","",INDEX('반배정'!H$7:H$156,$N7))</f>
         <v/>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="38">
         <f>IF($N7="","",INDEX('반배정'!I$7:I$156,$N7))</f>
         <v/>
       </c>
@@ -32920,7 +32939,7 @@
         <f>IF($N8="","",INDEX('반배정'!H$7:H$156,$N8))</f>
         <v/>
       </c>
-      <c r="H8" s="37">
+      <c r="H8" s="38">
         <f>IF($N8="","",INDEX('반배정'!I$7:I$156,$N8))</f>
         <v/>
       </c>
@@ -32978,7 +32997,7 @@
         <f>IF($N9="","",INDEX('반배정'!H$7:H$156,$N9))</f>
         <v/>
       </c>
-      <c r="H9" s="37">
+      <c r="H9" s="38">
         <f>IF($N9="","",INDEX('반배정'!I$7:I$156,$N9))</f>
         <v/>
       </c>
@@ -33036,7 +33055,7 @@
         <f>IF($N10="","",INDEX('반배정'!H$7:H$156,$N10))</f>
         <v/>
       </c>
-      <c r="H10" s="37">
+      <c r="H10" s="38">
         <f>IF($N10="","",INDEX('반배정'!I$7:I$156,$N10))</f>
         <v/>
       </c>
@@ -33094,7 +33113,7 @@
         <f>IF($N11="","",INDEX('반배정'!H$7:H$156,$N11))</f>
         <v/>
       </c>
-      <c r="H11" s="37">
+      <c r="H11" s="38">
         <f>IF($N11="","",INDEX('반배정'!I$7:I$156,$N11))</f>
         <v/>
       </c>
@@ -33152,7 +33171,7 @@
         <f>IF($N12="","",INDEX('반배정'!H$7:H$156,$N12))</f>
         <v/>
       </c>
-      <c r="H12" s="37">
+      <c r="H12" s="38">
         <f>IF($N12="","",INDEX('반배정'!I$7:I$156,$N12))</f>
         <v/>
       </c>
@@ -33210,7 +33229,7 @@
         <f>IF($N13="","",INDEX('반배정'!H$7:H$156,$N13))</f>
         <v/>
       </c>
-      <c r="H13" s="37">
+      <c r="H13" s="38">
         <f>IF($N13="","",INDEX('반배정'!I$7:I$156,$N13))</f>
         <v/>
       </c>
@@ -33268,7 +33287,7 @@
         <f>IF($N14="","",INDEX('반배정'!H$7:H$156,$N14))</f>
         <v/>
       </c>
-      <c r="H14" s="37">
+      <c r="H14" s="38">
         <f>IF($N14="","",INDEX('반배정'!I$7:I$156,$N14))</f>
         <v/>
       </c>
@@ -33326,7 +33345,7 @@
         <f>IF($N15="","",INDEX('반배정'!H$7:H$156,$N15))</f>
         <v/>
       </c>
-      <c r="H15" s="37">
+      <c r="H15" s="38">
         <f>IF($N15="","",INDEX('반배정'!I$7:I$156,$N15))</f>
         <v/>
       </c>
@@ -33384,7 +33403,7 @@
         <f>IF($N16="","",INDEX('반배정'!H$7:H$156,$N16))</f>
         <v/>
       </c>
-      <c r="H16" s="37">
+      <c r="H16" s="38">
         <f>IF($N16="","",INDEX('반배정'!I$7:I$156,$N16))</f>
         <v/>
       </c>
@@ -33442,7 +33461,7 @@
         <f>IF($N17="","",INDEX('반배정'!H$7:H$156,$N17))</f>
         <v/>
       </c>
-      <c r="H17" s="37">
+      <c r="H17" s="38">
         <f>IF($N17="","",INDEX('반배정'!I$7:I$156,$N17))</f>
         <v/>
       </c>
@@ -33500,7 +33519,7 @@
         <f>IF($N18="","",INDEX('반배정'!H$7:H$156,$N18))</f>
         <v/>
       </c>
-      <c r="H18" s="37">
+      <c r="H18" s="38">
         <f>IF($N18="","",INDEX('반배정'!I$7:I$156,$N18))</f>
         <v/>
       </c>
@@ -33558,7 +33577,7 @@
         <f>IF($N19="","",INDEX('반배정'!H$7:H$156,$N19))</f>
         <v/>
       </c>
-      <c r="H19" s="37">
+      <c r="H19" s="38">
         <f>IF($N19="","",INDEX('반배정'!I$7:I$156,$N19))</f>
         <v/>
       </c>
@@ -33616,7 +33635,7 @@
         <f>IF($N20="","",INDEX('반배정'!H$7:H$156,$N20))</f>
         <v/>
       </c>
-      <c r="H20" s="37">
+      <c r="H20" s="38">
         <f>IF($N20="","",INDEX('반배정'!I$7:I$156,$N20))</f>
         <v/>
       </c>
@@ -33674,7 +33693,7 @@
         <f>IF($N21="","",INDEX('반배정'!H$7:H$156,$N21))</f>
         <v/>
       </c>
-      <c r="H21" s="37">
+      <c r="H21" s="38">
         <f>IF($N21="","",INDEX('반배정'!I$7:I$156,$N21))</f>
         <v/>
       </c>
@@ -33732,7 +33751,7 @@
         <f>IF($N22="","",INDEX('반배정'!H$7:H$156,$N22))</f>
         <v/>
       </c>
-      <c r="H22" s="37">
+      <c r="H22" s="38">
         <f>IF($N22="","",INDEX('반배정'!I$7:I$156,$N22))</f>
         <v/>
       </c>
@@ -33790,7 +33809,7 @@
         <f>IF($N23="","",INDEX('반배정'!H$7:H$156,$N23))</f>
         <v/>
       </c>
-      <c r="H23" s="37">
+      <c r="H23" s="38">
         <f>IF($N23="","",INDEX('반배정'!I$7:I$156,$N23))</f>
         <v/>
       </c>
@@ -33848,7 +33867,7 @@
         <f>IF($N24="","",INDEX('반배정'!H$7:H$156,$N24))</f>
         <v/>
       </c>
-      <c r="H24" s="37">
+      <c r="H24" s="38">
         <f>IF($N24="","",INDEX('반배정'!I$7:I$156,$N24))</f>
         <v/>
       </c>
@@ -33906,7 +33925,7 @@
         <f>IF($N25="","",INDEX('반배정'!H$7:H$156,$N25))</f>
         <v/>
       </c>
-      <c r="H25" s="37">
+      <c r="H25" s="38">
         <f>IF($N25="","",INDEX('반배정'!I$7:I$156,$N25))</f>
         <v/>
       </c>
@@ -33964,7 +33983,7 @@
         <f>IF($N26="","",INDEX('반배정'!H$7:H$156,$N26))</f>
         <v/>
       </c>
-      <c r="H26" s="37">
+      <c r="H26" s="38">
         <f>IF($N26="","",INDEX('반배정'!I$7:I$156,$N26))</f>
         <v/>
       </c>
@@ -34022,7 +34041,7 @@
         <f>IF($N27="","",INDEX('반배정'!H$7:H$156,$N27))</f>
         <v/>
       </c>
-      <c r="H27" s="37">
+      <c r="H27" s="38">
         <f>IF($N27="","",INDEX('반배정'!I$7:I$156,$N27))</f>
         <v/>
       </c>
@@ -34080,7 +34099,7 @@
         <f>IF($N28="","",INDEX('반배정'!H$7:H$156,$N28))</f>
         <v/>
       </c>
-      <c r="H28" s="37">
+      <c r="H28" s="38">
         <f>IF($N28="","",INDEX('반배정'!I$7:I$156,$N28))</f>
         <v/>
       </c>
@@ -34138,7 +34157,7 @@
         <f>IF($N29="","",INDEX('반배정'!H$7:H$156,$N29))</f>
         <v/>
       </c>
-      <c r="H29" s="37">
+      <c r="H29" s="38">
         <f>IF($N29="","",INDEX('반배정'!I$7:I$156,$N29))</f>
         <v/>
       </c>
@@ -34196,7 +34215,7 @@
         <f>IF($N30="","",INDEX('반배정'!H$7:H$156,$N30))</f>
         <v/>
       </c>
-      <c r="H30" s="37">
+      <c r="H30" s="38">
         <f>IF($N30="","",INDEX('반배정'!I$7:I$156,$N30))</f>
         <v/>
       </c>
@@ -34254,7 +34273,7 @@
         <f>IF($N31="","",INDEX('반배정'!H$7:H$156,$N31))</f>
         <v/>
       </c>
-      <c r="H31" s="37">
+      <c r="H31" s="38">
         <f>IF($N31="","",INDEX('반배정'!I$7:I$156,$N31))</f>
         <v/>
       </c>
@@ -34312,7 +34331,7 @@
         <f>IF($N32="","",INDEX('반배정'!H$7:H$156,$N32))</f>
         <v/>
       </c>
-      <c r="H32" s="37">
+      <c r="H32" s="38">
         <f>IF($N32="","",INDEX('반배정'!I$7:I$156,$N32))</f>
         <v/>
       </c>
@@ -34370,7 +34389,7 @@
         <f>IF($N33="","",INDEX('반배정'!H$7:H$156,$N33))</f>
         <v/>
       </c>
-      <c r="H33" s="37">
+      <c r="H33" s="38">
         <f>IF($N33="","",INDEX('반배정'!I$7:I$156,$N33))</f>
         <v/>
       </c>
@@ -34428,7 +34447,7 @@
         <f>IF($N34="","",INDEX('반배정'!H$7:H$156,$N34))</f>
         <v/>
       </c>
-      <c r="H34" s="37">
+      <c r="H34" s="38">
         <f>IF($N34="","",INDEX('반배정'!I$7:I$156,$N34))</f>
         <v/>
       </c>
@@ -34486,7 +34505,7 @@
         <f>IF($N35="","",INDEX('반배정'!H$7:H$156,$N35))</f>
         <v/>
       </c>
-      <c r="H35" s="37">
+      <c r="H35" s="38">
         <f>IF($N35="","",INDEX('반배정'!I$7:I$156,$N35))</f>
         <v/>
       </c>
@@ -34544,7 +34563,7 @@
         <f>IF($N36="","",INDEX('반배정'!H$7:H$156,$N36))</f>
         <v/>
       </c>
-      <c r="H36" s="37">
+      <c r="H36" s="38">
         <f>IF($N36="","",INDEX('반배정'!I$7:I$156,$N36))</f>
         <v/>
       </c>
@@ -34602,7 +34621,7 @@
         <f>IF($N37="","",INDEX('반배정'!H$7:H$156,$N37))</f>
         <v/>
       </c>
-      <c r="H37" s="37">
+      <c r="H37" s="38">
         <f>IF($N37="","",INDEX('반배정'!I$7:I$156,$N37))</f>
         <v/>
       </c>
@@ -34660,7 +34679,7 @@
         <f>IF($N38="","",INDEX('반배정'!H$7:H$156,$N38))</f>
         <v/>
       </c>
-      <c r="H38" s="37">
+      <c r="H38" s="38">
         <f>IF($N38="","",INDEX('반배정'!I$7:I$156,$N38))</f>
         <v/>
       </c>
@@ -34718,7 +34737,7 @@
         <f>IF($N39="","",INDEX('반배정'!H$7:H$156,$N39))</f>
         <v/>
       </c>
-      <c r="H39" s="37">
+      <c r="H39" s="38">
         <f>IF($N39="","",INDEX('반배정'!I$7:I$156,$N39))</f>
         <v/>
       </c>
@@ -34776,7 +34795,7 @@
         <f>IF($N40="","",INDEX('반배정'!H$7:H$156,$N40))</f>
         <v/>
       </c>
-      <c r="H40" s="37">
+      <c r="H40" s="38">
         <f>IF($N40="","",INDEX('반배정'!I$7:I$156,$N40))</f>
         <v/>
       </c>
@@ -34834,7 +34853,7 @@
         <f>IF($N41="","",INDEX('반배정'!H$7:H$156,$N41))</f>
         <v/>
       </c>
-      <c r="H41" s="37">
+      <c r="H41" s="38">
         <f>IF($N41="","",INDEX('반배정'!I$7:I$156,$N41))</f>
         <v/>
       </c>
@@ -34892,7 +34911,7 @@
         <f>IF($N42="","",INDEX('반배정'!H$7:H$156,$N42))</f>
         <v/>
       </c>
-      <c r="H42" s="37">
+      <c r="H42" s="38">
         <f>IF($N42="","",INDEX('반배정'!I$7:I$156,$N42))</f>
         <v/>
       </c>
@@ -34950,7 +34969,7 @@
         <f>IF($N43="","",INDEX('반배정'!H$7:H$156,$N43))</f>
         <v/>
       </c>
-      <c r="H43" s="37">
+      <c r="H43" s="38">
         <f>IF($N43="","",INDEX('반배정'!I$7:I$156,$N43))</f>
         <v/>
       </c>
@@ -35008,7 +35027,7 @@
         <f>IF($N44="","",INDEX('반배정'!H$7:H$156,$N44))</f>
         <v/>
       </c>
-      <c r="H44" s="37">
+      <c r="H44" s="38">
         <f>IF($N44="","",INDEX('반배정'!I$7:I$156,$N44))</f>
         <v/>
       </c>
@@ -35066,7 +35085,7 @@
         <f>IF($N45="","",INDEX('반배정'!H$7:H$156,$N45))</f>
         <v/>
       </c>
-      <c r="H45" s="37">
+      <c r="H45" s="38">
         <f>IF($N45="","",INDEX('반배정'!I$7:I$156,$N45))</f>
         <v/>
       </c>
@@ -35124,7 +35143,7 @@
         <f>IF($N46="","",INDEX('반배정'!H$7:H$156,$N46))</f>
         <v/>
       </c>
-      <c r="H46" s="37">
+      <c r="H46" s="38">
         <f>IF($N46="","",INDEX('반배정'!I$7:I$156,$N46))</f>
         <v/>
       </c>
@@ -35182,7 +35201,7 @@
         <f>IF($N47="","",INDEX('반배정'!H$7:H$156,$N47))</f>
         <v/>
       </c>
-      <c r="H47" s="37">
+      <c r="H47" s="38">
         <f>IF($N47="","",INDEX('반배정'!I$7:I$156,$N47))</f>
         <v/>
       </c>
@@ -35240,7 +35259,7 @@
         <f>IF($N48="","",INDEX('반배정'!H$7:H$156,$N48))</f>
         <v/>
       </c>
-      <c r="H48" s="37">
+      <c r="H48" s="38">
         <f>IF($N48="","",INDEX('반배정'!I$7:I$156,$N48))</f>
         <v/>
       </c>
@@ -35298,7 +35317,7 @@
         <f>IF($N49="","",INDEX('반배정'!H$7:H$156,$N49))</f>
         <v/>
       </c>
-      <c r="H49" s="37">
+      <c r="H49" s="38">
         <f>IF($N49="","",INDEX('반배정'!I$7:I$156,$N49))</f>
         <v/>
       </c>
@@ -35356,7 +35375,7 @@
         <f>IF($N50="","",INDEX('반배정'!H$7:H$156,$N50))</f>
         <v/>
       </c>
-      <c r="H50" s="37">
+      <c r="H50" s="38">
         <f>IF($N50="","",INDEX('반배정'!I$7:I$156,$N50))</f>
         <v/>
       </c>
@@ -35414,7 +35433,7 @@
         <f>IF($N51="","",INDEX('반배정'!H$7:H$156,$N51))</f>
         <v/>
       </c>
-      <c r="H51" s="37">
+      <c r="H51" s="38">
         <f>IF($N51="","",INDEX('반배정'!I$7:I$156,$N51))</f>
         <v/>
       </c>
@@ -35472,7 +35491,7 @@
         <f>IF($N52="","",INDEX('반배정'!H$7:H$156,$N52))</f>
         <v/>
       </c>
-      <c r="H52" s="37">
+      <c r="H52" s="38">
         <f>IF($N52="","",INDEX('반배정'!I$7:I$156,$N52))</f>
         <v/>
       </c>
@@ -35530,7 +35549,7 @@
         <f>IF($N53="","",INDEX('반배정'!H$7:H$156,$N53))</f>
         <v/>
       </c>
-      <c r="H53" s="37">
+      <c r="H53" s="38">
         <f>IF($N53="","",INDEX('반배정'!I$7:I$156,$N53))</f>
         <v/>
       </c>
@@ -35588,7 +35607,7 @@
         <f>IF($N54="","",INDEX('반배정'!H$7:H$156,$N54))</f>
         <v/>
       </c>
-      <c r="H54" s="37">
+      <c r="H54" s="38">
         <f>IF($N54="","",INDEX('반배정'!I$7:I$156,$N54))</f>
         <v/>
       </c>
@@ -35646,7 +35665,7 @@
         <f>IF($N55="","",INDEX('반배정'!H$7:H$156,$N55))</f>
         <v/>
       </c>
-      <c r="H55" s="37">
+      <c r="H55" s="38">
         <f>IF($N55="","",INDEX('반배정'!I$7:I$156,$N55))</f>
         <v/>
       </c>
@@ -35704,7 +35723,7 @@
         <f>IF($N56="","",INDEX('반배정'!H$7:H$156,$N56))</f>
         <v/>
       </c>
-      <c r="H56" s="37">
+      <c r="H56" s="38">
         <f>IF($N56="","",INDEX('반배정'!I$7:I$156,$N56))</f>
         <v/>
       </c>
@@ -35762,7 +35781,7 @@
         <f>IF($N57="","",INDEX('반배정'!H$7:H$156,$N57))</f>
         <v/>
       </c>
-      <c r="H57" s="37">
+      <c r="H57" s="38">
         <f>IF($N57="","",INDEX('반배정'!I$7:I$156,$N57))</f>
         <v/>
       </c>
@@ -35820,7 +35839,7 @@
         <f>IF($N58="","",INDEX('반배정'!H$7:H$156,$N58))</f>
         <v/>
       </c>
-      <c r="H58" s="37">
+      <c r="H58" s="38">
         <f>IF($N58="","",INDEX('반배정'!I$7:I$156,$N58))</f>
         <v/>
       </c>
@@ -35878,7 +35897,7 @@
         <f>IF($N59="","",INDEX('반배정'!H$7:H$156,$N59))</f>
         <v/>
       </c>
-      <c r="H59" s="37">
+      <c r="H59" s="38">
         <f>IF($N59="","",INDEX('반배정'!I$7:I$156,$N59))</f>
         <v/>
       </c>
@@ -35936,7 +35955,7 @@
         <f>IF($N60="","",INDEX('반배정'!H$7:H$156,$N60))</f>
         <v/>
       </c>
-      <c r="H60" s="37">
+      <c r="H60" s="38">
         <f>IF($N60="","",INDEX('반배정'!I$7:I$156,$N60))</f>
         <v/>
       </c>
@@ -35994,7 +36013,7 @@
         <f>IF($N61="","",INDEX('반배정'!H$7:H$156,$N61))</f>
         <v/>
       </c>
-      <c r="H61" s="37">
+      <c r="H61" s="38">
         <f>IF($N61="","",INDEX('반배정'!I$7:I$156,$N61))</f>
         <v/>
       </c>
@@ -36052,7 +36071,7 @@
         <f>IF($N62="","",INDEX('반배정'!H$7:H$156,$N62))</f>
         <v/>
       </c>
-      <c r="H62" s="37">
+      <c r="H62" s="38">
         <f>IF($N62="","",INDEX('반배정'!I$7:I$156,$N62))</f>
         <v/>
       </c>
@@ -36110,7 +36129,7 @@
         <f>IF($N63="","",INDEX('반배정'!H$7:H$156,$N63))</f>
         <v/>
       </c>
-      <c r="H63" s="37">
+      <c r="H63" s="38">
         <f>IF($N63="","",INDEX('반배정'!I$7:I$156,$N63))</f>
         <v/>
       </c>
@@ -36168,7 +36187,7 @@
         <f>IF($N64="","",INDEX('반배정'!H$7:H$156,$N64))</f>
         <v/>
       </c>
-      <c r="H64" s="37">
+      <c r="H64" s="38">
         <f>IF($N64="","",INDEX('반배정'!I$7:I$156,$N64))</f>
         <v/>
       </c>
@@ -36226,7 +36245,7 @@
         <f>IF($N65="","",INDEX('반배정'!H$7:H$156,$N65))</f>
         <v/>
       </c>
-      <c r="H65" s="37">
+      <c r="H65" s="38">
         <f>IF($N65="","",INDEX('반배정'!I$7:I$156,$N65))</f>
         <v/>
       </c>
@@ -36284,7 +36303,7 @@
         <f>IF($N66="","",INDEX('반배정'!H$7:H$156,$N66))</f>
         <v/>
       </c>
-      <c r="H66" s="37">
+      <c r="H66" s="38">
         <f>IF($N66="","",INDEX('반배정'!I$7:I$156,$N66))</f>
         <v/>
       </c>
@@ -36342,7 +36361,7 @@
         <f>IF($N67="","",INDEX('반배정'!H$7:H$156,$N67))</f>
         <v/>
       </c>
-      <c r="H67" s="37">
+      <c r="H67" s="38">
         <f>IF($N67="","",INDEX('반배정'!I$7:I$156,$N67))</f>
         <v/>
       </c>
@@ -36400,7 +36419,7 @@
         <f>IF($N68="","",INDEX('반배정'!H$7:H$156,$N68))</f>
         <v/>
       </c>
-      <c r="H68" s="37">
+      <c r="H68" s="38">
         <f>IF($N68="","",INDEX('반배정'!I$7:I$156,$N68))</f>
         <v/>
       </c>
@@ -36458,7 +36477,7 @@
         <f>IF($N69="","",INDEX('반배정'!H$7:H$156,$N69))</f>
         <v/>
       </c>
-      <c r="H69" s="37">
+      <c r="H69" s="38">
         <f>IF($N69="","",INDEX('반배정'!I$7:I$156,$N69))</f>
         <v/>
       </c>
@@ -36516,7 +36535,7 @@
         <f>IF($N70="","",INDEX('반배정'!H$7:H$156,$N70))</f>
         <v/>
       </c>
-      <c r="H70" s="37">
+      <c r="H70" s="38">
         <f>IF($N70="","",INDEX('반배정'!I$7:I$156,$N70))</f>
         <v/>
       </c>
@@ -36574,7 +36593,7 @@
         <f>IF($N71="","",INDEX('반배정'!H$7:H$156,$N71))</f>
         <v/>
       </c>
-      <c r="H71" s="37">
+      <c r="H71" s="38">
         <f>IF($N71="","",INDEX('반배정'!I$7:I$156,$N71))</f>
         <v/>
       </c>
@@ -36632,7 +36651,7 @@
         <f>IF($N72="","",INDEX('반배정'!H$7:H$156,$N72))</f>
         <v/>
       </c>
-      <c r="H72" s="37">
+      <c r="H72" s="38">
         <f>IF($N72="","",INDEX('반배정'!I$7:I$156,$N72))</f>
         <v/>
       </c>
@@ -36690,7 +36709,7 @@
         <f>IF($N73="","",INDEX('반배정'!H$7:H$156,$N73))</f>
         <v/>
       </c>
-      <c r="H73" s="37">
+      <c r="H73" s="38">
         <f>IF($N73="","",INDEX('반배정'!I$7:I$156,$N73))</f>
         <v/>
       </c>
@@ -36748,7 +36767,7 @@
         <f>IF($N74="","",INDEX('반배정'!H$7:H$156,$N74))</f>
         <v/>
       </c>
-      <c r="H74" s="37">
+      <c r="H74" s="38">
         <f>IF($N74="","",INDEX('반배정'!I$7:I$156,$N74))</f>
         <v/>
       </c>
@@ -36806,7 +36825,7 @@
         <f>IF($N75="","",INDEX('반배정'!H$7:H$156,$N75))</f>
         <v/>
       </c>
-      <c r="H75" s="37">
+      <c r="H75" s="38">
         <f>IF($N75="","",INDEX('반배정'!I$7:I$156,$N75))</f>
         <v/>
       </c>
@@ -36864,7 +36883,7 @@
         <f>IF($N76="","",INDEX('반배정'!H$7:H$156,$N76))</f>
         <v/>
       </c>
-      <c r="H76" s="37">
+      <c r="H76" s="38">
         <f>IF($N76="","",INDEX('반배정'!I$7:I$156,$N76))</f>
         <v/>
       </c>
@@ -36922,7 +36941,7 @@
         <f>IF($N77="","",INDEX('반배정'!H$7:H$156,$N77))</f>
         <v/>
       </c>
-      <c r="H77" s="37">
+      <c r="H77" s="38">
         <f>IF($N77="","",INDEX('반배정'!I$7:I$156,$N77))</f>
         <v/>
       </c>
@@ -36980,7 +36999,7 @@
         <f>IF($N78="","",INDEX('반배정'!H$7:H$156,$N78))</f>
         <v/>
       </c>
-      <c r="H78" s="37">
+      <c r="H78" s="38">
         <f>IF($N78="","",INDEX('반배정'!I$7:I$156,$N78))</f>
         <v/>
       </c>
@@ -37038,7 +37057,7 @@
         <f>IF($N79="","",INDEX('반배정'!H$7:H$156,$N79))</f>
         <v/>
       </c>
-      <c r="H79" s="37">
+      <c r="H79" s="38">
         <f>IF($N79="","",INDEX('반배정'!I$7:I$156,$N79))</f>
         <v/>
       </c>
@@ -37096,7 +37115,7 @@
         <f>IF($N80="","",INDEX('반배정'!H$7:H$156,$N80))</f>
         <v/>
       </c>
-      <c r="H80" s="37">
+      <c r="H80" s="38">
         <f>IF($N80="","",INDEX('반배정'!I$7:I$156,$N80))</f>
         <v/>
       </c>
@@ -37154,7 +37173,7 @@
         <f>IF($N81="","",INDEX('반배정'!H$7:H$156,$N81))</f>
         <v/>
       </c>
-      <c r="H81" s="37">
+      <c r="H81" s="38">
         <f>IF($N81="","",INDEX('반배정'!I$7:I$156,$N81))</f>
         <v/>
       </c>
@@ -37212,7 +37231,7 @@
         <f>IF($N82="","",INDEX('반배정'!H$7:H$156,$N82))</f>
         <v/>
       </c>
-      <c r="H82" s="37">
+      <c r="H82" s="38">
         <f>IF($N82="","",INDEX('반배정'!I$7:I$156,$N82))</f>
         <v/>
       </c>
@@ -37270,7 +37289,7 @@
         <f>IF($N83="","",INDEX('반배정'!H$7:H$156,$N83))</f>
         <v/>
       </c>
-      <c r="H83" s="37">
+      <c r="H83" s="38">
         <f>IF($N83="","",INDEX('반배정'!I$7:I$156,$N83))</f>
         <v/>
       </c>
@@ -37328,7 +37347,7 @@
         <f>IF($N84="","",INDEX('반배정'!H$7:H$156,$N84))</f>
         <v/>
       </c>
-      <c r="H84" s="37">
+      <c r="H84" s="38">
         <f>IF($N84="","",INDEX('반배정'!I$7:I$156,$N84))</f>
         <v/>
       </c>
@@ -37386,7 +37405,7 @@
         <f>IF($N85="","",INDEX('반배정'!H$7:H$156,$N85))</f>
         <v/>
       </c>
-      <c r="H85" s="37">
+      <c r="H85" s="38">
         <f>IF($N85="","",INDEX('반배정'!I$7:I$156,$N85))</f>
         <v/>
       </c>
@@ -37444,7 +37463,7 @@
         <f>IF($N86="","",INDEX('반배정'!H$7:H$156,$N86))</f>
         <v/>
       </c>
-      <c r="H86" s="37">
+      <c r="H86" s="38">
         <f>IF($N86="","",INDEX('반배정'!I$7:I$156,$N86))</f>
         <v/>
       </c>
@@ -37502,7 +37521,7 @@
         <f>IF($N87="","",INDEX('반배정'!H$7:H$156,$N87))</f>
         <v/>
       </c>
-      <c r="H87" s="37">
+      <c r="H87" s="38">
         <f>IF($N87="","",INDEX('반배정'!I$7:I$156,$N87))</f>
         <v/>
       </c>
@@ -37560,7 +37579,7 @@
         <f>IF($N88="","",INDEX('반배정'!H$7:H$156,$N88))</f>
         <v/>
       </c>
-      <c r="H88" s="37">
+      <c r="H88" s="38">
         <f>IF($N88="","",INDEX('반배정'!I$7:I$156,$N88))</f>
         <v/>
       </c>
@@ -37618,7 +37637,7 @@
         <f>IF($N89="","",INDEX('반배정'!H$7:H$156,$N89))</f>
         <v/>
       </c>
-      <c r="H89" s="37">
+      <c r="H89" s="38">
         <f>IF($N89="","",INDEX('반배정'!I$7:I$156,$N89))</f>
         <v/>
       </c>
@@ -37676,7 +37695,7 @@
         <f>IF($N90="","",INDEX('반배정'!H$7:H$156,$N90))</f>
         <v/>
       </c>
-      <c r="H90" s="37">
+      <c r="H90" s="38">
         <f>IF($N90="","",INDEX('반배정'!I$7:I$156,$N90))</f>
         <v/>
       </c>
@@ -37734,7 +37753,7 @@
         <f>IF($N91="","",INDEX('반배정'!H$7:H$156,$N91))</f>
         <v/>
       </c>
-      <c r="H91" s="37">
+      <c r="H91" s="38">
         <f>IF($N91="","",INDEX('반배정'!I$7:I$156,$N91))</f>
         <v/>
       </c>
@@ -37792,7 +37811,7 @@
         <f>IF($N92="","",INDEX('반배정'!H$7:H$156,$N92))</f>
         <v/>
       </c>
-      <c r="H92" s="37">
+      <c r="H92" s="38">
         <f>IF($N92="","",INDEX('반배정'!I$7:I$156,$N92))</f>
         <v/>
       </c>
@@ -37850,7 +37869,7 @@
         <f>IF($N93="","",INDEX('반배정'!H$7:H$156,$N93))</f>
         <v/>
       </c>
-      <c r="H93" s="37">
+      <c r="H93" s="38">
         <f>IF($N93="","",INDEX('반배정'!I$7:I$156,$N93))</f>
         <v/>
       </c>
@@ -37908,7 +37927,7 @@
         <f>IF($N94="","",INDEX('반배정'!H$7:H$156,$N94))</f>
         <v/>
       </c>
-      <c r="H94" s="37">
+      <c r="H94" s="38">
         <f>IF($N94="","",INDEX('반배정'!I$7:I$156,$N94))</f>
         <v/>
       </c>
@@ -37966,7 +37985,7 @@
         <f>IF($N95="","",INDEX('반배정'!H$7:H$156,$N95))</f>
         <v/>
       </c>
-      <c r="H95" s="37">
+      <c r="H95" s="38">
         <f>IF($N95="","",INDEX('반배정'!I$7:I$156,$N95))</f>
         <v/>
       </c>
@@ -38024,7 +38043,7 @@
         <f>IF($N96="","",INDEX('반배정'!H$7:H$156,$N96))</f>
         <v/>
       </c>
-      <c r="H96" s="37">
+      <c r="H96" s="38">
         <f>IF($N96="","",INDEX('반배정'!I$7:I$156,$N96))</f>
         <v/>
       </c>
@@ -38082,7 +38101,7 @@
         <f>IF($N97="","",INDEX('반배정'!H$7:H$156,$N97))</f>
         <v/>
       </c>
-      <c r="H97" s="37">
+      <c r="H97" s="38">
         <f>IF($N97="","",INDEX('반배정'!I$7:I$156,$N97))</f>
         <v/>
       </c>
@@ -38140,7 +38159,7 @@
         <f>IF($N98="","",INDEX('반배정'!H$7:H$156,$N98))</f>
         <v/>
       </c>
-      <c r="H98" s="37">
+      <c r="H98" s="38">
         <f>IF($N98="","",INDEX('반배정'!I$7:I$156,$N98))</f>
         <v/>
       </c>
@@ -38198,7 +38217,7 @@
         <f>IF($N99="","",INDEX('반배정'!H$7:H$156,$N99))</f>
         <v/>
       </c>
-      <c r="H99" s="37">
+      <c r="H99" s="38">
         <f>IF($N99="","",INDEX('반배정'!I$7:I$156,$N99))</f>
         <v/>
       </c>
@@ -38256,7 +38275,7 @@
         <f>IF($N100="","",INDEX('반배정'!H$7:H$156,$N100))</f>
         <v/>
       </c>
-      <c r="H100" s="37">
+      <c r="H100" s="38">
         <f>IF($N100="","",INDEX('반배정'!I$7:I$156,$N100))</f>
         <v/>
       </c>
@@ -38314,7 +38333,7 @@
         <f>IF($N101="","",INDEX('반배정'!H$7:H$156,$N101))</f>
         <v/>
       </c>
-      <c r="H101" s="37">
+      <c r="H101" s="38">
         <f>IF($N101="","",INDEX('반배정'!I$7:I$156,$N101))</f>
         <v/>
       </c>
@@ -38372,7 +38391,7 @@
         <f>IF($N102="","",INDEX('반배정'!H$7:H$156,$N102))</f>
         <v/>
       </c>
-      <c r="H102" s="37">
+      <c r="H102" s="38">
         <f>IF($N102="","",INDEX('반배정'!I$7:I$156,$N102))</f>
         <v/>
       </c>
@@ -38430,7 +38449,7 @@
         <f>IF($N103="","",INDEX('반배정'!H$7:H$156,$N103))</f>
         <v/>
       </c>
-      <c r="H103" s="37">
+      <c r="H103" s="38">
         <f>IF($N103="","",INDEX('반배정'!I$7:I$156,$N103))</f>
         <v/>
       </c>
@@ -38488,7 +38507,7 @@
         <f>IF($N104="","",INDEX('반배정'!H$7:H$156,$N104))</f>
         <v/>
       </c>
-      <c r="H104" s="37">
+      <c r="H104" s="38">
         <f>IF($N104="","",INDEX('반배정'!I$7:I$156,$N104))</f>
         <v/>
       </c>
@@ -38546,7 +38565,7 @@
         <f>IF($N105="","",INDEX('반배정'!H$7:H$156,$N105))</f>
         <v/>
       </c>
-      <c r="H105" s="37">
+      <c r="H105" s="38">
         <f>IF($N105="","",INDEX('반배정'!I$7:I$156,$N105))</f>
         <v/>
       </c>
@@ -38604,7 +38623,7 @@
         <f>IF($N106="","",INDEX('반배정'!H$7:H$156,$N106))</f>
         <v/>
       </c>
-      <c r="H106" s="37">
+      <c r="H106" s="38">
         <f>IF($N106="","",INDEX('반배정'!I$7:I$156,$N106))</f>
         <v/>
       </c>
@@ -38662,7 +38681,7 @@
         <f>IF($N107="","",INDEX('반배정'!H$7:H$156,$N107))</f>
         <v/>
       </c>
-      <c r="H107" s="37">
+      <c r="H107" s="38">
         <f>IF($N107="","",INDEX('반배정'!I$7:I$156,$N107))</f>
         <v/>
       </c>
@@ -38720,7 +38739,7 @@
         <f>IF($N108="","",INDEX('반배정'!H$7:H$156,$N108))</f>
         <v/>
       </c>
-      <c r="H108" s="37">
+      <c r="H108" s="38">
         <f>IF($N108="","",INDEX('반배정'!I$7:I$156,$N108))</f>
         <v/>
       </c>
@@ -38778,7 +38797,7 @@
         <f>IF($N109="","",INDEX('반배정'!H$7:H$156,$N109))</f>
         <v/>
       </c>
-      <c r="H109" s="37">
+      <c r="H109" s="38">
         <f>IF($N109="","",INDEX('반배정'!I$7:I$156,$N109))</f>
         <v/>
       </c>
@@ -38836,7 +38855,7 @@
         <f>IF($N110="","",INDEX('반배정'!H$7:H$156,$N110))</f>
         <v/>
       </c>
-      <c r="H110" s="37">
+      <c r="H110" s="38">
         <f>IF($N110="","",INDEX('반배정'!I$7:I$156,$N110))</f>
         <v/>
       </c>
@@ -38894,7 +38913,7 @@
         <f>IF($N111="","",INDEX('반배정'!H$7:H$156,$N111))</f>
         <v/>
       </c>
-      <c r="H111" s="37">
+      <c r="H111" s="38">
         <f>IF($N111="","",INDEX('반배정'!I$7:I$156,$N111))</f>
         <v/>
       </c>
@@ -38952,7 +38971,7 @@
         <f>IF($N112="","",INDEX('반배정'!H$7:H$156,$N112))</f>
         <v/>
       </c>
-      <c r="H112" s="37">
+      <c r="H112" s="38">
         <f>IF($N112="","",INDEX('반배정'!I$7:I$156,$N112))</f>
         <v/>
       </c>
@@ -39010,7 +39029,7 @@
         <f>IF($N113="","",INDEX('반배정'!H$7:H$156,$N113))</f>
         <v/>
       </c>
-      <c r="H113" s="37">
+      <c r="H113" s="38">
         <f>IF($N113="","",INDEX('반배정'!I$7:I$156,$N113))</f>
         <v/>
       </c>
@@ -39068,7 +39087,7 @@
         <f>IF($N114="","",INDEX('반배정'!H$7:H$156,$N114))</f>
         <v/>
       </c>
-      <c r="H114" s="37">
+      <c r="H114" s="38">
         <f>IF($N114="","",INDEX('반배정'!I$7:I$156,$N114))</f>
         <v/>
       </c>
@@ -39126,7 +39145,7 @@
         <f>IF($N115="","",INDEX('반배정'!H$7:H$156,$N115))</f>
         <v/>
       </c>
-      <c r="H115" s="37">
+      <c r="H115" s="38">
         <f>IF($N115="","",INDEX('반배정'!I$7:I$156,$N115))</f>
         <v/>
       </c>
@@ -39184,7 +39203,7 @@
         <f>IF($N116="","",INDEX('반배정'!H$7:H$156,$N116))</f>
         <v/>
       </c>
-      <c r="H116" s="37">
+      <c r="H116" s="38">
         <f>IF($N116="","",INDEX('반배정'!I$7:I$156,$N116))</f>
         <v/>
       </c>
@@ -39242,7 +39261,7 @@
         <f>IF($N117="","",INDEX('반배정'!H$7:H$156,$N117))</f>
         <v/>
       </c>
-      <c r="H117" s="37">
+      <c r="H117" s="38">
         <f>IF($N117="","",INDEX('반배정'!I$7:I$156,$N117))</f>
         <v/>
       </c>
@@ -39300,7 +39319,7 @@
         <f>IF($N118="","",INDEX('반배정'!H$7:H$156,$N118))</f>
         <v/>
       </c>
-      <c r="H118" s="37">
+      <c r="H118" s="38">
         <f>IF($N118="","",INDEX('반배정'!I$7:I$156,$N118))</f>
         <v/>
       </c>
@@ -39358,7 +39377,7 @@
         <f>IF($N119="","",INDEX('반배정'!H$7:H$156,$N119))</f>
         <v/>
       </c>
-      <c r="H119" s="37">
+      <c r="H119" s="38">
         <f>IF($N119="","",INDEX('반배정'!I$7:I$156,$N119))</f>
         <v/>
       </c>
@@ -39416,7 +39435,7 @@
         <f>IF($N120="","",INDEX('반배정'!H$7:H$156,$N120))</f>
         <v/>
       </c>
-      <c r="H120" s="37">
+      <c r="H120" s="38">
         <f>IF($N120="","",INDEX('반배정'!I$7:I$156,$N120))</f>
         <v/>
       </c>
@@ -39474,7 +39493,7 @@
         <f>IF($N121="","",INDEX('반배정'!H$7:H$156,$N121))</f>
         <v/>
       </c>
-      <c r="H121" s="37">
+      <c r="H121" s="38">
         <f>IF($N121="","",INDEX('반배정'!I$7:I$156,$N121))</f>
         <v/>
       </c>
@@ -39532,7 +39551,7 @@
         <f>IF($N122="","",INDEX('반배정'!H$7:H$156,$N122))</f>
         <v/>
       </c>
-      <c r="H122" s="37">
+      <c r="H122" s="38">
         <f>IF($N122="","",INDEX('반배정'!I$7:I$156,$N122))</f>
         <v/>
       </c>
@@ -39590,7 +39609,7 @@
         <f>IF($N123="","",INDEX('반배정'!H$7:H$156,$N123))</f>
         <v/>
       </c>
-      <c r="H123" s="37">
+      <c r="H123" s="38">
         <f>IF($N123="","",INDEX('반배정'!I$7:I$156,$N123))</f>
         <v/>
       </c>
@@ -39648,7 +39667,7 @@
         <f>IF($N124="","",INDEX('반배정'!H$7:H$156,$N124))</f>
         <v/>
       </c>
-      <c r="H124" s="37">
+      <c r="H124" s="38">
         <f>IF($N124="","",INDEX('반배정'!I$7:I$156,$N124))</f>
         <v/>
       </c>
@@ -39706,7 +39725,7 @@
         <f>IF($N125="","",INDEX('반배정'!H$7:H$156,$N125))</f>
         <v/>
       </c>
-      <c r="H125" s="37">
+      <c r="H125" s="38">
         <f>IF($N125="","",INDEX('반배정'!I$7:I$156,$N125))</f>
         <v/>
       </c>
@@ -39764,7 +39783,7 @@
         <f>IF($N126="","",INDEX('반배정'!H$7:H$156,$N126))</f>
         <v/>
       </c>
-      <c r="H126" s="37">
+      <c r="H126" s="38">
         <f>IF($N126="","",INDEX('반배정'!I$7:I$156,$N126))</f>
         <v/>
       </c>
@@ -39822,7 +39841,7 @@
         <f>IF($N127="","",INDEX('반배정'!H$7:H$156,$N127))</f>
         <v/>
       </c>
-      <c r="H127" s="37">
+      <c r="H127" s="38">
         <f>IF($N127="","",INDEX('반배정'!I$7:I$156,$N127))</f>
         <v/>
       </c>
@@ -39880,7 +39899,7 @@
         <f>IF($N128="","",INDEX('반배정'!H$7:H$156,$N128))</f>
         <v/>
       </c>
-      <c r="H128" s="37">
+      <c r="H128" s="38">
         <f>IF($N128="","",INDEX('반배정'!I$7:I$156,$N128))</f>
         <v/>
       </c>
@@ -39938,7 +39957,7 @@
         <f>IF($N129="","",INDEX('반배정'!H$7:H$156,$N129))</f>
         <v/>
       </c>
-      <c r="H129" s="37">
+      <c r="H129" s="38">
         <f>IF($N129="","",INDEX('반배정'!I$7:I$156,$N129))</f>
         <v/>
       </c>
@@ -39996,7 +40015,7 @@
         <f>IF($N130="","",INDEX('반배정'!H$7:H$156,$N130))</f>
         <v/>
       </c>
-      <c r="H130" s="37">
+      <c r="H130" s="38">
         <f>IF($N130="","",INDEX('반배정'!I$7:I$156,$N130))</f>
         <v/>
       </c>
@@ -40054,7 +40073,7 @@
         <f>IF($N131="","",INDEX('반배정'!H$7:H$156,$N131))</f>
         <v/>
       </c>
-      <c r="H131" s="37">
+      <c r="H131" s="38">
         <f>IF($N131="","",INDEX('반배정'!I$7:I$156,$N131))</f>
         <v/>
       </c>
@@ -40112,7 +40131,7 @@
         <f>IF($N132="","",INDEX('반배정'!H$7:H$156,$N132))</f>
         <v/>
       </c>
-      <c r="H132" s="37">
+      <c r="H132" s="38">
         <f>IF($N132="","",INDEX('반배정'!I$7:I$156,$N132))</f>
         <v/>
       </c>
@@ -40170,7 +40189,7 @@
         <f>IF($N133="","",INDEX('반배정'!H$7:H$156,$N133))</f>
         <v/>
       </c>
-      <c r="H133" s="37">
+      <c r="H133" s="38">
         <f>IF($N133="","",INDEX('반배정'!I$7:I$156,$N133))</f>
         <v/>
       </c>
@@ -40228,7 +40247,7 @@
         <f>IF($N134="","",INDEX('반배정'!H$7:H$156,$N134))</f>
         <v/>
       </c>
-      <c r="H134" s="37">
+      <c r="H134" s="38">
         <f>IF($N134="","",INDEX('반배정'!I$7:I$156,$N134))</f>
         <v/>
       </c>
@@ -40286,7 +40305,7 @@
         <f>IF($N135="","",INDEX('반배정'!H$7:H$156,$N135))</f>
         <v/>
       </c>
-      <c r="H135" s="37">
+      <c r="H135" s="38">
         <f>IF($N135="","",INDEX('반배정'!I$7:I$156,$N135))</f>
         <v/>
       </c>
@@ -40344,7 +40363,7 @@
         <f>IF($N136="","",INDEX('반배정'!H$7:H$156,$N136))</f>
         <v/>
       </c>
-      <c r="H136" s="37">
+      <c r="H136" s="38">
         <f>IF($N136="","",INDEX('반배정'!I$7:I$156,$N136))</f>
         <v/>
       </c>
@@ -40402,7 +40421,7 @@
         <f>IF($N137="","",INDEX('반배정'!H$7:H$156,$N137))</f>
         <v/>
       </c>
-      <c r="H137" s="37">
+      <c r="H137" s="38">
         <f>IF($N137="","",INDEX('반배정'!I$7:I$156,$N137))</f>
         <v/>
       </c>
@@ -40460,7 +40479,7 @@
         <f>IF($N138="","",INDEX('반배정'!H$7:H$156,$N138))</f>
         <v/>
       </c>
-      <c r="H138" s="37">
+      <c r="H138" s="38">
         <f>IF($N138="","",INDEX('반배정'!I$7:I$156,$N138))</f>
         <v/>
       </c>
@@ -40518,7 +40537,7 @@
         <f>IF($N139="","",INDEX('반배정'!H$7:H$156,$N139))</f>
         <v/>
       </c>
-      <c r="H139" s="37">
+      <c r="H139" s="38">
         <f>IF($N139="","",INDEX('반배정'!I$7:I$156,$N139))</f>
         <v/>
       </c>
@@ -40576,7 +40595,7 @@
         <f>IF($N140="","",INDEX('반배정'!H$7:H$156,$N140))</f>
         <v/>
       </c>
-      <c r="H140" s="37">
+      <c r="H140" s="38">
         <f>IF($N140="","",INDEX('반배정'!I$7:I$156,$N140))</f>
         <v/>
       </c>
@@ -40634,7 +40653,7 @@
         <f>IF($N141="","",INDEX('반배정'!H$7:H$156,$N141))</f>
         <v/>
       </c>
-      <c r="H141" s="37">
+      <c r="H141" s="38">
         <f>IF($N141="","",INDEX('반배정'!I$7:I$156,$N141))</f>
         <v/>
       </c>
@@ -40692,7 +40711,7 @@
         <f>IF($N142="","",INDEX('반배정'!H$7:H$156,$N142))</f>
         <v/>
       </c>
-      <c r="H142" s="37">
+      <c r="H142" s="38">
         <f>IF($N142="","",INDEX('반배정'!I$7:I$156,$N142))</f>
         <v/>
       </c>
@@ -40750,7 +40769,7 @@
         <f>IF($N143="","",INDEX('반배정'!H$7:H$156,$N143))</f>
         <v/>
       </c>
-      <c r="H143" s="37">
+      <c r="H143" s="38">
         <f>IF($N143="","",INDEX('반배정'!I$7:I$156,$N143))</f>
         <v/>
       </c>
@@ -40808,7 +40827,7 @@
         <f>IF($N144="","",INDEX('반배정'!H$7:H$156,$N144))</f>
         <v/>
       </c>
-      <c r="H144" s="37">
+      <c r="H144" s="38">
         <f>IF($N144="","",INDEX('반배정'!I$7:I$156,$N144))</f>
         <v/>
       </c>
@@ -40866,7 +40885,7 @@
         <f>IF($N145="","",INDEX('반배정'!H$7:H$156,$N145))</f>
         <v/>
       </c>
-      <c r="H145" s="37">
+      <c r="H145" s="38">
         <f>IF($N145="","",INDEX('반배정'!I$7:I$156,$N145))</f>
         <v/>
       </c>
@@ -40924,7 +40943,7 @@
         <f>IF($N146="","",INDEX('반배정'!H$7:H$156,$N146))</f>
         <v/>
       </c>
-      <c r="H146" s="37">
+      <c r="H146" s="38">
         <f>IF($N146="","",INDEX('반배정'!I$7:I$156,$N146))</f>
         <v/>
       </c>
@@ -40982,7 +41001,7 @@
         <f>IF($N147="","",INDEX('반배정'!H$7:H$156,$N147))</f>
         <v/>
       </c>
-      <c r="H147" s="37">
+      <c r="H147" s="38">
         <f>IF($N147="","",INDEX('반배정'!I$7:I$156,$N147))</f>
         <v/>
       </c>
@@ -41040,7 +41059,7 @@
         <f>IF($N148="","",INDEX('반배정'!H$7:H$156,$N148))</f>
         <v/>
       </c>
-      <c r="H148" s="37">
+      <c r="H148" s="38">
         <f>IF($N148="","",INDEX('반배정'!I$7:I$156,$N148))</f>
         <v/>
       </c>
@@ -41098,7 +41117,7 @@
         <f>IF($N149="","",INDEX('반배정'!H$7:H$156,$N149))</f>
         <v/>
       </c>
-      <c r="H149" s="37">
+      <c r="H149" s="38">
         <f>IF($N149="","",INDEX('반배정'!I$7:I$156,$N149))</f>
         <v/>
       </c>
@@ -41156,7 +41175,7 @@
         <f>IF($N150="","",INDEX('반배정'!H$7:H$156,$N150))</f>
         <v/>
       </c>
-      <c r="H150" s="37">
+      <c r="H150" s="38">
         <f>IF($N150="","",INDEX('반배정'!I$7:I$156,$N150))</f>
         <v/>
       </c>
@@ -41214,7 +41233,7 @@
         <f>IF($N151="","",INDEX('반배정'!H$7:H$156,$N151))</f>
         <v/>
       </c>
-      <c r="H151" s="37">
+      <c r="H151" s="38">
         <f>IF($N151="","",INDEX('반배정'!I$7:I$156,$N151))</f>
         <v/>
       </c>
@@ -41272,7 +41291,7 @@
         <f>IF($N152="","",INDEX('반배정'!H$7:H$156,$N152))</f>
         <v/>
       </c>
-      <c r="H152" s="37">
+      <c r="H152" s="38">
         <f>IF($N152="","",INDEX('반배정'!I$7:I$156,$N152))</f>
         <v/>
       </c>
@@ -41330,7 +41349,7 @@
         <f>IF($N153="","",INDEX('반배정'!H$7:H$156,$N153))</f>
         <v/>
       </c>
-      <c r="H153" s="37">
+      <c r="H153" s="38">
         <f>IF($N153="","",INDEX('반배정'!I$7:I$156,$N153))</f>
         <v/>
       </c>
@@ -41388,7 +41407,7 @@
         <f>IF($N154="","",INDEX('반배정'!H$7:H$156,$N154))</f>
         <v/>
       </c>
-      <c r="H154" s="37">
+      <c r="H154" s="38">
         <f>IF($N154="","",INDEX('반배정'!I$7:I$156,$N154))</f>
         <v/>
       </c>
@@ -41446,7 +41465,7 @@
         <f>IF($N155="","",INDEX('반배정'!H$7:H$156,$N155))</f>
         <v/>
       </c>
-      <c r="H155" s="37">
+      <c r="H155" s="38">
         <f>IF($N155="","",INDEX('반배정'!I$7:I$156,$N155))</f>
         <v/>
       </c>
@@ -41504,7 +41523,7 @@
         <f>IF($N156="","",INDEX('반배정'!H$7:H$156,$N156))</f>
         <v/>
       </c>
-      <c r="H156" s="37">
+      <c r="H156" s="38">
         <f>IF($N156="","",INDEX('반배정'!I$7:I$156,$N156))</f>
         <v/>
       </c>
@@ -41602,7 +41621,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>공통수학1</t>
         </is>
@@ -41711,7 +41730,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C6" s="39">
+      <c r="C6" s="40">
         <f>'공수1'!D4</f>
         <v/>
       </c>
@@ -41723,7 +41742,7 @@
         <f>'공수1'!D3</f>
         <v/>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="41">
         <f>IF('공수1'!$D$2="","",'공수1'!$D$2)</f>
         <v/>
       </c>
@@ -41735,47 +41754,47 @@
         <f>IF(F6="","",SUMPRODUCT(('공수1'!$D$7:$D$156='공수1'!$D$2)*('공수1'!$D$7:$D$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I6" s="41">
+      <c r="I6" s="42">
         <f>IF(OR(F6="",G6=0),"",H6/G6)</f>
         <v/>
       </c>
-      <c r="J6" s="42">
+      <c r="J6" s="43">
         <f>IF(F6="","",IFERROR(SUMPRODUCT(('공수1'!$D$7:$D$156='공수1'!$D$2)*('공수1'!$D$7:$D$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K6" s="42">
+      <c r="K6" s="43">
         <f>IF(F6="","",IFERROR(SUMPRODUCT(('공수1'!$D$7:$D$156='공수1'!$D$2)*('공수1'!$D$7:$D$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L6" s="42">
+      <c r="L6" s="43">
         <f>IF(F6="","",IFERROR(SUMPRODUCT(('공수1'!$D$7:$D$156='공수1'!$D$2)*('공수1'!$D$7:$D$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M6" s="43">
+      <c r="M6" s="44">
         <f>IF(OR(J6="",K6=""),"",J6-K6)</f>
         <v/>
       </c>
-      <c r="N6" s="39">
+      <c r="N6" s="40">
         <f>IF(I6="","",IF(AND(M6&lt;&gt;"",M6&lt;0),"역변별·문항검토",IF(I6&gt;=0.9,"매우 쉬움",IF(I6&lt;=0.15,"매우 어려움",IF(AND(M6&lt;&gt;"",M6&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O6" s="39">
+      <c r="O6" s="40">
         <f>IF(G6=0,"",COUNTIF('공수1'!$D$7:$D$156,1))</f>
         <v/>
       </c>
-      <c r="P6" s="39">
+      <c r="P6" s="40">
         <f>IF(G6=0,"",COUNTIF('공수1'!$D$7:$D$156,2))</f>
         <v/>
       </c>
-      <c r="Q6" s="39">
+      <c r="Q6" s="40">
         <f>IF(G6=0,"",COUNTIF('공수1'!$D$7:$D$156,3))</f>
         <v/>
       </c>
-      <c r="R6" s="39">
+      <c r="R6" s="40">
         <f>IF(G6=0,"",COUNTIF('공수1'!$D$7:$D$156,4))</f>
         <v/>
       </c>
-      <c r="S6" s="39">
+      <c r="S6" s="40">
         <f>IF(G6=0,"",COUNTIF('공수1'!$D$7:$D$156,5))</f>
         <v/>
       </c>
@@ -41789,7 +41808,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="40">
         <f>'공수1'!E4</f>
         <v/>
       </c>
@@ -41801,7 +41820,7 @@
         <f>'공수1'!E3</f>
         <v/>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="41">
         <f>IF('공수1'!$E$2="","",'공수1'!$E$2)</f>
         <v/>
       </c>
@@ -41813,47 +41832,47 @@
         <f>IF(F7="","",SUMPRODUCT(('공수1'!$E$7:$E$156='공수1'!$E$2)*('공수1'!$E$7:$E$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I7" s="41">
+      <c r="I7" s="42">
         <f>IF(OR(F7="",G7=0),"",H7/G7)</f>
         <v/>
       </c>
-      <c r="J7" s="42">
+      <c r="J7" s="43">
         <f>IF(F7="","",IFERROR(SUMPRODUCT(('공수1'!$E$7:$E$156='공수1'!$E$2)*('공수1'!$E$7:$E$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K7" s="42">
+      <c r="K7" s="43">
         <f>IF(F7="","",IFERROR(SUMPRODUCT(('공수1'!$E$7:$E$156='공수1'!$E$2)*('공수1'!$E$7:$E$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L7" s="42">
+      <c r="L7" s="43">
         <f>IF(F7="","",IFERROR(SUMPRODUCT(('공수1'!$E$7:$E$156='공수1'!$E$2)*('공수1'!$E$7:$E$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M7" s="43">
+      <c r="M7" s="44">
         <f>IF(OR(J7="",K7=""),"",J7-K7)</f>
         <v/>
       </c>
-      <c r="N7" s="39">
+      <c r="N7" s="40">
         <f>IF(I7="","",IF(AND(M7&lt;&gt;"",M7&lt;0),"역변별·문항검토",IF(I7&gt;=0.9,"매우 쉬움",IF(I7&lt;=0.15,"매우 어려움",IF(AND(M7&lt;&gt;"",M7&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O7" s="39">
+      <c r="O7" s="40">
         <f>IF(G7=0,"",COUNTIF('공수1'!$E$7:$E$156,1))</f>
         <v/>
       </c>
-      <c r="P7" s="39">
+      <c r="P7" s="40">
         <f>IF(G7=0,"",COUNTIF('공수1'!$E$7:$E$156,2))</f>
         <v/>
       </c>
-      <c r="Q7" s="39">
+      <c r="Q7" s="40">
         <f>IF(G7=0,"",COUNTIF('공수1'!$E$7:$E$156,3))</f>
         <v/>
       </c>
-      <c r="R7" s="39">
+      <c r="R7" s="40">
         <f>IF(G7=0,"",COUNTIF('공수1'!$E$7:$E$156,4))</f>
         <v/>
       </c>
-      <c r="S7" s="39">
+      <c r="S7" s="40">
         <f>IF(G7=0,"",COUNTIF('공수1'!$E$7:$E$156,5))</f>
         <v/>
       </c>
@@ -41867,7 +41886,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C8" s="39">
+      <c r="C8" s="40">
         <f>'공수1'!F4</f>
         <v/>
       </c>
@@ -41879,7 +41898,7 @@
         <f>'공수1'!F3</f>
         <v/>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="41">
         <f>IF('공수1'!$F$2="","",'공수1'!$F$2)</f>
         <v/>
       </c>
@@ -41891,47 +41910,47 @@
         <f>IF(F8="","",SUMPRODUCT(('공수1'!$F$7:$F$156='공수1'!$F$2)*('공수1'!$F$7:$F$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="42">
         <f>IF(OR(F8="",G8=0),"",H8/G8)</f>
         <v/>
       </c>
-      <c r="J8" s="42">
+      <c r="J8" s="43">
         <f>IF(F8="","",IFERROR(SUMPRODUCT(('공수1'!$F$7:$F$156='공수1'!$F$2)*('공수1'!$F$7:$F$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K8" s="42">
+      <c r="K8" s="43">
         <f>IF(F8="","",IFERROR(SUMPRODUCT(('공수1'!$F$7:$F$156='공수1'!$F$2)*('공수1'!$F$7:$F$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L8" s="42">
+      <c r="L8" s="43">
         <f>IF(F8="","",IFERROR(SUMPRODUCT(('공수1'!$F$7:$F$156='공수1'!$F$2)*('공수1'!$F$7:$F$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M8" s="43">
+      <c r="M8" s="44">
         <f>IF(OR(J8="",K8=""),"",J8-K8)</f>
         <v/>
       </c>
-      <c r="N8" s="39">
+      <c r="N8" s="40">
         <f>IF(I8="","",IF(AND(M8&lt;&gt;"",M8&lt;0),"역변별·문항검토",IF(I8&gt;=0.9,"매우 쉬움",IF(I8&lt;=0.15,"매우 어려움",IF(AND(M8&lt;&gt;"",M8&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O8" s="39">
+      <c r="O8" s="40">
         <f>IF(G8=0,"",COUNTIF('공수1'!$F$7:$F$156,1))</f>
         <v/>
       </c>
-      <c r="P8" s="39">
+      <c r="P8" s="40">
         <f>IF(G8=0,"",COUNTIF('공수1'!$F$7:$F$156,2))</f>
         <v/>
       </c>
-      <c r="Q8" s="39">
+      <c r="Q8" s="40">
         <f>IF(G8=0,"",COUNTIF('공수1'!$F$7:$F$156,3))</f>
         <v/>
       </c>
-      <c r="R8" s="39">
+      <c r="R8" s="40">
         <f>IF(G8=0,"",COUNTIF('공수1'!$F$7:$F$156,4))</f>
         <v/>
       </c>
-      <c r="S8" s="39">
+      <c r="S8" s="40">
         <f>IF(G8=0,"",COUNTIF('공수1'!$F$7:$F$156,5))</f>
         <v/>
       </c>
@@ -41945,7 +41964,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="40">
         <f>'공수1'!G4</f>
         <v/>
       </c>
@@ -41957,7 +41976,7 @@
         <f>'공수1'!G3</f>
         <v/>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="41">
         <f>IF('공수1'!$G$2="","",'공수1'!$G$2)</f>
         <v/>
       </c>
@@ -41969,47 +41988,47 @@
         <f>IF(F9="","",SUMPRODUCT(('공수1'!$G$7:$G$156='공수1'!$G$2)*('공수1'!$G$7:$G$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="42">
         <f>IF(OR(F9="",G9=0),"",H9/G9)</f>
         <v/>
       </c>
-      <c r="J9" s="42">
+      <c r="J9" s="43">
         <f>IF(F9="","",IFERROR(SUMPRODUCT(('공수1'!$G$7:$G$156='공수1'!$G$2)*('공수1'!$G$7:$G$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K9" s="42">
+      <c r="K9" s="43">
         <f>IF(F9="","",IFERROR(SUMPRODUCT(('공수1'!$G$7:$G$156='공수1'!$G$2)*('공수1'!$G$7:$G$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L9" s="42">
+      <c r="L9" s="43">
         <f>IF(F9="","",IFERROR(SUMPRODUCT(('공수1'!$G$7:$G$156='공수1'!$G$2)*('공수1'!$G$7:$G$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M9" s="43">
+      <c r="M9" s="44">
         <f>IF(OR(J9="",K9=""),"",J9-K9)</f>
         <v/>
       </c>
-      <c r="N9" s="39">
+      <c r="N9" s="40">
         <f>IF(I9="","",IF(AND(M9&lt;&gt;"",M9&lt;0),"역변별·문항검토",IF(I9&gt;=0.9,"매우 쉬움",IF(I9&lt;=0.15,"매우 어려움",IF(AND(M9&lt;&gt;"",M9&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O9" s="39">
+      <c r="O9" s="40">
         <f>IF(G9=0,"",COUNTIF('공수1'!$G$7:$G$156,1))</f>
         <v/>
       </c>
-      <c r="P9" s="39">
+      <c r="P9" s="40">
         <f>IF(G9=0,"",COUNTIF('공수1'!$G$7:$G$156,2))</f>
         <v/>
       </c>
-      <c r="Q9" s="39">
+      <c r="Q9" s="40">
         <f>IF(G9=0,"",COUNTIF('공수1'!$G$7:$G$156,3))</f>
         <v/>
       </c>
-      <c r="R9" s="39">
+      <c r="R9" s="40">
         <f>IF(G9=0,"",COUNTIF('공수1'!$G$7:$G$156,4))</f>
         <v/>
       </c>
-      <c r="S9" s="39">
+      <c r="S9" s="40">
         <f>IF(G9=0,"",COUNTIF('공수1'!$G$7:$G$156,5))</f>
         <v/>
       </c>
@@ -42023,7 +42042,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="40">
         <f>'공수1'!H4</f>
         <v/>
       </c>
@@ -42035,7 +42054,7 @@
         <f>'공수1'!H3</f>
         <v/>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="41">
         <f>IF('공수1'!$H$2="","",'공수1'!$H$2)</f>
         <v/>
       </c>
@@ -42047,47 +42066,47 @@
         <f>IF(F10="","",SUMPRODUCT(('공수1'!$H$7:$H$156='공수1'!$H$2)*('공수1'!$H$7:$H$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I10" s="41">
+      <c r="I10" s="42">
         <f>IF(OR(F10="",G10=0),"",H10/G10)</f>
         <v/>
       </c>
-      <c r="J10" s="42">
+      <c r="J10" s="43">
         <f>IF(F10="","",IFERROR(SUMPRODUCT(('공수1'!$H$7:$H$156='공수1'!$H$2)*('공수1'!$H$7:$H$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K10" s="42">
+      <c r="K10" s="43">
         <f>IF(F10="","",IFERROR(SUMPRODUCT(('공수1'!$H$7:$H$156='공수1'!$H$2)*('공수1'!$H$7:$H$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L10" s="42">
+      <c r="L10" s="43">
         <f>IF(F10="","",IFERROR(SUMPRODUCT(('공수1'!$H$7:$H$156='공수1'!$H$2)*('공수1'!$H$7:$H$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M10" s="43">
+      <c r="M10" s="44">
         <f>IF(OR(J10="",K10=""),"",J10-K10)</f>
         <v/>
       </c>
-      <c r="N10" s="39">
+      <c r="N10" s="40">
         <f>IF(I10="","",IF(AND(M10&lt;&gt;"",M10&lt;0),"역변별·문항검토",IF(I10&gt;=0.9,"매우 쉬움",IF(I10&lt;=0.15,"매우 어려움",IF(AND(M10&lt;&gt;"",M10&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O10" s="39">
+      <c r="O10" s="40">
         <f>IF(G10=0,"",COUNTIF('공수1'!$H$7:$H$156,1))</f>
         <v/>
       </c>
-      <c r="P10" s="39">
+      <c r="P10" s="40">
         <f>IF(G10=0,"",COUNTIF('공수1'!$H$7:$H$156,2))</f>
         <v/>
       </c>
-      <c r="Q10" s="39">
+      <c r="Q10" s="40">
         <f>IF(G10=0,"",COUNTIF('공수1'!$H$7:$H$156,3))</f>
         <v/>
       </c>
-      <c r="R10" s="39">
+      <c r="R10" s="40">
         <f>IF(G10=0,"",COUNTIF('공수1'!$H$7:$H$156,4))</f>
         <v/>
       </c>
-      <c r="S10" s="39">
+      <c r="S10" s="40">
         <f>IF(G10=0,"",COUNTIF('공수1'!$H$7:$H$156,5))</f>
         <v/>
       </c>
@@ -42101,7 +42120,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="40">
         <f>'공수1'!I4</f>
         <v/>
       </c>
@@ -42113,7 +42132,7 @@
         <f>'공수1'!I3</f>
         <v/>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="41">
         <f>IF('공수1'!$I$2="","",'공수1'!$I$2)</f>
         <v/>
       </c>
@@ -42125,47 +42144,47 @@
         <f>IF(F11="","",SUMPRODUCT(('공수1'!$I$7:$I$156='공수1'!$I$2)*('공수1'!$I$7:$I$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="42">
         <f>IF(OR(F11="",G11=0),"",H11/G11)</f>
         <v/>
       </c>
-      <c r="J11" s="42">
+      <c r="J11" s="43">
         <f>IF(F11="","",IFERROR(SUMPRODUCT(('공수1'!$I$7:$I$156='공수1'!$I$2)*('공수1'!$I$7:$I$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K11" s="42">
+      <c r="K11" s="43">
         <f>IF(F11="","",IFERROR(SUMPRODUCT(('공수1'!$I$7:$I$156='공수1'!$I$2)*('공수1'!$I$7:$I$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L11" s="42">
+      <c r="L11" s="43">
         <f>IF(F11="","",IFERROR(SUMPRODUCT(('공수1'!$I$7:$I$156='공수1'!$I$2)*('공수1'!$I$7:$I$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M11" s="43">
+      <c r="M11" s="44">
         <f>IF(OR(J11="",K11=""),"",J11-K11)</f>
         <v/>
       </c>
-      <c r="N11" s="39">
+      <c r="N11" s="40">
         <f>IF(I11="","",IF(AND(M11&lt;&gt;"",M11&lt;0),"역변별·문항검토",IF(I11&gt;=0.9,"매우 쉬움",IF(I11&lt;=0.15,"매우 어려움",IF(AND(M11&lt;&gt;"",M11&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O11" s="39">
+      <c r="O11" s="40">
         <f>IF(G11=0,"",COUNTIF('공수1'!$I$7:$I$156,1))</f>
         <v/>
       </c>
-      <c r="P11" s="39">
+      <c r="P11" s="40">
         <f>IF(G11=0,"",COUNTIF('공수1'!$I$7:$I$156,2))</f>
         <v/>
       </c>
-      <c r="Q11" s="39">
+      <c r="Q11" s="40">
         <f>IF(G11=0,"",COUNTIF('공수1'!$I$7:$I$156,3))</f>
         <v/>
       </c>
-      <c r="R11" s="39">
+      <c r="R11" s="40">
         <f>IF(G11=0,"",COUNTIF('공수1'!$I$7:$I$156,4))</f>
         <v/>
       </c>
-      <c r="S11" s="39">
+      <c r="S11" s="40">
         <f>IF(G11=0,"",COUNTIF('공수1'!$I$7:$I$156,5))</f>
         <v/>
       </c>
@@ -42179,7 +42198,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="40">
         <f>'공수1'!J4</f>
         <v/>
       </c>
@@ -42191,7 +42210,7 @@
         <f>'공수1'!J3</f>
         <v/>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="41">
         <f>IF('공수1'!$J$2="","",'공수1'!$J$2)</f>
         <v/>
       </c>
@@ -42203,47 +42222,47 @@
         <f>IF(F12="","",SUMPRODUCT(('공수1'!$J$7:$J$156='공수1'!$J$2)*('공수1'!$J$7:$J$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="42">
         <f>IF(OR(F12="",G12=0),"",H12/G12)</f>
         <v/>
       </c>
-      <c r="J12" s="42">
+      <c r="J12" s="43">
         <f>IF(F12="","",IFERROR(SUMPRODUCT(('공수1'!$J$7:$J$156='공수1'!$J$2)*('공수1'!$J$7:$J$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K12" s="42">
+      <c r="K12" s="43">
         <f>IF(F12="","",IFERROR(SUMPRODUCT(('공수1'!$J$7:$J$156='공수1'!$J$2)*('공수1'!$J$7:$J$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L12" s="42">
+      <c r="L12" s="43">
         <f>IF(F12="","",IFERROR(SUMPRODUCT(('공수1'!$J$7:$J$156='공수1'!$J$2)*('공수1'!$J$7:$J$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M12" s="43">
+      <c r="M12" s="44">
         <f>IF(OR(J12="",K12=""),"",J12-K12)</f>
         <v/>
       </c>
-      <c r="N12" s="39">
+      <c r="N12" s="40">
         <f>IF(I12="","",IF(AND(M12&lt;&gt;"",M12&lt;0),"역변별·문항검토",IF(I12&gt;=0.9,"매우 쉬움",IF(I12&lt;=0.15,"매우 어려움",IF(AND(M12&lt;&gt;"",M12&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O12" s="39">
+      <c r="O12" s="40">
         <f>IF(G12=0,"",COUNTIF('공수1'!$J$7:$J$156,1))</f>
         <v/>
       </c>
-      <c r="P12" s="39">
+      <c r="P12" s="40">
         <f>IF(G12=0,"",COUNTIF('공수1'!$J$7:$J$156,2))</f>
         <v/>
       </c>
-      <c r="Q12" s="39">
+      <c r="Q12" s="40">
         <f>IF(G12=0,"",COUNTIF('공수1'!$J$7:$J$156,3))</f>
         <v/>
       </c>
-      <c r="R12" s="39">
+      <c r="R12" s="40">
         <f>IF(G12=0,"",COUNTIF('공수1'!$J$7:$J$156,4))</f>
         <v/>
       </c>
-      <c r="S12" s="39">
+      <c r="S12" s="40">
         <f>IF(G12=0,"",COUNTIF('공수1'!$J$7:$J$156,5))</f>
         <v/>
       </c>
@@ -42257,7 +42276,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="40">
         <f>'공수1'!K4</f>
         <v/>
       </c>
@@ -42269,7 +42288,7 @@
         <f>'공수1'!K3</f>
         <v/>
       </c>
-      <c r="F13" s="40">
+      <c r="F13" s="41">
         <f>IF('공수1'!$K$2="","",'공수1'!$K$2)</f>
         <v/>
       </c>
@@ -42281,47 +42300,47 @@
         <f>IF(F13="","",SUMPRODUCT(('공수1'!$K$7:$K$156='공수1'!$K$2)*('공수1'!$K$7:$K$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="42">
         <f>IF(OR(F13="",G13=0),"",H13/G13)</f>
         <v/>
       </c>
-      <c r="J13" s="42">
+      <c r="J13" s="43">
         <f>IF(F13="","",IFERROR(SUMPRODUCT(('공수1'!$K$7:$K$156='공수1'!$K$2)*('공수1'!$K$7:$K$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K13" s="42">
+      <c r="K13" s="43">
         <f>IF(F13="","",IFERROR(SUMPRODUCT(('공수1'!$K$7:$K$156='공수1'!$K$2)*('공수1'!$K$7:$K$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L13" s="42">
+      <c r="L13" s="43">
         <f>IF(F13="","",IFERROR(SUMPRODUCT(('공수1'!$K$7:$K$156='공수1'!$K$2)*('공수1'!$K$7:$K$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M13" s="43">
+      <c r="M13" s="44">
         <f>IF(OR(J13="",K13=""),"",J13-K13)</f>
         <v/>
       </c>
-      <c r="N13" s="39">
+      <c r="N13" s="40">
         <f>IF(I13="","",IF(AND(M13&lt;&gt;"",M13&lt;0),"역변별·문항검토",IF(I13&gt;=0.9,"매우 쉬움",IF(I13&lt;=0.15,"매우 어려움",IF(AND(M13&lt;&gt;"",M13&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O13" s="39">
+      <c r="O13" s="40">
         <f>IF(G13=0,"",COUNTIF('공수1'!$K$7:$K$156,1))</f>
         <v/>
       </c>
-      <c r="P13" s="39">
+      <c r="P13" s="40">
         <f>IF(G13=0,"",COUNTIF('공수1'!$K$7:$K$156,2))</f>
         <v/>
       </c>
-      <c r="Q13" s="39">
+      <c r="Q13" s="40">
         <f>IF(G13=0,"",COUNTIF('공수1'!$K$7:$K$156,3))</f>
         <v/>
       </c>
-      <c r="R13" s="39">
+      <c r="R13" s="40">
         <f>IF(G13=0,"",COUNTIF('공수1'!$K$7:$K$156,4))</f>
         <v/>
       </c>
-      <c r="S13" s="39">
+      <c r="S13" s="40">
         <f>IF(G13=0,"",COUNTIF('공수1'!$K$7:$K$156,5))</f>
         <v/>
       </c>
@@ -42335,7 +42354,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="40">
         <f>'공수1'!L4</f>
         <v/>
       </c>
@@ -42347,7 +42366,7 @@
         <f>'공수1'!L3</f>
         <v/>
       </c>
-      <c r="F14" s="40">
+      <c r="F14" s="41">
         <f>IF('공수1'!$L$2="","",'공수1'!$L$2)</f>
         <v/>
       </c>
@@ -42359,47 +42378,47 @@
         <f>IF(F14="","",SUMPRODUCT(('공수1'!$L$7:$L$156='공수1'!$L$2)*('공수1'!$L$7:$L$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="42">
         <f>IF(OR(F14="",G14=0),"",H14/G14)</f>
         <v/>
       </c>
-      <c r="J14" s="42">
+      <c r="J14" s="43">
         <f>IF(F14="","",IFERROR(SUMPRODUCT(('공수1'!$L$7:$L$156='공수1'!$L$2)*('공수1'!$L$7:$L$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K14" s="42">
+      <c r="K14" s="43">
         <f>IF(F14="","",IFERROR(SUMPRODUCT(('공수1'!$L$7:$L$156='공수1'!$L$2)*('공수1'!$L$7:$L$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L14" s="42">
+      <c r="L14" s="43">
         <f>IF(F14="","",IFERROR(SUMPRODUCT(('공수1'!$L$7:$L$156='공수1'!$L$2)*('공수1'!$L$7:$L$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M14" s="43">
+      <c r="M14" s="44">
         <f>IF(OR(J14="",K14=""),"",J14-K14)</f>
         <v/>
       </c>
-      <c r="N14" s="39">
+      <c r="N14" s="40">
         <f>IF(I14="","",IF(AND(M14&lt;&gt;"",M14&lt;0),"역변별·문항검토",IF(I14&gt;=0.9,"매우 쉬움",IF(I14&lt;=0.15,"매우 어려움",IF(AND(M14&lt;&gt;"",M14&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O14" s="39">
+      <c r="O14" s="40">
         <f>IF(G14=0,"",COUNTIF('공수1'!$L$7:$L$156,1))</f>
         <v/>
       </c>
-      <c r="P14" s="39">
+      <c r="P14" s="40">
         <f>IF(G14=0,"",COUNTIF('공수1'!$L$7:$L$156,2))</f>
         <v/>
       </c>
-      <c r="Q14" s="39">
+      <c r="Q14" s="40">
         <f>IF(G14=0,"",COUNTIF('공수1'!$L$7:$L$156,3))</f>
         <v/>
       </c>
-      <c r="R14" s="39">
+      <c r="R14" s="40">
         <f>IF(G14=0,"",COUNTIF('공수1'!$L$7:$L$156,4))</f>
         <v/>
       </c>
-      <c r="S14" s="39">
+      <c r="S14" s="40">
         <f>IF(G14=0,"",COUNTIF('공수1'!$L$7:$L$156,5))</f>
         <v/>
       </c>
@@ -42413,7 +42432,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="40">
         <f>'공수1'!M4</f>
         <v/>
       </c>
@@ -42425,7 +42444,7 @@
         <f>'공수1'!M3</f>
         <v/>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="41">
         <f>IF('공수1'!$M$2="","",'공수1'!$M$2)</f>
         <v/>
       </c>
@@ -42437,47 +42456,47 @@
         <f>IF(F15="","",SUMPRODUCT(('공수1'!$M$7:$M$156='공수1'!$M$2)*('공수1'!$M$7:$M$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="42">
         <f>IF(OR(F15="",G15=0),"",H15/G15)</f>
         <v/>
       </c>
-      <c r="J15" s="42">
+      <c r="J15" s="43">
         <f>IF(F15="","",IFERROR(SUMPRODUCT(('공수1'!$M$7:$M$156='공수1'!$M$2)*('공수1'!$M$7:$M$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K15" s="42">
+      <c r="K15" s="43">
         <f>IF(F15="","",IFERROR(SUMPRODUCT(('공수1'!$M$7:$M$156='공수1'!$M$2)*('공수1'!$M$7:$M$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L15" s="42">
+      <c r="L15" s="43">
         <f>IF(F15="","",IFERROR(SUMPRODUCT(('공수1'!$M$7:$M$156='공수1'!$M$2)*('공수1'!$M$7:$M$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M15" s="43">
+      <c r="M15" s="44">
         <f>IF(OR(J15="",K15=""),"",J15-K15)</f>
         <v/>
       </c>
-      <c r="N15" s="39">
+      <c r="N15" s="40">
         <f>IF(I15="","",IF(AND(M15&lt;&gt;"",M15&lt;0),"역변별·문항검토",IF(I15&gt;=0.9,"매우 쉬움",IF(I15&lt;=0.15,"매우 어려움",IF(AND(M15&lt;&gt;"",M15&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O15" s="39">
+      <c r="O15" s="40">
         <f>IF(G15=0,"",COUNTIF('공수1'!$M$7:$M$156,1))</f>
         <v/>
       </c>
-      <c r="P15" s="39">
+      <c r="P15" s="40">
         <f>IF(G15=0,"",COUNTIF('공수1'!$M$7:$M$156,2))</f>
         <v/>
       </c>
-      <c r="Q15" s="39">
+      <c r="Q15" s="40">
         <f>IF(G15=0,"",COUNTIF('공수1'!$M$7:$M$156,3))</f>
         <v/>
       </c>
-      <c r="R15" s="39">
+      <c r="R15" s="40">
         <f>IF(G15=0,"",COUNTIF('공수1'!$M$7:$M$156,4))</f>
         <v/>
       </c>
-      <c r="S15" s="39">
+      <c r="S15" s="40">
         <f>IF(G15=0,"",COUNTIF('공수1'!$M$7:$M$156,5))</f>
         <v/>
       </c>
@@ -42491,7 +42510,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="40">
         <f>'공수1'!N4</f>
         <v/>
       </c>
@@ -42503,7 +42522,7 @@
         <f>'공수1'!N3</f>
         <v/>
       </c>
-      <c r="F16" s="40">
+      <c r="F16" s="41">
         <f>IF('공수1'!$N$2="","",'공수1'!$N$2)</f>
         <v/>
       </c>
@@ -42515,47 +42534,47 @@
         <f>IF(F16="","",SUMPRODUCT(('공수1'!$N$7:$N$156='공수1'!$N$2)*('공수1'!$N$7:$N$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="42">
         <f>IF(OR(F16="",G16=0),"",H16/G16)</f>
         <v/>
       </c>
-      <c r="J16" s="42">
+      <c r="J16" s="43">
         <f>IF(F16="","",IFERROR(SUMPRODUCT(('공수1'!$N$7:$N$156='공수1'!$N$2)*('공수1'!$N$7:$N$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K16" s="42">
+      <c r="K16" s="43">
         <f>IF(F16="","",IFERROR(SUMPRODUCT(('공수1'!$N$7:$N$156='공수1'!$N$2)*('공수1'!$N$7:$N$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L16" s="42">
+      <c r="L16" s="43">
         <f>IF(F16="","",IFERROR(SUMPRODUCT(('공수1'!$N$7:$N$156='공수1'!$N$2)*('공수1'!$N$7:$N$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M16" s="43">
+      <c r="M16" s="44">
         <f>IF(OR(J16="",K16=""),"",J16-K16)</f>
         <v/>
       </c>
-      <c r="N16" s="39">
+      <c r="N16" s="40">
         <f>IF(I16="","",IF(AND(M16&lt;&gt;"",M16&lt;0),"역변별·문항검토",IF(I16&gt;=0.9,"매우 쉬움",IF(I16&lt;=0.15,"매우 어려움",IF(AND(M16&lt;&gt;"",M16&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O16" s="39">
+      <c r="O16" s="40">
         <f>IF(G16=0,"",COUNTIF('공수1'!$N$7:$N$156,1))</f>
         <v/>
       </c>
-      <c r="P16" s="39">
+      <c r="P16" s="40">
         <f>IF(G16=0,"",COUNTIF('공수1'!$N$7:$N$156,2))</f>
         <v/>
       </c>
-      <c r="Q16" s="39">
+      <c r="Q16" s="40">
         <f>IF(G16=0,"",COUNTIF('공수1'!$N$7:$N$156,3))</f>
         <v/>
       </c>
-      <c r="R16" s="39">
+      <c r="R16" s="40">
         <f>IF(G16=0,"",COUNTIF('공수1'!$N$7:$N$156,4))</f>
         <v/>
       </c>
-      <c r="S16" s="39">
+      <c r="S16" s="40">
         <f>IF(G16=0,"",COUNTIF('공수1'!$N$7:$N$156,5))</f>
         <v/>
       </c>
@@ -42569,7 +42588,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C17" s="39">
+      <c r="C17" s="40">
         <f>'공수1'!O4</f>
         <v/>
       </c>
@@ -42581,7 +42600,7 @@
         <f>'공수1'!O3</f>
         <v/>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="41">
         <f>IF('공수1'!$O$2="","",'공수1'!$O$2)</f>
         <v/>
       </c>
@@ -42593,47 +42612,47 @@
         <f>IF(F17="","",SUMPRODUCT(('공수1'!$O$7:$O$156='공수1'!$O$2)*('공수1'!$O$7:$O$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="42">
         <f>IF(OR(F17="",G17=0),"",H17/G17)</f>
         <v/>
       </c>
-      <c r="J17" s="42">
+      <c r="J17" s="43">
         <f>IF(F17="","",IFERROR(SUMPRODUCT(('공수1'!$O$7:$O$156='공수1'!$O$2)*('공수1'!$O$7:$O$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K17" s="42">
+      <c r="K17" s="43">
         <f>IF(F17="","",IFERROR(SUMPRODUCT(('공수1'!$O$7:$O$156='공수1'!$O$2)*('공수1'!$O$7:$O$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L17" s="42">
+      <c r="L17" s="43">
         <f>IF(F17="","",IFERROR(SUMPRODUCT(('공수1'!$O$7:$O$156='공수1'!$O$2)*('공수1'!$O$7:$O$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M17" s="43">
+      <c r="M17" s="44">
         <f>IF(OR(J17="",K17=""),"",J17-K17)</f>
         <v/>
       </c>
-      <c r="N17" s="39">
+      <c r="N17" s="40">
         <f>IF(I17="","",IF(AND(M17&lt;&gt;"",M17&lt;0),"역변별·문항검토",IF(I17&gt;=0.9,"매우 쉬움",IF(I17&lt;=0.15,"매우 어려움",IF(AND(M17&lt;&gt;"",M17&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O17" s="39">
+      <c r="O17" s="40">
         <f>IF(G17=0,"",COUNTIF('공수1'!$O$7:$O$156,1))</f>
         <v/>
       </c>
-      <c r="P17" s="39">
+      <c r="P17" s="40">
         <f>IF(G17=0,"",COUNTIF('공수1'!$O$7:$O$156,2))</f>
         <v/>
       </c>
-      <c r="Q17" s="39">
+      <c r="Q17" s="40">
         <f>IF(G17=0,"",COUNTIF('공수1'!$O$7:$O$156,3))</f>
         <v/>
       </c>
-      <c r="R17" s="39">
+      <c r="R17" s="40">
         <f>IF(G17=0,"",COUNTIF('공수1'!$O$7:$O$156,4))</f>
         <v/>
       </c>
-      <c r="S17" s="39">
+      <c r="S17" s="40">
         <f>IF(G17=0,"",COUNTIF('공수1'!$O$7:$O$156,5))</f>
         <v/>
       </c>
@@ -42647,7 +42666,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C18" s="39">
+      <c r="C18" s="40">
         <f>'공수1'!P4</f>
         <v/>
       </c>
@@ -42659,7 +42678,7 @@
         <f>'공수1'!P3</f>
         <v/>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="41">
         <f>IF('공수1'!$P$2="","",'공수1'!$P$2)</f>
         <v/>
       </c>
@@ -42671,47 +42690,47 @@
         <f>IF(F18="","",SUMPRODUCT(('공수1'!$P$7:$P$156='공수1'!$P$2)*('공수1'!$P$7:$P$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I18" s="41">
+      <c r="I18" s="42">
         <f>IF(OR(F18="",G18=0),"",H18/G18)</f>
         <v/>
       </c>
-      <c r="J18" s="42">
+      <c r="J18" s="43">
         <f>IF(F18="","",IFERROR(SUMPRODUCT(('공수1'!$P$7:$P$156='공수1'!$P$2)*('공수1'!$P$7:$P$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K18" s="42">
+      <c r="K18" s="43">
         <f>IF(F18="","",IFERROR(SUMPRODUCT(('공수1'!$P$7:$P$156='공수1'!$P$2)*('공수1'!$P$7:$P$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L18" s="42">
+      <c r="L18" s="43">
         <f>IF(F18="","",IFERROR(SUMPRODUCT(('공수1'!$P$7:$P$156='공수1'!$P$2)*('공수1'!$P$7:$P$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M18" s="43">
+      <c r="M18" s="44">
         <f>IF(OR(J18="",K18=""),"",J18-K18)</f>
         <v/>
       </c>
-      <c r="N18" s="39">
+      <c r="N18" s="40">
         <f>IF(I18="","",IF(AND(M18&lt;&gt;"",M18&lt;0),"역변별·문항검토",IF(I18&gt;=0.9,"매우 쉬움",IF(I18&lt;=0.15,"매우 어려움",IF(AND(M18&lt;&gt;"",M18&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O18" s="39">
+      <c r="O18" s="40">
         <f>IF(G18=0,"",COUNTIF('공수1'!$P$7:$P$156,1))</f>
         <v/>
       </c>
-      <c r="P18" s="39">
+      <c r="P18" s="40">
         <f>IF(G18=0,"",COUNTIF('공수1'!$P$7:$P$156,2))</f>
         <v/>
       </c>
-      <c r="Q18" s="39">
+      <c r="Q18" s="40">
         <f>IF(G18=0,"",COUNTIF('공수1'!$P$7:$P$156,3))</f>
         <v/>
       </c>
-      <c r="R18" s="39">
+      <c r="R18" s="40">
         <f>IF(G18=0,"",COUNTIF('공수1'!$P$7:$P$156,4))</f>
         <v/>
       </c>
-      <c r="S18" s="39">
+      <c r="S18" s="40">
         <f>IF(G18=0,"",COUNTIF('공수1'!$P$7:$P$156,5))</f>
         <v/>
       </c>
@@ -42725,7 +42744,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C19" s="39">
+      <c r="C19" s="40">
         <f>'공수1'!Q4</f>
         <v/>
       </c>
@@ -42737,7 +42756,7 @@
         <f>'공수1'!Q3</f>
         <v/>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="41">
         <f>IF('공수1'!$Q$2="","",'공수1'!$Q$2)</f>
         <v/>
       </c>
@@ -42749,47 +42768,47 @@
         <f>IF(F19="","",SUMPRODUCT(('공수1'!$Q$7:$Q$156='공수1'!$Q$2)*('공수1'!$Q$7:$Q$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="42">
         <f>IF(OR(F19="",G19=0),"",H19/G19)</f>
         <v/>
       </c>
-      <c r="J19" s="42">
+      <c r="J19" s="43">
         <f>IF(F19="","",IFERROR(SUMPRODUCT(('공수1'!$Q$7:$Q$156='공수1'!$Q$2)*('공수1'!$Q$7:$Q$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K19" s="42">
+      <c r="K19" s="43">
         <f>IF(F19="","",IFERROR(SUMPRODUCT(('공수1'!$Q$7:$Q$156='공수1'!$Q$2)*('공수1'!$Q$7:$Q$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L19" s="42">
+      <c r="L19" s="43">
         <f>IF(F19="","",IFERROR(SUMPRODUCT(('공수1'!$Q$7:$Q$156='공수1'!$Q$2)*('공수1'!$Q$7:$Q$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M19" s="43">
+      <c r="M19" s="44">
         <f>IF(OR(J19="",K19=""),"",J19-K19)</f>
         <v/>
       </c>
-      <c r="N19" s="39">
+      <c r="N19" s="40">
         <f>IF(I19="","",IF(AND(M19&lt;&gt;"",M19&lt;0),"역변별·문항검토",IF(I19&gt;=0.9,"매우 쉬움",IF(I19&lt;=0.15,"매우 어려움",IF(AND(M19&lt;&gt;"",M19&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O19" s="39">
+      <c r="O19" s="40">
         <f>IF(G19=0,"",COUNTIF('공수1'!$Q$7:$Q$156,1))</f>
         <v/>
       </c>
-      <c r="P19" s="39">
+      <c r="P19" s="40">
         <f>IF(G19=0,"",COUNTIF('공수1'!$Q$7:$Q$156,2))</f>
         <v/>
       </c>
-      <c r="Q19" s="39">
+      <c r="Q19" s="40">
         <f>IF(G19=0,"",COUNTIF('공수1'!$Q$7:$Q$156,3))</f>
         <v/>
       </c>
-      <c r="R19" s="39">
+      <c r="R19" s="40">
         <f>IF(G19=0,"",COUNTIF('공수1'!$Q$7:$Q$156,4))</f>
         <v/>
       </c>
-      <c r="S19" s="39">
+      <c r="S19" s="40">
         <f>IF(G19=0,"",COUNTIF('공수1'!$Q$7:$Q$156,5))</f>
         <v/>
       </c>
@@ -42803,7 +42822,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C20" s="39">
+      <c r="C20" s="40">
         <f>'공수1'!R4</f>
         <v/>
       </c>
@@ -42815,7 +42834,7 @@
         <f>'공수1'!R3</f>
         <v/>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="41">
         <f>IF('공수1'!$R$2="","","24")</f>
         <v/>
       </c>
@@ -42827,51 +42846,51 @@
         <f>IF(F20="","",SUMPRODUCT(('공수1'!$R$7:$R$156='공수1'!$R$2)*('공수1'!$R$7:$R$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I20" s="41">
+      <c r="I20" s="42">
         <f>IF(OR(F20="",G20=0),"",H20/G20)</f>
         <v/>
       </c>
-      <c r="J20" s="42">
+      <c r="J20" s="43">
         <f>IF(F20="","",IFERROR(SUMPRODUCT(('공수1'!$R$7:$R$156='공수1'!$R$2)*('공수1'!$R$7:$R$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K20" s="42">
+      <c r="K20" s="43">
         <f>IF(F20="","",IFERROR(SUMPRODUCT(('공수1'!$R$7:$R$156='공수1'!$R$2)*('공수1'!$R$7:$R$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L20" s="42">
+      <c r="L20" s="43">
         <f>IF(F20="","",IFERROR(SUMPRODUCT(('공수1'!$R$7:$R$156='공수1'!$R$2)*('공수1'!$R$7:$R$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M20" s="43">
+      <c r="M20" s="44">
         <f>IF(OR(J20="",K20=""),"",J20-K20)</f>
         <v/>
       </c>
-      <c r="N20" s="39">
+      <c r="N20" s="40">
         <f>IF(I20="","",IF(AND(M20&lt;&gt;"",M20&lt;0),"역변별·문항검토",IF(I20&gt;=0.9,"매우 쉬움",IF(I20&lt;=0.15,"매우 어려움",IF(AND(M20&lt;&gt;"",M20&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O20" s="44" t="inlineStr">
+      <c r="O20" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P20" s="44" t="inlineStr">
+      <c r="P20" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q20" s="44" t="inlineStr">
+      <c r="Q20" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R20" s="44" t="inlineStr">
+      <c r="R20" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S20" s="44" t="inlineStr">
+      <c r="S20" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -42886,7 +42905,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C21" s="39">
+      <c r="C21" s="40">
         <f>'공수1'!S4</f>
         <v/>
       </c>
@@ -42898,7 +42917,7 @@
         <f>'공수1'!S3</f>
         <v/>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="41">
         <f>IF('공수1'!$S$2="","","864")</f>
         <v/>
       </c>
@@ -42910,51 +42929,51 @@
         <f>IF(F21="","",SUMPRODUCT(('공수1'!$S$7:$S$156='공수1'!$S$2)*('공수1'!$S$7:$S$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I21" s="41">
+      <c r="I21" s="42">
         <f>IF(OR(F21="",G21=0),"",H21/G21)</f>
         <v/>
       </c>
-      <c r="J21" s="42">
+      <c r="J21" s="43">
         <f>IF(F21="","",IFERROR(SUMPRODUCT(('공수1'!$S$7:$S$156='공수1'!$S$2)*('공수1'!$S$7:$S$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K21" s="42">
+      <c r="K21" s="43">
         <f>IF(F21="","",IFERROR(SUMPRODUCT(('공수1'!$S$7:$S$156='공수1'!$S$2)*('공수1'!$S$7:$S$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L21" s="42">
+      <c r="L21" s="43">
         <f>IF(F21="","",IFERROR(SUMPRODUCT(('공수1'!$S$7:$S$156='공수1'!$S$2)*('공수1'!$S$7:$S$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M21" s="43">
+      <c r="M21" s="44">
         <f>IF(OR(J21="",K21=""),"",J21-K21)</f>
         <v/>
       </c>
-      <c r="N21" s="39">
+      <c r="N21" s="40">
         <f>IF(I21="","",IF(AND(M21&lt;&gt;"",M21&lt;0),"역변별·문항검토",IF(I21&gt;=0.9,"매우 쉬움",IF(I21&lt;=0.15,"매우 어려움",IF(AND(M21&lt;&gt;"",M21&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O21" s="44" t="inlineStr">
+      <c r="O21" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P21" s="44" t="inlineStr">
+      <c r="P21" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q21" s="44" t="inlineStr">
+      <c r="Q21" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R21" s="44" t="inlineStr">
+      <c r="R21" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S21" s="44" t="inlineStr">
+      <c r="S21" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -42969,7 +42988,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C22" s="39">
+      <c r="C22" s="40">
         <f>'공수1'!T4</f>
         <v/>
       </c>
@@ -42981,7 +43000,7 @@
         <f>'공수1'!T3</f>
         <v/>
       </c>
-      <c r="F22" s="40">
+      <c r="F22" s="41">
         <f>IF('공수1'!$T$2="","","8")</f>
         <v/>
       </c>
@@ -42993,51 +43012,51 @@
         <f>IF(F22="","",SUMPRODUCT(('공수1'!$T$7:$T$156='공수1'!$T$2)*('공수1'!$T$7:$T$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I22" s="41">
+      <c r="I22" s="42">
         <f>IF(OR(F22="",G22=0),"",H22/G22)</f>
         <v/>
       </c>
-      <c r="J22" s="42">
+      <c r="J22" s="43">
         <f>IF(F22="","",IFERROR(SUMPRODUCT(('공수1'!$T$7:$T$156='공수1'!$T$2)*('공수1'!$T$7:$T$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K22" s="42">
+      <c r="K22" s="43">
         <f>IF(F22="","",IFERROR(SUMPRODUCT(('공수1'!$T$7:$T$156='공수1'!$T$2)*('공수1'!$T$7:$T$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L22" s="42">
+      <c r="L22" s="43">
         <f>IF(F22="","",IFERROR(SUMPRODUCT(('공수1'!$T$7:$T$156='공수1'!$T$2)*('공수1'!$T$7:$T$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M22" s="43">
+      <c r="M22" s="44">
         <f>IF(OR(J22="",K22=""),"",J22-K22)</f>
         <v/>
       </c>
-      <c r="N22" s="39">
+      <c r="N22" s="40">
         <f>IF(I22="","",IF(AND(M22&lt;&gt;"",M22&lt;0),"역변별·문항검토",IF(I22&gt;=0.9,"매우 쉬움",IF(I22&lt;=0.15,"매우 어려움",IF(AND(M22&lt;&gt;"",M22&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O22" s="44" t="inlineStr">
+      <c r="O22" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P22" s="44" t="inlineStr">
+      <c r="P22" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q22" s="44" t="inlineStr">
+      <c r="Q22" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R22" s="44" t="inlineStr">
+      <c r="R22" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S22" s="44" t="inlineStr">
+      <c r="S22" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -43052,7 +43071,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C23" s="39">
+      <c r="C23" s="40">
         <f>'공수1'!U4</f>
         <v/>
       </c>
@@ -43064,7 +43083,7 @@
         <f>'공수1'!U3</f>
         <v/>
       </c>
-      <c r="F23" s="40">
+      <c r="F23" s="41">
         <f>IF('공수1'!$U$2="","","76")</f>
         <v/>
       </c>
@@ -43076,51 +43095,51 @@
         <f>IF(F23="","",SUMPRODUCT(('공수1'!$U$7:$U$156='공수1'!$U$2)*('공수1'!$U$7:$U$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I23" s="41">
+      <c r="I23" s="42">
         <f>IF(OR(F23="",G23=0),"",H23/G23)</f>
         <v/>
       </c>
-      <c r="J23" s="42">
+      <c r="J23" s="43">
         <f>IF(F23="","",IFERROR(SUMPRODUCT(('공수1'!$U$7:$U$156='공수1'!$U$2)*('공수1'!$U$7:$U$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K23" s="42">
+      <c r="K23" s="43">
         <f>IF(F23="","",IFERROR(SUMPRODUCT(('공수1'!$U$7:$U$156='공수1'!$U$2)*('공수1'!$U$7:$U$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L23" s="42">
+      <c r="L23" s="43">
         <f>IF(F23="","",IFERROR(SUMPRODUCT(('공수1'!$U$7:$U$156='공수1'!$U$2)*('공수1'!$U$7:$U$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M23" s="43">
+      <c r="M23" s="44">
         <f>IF(OR(J23="",K23=""),"",J23-K23)</f>
         <v/>
       </c>
-      <c r="N23" s="39">
+      <c r="N23" s="40">
         <f>IF(I23="","",IF(AND(M23&lt;&gt;"",M23&lt;0),"역변별·문항검토",IF(I23&gt;=0.9,"매우 쉬움",IF(I23&lt;=0.15,"매우 어려움",IF(AND(M23&lt;&gt;"",M23&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O23" s="44" t="inlineStr">
+      <c r="O23" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P23" s="44" t="inlineStr">
+      <c r="P23" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q23" s="44" t="inlineStr">
+      <c r="Q23" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R23" s="44" t="inlineStr">
+      <c r="R23" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S23" s="44" t="inlineStr">
+      <c r="S23" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -43135,7 +43154,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C24" s="39">
+      <c r="C24" s="40">
         <f>'공수1'!V4</f>
         <v/>
       </c>
@@ -43147,7 +43166,7 @@
         <f>'공수1'!V3</f>
         <v/>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="41">
         <f>IF('공수1'!$V$2="","","27")</f>
         <v/>
       </c>
@@ -43159,51 +43178,51 @@
         <f>IF(F24="","",SUMPRODUCT(('공수1'!$V$7:$V$156='공수1'!$V$2)*('공수1'!$V$7:$V$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I24" s="41">
+      <c r="I24" s="42">
         <f>IF(OR(F24="",G24=0),"",H24/G24)</f>
         <v/>
       </c>
-      <c r="J24" s="42">
+      <c r="J24" s="43">
         <f>IF(F24="","",IFERROR(SUMPRODUCT(('공수1'!$V$7:$V$156='공수1'!$V$2)*('공수1'!$V$7:$V$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K24" s="42">
+      <c r="K24" s="43">
         <f>IF(F24="","",IFERROR(SUMPRODUCT(('공수1'!$V$7:$V$156='공수1'!$V$2)*('공수1'!$V$7:$V$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L24" s="42">
+      <c r="L24" s="43">
         <f>IF(F24="","",IFERROR(SUMPRODUCT(('공수1'!$V$7:$V$156='공수1'!$V$2)*('공수1'!$V$7:$V$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M24" s="43">
+      <c r="M24" s="44">
         <f>IF(OR(J24="",K24=""),"",J24-K24)</f>
         <v/>
       </c>
-      <c r="N24" s="39">
+      <c r="N24" s="40">
         <f>IF(I24="","",IF(AND(M24&lt;&gt;"",M24&lt;0),"역변별·문항검토",IF(I24&gt;=0.9,"매우 쉬움",IF(I24&lt;=0.15,"매우 어려움",IF(AND(M24&lt;&gt;"",M24&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O24" s="44" t="inlineStr">
+      <c r="O24" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P24" s="44" t="inlineStr">
+      <c r="P24" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q24" s="44" t="inlineStr">
+      <c r="Q24" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R24" s="44" t="inlineStr">
+      <c r="R24" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S24" s="44" t="inlineStr">
+      <c r="S24" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -43218,7 +43237,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C25" s="39">
+      <c r="C25" s="40">
         <f>'공수1'!W4</f>
         <v/>
       </c>
@@ -43230,7 +43249,7 @@
         <f>'공수1'!W3</f>
         <v/>
       </c>
-      <c r="F25" s="40">
+      <c r="F25" s="41">
         <f>IF('공수1'!$W$2="","","65")</f>
         <v/>
       </c>
@@ -43242,58 +43261,58 @@
         <f>IF(F25="","",SUMPRODUCT(('공수1'!$W$7:$W$156='공수1'!$W$2)*('공수1'!$W$7:$W$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I25" s="41">
+      <c r="I25" s="42">
         <f>IF(OR(F25="",G25=0),"",H25/G25)</f>
         <v/>
       </c>
-      <c r="J25" s="42">
+      <c r="J25" s="43">
         <f>IF(F25="","",IFERROR(SUMPRODUCT(('공수1'!$W$7:$W$156='공수1'!$W$2)*('공수1'!$W$7:$W$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K25" s="42">
+      <c r="K25" s="43">
         <f>IF(F25="","",IFERROR(SUMPRODUCT(('공수1'!$W$7:$W$156='공수1'!$W$2)*('공수1'!$W$7:$W$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L25" s="42">
+      <c r="L25" s="43">
         <f>IF(F25="","",IFERROR(SUMPRODUCT(('공수1'!$W$7:$W$156='공수1'!$W$2)*('공수1'!$W$7:$W$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수1'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M25" s="43">
+      <c r="M25" s="44">
         <f>IF(OR(J25="",K25=""),"",J25-K25)</f>
         <v/>
       </c>
-      <c r="N25" s="39">
+      <c r="N25" s="40">
         <f>IF(I25="","",IF(AND(M25&lt;&gt;"",M25&lt;0),"역변별·문항검토",IF(I25&gt;=0.9,"매우 쉬움",IF(I25&lt;=0.15,"매우 어려움",IF(AND(M25&lt;&gt;"",M25&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O25" s="44" t="inlineStr">
+      <c r="O25" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P25" s="44" t="inlineStr">
+      <c r="P25" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q25" s="44" t="inlineStr">
+      <c r="Q25" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R25" s="44" t="inlineStr">
+      <c r="R25" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S25" s="44" t="inlineStr">
+      <c r="S25" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="38" t="inlineStr">
+      <c r="A28" s="39" t="inlineStr">
         <is>
           <t>공통수학2</t>
         </is>
@@ -43402,7 +43421,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C30" s="39">
+      <c r="C30" s="40">
         <f>'공수2'!D4</f>
         <v/>
       </c>
@@ -43414,7 +43433,7 @@
         <f>'공수2'!D3</f>
         <v/>
       </c>
-      <c r="F30" s="40">
+      <c r="F30" s="41">
         <f>IF('공수2'!$D$2="","",'공수2'!$D$2)</f>
         <v/>
       </c>
@@ -43426,47 +43445,47 @@
         <f>IF(F30="","",SUMPRODUCT(('공수2'!$D$7:$D$156='공수2'!$D$2)*('공수2'!$D$7:$D$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I30" s="41">
+      <c r="I30" s="42">
         <f>IF(OR(F30="",G30=0),"",H30/G30)</f>
         <v/>
       </c>
-      <c r="J30" s="42">
+      <c r="J30" s="43">
         <f>IF(F30="","",IFERROR(SUMPRODUCT(('공수2'!$D$7:$D$156='공수2'!$D$2)*('공수2'!$D$7:$D$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K30" s="42">
+      <c r="K30" s="43">
         <f>IF(F30="","",IFERROR(SUMPRODUCT(('공수2'!$D$7:$D$156='공수2'!$D$2)*('공수2'!$D$7:$D$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L30" s="42">
+      <c r="L30" s="43">
         <f>IF(F30="","",IFERROR(SUMPRODUCT(('공수2'!$D$7:$D$156='공수2'!$D$2)*('공수2'!$D$7:$D$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M30" s="43">
+      <c r="M30" s="44">
         <f>IF(OR(J30="",K30=""),"",J30-K30)</f>
         <v/>
       </c>
-      <c r="N30" s="39">
+      <c r="N30" s="40">
         <f>IF(I30="","",IF(AND(M30&lt;&gt;"",M30&lt;0),"역변별·문항검토",IF(I30&gt;=0.9,"매우 쉬움",IF(I30&lt;=0.15,"매우 어려움",IF(AND(M30&lt;&gt;"",M30&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O30" s="39">
+      <c r="O30" s="40">
         <f>IF(G30=0,"",COUNTIF('공수2'!$D$7:$D$156,1))</f>
         <v/>
       </c>
-      <c r="P30" s="39">
+      <c r="P30" s="40">
         <f>IF(G30=0,"",COUNTIF('공수2'!$D$7:$D$156,2))</f>
         <v/>
       </c>
-      <c r="Q30" s="39">
+      <c r="Q30" s="40">
         <f>IF(G30=0,"",COUNTIF('공수2'!$D$7:$D$156,3))</f>
         <v/>
       </c>
-      <c r="R30" s="39">
+      <c r="R30" s="40">
         <f>IF(G30=0,"",COUNTIF('공수2'!$D$7:$D$156,4))</f>
         <v/>
       </c>
-      <c r="S30" s="39">
+      <c r="S30" s="40">
         <f>IF(G30=0,"",COUNTIF('공수2'!$D$7:$D$156,5))</f>
         <v/>
       </c>
@@ -43480,7 +43499,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C31" s="39">
+      <c r="C31" s="40">
         <f>'공수2'!E4</f>
         <v/>
       </c>
@@ -43492,7 +43511,7 @@
         <f>'공수2'!E3</f>
         <v/>
       </c>
-      <c r="F31" s="40">
+      <c r="F31" s="41">
         <f>IF('공수2'!$E$2="","",'공수2'!$E$2)</f>
         <v/>
       </c>
@@ -43504,47 +43523,47 @@
         <f>IF(F31="","",SUMPRODUCT(('공수2'!$E$7:$E$156='공수2'!$E$2)*('공수2'!$E$7:$E$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I31" s="41">
+      <c r="I31" s="42">
         <f>IF(OR(F31="",G31=0),"",H31/G31)</f>
         <v/>
       </c>
-      <c r="J31" s="42">
+      <c r="J31" s="43">
         <f>IF(F31="","",IFERROR(SUMPRODUCT(('공수2'!$E$7:$E$156='공수2'!$E$2)*('공수2'!$E$7:$E$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K31" s="42">
+      <c r="K31" s="43">
         <f>IF(F31="","",IFERROR(SUMPRODUCT(('공수2'!$E$7:$E$156='공수2'!$E$2)*('공수2'!$E$7:$E$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L31" s="42">
+      <c r="L31" s="43">
         <f>IF(F31="","",IFERROR(SUMPRODUCT(('공수2'!$E$7:$E$156='공수2'!$E$2)*('공수2'!$E$7:$E$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M31" s="43">
+      <c r="M31" s="44">
         <f>IF(OR(J31="",K31=""),"",J31-K31)</f>
         <v/>
       </c>
-      <c r="N31" s="39">
+      <c r="N31" s="40">
         <f>IF(I31="","",IF(AND(M31&lt;&gt;"",M31&lt;0),"역변별·문항검토",IF(I31&gt;=0.9,"매우 쉬움",IF(I31&lt;=0.15,"매우 어려움",IF(AND(M31&lt;&gt;"",M31&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O31" s="39">
+      <c r="O31" s="40">
         <f>IF(G31=0,"",COUNTIF('공수2'!$E$7:$E$156,1))</f>
         <v/>
       </c>
-      <c r="P31" s="39">
+      <c r="P31" s="40">
         <f>IF(G31=0,"",COUNTIF('공수2'!$E$7:$E$156,2))</f>
         <v/>
       </c>
-      <c r="Q31" s="39">
+      <c r="Q31" s="40">
         <f>IF(G31=0,"",COUNTIF('공수2'!$E$7:$E$156,3))</f>
         <v/>
       </c>
-      <c r="R31" s="39">
+      <c r="R31" s="40">
         <f>IF(G31=0,"",COUNTIF('공수2'!$E$7:$E$156,4))</f>
         <v/>
       </c>
-      <c r="S31" s="39">
+      <c r="S31" s="40">
         <f>IF(G31=0,"",COUNTIF('공수2'!$E$7:$E$156,5))</f>
         <v/>
       </c>
@@ -43558,7 +43577,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C32" s="39">
+      <c r="C32" s="40">
         <f>'공수2'!F4</f>
         <v/>
       </c>
@@ -43570,7 +43589,7 @@
         <f>'공수2'!F3</f>
         <v/>
       </c>
-      <c r="F32" s="40">
+      <c r="F32" s="41">
         <f>IF('공수2'!$F$2="","",'공수2'!$F$2)</f>
         <v/>
       </c>
@@ -43582,47 +43601,47 @@
         <f>IF(F32="","",SUMPRODUCT(('공수2'!$F$7:$F$156='공수2'!$F$2)*('공수2'!$F$7:$F$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I32" s="41">
+      <c r="I32" s="42">
         <f>IF(OR(F32="",G32=0),"",H32/G32)</f>
         <v/>
       </c>
-      <c r="J32" s="42">
+      <c r="J32" s="43">
         <f>IF(F32="","",IFERROR(SUMPRODUCT(('공수2'!$F$7:$F$156='공수2'!$F$2)*('공수2'!$F$7:$F$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K32" s="42">
+      <c r="K32" s="43">
         <f>IF(F32="","",IFERROR(SUMPRODUCT(('공수2'!$F$7:$F$156='공수2'!$F$2)*('공수2'!$F$7:$F$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L32" s="42">
+      <c r="L32" s="43">
         <f>IF(F32="","",IFERROR(SUMPRODUCT(('공수2'!$F$7:$F$156='공수2'!$F$2)*('공수2'!$F$7:$F$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M32" s="43">
+      <c r="M32" s="44">
         <f>IF(OR(J32="",K32=""),"",J32-K32)</f>
         <v/>
       </c>
-      <c r="N32" s="39">
+      <c r="N32" s="40">
         <f>IF(I32="","",IF(AND(M32&lt;&gt;"",M32&lt;0),"역변별·문항검토",IF(I32&gt;=0.9,"매우 쉬움",IF(I32&lt;=0.15,"매우 어려움",IF(AND(M32&lt;&gt;"",M32&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O32" s="39">
+      <c r="O32" s="40">
         <f>IF(G32=0,"",COUNTIF('공수2'!$F$7:$F$156,1))</f>
         <v/>
       </c>
-      <c r="P32" s="39">
+      <c r="P32" s="40">
         <f>IF(G32=0,"",COUNTIF('공수2'!$F$7:$F$156,2))</f>
         <v/>
       </c>
-      <c r="Q32" s="39">
+      <c r="Q32" s="40">
         <f>IF(G32=0,"",COUNTIF('공수2'!$F$7:$F$156,3))</f>
         <v/>
       </c>
-      <c r="R32" s="39">
+      <c r="R32" s="40">
         <f>IF(G32=0,"",COUNTIF('공수2'!$F$7:$F$156,4))</f>
         <v/>
       </c>
-      <c r="S32" s="39">
+      <c r="S32" s="40">
         <f>IF(G32=0,"",COUNTIF('공수2'!$F$7:$F$156,5))</f>
         <v/>
       </c>
@@ -43636,7 +43655,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C33" s="39">
+      <c r="C33" s="40">
         <f>'공수2'!G4</f>
         <v/>
       </c>
@@ -43648,7 +43667,7 @@
         <f>'공수2'!G3</f>
         <v/>
       </c>
-      <c r="F33" s="40">
+      <c r="F33" s="41">
         <f>IF('공수2'!$G$2="","",'공수2'!$G$2)</f>
         <v/>
       </c>
@@ -43660,47 +43679,47 @@
         <f>IF(F33="","",SUMPRODUCT(('공수2'!$G$7:$G$156='공수2'!$G$2)*('공수2'!$G$7:$G$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I33" s="41">
+      <c r="I33" s="42">
         <f>IF(OR(F33="",G33=0),"",H33/G33)</f>
         <v/>
       </c>
-      <c r="J33" s="42">
+      <c r="J33" s="43">
         <f>IF(F33="","",IFERROR(SUMPRODUCT(('공수2'!$G$7:$G$156='공수2'!$G$2)*('공수2'!$G$7:$G$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K33" s="42">
+      <c r="K33" s="43">
         <f>IF(F33="","",IFERROR(SUMPRODUCT(('공수2'!$G$7:$G$156='공수2'!$G$2)*('공수2'!$G$7:$G$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L33" s="42">
+      <c r="L33" s="43">
         <f>IF(F33="","",IFERROR(SUMPRODUCT(('공수2'!$G$7:$G$156='공수2'!$G$2)*('공수2'!$G$7:$G$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M33" s="43">
+      <c r="M33" s="44">
         <f>IF(OR(J33="",K33=""),"",J33-K33)</f>
         <v/>
       </c>
-      <c r="N33" s="39">
+      <c r="N33" s="40">
         <f>IF(I33="","",IF(AND(M33&lt;&gt;"",M33&lt;0),"역변별·문항검토",IF(I33&gt;=0.9,"매우 쉬움",IF(I33&lt;=0.15,"매우 어려움",IF(AND(M33&lt;&gt;"",M33&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O33" s="39">
+      <c r="O33" s="40">
         <f>IF(G33=0,"",COUNTIF('공수2'!$G$7:$G$156,1))</f>
         <v/>
       </c>
-      <c r="P33" s="39">
+      <c r="P33" s="40">
         <f>IF(G33=0,"",COUNTIF('공수2'!$G$7:$G$156,2))</f>
         <v/>
       </c>
-      <c r="Q33" s="39">
+      <c r="Q33" s="40">
         <f>IF(G33=0,"",COUNTIF('공수2'!$G$7:$G$156,3))</f>
         <v/>
       </c>
-      <c r="R33" s="39">
+      <c r="R33" s="40">
         <f>IF(G33=0,"",COUNTIF('공수2'!$G$7:$G$156,4))</f>
         <v/>
       </c>
-      <c r="S33" s="39">
+      <c r="S33" s="40">
         <f>IF(G33=0,"",COUNTIF('공수2'!$G$7:$G$156,5))</f>
         <v/>
       </c>
@@ -43714,7 +43733,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C34" s="39">
+      <c r="C34" s="40">
         <f>'공수2'!H4</f>
         <v/>
       </c>
@@ -43726,7 +43745,7 @@
         <f>'공수2'!H3</f>
         <v/>
       </c>
-      <c r="F34" s="40">
+      <c r="F34" s="41">
         <f>IF('공수2'!$H$2="","",'공수2'!$H$2)</f>
         <v/>
       </c>
@@ -43738,47 +43757,47 @@
         <f>IF(F34="","",SUMPRODUCT(('공수2'!$H$7:$H$156='공수2'!$H$2)*('공수2'!$H$7:$H$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I34" s="41">
+      <c r="I34" s="42">
         <f>IF(OR(F34="",G34=0),"",H34/G34)</f>
         <v/>
       </c>
-      <c r="J34" s="42">
+      <c r="J34" s="43">
         <f>IF(F34="","",IFERROR(SUMPRODUCT(('공수2'!$H$7:$H$156='공수2'!$H$2)*('공수2'!$H$7:$H$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K34" s="42">
+      <c r="K34" s="43">
         <f>IF(F34="","",IFERROR(SUMPRODUCT(('공수2'!$H$7:$H$156='공수2'!$H$2)*('공수2'!$H$7:$H$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L34" s="42">
+      <c r="L34" s="43">
         <f>IF(F34="","",IFERROR(SUMPRODUCT(('공수2'!$H$7:$H$156='공수2'!$H$2)*('공수2'!$H$7:$H$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M34" s="43">
+      <c r="M34" s="44">
         <f>IF(OR(J34="",K34=""),"",J34-K34)</f>
         <v/>
       </c>
-      <c r="N34" s="39">
+      <c r="N34" s="40">
         <f>IF(I34="","",IF(AND(M34&lt;&gt;"",M34&lt;0),"역변별·문항검토",IF(I34&gt;=0.9,"매우 쉬움",IF(I34&lt;=0.15,"매우 어려움",IF(AND(M34&lt;&gt;"",M34&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O34" s="39">
+      <c r="O34" s="40">
         <f>IF(G34=0,"",COUNTIF('공수2'!$H$7:$H$156,1))</f>
         <v/>
       </c>
-      <c r="P34" s="39">
+      <c r="P34" s="40">
         <f>IF(G34=0,"",COUNTIF('공수2'!$H$7:$H$156,2))</f>
         <v/>
       </c>
-      <c r="Q34" s="39">
+      <c r="Q34" s="40">
         <f>IF(G34=0,"",COUNTIF('공수2'!$H$7:$H$156,3))</f>
         <v/>
       </c>
-      <c r="R34" s="39">
+      <c r="R34" s="40">
         <f>IF(G34=0,"",COUNTIF('공수2'!$H$7:$H$156,4))</f>
         <v/>
       </c>
-      <c r="S34" s="39">
+      <c r="S34" s="40">
         <f>IF(G34=0,"",COUNTIF('공수2'!$H$7:$H$156,5))</f>
         <v/>
       </c>
@@ -43792,7 +43811,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C35" s="39">
+      <c r="C35" s="40">
         <f>'공수2'!I4</f>
         <v/>
       </c>
@@ -43804,7 +43823,7 @@
         <f>'공수2'!I3</f>
         <v/>
       </c>
-      <c r="F35" s="40">
+      <c r="F35" s="41">
         <f>IF('공수2'!$I$2="","",'공수2'!$I$2)</f>
         <v/>
       </c>
@@ -43816,47 +43835,47 @@
         <f>IF(F35="","",SUMPRODUCT(('공수2'!$I$7:$I$156='공수2'!$I$2)*('공수2'!$I$7:$I$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I35" s="41">
+      <c r="I35" s="42">
         <f>IF(OR(F35="",G35=0),"",H35/G35)</f>
         <v/>
       </c>
-      <c r="J35" s="42">
+      <c r="J35" s="43">
         <f>IF(F35="","",IFERROR(SUMPRODUCT(('공수2'!$I$7:$I$156='공수2'!$I$2)*('공수2'!$I$7:$I$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K35" s="42">
+      <c r="K35" s="43">
         <f>IF(F35="","",IFERROR(SUMPRODUCT(('공수2'!$I$7:$I$156='공수2'!$I$2)*('공수2'!$I$7:$I$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L35" s="42">
+      <c r="L35" s="43">
         <f>IF(F35="","",IFERROR(SUMPRODUCT(('공수2'!$I$7:$I$156='공수2'!$I$2)*('공수2'!$I$7:$I$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M35" s="43">
+      <c r="M35" s="44">
         <f>IF(OR(J35="",K35=""),"",J35-K35)</f>
         <v/>
       </c>
-      <c r="N35" s="39">
+      <c r="N35" s="40">
         <f>IF(I35="","",IF(AND(M35&lt;&gt;"",M35&lt;0),"역변별·문항검토",IF(I35&gt;=0.9,"매우 쉬움",IF(I35&lt;=0.15,"매우 어려움",IF(AND(M35&lt;&gt;"",M35&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O35" s="39">
+      <c r="O35" s="40">
         <f>IF(G35=0,"",COUNTIF('공수2'!$I$7:$I$156,1))</f>
         <v/>
       </c>
-      <c r="P35" s="39">
+      <c r="P35" s="40">
         <f>IF(G35=0,"",COUNTIF('공수2'!$I$7:$I$156,2))</f>
         <v/>
       </c>
-      <c r="Q35" s="39">
+      <c r="Q35" s="40">
         <f>IF(G35=0,"",COUNTIF('공수2'!$I$7:$I$156,3))</f>
         <v/>
       </c>
-      <c r="R35" s="39">
+      <c r="R35" s="40">
         <f>IF(G35=0,"",COUNTIF('공수2'!$I$7:$I$156,4))</f>
         <v/>
       </c>
-      <c r="S35" s="39">
+      <c r="S35" s="40">
         <f>IF(G35=0,"",COUNTIF('공수2'!$I$7:$I$156,5))</f>
         <v/>
       </c>
@@ -43870,7 +43889,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="40">
         <f>'공수2'!J4</f>
         <v/>
       </c>
@@ -43882,7 +43901,7 @@
         <f>'공수2'!J3</f>
         <v/>
       </c>
-      <c r="F36" s="40">
+      <c r="F36" s="41">
         <f>IF('공수2'!$J$2="","",'공수2'!$J$2)</f>
         <v/>
       </c>
@@ -43894,47 +43913,47 @@
         <f>IF(F36="","",SUMPRODUCT(('공수2'!$J$7:$J$156='공수2'!$J$2)*('공수2'!$J$7:$J$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I36" s="41">
+      <c r="I36" s="42">
         <f>IF(OR(F36="",G36=0),"",H36/G36)</f>
         <v/>
       </c>
-      <c r="J36" s="42">
+      <c r="J36" s="43">
         <f>IF(F36="","",IFERROR(SUMPRODUCT(('공수2'!$J$7:$J$156='공수2'!$J$2)*('공수2'!$J$7:$J$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K36" s="42">
+      <c r="K36" s="43">
         <f>IF(F36="","",IFERROR(SUMPRODUCT(('공수2'!$J$7:$J$156='공수2'!$J$2)*('공수2'!$J$7:$J$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L36" s="42">
+      <c r="L36" s="43">
         <f>IF(F36="","",IFERROR(SUMPRODUCT(('공수2'!$J$7:$J$156='공수2'!$J$2)*('공수2'!$J$7:$J$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M36" s="43">
+      <c r="M36" s="44">
         <f>IF(OR(J36="",K36=""),"",J36-K36)</f>
         <v/>
       </c>
-      <c r="N36" s="39">
+      <c r="N36" s="40">
         <f>IF(I36="","",IF(AND(M36&lt;&gt;"",M36&lt;0),"역변별·문항검토",IF(I36&gt;=0.9,"매우 쉬움",IF(I36&lt;=0.15,"매우 어려움",IF(AND(M36&lt;&gt;"",M36&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O36" s="39">
+      <c r="O36" s="40">
         <f>IF(G36=0,"",COUNTIF('공수2'!$J$7:$J$156,1))</f>
         <v/>
       </c>
-      <c r="P36" s="39">
+      <c r="P36" s="40">
         <f>IF(G36=0,"",COUNTIF('공수2'!$J$7:$J$156,2))</f>
         <v/>
       </c>
-      <c r="Q36" s="39">
+      <c r="Q36" s="40">
         <f>IF(G36=0,"",COUNTIF('공수2'!$J$7:$J$156,3))</f>
         <v/>
       </c>
-      <c r="R36" s="39">
+      <c r="R36" s="40">
         <f>IF(G36=0,"",COUNTIF('공수2'!$J$7:$J$156,4))</f>
         <v/>
       </c>
-      <c r="S36" s="39">
+      <c r="S36" s="40">
         <f>IF(G36=0,"",COUNTIF('공수2'!$J$7:$J$156,5))</f>
         <v/>
       </c>
@@ -43948,7 +43967,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C37" s="39">
+      <c r="C37" s="40">
         <f>'공수2'!K4</f>
         <v/>
       </c>
@@ -43960,7 +43979,7 @@
         <f>'공수2'!K3</f>
         <v/>
       </c>
-      <c r="F37" s="40">
+      <c r="F37" s="41">
         <f>IF('공수2'!$K$2="","",'공수2'!$K$2)</f>
         <v/>
       </c>
@@ -43972,47 +43991,47 @@
         <f>IF(F37="","",SUMPRODUCT(('공수2'!$K$7:$K$156='공수2'!$K$2)*('공수2'!$K$7:$K$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I37" s="41">
+      <c r="I37" s="42">
         <f>IF(OR(F37="",G37=0),"",H37/G37)</f>
         <v/>
       </c>
-      <c r="J37" s="42">
+      <c r="J37" s="43">
         <f>IF(F37="","",IFERROR(SUMPRODUCT(('공수2'!$K$7:$K$156='공수2'!$K$2)*('공수2'!$K$7:$K$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K37" s="42">
+      <c r="K37" s="43">
         <f>IF(F37="","",IFERROR(SUMPRODUCT(('공수2'!$K$7:$K$156='공수2'!$K$2)*('공수2'!$K$7:$K$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L37" s="42">
+      <c r="L37" s="43">
         <f>IF(F37="","",IFERROR(SUMPRODUCT(('공수2'!$K$7:$K$156='공수2'!$K$2)*('공수2'!$K$7:$K$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M37" s="43">
+      <c r="M37" s="44">
         <f>IF(OR(J37="",K37=""),"",J37-K37)</f>
         <v/>
       </c>
-      <c r="N37" s="39">
+      <c r="N37" s="40">
         <f>IF(I37="","",IF(AND(M37&lt;&gt;"",M37&lt;0),"역변별·문항검토",IF(I37&gt;=0.9,"매우 쉬움",IF(I37&lt;=0.15,"매우 어려움",IF(AND(M37&lt;&gt;"",M37&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O37" s="39">
+      <c r="O37" s="40">
         <f>IF(G37=0,"",COUNTIF('공수2'!$K$7:$K$156,1))</f>
         <v/>
       </c>
-      <c r="P37" s="39">
+      <c r="P37" s="40">
         <f>IF(G37=0,"",COUNTIF('공수2'!$K$7:$K$156,2))</f>
         <v/>
       </c>
-      <c r="Q37" s="39">
+      <c r="Q37" s="40">
         <f>IF(G37=0,"",COUNTIF('공수2'!$K$7:$K$156,3))</f>
         <v/>
       </c>
-      <c r="R37" s="39">
+      <c r="R37" s="40">
         <f>IF(G37=0,"",COUNTIF('공수2'!$K$7:$K$156,4))</f>
         <v/>
       </c>
-      <c r="S37" s="39">
+      <c r="S37" s="40">
         <f>IF(G37=0,"",COUNTIF('공수2'!$K$7:$K$156,5))</f>
         <v/>
       </c>
@@ -44026,7 +44045,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C38" s="39">
+      <c r="C38" s="40">
         <f>'공수2'!L4</f>
         <v/>
       </c>
@@ -44038,7 +44057,7 @@
         <f>'공수2'!L3</f>
         <v/>
       </c>
-      <c r="F38" s="40">
+      <c r="F38" s="41">
         <f>IF('공수2'!$L$2="","",'공수2'!$L$2)</f>
         <v/>
       </c>
@@ -44050,47 +44069,47 @@
         <f>IF(F38="","",SUMPRODUCT(('공수2'!$L$7:$L$156='공수2'!$L$2)*('공수2'!$L$7:$L$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I38" s="41">
+      <c r="I38" s="42">
         <f>IF(OR(F38="",G38=0),"",H38/G38)</f>
         <v/>
       </c>
-      <c r="J38" s="42">
+      <c r="J38" s="43">
         <f>IF(F38="","",IFERROR(SUMPRODUCT(('공수2'!$L$7:$L$156='공수2'!$L$2)*('공수2'!$L$7:$L$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K38" s="42">
+      <c r="K38" s="43">
         <f>IF(F38="","",IFERROR(SUMPRODUCT(('공수2'!$L$7:$L$156='공수2'!$L$2)*('공수2'!$L$7:$L$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L38" s="42">
+      <c r="L38" s="43">
         <f>IF(F38="","",IFERROR(SUMPRODUCT(('공수2'!$L$7:$L$156='공수2'!$L$2)*('공수2'!$L$7:$L$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M38" s="43">
+      <c r="M38" s="44">
         <f>IF(OR(J38="",K38=""),"",J38-K38)</f>
         <v/>
       </c>
-      <c r="N38" s="39">
+      <c r="N38" s="40">
         <f>IF(I38="","",IF(AND(M38&lt;&gt;"",M38&lt;0),"역변별·문항검토",IF(I38&gt;=0.9,"매우 쉬움",IF(I38&lt;=0.15,"매우 어려움",IF(AND(M38&lt;&gt;"",M38&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O38" s="39">
+      <c r="O38" s="40">
         <f>IF(G38=0,"",COUNTIF('공수2'!$L$7:$L$156,1))</f>
         <v/>
       </c>
-      <c r="P38" s="39">
+      <c r="P38" s="40">
         <f>IF(G38=0,"",COUNTIF('공수2'!$L$7:$L$156,2))</f>
         <v/>
       </c>
-      <c r="Q38" s="39">
+      <c r="Q38" s="40">
         <f>IF(G38=0,"",COUNTIF('공수2'!$L$7:$L$156,3))</f>
         <v/>
       </c>
-      <c r="R38" s="39">
+      <c r="R38" s="40">
         <f>IF(G38=0,"",COUNTIF('공수2'!$L$7:$L$156,4))</f>
         <v/>
       </c>
-      <c r="S38" s="39">
+      <c r="S38" s="40">
         <f>IF(G38=0,"",COUNTIF('공수2'!$L$7:$L$156,5))</f>
         <v/>
       </c>
@@ -44104,7 +44123,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C39" s="39">
+      <c r="C39" s="40">
         <f>'공수2'!M4</f>
         <v/>
       </c>
@@ -44116,7 +44135,7 @@
         <f>'공수2'!M3</f>
         <v/>
       </c>
-      <c r="F39" s="40">
+      <c r="F39" s="41">
         <f>IF('공수2'!$M$2="","",'공수2'!$M$2)</f>
         <v/>
       </c>
@@ -44128,47 +44147,47 @@
         <f>IF(F39="","",SUMPRODUCT(('공수2'!$M$7:$M$156='공수2'!$M$2)*('공수2'!$M$7:$M$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I39" s="41">
+      <c r="I39" s="42">
         <f>IF(OR(F39="",G39=0),"",H39/G39)</f>
         <v/>
       </c>
-      <c r="J39" s="42">
+      <c r="J39" s="43">
         <f>IF(F39="","",IFERROR(SUMPRODUCT(('공수2'!$M$7:$M$156='공수2'!$M$2)*('공수2'!$M$7:$M$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K39" s="42">
+      <c r="K39" s="43">
         <f>IF(F39="","",IFERROR(SUMPRODUCT(('공수2'!$M$7:$M$156='공수2'!$M$2)*('공수2'!$M$7:$M$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L39" s="42">
+      <c r="L39" s="43">
         <f>IF(F39="","",IFERROR(SUMPRODUCT(('공수2'!$M$7:$M$156='공수2'!$M$2)*('공수2'!$M$7:$M$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M39" s="43">
+      <c r="M39" s="44">
         <f>IF(OR(J39="",K39=""),"",J39-K39)</f>
         <v/>
       </c>
-      <c r="N39" s="39">
+      <c r="N39" s="40">
         <f>IF(I39="","",IF(AND(M39&lt;&gt;"",M39&lt;0),"역변별·문항검토",IF(I39&gt;=0.9,"매우 쉬움",IF(I39&lt;=0.15,"매우 어려움",IF(AND(M39&lt;&gt;"",M39&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O39" s="39">
+      <c r="O39" s="40">
         <f>IF(G39=0,"",COUNTIF('공수2'!$M$7:$M$156,1))</f>
         <v/>
       </c>
-      <c r="P39" s="39">
+      <c r="P39" s="40">
         <f>IF(G39=0,"",COUNTIF('공수2'!$M$7:$M$156,2))</f>
         <v/>
       </c>
-      <c r="Q39" s="39">
+      <c r="Q39" s="40">
         <f>IF(G39=0,"",COUNTIF('공수2'!$M$7:$M$156,3))</f>
         <v/>
       </c>
-      <c r="R39" s="39">
+      <c r="R39" s="40">
         <f>IF(G39=0,"",COUNTIF('공수2'!$M$7:$M$156,4))</f>
         <v/>
       </c>
-      <c r="S39" s="39">
+      <c r="S39" s="40">
         <f>IF(G39=0,"",COUNTIF('공수2'!$M$7:$M$156,5))</f>
         <v/>
       </c>
@@ -44182,7 +44201,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C40" s="39">
+      <c r="C40" s="40">
         <f>'공수2'!N4</f>
         <v/>
       </c>
@@ -44194,7 +44213,7 @@
         <f>'공수2'!N3</f>
         <v/>
       </c>
-      <c r="F40" s="40">
+      <c r="F40" s="41">
         <f>IF('공수2'!$N$2="","",'공수2'!$N$2)</f>
         <v/>
       </c>
@@ -44206,47 +44225,47 @@
         <f>IF(F40="","",SUMPRODUCT(('공수2'!$N$7:$N$156='공수2'!$N$2)*('공수2'!$N$7:$N$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I40" s="41">
+      <c r="I40" s="42">
         <f>IF(OR(F40="",G40=0),"",H40/G40)</f>
         <v/>
       </c>
-      <c r="J40" s="42">
+      <c r="J40" s="43">
         <f>IF(F40="","",IFERROR(SUMPRODUCT(('공수2'!$N$7:$N$156='공수2'!$N$2)*('공수2'!$N$7:$N$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K40" s="42">
+      <c r="K40" s="43">
         <f>IF(F40="","",IFERROR(SUMPRODUCT(('공수2'!$N$7:$N$156='공수2'!$N$2)*('공수2'!$N$7:$N$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L40" s="42">
+      <c r="L40" s="43">
         <f>IF(F40="","",IFERROR(SUMPRODUCT(('공수2'!$N$7:$N$156='공수2'!$N$2)*('공수2'!$N$7:$N$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M40" s="43">
+      <c r="M40" s="44">
         <f>IF(OR(J40="",K40=""),"",J40-K40)</f>
         <v/>
       </c>
-      <c r="N40" s="39">
+      <c r="N40" s="40">
         <f>IF(I40="","",IF(AND(M40&lt;&gt;"",M40&lt;0),"역변별·문항검토",IF(I40&gt;=0.9,"매우 쉬움",IF(I40&lt;=0.15,"매우 어려움",IF(AND(M40&lt;&gt;"",M40&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O40" s="39">
+      <c r="O40" s="40">
         <f>IF(G40=0,"",COUNTIF('공수2'!$N$7:$N$156,1))</f>
         <v/>
       </c>
-      <c r="P40" s="39">
+      <c r="P40" s="40">
         <f>IF(G40=0,"",COUNTIF('공수2'!$N$7:$N$156,2))</f>
         <v/>
       </c>
-      <c r="Q40" s="39">
+      <c r="Q40" s="40">
         <f>IF(G40=0,"",COUNTIF('공수2'!$N$7:$N$156,3))</f>
         <v/>
       </c>
-      <c r="R40" s="39">
+      <c r="R40" s="40">
         <f>IF(G40=0,"",COUNTIF('공수2'!$N$7:$N$156,4))</f>
         <v/>
       </c>
-      <c r="S40" s="39">
+      <c r="S40" s="40">
         <f>IF(G40=0,"",COUNTIF('공수2'!$N$7:$N$156,5))</f>
         <v/>
       </c>
@@ -44260,7 +44279,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C41" s="39">
+      <c r="C41" s="40">
         <f>'공수2'!O4</f>
         <v/>
       </c>
@@ -44272,7 +44291,7 @@
         <f>'공수2'!O3</f>
         <v/>
       </c>
-      <c r="F41" s="40">
+      <c r="F41" s="41">
         <f>IF('공수2'!$O$2="","",'공수2'!$O$2)</f>
         <v/>
       </c>
@@ -44284,47 +44303,47 @@
         <f>IF(F41="","",SUMPRODUCT(('공수2'!$O$7:$O$156='공수2'!$O$2)*('공수2'!$O$7:$O$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I41" s="41">
+      <c r="I41" s="42">
         <f>IF(OR(F41="",G41=0),"",H41/G41)</f>
         <v/>
       </c>
-      <c r="J41" s="42">
+      <c r="J41" s="43">
         <f>IF(F41="","",IFERROR(SUMPRODUCT(('공수2'!$O$7:$O$156='공수2'!$O$2)*('공수2'!$O$7:$O$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K41" s="42">
+      <c r="K41" s="43">
         <f>IF(F41="","",IFERROR(SUMPRODUCT(('공수2'!$O$7:$O$156='공수2'!$O$2)*('공수2'!$O$7:$O$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L41" s="42">
+      <c r="L41" s="43">
         <f>IF(F41="","",IFERROR(SUMPRODUCT(('공수2'!$O$7:$O$156='공수2'!$O$2)*('공수2'!$O$7:$O$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M41" s="43">
+      <c r="M41" s="44">
         <f>IF(OR(J41="",K41=""),"",J41-K41)</f>
         <v/>
       </c>
-      <c r="N41" s="39">
+      <c r="N41" s="40">
         <f>IF(I41="","",IF(AND(M41&lt;&gt;"",M41&lt;0),"역변별·문항검토",IF(I41&gt;=0.9,"매우 쉬움",IF(I41&lt;=0.15,"매우 어려움",IF(AND(M41&lt;&gt;"",M41&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O41" s="39">
+      <c r="O41" s="40">
         <f>IF(G41=0,"",COUNTIF('공수2'!$O$7:$O$156,1))</f>
         <v/>
       </c>
-      <c r="P41" s="39">
+      <c r="P41" s="40">
         <f>IF(G41=0,"",COUNTIF('공수2'!$O$7:$O$156,2))</f>
         <v/>
       </c>
-      <c r="Q41" s="39">
+      <c r="Q41" s="40">
         <f>IF(G41=0,"",COUNTIF('공수2'!$O$7:$O$156,3))</f>
         <v/>
       </c>
-      <c r="R41" s="39">
+      <c r="R41" s="40">
         <f>IF(G41=0,"",COUNTIF('공수2'!$O$7:$O$156,4))</f>
         <v/>
       </c>
-      <c r="S41" s="39">
+      <c r="S41" s="40">
         <f>IF(G41=0,"",COUNTIF('공수2'!$O$7:$O$156,5))</f>
         <v/>
       </c>
@@ -44338,7 +44357,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C42" s="39">
+      <c r="C42" s="40">
         <f>'공수2'!P4</f>
         <v/>
       </c>
@@ -44350,7 +44369,7 @@
         <f>'공수2'!P3</f>
         <v/>
       </c>
-      <c r="F42" s="40">
+      <c r="F42" s="41">
         <f>IF('공수2'!$P$2="","",'공수2'!$P$2)</f>
         <v/>
       </c>
@@ -44362,47 +44381,47 @@
         <f>IF(F42="","",SUMPRODUCT(('공수2'!$P$7:$P$156='공수2'!$P$2)*('공수2'!$P$7:$P$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I42" s="41">
+      <c r="I42" s="42">
         <f>IF(OR(F42="",G42=0),"",H42/G42)</f>
         <v/>
       </c>
-      <c r="J42" s="42">
+      <c r="J42" s="43">
         <f>IF(F42="","",IFERROR(SUMPRODUCT(('공수2'!$P$7:$P$156='공수2'!$P$2)*('공수2'!$P$7:$P$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K42" s="42">
+      <c r="K42" s="43">
         <f>IF(F42="","",IFERROR(SUMPRODUCT(('공수2'!$P$7:$P$156='공수2'!$P$2)*('공수2'!$P$7:$P$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L42" s="42">
+      <c r="L42" s="43">
         <f>IF(F42="","",IFERROR(SUMPRODUCT(('공수2'!$P$7:$P$156='공수2'!$P$2)*('공수2'!$P$7:$P$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M42" s="43">
+      <c r="M42" s="44">
         <f>IF(OR(J42="",K42=""),"",J42-K42)</f>
         <v/>
       </c>
-      <c r="N42" s="39">
+      <c r="N42" s="40">
         <f>IF(I42="","",IF(AND(M42&lt;&gt;"",M42&lt;0),"역변별·문항검토",IF(I42&gt;=0.9,"매우 쉬움",IF(I42&lt;=0.15,"매우 어려움",IF(AND(M42&lt;&gt;"",M42&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O42" s="39">
+      <c r="O42" s="40">
         <f>IF(G42=0,"",COUNTIF('공수2'!$P$7:$P$156,1))</f>
         <v/>
       </c>
-      <c r="P42" s="39">
+      <c r="P42" s="40">
         <f>IF(G42=0,"",COUNTIF('공수2'!$P$7:$P$156,2))</f>
         <v/>
       </c>
-      <c r="Q42" s="39">
+      <c r="Q42" s="40">
         <f>IF(G42=0,"",COUNTIF('공수2'!$P$7:$P$156,3))</f>
         <v/>
       </c>
-      <c r="R42" s="39">
+      <c r="R42" s="40">
         <f>IF(G42=0,"",COUNTIF('공수2'!$P$7:$P$156,4))</f>
         <v/>
       </c>
-      <c r="S42" s="39">
+      <c r="S42" s="40">
         <f>IF(G42=0,"",COUNTIF('공수2'!$P$7:$P$156,5))</f>
         <v/>
       </c>
@@ -44416,7 +44435,7 @@
           <t>객관식</t>
         </is>
       </c>
-      <c r="C43" s="39">
+      <c r="C43" s="40">
         <f>'공수2'!Q4</f>
         <v/>
       </c>
@@ -44428,7 +44447,7 @@
         <f>'공수2'!Q3</f>
         <v/>
       </c>
-      <c r="F43" s="40">
+      <c r="F43" s="41">
         <f>IF('공수2'!$Q$2="","",'공수2'!$Q$2)</f>
         <v/>
       </c>
@@ -44440,47 +44459,47 @@
         <f>IF(F43="","",SUMPRODUCT(('공수2'!$Q$7:$Q$156='공수2'!$Q$2)*('공수2'!$Q$7:$Q$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I43" s="41">
+      <c r="I43" s="42">
         <f>IF(OR(F43="",G43=0),"",H43/G43)</f>
         <v/>
       </c>
-      <c r="J43" s="42">
+      <c r="J43" s="43">
         <f>IF(F43="","",IFERROR(SUMPRODUCT(('공수2'!$Q$7:$Q$156='공수2'!$Q$2)*('공수2'!$Q$7:$Q$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K43" s="42">
+      <c r="K43" s="43">
         <f>IF(F43="","",IFERROR(SUMPRODUCT(('공수2'!$Q$7:$Q$156='공수2'!$Q$2)*('공수2'!$Q$7:$Q$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L43" s="42">
+      <c r="L43" s="43">
         <f>IF(F43="","",IFERROR(SUMPRODUCT(('공수2'!$Q$7:$Q$156='공수2'!$Q$2)*('공수2'!$Q$7:$Q$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M43" s="43">
+      <c r="M43" s="44">
         <f>IF(OR(J43="",K43=""),"",J43-K43)</f>
         <v/>
       </c>
-      <c r="N43" s="39">
+      <c r="N43" s="40">
         <f>IF(I43="","",IF(AND(M43&lt;&gt;"",M43&lt;0),"역변별·문항검토",IF(I43&gt;=0.9,"매우 쉬움",IF(I43&lt;=0.15,"매우 어려움",IF(AND(M43&lt;&gt;"",M43&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O43" s="39">
+      <c r="O43" s="40">
         <f>IF(G43=0,"",COUNTIF('공수2'!$Q$7:$Q$156,1))</f>
         <v/>
       </c>
-      <c r="P43" s="39">
+      <c r="P43" s="40">
         <f>IF(G43=0,"",COUNTIF('공수2'!$Q$7:$Q$156,2))</f>
         <v/>
       </c>
-      <c r="Q43" s="39">
+      <c r="Q43" s="40">
         <f>IF(G43=0,"",COUNTIF('공수2'!$Q$7:$Q$156,3))</f>
         <v/>
       </c>
-      <c r="R43" s="39">
+      <c r="R43" s="40">
         <f>IF(G43=0,"",COUNTIF('공수2'!$Q$7:$Q$156,4))</f>
         <v/>
       </c>
-      <c r="S43" s="39">
+      <c r="S43" s="40">
         <f>IF(G43=0,"",COUNTIF('공수2'!$Q$7:$Q$156,5))</f>
         <v/>
       </c>
@@ -44494,7 +44513,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C44" s="39">
+      <c r="C44" s="40">
         <f>'공수2'!R4</f>
         <v/>
       </c>
@@ -44506,7 +44525,7 @@
         <f>'공수2'!R3</f>
         <v/>
       </c>
-      <c r="F44" s="40">
+      <c r="F44" s="41">
         <f>IF('공수2'!$R$2="","","9")</f>
         <v/>
       </c>
@@ -44518,51 +44537,51 @@
         <f>IF(F44="","",SUMPRODUCT(('공수2'!$R$7:$R$156='공수2'!$R$2)*('공수2'!$R$7:$R$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I44" s="41">
+      <c r="I44" s="42">
         <f>IF(OR(F44="",G44=0),"",H44/G44)</f>
         <v/>
       </c>
-      <c r="J44" s="42">
+      <c r="J44" s="43">
         <f>IF(F44="","",IFERROR(SUMPRODUCT(('공수2'!$R$7:$R$156='공수2'!$R$2)*('공수2'!$R$7:$R$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K44" s="42">
+      <c r="K44" s="43">
         <f>IF(F44="","",IFERROR(SUMPRODUCT(('공수2'!$R$7:$R$156='공수2'!$R$2)*('공수2'!$R$7:$R$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L44" s="42">
+      <c r="L44" s="43">
         <f>IF(F44="","",IFERROR(SUMPRODUCT(('공수2'!$R$7:$R$156='공수2'!$R$2)*('공수2'!$R$7:$R$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M44" s="43">
+      <c r="M44" s="44">
         <f>IF(OR(J44="",K44=""),"",J44-K44)</f>
         <v/>
       </c>
-      <c r="N44" s="39">
+      <c r="N44" s="40">
         <f>IF(I44="","",IF(AND(M44&lt;&gt;"",M44&lt;0),"역변별·문항검토",IF(I44&gt;=0.9,"매우 쉬움",IF(I44&lt;=0.15,"매우 어려움",IF(AND(M44&lt;&gt;"",M44&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O44" s="44" t="inlineStr">
+      <c r="O44" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P44" s="44" t="inlineStr">
+      <c r="P44" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q44" s="44" t="inlineStr">
+      <c r="Q44" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R44" s="44" t="inlineStr">
+      <c r="R44" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S44" s="44" t="inlineStr">
+      <c r="S44" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -44577,7 +44596,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C45" s="39">
+      <c r="C45" s="40">
         <f>'공수2'!S4</f>
         <v/>
       </c>
@@ -44589,7 +44608,7 @@
         <f>'공수2'!S3</f>
         <v/>
       </c>
-      <c r="F45" s="40">
+      <c r="F45" s="41">
         <f>IF('공수2'!$S$2="","","160")</f>
         <v/>
       </c>
@@ -44601,51 +44620,51 @@
         <f>IF(F45="","",SUMPRODUCT(('공수2'!$S$7:$S$156='공수2'!$S$2)*('공수2'!$S$7:$S$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I45" s="41">
+      <c r="I45" s="42">
         <f>IF(OR(F45="",G45=0),"",H45/G45)</f>
         <v/>
       </c>
-      <c r="J45" s="42">
+      <c r="J45" s="43">
         <f>IF(F45="","",IFERROR(SUMPRODUCT(('공수2'!$S$7:$S$156='공수2'!$S$2)*('공수2'!$S$7:$S$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K45" s="42">
+      <c r="K45" s="43">
         <f>IF(F45="","",IFERROR(SUMPRODUCT(('공수2'!$S$7:$S$156='공수2'!$S$2)*('공수2'!$S$7:$S$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L45" s="42">
+      <c r="L45" s="43">
         <f>IF(F45="","",IFERROR(SUMPRODUCT(('공수2'!$S$7:$S$156='공수2'!$S$2)*('공수2'!$S$7:$S$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M45" s="43">
+      <c r="M45" s="44">
         <f>IF(OR(J45="",K45=""),"",J45-K45)</f>
         <v/>
       </c>
-      <c r="N45" s="39">
+      <c r="N45" s="40">
         <f>IF(I45="","",IF(AND(M45&lt;&gt;"",M45&lt;0),"역변별·문항검토",IF(I45&gt;=0.9,"매우 쉬움",IF(I45&lt;=0.15,"매우 어려움",IF(AND(M45&lt;&gt;"",M45&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O45" s="44" t="inlineStr">
+      <c r="O45" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P45" s="44" t="inlineStr">
+      <c r="P45" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q45" s="44" t="inlineStr">
+      <c r="Q45" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R45" s="44" t="inlineStr">
+      <c r="R45" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S45" s="44" t="inlineStr">
+      <c r="S45" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -44660,7 +44679,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C46" s="39">
+      <c r="C46" s="40">
         <f>'공수2'!T4</f>
         <v/>
       </c>
@@ -44672,7 +44691,7 @@
         <f>'공수2'!T3</f>
         <v/>
       </c>
-      <c r="F46" s="40">
+      <c r="F46" s="41">
         <f>IF('공수2'!$T$2="","","12")</f>
         <v/>
       </c>
@@ -44684,51 +44703,51 @@
         <f>IF(F46="","",SUMPRODUCT(('공수2'!$T$7:$T$156='공수2'!$T$2)*('공수2'!$T$7:$T$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I46" s="41">
+      <c r="I46" s="42">
         <f>IF(OR(F46="",G46=0),"",H46/G46)</f>
         <v/>
       </c>
-      <c r="J46" s="42">
+      <c r="J46" s="43">
         <f>IF(F46="","",IFERROR(SUMPRODUCT(('공수2'!$T$7:$T$156='공수2'!$T$2)*('공수2'!$T$7:$T$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K46" s="42">
+      <c r="K46" s="43">
         <f>IF(F46="","",IFERROR(SUMPRODUCT(('공수2'!$T$7:$T$156='공수2'!$T$2)*('공수2'!$T$7:$T$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L46" s="42">
+      <c r="L46" s="43">
         <f>IF(F46="","",IFERROR(SUMPRODUCT(('공수2'!$T$7:$T$156='공수2'!$T$2)*('공수2'!$T$7:$T$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M46" s="43">
+      <c r="M46" s="44">
         <f>IF(OR(J46="",K46=""),"",J46-K46)</f>
         <v/>
       </c>
-      <c r="N46" s="39">
+      <c r="N46" s="40">
         <f>IF(I46="","",IF(AND(M46&lt;&gt;"",M46&lt;0),"역변별·문항검토",IF(I46&gt;=0.9,"매우 쉬움",IF(I46&lt;=0.15,"매우 어려움",IF(AND(M46&lt;&gt;"",M46&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O46" s="44" t="inlineStr">
+      <c r="O46" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P46" s="44" t="inlineStr">
+      <c r="P46" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q46" s="44" t="inlineStr">
+      <c r="Q46" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R46" s="44" t="inlineStr">
+      <c r="R46" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S46" s="44" t="inlineStr">
+      <c r="S46" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -44743,7 +44762,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C47" s="39">
+      <c r="C47" s="40">
         <f>'공수2'!U4</f>
         <v/>
       </c>
@@ -44755,7 +44774,7 @@
         <f>'공수2'!U3</f>
         <v/>
       </c>
-      <c r="F47" s="40">
+      <c r="F47" s="41">
         <f>IF('공수2'!$U$2="","","14")</f>
         <v/>
       </c>
@@ -44767,51 +44786,51 @@
         <f>IF(F47="","",SUMPRODUCT(('공수2'!$U$7:$U$156='공수2'!$U$2)*('공수2'!$U$7:$U$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I47" s="41">
+      <c r="I47" s="42">
         <f>IF(OR(F47="",G47=0),"",H47/G47)</f>
         <v/>
       </c>
-      <c r="J47" s="42">
+      <c r="J47" s="43">
         <f>IF(F47="","",IFERROR(SUMPRODUCT(('공수2'!$U$7:$U$156='공수2'!$U$2)*('공수2'!$U$7:$U$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K47" s="42">
+      <c r="K47" s="43">
         <f>IF(F47="","",IFERROR(SUMPRODUCT(('공수2'!$U$7:$U$156='공수2'!$U$2)*('공수2'!$U$7:$U$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L47" s="42">
+      <c r="L47" s="43">
         <f>IF(F47="","",IFERROR(SUMPRODUCT(('공수2'!$U$7:$U$156='공수2'!$U$2)*('공수2'!$U$7:$U$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M47" s="43">
+      <c r="M47" s="44">
         <f>IF(OR(J47="",K47=""),"",J47-K47)</f>
         <v/>
       </c>
-      <c r="N47" s="39">
+      <c r="N47" s="40">
         <f>IF(I47="","",IF(AND(M47&lt;&gt;"",M47&lt;0),"역변별·문항검토",IF(I47&gt;=0.9,"매우 쉬움",IF(I47&lt;=0.15,"매우 어려움",IF(AND(M47&lt;&gt;"",M47&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O47" s="44" t="inlineStr">
+      <c r="O47" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P47" s="44" t="inlineStr">
+      <c r="P47" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q47" s="44" t="inlineStr">
+      <c r="Q47" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R47" s="44" t="inlineStr">
+      <c r="R47" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S47" s="44" t="inlineStr">
+      <c r="S47" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -44826,7 +44845,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C48" s="39">
+      <c r="C48" s="40">
         <f>'공수2'!V4</f>
         <v/>
       </c>
@@ -44838,7 +44857,7 @@
         <f>'공수2'!V3</f>
         <v/>
       </c>
-      <c r="F48" s="40">
+      <c r="F48" s="41">
         <f>IF('공수2'!$V$2="","","15")</f>
         <v/>
       </c>
@@ -44850,51 +44869,51 @@
         <f>IF(F48="","",SUMPRODUCT(('공수2'!$V$7:$V$156='공수2'!$V$2)*('공수2'!$V$7:$V$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I48" s="41">
+      <c r="I48" s="42">
         <f>IF(OR(F48="",G48=0),"",H48/G48)</f>
         <v/>
       </c>
-      <c r="J48" s="42">
+      <c r="J48" s="43">
         <f>IF(F48="","",IFERROR(SUMPRODUCT(('공수2'!$V$7:$V$156='공수2'!$V$2)*('공수2'!$V$7:$V$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K48" s="42">
+      <c r="K48" s="43">
         <f>IF(F48="","",IFERROR(SUMPRODUCT(('공수2'!$V$7:$V$156='공수2'!$V$2)*('공수2'!$V$7:$V$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L48" s="42">
+      <c r="L48" s="43">
         <f>IF(F48="","",IFERROR(SUMPRODUCT(('공수2'!$V$7:$V$156='공수2'!$V$2)*('공수2'!$V$7:$V$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M48" s="43">
+      <c r="M48" s="44">
         <f>IF(OR(J48="",K48=""),"",J48-K48)</f>
         <v/>
       </c>
-      <c r="N48" s="39">
+      <c r="N48" s="40">
         <f>IF(I48="","",IF(AND(M48&lt;&gt;"",M48&lt;0),"역변별·문항검토",IF(I48&gt;=0.9,"매우 쉬움",IF(I48&lt;=0.15,"매우 어려움",IF(AND(M48&lt;&gt;"",M48&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O48" s="44" t="inlineStr">
+      <c r="O48" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P48" s="44" t="inlineStr">
+      <c r="P48" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q48" s="44" t="inlineStr">
+      <c r="Q48" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R48" s="44" t="inlineStr">
+      <c r="R48" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S48" s="44" t="inlineStr">
+      <c r="S48" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -44909,7 +44928,7 @@
           <t>단답형</t>
         </is>
       </c>
-      <c r="C49" s="39">
+      <c r="C49" s="40">
         <f>'공수2'!W4</f>
         <v/>
       </c>
@@ -44921,7 +44940,7 @@
         <f>'공수2'!W3</f>
         <v/>
       </c>
-      <c r="F49" s="40">
+      <c r="F49" s="41">
         <f>IF('공수2'!$W$2="","","13")</f>
         <v/>
       </c>
@@ -44933,51 +44952,51 @@
         <f>IF(F49="","",SUMPRODUCT(('공수2'!$W$7:$W$156='공수2'!$W$2)*('공수2'!$W$7:$W$156&lt;&gt;"")))</f>
         <v/>
       </c>
-      <c r="I49" s="41">
+      <c r="I49" s="42">
         <f>IF(OR(F49="",G49=0),"",H49/G49)</f>
         <v/>
       </c>
-      <c r="J49" s="42">
+      <c r="J49" s="43">
         <f>IF(F49="","",IFERROR(SUMPRODUCT(('공수2'!$W$7:$W$156='공수2'!$W$2)*('공수2'!$W$7:$W$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$6))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$6,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="K49" s="42">
+      <c r="K49" s="43">
         <f>IF(F49="","",IFERROR(SUMPRODUCT(('공수2'!$W$7:$W$156='공수2'!$W$2)*('공수2'!$W$7:$W$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$7))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$7,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="L49" s="42">
+      <c r="L49" s="43">
         <f>IF(F49="","",IFERROR(SUMPRODUCT(('공수2'!$W$7:$W$156='공수2'!$W$2)*('공수2'!$W$7:$W$156&lt;&gt;"")*('반배정'!$K$7:$K$156='설정'!$B$8))/COUNTIFS('반배정'!$K$7:$K$156,'설정'!$B$8,'공수2'!$Y$7:$Y$156,"&gt;=0"),""))</f>
         <v/>
       </c>
-      <c r="M49" s="43">
+      <c r="M49" s="44">
         <f>IF(OR(J49="",K49=""),"",J49-K49)</f>
         <v/>
       </c>
-      <c r="N49" s="39">
+      <c r="N49" s="40">
         <f>IF(I49="","",IF(AND(M49&lt;&gt;"",M49&lt;0),"역변별·문항검토",IF(I49&gt;=0.9,"매우 쉬움",IF(I49&lt;=0.15,"매우 어려움",IF(AND(M49&lt;&gt;"",M49&lt;0.2),"변별력 낮음","양호")))))</f>
         <v/>
       </c>
-      <c r="O49" s="44" t="inlineStr">
+      <c r="O49" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P49" s="44" t="inlineStr">
+      <c r="P49" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q49" s="44" t="inlineStr">
+      <c r="Q49" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R49" s="44" t="inlineStr">
+      <c r="R49" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S49" s="44" t="inlineStr">
+      <c r="S49" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -23039,7 +23039,7 @@
       <c r="M7" s="7" t="n"/>
       <c r="N7" s="7" t="n"/>
       <c r="O7" s="27">
-        <f>IF(M7&lt;&gt;"",M7,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K7&lt;&gt;""),'설정'!$B$10,IF(OR(K7='설정'!$B$6,K7='설정'!$B$8),SUBSTITUTE(K7,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G7)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G7)),"화목","반")),K7)))</f>
+        <f>IF(M7&lt;&gt;"",M7,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K7&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K7="","미응시",SUBSTITUTE(K7,"반",""))&amp;")",IF(OR(K7='설정'!$B$6,K7='설정'!$B$8),SUBSTITUTE(K7,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G7)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G7)),"화목","반")),K7)))</f>
         <v/>
       </c>
       <c r="P7" s="30">
@@ -23130,7 +23130,7 @@
       <c r="M8" s="7" t="n"/>
       <c r="N8" s="7" t="n"/>
       <c r="O8" s="27">
-        <f>IF(M8&lt;&gt;"",M8,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K8&lt;&gt;""),'설정'!$B$10,IF(OR(K8='설정'!$B$6,K8='설정'!$B$8),SUBSTITUTE(K8,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G8)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G8)),"화목","반")),K8)))</f>
+        <f>IF(M8&lt;&gt;"",M8,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K8&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K8="","미응시",SUBSTITUTE(K8,"반",""))&amp;")",IF(OR(K8='설정'!$B$6,K8='설정'!$B$8),SUBSTITUTE(K8,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G8)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G8)),"화목","반")),K8)))</f>
         <v/>
       </c>
       <c r="P8" s="30">
@@ -23221,7 +23221,7 @@
       <c r="M9" s="7" t="n"/>
       <c r="N9" s="7" t="n"/>
       <c r="O9" s="27">
-        <f>IF(M9&lt;&gt;"",M9,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K9&lt;&gt;""),'설정'!$B$10,IF(OR(K9='설정'!$B$6,K9='설정'!$B$8),SUBSTITUTE(K9,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G9)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G9)),"화목","반")),K9)))</f>
+        <f>IF(M9&lt;&gt;"",M9,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K9&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K9="","미응시",SUBSTITUTE(K9,"반",""))&amp;")",IF(OR(K9='설정'!$B$6,K9='설정'!$B$8),SUBSTITUTE(K9,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G9)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G9)),"화목","반")),K9)))</f>
         <v/>
       </c>
       <c r="P9" s="30">
@@ -23312,7 +23312,7 @@
       <c r="M10" s="7" t="n"/>
       <c r="N10" s="7" t="n"/>
       <c r="O10" s="27">
-        <f>IF(M10&lt;&gt;"",M10,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K10&lt;&gt;""),'설정'!$B$10,IF(OR(K10='설정'!$B$6,K10='설정'!$B$8),SUBSTITUTE(K10,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G10)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G10)),"화목","반")),K10)))</f>
+        <f>IF(M10&lt;&gt;"",M10,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K10&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K10="","미응시",SUBSTITUTE(K10,"반",""))&amp;")",IF(OR(K10='설정'!$B$6,K10='설정'!$B$8),SUBSTITUTE(K10,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G10)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G10)),"화목","반")),K10)))</f>
         <v/>
       </c>
       <c r="P10" s="30">
@@ -23403,7 +23403,7 @@
       <c r="M11" s="7" t="n"/>
       <c r="N11" s="7" t="n"/>
       <c r="O11" s="27">
-        <f>IF(M11&lt;&gt;"",M11,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K11&lt;&gt;""),'설정'!$B$10,IF(OR(K11='설정'!$B$6,K11='설정'!$B$8),SUBSTITUTE(K11,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G11)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G11)),"화목","반")),K11)))</f>
+        <f>IF(M11&lt;&gt;"",M11,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K11&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K11="","미응시",SUBSTITUTE(K11,"반",""))&amp;")",IF(OR(K11='설정'!$B$6,K11='설정'!$B$8),SUBSTITUTE(K11,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G11)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G11)),"화목","반")),K11)))</f>
         <v/>
       </c>
       <c r="P11" s="30">
@@ -23495,7 +23495,7 @@
       <c r="M12" s="7" t="n"/>
       <c r="N12" s="7" t="n"/>
       <c r="O12" s="27">
-        <f>IF(M12&lt;&gt;"",M12,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K12&lt;&gt;""),'설정'!$B$10,IF(OR(K12='설정'!$B$6,K12='설정'!$B$8),SUBSTITUTE(K12,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G12)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G12)),"화목","반")),K12)))</f>
+        <f>IF(M12&lt;&gt;"",M12,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K12&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K12="","미응시",SUBSTITUTE(K12,"반",""))&amp;")",IF(OR(K12='설정'!$B$6,K12='설정'!$B$8),SUBSTITUTE(K12,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G12)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G12)),"화목","반")),K12)))</f>
         <v/>
       </c>
       <c r="P12" s="30">
@@ -23507,7 +23507,7 @@
         <v/>
       </c>
       <c r="S12" s="37">
-        <f>IF('설정'!$B$10="","","※ "&amp;'설정'!$B$10&amp;" "&amp;COUNTIF($O$7:$O$156,'설정'!$B$10)&amp;"명은 위 반별 인원에 없음(아래 요일반 표)")</f>
+        <f>IF('설정'!$B$10="","","※ "&amp;'설정'!$B$10&amp;" "&amp;COUNTIF($O$7:$O$156,'설정'!$B$10&amp;"(*")&amp;"명은 위 반별 인원에 없음(아래 요일반 표)")</f>
         <v/>
       </c>
     </row>
@@ -23562,7 +23562,7 @@
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n"/>
       <c r="O13" s="27">
-        <f>IF(M13&lt;&gt;"",M13,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K13&lt;&gt;""),'설정'!$B$10,IF(OR(K13='설정'!$B$6,K13='설정'!$B$8),SUBSTITUTE(K13,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G13)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G13)),"화목","반")),K13)))</f>
+        <f>IF(M13&lt;&gt;"",M13,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K13&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K13="","미응시",SUBSTITUTE(K13,"반",""))&amp;")",IF(OR(K13='설정'!$B$6,K13='설정'!$B$8),SUBSTITUTE(K13,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G13)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G13)),"화목","반")),K13)))</f>
         <v/>
       </c>
       <c r="P13" s="30">
@@ -23577,7 +23577,7 @@
         <is>
           <t>· 자동배정은 '설정' ①의 기준(공수1 점수·한 과목 점수·합계)
 · 경계 = 과목 점수나 합계가 기준 점수와 경계 범위 이내
-· 공통수학반(최종): '자사/일반'에 학교가 적힌 학생은 '설정' B10 반, 그 외 TF1·TF2는 등원 요일에 따라 월금/화목
+· 공통수학반(최종): '자사/일반'에 학교가 적힌 학생은 '설정' B10 반(괄호 안은 성적상 반), 그 외 TF1·TF2는 등원 요일에 따라 월금/화목
 · 공통수학반·선행반은 목록에서 고르거나 직접 입력('설정' ⑥·⑦에 반 소개 추가 가능)
 · 환산총점·석차는 참고용</t>
         </is>
@@ -23634,7 +23634,7 @@
       <c r="M14" s="7" t="n"/>
       <c r="N14" s="7" t="n"/>
       <c r="O14" s="27">
-        <f>IF(M14&lt;&gt;"",M14,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K14&lt;&gt;""),'설정'!$B$10,IF(OR(K14='설정'!$B$6,K14='설정'!$B$8),SUBSTITUTE(K14,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G14)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G14)),"화목","반")),K14)))</f>
+        <f>IF(M14&lt;&gt;"",M14,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K14&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K14="","미응시",SUBSTITUTE(K14,"반",""))&amp;")",IF(OR(K14='설정'!$B$6,K14='설정'!$B$8),SUBSTITUTE(K14,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G14)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G14)),"화목","반")),K14)))</f>
         <v/>
       </c>
       <c r="P14" s="30">
@@ -23697,7 +23697,7 @@
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
       <c r="O15" s="27">
-        <f>IF(M15&lt;&gt;"",M15,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K15&lt;&gt;""),'설정'!$B$10,IF(OR(K15='설정'!$B$6,K15='설정'!$B$8),SUBSTITUTE(K15,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G15)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G15)),"화목","반")),K15)))</f>
+        <f>IF(M15&lt;&gt;"",M15,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K15&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K15="","미응시",SUBSTITUTE(K15,"반",""))&amp;")",IF(OR(K15='설정'!$B$6,K15='설정'!$B$8),SUBSTITUTE(K15,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G15)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G15)),"화목","반")),K15)))</f>
         <v/>
       </c>
       <c r="P15" s="30">
@@ -23760,7 +23760,7 @@
       <c r="M16" s="7" t="n"/>
       <c r="N16" s="7" t="n"/>
       <c r="O16" s="27">
-        <f>IF(M16&lt;&gt;"",M16,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K16&lt;&gt;""),'설정'!$B$10,IF(OR(K16='설정'!$B$6,K16='설정'!$B$8),SUBSTITUTE(K16,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G16)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G16)),"화목","반")),K16)))</f>
+        <f>IF(M16&lt;&gt;"",M16,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K16&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K16="","미응시",SUBSTITUTE(K16,"반",""))&amp;")",IF(OR(K16='설정'!$B$6,K16='설정'!$B$8),SUBSTITUTE(K16,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G16)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G16)),"화목","반")),K16)))</f>
         <v/>
       </c>
       <c r="P16" s="30">
@@ -23823,7 +23823,7 @@
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="7" t="n"/>
       <c r="O17" s="27">
-        <f>IF(M17&lt;&gt;"",M17,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K17&lt;&gt;""),'설정'!$B$10,IF(OR(K17='설정'!$B$6,K17='설정'!$B$8),SUBSTITUTE(K17,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G17)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G17)),"화목","반")),K17)))</f>
+        <f>IF(M17&lt;&gt;"",M17,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K17&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K17="","미응시",SUBSTITUTE(K17,"반",""))&amp;")",IF(OR(K17='설정'!$B$6,K17='설정'!$B$8),SUBSTITUTE(K17,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G17)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G17)),"화목","반")),K17)))</f>
         <v/>
       </c>
       <c r="P17" s="30">
@@ -23886,7 +23886,7 @@
       <c r="M18" s="7" t="n"/>
       <c r="N18" s="7" t="n"/>
       <c r="O18" s="27">
-        <f>IF(M18&lt;&gt;"",M18,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K18&lt;&gt;""),'설정'!$B$10,IF(OR(K18='설정'!$B$6,K18='설정'!$B$8),SUBSTITUTE(K18,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G18)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G18)),"화목","반")),K18)))</f>
+        <f>IF(M18&lt;&gt;"",M18,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K18&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K18="","미응시",SUBSTITUTE(K18,"반",""))&amp;")",IF(OR(K18='설정'!$B$6,K18='설정'!$B$8),SUBSTITUTE(K18,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G18)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G18)),"화목","반")),K18)))</f>
         <v/>
       </c>
       <c r="P18" s="30">
@@ -23949,7 +23949,7 @@
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n"/>
       <c r="O19" s="27">
-        <f>IF(M19&lt;&gt;"",M19,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K19&lt;&gt;""),'설정'!$B$10,IF(OR(K19='설정'!$B$6,K19='설정'!$B$8),SUBSTITUTE(K19,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G19)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G19)),"화목","반")),K19)))</f>
+        <f>IF(M19&lt;&gt;"",M19,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K19&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K19="","미응시",SUBSTITUTE(K19,"반",""))&amp;")",IF(OR(K19='설정'!$B$6,K19='설정'!$B$8),SUBSTITUTE(K19,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G19)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G19)),"화목","반")),K19)))</f>
         <v/>
       </c>
       <c r="P19" s="30">
@@ -24012,7 +24012,7 @@
       <c r="M20" s="7" t="n"/>
       <c r="N20" s="7" t="n"/>
       <c r="O20" s="27">
-        <f>IF(M20&lt;&gt;"",M20,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K20&lt;&gt;""),'설정'!$B$10,IF(OR(K20='설정'!$B$6,K20='설정'!$B$8),SUBSTITUTE(K20,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G20)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G20)),"화목","반")),K20)))</f>
+        <f>IF(M20&lt;&gt;"",M20,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K20&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K20="","미응시",SUBSTITUTE(K20,"반",""))&amp;")",IF(OR(K20='설정'!$B$6,K20='설정'!$B$8),SUBSTITUTE(K20,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G20)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G20)),"화목","반")),K20)))</f>
         <v/>
       </c>
       <c r="P20" s="30">
@@ -24080,7 +24080,7 @@
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n"/>
       <c r="O21" s="27">
-        <f>IF(M21&lt;&gt;"",M21,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K21&lt;&gt;""),'설정'!$B$10,IF(OR(K21='설정'!$B$6,K21='설정'!$B$8),SUBSTITUTE(K21,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G21)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G21)),"화목","반")),K21)))</f>
+        <f>IF(M21&lt;&gt;"",M21,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K21&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K21="","미응시",SUBSTITUTE(K21,"반",""))&amp;")",IF(OR(K21='설정'!$B$6,K21='설정'!$B$8),SUBSTITUTE(K21,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G21)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G21)),"화목","반")),K21)))</f>
         <v/>
       </c>
       <c r="P21" s="30">
@@ -24165,7 +24165,7 @@
       <c r="M22" s="7" t="n"/>
       <c r="N22" s="7" t="n"/>
       <c r="O22" s="27">
-        <f>IF(M22&lt;&gt;"",M22,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K22&lt;&gt;""),'설정'!$B$10,IF(OR(K22='설정'!$B$6,K22='설정'!$B$8),SUBSTITUTE(K22,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G22)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G22)),"화목","반")),K22)))</f>
+        <f>IF(M22&lt;&gt;"",M22,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K22&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K22="","미응시",SUBSTITUTE(K22,"반",""))&amp;")",IF(OR(K22='설정'!$B$6,K22='설정'!$B$8),SUBSTITUTE(K22,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G22)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G22)),"화목","반")),K22)))</f>
         <v/>
       </c>
       <c r="P22" s="30">
@@ -24181,15 +24181,15 @@
         <v/>
       </c>
       <c r="T22" s="27">
-        <f>COUNTIF($O$7:$O$156,S22)</f>
+        <f>COUNTIF($O$7:$O$156,S22&amp;"(*")</f>
         <v/>
       </c>
       <c r="U22" s="32">
-        <f>IFERROR(AVERAGEIF($O$7:$O$156,S22,$G$7:$G$156),"")</f>
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,S22&amp;"(*",$G$7:$G$156),"")</f>
         <v/>
       </c>
       <c r="V22" s="32">
-        <f>IFERROR(AVERAGEIF($O$7:$O$156,S22,$H$7:$H$156),"")</f>
+        <f>IFERROR(AVERAGEIF($O$7:$O$156,S22&amp;"(*",$H$7:$H$156),"")</f>
         <v/>
       </c>
     </row>
@@ -24244,7 +24244,7 @@
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n"/>
       <c r="O23" s="27">
-        <f>IF(M23&lt;&gt;"",M23,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K23&lt;&gt;""),'설정'!$B$10,IF(OR(K23='설정'!$B$6,K23='설정'!$B$8),SUBSTITUTE(K23,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G23)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G23)),"화목","반")),K23)))</f>
+        <f>IF(M23&lt;&gt;"",M23,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K23&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K23="","미응시",SUBSTITUTE(K23,"반",""))&amp;")",IF(OR(K23='설정'!$B$6,K23='설정'!$B$8),SUBSTITUTE(K23,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G23)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G23)),"화목","반")),K23)))</f>
         <v/>
       </c>
       <c r="P23" s="30">
@@ -24323,7 +24323,7 @@
       <c r="M24" s="7" t="n"/>
       <c r="N24" s="7" t="n"/>
       <c r="O24" s="27">
-        <f>IF(M24&lt;&gt;"",M24,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K24&lt;&gt;""),'설정'!$B$10,IF(OR(K24='설정'!$B$6,K24='설정'!$B$8),SUBSTITUTE(K24,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G24)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G24)),"화목","반")),K24)))</f>
+        <f>IF(M24&lt;&gt;"",M24,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K24&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K24="","미응시",SUBSTITUTE(K24,"반",""))&amp;")",IF(OR(K24='설정'!$B$6,K24='설정'!$B$8),SUBSTITUTE(K24,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G24)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G24)),"화목","반")),K24)))</f>
         <v/>
       </c>
       <c r="P24" s="30">
@@ -24402,7 +24402,7 @@
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
       <c r="O25" s="27">
-        <f>IF(M25&lt;&gt;"",M25,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K25&lt;&gt;""),'설정'!$B$10,IF(OR(K25='설정'!$B$6,K25='설정'!$B$8),SUBSTITUTE(K25,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G25)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G25)),"화목","반")),K25)))</f>
+        <f>IF(M25&lt;&gt;"",M25,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K25&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K25="","미응시",SUBSTITUTE(K25,"반",""))&amp;")",IF(OR(K25='설정'!$B$6,K25='설정'!$B$8),SUBSTITUTE(K25,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G25)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G25)),"화목","반")),K25)))</f>
         <v/>
       </c>
       <c r="P25" s="30">
@@ -24481,7 +24481,7 @@
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="7" t="n"/>
       <c r="O26" s="27">
-        <f>IF(M26&lt;&gt;"",M26,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K26&lt;&gt;""),'설정'!$B$10,IF(OR(K26='설정'!$B$6,K26='설정'!$B$8),SUBSTITUTE(K26,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G26)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G26)),"화목","반")),K26)))</f>
+        <f>IF(M26&lt;&gt;"",M26,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K26&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K26="","미응시",SUBSTITUTE(K26,"반",""))&amp;")",IF(OR(K26='설정'!$B$6,K26='설정'!$B$8),SUBSTITUTE(K26,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G26)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G26)),"화목","반")),K26)))</f>
         <v/>
       </c>
       <c r="P26" s="30">
@@ -24560,7 +24560,7 @@
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
       <c r="O27" s="27">
-        <f>IF(M27&lt;&gt;"",M27,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K27&lt;&gt;""),'설정'!$B$10,IF(OR(K27='설정'!$B$6,K27='설정'!$B$8),SUBSTITUTE(K27,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G27)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G27)),"화목","반")),K27)))</f>
+        <f>IF(M27&lt;&gt;"",M27,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K27&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K27="","미응시",SUBSTITUTE(K27,"반",""))&amp;")",IF(OR(K27='설정'!$B$6,K27='설정'!$B$8),SUBSTITUTE(K27,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G27)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G27)),"화목","반")),K27)))</f>
         <v/>
       </c>
       <c r="P27" s="30">
@@ -24623,7 +24623,7 @@
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="7" t="n"/>
       <c r="O28" s="27">
-        <f>IF(M28&lt;&gt;"",M28,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K28&lt;&gt;""),'설정'!$B$10,IF(OR(K28='설정'!$B$6,K28='설정'!$B$8),SUBSTITUTE(K28,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G28)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G28)),"화목","반")),K28)))</f>
+        <f>IF(M28&lt;&gt;"",M28,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K28&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K28="","미응시",SUBSTITUTE(K28,"반",""))&amp;")",IF(OR(K28='설정'!$B$6,K28='설정'!$B$8),SUBSTITUTE(K28,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G28)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G28)),"화목","반")),K28)))</f>
         <v/>
       </c>
       <c r="P28" s="30">
@@ -24686,7 +24686,7 @@
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
       <c r="O29" s="27">
-        <f>IF(M29&lt;&gt;"",M29,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K29&lt;&gt;""),'설정'!$B$10,IF(OR(K29='설정'!$B$6,K29='설정'!$B$8),SUBSTITUTE(K29,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G29)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G29)),"화목","반")),K29)))</f>
+        <f>IF(M29&lt;&gt;"",M29,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K29&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K29="","미응시",SUBSTITUTE(K29,"반",""))&amp;")",IF(OR(K29='설정'!$B$6,K29='설정'!$B$8),SUBSTITUTE(K29,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G29)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G29)),"화목","반")),K29)))</f>
         <v/>
       </c>
       <c r="P29" s="30">
@@ -24749,7 +24749,7 @@
       <c r="M30" s="7" t="n"/>
       <c r="N30" s="7" t="n"/>
       <c r="O30" s="27">
-        <f>IF(M30&lt;&gt;"",M30,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K30&lt;&gt;""),'설정'!$B$10,IF(OR(K30='설정'!$B$6,K30='설정'!$B$8),SUBSTITUTE(K30,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G30)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G30)),"화목","반")),K30)))</f>
+        <f>IF(M30&lt;&gt;"",M30,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K30&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K30="","미응시",SUBSTITUTE(K30,"반",""))&amp;")",IF(OR(K30='설정'!$B$6,K30='설정'!$B$8),SUBSTITUTE(K30,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G30)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G30)),"화목","반")),K30)))</f>
         <v/>
       </c>
       <c r="P30" s="30">
@@ -24812,7 +24812,7 @@
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n"/>
       <c r="O31" s="27">
-        <f>IF(M31&lt;&gt;"",M31,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K31&lt;&gt;""),'설정'!$B$10,IF(OR(K31='설정'!$B$6,K31='설정'!$B$8),SUBSTITUTE(K31,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G31)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G31)),"화목","반")),K31)))</f>
+        <f>IF(M31&lt;&gt;"",M31,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K31&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K31="","미응시",SUBSTITUTE(K31,"반",""))&amp;")",IF(OR(K31='설정'!$B$6,K31='설정'!$B$8),SUBSTITUTE(K31,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G31)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G31)),"화목","반")),K31)))</f>
         <v/>
       </c>
       <c r="P31" s="30">
@@ -24875,7 +24875,7 @@
       <c r="M32" s="7" t="n"/>
       <c r="N32" s="7" t="n"/>
       <c r="O32" s="27">
-        <f>IF(M32&lt;&gt;"",M32,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K32&lt;&gt;""),'설정'!$B$10,IF(OR(K32='설정'!$B$6,K32='설정'!$B$8),SUBSTITUTE(K32,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G32)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G32)),"화목","반")),K32)))</f>
+        <f>IF(M32&lt;&gt;"",M32,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K32&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K32="","미응시",SUBSTITUTE(K32,"반",""))&amp;")",IF(OR(K32='설정'!$B$6,K32='설정'!$B$8),SUBSTITUTE(K32,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G32)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G32)),"화목","반")),K32)))</f>
         <v/>
       </c>
       <c r="P32" s="30">
@@ -24938,7 +24938,7 @@
       <c r="M33" s="7" t="n"/>
       <c r="N33" s="7" t="n"/>
       <c r="O33" s="27">
-        <f>IF(M33&lt;&gt;"",M33,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K33&lt;&gt;""),'설정'!$B$10,IF(OR(K33='설정'!$B$6,K33='설정'!$B$8),SUBSTITUTE(K33,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G33)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G33)),"화목","반")),K33)))</f>
+        <f>IF(M33&lt;&gt;"",M33,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K33&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K33="","미응시",SUBSTITUTE(K33,"반",""))&amp;")",IF(OR(K33='설정'!$B$6,K33='설정'!$B$8),SUBSTITUTE(K33,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G33)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G33)),"화목","반")),K33)))</f>
         <v/>
       </c>
       <c r="P33" s="30">
@@ -25001,7 +25001,7 @@
       <c r="M34" s="7" t="n"/>
       <c r="N34" s="7" t="n"/>
       <c r="O34" s="27">
-        <f>IF(M34&lt;&gt;"",M34,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K34&lt;&gt;""),'설정'!$B$10,IF(OR(K34='설정'!$B$6,K34='설정'!$B$8),SUBSTITUTE(K34,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G34)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G34)),"화목","반")),K34)))</f>
+        <f>IF(M34&lt;&gt;"",M34,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K34&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K34="","미응시",SUBSTITUTE(K34,"반",""))&amp;")",IF(OR(K34='설정'!$B$6,K34='설정'!$B$8),SUBSTITUTE(K34,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G34)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G34)),"화목","반")),K34)))</f>
         <v/>
       </c>
       <c r="P34" s="30">
@@ -25064,7 +25064,7 @@
       <c r="M35" s="7" t="n"/>
       <c r="N35" s="7" t="n"/>
       <c r="O35" s="27">
-        <f>IF(M35&lt;&gt;"",M35,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K35&lt;&gt;""),'설정'!$B$10,IF(OR(K35='설정'!$B$6,K35='설정'!$B$8),SUBSTITUTE(K35,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G35)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G35)),"화목","반")),K35)))</f>
+        <f>IF(M35&lt;&gt;"",M35,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K35&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K35="","미응시",SUBSTITUTE(K35,"반",""))&amp;")",IF(OR(K35='설정'!$B$6,K35='설정'!$B$8),SUBSTITUTE(K35,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G35)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G35)),"화목","반")),K35)))</f>
         <v/>
       </c>
       <c r="P35" s="30">
@@ -25127,7 +25127,7 @@
       <c r="M36" s="7" t="n"/>
       <c r="N36" s="7" t="n"/>
       <c r="O36" s="27">
-        <f>IF(M36&lt;&gt;"",M36,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K36&lt;&gt;""),'설정'!$B$10,IF(OR(K36='설정'!$B$6,K36='설정'!$B$8),SUBSTITUTE(K36,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G36)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G36)),"화목","반")),K36)))</f>
+        <f>IF(M36&lt;&gt;"",M36,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K36&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K36="","미응시",SUBSTITUTE(K36,"반",""))&amp;")",IF(OR(K36='설정'!$B$6,K36='설정'!$B$8),SUBSTITUTE(K36,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G36)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G36)),"화목","반")),K36)))</f>
         <v/>
       </c>
       <c r="P36" s="30">
@@ -25190,7 +25190,7 @@
       <c r="M37" s="7" t="n"/>
       <c r="N37" s="7" t="n"/>
       <c r="O37" s="27">
-        <f>IF(M37&lt;&gt;"",M37,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K37&lt;&gt;""),'설정'!$B$10,IF(OR(K37='설정'!$B$6,K37='설정'!$B$8),SUBSTITUTE(K37,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G37)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G37)),"화목","반")),K37)))</f>
+        <f>IF(M37&lt;&gt;"",M37,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K37&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K37="","미응시",SUBSTITUTE(K37,"반",""))&amp;")",IF(OR(K37='설정'!$B$6,K37='설정'!$B$8),SUBSTITUTE(K37,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G37)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G37)),"화목","반")),K37)))</f>
         <v/>
       </c>
       <c r="P37" s="30">
@@ -25253,7 +25253,7 @@
       <c r="M38" s="7" t="n"/>
       <c r="N38" s="7" t="n"/>
       <c r="O38" s="27">
-        <f>IF(M38&lt;&gt;"",M38,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K38&lt;&gt;""),'설정'!$B$10,IF(OR(K38='설정'!$B$6,K38='설정'!$B$8),SUBSTITUTE(K38,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G38)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G38)),"화목","반")),K38)))</f>
+        <f>IF(M38&lt;&gt;"",M38,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K38&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K38="","미응시",SUBSTITUTE(K38,"반",""))&amp;")",IF(OR(K38='설정'!$B$6,K38='설정'!$B$8),SUBSTITUTE(K38,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G38)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G38)),"화목","반")),K38)))</f>
         <v/>
       </c>
       <c r="P38" s="30">
@@ -25316,7 +25316,7 @@
       <c r="M39" s="7" t="n"/>
       <c r="N39" s="7" t="n"/>
       <c r="O39" s="27">
-        <f>IF(M39&lt;&gt;"",M39,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K39&lt;&gt;""),'설정'!$B$10,IF(OR(K39='설정'!$B$6,K39='설정'!$B$8),SUBSTITUTE(K39,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G39)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G39)),"화목","반")),K39)))</f>
+        <f>IF(M39&lt;&gt;"",M39,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K39&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K39="","미응시",SUBSTITUTE(K39,"반",""))&amp;")",IF(OR(K39='설정'!$B$6,K39='설정'!$B$8),SUBSTITUTE(K39,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G39)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G39)),"화목","반")),K39)))</f>
         <v/>
       </c>
       <c r="P39" s="30">
@@ -25379,7 +25379,7 @@
       <c r="M40" s="7" t="n"/>
       <c r="N40" s="7" t="n"/>
       <c r="O40" s="27">
-        <f>IF(M40&lt;&gt;"",M40,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K40&lt;&gt;""),'설정'!$B$10,IF(OR(K40='설정'!$B$6,K40='설정'!$B$8),SUBSTITUTE(K40,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G40)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G40)),"화목","반")),K40)))</f>
+        <f>IF(M40&lt;&gt;"",M40,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K40&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K40="","미응시",SUBSTITUTE(K40,"반",""))&amp;")",IF(OR(K40='설정'!$B$6,K40='설정'!$B$8),SUBSTITUTE(K40,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G40)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G40)),"화목","반")),K40)))</f>
         <v/>
       </c>
       <c r="P40" s="30">
@@ -25442,7 +25442,7 @@
       <c r="M41" s="7" t="n"/>
       <c r="N41" s="7" t="n"/>
       <c r="O41" s="27">
-        <f>IF(M41&lt;&gt;"",M41,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K41&lt;&gt;""),'설정'!$B$10,IF(OR(K41='설정'!$B$6,K41='설정'!$B$8),SUBSTITUTE(K41,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G41)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G41)),"화목","반")),K41)))</f>
+        <f>IF(M41&lt;&gt;"",M41,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K41&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K41="","미응시",SUBSTITUTE(K41,"반",""))&amp;")",IF(OR(K41='설정'!$B$6,K41='설정'!$B$8),SUBSTITUTE(K41,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G41)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G41)),"화목","반")),K41)))</f>
         <v/>
       </c>
       <c r="P41" s="30">
@@ -25505,7 +25505,7 @@
       <c r="M42" s="7" t="n"/>
       <c r="N42" s="7" t="n"/>
       <c r="O42" s="27">
-        <f>IF(M42&lt;&gt;"",M42,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K42&lt;&gt;""),'설정'!$B$10,IF(OR(K42='설정'!$B$6,K42='설정'!$B$8),SUBSTITUTE(K42,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G42)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G42)),"화목","반")),K42)))</f>
+        <f>IF(M42&lt;&gt;"",M42,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K42&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K42="","미응시",SUBSTITUTE(K42,"반",""))&amp;")",IF(OR(K42='설정'!$B$6,K42='설정'!$B$8),SUBSTITUTE(K42,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G42)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G42)),"화목","반")),K42)))</f>
         <v/>
       </c>
       <c r="P42" s="30">
@@ -25568,7 +25568,7 @@
       <c r="M43" s="7" t="n"/>
       <c r="N43" s="7" t="n"/>
       <c r="O43" s="27">
-        <f>IF(M43&lt;&gt;"",M43,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K43&lt;&gt;""),'설정'!$B$10,IF(OR(K43='설정'!$B$6,K43='설정'!$B$8),SUBSTITUTE(K43,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G43)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G43)),"화목","반")),K43)))</f>
+        <f>IF(M43&lt;&gt;"",M43,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K43&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K43="","미응시",SUBSTITUTE(K43,"반",""))&amp;")",IF(OR(K43='설정'!$B$6,K43='설정'!$B$8),SUBSTITUTE(K43,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G43)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G43)),"화목","반")),K43)))</f>
         <v/>
       </c>
       <c r="P43" s="30">
@@ -25631,7 +25631,7 @@
       <c r="M44" s="7" t="n"/>
       <c r="N44" s="7" t="n"/>
       <c r="O44" s="27">
-        <f>IF(M44&lt;&gt;"",M44,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K44&lt;&gt;""),'설정'!$B$10,IF(OR(K44='설정'!$B$6,K44='설정'!$B$8),SUBSTITUTE(K44,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G44)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G44)),"화목","반")),K44)))</f>
+        <f>IF(M44&lt;&gt;"",M44,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K44&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K44="","미응시",SUBSTITUTE(K44,"반",""))&amp;")",IF(OR(K44='설정'!$B$6,K44='설정'!$B$8),SUBSTITUTE(K44,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G44)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G44)),"화목","반")),K44)))</f>
         <v/>
       </c>
       <c r="P44" s="30">
@@ -25694,7 +25694,7 @@
       <c r="M45" s="7" t="n"/>
       <c r="N45" s="7" t="n"/>
       <c r="O45" s="27">
-        <f>IF(M45&lt;&gt;"",M45,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K45&lt;&gt;""),'설정'!$B$10,IF(OR(K45='설정'!$B$6,K45='설정'!$B$8),SUBSTITUTE(K45,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G45)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G45)),"화목","반")),K45)))</f>
+        <f>IF(M45&lt;&gt;"",M45,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K45&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K45="","미응시",SUBSTITUTE(K45,"반",""))&amp;")",IF(OR(K45='설정'!$B$6,K45='설정'!$B$8),SUBSTITUTE(K45,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G45)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G45)),"화목","반")),K45)))</f>
         <v/>
       </c>
       <c r="P45" s="30">
@@ -25757,7 +25757,7 @@
       <c r="M46" s="7" t="n"/>
       <c r="N46" s="7" t="n"/>
       <c r="O46" s="27">
-        <f>IF(M46&lt;&gt;"",M46,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K46&lt;&gt;""),'설정'!$B$10,IF(OR(K46='설정'!$B$6,K46='설정'!$B$8),SUBSTITUTE(K46,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G46)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G46)),"화목","반")),K46)))</f>
+        <f>IF(M46&lt;&gt;"",M46,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K46&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K46="","미응시",SUBSTITUTE(K46,"반",""))&amp;")",IF(OR(K46='설정'!$B$6,K46='설정'!$B$8),SUBSTITUTE(K46,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G46)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G46)),"화목","반")),K46)))</f>
         <v/>
       </c>
       <c r="P46" s="30">
@@ -25820,7 +25820,7 @@
       <c r="M47" s="7" t="n"/>
       <c r="N47" s="7" t="n"/>
       <c r="O47" s="27">
-        <f>IF(M47&lt;&gt;"",M47,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K47&lt;&gt;""),'설정'!$B$10,IF(OR(K47='설정'!$B$6,K47='설정'!$B$8),SUBSTITUTE(K47,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G47)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G47)),"화목","반")),K47)))</f>
+        <f>IF(M47&lt;&gt;"",M47,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K47&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K47="","미응시",SUBSTITUTE(K47,"반",""))&amp;")",IF(OR(K47='설정'!$B$6,K47='설정'!$B$8),SUBSTITUTE(K47,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G47)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G47)),"화목","반")),K47)))</f>
         <v/>
       </c>
       <c r="P47" s="30">
@@ -25883,7 +25883,7 @@
       <c r="M48" s="7" t="n"/>
       <c r="N48" s="7" t="n"/>
       <c r="O48" s="27">
-        <f>IF(M48&lt;&gt;"",M48,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K48&lt;&gt;""),'설정'!$B$10,IF(OR(K48='설정'!$B$6,K48='설정'!$B$8),SUBSTITUTE(K48,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G48)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G48)),"화목","반")),K48)))</f>
+        <f>IF(M48&lt;&gt;"",M48,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K48&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K48="","미응시",SUBSTITUTE(K48,"반",""))&amp;")",IF(OR(K48='설정'!$B$6,K48='설정'!$B$8),SUBSTITUTE(K48,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G48)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G48)),"화목","반")),K48)))</f>
         <v/>
       </c>
       <c r="P48" s="30">
@@ -25946,7 +25946,7 @@
       <c r="M49" s="7" t="n"/>
       <c r="N49" s="7" t="n"/>
       <c r="O49" s="27">
-        <f>IF(M49&lt;&gt;"",M49,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K49&lt;&gt;""),'설정'!$B$10,IF(OR(K49='설정'!$B$6,K49='설정'!$B$8),SUBSTITUTE(K49,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G49)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G49)),"화목","반")),K49)))</f>
+        <f>IF(M49&lt;&gt;"",M49,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K49&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K49="","미응시",SUBSTITUTE(K49,"반",""))&amp;")",IF(OR(K49='설정'!$B$6,K49='설정'!$B$8),SUBSTITUTE(K49,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G49)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G49)),"화목","반")),K49)))</f>
         <v/>
       </c>
       <c r="P49" s="30">
@@ -26009,7 +26009,7 @@
       <c r="M50" s="7" t="n"/>
       <c r="N50" s="7" t="n"/>
       <c r="O50" s="27">
-        <f>IF(M50&lt;&gt;"",M50,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K50&lt;&gt;""),'설정'!$B$10,IF(OR(K50='설정'!$B$6,K50='설정'!$B$8),SUBSTITUTE(K50,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G50)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G50)),"화목","반")),K50)))</f>
+        <f>IF(M50&lt;&gt;"",M50,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K50&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K50="","미응시",SUBSTITUTE(K50,"반",""))&amp;")",IF(OR(K50='설정'!$B$6,K50='설정'!$B$8),SUBSTITUTE(K50,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G50)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G50)),"화목","반")),K50)))</f>
         <v/>
       </c>
       <c r="P50" s="30">
@@ -26072,7 +26072,7 @@
       <c r="M51" s="7" t="n"/>
       <c r="N51" s="7" t="n"/>
       <c r="O51" s="27">
-        <f>IF(M51&lt;&gt;"",M51,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K51&lt;&gt;""),'설정'!$B$10,IF(OR(K51='설정'!$B$6,K51='설정'!$B$8),SUBSTITUTE(K51,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G51)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G51)),"화목","반")),K51)))</f>
+        <f>IF(M51&lt;&gt;"",M51,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K51&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K51="","미응시",SUBSTITUTE(K51,"반",""))&amp;")",IF(OR(K51='설정'!$B$6,K51='설정'!$B$8),SUBSTITUTE(K51,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G51)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G51)),"화목","반")),K51)))</f>
         <v/>
       </c>
       <c r="P51" s="30">
@@ -26135,7 +26135,7 @@
       <c r="M52" s="7" t="n"/>
       <c r="N52" s="7" t="n"/>
       <c r="O52" s="27">
-        <f>IF(M52&lt;&gt;"",M52,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K52&lt;&gt;""),'설정'!$B$10,IF(OR(K52='설정'!$B$6,K52='설정'!$B$8),SUBSTITUTE(K52,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G52)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G52)),"화목","반")),K52)))</f>
+        <f>IF(M52&lt;&gt;"",M52,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K52&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K52="","미응시",SUBSTITUTE(K52,"반",""))&amp;")",IF(OR(K52='설정'!$B$6,K52='설정'!$B$8),SUBSTITUTE(K52,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G52)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G52)),"화목","반")),K52)))</f>
         <v/>
       </c>
       <c r="P52" s="30">
@@ -26198,7 +26198,7 @@
       <c r="M53" s="7" t="n"/>
       <c r="N53" s="7" t="n"/>
       <c r="O53" s="27">
-        <f>IF(M53&lt;&gt;"",M53,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K53&lt;&gt;""),'설정'!$B$10,IF(OR(K53='설정'!$B$6,K53='설정'!$B$8),SUBSTITUTE(K53,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G53)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G53)),"화목","반")),K53)))</f>
+        <f>IF(M53&lt;&gt;"",M53,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K53&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K53="","미응시",SUBSTITUTE(K53,"반",""))&amp;")",IF(OR(K53='설정'!$B$6,K53='설정'!$B$8),SUBSTITUTE(K53,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G53)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G53)),"화목","반")),K53)))</f>
         <v/>
       </c>
       <c r="P53" s="30">
@@ -26261,7 +26261,7 @@
       <c r="M54" s="7" t="n"/>
       <c r="N54" s="7" t="n"/>
       <c r="O54" s="27">
-        <f>IF(M54&lt;&gt;"",M54,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K54&lt;&gt;""),'설정'!$B$10,IF(OR(K54='설정'!$B$6,K54='설정'!$B$8),SUBSTITUTE(K54,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G54)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G54)),"화목","반")),K54)))</f>
+        <f>IF(M54&lt;&gt;"",M54,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K54&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K54="","미응시",SUBSTITUTE(K54,"반",""))&amp;")",IF(OR(K54='설정'!$B$6,K54='설정'!$B$8),SUBSTITUTE(K54,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G54)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G54)),"화목","반")),K54)))</f>
         <v/>
       </c>
       <c r="P54" s="30">
@@ -26324,7 +26324,7 @@
       <c r="M55" s="7" t="n"/>
       <c r="N55" s="7" t="n"/>
       <c r="O55" s="27">
-        <f>IF(M55&lt;&gt;"",M55,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K55&lt;&gt;""),'설정'!$B$10,IF(OR(K55='설정'!$B$6,K55='설정'!$B$8),SUBSTITUTE(K55,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G55)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G55)),"화목","반")),K55)))</f>
+        <f>IF(M55&lt;&gt;"",M55,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K55&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K55="","미응시",SUBSTITUTE(K55,"반",""))&amp;")",IF(OR(K55='설정'!$B$6,K55='설정'!$B$8),SUBSTITUTE(K55,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G55)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G55)),"화목","반")),K55)))</f>
         <v/>
       </c>
       <c r="P55" s="30">
@@ -26387,7 +26387,7 @@
       <c r="M56" s="7" t="n"/>
       <c r="N56" s="7" t="n"/>
       <c r="O56" s="27">
-        <f>IF(M56&lt;&gt;"",M56,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K56&lt;&gt;""),'설정'!$B$10,IF(OR(K56='설정'!$B$6,K56='설정'!$B$8),SUBSTITUTE(K56,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G56)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G56)),"화목","반")),K56)))</f>
+        <f>IF(M56&lt;&gt;"",M56,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K56&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K56="","미응시",SUBSTITUTE(K56,"반",""))&amp;")",IF(OR(K56='설정'!$B$6,K56='설정'!$B$8),SUBSTITUTE(K56,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G56)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G56)),"화목","반")),K56)))</f>
         <v/>
       </c>
       <c r="P56" s="30">
@@ -26450,7 +26450,7 @@
       <c r="M57" s="7" t="n"/>
       <c r="N57" s="7" t="n"/>
       <c r="O57" s="27">
-        <f>IF(M57&lt;&gt;"",M57,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K57&lt;&gt;""),'설정'!$B$10,IF(OR(K57='설정'!$B$6,K57='설정'!$B$8),SUBSTITUTE(K57,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G57)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G57)),"화목","반")),K57)))</f>
+        <f>IF(M57&lt;&gt;"",M57,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K57&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K57="","미응시",SUBSTITUTE(K57,"반",""))&amp;")",IF(OR(K57='설정'!$B$6,K57='설정'!$B$8),SUBSTITUTE(K57,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G57)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G57)),"화목","반")),K57)))</f>
         <v/>
       </c>
       <c r="P57" s="30">
@@ -26513,7 +26513,7 @@
       <c r="M58" s="7" t="n"/>
       <c r="N58" s="7" t="n"/>
       <c r="O58" s="27">
-        <f>IF(M58&lt;&gt;"",M58,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K58&lt;&gt;""),'설정'!$B$10,IF(OR(K58='설정'!$B$6,K58='설정'!$B$8),SUBSTITUTE(K58,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G58)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G58)),"화목","반")),K58)))</f>
+        <f>IF(M58&lt;&gt;"",M58,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K58&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K58="","미응시",SUBSTITUTE(K58,"반",""))&amp;")",IF(OR(K58='설정'!$B$6,K58='설정'!$B$8),SUBSTITUTE(K58,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G58)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G58)),"화목","반")),K58)))</f>
         <v/>
       </c>
       <c r="P58" s="30">
@@ -26576,7 +26576,7 @@
       <c r="M59" s="7" t="n"/>
       <c r="N59" s="7" t="n"/>
       <c r="O59" s="27">
-        <f>IF(M59&lt;&gt;"",M59,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K59&lt;&gt;""),'설정'!$B$10,IF(OR(K59='설정'!$B$6,K59='설정'!$B$8),SUBSTITUTE(K59,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G59)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G59)),"화목","반")),K59)))</f>
+        <f>IF(M59&lt;&gt;"",M59,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K59&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K59="","미응시",SUBSTITUTE(K59,"반",""))&amp;")",IF(OR(K59='설정'!$B$6,K59='설정'!$B$8),SUBSTITUTE(K59,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G59)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G59)),"화목","반")),K59)))</f>
         <v/>
       </c>
       <c r="P59" s="30">
@@ -26639,7 +26639,7 @@
       <c r="M60" s="7" t="n"/>
       <c r="N60" s="7" t="n"/>
       <c r="O60" s="27">
-        <f>IF(M60&lt;&gt;"",M60,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K60&lt;&gt;""),'설정'!$B$10,IF(OR(K60='설정'!$B$6,K60='설정'!$B$8),SUBSTITUTE(K60,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G60)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G60)),"화목","반")),K60)))</f>
+        <f>IF(M60&lt;&gt;"",M60,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K60&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K60="","미응시",SUBSTITUTE(K60,"반",""))&amp;")",IF(OR(K60='설정'!$B$6,K60='설정'!$B$8),SUBSTITUTE(K60,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G60)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G60)),"화목","반")),K60)))</f>
         <v/>
       </c>
       <c r="P60" s="30">
@@ -26702,7 +26702,7 @@
       <c r="M61" s="7" t="n"/>
       <c r="N61" s="7" t="n"/>
       <c r="O61" s="27">
-        <f>IF(M61&lt;&gt;"",M61,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K61&lt;&gt;""),'설정'!$B$10,IF(OR(K61='설정'!$B$6,K61='설정'!$B$8),SUBSTITUTE(K61,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G61)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G61)),"화목","반")),K61)))</f>
+        <f>IF(M61&lt;&gt;"",M61,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K61&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K61="","미응시",SUBSTITUTE(K61,"반",""))&amp;")",IF(OR(K61='설정'!$B$6,K61='설정'!$B$8),SUBSTITUTE(K61,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G61)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G61)),"화목","반")),K61)))</f>
         <v/>
       </c>
       <c r="P61" s="30">
@@ -26765,7 +26765,7 @@
       <c r="M62" s="7" t="n"/>
       <c r="N62" s="7" t="n"/>
       <c r="O62" s="27">
-        <f>IF(M62&lt;&gt;"",M62,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K62&lt;&gt;""),'설정'!$B$10,IF(OR(K62='설정'!$B$6,K62='설정'!$B$8),SUBSTITUTE(K62,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G62)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G62)),"화목","반")),K62)))</f>
+        <f>IF(M62&lt;&gt;"",M62,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K62&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K62="","미응시",SUBSTITUTE(K62,"반",""))&amp;")",IF(OR(K62='설정'!$B$6,K62='설정'!$B$8),SUBSTITUTE(K62,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G62)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G62)),"화목","반")),K62)))</f>
         <v/>
       </c>
       <c r="P62" s="30">
@@ -26828,7 +26828,7 @@
       <c r="M63" s="7" t="n"/>
       <c r="N63" s="7" t="n"/>
       <c r="O63" s="27">
-        <f>IF(M63&lt;&gt;"",M63,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K63&lt;&gt;""),'설정'!$B$10,IF(OR(K63='설정'!$B$6,K63='설정'!$B$8),SUBSTITUTE(K63,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G63)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G63)),"화목","반")),K63)))</f>
+        <f>IF(M63&lt;&gt;"",M63,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K63&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K63="","미응시",SUBSTITUTE(K63,"반",""))&amp;")",IF(OR(K63='설정'!$B$6,K63='설정'!$B$8),SUBSTITUTE(K63,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G63)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G63)),"화목","반")),K63)))</f>
         <v/>
       </c>
       <c r="P63" s="30">
@@ -26891,7 +26891,7 @@
       <c r="M64" s="7" t="n"/>
       <c r="N64" s="7" t="n"/>
       <c r="O64" s="27">
-        <f>IF(M64&lt;&gt;"",M64,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K64&lt;&gt;""),'설정'!$B$10,IF(OR(K64='설정'!$B$6,K64='설정'!$B$8),SUBSTITUTE(K64,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G64)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G64)),"화목","반")),K64)))</f>
+        <f>IF(M64&lt;&gt;"",M64,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K64&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K64="","미응시",SUBSTITUTE(K64,"반",""))&amp;")",IF(OR(K64='설정'!$B$6,K64='설정'!$B$8),SUBSTITUTE(K64,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G64)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G64)),"화목","반")),K64)))</f>
         <v/>
       </c>
       <c r="P64" s="30">
@@ -26954,7 +26954,7 @@
       <c r="M65" s="7" t="n"/>
       <c r="N65" s="7" t="n"/>
       <c r="O65" s="27">
-        <f>IF(M65&lt;&gt;"",M65,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K65&lt;&gt;""),'설정'!$B$10,IF(OR(K65='설정'!$B$6,K65='설정'!$B$8),SUBSTITUTE(K65,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G65)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G65)),"화목","반")),K65)))</f>
+        <f>IF(M65&lt;&gt;"",M65,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K65&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K65="","미응시",SUBSTITUTE(K65,"반",""))&amp;")",IF(OR(K65='설정'!$B$6,K65='설정'!$B$8),SUBSTITUTE(K65,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G65)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G65)),"화목","반")),K65)))</f>
         <v/>
       </c>
       <c r="P65" s="30">
@@ -27017,7 +27017,7 @@
       <c r="M66" s="7" t="n"/>
       <c r="N66" s="7" t="n"/>
       <c r="O66" s="27">
-        <f>IF(M66&lt;&gt;"",M66,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K66&lt;&gt;""),'설정'!$B$10,IF(OR(K66='설정'!$B$6,K66='설정'!$B$8),SUBSTITUTE(K66,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G66)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G66)),"화목","반")),K66)))</f>
+        <f>IF(M66&lt;&gt;"",M66,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K66&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K66="","미응시",SUBSTITUTE(K66,"반",""))&amp;")",IF(OR(K66='설정'!$B$6,K66='설정'!$B$8),SUBSTITUTE(K66,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G66)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G66)),"화목","반")),K66)))</f>
         <v/>
       </c>
       <c r="P66" s="30">
@@ -27080,7 +27080,7 @@
       <c r="M67" s="7" t="n"/>
       <c r="N67" s="7" t="n"/>
       <c r="O67" s="27">
-        <f>IF(M67&lt;&gt;"",M67,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K67&lt;&gt;""),'설정'!$B$10,IF(OR(K67='설정'!$B$6,K67='설정'!$B$8),SUBSTITUTE(K67,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G67)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G67)),"화목","반")),K67)))</f>
+        <f>IF(M67&lt;&gt;"",M67,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K67&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K67="","미응시",SUBSTITUTE(K67,"반",""))&amp;")",IF(OR(K67='설정'!$B$6,K67='설정'!$B$8),SUBSTITUTE(K67,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G67)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G67)),"화목","반")),K67)))</f>
         <v/>
       </c>
       <c r="P67" s="30">
@@ -27143,7 +27143,7 @@
       <c r="M68" s="7" t="n"/>
       <c r="N68" s="7" t="n"/>
       <c r="O68" s="27">
-        <f>IF(M68&lt;&gt;"",M68,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K68&lt;&gt;""),'설정'!$B$10,IF(OR(K68='설정'!$B$6,K68='설정'!$B$8),SUBSTITUTE(K68,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G68)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G68)),"화목","반")),K68)))</f>
+        <f>IF(M68&lt;&gt;"",M68,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K68&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K68="","미응시",SUBSTITUTE(K68,"반",""))&amp;")",IF(OR(K68='설정'!$B$6,K68='설정'!$B$8),SUBSTITUTE(K68,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G68)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G68)),"화목","반")),K68)))</f>
         <v/>
       </c>
       <c r="P68" s="30">
@@ -27206,7 +27206,7 @@
       <c r="M69" s="7" t="n"/>
       <c r="N69" s="7" t="n"/>
       <c r="O69" s="27">
-        <f>IF(M69&lt;&gt;"",M69,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K69&lt;&gt;""),'설정'!$B$10,IF(OR(K69='설정'!$B$6,K69='설정'!$B$8),SUBSTITUTE(K69,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G69)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G69)),"화목","반")),K69)))</f>
+        <f>IF(M69&lt;&gt;"",M69,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K69&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K69="","미응시",SUBSTITUTE(K69,"반",""))&amp;")",IF(OR(K69='설정'!$B$6,K69='설정'!$B$8),SUBSTITUTE(K69,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G69)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G69)),"화목","반")),K69)))</f>
         <v/>
       </c>
       <c r="P69" s="30">
@@ -27269,7 +27269,7 @@
       <c r="M70" s="7" t="n"/>
       <c r="N70" s="7" t="n"/>
       <c r="O70" s="27">
-        <f>IF(M70&lt;&gt;"",M70,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K70&lt;&gt;""),'설정'!$B$10,IF(OR(K70='설정'!$B$6,K70='설정'!$B$8),SUBSTITUTE(K70,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G70)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G70)),"화목","반")),K70)))</f>
+        <f>IF(M70&lt;&gt;"",M70,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K70&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K70="","미응시",SUBSTITUTE(K70,"반",""))&amp;")",IF(OR(K70='설정'!$B$6,K70='설정'!$B$8),SUBSTITUTE(K70,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G70)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G70)),"화목","반")),K70)))</f>
         <v/>
       </c>
       <c r="P70" s="30">
@@ -27332,7 +27332,7 @@
       <c r="M71" s="7" t="n"/>
       <c r="N71" s="7" t="n"/>
       <c r="O71" s="27">
-        <f>IF(M71&lt;&gt;"",M71,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K71&lt;&gt;""),'설정'!$B$10,IF(OR(K71='설정'!$B$6,K71='설정'!$B$8),SUBSTITUTE(K71,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G71)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G71)),"화목","반")),K71)))</f>
+        <f>IF(M71&lt;&gt;"",M71,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K71&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K71="","미응시",SUBSTITUTE(K71,"반",""))&amp;")",IF(OR(K71='설정'!$B$6,K71='설정'!$B$8),SUBSTITUTE(K71,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G71)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G71)),"화목","반")),K71)))</f>
         <v/>
       </c>
       <c r="P71" s="30">
@@ -27395,7 +27395,7 @@
       <c r="M72" s="7" t="n"/>
       <c r="N72" s="7" t="n"/>
       <c r="O72" s="27">
-        <f>IF(M72&lt;&gt;"",M72,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K72&lt;&gt;""),'설정'!$B$10,IF(OR(K72='설정'!$B$6,K72='설정'!$B$8),SUBSTITUTE(K72,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G72)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G72)),"화목","반")),K72)))</f>
+        <f>IF(M72&lt;&gt;"",M72,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K72&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K72="","미응시",SUBSTITUTE(K72,"반",""))&amp;")",IF(OR(K72='설정'!$B$6,K72='설정'!$B$8),SUBSTITUTE(K72,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G72)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G72)),"화목","반")),K72)))</f>
         <v/>
       </c>
       <c r="P72" s="30">
@@ -27458,7 +27458,7 @@
       <c r="M73" s="7" t="n"/>
       <c r="N73" s="7" t="n"/>
       <c r="O73" s="27">
-        <f>IF(M73&lt;&gt;"",M73,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K73&lt;&gt;""),'설정'!$B$10,IF(OR(K73='설정'!$B$6,K73='설정'!$B$8),SUBSTITUTE(K73,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G73)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G73)),"화목","반")),K73)))</f>
+        <f>IF(M73&lt;&gt;"",M73,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K73&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K73="","미응시",SUBSTITUTE(K73,"반",""))&amp;")",IF(OR(K73='설정'!$B$6,K73='설정'!$B$8),SUBSTITUTE(K73,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G73)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G73)),"화목","반")),K73)))</f>
         <v/>
       </c>
       <c r="P73" s="30">
@@ -27521,7 +27521,7 @@
       <c r="M74" s="7" t="n"/>
       <c r="N74" s="7" t="n"/>
       <c r="O74" s="27">
-        <f>IF(M74&lt;&gt;"",M74,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K74&lt;&gt;""),'설정'!$B$10,IF(OR(K74='설정'!$B$6,K74='설정'!$B$8),SUBSTITUTE(K74,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G74)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G74)),"화목","반")),K74)))</f>
+        <f>IF(M74&lt;&gt;"",M74,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K74&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K74="","미응시",SUBSTITUTE(K74,"반",""))&amp;")",IF(OR(K74='설정'!$B$6,K74='설정'!$B$8),SUBSTITUTE(K74,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G74)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G74)),"화목","반")),K74)))</f>
         <v/>
       </c>
       <c r="P74" s="30">
@@ -27584,7 +27584,7 @@
       <c r="M75" s="7" t="n"/>
       <c r="N75" s="7" t="n"/>
       <c r="O75" s="27">
-        <f>IF(M75&lt;&gt;"",M75,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K75&lt;&gt;""),'설정'!$B$10,IF(OR(K75='설정'!$B$6,K75='설정'!$B$8),SUBSTITUTE(K75,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G75)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G75)),"화목","반")),K75)))</f>
+        <f>IF(M75&lt;&gt;"",M75,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K75&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K75="","미응시",SUBSTITUTE(K75,"반",""))&amp;")",IF(OR(K75='설정'!$B$6,K75='설정'!$B$8),SUBSTITUTE(K75,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G75)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G75)),"화목","반")),K75)))</f>
         <v/>
       </c>
       <c r="P75" s="30">
@@ -27647,7 +27647,7 @@
       <c r="M76" s="7" t="n"/>
       <c r="N76" s="7" t="n"/>
       <c r="O76" s="27">
-        <f>IF(M76&lt;&gt;"",M76,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K76&lt;&gt;""),'설정'!$B$10,IF(OR(K76='설정'!$B$6,K76='설정'!$B$8),SUBSTITUTE(K76,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G76)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G76)),"화목","반")),K76)))</f>
+        <f>IF(M76&lt;&gt;"",M76,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K76&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K76="","미응시",SUBSTITUTE(K76,"반",""))&amp;")",IF(OR(K76='설정'!$B$6,K76='설정'!$B$8),SUBSTITUTE(K76,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G76)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G76)),"화목","반")),K76)))</f>
         <v/>
       </c>
       <c r="P76" s="30">
@@ -27710,7 +27710,7 @@
       <c r="M77" s="7" t="n"/>
       <c r="N77" s="7" t="n"/>
       <c r="O77" s="27">
-        <f>IF(M77&lt;&gt;"",M77,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K77&lt;&gt;""),'설정'!$B$10,IF(OR(K77='설정'!$B$6,K77='설정'!$B$8),SUBSTITUTE(K77,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G77)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G77)),"화목","반")),K77)))</f>
+        <f>IF(M77&lt;&gt;"",M77,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K77&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K77="","미응시",SUBSTITUTE(K77,"반",""))&amp;")",IF(OR(K77='설정'!$B$6,K77='설정'!$B$8),SUBSTITUTE(K77,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G77)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G77)),"화목","반")),K77)))</f>
         <v/>
       </c>
       <c r="P77" s="30">
@@ -27773,7 +27773,7 @@
       <c r="M78" s="7" t="n"/>
       <c r="N78" s="7" t="n"/>
       <c r="O78" s="27">
-        <f>IF(M78&lt;&gt;"",M78,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K78&lt;&gt;""),'설정'!$B$10,IF(OR(K78='설정'!$B$6,K78='설정'!$B$8),SUBSTITUTE(K78,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G78)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G78)),"화목","반")),K78)))</f>
+        <f>IF(M78&lt;&gt;"",M78,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K78&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K78="","미응시",SUBSTITUTE(K78,"반",""))&amp;")",IF(OR(K78='설정'!$B$6,K78='설정'!$B$8),SUBSTITUTE(K78,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G78)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G78)),"화목","반")),K78)))</f>
         <v/>
       </c>
       <c r="P78" s="30">
@@ -27836,7 +27836,7 @@
       <c r="M79" s="7" t="n"/>
       <c r="N79" s="7" t="n"/>
       <c r="O79" s="27">
-        <f>IF(M79&lt;&gt;"",M79,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K79&lt;&gt;""),'설정'!$B$10,IF(OR(K79='설정'!$B$6,K79='설정'!$B$8),SUBSTITUTE(K79,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G79)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G79)),"화목","반")),K79)))</f>
+        <f>IF(M79&lt;&gt;"",M79,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K79&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K79="","미응시",SUBSTITUTE(K79,"반",""))&amp;")",IF(OR(K79='설정'!$B$6,K79='설정'!$B$8),SUBSTITUTE(K79,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G79)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G79)),"화목","반")),K79)))</f>
         <v/>
       </c>
       <c r="P79" s="30">
@@ -27899,7 +27899,7 @@
       <c r="M80" s="7" t="n"/>
       <c r="N80" s="7" t="n"/>
       <c r="O80" s="27">
-        <f>IF(M80&lt;&gt;"",M80,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K80&lt;&gt;""),'설정'!$B$10,IF(OR(K80='설정'!$B$6,K80='설정'!$B$8),SUBSTITUTE(K80,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G80)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G80)),"화목","반")),K80)))</f>
+        <f>IF(M80&lt;&gt;"",M80,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K80&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K80="","미응시",SUBSTITUTE(K80,"반",""))&amp;")",IF(OR(K80='설정'!$B$6,K80='설정'!$B$8),SUBSTITUTE(K80,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G80)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G80)),"화목","반")),K80)))</f>
         <v/>
       </c>
       <c r="P80" s="30">
@@ -27962,7 +27962,7 @@
       <c r="M81" s="7" t="n"/>
       <c r="N81" s="7" t="n"/>
       <c r="O81" s="27">
-        <f>IF(M81&lt;&gt;"",M81,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K81&lt;&gt;""),'설정'!$B$10,IF(OR(K81='설정'!$B$6,K81='설정'!$B$8),SUBSTITUTE(K81,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G81)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G81)),"화목","반")),K81)))</f>
+        <f>IF(M81&lt;&gt;"",M81,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K81&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K81="","미응시",SUBSTITUTE(K81,"반",""))&amp;")",IF(OR(K81='설정'!$B$6,K81='설정'!$B$8),SUBSTITUTE(K81,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G81)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G81)),"화목","반")),K81)))</f>
         <v/>
       </c>
       <c r="P81" s="30">
@@ -28025,7 +28025,7 @@
       <c r="M82" s="7" t="n"/>
       <c r="N82" s="7" t="n"/>
       <c r="O82" s="27">
-        <f>IF(M82&lt;&gt;"",M82,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K82&lt;&gt;""),'설정'!$B$10,IF(OR(K82='설정'!$B$6,K82='설정'!$B$8),SUBSTITUTE(K82,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G82)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G82)),"화목","반")),K82)))</f>
+        <f>IF(M82&lt;&gt;"",M82,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K82&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K82="","미응시",SUBSTITUTE(K82,"반",""))&amp;")",IF(OR(K82='설정'!$B$6,K82='설정'!$B$8),SUBSTITUTE(K82,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G82)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G82)),"화목","반")),K82)))</f>
         <v/>
       </c>
       <c r="P82" s="30">
@@ -28088,7 +28088,7 @@
       <c r="M83" s="7" t="n"/>
       <c r="N83" s="7" t="n"/>
       <c r="O83" s="27">
-        <f>IF(M83&lt;&gt;"",M83,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K83&lt;&gt;""),'설정'!$B$10,IF(OR(K83='설정'!$B$6,K83='설정'!$B$8),SUBSTITUTE(K83,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G83)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G83)),"화목","반")),K83)))</f>
+        <f>IF(M83&lt;&gt;"",M83,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K83&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K83="","미응시",SUBSTITUTE(K83,"반",""))&amp;")",IF(OR(K83='설정'!$B$6,K83='설정'!$B$8),SUBSTITUTE(K83,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G83)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G83)),"화목","반")),K83)))</f>
         <v/>
       </c>
       <c r="P83" s="30">
@@ -28151,7 +28151,7 @@
       <c r="M84" s="7" t="n"/>
       <c r="N84" s="7" t="n"/>
       <c r="O84" s="27">
-        <f>IF(M84&lt;&gt;"",M84,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K84&lt;&gt;""),'설정'!$B$10,IF(OR(K84='설정'!$B$6,K84='설정'!$B$8),SUBSTITUTE(K84,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G84)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G84)),"화목","반")),K84)))</f>
+        <f>IF(M84&lt;&gt;"",M84,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K84&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K84="","미응시",SUBSTITUTE(K84,"반",""))&amp;")",IF(OR(K84='설정'!$B$6,K84='설정'!$B$8),SUBSTITUTE(K84,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G84)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G84)),"화목","반")),K84)))</f>
         <v/>
       </c>
       <c r="P84" s="30">
@@ -28214,7 +28214,7 @@
       <c r="M85" s="7" t="n"/>
       <c r="N85" s="7" t="n"/>
       <c r="O85" s="27">
-        <f>IF(M85&lt;&gt;"",M85,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K85&lt;&gt;""),'설정'!$B$10,IF(OR(K85='설정'!$B$6,K85='설정'!$B$8),SUBSTITUTE(K85,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G85)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G85)),"화목","반")),K85)))</f>
+        <f>IF(M85&lt;&gt;"",M85,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K85&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K85="","미응시",SUBSTITUTE(K85,"반",""))&amp;")",IF(OR(K85='설정'!$B$6,K85='설정'!$B$8),SUBSTITUTE(K85,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G85)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G85)),"화목","반")),K85)))</f>
         <v/>
       </c>
       <c r="P85" s="30">
@@ -28277,7 +28277,7 @@
       <c r="M86" s="7" t="n"/>
       <c r="N86" s="7" t="n"/>
       <c r="O86" s="27">
-        <f>IF(M86&lt;&gt;"",M86,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K86&lt;&gt;""),'설정'!$B$10,IF(OR(K86='설정'!$B$6,K86='설정'!$B$8),SUBSTITUTE(K86,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G86)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G86)),"화목","반")),K86)))</f>
+        <f>IF(M86&lt;&gt;"",M86,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K86&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K86="","미응시",SUBSTITUTE(K86,"반",""))&amp;")",IF(OR(K86='설정'!$B$6,K86='설정'!$B$8),SUBSTITUTE(K86,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G86)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G86)),"화목","반")),K86)))</f>
         <v/>
       </c>
       <c r="P86" s="30">
@@ -28340,7 +28340,7 @@
       <c r="M87" s="7" t="n"/>
       <c r="N87" s="7" t="n"/>
       <c r="O87" s="27">
-        <f>IF(M87&lt;&gt;"",M87,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K87&lt;&gt;""),'설정'!$B$10,IF(OR(K87='설정'!$B$6,K87='설정'!$B$8),SUBSTITUTE(K87,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G87)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G87)),"화목","반")),K87)))</f>
+        <f>IF(M87&lt;&gt;"",M87,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K87&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K87="","미응시",SUBSTITUTE(K87,"반",""))&amp;")",IF(OR(K87='설정'!$B$6,K87='설정'!$B$8),SUBSTITUTE(K87,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G87)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G87)),"화목","반")),K87)))</f>
         <v/>
       </c>
       <c r="P87" s="30">
@@ -28403,7 +28403,7 @@
       <c r="M88" s="7" t="n"/>
       <c r="N88" s="7" t="n"/>
       <c r="O88" s="27">
-        <f>IF(M88&lt;&gt;"",M88,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K88&lt;&gt;""),'설정'!$B$10,IF(OR(K88='설정'!$B$6,K88='설정'!$B$8),SUBSTITUTE(K88,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G88)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G88)),"화목","반")),K88)))</f>
+        <f>IF(M88&lt;&gt;"",M88,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K88&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K88="","미응시",SUBSTITUTE(K88,"반",""))&amp;")",IF(OR(K88='설정'!$B$6,K88='설정'!$B$8),SUBSTITUTE(K88,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G88)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G88)),"화목","반")),K88)))</f>
         <v/>
       </c>
       <c r="P88" s="30">
@@ -28466,7 +28466,7 @@
       <c r="M89" s="7" t="n"/>
       <c r="N89" s="7" t="n"/>
       <c r="O89" s="27">
-        <f>IF(M89&lt;&gt;"",M89,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K89&lt;&gt;""),'설정'!$B$10,IF(OR(K89='설정'!$B$6,K89='설정'!$B$8),SUBSTITUTE(K89,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G89)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G89)),"화목","반")),K89)))</f>
+        <f>IF(M89&lt;&gt;"",M89,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K89&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K89="","미응시",SUBSTITUTE(K89,"반",""))&amp;")",IF(OR(K89='설정'!$B$6,K89='설정'!$B$8),SUBSTITUTE(K89,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G89)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G89)),"화목","반")),K89)))</f>
         <v/>
       </c>
       <c r="P89" s="30">
@@ -28529,7 +28529,7 @@
       <c r="M90" s="7" t="n"/>
       <c r="N90" s="7" t="n"/>
       <c r="O90" s="27">
-        <f>IF(M90&lt;&gt;"",M90,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K90&lt;&gt;""),'설정'!$B$10,IF(OR(K90='설정'!$B$6,K90='설정'!$B$8),SUBSTITUTE(K90,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G90)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G90)),"화목","반")),K90)))</f>
+        <f>IF(M90&lt;&gt;"",M90,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K90&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K90="","미응시",SUBSTITUTE(K90,"반",""))&amp;")",IF(OR(K90='설정'!$B$6,K90='설정'!$B$8),SUBSTITUTE(K90,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G90)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G90)),"화목","반")),K90)))</f>
         <v/>
       </c>
       <c r="P90" s="30">
@@ -28592,7 +28592,7 @@
       <c r="M91" s="7" t="n"/>
       <c r="N91" s="7" t="n"/>
       <c r="O91" s="27">
-        <f>IF(M91&lt;&gt;"",M91,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K91&lt;&gt;""),'설정'!$B$10,IF(OR(K91='설정'!$B$6,K91='설정'!$B$8),SUBSTITUTE(K91,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G91)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G91)),"화목","반")),K91)))</f>
+        <f>IF(M91&lt;&gt;"",M91,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K91&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K91="","미응시",SUBSTITUTE(K91,"반",""))&amp;")",IF(OR(K91='설정'!$B$6,K91='설정'!$B$8),SUBSTITUTE(K91,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G91)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G91)),"화목","반")),K91)))</f>
         <v/>
       </c>
       <c r="P91" s="30">
@@ -28655,7 +28655,7 @@
       <c r="M92" s="7" t="n"/>
       <c r="N92" s="7" t="n"/>
       <c r="O92" s="27">
-        <f>IF(M92&lt;&gt;"",M92,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K92&lt;&gt;""),'설정'!$B$10,IF(OR(K92='설정'!$B$6,K92='설정'!$B$8),SUBSTITUTE(K92,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G92)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G92)),"화목","반")),K92)))</f>
+        <f>IF(M92&lt;&gt;"",M92,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K92&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K92="","미응시",SUBSTITUTE(K92,"반",""))&amp;")",IF(OR(K92='설정'!$B$6,K92='설정'!$B$8),SUBSTITUTE(K92,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G92)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G92)),"화목","반")),K92)))</f>
         <v/>
       </c>
       <c r="P92" s="30">
@@ -28718,7 +28718,7 @@
       <c r="M93" s="7" t="n"/>
       <c r="N93" s="7" t="n"/>
       <c r="O93" s="27">
-        <f>IF(M93&lt;&gt;"",M93,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K93&lt;&gt;""),'설정'!$B$10,IF(OR(K93='설정'!$B$6,K93='설정'!$B$8),SUBSTITUTE(K93,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G93)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G93)),"화목","반")),K93)))</f>
+        <f>IF(M93&lt;&gt;"",M93,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K93&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K93="","미응시",SUBSTITUTE(K93,"반",""))&amp;")",IF(OR(K93='설정'!$B$6,K93='설정'!$B$8),SUBSTITUTE(K93,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G93)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G93)),"화목","반")),K93)))</f>
         <v/>
       </c>
       <c r="P93" s="30">
@@ -28781,7 +28781,7 @@
       <c r="M94" s="7" t="n"/>
       <c r="N94" s="7" t="n"/>
       <c r="O94" s="27">
-        <f>IF(M94&lt;&gt;"",M94,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K94&lt;&gt;""),'설정'!$B$10,IF(OR(K94='설정'!$B$6,K94='설정'!$B$8),SUBSTITUTE(K94,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G94)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G94)),"화목","반")),K94)))</f>
+        <f>IF(M94&lt;&gt;"",M94,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K94&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K94="","미응시",SUBSTITUTE(K94,"반",""))&amp;")",IF(OR(K94='설정'!$B$6,K94='설정'!$B$8),SUBSTITUTE(K94,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G94)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G94)),"화목","반")),K94)))</f>
         <v/>
       </c>
       <c r="P94" s="30">
@@ -28844,7 +28844,7 @@
       <c r="M95" s="7" t="n"/>
       <c r="N95" s="7" t="n"/>
       <c r="O95" s="27">
-        <f>IF(M95&lt;&gt;"",M95,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K95&lt;&gt;""),'설정'!$B$10,IF(OR(K95='설정'!$B$6,K95='설정'!$B$8),SUBSTITUTE(K95,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G95)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G95)),"화목","반")),K95)))</f>
+        <f>IF(M95&lt;&gt;"",M95,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K95&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K95="","미응시",SUBSTITUTE(K95,"반",""))&amp;")",IF(OR(K95='설정'!$B$6,K95='설정'!$B$8),SUBSTITUTE(K95,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G95)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G95)),"화목","반")),K95)))</f>
         <v/>
       </c>
       <c r="P95" s="30">
@@ -28907,7 +28907,7 @@
       <c r="M96" s="7" t="n"/>
       <c r="N96" s="7" t="n"/>
       <c r="O96" s="27">
-        <f>IF(M96&lt;&gt;"",M96,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K96&lt;&gt;""),'설정'!$B$10,IF(OR(K96='설정'!$B$6,K96='설정'!$B$8),SUBSTITUTE(K96,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G96)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G96)),"화목","반")),K96)))</f>
+        <f>IF(M96&lt;&gt;"",M96,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K96&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K96="","미응시",SUBSTITUTE(K96,"반",""))&amp;")",IF(OR(K96='설정'!$B$6,K96='설정'!$B$8),SUBSTITUTE(K96,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G96)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G96)),"화목","반")),K96)))</f>
         <v/>
       </c>
       <c r="P96" s="30">
@@ -28970,7 +28970,7 @@
       <c r="M97" s="7" t="n"/>
       <c r="N97" s="7" t="n"/>
       <c r="O97" s="27">
-        <f>IF(M97&lt;&gt;"",M97,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K97&lt;&gt;""),'설정'!$B$10,IF(OR(K97='설정'!$B$6,K97='설정'!$B$8),SUBSTITUTE(K97,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G97)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G97)),"화목","반")),K97)))</f>
+        <f>IF(M97&lt;&gt;"",M97,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K97&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K97="","미응시",SUBSTITUTE(K97,"반",""))&amp;")",IF(OR(K97='설정'!$B$6,K97='설정'!$B$8),SUBSTITUTE(K97,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G97)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G97)),"화목","반")),K97)))</f>
         <v/>
       </c>
       <c r="P97" s="30">
@@ -29033,7 +29033,7 @@
       <c r="M98" s="7" t="n"/>
       <c r="N98" s="7" t="n"/>
       <c r="O98" s="27">
-        <f>IF(M98&lt;&gt;"",M98,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K98&lt;&gt;""),'설정'!$B$10,IF(OR(K98='설정'!$B$6,K98='설정'!$B$8),SUBSTITUTE(K98,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G98)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G98)),"화목","반")),K98)))</f>
+        <f>IF(M98&lt;&gt;"",M98,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K98&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K98="","미응시",SUBSTITUTE(K98,"반",""))&amp;")",IF(OR(K98='설정'!$B$6,K98='설정'!$B$8),SUBSTITUTE(K98,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G98)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G98)),"화목","반")),K98)))</f>
         <v/>
       </c>
       <c r="P98" s="30">
@@ -29096,7 +29096,7 @@
       <c r="M99" s="7" t="n"/>
       <c r="N99" s="7" t="n"/>
       <c r="O99" s="27">
-        <f>IF(M99&lt;&gt;"",M99,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K99&lt;&gt;""),'설정'!$B$10,IF(OR(K99='설정'!$B$6,K99='설정'!$B$8),SUBSTITUTE(K99,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G99)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G99)),"화목","반")),K99)))</f>
+        <f>IF(M99&lt;&gt;"",M99,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K99&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K99="","미응시",SUBSTITUTE(K99,"반",""))&amp;")",IF(OR(K99='설정'!$B$6,K99='설정'!$B$8),SUBSTITUTE(K99,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G99)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G99)),"화목","반")),K99)))</f>
         <v/>
       </c>
       <c r="P99" s="30">
@@ -29159,7 +29159,7 @@
       <c r="M100" s="7" t="n"/>
       <c r="N100" s="7" t="n"/>
       <c r="O100" s="27">
-        <f>IF(M100&lt;&gt;"",M100,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K100&lt;&gt;""),'설정'!$B$10,IF(OR(K100='설정'!$B$6,K100='설정'!$B$8),SUBSTITUTE(K100,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G100)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G100)),"화목","반")),K100)))</f>
+        <f>IF(M100&lt;&gt;"",M100,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K100&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K100="","미응시",SUBSTITUTE(K100,"반",""))&amp;")",IF(OR(K100='설정'!$B$6,K100='설정'!$B$8),SUBSTITUTE(K100,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G100)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G100)),"화목","반")),K100)))</f>
         <v/>
       </c>
       <c r="P100" s="30">
@@ -29222,7 +29222,7 @@
       <c r="M101" s="7" t="n"/>
       <c r="N101" s="7" t="n"/>
       <c r="O101" s="27">
-        <f>IF(M101&lt;&gt;"",M101,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K101&lt;&gt;""),'설정'!$B$10,IF(OR(K101='설정'!$B$6,K101='설정'!$B$8),SUBSTITUTE(K101,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G101)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G101)),"화목","반")),K101)))</f>
+        <f>IF(M101&lt;&gt;"",M101,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K101&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K101="","미응시",SUBSTITUTE(K101,"반",""))&amp;")",IF(OR(K101='설정'!$B$6,K101='설정'!$B$8),SUBSTITUTE(K101,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G101)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G101)),"화목","반")),K101)))</f>
         <v/>
       </c>
       <c r="P101" s="30">
@@ -29285,7 +29285,7 @@
       <c r="M102" s="7" t="n"/>
       <c r="N102" s="7" t="n"/>
       <c r="O102" s="27">
-        <f>IF(M102&lt;&gt;"",M102,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K102&lt;&gt;""),'설정'!$B$10,IF(OR(K102='설정'!$B$6,K102='설정'!$B$8),SUBSTITUTE(K102,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G102)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G102)),"화목","반")),K102)))</f>
+        <f>IF(M102&lt;&gt;"",M102,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K102&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K102="","미응시",SUBSTITUTE(K102,"반",""))&amp;")",IF(OR(K102='설정'!$B$6,K102='설정'!$B$8),SUBSTITUTE(K102,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G102)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G102)),"화목","반")),K102)))</f>
         <v/>
       </c>
       <c r="P102" s="30">
@@ -29348,7 +29348,7 @@
       <c r="M103" s="7" t="n"/>
       <c r="N103" s="7" t="n"/>
       <c r="O103" s="27">
-        <f>IF(M103&lt;&gt;"",M103,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K103&lt;&gt;""),'설정'!$B$10,IF(OR(K103='설정'!$B$6,K103='설정'!$B$8),SUBSTITUTE(K103,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G103)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G103)),"화목","반")),K103)))</f>
+        <f>IF(M103&lt;&gt;"",M103,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K103&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K103="","미응시",SUBSTITUTE(K103,"반",""))&amp;")",IF(OR(K103='설정'!$B$6,K103='설정'!$B$8),SUBSTITUTE(K103,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G103)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G103)),"화목","반")),K103)))</f>
         <v/>
       </c>
       <c r="P103" s="30">
@@ -29411,7 +29411,7 @@
       <c r="M104" s="7" t="n"/>
       <c r="N104" s="7" t="n"/>
       <c r="O104" s="27">
-        <f>IF(M104&lt;&gt;"",M104,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K104&lt;&gt;""),'설정'!$B$10,IF(OR(K104='설정'!$B$6,K104='설정'!$B$8),SUBSTITUTE(K104,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G104)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G104)),"화목","반")),K104)))</f>
+        <f>IF(M104&lt;&gt;"",M104,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K104&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K104="","미응시",SUBSTITUTE(K104,"반",""))&amp;")",IF(OR(K104='설정'!$B$6,K104='설정'!$B$8),SUBSTITUTE(K104,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G104)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G104)),"화목","반")),K104)))</f>
         <v/>
       </c>
       <c r="P104" s="30">
@@ -29474,7 +29474,7 @@
       <c r="M105" s="7" t="n"/>
       <c r="N105" s="7" t="n"/>
       <c r="O105" s="27">
-        <f>IF(M105&lt;&gt;"",M105,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K105&lt;&gt;""),'설정'!$B$10,IF(OR(K105='설정'!$B$6,K105='설정'!$B$8),SUBSTITUTE(K105,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G105)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G105)),"화목","반")),K105)))</f>
+        <f>IF(M105&lt;&gt;"",M105,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K105&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K105="","미응시",SUBSTITUTE(K105,"반",""))&amp;")",IF(OR(K105='설정'!$B$6,K105='설정'!$B$8),SUBSTITUTE(K105,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G105)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G105)),"화목","반")),K105)))</f>
         <v/>
       </c>
       <c r="P105" s="30">
@@ -29537,7 +29537,7 @@
       <c r="M106" s="7" t="n"/>
       <c r="N106" s="7" t="n"/>
       <c r="O106" s="27">
-        <f>IF(M106&lt;&gt;"",M106,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K106&lt;&gt;""),'설정'!$B$10,IF(OR(K106='설정'!$B$6,K106='설정'!$B$8),SUBSTITUTE(K106,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G106)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G106)),"화목","반")),K106)))</f>
+        <f>IF(M106&lt;&gt;"",M106,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K106&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K106="","미응시",SUBSTITUTE(K106,"반",""))&amp;")",IF(OR(K106='설정'!$B$6,K106='설정'!$B$8),SUBSTITUTE(K106,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G106)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G106)),"화목","반")),K106)))</f>
         <v/>
       </c>
       <c r="P106" s="30">
@@ -29600,7 +29600,7 @@
       <c r="M107" s="7" t="n"/>
       <c r="N107" s="7" t="n"/>
       <c r="O107" s="27">
-        <f>IF(M107&lt;&gt;"",M107,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K107&lt;&gt;""),'설정'!$B$10,IF(OR(K107='설정'!$B$6,K107='설정'!$B$8),SUBSTITUTE(K107,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G107)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G107)),"화목","반")),K107)))</f>
+        <f>IF(M107&lt;&gt;"",M107,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K107&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K107="","미응시",SUBSTITUTE(K107,"반",""))&amp;")",IF(OR(K107='설정'!$B$6,K107='설정'!$B$8),SUBSTITUTE(K107,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G107)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G107)),"화목","반")),K107)))</f>
         <v/>
       </c>
       <c r="P107" s="30">
@@ -29663,7 +29663,7 @@
       <c r="M108" s="7" t="n"/>
       <c r="N108" s="7" t="n"/>
       <c r="O108" s="27">
-        <f>IF(M108&lt;&gt;"",M108,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K108&lt;&gt;""),'설정'!$B$10,IF(OR(K108='설정'!$B$6,K108='설정'!$B$8),SUBSTITUTE(K108,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G108)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G108)),"화목","반")),K108)))</f>
+        <f>IF(M108&lt;&gt;"",M108,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K108&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K108="","미응시",SUBSTITUTE(K108,"반",""))&amp;")",IF(OR(K108='설정'!$B$6,K108='설정'!$B$8),SUBSTITUTE(K108,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G108)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G108)),"화목","반")),K108)))</f>
         <v/>
       </c>
       <c r="P108" s="30">
@@ -29726,7 +29726,7 @@
       <c r="M109" s="7" t="n"/>
       <c r="N109" s="7" t="n"/>
       <c r="O109" s="27">
-        <f>IF(M109&lt;&gt;"",M109,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K109&lt;&gt;""),'설정'!$B$10,IF(OR(K109='설정'!$B$6,K109='설정'!$B$8),SUBSTITUTE(K109,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G109)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G109)),"화목","반")),K109)))</f>
+        <f>IF(M109&lt;&gt;"",M109,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K109&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K109="","미응시",SUBSTITUTE(K109,"반",""))&amp;")",IF(OR(K109='설정'!$B$6,K109='설정'!$B$8),SUBSTITUTE(K109,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G109)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G109)),"화목","반")),K109)))</f>
         <v/>
       </c>
       <c r="P109" s="30">
@@ -29789,7 +29789,7 @@
       <c r="M110" s="7" t="n"/>
       <c r="N110" s="7" t="n"/>
       <c r="O110" s="27">
-        <f>IF(M110&lt;&gt;"",M110,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K110&lt;&gt;""),'설정'!$B$10,IF(OR(K110='설정'!$B$6,K110='설정'!$B$8),SUBSTITUTE(K110,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G110)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G110)),"화목","반")),K110)))</f>
+        <f>IF(M110&lt;&gt;"",M110,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K110&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K110="","미응시",SUBSTITUTE(K110,"반",""))&amp;")",IF(OR(K110='설정'!$B$6,K110='설정'!$B$8),SUBSTITUTE(K110,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G110)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G110)),"화목","반")),K110)))</f>
         <v/>
       </c>
       <c r="P110" s="30">
@@ -29852,7 +29852,7 @@
       <c r="M111" s="7" t="n"/>
       <c r="N111" s="7" t="n"/>
       <c r="O111" s="27">
-        <f>IF(M111&lt;&gt;"",M111,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K111&lt;&gt;""),'설정'!$B$10,IF(OR(K111='설정'!$B$6,K111='설정'!$B$8),SUBSTITUTE(K111,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G111)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G111)),"화목","반")),K111)))</f>
+        <f>IF(M111&lt;&gt;"",M111,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K111&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K111="","미응시",SUBSTITUTE(K111,"반",""))&amp;")",IF(OR(K111='설정'!$B$6,K111='설정'!$B$8),SUBSTITUTE(K111,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G111)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G111)),"화목","반")),K111)))</f>
         <v/>
       </c>
       <c r="P111" s="30">
@@ -29915,7 +29915,7 @@
       <c r="M112" s="7" t="n"/>
       <c r="N112" s="7" t="n"/>
       <c r="O112" s="27">
-        <f>IF(M112&lt;&gt;"",M112,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K112&lt;&gt;""),'설정'!$B$10,IF(OR(K112='설정'!$B$6,K112='설정'!$B$8),SUBSTITUTE(K112,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G112)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G112)),"화목","반")),K112)))</f>
+        <f>IF(M112&lt;&gt;"",M112,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K112&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K112="","미응시",SUBSTITUTE(K112,"반",""))&amp;")",IF(OR(K112='설정'!$B$6,K112='설정'!$B$8),SUBSTITUTE(K112,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G112)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G112)),"화목","반")),K112)))</f>
         <v/>
       </c>
       <c r="P112" s="30">
@@ -29978,7 +29978,7 @@
       <c r="M113" s="7" t="n"/>
       <c r="N113" s="7" t="n"/>
       <c r="O113" s="27">
-        <f>IF(M113&lt;&gt;"",M113,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K113&lt;&gt;""),'설정'!$B$10,IF(OR(K113='설정'!$B$6,K113='설정'!$B$8),SUBSTITUTE(K113,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G113)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G113)),"화목","반")),K113)))</f>
+        <f>IF(M113&lt;&gt;"",M113,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K113&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K113="","미응시",SUBSTITUTE(K113,"반",""))&amp;")",IF(OR(K113='설정'!$B$6,K113='설정'!$B$8),SUBSTITUTE(K113,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G113)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G113)),"화목","반")),K113)))</f>
         <v/>
       </c>
       <c r="P113" s="30">
@@ -30041,7 +30041,7 @@
       <c r="M114" s="7" t="n"/>
       <c r="N114" s="7" t="n"/>
       <c r="O114" s="27">
-        <f>IF(M114&lt;&gt;"",M114,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K114&lt;&gt;""),'설정'!$B$10,IF(OR(K114='설정'!$B$6,K114='설정'!$B$8),SUBSTITUTE(K114,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G114)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G114)),"화목","반")),K114)))</f>
+        <f>IF(M114&lt;&gt;"",M114,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K114&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K114="","미응시",SUBSTITUTE(K114,"반",""))&amp;")",IF(OR(K114='설정'!$B$6,K114='설정'!$B$8),SUBSTITUTE(K114,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G114)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G114)),"화목","반")),K114)))</f>
         <v/>
       </c>
       <c r="P114" s="30">
@@ -30104,7 +30104,7 @@
       <c r="M115" s="7" t="n"/>
       <c r="N115" s="7" t="n"/>
       <c r="O115" s="27">
-        <f>IF(M115&lt;&gt;"",M115,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K115&lt;&gt;""),'설정'!$B$10,IF(OR(K115='설정'!$B$6,K115='설정'!$B$8),SUBSTITUTE(K115,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G115)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G115)),"화목","반")),K115)))</f>
+        <f>IF(M115&lt;&gt;"",M115,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K115&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K115="","미응시",SUBSTITUTE(K115,"반",""))&amp;")",IF(OR(K115='설정'!$B$6,K115='설정'!$B$8),SUBSTITUTE(K115,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G115)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G115)),"화목","반")),K115)))</f>
         <v/>
       </c>
       <c r="P115" s="30">
@@ -30167,7 +30167,7 @@
       <c r="M116" s="7" t="n"/>
       <c r="N116" s="7" t="n"/>
       <c r="O116" s="27">
-        <f>IF(M116&lt;&gt;"",M116,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K116&lt;&gt;""),'설정'!$B$10,IF(OR(K116='설정'!$B$6,K116='설정'!$B$8),SUBSTITUTE(K116,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G116)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G116)),"화목","반")),K116)))</f>
+        <f>IF(M116&lt;&gt;"",M116,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K116&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K116="","미응시",SUBSTITUTE(K116,"반",""))&amp;")",IF(OR(K116='설정'!$B$6,K116='설정'!$B$8),SUBSTITUTE(K116,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G116)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G116)),"화목","반")),K116)))</f>
         <v/>
       </c>
       <c r="P116" s="30">
@@ -30230,7 +30230,7 @@
       <c r="M117" s="7" t="n"/>
       <c r="N117" s="7" t="n"/>
       <c r="O117" s="27">
-        <f>IF(M117&lt;&gt;"",M117,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K117&lt;&gt;""),'설정'!$B$10,IF(OR(K117='설정'!$B$6,K117='설정'!$B$8),SUBSTITUTE(K117,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G117)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G117)),"화목","반")),K117)))</f>
+        <f>IF(M117&lt;&gt;"",M117,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K117&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K117="","미응시",SUBSTITUTE(K117,"반",""))&amp;")",IF(OR(K117='설정'!$B$6,K117='설정'!$B$8),SUBSTITUTE(K117,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G117)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G117)),"화목","반")),K117)))</f>
         <v/>
       </c>
       <c r="P117" s="30">
@@ -30293,7 +30293,7 @@
       <c r="M118" s="7" t="n"/>
       <c r="N118" s="7" t="n"/>
       <c r="O118" s="27">
-        <f>IF(M118&lt;&gt;"",M118,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K118&lt;&gt;""),'설정'!$B$10,IF(OR(K118='설정'!$B$6,K118='설정'!$B$8),SUBSTITUTE(K118,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G118)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G118)),"화목","반")),K118)))</f>
+        <f>IF(M118&lt;&gt;"",M118,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K118&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K118="","미응시",SUBSTITUTE(K118,"반",""))&amp;")",IF(OR(K118='설정'!$B$6,K118='설정'!$B$8),SUBSTITUTE(K118,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G118)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G118)),"화목","반")),K118)))</f>
         <v/>
       </c>
       <c r="P118" s="30">
@@ -30356,7 +30356,7 @@
       <c r="M119" s="7" t="n"/>
       <c r="N119" s="7" t="n"/>
       <c r="O119" s="27">
-        <f>IF(M119&lt;&gt;"",M119,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K119&lt;&gt;""),'설정'!$B$10,IF(OR(K119='설정'!$B$6,K119='설정'!$B$8),SUBSTITUTE(K119,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G119)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G119)),"화목","반")),K119)))</f>
+        <f>IF(M119&lt;&gt;"",M119,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K119&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K119="","미응시",SUBSTITUTE(K119,"반",""))&amp;")",IF(OR(K119='설정'!$B$6,K119='설정'!$B$8),SUBSTITUTE(K119,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G119)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G119)),"화목","반")),K119)))</f>
         <v/>
       </c>
       <c r="P119" s="30">
@@ -30419,7 +30419,7 @@
       <c r="M120" s="7" t="n"/>
       <c r="N120" s="7" t="n"/>
       <c r="O120" s="27">
-        <f>IF(M120&lt;&gt;"",M120,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K120&lt;&gt;""),'설정'!$B$10,IF(OR(K120='설정'!$B$6,K120='설정'!$B$8),SUBSTITUTE(K120,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G120)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G120)),"화목","반")),K120)))</f>
+        <f>IF(M120&lt;&gt;"",M120,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K120&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K120="","미응시",SUBSTITUTE(K120,"반",""))&amp;")",IF(OR(K120='설정'!$B$6,K120='설정'!$B$8),SUBSTITUTE(K120,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G120)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G120)),"화목","반")),K120)))</f>
         <v/>
       </c>
       <c r="P120" s="30">
@@ -30482,7 +30482,7 @@
       <c r="M121" s="7" t="n"/>
       <c r="N121" s="7" t="n"/>
       <c r="O121" s="27">
-        <f>IF(M121&lt;&gt;"",M121,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K121&lt;&gt;""),'설정'!$B$10,IF(OR(K121='설정'!$B$6,K121='설정'!$B$8),SUBSTITUTE(K121,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G121)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G121)),"화목","반")),K121)))</f>
+        <f>IF(M121&lt;&gt;"",M121,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K121&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K121="","미응시",SUBSTITUTE(K121,"반",""))&amp;")",IF(OR(K121='설정'!$B$6,K121='설정'!$B$8),SUBSTITUTE(K121,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G121)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G121)),"화목","반")),K121)))</f>
         <v/>
       </c>
       <c r="P121" s="30">
@@ -30545,7 +30545,7 @@
       <c r="M122" s="7" t="n"/>
       <c r="N122" s="7" t="n"/>
       <c r="O122" s="27">
-        <f>IF(M122&lt;&gt;"",M122,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K122&lt;&gt;""),'설정'!$B$10,IF(OR(K122='설정'!$B$6,K122='설정'!$B$8),SUBSTITUTE(K122,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G122)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G122)),"화목","반")),K122)))</f>
+        <f>IF(M122&lt;&gt;"",M122,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K122&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K122="","미응시",SUBSTITUTE(K122,"반",""))&amp;")",IF(OR(K122='설정'!$B$6,K122='설정'!$B$8),SUBSTITUTE(K122,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G122)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G122)),"화목","반")),K122)))</f>
         <v/>
       </c>
       <c r="P122" s="30">
@@ -30608,7 +30608,7 @@
       <c r="M123" s="7" t="n"/>
       <c r="N123" s="7" t="n"/>
       <c r="O123" s="27">
-        <f>IF(M123&lt;&gt;"",M123,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K123&lt;&gt;""),'설정'!$B$10,IF(OR(K123='설정'!$B$6,K123='설정'!$B$8),SUBSTITUTE(K123,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G123)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G123)),"화목","반")),K123)))</f>
+        <f>IF(M123&lt;&gt;"",M123,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K123&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K123="","미응시",SUBSTITUTE(K123,"반",""))&amp;")",IF(OR(K123='설정'!$B$6,K123='설정'!$B$8),SUBSTITUTE(K123,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G123)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G123)),"화목","반")),K123)))</f>
         <v/>
       </c>
       <c r="P123" s="30">
@@ -30671,7 +30671,7 @@
       <c r="M124" s="7" t="n"/>
       <c r="N124" s="7" t="n"/>
       <c r="O124" s="27">
-        <f>IF(M124&lt;&gt;"",M124,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K124&lt;&gt;""),'설정'!$B$10,IF(OR(K124='설정'!$B$6,K124='설정'!$B$8),SUBSTITUTE(K124,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G124)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G124)),"화목","반")),K124)))</f>
+        <f>IF(M124&lt;&gt;"",M124,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K124&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K124="","미응시",SUBSTITUTE(K124,"반",""))&amp;")",IF(OR(K124='설정'!$B$6,K124='설정'!$B$8),SUBSTITUTE(K124,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G124)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G124)),"화목","반")),K124)))</f>
         <v/>
       </c>
       <c r="P124" s="30">
@@ -30734,7 +30734,7 @@
       <c r="M125" s="7" t="n"/>
       <c r="N125" s="7" t="n"/>
       <c r="O125" s="27">
-        <f>IF(M125&lt;&gt;"",M125,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K125&lt;&gt;""),'설정'!$B$10,IF(OR(K125='설정'!$B$6,K125='설정'!$B$8),SUBSTITUTE(K125,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G125)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G125)),"화목","반")),K125)))</f>
+        <f>IF(M125&lt;&gt;"",M125,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K125&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K125="","미응시",SUBSTITUTE(K125,"반",""))&amp;")",IF(OR(K125='설정'!$B$6,K125='설정'!$B$8),SUBSTITUTE(K125,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G125)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G125)),"화목","반")),K125)))</f>
         <v/>
       </c>
       <c r="P125" s="30">
@@ -30797,7 +30797,7 @@
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="n"/>
       <c r="O126" s="27">
-        <f>IF(M126&lt;&gt;"",M126,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K126&lt;&gt;""),'설정'!$B$10,IF(OR(K126='설정'!$B$6,K126='설정'!$B$8),SUBSTITUTE(K126,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G126)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G126)),"화목","반")),K126)))</f>
+        <f>IF(M126&lt;&gt;"",M126,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K126&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K126="","미응시",SUBSTITUTE(K126,"반",""))&amp;")",IF(OR(K126='설정'!$B$6,K126='설정'!$B$8),SUBSTITUTE(K126,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G126)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G126)),"화목","반")),K126)))</f>
         <v/>
       </c>
       <c r="P126" s="30">
@@ -30860,7 +30860,7 @@
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="n"/>
       <c r="O127" s="27">
-        <f>IF(M127&lt;&gt;"",M127,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K127&lt;&gt;""),'설정'!$B$10,IF(OR(K127='설정'!$B$6,K127='설정'!$B$8),SUBSTITUTE(K127,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G127)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G127)),"화목","반")),K127)))</f>
+        <f>IF(M127&lt;&gt;"",M127,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K127&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K127="","미응시",SUBSTITUTE(K127,"반",""))&amp;")",IF(OR(K127='설정'!$B$6,K127='설정'!$B$8),SUBSTITUTE(K127,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G127)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G127)),"화목","반")),K127)))</f>
         <v/>
       </c>
       <c r="P127" s="30">
@@ -30923,7 +30923,7 @@
       <c r="M128" s="7" t="n"/>
       <c r="N128" s="7" t="n"/>
       <c r="O128" s="27">
-        <f>IF(M128&lt;&gt;"",M128,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K128&lt;&gt;""),'설정'!$B$10,IF(OR(K128='설정'!$B$6,K128='설정'!$B$8),SUBSTITUTE(K128,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G128)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G128)),"화목","반")),K128)))</f>
+        <f>IF(M128&lt;&gt;"",M128,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K128&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K128="","미응시",SUBSTITUTE(K128,"반",""))&amp;")",IF(OR(K128='설정'!$B$6,K128='설정'!$B$8),SUBSTITUTE(K128,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G128)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G128)),"화목","반")),K128)))</f>
         <v/>
       </c>
       <c r="P128" s="30">
@@ -30986,7 +30986,7 @@
       <c r="M129" s="7" t="n"/>
       <c r="N129" s="7" t="n"/>
       <c r="O129" s="27">
-        <f>IF(M129&lt;&gt;"",M129,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K129&lt;&gt;""),'설정'!$B$10,IF(OR(K129='설정'!$B$6,K129='설정'!$B$8),SUBSTITUTE(K129,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G129)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G129)),"화목","반")),K129)))</f>
+        <f>IF(M129&lt;&gt;"",M129,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K129&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K129="","미응시",SUBSTITUTE(K129,"반",""))&amp;")",IF(OR(K129='설정'!$B$6,K129='설정'!$B$8),SUBSTITUTE(K129,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G129)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G129)),"화목","반")),K129)))</f>
         <v/>
       </c>
       <c r="P129" s="30">
@@ -31049,7 +31049,7 @@
       <c r="M130" s="7" t="n"/>
       <c r="N130" s="7" t="n"/>
       <c r="O130" s="27">
-        <f>IF(M130&lt;&gt;"",M130,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K130&lt;&gt;""),'설정'!$B$10,IF(OR(K130='설정'!$B$6,K130='설정'!$B$8),SUBSTITUTE(K130,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G130)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G130)),"화목","반")),K130)))</f>
+        <f>IF(M130&lt;&gt;"",M130,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K130&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K130="","미응시",SUBSTITUTE(K130,"반",""))&amp;")",IF(OR(K130='설정'!$B$6,K130='설정'!$B$8),SUBSTITUTE(K130,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G130)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G130)),"화목","반")),K130)))</f>
         <v/>
       </c>
       <c r="P130" s="30">
@@ -31112,7 +31112,7 @@
       <c r="M131" s="7" t="n"/>
       <c r="N131" s="7" t="n"/>
       <c r="O131" s="27">
-        <f>IF(M131&lt;&gt;"",M131,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K131&lt;&gt;""),'설정'!$B$10,IF(OR(K131='설정'!$B$6,K131='설정'!$B$8),SUBSTITUTE(K131,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G131)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G131)),"화목","반")),K131)))</f>
+        <f>IF(M131&lt;&gt;"",M131,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K131&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K131="","미응시",SUBSTITUTE(K131,"반",""))&amp;")",IF(OR(K131='설정'!$B$6,K131='설정'!$B$8),SUBSTITUTE(K131,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G131)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G131)),"화목","반")),K131)))</f>
         <v/>
       </c>
       <c r="P131" s="30">
@@ -31175,7 +31175,7 @@
       <c r="M132" s="7" t="n"/>
       <c r="N132" s="7" t="n"/>
       <c r="O132" s="27">
-        <f>IF(M132&lt;&gt;"",M132,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K132&lt;&gt;""),'설정'!$B$10,IF(OR(K132='설정'!$B$6,K132='설정'!$B$8),SUBSTITUTE(K132,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G132)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G132)),"화목","반")),K132)))</f>
+        <f>IF(M132&lt;&gt;"",M132,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K132&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K132="","미응시",SUBSTITUTE(K132,"반",""))&amp;")",IF(OR(K132='설정'!$B$6,K132='설정'!$B$8),SUBSTITUTE(K132,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G132)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G132)),"화목","반")),K132)))</f>
         <v/>
       </c>
       <c r="P132" s="30">
@@ -31238,7 +31238,7 @@
       <c r="M133" s="7" t="n"/>
       <c r="N133" s="7" t="n"/>
       <c r="O133" s="27">
-        <f>IF(M133&lt;&gt;"",M133,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K133&lt;&gt;""),'설정'!$B$10,IF(OR(K133='설정'!$B$6,K133='설정'!$B$8),SUBSTITUTE(K133,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G133)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G133)),"화목","반")),K133)))</f>
+        <f>IF(M133&lt;&gt;"",M133,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K133&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K133="","미응시",SUBSTITUTE(K133,"반",""))&amp;")",IF(OR(K133='설정'!$B$6,K133='설정'!$B$8),SUBSTITUTE(K133,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G133)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G133)),"화목","반")),K133)))</f>
         <v/>
       </c>
       <c r="P133" s="30">
@@ -31301,7 +31301,7 @@
       <c r="M134" s="7" t="n"/>
       <c r="N134" s="7" t="n"/>
       <c r="O134" s="27">
-        <f>IF(M134&lt;&gt;"",M134,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K134&lt;&gt;""),'설정'!$B$10,IF(OR(K134='설정'!$B$6,K134='설정'!$B$8),SUBSTITUTE(K134,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G134)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G134)),"화목","반")),K134)))</f>
+        <f>IF(M134&lt;&gt;"",M134,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K134&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K134="","미응시",SUBSTITUTE(K134,"반",""))&amp;")",IF(OR(K134='설정'!$B$6,K134='설정'!$B$8),SUBSTITUTE(K134,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G134)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G134)),"화목","반")),K134)))</f>
         <v/>
       </c>
       <c r="P134" s="30">
@@ -31364,7 +31364,7 @@
       <c r="M135" s="7" t="n"/>
       <c r="N135" s="7" t="n"/>
       <c r="O135" s="27">
-        <f>IF(M135&lt;&gt;"",M135,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K135&lt;&gt;""),'설정'!$B$10,IF(OR(K135='설정'!$B$6,K135='설정'!$B$8),SUBSTITUTE(K135,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G135)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G135)),"화목","반")),K135)))</f>
+        <f>IF(M135&lt;&gt;"",M135,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K135&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K135="","미응시",SUBSTITUTE(K135,"반",""))&amp;")",IF(OR(K135='설정'!$B$6,K135='설정'!$B$8),SUBSTITUTE(K135,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G135)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G135)),"화목","반")),K135)))</f>
         <v/>
       </c>
       <c r="P135" s="30">
@@ -31427,7 +31427,7 @@
       <c r="M136" s="7" t="n"/>
       <c r="N136" s="7" t="n"/>
       <c r="O136" s="27">
-        <f>IF(M136&lt;&gt;"",M136,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K136&lt;&gt;""),'설정'!$B$10,IF(OR(K136='설정'!$B$6,K136='설정'!$B$8),SUBSTITUTE(K136,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G136)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G136)),"화목","반")),K136)))</f>
+        <f>IF(M136&lt;&gt;"",M136,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K136&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K136="","미응시",SUBSTITUTE(K136,"반",""))&amp;")",IF(OR(K136='설정'!$B$6,K136='설정'!$B$8),SUBSTITUTE(K136,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G136)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G136)),"화목","반")),K136)))</f>
         <v/>
       </c>
       <c r="P136" s="30">
@@ -31490,7 +31490,7 @@
       <c r="M137" s="7" t="n"/>
       <c r="N137" s="7" t="n"/>
       <c r="O137" s="27">
-        <f>IF(M137&lt;&gt;"",M137,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K137&lt;&gt;""),'설정'!$B$10,IF(OR(K137='설정'!$B$6,K137='설정'!$B$8),SUBSTITUTE(K137,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G137)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G137)),"화목","반")),K137)))</f>
+        <f>IF(M137&lt;&gt;"",M137,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K137&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K137="","미응시",SUBSTITUTE(K137,"반",""))&amp;")",IF(OR(K137='설정'!$B$6,K137='설정'!$B$8),SUBSTITUTE(K137,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G137)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G137)),"화목","반")),K137)))</f>
         <v/>
       </c>
       <c r="P137" s="30">
@@ -31553,7 +31553,7 @@
       <c r="M138" s="7" t="n"/>
       <c r="N138" s="7" t="n"/>
       <c r="O138" s="27">
-        <f>IF(M138&lt;&gt;"",M138,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K138&lt;&gt;""),'설정'!$B$10,IF(OR(K138='설정'!$B$6,K138='설정'!$B$8),SUBSTITUTE(K138,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G138)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G138)),"화목","반")),K138)))</f>
+        <f>IF(M138&lt;&gt;"",M138,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K138&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K138="","미응시",SUBSTITUTE(K138,"반",""))&amp;")",IF(OR(K138='설정'!$B$6,K138='설정'!$B$8),SUBSTITUTE(K138,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G138)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G138)),"화목","반")),K138)))</f>
         <v/>
       </c>
       <c r="P138" s="30">
@@ -31616,7 +31616,7 @@
       <c r="M139" s="7" t="n"/>
       <c r="N139" s="7" t="n"/>
       <c r="O139" s="27">
-        <f>IF(M139&lt;&gt;"",M139,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K139&lt;&gt;""),'설정'!$B$10,IF(OR(K139='설정'!$B$6,K139='설정'!$B$8),SUBSTITUTE(K139,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G139)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G139)),"화목","반")),K139)))</f>
+        <f>IF(M139&lt;&gt;"",M139,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K139&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K139="","미응시",SUBSTITUTE(K139,"반",""))&amp;")",IF(OR(K139='설정'!$B$6,K139='설정'!$B$8),SUBSTITUTE(K139,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G139)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G139)),"화목","반")),K139)))</f>
         <v/>
       </c>
       <c r="P139" s="30">
@@ -31679,7 +31679,7 @@
       <c r="M140" s="7" t="n"/>
       <c r="N140" s="7" t="n"/>
       <c r="O140" s="27">
-        <f>IF(M140&lt;&gt;"",M140,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K140&lt;&gt;""),'설정'!$B$10,IF(OR(K140='설정'!$B$6,K140='설정'!$B$8),SUBSTITUTE(K140,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G140)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G140)),"화목","반")),K140)))</f>
+        <f>IF(M140&lt;&gt;"",M140,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K140&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K140="","미응시",SUBSTITUTE(K140,"반",""))&amp;")",IF(OR(K140='설정'!$B$6,K140='설정'!$B$8),SUBSTITUTE(K140,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G140)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G140)),"화목","반")),K140)))</f>
         <v/>
       </c>
       <c r="P140" s="30">
@@ -31742,7 +31742,7 @@
       <c r="M141" s="7" t="n"/>
       <c r="N141" s="7" t="n"/>
       <c r="O141" s="27">
-        <f>IF(M141&lt;&gt;"",M141,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K141&lt;&gt;""),'설정'!$B$10,IF(OR(K141='설정'!$B$6,K141='설정'!$B$8),SUBSTITUTE(K141,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G141)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G141)),"화목","반")),K141)))</f>
+        <f>IF(M141&lt;&gt;"",M141,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K141&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K141="","미응시",SUBSTITUTE(K141,"반",""))&amp;")",IF(OR(K141='설정'!$B$6,K141='설정'!$B$8),SUBSTITUTE(K141,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G141)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G141)),"화목","반")),K141)))</f>
         <v/>
       </c>
       <c r="P141" s="30">
@@ -31805,7 +31805,7 @@
       <c r="M142" s="7" t="n"/>
       <c r="N142" s="7" t="n"/>
       <c r="O142" s="27">
-        <f>IF(M142&lt;&gt;"",M142,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K142&lt;&gt;""),'설정'!$B$10,IF(OR(K142='설정'!$B$6,K142='설정'!$B$8),SUBSTITUTE(K142,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G142)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G142)),"화목","반")),K142)))</f>
+        <f>IF(M142&lt;&gt;"",M142,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K142&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K142="","미응시",SUBSTITUTE(K142,"반",""))&amp;")",IF(OR(K142='설정'!$B$6,K142='설정'!$B$8),SUBSTITUTE(K142,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G142)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G142)),"화목","반")),K142)))</f>
         <v/>
       </c>
       <c r="P142" s="30">
@@ -31868,7 +31868,7 @@
       <c r="M143" s="7" t="n"/>
       <c r="N143" s="7" t="n"/>
       <c r="O143" s="27">
-        <f>IF(M143&lt;&gt;"",M143,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K143&lt;&gt;""),'설정'!$B$10,IF(OR(K143='설정'!$B$6,K143='설정'!$B$8),SUBSTITUTE(K143,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G143)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G143)),"화목","반")),K143)))</f>
+        <f>IF(M143&lt;&gt;"",M143,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K143&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K143="","미응시",SUBSTITUTE(K143,"반",""))&amp;")",IF(OR(K143='설정'!$B$6,K143='설정'!$B$8),SUBSTITUTE(K143,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G143)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G143)),"화목","반")),K143)))</f>
         <v/>
       </c>
       <c r="P143" s="30">
@@ -31931,7 +31931,7 @@
       <c r="M144" s="7" t="n"/>
       <c r="N144" s="7" t="n"/>
       <c r="O144" s="27">
-        <f>IF(M144&lt;&gt;"",M144,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K144&lt;&gt;""),'설정'!$B$10,IF(OR(K144='설정'!$B$6,K144='설정'!$B$8),SUBSTITUTE(K144,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G144)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G144)),"화목","반")),K144)))</f>
+        <f>IF(M144&lt;&gt;"",M144,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K144&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K144="","미응시",SUBSTITUTE(K144,"반",""))&amp;")",IF(OR(K144='설정'!$B$6,K144='설정'!$B$8),SUBSTITUTE(K144,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G144)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G144)),"화목","반")),K144)))</f>
         <v/>
       </c>
       <c r="P144" s="30">
@@ -31994,7 +31994,7 @@
       <c r="M145" s="7" t="n"/>
       <c r="N145" s="7" t="n"/>
       <c r="O145" s="27">
-        <f>IF(M145&lt;&gt;"",M145,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K145&lt;&gt;""),'설정'!$B$10,IF(OR(K145='설정'!$B$6,K145='설정'!$B$8),SUBSTITUTE(K145,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G145)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G145)),"화목","반")),K145)))</f>
+        <f>IF(M145&lt;&gt;"",M145,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K145&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K145="","미응시",SUBSTITUTE(K145,"반",""))&amp;")",IF(OR(K145='설정'!$B$6,K145='설정'!$B$8),SUBSTITUTE(K145,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G145)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G145)),"화목","반")),K145)))</f>
         <v/>
       </c>
       <c r="P145" s="30">
@@ -32057,7 +32057,7 @@
       <c r="M146" s="7" t="n"/>
       <c r="N146" s="7" t="n"/>
       <c r="O146" s="27">
-        <f>IF(M146&lt;&gt;"",M146,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K146&lt;&gt;""),'설정'!$B$10,IF(OR(K146='설정'!$B$6,K146='설정'!$B$8),SUBSTITUTE(K146,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G146)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G146)),"화목","반")),K146)))</f>
+        <f>IF(M146&lt;&gt;"",M146,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K146&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K146="","미응시",SUBSTITUTE(K146,"반",""))&amp;")",IF(OR(K146='설정'!$B$6,K146='설정'!$B$8),SUBSTITUTE(K146,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G146)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G146)),"화목","반")),K146)))</f>
         <v/>
       </c>
       <c r="P146" s="30">
@@ -32120,7 +32120,7 @@
       <c r="M147" s="7" t="n"/>
       <c r="N147" s="7" t="n"/>
       <c r="O147" s="27">
-        <f>IF(M147&lt;&gt;"",M147,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K147&lt;&gt;""),'설정'!$B$10,IF(OR(K147='설정'!$B$6,K147='설정'!$B$8),SUBSTITUTE(K147,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G147)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G147)),"화목","반")),K147)))</f>
+        <f>IF(M147&lt;&gt;"",M147,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K147&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K147="","미응시",SUBSTITUTE(K147,"반",""))&amp;")",IF(OR(K147='설정'!$B$6,K147='설정'!$B$8),SUBSTITUTE(K147,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G147)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G147)),"화목","반")),K147)))</f>
         <v/>
       </c>
       <c r="P147" s="30">
@@ -32183,7 +32183,7 @@
       <c r="M148" s="7" t="n"/>
       <c r="N148" s="7" t="n"/>
       <c r="O148" s="27">
-        <f>IF(M148&lt;&gt;"",M148,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K148&lt;&gt;""),'설정'!$B$10,IF(OR(K148='설정'!$B$6,K148='설정'!$B$8),SUBSTITUTE(K148,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G148)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G148)),"화목","반")),K148)))</f>
+        <f>IF(M148&lt;&gt;"",M148,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K148&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K148="","미응시",SUBSTITUTE(K148,"반",""))&amp;")",IF(OR(K148='설정'!$B$6,K148='설정'!$B$8),SUBSTITUTE(K148,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G148)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G148)),"화목","반")),K148)))</f>
         <v/>
       </c>
       <c r="P148" s="30">
@@ -32246,7 +32246,7 @@
       <c r="M149" s="7" t="n"/>
       <c r="N149" s="7" t="n"/>
       <c r="O149" s="27">
-        <f>IF(M149&lt;&gt;"",M149,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K149&lt;&gt;""),'설정'!$B$10,IF(OR(K149='설정'!$B$6,K149='설정'!$B$8),SUBSTITUTE(K149,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G149)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G149)),"화목","반")),K149)))</f>
+        <f>IF(M149&lt;&gt;"",M149,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K149&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K149="","미응시",SUBSTITUTE(K149,"반",""))&amp;")",IF(OR(K149='설정'!$B$6,K149='설정'!$B$8),SUBSTITUTE(K149,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G149)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G149)),"화목","반")),K149)))</f>
         <v/>
       </c>
       <c r="P149" s="30">
@@ -32309,7 +32309,7 @@
       <c r="M150" s="7" t="n"/>
       <c r="N150" s="7" t="n"/>
       <c r="O150" s="27">
-        <f>IF(M150&lt;&gt;"",M150,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K150&lt;&gt;""),'설정'!$B$10,IF(OR(K150='설정'!$B$6,K150='설정'!$B$8),SUBSTITUTE(K150,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G150)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G150)),"화목","반")),K150)))</f>
+        <f>IF(M150&lt;&gt;"",M150,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K150&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K150="","미응시",SUBSTITUTE(K150,"반",""))&amp;")",IF(OR(K150='설정'!$B$6,K150='설정'!$B$8),SUBSTITUTE(K150,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G150)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G150)),"화목","반")),K150)))</f>
         <v/>
       </c>
       <c r="P150" s="30">
@@ -32372,7 +32372,7 @@
       <c r="M151" s="7" t="n"/>
       <c r="N151" s="7" t="n"/>
       <c r="O151" s="27">
-        <f>IF(M151&lt;&gt;"",M151,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K151&lt;&gt;""),'설정'!$B$10,IF(OR(K151='설정'!$B$6,K151='설정'!$B$8),SUBSTITUTE(K151,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G151)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G151)),"화목","반")),K151)))</f>
+        <f>IF(M151&lt;&gt;"",M151,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K151&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K151="","미응시",SUBSTITUTE(K151,"반",""))&amp;")",IF(OR(K151='설정'!$B$6,K151='설정'!$B$8),SUBSTITUTE(K151,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G151)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G151)),"화목","반")),K151)))</f>
         <v/>
       </c>
       <c r="P151" s="30">
@@ -32435,7 +32435,7 @@
       <c r="M152" s="7" t="n"/>
       <c r="N152" s="7" t="n"/>
       <c r="O152" s="27">
-        <f>IF(M152&lt;&gt;"",M152,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K152&lt;&gt;""),'설정'!$B$10,IF(OR(K152='설정'!$B$6,K152='설정'!$B$8),SUBSTITUTE(K152,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G152)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G152)),"화목","반")),K152)))</f>
+        <f>IF(M152&lt;&gt;"",M152,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K152&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K152="","미응시",SUBSTITUTE(K152,"반",""))&amp;")",IF(OR(K152='설정'!$B$6,K152='설정'!$B$8),SUBSTITUTE(K152,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G152)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G152)),"화목","반")),K152)))</f>
         <v/>
       </c>
       <c r="P152" s="30">
@@ -32498,7 +32498,7 @@
       <c r="M153" s="7" t="n"/>
       <c r="N153" s="7" t="n"/>
       <c r="O153" s="27">
-        <f>IF(M153&lt;&gt;"",M153,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K153&lt;&gt;""),'설정'!$B$10,IF(OR(K153='설정'!$B$6,K153='설정'!$B$8),SUBSTITUTE(K153,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G153)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G153)),"화목","반")),K153)))</f>
+        <f>IF(M153&lt;&gt;"",M153,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K153&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K153="","미응시",SUBSTITUTE(K153,"반",""))&amp;")",IF(OR(K153='설정'!$B$6,K153='설정'!$B$8),SUBSTITUTE(K153,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G153)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G153)),"화목","반")),K153)))</f>
         <v/>
       </c>
       <c r="P153" s="30">
@@ -32561,7 +32561,7 @@
       <c r="M154" s="7" t="n"/>
       <c r="N154" s="7" t="n"/>
       <c r="O154" s="27">
-        <f>IF(M154&lt;&gt;"",M154,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K154&lt;&gt;""),'설정'!$B$10,IF(OR(K154='설정'!$B$6,K154='설정'!$B$8),SUBSTITUTE(K154,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G154)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G154)),"화목","반")),K154)))</f>
+        <f>IF(M154&lt;&gt;"",M154,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K154&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K154="","미응시",SUBSTITUTE(K154,"반",""))&amp;")",IF(OR(K154='설정'!$B$6,K154='설정'!$B$8),SUBSTITUTE(K154,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G154)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G154)),"화목","반")),K154)))</f>
         <v/>
       </c>
       <c r="P154" s="30">
@@ -32624,7 +32624,7 @@
       <c r="M155" s="7" t="n"/>
       <c r="N155" s="7" t="n"/>
       <c r="O155" s="27">
-        <f>IF(M155&lt;&gt;"",M155,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K155&lt;&gt;""),'설정'!$B$10,IF(OR(K155='설정'!$B$6,K155='설정'!$B$8),SUBSTITUTE(K155,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G155)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G155)),"화목","반")),K155)))</f>
+        <f>IF(M155&lt;&gt;"",M155,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K155&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K155="","미응시",SUBSTITUTE(K155,"반",""))&amp;")",IF(OR(K155='설정'!$B$6,K155='설정'!$B$8),SUBSTITUTE(K155,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G155)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G155)),"화목","반")),K155)))</f>
         <v/>
       </c>
       <c r="P155" s="30">
@@ -32687,7 +32687,7 @@
       <c r="M156" s="7" t="n"/>
       <c r="N156" s="7" t="n"/>
       <c r="O156" s="27">
-        <f>IF(M156&lt;&gt;"",M156,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K156&lt;&gt;""),'설정'!$B$10,IF(OR(K156='설정'!$B$6,K156='설정'!$B$8),SUBSTITUTE(K156,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G156)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G156)),"화목","반")),K156)))</f>
+        <f>IF(M156&lt;&gt;"",M156,IF(AND('설정'!$B$10&lt;&gt;"",'학생명단'!K156&lt;&gt;""),'설정'!$B$10&amp;"("&amp;IF(K156="","미응시",SUBSTITUTE(K156,"반",""))&amp;")",IF(OR(K156='설정'!$B$6,K156='설정'!$B$8),SUBSTITUTE(K156,"반","")&amp;IF(ISNUMBER(SEARCH("월",'학생명단'!G156)),"월금",IF(ISNUMBER(SEARCH("화",'학생명단'!G156)),"화목","반")),K156)))</f>
         <v/>
       </c>
       <c r="P156" s="30">

--- a/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
+++ b/반편성고사/예비고1_반편성고사_채점_반배정.xlsx
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>자사고·특목고 진학 예정 학생을 위한 반으로, 고교 내신과 심화 문항 해결력을 함께 준비합니다.</t>
+          <t>자사고·특목고 진학 예정 학생을 위한 TF집중속진반(TF11·TF12, 12월 28일 개강)으로, 1·2월 공통수학을 집중속진 과정으로 학습합니다.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
